--- a/tools/itinerary.xlsx
+++ b/tools/itinerary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jitwei/Library/Mobile Documents/com~apple~CloudDocs/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2406BDD5-9AE0-784C-A160-D80875152CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A39598-DE4D-6B4F-9112-248D58D61379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-6080" yWindow="-21000" windowWidth="38400" windowHeight="21000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="17020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="987">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="1014">
   <si>
     <r>
       <rPr>
@@ -7078,28 +7078,6 @@
     <t>Logistics</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Day 1 — Sun 15 Nov  ·  Arrival → Hangzhou · Arrive PVG 14:15 (MH388) · overnight Conrad Hangzhou </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>康莱德</t>
-    </r>
-  </si>
-  <si>
     <t>Day 1
 Sun 15 Nov</t>
   </si>
@@ -7203,41 +7181,6 @@
     </r>
   </si>
   <si>
-    <t>15:15–15:35</t>
-  </si>
-  <si>
-    <t>SIM/eSIM &amp; mobile pay setup</t>
-  </si>
-  <si>
-    <t>China SIM/eSIM; top up Alipay/WeChat; add foreign card.</t>
-  </si>
-  <si>
-    <t>~20 min</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">PVG T2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>到达层</t>
-    </r>
-  </si>
-  <si>
-    <t>15:35–16:40</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -7258,9 +7201,6 @@
     </r>
   </si>
   <si>
-    <t>Metro L2 (~60–75 min) or DiDi (~50–70 min).</t>
-  </si>
-  <si>
     <t>Metro L2</t>
   </si>
   <si>
@@ -7670,48 +7610,6 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>康莱德</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Day 2 — Mon 16 Nov  ·  Hangzhou West Lake </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">西湖 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">· granular loop, tea &amp; foliage · overnight Conrad </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -8149,9 +8047,6 @@
     </r>
   </si>
   <si>
-    <t>12:15–12:45</t>
-  </si>
-  <si>
     <t>Coffee — % Arabica lakeside</t>
   </si>
   <si>
@@ -8161,9 +8056,6 @@
     <t>% Arabica</t>
   </si>
   <si>
-    <t>12:45–14:00</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -8231,9 +8123,6 @@
     </r>
   </si>
   <si>
-    <t>14:15–15:00</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -8263,9 +8152,6 @@
     <t>西湖区杨公堤</t>
   </si>
   <si>
-    <t>15:00–16:00</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -8321,9 +8207,6 @@
     </r>
   </si>
   <si>
-    <t>16:15–17:45</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -8379,171 +8262,6 @@
     <t>西湖区龙井村</t>
   </si>
   <si>
-    <t>18:15–19:15</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Dinner — Grandma's Kitchen </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">外婆家 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>OR ★</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">宫宴 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>banquet</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Home-style near Hefang; OR the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">宫宴 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Song banquet (~2–3h, Hanfu, 5.0★, ¥300+, book ahead, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>曙光路</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>122</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>号</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>).</t>
-    </r>
-  </si>
-  <si>
-    <t>¥60–100 / ¥300+</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">上城区河坊街 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>西湖区曙光路</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>122</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>号</t>
-    </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -8712,28 +8430,6 @@
         <family val="2"/>
       </rPr>
       <t>(DiDi ~20 min)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Day 3 — Tue 17 Nov  ·  Hangzhou Culture &amp; Canal · NW hills → centre → north · overnight Conrad </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>康莱德</t>
     </r>
   </si>
   <si>
@@ -9179,35 +8875,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">③ Metro L5 north. Canal museum &amp; Xiaohe Direct St </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>小河直街</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
     <t>Metro L5</t>
   </si>
   <si>
@@ -9249,9 +8916,6 @@
     </r>
   </si>
   <si>
-    <t>17:45–18:30</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -9272,9 +8936,6 @@
     </r>
   </si>
   <si>
-    <t>Short cruise past illuminated bridges.</t>
-  </si>
-  <si>
     <t>Optional</t>
   </si>
   <si>
@@ -9284,35 +8945,9 @@
     <t>18:30–19:45</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Dinner — canal-side </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>小河直街</t>
-    </r>
-  </si>
-  <si>
-    <t>Restored canal-warehouse district; cafés &amp; bars.</t>
-  </si>
-  <si>
     <t>Dinner</t>
   </si>
   <si>
-    <t>19:45</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -9351,9 +8986,6 @@
     </r>
   </si>
   <si>
-    <t>Metro L5→L4 or DiDi.</t>
-  </si>
-  <si>
     <t>Alt</t>
   </si>
   <si>
@@ -9458,38 +9090,6 @@
         <family val="2"/>
       </rPr>
       <t>号</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Day 4 — Wed 18 Nov  ·  Hangzhou → Nanjing · to Ritz-Carlton </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">丽思 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Xinjiekou) · Confucius Temple evening</t>
     </r>
   </si>
   <si>
@@ -10414,88 +10014,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Day 5 — Thu 19 Nov  ·  Nanjing History · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">钟山 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">east cluster → </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>玄武</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鸡鸣寺 → </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">return to Xinjiekou · overnight Ritz </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>丽思</t>
-    </r>
-  </si>
-  <si>
     <t>Day 5
 Thu 19 Nov</t>
   </si>
@@ -11596,38 +11114,6 @@
     <t>鼓楼区颐和路</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Day 6 — Fri 20 Nov  ·  Nanjing → Suzhou · to Ritz-Carlton </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">丽思 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Gusu west) · gardens &amp; Pingjiang evening</t>
-    </r>
-  </si>
-  <si>
     <t>Day 6
 Fri 20 Nov</t>
   </si>
@@ -12571,106 +12057,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Optional: Eslite </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>诚品书店</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">If detouring to Jinji Lake </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">金鸡湖 — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>the landmark Eslite bookstore.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>工业园区月廊街</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>号</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Day 7 — Sat 21 Nov  ·  Suzhou Gardens &amp; Canals · west gardens AT THE HOTEL → centre → south · overnight Ritz </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>丽思</t>
-    </r>
-  </si>
-  <si>
     <t>Day 7
 Sat 21 Nov</t>
   </si>
@@ -13671,55 +13057,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">🍁 SEASONAL swap: Tianping Mountain </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>天平山红枫节</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Half-day to Mudu </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">木渎 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>for PEAK red maples. ¥30.</t>
-    </r>
-  </si>
-  <si>
     <t>吴中区木渎镇天平山</t>
   </si>
   <si>
@@ -14516,20 +13853,551 @@
     <t>西湖区北山路82号 (岳湖景区, 岳庙对面)</t>
   </si>
   <si>
-    <t>18:50–19:30</t>
-  </si>
-  <si>
     <t>Quick browse — head to 岳湖 by 19:00 for the show.</t>
   </si>
   <si>
     <t>20:45–21:30</t>
+  </si>
+  <si>
+    <t>Optional: North Temple Pagoda 北寺塔 &amp; Taohuawu 桃花坞 / Changmen 阊门</t>
+  </si>
+  <si>
+    <t>Suzhou's tallest ancient pagoda (76m, climbable city view) + the 桃花坞 woodblock-print quarter &amp; 阊门 gate. All on the NW side between 虎丘 and the old town — a natural add on the way to lunch.</t>
+  </si>
+  <si>
+    <t>Opt · ¥25</t>
+  </si>
+  <si>
+    <t>姑苏区人民路1918号 (北寺塔)</t>
+  </si>
+  <si>
+    <t>📚 Optional: Momi/猫的天空之城 &amp; Slow Bookstore 慢书房</t>
+  </si>
+  <si>
+    <t>On 平江路 itself — 猫空 concept bookstore (originated in Suzhou; 'mail a postcard to the future') + indie 慢书房. Zero detour from the Pingjiang walk.</t>
+  </si>
+  <si>
+    <t>Optional alt: Nanjing Eye 南京眼 &amp; Yuzui Wetland 鱼嘴湿地</t>
+  </si>
+  <si>
+    <t>Cable-stayed pedestrian bridge + 'Nanjing's Santorini' sunset pier, 建邺/河西 west. Very viral 打卡. Far west — best SWAPPED IN for the 玄武湖 sunset block, not added.</t>
+  </si>
+  <si>
+    <t>建邺区江山大街 (南京眼/鱼嘴)</t>
+  </si>
+  <si>
+    <t>🆕 Optional: Xinanli 熙南里 &amp; Pingshi St 评事街</t>
+  </si>
+  <si>
+    <t>Restored Qing block just S of 新街口 — 甘熙故居, indie shops, night market &amp; 打卡 lanes. Much closer to the Ritz than 老门东.</t>
+  </si>
+  <si>
+    <t>秦淮区升州路 (熙南里)</t>
+  </si>
+  <si>
+    <t>🆕 TRENDY alt: Yuniaoji 玉鸟集 &amp; Da Wuding 大屋顶 (良渚)</t>
+  </si>
+  <si>
+    <t>Hangzhou's art ceiling' — Tadao Ando 安藤忠雄 大屋顶 + 柳亦春 大谷仓 with 单向空间 bookstore; 128 boutiques, 85% independent. Metro L2 to 良渚 — needs a half-day, so swap for 西溪湿地.</t>
+  </si>
+  <si>
+    <t>Optional alt · 余杭</t>
+  </si>
+  <si>
+    <t>余杭区良渚文化村玉鸟街</t>
+  </si>
+  <si>
+    <t>Optional: Southern Song Imperial St 南宋御街</t>
+  </si>
+  <si>
+    <t>Runs straight into 清河坊 — the Song-dynasty imperial way, restored by 王澍. Free add-on to the walk you're already doing.</t>
+  </si>
+  <si>
+    <t>上城区中山中路 (南宋御街)</t>
+  </si>
+  <si>
+    <t>🍁 Optional: Jiuxi 九溪烟树 · Manjuelong 满觉陇 · Siyanjing 四眼井</t>
+  </si>
+  <si>
+    <t>Classic NOVEMBER foliage walks in the same SW hills as 龙井 — 九溪 maples &amp; 十八涧 stream. Peak-season 打卡; add if the tea village runs short.</t>
+  </si>
+  <si>
+    <t>西湖区九溪路 / 满觉陇路</t>
+  </si>
+  <si>
+    <t>上城区湖滨路 (in77)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Day 1 — Sun 15 Nov  ·  Arrival → Hangzhou · Arrive PVG 14:15 (MH388) · overnight Conrad Hangzhou </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>康莱德</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Day 2 — Mon 16 Nov  ·  Hangzhou West Lake </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">西湖 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· granular loop, tea &amp; foliage · overnight Conrad </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>康莱德</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Day 3 — Tue 17 Nov  ·  Hangzhou Culture &amp; Canal · NW hills → centre → north · overnight Conrad </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>康莱德</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Day 5 — Thu 19 Nov  ·  Nanjing History · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">钟山 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">east cluster → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>玄武</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鸡鸣寺 → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">return to Xinjiekou · overnight Ritz </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>丽思</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Optional: Eslite </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>诚品书店</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">If detouring to Jinji Lake </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">金鸡湖 — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>the landmark Eslite bookstore.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>工业园区月廊街</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">🍁 SEASONAL swap: Tianping Mountain </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>天平山红枫节</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Half-day to Mudu </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">木渎 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>for PEAK red maples. ¥30.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Day 4 — Wed 18 Nov  ·  Hangzhou → Nanjing · to Ritz-Carlton </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">丽思 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>(Xinjiekou) · Confucius Temple evening</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Day 6 — Fri 20 Nov  ·  Nanjing → Suzhou · to Ritz-Carlton </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">丽思 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>(Gusu west) · gardens &amp; Pingjiang evening</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Day 7 — Sat 21 Nov  ·  Suzhou Gardens &amp; Canals · west gardens AT THE HOTEL → centre → south · overnight Ritz </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>丽思</t>
+    </r>
+  </si>
+  <si>
+    <t>15:15–16:20</t>
+  </si>
+  <si>
+    <t>Metro L2 (~60–75 min) or DiDi (~50–70 min). Earlier start = comfortable buffer at Hongqiao.</t>
+  </si>
+  <si>
+    <t>🛍 SHOP: Hubin Pedestrian St 湖滨步行街 &amp; 湖滨银泰 in77</t>
+  </si>
+  <si>
+    <t>West Lake waterfront strip — musical fountain 音乐喷泉, flagship stores, Hangzhou's most-filmed 打卡 street. Directly continues from the % Arabica stop on the same road.</t>
+  </si>
+  <si>
+    <t>湖滨 · Walk</t>
+  </si>
+  <si>
+    <t>11:55–12:15</t>
+  </si>
+  <si>
+    <t>13:00–14:10</t>
+  </si>
+  <si>
+    <t>14:25–15:10</t>
+  </si>
+  <si>
+    <t>15:10–16:05</t>
+  </si>
+  <si>
+    <t>16:20–17:45</t>
+  </si>
+  <si>
+    <t>18:00–18:50</t>
+  </si>
+  <si>
+    <t>18:50–19:20</t>
+  </si>
+  <si>
+    <t>11:15–11:55</t>
+  </si>
+  <si>
+    <t>Dinner — Grandma's Kitchen 外婆家</t>
+  </si>
+  <si>
+    <t>Home-style Hangzhou near Hefang 河坊街. (宫宴 banquet moved to Day 3 — it clashes with tonight's 印象西湖 show.)</t>
+  </si>
+  <si>
+    <t>16:15–17:30</t>
+  </si>
+  <si>
+    <t>③ Metro L5 north. Canal museum &amp; Xiaohe Direct St 小河直街. Trimmed to allow transfer to 宫宴.</t>
+  </si>
+  <si>
+    <t>Short cruise past illuminated bridges. Only if you skip 宫宴 — it cannot fit before the 19:00 seating.</t>
+  </si>
+  <si>
+    <t>Opt · 运河</t>
+  </si>
+  <si>
+    <t>17:30–18:45</t>
+  </si>
+  <si>
+    <t>Transfer: Grand Canal 拱宸桥 → 宫宴 (曙光路)</t>
+  </si>
+  <si>
+    <t>DiDi ~40–45 min across town to the West Lake west side. Leave the canal by 17:30 to arrive with time for 妆造 (Hanfu hair &amp; makeup) before the seating.</t>
+  </si>
+  <si>
+    <t>DiDi ~40 min</t>
+  </si>
+  <si>
+    <t>西湖区曙光路122号</t>
+  </si>
+  <si>
+    <t>19:00–21:30</t>
+  </si>
+  <si>
+    <t>★ DINNER SHOW: 宫宴 Song Imperial Banquet</t>
+  </si>
+  <si>
+    <t>晚宴 seats 19:00 sharp; runs ~2–3h. Hanfu 妆造 add-on ~¥126 (cannot be booked alone — add to the meal). BOOK BY ~16 OCT 2026 — vendor advises 1 month ahead; sells out 1–2 weeks out. Non-cancellable; confirmed within 1 day.</t>
+  </si>
+  <si>
+    <t>¥660+ · 晚宴 19:00</t>
+  </si>
+  <si>
+    <t>DiDi ~20 min from 曙光路 back to the CBD. Pack for Nanjing 南京.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -14644,6 +14512,18 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -15076,7 +14956,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="207">
+  <cellXfs count="216">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -15522,31 +15402,7 @@
     <xf numFmtId="0" fontId="7" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -15576,6 +15432,33 @@
     <xf numFmtId="0" fontId="3" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -15603,6 +15486,42 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -15620,42 +15539,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -15687,7 +15570,31 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="24" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -15968,31 +15875,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="31.5" customHeight="1">
-      <c r="A1" s="171" t="s">
+      <c r="A1" s="172" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="171"/>
-      <c r="C1" s="171"/>
-      <c r="D1" s="171"/>
-      <c r="E1" s="171"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
     </row>
     <row r="2" spans="1:5" ht="21.75" customHeight="1">
-      <c r="A2" s="172" t="s">
+      <c r="A2" s="173" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="172"/>
-      <c r="C2" s="172"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="172"/>
+      <c r="B2" s="173"/>
+      <c r="C2" s="173"/>
+      <c r="D2" s="173"/>
+      <c r="E2" s="173"/>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1">
-      <c r="A4" s="173" t="s">
+      <c r="A4" s="174" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="173"/>
-      <c r="C4" s="173"/>
-      <c r="D4" s="173"/>
-      <c r="E4" s="173"/>
+      <c r="B4" s="174"/>
+      <c r="C4" s="174"/>
+      <c r="D4" s="174"/>
+      <c r="E4" s="174"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
@@ -16046,13 +15953,13 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1">
-      <c r="A9" s="174" t="s">
+      <c r="A9" s="175" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="174"/>
-      <c r="C9" s="174"/>
-      <c r="D9" s="174"/>
-      <c r="E9" s="174"/>
+      <c r="B9" s="175"/>
+      <c r="C9" s="175"/>
+      <c r="D9" s="175"/>
+      <c r="E9" s="175"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
@@ -16123,40 +16030,40 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1">
-      <c r="A15" s="175" t="s">
+      <c r="A15" s="176" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="175"/>
-      <c r="C15" s="175"/>
-      <c r="D15" s="175"/>
-      <c r="E15" s="175"/>
+      <c r="B15" s="176"/>
+      <c r="C15" s="176"/>
+      <c r="D15" s="176"/>
+      <c r="E15" s="176"/>
     </row>
     <row r="16" spans="1:5" ht="72" customHeight="1">
-      <c r="A16" s="169" t="s">
+      <c r="A16" s="170" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="169"/>
-      <c r="C16" s="169"/>
-      <c r="D16" s="169"/>
-      <c r="E16" s="169"/>
+      <c r="B16" s="170"/>
+      <c r="C16" s="170"/>
+      <c r="D16" s="170"/>
+      <c r="E16" s="170"/>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1">
-      <c r="A18" s="170" t="s">
+      <c r="A18" s="171" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="170"/>
-      <c r="C18" s="170"/>
-      <c r="D18" s="170"/>
-      <c r="E18" s="170"/>
+      <c r="B18" s="171"/>
+      <c r="C18" s="171"/>
+      <c r="D18" s="171"/>
+      <c r="E18" s="171"/>
     </row>
     <row r="19" spans="1:5" ht="31.5" customHeight="1">
-      <c r="A19" s="169" t="s">
+      <c r="A19" s="170" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="169"/>
-      <c r="C19" s="169"/>
-      <c r="D19" s="169"/>
-      <c r="E19" s="169"/>
+      <c r="B19" s="170"/>
+      <c r="C19" s="170"/>
+      <c r="D19" s="170"/>
+      <c r="E19" s="170"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -16179,7 +16086,7 @@
   <sheetPr>
     <tabColor rgb="FFC55A11"/>
   </sheetPr>
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F133"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -16191,24 +16098,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="161" t="s">
         <v>396</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
-      <c r="E1" s="152"/>
-      <c r="F1" s="153"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="162"/>
+      <c r="E1" s="162"/>
+      <c r="F1" s="163"/>
     </row>
     <row r="2" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A2" s="154" t="s">
+      <c r="A2" s="164" t="s">
         <v>397</v>
       </c>
-      <c r="B2" s="155"/>
-      <c r="C2" s="155"/>
-      <c r="D2" s="155"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="156"/>
+      <c r="B2" s="165"/>
+      <c r="C2" s="165"/>
+      <c r="D2" s="165"/>
+      <c r="E2" s="165"/>
+      <c r="F2" s="166"/>
     </row>
     <row r="3" spans="1:6" ht="19.5" customHeight="1">
       <c r="A3" s="77" t="s">
@@ -16230,378 +16137,378 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A4" s="157" t="s">
-        <v>403</v>
-      </c>
-      <c r="B4" s="158"/>
-      <c r="C4" s="158"/>
-      <c r="D4" s="158"/>
-      <c r="E4" s="158"/>
-      <c r="F4" s="159"/>
+    <row r="4" spans="1:6" ht="30" customHeight="1">
+      <c r="A4" s="167" t="s">
+        <v>973</v>
+      </c>
+      <c r="B4" s="168"/>
+      <c r="C4" s="168"/>
+      <c r="D4" s="168"/>
+      <c r="E4" s="168"/>
+      <c r="F4" s="169"/>
     </row>
     <row r="5" spans="1:6" ht="25.5" customHeight="1">
       <c r="A5" s="98" t="s">
+        <v>403</v>
+      </c>
+      <c r="B5" s="53" t="s">
         <v>404</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="C5" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="86" t="s">
         <v>408</v>
-      </c>
-      <c r="F5" s="86" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="25.5" customHeight="1">
       <c r="A6" s="99" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B6" s="54" t="s">
+        <v>409</v>
+      </c>
+      <c r="C6" s="15" t="s">
         <v>410</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="D6" s="15" t="s">
         <v>411</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="E6" s="15" t="s">
         <v>412</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="F6" s="113" t="s">
         <v>413</v>
       </c>
-      <c r="F6" s="113" t="s">
+    </row>
+    <row r="7" spans="1:6" ht="30" customHeight="1">
+      <c r="A7" s="100" t="s">
+        <v>403</v>
+      </c>
+      <c r="B7" s="213" t="s">
+        <v>985</v>
+      </c>
+      <c r="C7" s="50" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="30" customHeight="1">
-      <c r="A7" s="98" t="s">
-        <v>404</v>
-      </c>
-      <c r="B7" s="53" t="s">
+      <c r="D7" s="50" t="s">
+        <v>986</v>
+      </c>
+      <c r="E7" s="50" t="s">
         <v>415</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="F7" s="115" t="s">
         <v>416</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="F7" s="114" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="25.5" customHeight="1">
       <c r="A8" s="100" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B8" s="55" t="s">
+        <v>417</v>
+      </c>
+      <c r="C8" s="50" t="s">
+        <v>418</v>
+      </c>
+      <c r="D8" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="E8" s="50" t="s">
         <v>420</v>
       </c>
-      <c r="C8" s="50" t="s">
+      <c r="F8" s="115" t="s">
         <v>421</v>
-      </c>
-      <c r="D8" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="E8" s="50" t="s">
-        <v>423</v>
-      </c>
-      <c r="F8" s="115" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="25.5" customHeight="1">
       <c r="A9" s="100" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B9" s="55" t="s">
+        <v>422</v>
+      </c>
+      <c r="C9" s="50" t="s">
+        <v>423</v>
+      </c>
+      <c r="D9" s="50" t="s">
+        <v>424</v>
+      </c>
+      <c r="E9" s="50" t="s">
         <v>425</v>
       </c>
-      <c r="C9" s="50" t="s">
+      <c r="F9" s="115" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="30" customHeight="1">
+      <c r="A10" s="101" t="s">
+        <v>403</v>
+      </c>
+      <c r="B10" s="56" t="s">
         <v>426</v>
       </c>
-      <c r="D9" s="50" t="s">
+      <c r="C10" s="10" t="s">
         <v>427</v>
       </c>
-      <c r="E9" s="50" t="s">
+      <c r="D10" s="10" t="s">
         <v>428</v>
       </c>
-      <c r="F9" s="115" t="s">
+      <c r="E10" s="10" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="30" customHeight="1">
-      <c r="A10" s="100" t="s">
-        <v>404</v>
-      </c>
-      <c r="B10" s="55" t="s">
+      <c r="F10" s="116" t="s">
         <v>430</v>
       </c>
-      <c r="C10" s="50" t="s">
+    </row>
+    <row r="11" spans="1:6" ht="30" customHeight="1">
+      <c r="A11" s="102" t="s">
+        <v>403</v>
+      </c>
+      <c r="B11" s="57" t="s">
         <v>431</v>
       </c>
-      <c r="D10" s="50" t="s">
+      <c r="C11" s="33" t="s">
         <v>432</v>
       </c>
-      <c r="E10" s="50" t="s">
+      <c r="D11" s="33" t="s">
         <v>433</v>
       </c>
-      <c r="F10" s="115" t="s">
+      <c r="E11" s="35" t="s">
+        <v>434</v>
+      </c>
+      <c r="F11" s="117" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="30" customHeight="1">
+      <c r="A12" s="103" t="s">
+        <v>403</v>
+      </c>
+      <c r="B12" s="58" t="s">
+        <v>435</v>
+      </c>
+      <c r="C12" s="39" t="s">
+        <v>436</v>
+      </c>
+      <c r="D12" s="39" t="s">
+        <v>437</v>
+      </c>
+      <c r="E12" s="41" t="s">
+        <v>438</v>
+      </c>
+      <c r="F12" s="118" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="30" customHeight="1">
+      <c r="A13" s="101" t="s">
+        <v>403</v>
+      </c>
+      <c r="B13" s="56" t="s">
+        <v>440</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="F13" s="116" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A14" s="167" t="s">
+        <v>974</v>
+      </c>
+      <c r="B14" s="168"/>
+      <c r="C14" s="168"/>
+      <c r="D14" s="168"/>
+      <c r="E14" s="168"/>
+      <c r="F14" s="169"/>
+    </row>
+    <row r="15" spans="1:6" ht="30" customHeight="1">
+      <c r="A15" s="101" t="s">
+        <v>444</v>
+      </c>
+      <c r="B15" s="56" t="s">
+        <v>445</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="116" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="30" customHeight="1">
-      <c r="A11" s="101" t="s">
-        <v>404</v>
-      </c>
-      <c r="B11" s="56" t="s">
-        <v>434</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>435</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>436</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>437</v>
-      </c>
-      <c r="F11" s="116" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="30" customHeight="1">
-      <c r="A12" s="102" t="s">
-        <v>404</v>
-      </c>
-      <c r="B12" s="57" t="s">
-        <v>439</v>
-      </c>
-      <c r="C12" s="33" t="s">
-        <v>440</v>
-      </c>
-      <c r="D12" s="33" t="s">
-        <v>441</v>
-      </c>
-      <c r="E12" s="35" t="s">
-        <v>442</v>
-      </c>
-      <c r="F12" s="117" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="30" customHeight="1">
-      <c r="A13" s="103" t="s">
-        <v>404</v>
-      </c>
-      <c r="B13" s="58" t="s">
-        <v>443</v>
-      </c>
-      <c r="C13" s="39" t="s">
+    <row r="16" spans="1:6" ht="30" customHeight="1">
+      <c r="A16" s="104" t="s">
         <v>444</v>
       </c>
-      <c r="D13" s="39" t="s">
-        <v>445</v>
-      </c>
-      <c r="E13" s="41" t="s">
-        <v>446</v>
-      </c>
-      <c r="F13" s="118" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A14" s="101" t="s">
-        <v>404</v>
-      </c>
-      <c r="B14" s="56" t="s">
+      <c r="B16" s="59" t="s">
         <v>448</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C16" s="47" t="s">
         <v>449</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D16" s="47" t="s">
         <v>450</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E16" s="47" t="s">
         <v>451</v>
       </c>
-      <c r="F14" s="116" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A15" s="157" t="s">
+      <c r="F16" s="119" t="s">
         <v>452</v>
       </c>
-      <c r="B15" s="158"/>
-      <c r="C15" s="158"/>
-      <c r="D15" s="158"/>
-      <c r="E15" s="158"/>
-      <c r="F15" s="159"/>
-    </row>
-    <row r="16" spans="1:6" ht="30" customHeight="1">
-      <c r="A16" s="101" t="s">
+    </row>
+    <row r="17" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A17" s="105" t="s">
+        <v>444</v>
+      </c>
+      <c r="B17" s="60" t="s">
         <v>453</v>
       </c>
-      <c r="B16" s="56" t="s">
+      <c r="C17" s="61" t="s">
         <v>454</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="D17" s="61" t="s">
         <v>455</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="E17" s="61" t="s">
+        <v>451</v>
+      </c>
+      <c r="F17" s="120" t="s">
         <v>456</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F16" s="116" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A17" s="104" t="s">
-        <v>453</v>
-      </c>
-      <c r="B17" s="59" t="s">
+    </row>
+    <row r="18" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A18" s="104" t="s">
+        <v>444</v>
+      </c>
+      <c r="B18" s="59" t="s">
         <v>457</v>
       </c>
-      <c r="C17" s="47" t="s">
+      <c r="C18" s="47" t="s">
         <v>458</v>
       </c>
-      <c r="D17" s="47" t="s">
+      <c r="D18" s="47" t="s">
         <v>459</v>
       </c>
-      <c r="E17" s="47" t="s">
+      <c r="E18" s="47" t="s">
+        <v>451</v>
+      </c>
+      <c r="F18" s="119" t="s">
         <v>460</v>
       </c>
-      <c r="F17" s="119" t="s">
+    </row>
+    <row r="19" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A19" s="105" t="s">
+        <v>444</v>
+      </c>
+      <c r="B19" s="60" t="s">
         <v>461</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A18" s="105" t="s">
-        <v>453</v>
-      </c>
-      <c r="B18" s="60" t="s">
+      <c r="C19" s="61" t="s">
         <v>462</v>
       </c>
-      <c r="C18" s="61" t="s">
+      <c r="D19" s="61" t="s">
         <v>463</v>
       </c>
-      <c r="D18" s="61" t="s">
+      <c r="E19" s="61" t="s">
         <v>464</v>
       </c>
-      <c r="E18" s="61" t="s">
-        <v>460</v>
-      </c>
-      <c r="F18" s="120" t="s">
+      <c r="F19" s="120" t="s">
         <v>465</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A19" s="104" t="s">
-        <v>453</v>
-      </c>
-      <c r="B19" s="59" t="s">
-        <v>466</v>
-      </c>
-      <c r="C19" s="47" t="s">
-        <v>467</v>
-      </c>
-      <c r="D19" s="47" t="s">
-        <v>468</v>
-      </c>
-      <c r="E19" s="47" t="s">
-        <v>460</v>
-      </c>
-      <c r="F19" s="119" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="25.5" customHeight="1">
       <c r="A20" s="105" t="s">
-        <v>453</v>
-      </c>
-      <c r="B20" s="60" t="s">
+        <v>444</v>
+      </c>
+      <c r="B20" s="207" t="s">
+        <v>997</v>
+      </c>
+      <c r="C20" s="61" t="s">
+        <v>467</v>
+      </c>
+      <c r="D20" s="61" t="s">
+        <v>468</v>
+      </c>
+      <c r="E20" s="61" t="s">
+        <v>469</v>
+      </c>
+      <c r="F20" s="120" t="s">
         <v>470</v>
       </c>
-      <c r="C20" s="61" t="s">
+    </row>
+    <row r="21" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A21" s="106" t="s">
+        <v>444</v>
+      </c>
+      <c r="B21" s="212" t="s">
+        <v>990</v>
+      </c>
+      <c r="C21" s="20" t="s">
         <v>471</v>
       </c>
-      <c r="D20" s="61" t="s">
+      <c r="D21" s="20" t="s">
         <v>472</v>
       </c>
-      <c r="E20" s="61" t="s">
+      <c r="E21" s="20" t="s">
         <v>473</v>
       </c>
-      <c r="F20" s="120" t="s">
+      <c r="F21" s="121" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="42" customHeight="1">
+      <c r="A22" s="106" t="s">
+        <v>444</v>
+      </c>
+      <c r="B22" s="212" t="s">
+        <v>562</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>987</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>988</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>989</v>
+      </c>
+      <c r="F22" s="121" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="42" customHeight="1">
+      <c r="A23" s="98" t="s">
+        <v>444</v>
+      </c>
+      <c r="B23" s="214" t="s">
+        <v>991</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A21" s="105" t="s">
-        <v>453</v>
-      </c>
-      <c r="B21" s="60" t="s">
+      <c r="D23" s="5" t="s">
         <v>475</v>
-      </c>
-      <c r="C21" s="61" t="s">
-        <v>476</v>
-      </c>
-      <c r="D21" s="61" t="s">
-        <v>477</v>
-      </c>
-      <c r="E21" s="61" t="s">
-        <v>478</v>
-      </c>
-      <c r="F21" s="120" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A22" s="106" t="s">
-        <v>453</v>
-      </c>
-      <c r="B22" s="63" t="s">
-        <v>480</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>481</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>482</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>483</v>
-      </c>
-      <c r="F22" s="121" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A23" s="98" t="s">
-        <v>453</v>
-      </c>
-      <c r="B23" s="53" t="s">
-        <v>484</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>486</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>57</v>
@@ -16612,1988 +16519,2148 @@
     </row>
     <row r="24" spans="1:6" ht="25.5" customHeight="1">
       <c r="A24" s="105" t="s">
-        <v>453</v>
-      </c>
-      <c r="B24" s="60" t="s">
-        <v>487</v>
+        <v>444</v>
+      </c>
+      <c r="B24" s="207" t="s">
+        <v>992</v>
       </c>
       <c r="C24" s="61" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="D24" s="61" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="E24" s="61" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="F24" s="120" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="25.5" customHeight="1">
       <c r="A25" s="105" t="s">
-        <v>453</v>
-      </c>
-      <c r="B25" s="60" t="s">
-        <v>492</v>
+        <v>444</v>
+      </c>
+      <c r="B25" s="207" t="s">
+        <v>993</v>
       </c>
       <c r="C25" s="61" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="D25" s="61" t="s">
-        <v>494</v>
+        <v>481</v>
       </c>
       <c r="E25" s="61" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
       <c r="F25" s="120" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="25.5" customHeight="1">
       <c r="A26" s="105" t="s">
-        <v>453</v>
-      </c>
-      <c r="B26" s="60" t="s">
+        <v>444</v>
+      </c>
+      <c r="B26" s="207" t="s">
+        <v>994</v>
+      </c>
+      <c r="C26" s="61" t="s">
+        <v>484</v>
+      </c>
+      <c r="D26" s="61" t="s">
+        <v>485</v>
+      </c>
+      <c r="E26" s="61" t="s">
+        <v>486</v>
+      </c>
+      <c r="F26" s="120" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="42" customHeight="1">
+      <c r="A27" s="105" t="s">
+        <v>444</v>
+      </c>
+      <c r="B27" s="207" t="s">
+        <v>707</v>
+      </c>
+      <c r="C27" s="61" t="s">
+        <v>969</v>
+      </c>
+      <c r="D27" s="61" t="s">
+        <v>970</v>
+      </c>
+      <c r="E27" s="61" t="s">
+        <v>631</v>
+      </c>
+      <c r="F27" s="120" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="42" customHeight="1">
+      <c r="A28" s="107" t="s">
+        <v>444</v>
+      </c>
+      <c r="B28" s="215" t="s">
+        <v>995</v>
+      </c>
+      <c r="C28" s="36" t="s">
+        <v>998</v>
+      </c>
+      <c r="D28" s="36" t="s">
+        <v>999</v>
+      </c>
+      <c r="E28" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="F28" s="122" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="28">
+      <c r="A29" s="102" t="s">
+        <v>444</v>
+      </c>
+      <c r="B29" s="209" t="s">
+        <v>996</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>488</v>
+      </c>
+      <c r="D29" s="33" t="s">
+        <v>948</v>
+      </c>
+      <c r="E29" s="33" t="s">
+        <v>489</v>
+      </c>
+      <c r="F29" s="117" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="25" customHeight="1">
+      <c r="A30" s="102" t="s">
+        <v>444</v>
+      </c>
+      <c r="B30" s="57" t="s">
+        <v>943</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>944</v>
+      </c>
+      <c r="D30" s="33" t="s">
+        <v>945</v>
+      </c>
+      <c r="E30" s="33" t="s">
+        <v>946</v>
+      </c>
+      <c r="F30" s="117" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="21.75" customHeight="1">
+      <c r="A31" s="107" t="s">
+        <v>444</v>
+      </c>
+      <c r="B31" s="64" t="s">
+        <v>949</v>
+      </c>
+      <c r="C31" s="36" t="s">
+        <v>490</v>
+      </c>
+      <c r="D31" s="36" t="s">
+        <v>491</v>
+      </c>
+      <c r="E31" s="36" t="s">
+        <v>492</v>
+      </c>
+      <c r="F31" s="122" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A32" s="101" t="s">
+        <v>444</v>
+      </c>
+      <c r="B32" s="151" t="s">
+        <v>932</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="F32" s="116" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A33" s="167" t="s">
+        <v>975</v>
+      </c>
+      <c r="B33" s="168"/>
+      <c r="C33" s="168"/>
+      <c r="D33" s="168"/>
+      <c r="E33" s="168"/>
+      <c r="F33" s="169"/>
+    </row>
+    <row r="34" spans="1:6" ht="30" customHeight="1">
+      <c r="A34" s="101" t="s">
+        <v>496</v>
+      </c>
+      <c r="B34" s="56" t="s">
         <v>497</v>
       </c>
-      <c r="C26" s="61" t="s">
+      <c r="C34" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="D34" s="10" t="s">
         <v>498</v>
       </c>
-      <c r="D26" s="61" t="s">
-        <v>499</v>
-      </c>
-      <c r="E26" s="61" t="s">
-        <v>500</v>
-      </c>
-      <c r="F26" s="120" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="30" customHeight="1">
-      <c r="A27" s="107" t="s">
-        <v>453</v>
-      </c>
-      <c r="B27" s="64" t="s">
-        <v>502</v>
-      </c>
-      <c r="C27" s="36" t="s">
-        <v>503</v>
-      </c>
-      <c r="D27" s="36" t="s">
-        <v>504</v>
-      </c>
-      <c r="E27" s="36" t="s">
-        <v>505</v>
-      </c>
-      <c r="F27" s="122" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A28" s="102" t="s">
-        <v>453</v>
-      </c>
-      <c r="B28" s="57" t="s">
-        <v>984</v>
-      </c>
-      <c r="C28" s="33" t="s">
-        <v>507</v>
-      </c>
-      <c r="D28" s="33" t="s">
-        <v>985</v>
-      </c>
-      <c r="E28" s="33" t="s">
-        <v>508</v>
-      </c>
-      <c r="F28" s="117" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="42">
-      <c r="A29" s="102" t="s">
-        <v>453</v>
-      </c>
-      <c r="B29" s="57" t="s">
-        <v>979</v>
-      </c>
-      <c r="C29" s="33" t="s">
-        <v>980</v>
-      </c>
-      <c r="D29" s="33" t="s">
-        <v>981</v>
-      </c>
-      <c r="E29" s="33" t="s">
-        <v>982</v>
-      </c>
-      <c r="F29" s="117" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="25" customHeight="1">
-      <c r="A30" s="107" t="s">
-        <v>453</v>
-      </c>
-      <c r="B30" s="64" t="s">
-        <v>986</v>
-      </c>
-      <c r="C30" s="36" t="s">
-        <v>509</v>
-      </c>
-      <c r="D30" s="36" t="s">
-        <v>510</v>
-      </c>
-      <c r="E30" s="36" t="s">
-        <v>511</v>
-      </c>
-      <c r="F30" s="122" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A31" s="101" t="s">
-        <v>453</v>
-      </c>
-      <c r="B31" s="206" t="s">
-        <v>968</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>514</v>
-      </c>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10" t="s">
-        <v>451</v>
-      </c>
-      <c r="F31" s="116" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A32" s="157" t="s">
-        <v>515</v>
-      </c>
-      <c r="B32" s="158"/>
-      <c r="C32" s="158"/>
-      <c r="D32" s="158"/>
-      <c r="E32" s="158"/>
-      <c r="F32" s="159"/>
-    </row>
-    <row r="33" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A33" s="101" t="s">
-        <v>516</v>
-      </c>
-      <c r="B33" s="56" t="s">
-        <v>517</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>455</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>518</v>
-      </c>
-      <c r="E33" s="10" t="s">
+      <c r="E34" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F33" s="116" t="s">
+      <c r="F34" s="116" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A34" s="105" t="s">
-        <v>516</v>
-      </c>
-      <c r="B34" s="60" t="s">
-        <v>519</v>
-      </c>
-      <c r="C34" s="61" t="s">
-        <v>520</v>
-      </c>
-      <c r="D34" s="61" t="s">
-        <v>521</v>
-      </c>
-      <c r="E34" s="61" t="s">
-        <v>522</v>
-      </c>
-      <c r="F34" s="120" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="25.5" customHeight="1">
       <c r="A35" s="105" t="s">
+        <v>496</v>
+      </c>
+      <c r="B35" s="60" t="s">
+        <v>499</v>
+      </c>
+      <c r="C35" s="61" t="s">
+        <v>500</v>
+      </c>
+      <c r="D35" s="61" t="s">
+        <v>501</v>
+      </c>
+      <c r="E35" s="61" t="s">
+        <v>502</v>
+      </c>
+      <c r="F35" s="120" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A36" s="105" t="s">
+        <v>496</v>
+      </c>
+      <c r="B36" s="60" t="s">
+        <v>504</v>
+      </c>
+      <c r="C36" s="61" t="s">
+        <v>505</v>
+      </c>
+      <c r="D36" s="61" t="s">
+        <v>506</v>
+      </c>
+      <c r="E36" s="61" t="s">
+        <v>507</v>
+      </c>
+      <c r="F36" s="120" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A37" s="104" t="s">
+        <v>496</v>
+      </c>
+      <c r="B37" s="59" t="s">
+        <v>509</v>
+      </c>
+      <c r="C37" s="47" t="s">
+        <v>510</v>
+      </c>
+      <c r="D37" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="E37" s="47" t="s">
+        <v>451</v>
+      </c>
+      <c r="F37" s="119" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A38" s="99" t="s">
+        <v>496</v>
+      </c>
+      <c r="B38" s="54" t="s">
+        <v>512</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>513</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>514</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F38" s="85" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="30" customHeight="1">
+      <c r="A39" s="105" t="s">
+        <v>496</v>
+      </c>
+      <c r="B39" s="60" t="s">
         <v>516</v>
       </c>
-      <c r="B35" s="60" t="s">
+      <c r="C39" s="61" t="s">
+        <v>517</v>
+      </c>
+      <c r="D39" s="61" t="s">
+        <v>518</v>
+      </c>
+      <c r="E39" s="61" t="s">
+        <v>507</v>
+      </c>
+      <c r="F39" s="120" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A40" s="103" t="s">
+        <v>496</v>
+      </c>
+      <c r="B40" s="58" t="s">
+        <v>520</v>
+      </c>
+      <c r="C40" s="39" t="s">
+        <v>521</v>
+      </c>
+      <c r="D40" s="39" t="s">
+        <v>522</v>
+      </c>
+      <c r="E40" s="39" t="s">
+        <v>523</v>
+      </c>
+      <c r="F40" s="118" t="s">
         <v>524</v>
       </c>
-      <c r="C35" s="61" t="s">
+    </row>
+    <row r="41" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A41" s="108" t="s">
+        <v>496</v>
+      </c>
+      <c r="B41" s="89" t="s">
+        <v>904</v>
+      </c>
+      <c r="C41" s="90" t="s">
+        <v>905</v>
+      </c>
+      <c r="D41" s="90" t="s">
+        <v>906</v>
+      </c>
+      <c r="E41" s="90" t="s">
+        <v>907</v>
+      </c>
+      <c r="F41" s="123" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="42" customHeight="1">
+      <c r="A42" s="102" t="s">
+        <v>496</v>
+      </c>
+      <c r="B42" s="57" t="s">
+        <v>633</v>
+      </c>
+      <c r="C42" s="33" t="s">
         <v>525</v>
       </c>
-      <c r="D35" s="61" t="s">
+      <c r="D42" s="33" t="s">
         <v>526</v>
       </c>
-      <c r="E35" s="61" t="s">
+      <c r="E42" s="35" t="s">
         <v>527</v>
       </c>
-      <c r="F35" s="120" t="s">
+      <c r="F42" s="117" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A36" s="104" t="s">
-        <v>516</v>
-      </c>
-      <c r="B36" s="59" t="s">
+    <row r="43" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A43" s="102" t="s">
+        <v>496</v>
+      </c>
+      <c r="B43" s="209" t="s">
+        <v>707</v>
+      </c>
+      <c r="C43" s="33" t="s">
+        <v>966</v>
+      </c>
+      <c r="D43" s="33" t="s">
+        <v>967</v>
+      </c>
+      <c r="E43" s="35" t="s">
+        <v>631</v>
+      </c>
+      <c r="F43" s="117" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="42" customHeight="1">
+      <c r="A44" s="106" t="s">
+        <v>496</v>
+      </c>
+      <c r="B44" s="63" t="s">
+        <v>926</v>
+      </c>
+      <c r="C44" s="20" t="s">
         <v>529</v>
       </c>
-      <c r="C36" s="47" t="s">
+      <c r="D44" s="20" t="s">
         <v>530</v>
       </c>
-      <c r="D36" s="47" t="s">
+      <c r="E44" s="20" t="s">
         <v>531</v>
       </c>
-      <c r="E36" s="47" t="s">
-        <v>460</v>
-      </c>
-      <c r="F36" s="119" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A37" s="99" t="s">
-        <v>516</v>
-      </c>
-      <c r="B37" s="54" t="s">
+      <c r="F44" s="121" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A45" s="105" t="s">
+        <v>496</v>
+      </c>
+      <c r="B45" s="207" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C45" s="61" t="s">
         <v>532</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="D45" s="61" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E45" s="61" t="s">
         <v>533</v>
       </c>
-      <c r="D37" s="15" t="s">
+      <c r="F45" s="120" t="s">
         <v>534</v>
       </c>
-      <c r="E37" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F37" s="85" t="s">
+    </row>
+    <row r="46" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A46" s="103" t="s">
+        <v>496</v>
+      </c>
+      <c r="B46" s="210" t="s">
+        <v>707</v>
+      </c>
+      <c r="C46" s="39" t="s">
         <v>535</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A38" s="105" t="s">
-        <v>516</v>
-      </c>
-      <c r="B38" s="60" t="s">
-        <v>536</v>
-      </c>
-      <c r="C38" s="61" t="s">
+      <c r="D46" s="39" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E46" s="39" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F46" s="118" t="s">
         <v>537</v>
       </c>
-      <c r="D38" s="61" t="s">
-        <v>538</v>
-      </c>
-      <c r="E38" s="61" t="s">
-        <v>527</v>
-      </c>
-      <c r="F38" s="120" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="30" customHeight="1">
-      <c r="A39" s="103" t="s">
-        <v>516</v>
-      </c>
-      <c r="B39" s="58" t="s">
+    </row>
+    <row r="47" spans="1:6" ht="42" customHeight="1">
+      <c r="A47" s="98" t="s">
+        <v>496</v>
+      </c>
+      <c r="B47" s="53" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F47" s="86" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="42" customHeight="1">
+      <c r="A48" s="98" t="s">
+        <v>496</v>
+      </c>
+      <c r="B48" s="214" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F48" s="86" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="42" customHeight="1">
+      <c r="A49" s="101" t="s">
+        <v>496</v>
+      </c>
+      <c r="B49" s="151" t="s">
+        <v>932</v>
+      </c>
+      <c r="C49" s="10" t="s">
         <v>540</v>
       </c>
-      <c r="C39" s="39" t="s">
+      <c r="D49" s="10" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="F49" s="116" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A50" s="109" t="s">
+        <v>496</v>
+      </c>
+      <c r="B50" s="65" t="s">
         <v>541</v>
       </c>
-      <c r="D39" s="39" t="s">
+      <c r="C50" s="42" t="s">
         <v>542</v>
       </c>
-      <c r="E39" s="39" t="s">
+      <c r="D50" s="42" t="s">
         <v>543</v>
       </c>
-      <c r="F39" s="118" t="s">
+      <c r="E50" s="42" t="s">
         <v>544</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A40" s="108" t="s">
-        <v>516</v>
-      </c>
-      <c r="B40" s="89" t="s">
-        <v>940</v>
-      </c>
-      <c r="C40" s="90" t="s">
-        <v>941</v>
-      </c>
-      <c r="D40" s="90" t="s">
-        <v>942</v>
-      </c>
-      <c r="E40" s="90" t="s">
-        <v>943</v>
-      </c>
-      <c r="F40" s="123" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A41" s="102" t="s">
-        <v>516</v>
-      </c>
-      <c r="B41" s="57" t="s">
-        <v>662</v>
-      </c>
-      <c r="C41" s="33" t="s">
+      <c r="F50" s="124" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A51" s="103" t="s">
+        <v>496</v>
+      </c>
+      <c r="B51" s="58" t="s">
+        <v>541</v>
+      </c>
+      <c r="C51" s="39" t="s">
         <v>545</v>
       </c>
-      <c r="D41" s="33" t="s">
+      <c r="D51" s="39" t="s">
         <v>546</v>
       </c>
-      <c r="E41" s="35" t="s">
+      <c r="E51" s="39" t="s">
+        <v>544</v>
+      </c>
+      <c r="F51" s="118" t="s">
         <v>547</v>
       </c>
-      <c r="F41" s="117" t="s">
+    </row>
+    <row r="52" spans="1:6" ht="42" customHeight="1">
+      <c r="A52" s="103" t="s">
+        <v>496</v>
+      </c>
+      <c r="B52" s="210" t="s">
+        <v>541</v>
+      </c>
+      <c r="C52" s="39" t="s">
+        <v>962</v>
+      </c>
+      <c r="D52" s="211" t="s">
+        <v>963</v>
+      </c>
+      <c r="E52" s="39" t="s">
+        <v>964</v>
+      </c>
+      <c r="F52" s="118" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="30" customHeight="1">
+      <c r="A53" s="152" t="s">
+        <v>982</v>
+      </c>
+      <c r="B53" s="153"/>
+      <c r="C53" s="153"/>
+      <c r="D53" s="153"/>
+      <c r="E53" s="153"/>
+      <c r="F53" s="154"/>
+    </row>
+    <row r="54" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A54" s="101" t="s">
         <v>548</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" ht="30" customHeight="1">
-      <c r="A42" s="106" t="s">
-        <v>516</v>
-      </c>
-      <c r="B42" s="63" t="s">
-        <v>962</v>
-      </c>
-      <c r="C42" s="20" t="s">
+      <c r="B54" s="56" t="s">
+        <v>497</v>
+      </c>
+      <c r="C54" s="10" t="s">
         <v>549</v>
       </c>
-      <c r="D42" s="20" t="s">
+      <c r="D54" s="10" t="s">
         <v>550</v>
       </c>
-      <c r="E42" s="20" t="s">
+      <c r="E54" s="10" t="s">
         <v>551</v>
       </c>
-      <c r="F42" s="121" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A43" s="105" t="s">
-        <v>516</v>
-      </c>
-      <c r="B43" s="60" t="s">
-        <v>497</v>
-      </c>
-      <c r="C43" s="61" t="s">
+      <c r="F54" s="116" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A55" s="100" t="s">
+        <v>548</v>
+      </c>
+      <c r="B55" s="55" t="s">
         <v>552</v>
       </c>
-      <c r="D43" s="61" t="s">
+      <c r="C55" s="50" t="s">
         <v>553</v>
       </c>
-      <c r="E43" s="61" t="s">
+      <c r="D55" s="50" t="s">
         <v>554</v>
       </c>
-      <c r="F43" s="120" t="s">
+      <c r="E55" s="50" t="s">
         <v>555</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A44" s="103" t="s">
-        <v>516</v>
-      </c>
-      <c r="B44" s="58" t="s">
+      <c r="F55" s="115" t="s">
         <v>556</v>
       </c>
-      <c r="C44" s="39" t="s">
+    </row>
+    <row r="56" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A56" s="100" t="s">
+        <v>548</v>
+      </c>
+      <c r="B56" s="55" t="s">
         <v>557</v>
       </c>
-      <c r="D44" s="39" t="s">
+      <c r="C56" s="50" t="s">
         <v>558</v>
       </c>
-      <c r="E44" s="39" t="s">
+      <c r="D56" s="50" t="s">
         <v>559</v>
       </c>
-      <c r="F44" s="118" t="s">
+      <c r="E56" s="50" t="s">
         <v>560</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A45" s="98" t="s">
-        <v>516</v>
-      </c>
-      <c r="B45" s="53" t="s">
+      <c r="F56" s="115" t="s">
         <v>561</v>
       </c>
-      <c r="C45" s="5" t="s">
+    </row>
+    <row r="57" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A57" s="101" t="s">
+        <v>548</v>
+      </c>
+      <c r="B57" s="56" t="s">
         <v>562</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="C57" s="10" t="s">
         <v>563</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="D57" s="10" t="s">
         <v>564</v>
       </c>
-      <c r="F45" s="86" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A46" s="101" t="s">
-        <v>516</v>
-      </c>
-      <c r="B46" s="56" t="s">
+      <c r="E57" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="F57" s="116" t="s">
         <v>565</v>
       </c>
-      <c r="C46" s="10" t="s">
+    </row>
+    <row r="58" spans="1:6" ht="45" customHeight="1">
+      <c r="A58" s="99" t="s">
+        <v>548</v>
+      </c>
+      <c r="B58" s="54" t="s">
         <v>566</v>
       </c>
-      <c r="D46" s="10" t="s">
+      <c r="C58" s="15" t="s">
         <v>567</v>
       </c>
-      <c r="E46" s="10" t="s">
-        <v>451</v>
-      </c>
-      <c r="F46" s="116" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A47" s="109" t="s">
-        <v>516</v>
-      </c>
-      <c r="B47" s="65" t="s">
+      <c r="D58" s="25" t="s">
         <v>568</v>
       </c>
-      <c r="C47" s="42" t="s">
+      <c r="E58" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="F58" s="85" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A59" s="105" t="s">
+        <v>548</v>
+      </c>
+      <c r="B59" s="60" t="s">
         <v>569</v>
       </c>
-      <c r="D47" s="42" t="s">
+      <c r="C59" s="61" t="s">
         <v>570</v>
       </c>
-      <c r="E47" s="42" t="s">
+      <c r="D59" s="61" t="s">
         <v>571</v>
       </c>
-      <c r="F47" s="124" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A48" s="103" t="s">
-        <v>516</v>
-      </c>
-      <c r="B48" s="58" t="s">
-        <v>568</v>
-      </c>
-      <c r="C48" s="39" t="s">
-        <v>572</v>
-      </c>
-      <c r="D48" s="39" t="s">
-        <v>573</v>
-      </c>
-      <c r="E48" s="39" t="s">
-        <v>571</v>
-      </c>
-      <c r="F48" s="118" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A49" s="160" t="s">
-        <v>575</v>
-      </c>
-      <c r="B49" s="161"/>
-      <c r="C49" s="161"/>
-      <c r="D49" s="161"/>
-      <c r="E49" s="161"/>
-      <c r="F49" s="162"/>
-    </row>
-    <row r="50" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A50" s="101" t="s">
-        <v>576</v>
-      </c>
-      <c r="B50" s="56" t="s">
-        <v>517</v>
-      </c>
-      <c r="C50" s="10" t="s">
-        <v>577</v>
-      </c>
-      <c r="D50" s="10" t="s">
-        <v>578</v>
-      </c>
-      <c r="E50" s="10" t="s">
-        <v>579</v>
-      </c>
-      <c r="F50" s="116" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A51" s="100" t="s">
-        <v>576</v>
-      </c>
-      <c r="B51" s="55" t="s">
-        <v>580</v>
-      </c>
-      <c r="C51" s="50" t="s">
-        <v>581</v>
-      </c>
-      <c r="D51" s="50" t="s">
-        <v>582</v>
-      </c>
-      <c r="E51" s="50" t="s">
-        <v>583</v>
-      </c>
-      <c r="F51" s="115" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="30" customHeight="1">
-      <c r="A52" s="100" t="s">
-        <v>576</v>
-      </c>
-      <c r="B52" s="55" t="s">
-        <v>585</v>
-      </c>
-      <c r="C52" s="50" t="s">
-        <v>586</v>
-      </c>
-      <c r="D52" s="50" t="s">
-        <v>587</v>
-      </c>
-      <c r="E52" s="50" t="s">
-        <v>588</v>
-      </c>
-      <c r="F52" s="115" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="30" customHeight="1">
-      <c r="A53" s="101" t="s">
-        <v>576</v>
-      </c>
-      <c r="B53" s="56" t="s">
-        <v>590</v>
-      </c>
-      <c r="C53" s="10" t="s">
-        <v>591</v>
-      </c>
-      <c r="D53" s="10" t="s">
-        <v>592</v>
-      </c>
-      <c r="E53" s="10" t="s">
-        <v>433</v>
-      </c>
-      <c r="F53" s="116" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A54" s="99" t="s">
-        <v>576</v>
-      </c>
-      <c r="B54" s="54" t="s">
-        <v>594</v>
-      </c>
-      <c r="C54" s="15" t="s">
-        <v>595</v>
-      </c>
-      <c r="D54" s="25" t="s">
-        <v>596</v>
-      </c>
-      <c r="E54" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="F54" s="85" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A55" s="105" t="s">
-        <v>576</v>
-      </c>
-      <c r="B55" s="60" t="s">
-        <v>597</v>
-      </c>
-      <c r="C55" s="61" t="s">
-        <v>598</v>
-      </c>
-      <c r="D55" s="61" t="s">
-        <v>599</v>
-      </c>
-      <c r="E55" s="61" t="s">
-        <v>527</v>
-      </c>
-      <c r="F55" s="120" t="s">
+      <c r="E59" s="61" t="s">
+        <v>507</v>
+      </c>
+      <c r="F59" s="120" t="s">
         <v>222</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A56" s="105" t="s">
-        <v>576</v>
-      </c>
-      <c r="B56" s="60" t="s">
-        <v>600</v>
-      </c>
-      <c r="C56" s="61" t="s">
-        <v>601</v>
-      </c>
-      <c r="D56" s="61" t="s">
-        <v>602</v>
-      </c>
-      <c r="E56" s="61" t="s">
-        <v>603</v>
-      </c>
-      <c r="F56" s="120" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A57" s="106" t="s">
-        <v>576</v>
-      </c>
-      <c r="B57" s="63" t="s">
-        <v>605</v>
-      </c>
-      <c r="C57" s="20" t="s">
-        <v>606</v>
-      </c>
-      <c r="D57" s="20" t="s">
-        <v>607</v>
-      </c>
-      <c r="E57" s="20" t="s">
-        <v>608</v>
-      </c>
-      <c r="F57" s="121" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="45" customHeight="1">
-      <c r="A58" s="105" t="s">
-        <v>576</v>
-      </c>
-      <c r="B58" s="60" t="s">
-        <v>610</v>
-      </c>
-      <c r="C58" s="61" t="s">
-        <v>611</v>
-      </c>
-      <c r="D58" s="61" t="s">
-        <v>612</v>
-      </c>
-      <c r="E58" s="61" t="s">
-        <v>603</v>
-      </c>
-      <c r="F58" s="120" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A59" s="110" t="s">
-        <v>576</v>
-      </c>
-      <c r="B59" s="91" t="s">
-        <v>963</v>
-      </c>
-      <c r="C59" s="92" t="s">
-        <v>945</v>
-      </c>
-      <c r="D59" s="92" t="s">
-        <v>946</v>
-      </c>
-      <c r="E59" s="92" t="s">
-        <v>947</v>
-      </c>
-      <c r="F59" s="125" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="30" customHeight="1">
       <c r="A60" s="105" t="s">
+        <v>548</v>
+      </c>
+      <c r="B60" s="60" t="s">
+        <v>572</v>
+      </c>
+      <c r="C60" s="61" t="s">
+        <v>573</v>
+      </c>
+      <c r="D60" s="61" t="s">
+        <v>574</v>
+      </c>
+      <c r="E60" s="61" t="s">
+        <v>575</v>
+      </c>
+      <c r="F60" s="120" t="s">
         <v>576</v>
       </c>
-      <c r="B60" s="60" t="s">
-        <v>618</v>
-      </c>
-      <c r="C60" s="61" t="s">
-        <v>614</v>
-      </c>
-      <c r="D60" s="61" t="s">
-        <v>615</v>
-      </c>
-      <c r="E60" s="61" t="s">
-        <v>616</v>
-      </c>
-      <c r="F60" s="120" t="s">
-        <v>617</v>
-      </c>
     </row>
     <row r="61" spans="1:6" ht="30" customHeight="1">
-      <c r="A61" s="107" t="s">
-        <v>576</v>
-      </c>
-      <c r="B61" s="64" t="s">
-        <v>964</v>
-      </c>
-      <c r="C61" s="36" t="s">
-        <v>619</v>
-      </c>
-      <c r="D61" s="36" t="s">
-        <v>620</v>
-      </c>
-      <c r="E61" s="36" t="s">
-        <v>621</v>
-      </c>
-      <c r="F61" s="122" t="s">
-        <v>622</v>
+      <c r="A61" s="106" t="s">
+        <v>548</v>
+      </c>
+      <c r="B61" s="63" t="s">
+        <v>577</v>
+      </c>
+      <c r="C61" s="20" t="s">
+        <v>578</v>
+      </c>
+      <c r="D61" s="20" t="s">
+        <v>579</v>
+      </c>
+      <c r="E61" s="20" t="s">
+        <v>580</v>
+      </c>
+      <c r="F61" s="121" t="s">
+        <v>581</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A62" s="109" t="s">
-        <v>576</v>
-      </c>
-      <c r="B62" s="65" t="s">
-        <v>965</v>
-      </c>
-      <c r="C62" s="42" t="s">
-        <v>623</v>
-      </c>
-      <c r="D62" s="44" t="s">
-        <v>624</v>
-      </c>
-      <c r="E62" s="42" t="s">
-        <v>625</v>
-      </c>
-      <c r="F62" s="124" t="s">
-        <v>626</v>
+      <c r="A62" s="105" t="s">
+        <v>548</v>
+      </c>
+      <c r="B62" s="60" t="s">
+        <v>582</v>
+      </c>
+      <c r="C62" s="61" t="s">
+        <v>583</v>
+      </c>
+      <c r="D62" s="61" t="s">
+        <v>584</v>
+      </c>
+      <c r="E62" s="61" t="s">
+        <v>575</v>
+      </c>
+      <c r="F62" s="120" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A63" s="101" t="s">
-        <v>576</v>
-      </c>
-      <c r="B63" s="128" t="s">
-        <v>968</v>
-      </c>
-      <c r="C63" s="10" t="s">
-        <v>628</v>
-      </c>
-      <c r="D63" s="10"/>
-      <c r="E63" s="10" t="s">
-        <v>629</v>
-      </c>
-      <c r="F63" s="116" t="s">
+      <c r="A63" s="110" t="s">
+        <v>548</v>
+      </c>
+      <c r="B63" s="91" t="s">
+        <v>927</v>
+      </c>
+      <c r="C63" s="92" t="s">
+        <v>909</v>
+      </c>
+      <c r="D63" s="92" t="s">
+        <v>910</v>
+      </c>
+      <c r="E63" s="92" t="s">
+        <v>911</v>
+      </c>
+      <c r="F63" s="125" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A64" s="105" t="s">
+        <v>548</v>
+      </c>
+      <c r="B64" s="60" t="s">
+        <v>590</v>
+      </c>
+      <c r="C64" s="61" t="s">
+        <v>586</v>
+      </c>
+      <c r="D64" s="61" t="s">
+        <v>587</v>
+      </c>
+      <c r="E64" s="61" t="s">
+        <v>588</v>
+      </c>
+      <c r="F64" s="120" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A65" s="107" t="s">
+        <v>548</v>
+      </c>
+      <c r="B65" s="64" t="s">
+        <v>928</v>
+      </c>
+      <c r="C65" s="36" t="s">
+        <v>591</v>
+      </c>
+      <c r="D65" s="36" t="s">
+        <v>592</v>
+      </c>
+      <c r="E65" s="36" t="s">
         <v>593</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A64" s="160" t="s">
-        <v>630</v>
-      </c>
-      <c r="B64" s="161"/>
-      <c r="C64" s="161"/>
-      <c r="D64" s="161"/>
-      <c r="E64" s="161"/>
-      <c r="F64" s="162"/>
-    </row>
-    <row r="65" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A65" s="101" t="s">
-        <v>631</v>
-      </c>
-      <c r="B65" s="56" t="s">
-        <v>517</v>
-      </c>
-      <c r="C65" s="10" t="s">
-        <v>632</v>
-      </c>
-      <c r="D65" s="10" t="s">
-        <v>633</v>
-      </c>
-      <c r="E65" s="10" t="s">
+      <c r="F65" s="122" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="30" customHeight="1">
+      <c r="A66" s="109" t="s">
+        <v>548</v>
+      </c>
+      <c r="B66" s="65" t="s">
+        <v>929</v>
+      </c>
+      <c r="C66" s="42" t="s">
+        <v>595</v>
+      </c>
+      <c r="D66" s="44" t="s">
+        <v>596</v>
+      </c>
+      <c r="E66" s="42" t="s">
+        <v>597</v>
+      </c>
+      <c r="F66" s="124" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="30" customHeight="1">
+      <c r="A67" s="101" t="s">
+        <v>548</v>
+      </c>
+      <c r="B67" s="128" t="s">
+        <v>932</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>600</v>
+      </c>
+      <c r="D67" s="10"/>
+      <c r="E67" s="10" t="s">
+        <v>601</v>
+      </c>
+      <c r="F67" s="116" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="30" customHeight="1">
+      <c r="A68" s="152" t="s">
+        <v>976</v>
+      </c>
+      <c r="B68" s="153"/>
+      <c r="C68" s="153"/>
+      <c r="D68" s="153"/>
+      <c r="E68" s="153"/>
+      <c r="F68" s="154"/>
+    </row>
+    <row r="69" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A69" s="101" t="s">
+        <v>602</v>
+      </c>
+      <c r="B69" s="56" t="s">
+        <v>497</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>603</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>604</v>
+      </c>
+      <c r="E69" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F65" s="116" t="s">
+      <c r="F69" s="116" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="30" customHeight="1">
-      <c r="A66" s="105" t="s">
-        <v>631</v>
-      </c>
-      <c r="B66" s="60" t="s">
-        <v>634</v>
-      </c>
-      <c r="C66" s="61" t="s">
-        <v>635</v>
-      </c>
-      <c r="D66" s="62" t="s">
-        <v>636</v>
-      </c>
-      <c r="E66" s="61" t="s">
-        <v>637</v>
-      </c>
-      <c r="F66" s="120" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="30" customHeight="1">
-      <c r="A67" s="108" t="s">
-        <v>631</v>
-      </c>
-      <c r="B67" s="89" t="s">
-        <v>949</v>
-      </c>
-      <c r="C67" s="90" t="s">
-        <v>950</v>
-      </c>
-      <c r="D67" s="90" t="s">
-        <v>951</v>
-      </c>
-      <c r="E67" s="90" t="s">
-        <v>952</v>
-      </c>
-      <c r="F67" s="123" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="30" customHeight="1">
-      <c r="A68" s="103" t="s">
-        <v>631</v>
-      </c>
-      <c r="B68" s="58" t="s">
-        <v>966</v>
-      </c>
-      <c r="C68" s="39" t="s">
-        <v>639</v>
-      </c>
-      <c r="D68" s="39" t="s">
-        <v>640</v>
-      </c>
-      <c r="E68" s="39" t="s">
-        <v>641</v>
-      </c>
-      <c r="F68" s="118" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A69" s="104" t="s">
-        <v>631</v>
-      </c>
-      <c r="B69" s="59" t="s">
-        <v>475</v>
-      </c>
-      <c r="C69" s="47" t="s">
-        <v>643</v>
-      </c>
-      <c r="D69" s="47" t="s">
-        <v>644</v>
-      </c>
-      <c r="E69" s="47" t="s">
-        <v>645</v>
-      </c>
-      <c r="F69" s="119" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="25.5" customHeight="1">
       <c r="A70" s="105" t="s">
-        <v>631</v>
+        <v>602</v>
       </c>
       <c r="B70" s="60" t="s">
-        <v>647</v>
+        <v>605</v>
       </c>
       <c r="C70" s="61" t="s">
-        <v>648</v>
-      </c>
-      <c r="D70" s="61" t="s">
-        <v>649</v>
+        <v>606</v>
+      </c>
+      <c r="D70" s="62" t="s">
+        <v>607</v>
       </c>
       <c r="E70" s="61" t="s">
-        <v>650</v>
+        <v>608</v>
       </c>
       <c r="F70" s="120" t="s">
-        <v>651</v>
+        <v>609</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="30" customHeight="1">
-      <c r="A71" s="98" t="s">
-        <v>631</v>
-      </c>
-      <c r="B71" s="53" t="s">
-        <v>652</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>653</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>654</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>655</v>
-      </c>
-      <c r="F71" s="86" t="s">
-        <v>656</v>
+      <c r="A71" s="108" t="s">
+        <v>602</v>
+      </c>
+      <c r="B71" s="89" t="s">
+        <v>913</v>
+      </c>
+      <c r="C71" s="90" t="s">
+        <v>914</v>
+      </c>
+      <c r="D71" s="90" t="s">
+        <v>915</v>
+      </c>
+      <c r="E71" s="90" t="s">
+        <v>916</v>
+      </c>
+      <c r="F71" s="123" t="s">
+        <v>917</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="30" customHeight="1">
       <c r="A72" s="103" t="s">
+        <v>602</v>
+      </c>
+      <c r="B72" s="58" t="s">
+        <v>930</v>
+      </c>
+      <c r="C72" s="39" t="s">
+        <v>610</v>
+      </c>
+      <c r="D72" s="39" t="s">
+        <v>611</v>
+      </c>
+      <c r="E72" s="39" t="s">
+        <v>612</v>
+      </c>
+      <c r="F72" s="118" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="30" customHeight="1">
+      <c r="A73" s="104" t="s">
+        <v>602</v>
+      </c>
+      <c r="B73" s="59" t="s">
+        <v>466</v>
+      </c>
+      <c r="C73" s="47" t="s">
+        <v>614</v>
+      </c>
+      <c r="D73" s="47" t="s">
+        <v>615</v>
+      </c>
+      <c r="E73" s="47" t="s">
+        <v>616</v>
+      </c>
+      <c r="F73" s="119" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A74" s="105" t="s">
+        <v>602</v>
+      </c>
+      <c r="B74" s="60" t="s">
+        <v>618</v>
+      </c>
+      <c r="C74" s="61" t="s">
+        <v>619</v>
+      </c>
+      <c r="D74" s="61" t="s">
+        <v>620</v>
+      </c>
+      <c r="E74" s="61" t="s">
+        <v>621</v>
+      </c>
+      <c r="F74" s="120" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="30" customHeight="1">
+      <c r="A75" s="98" t="s">
+        <v>602</v>
+      </c>
+      <c r="B75" s="53" t="s">
+        <v>623</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>624</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>626</v>
+      </c>
+      <c r="F75" s="86" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="30" customHeight="1">
+      <c r="A76" s="103" t="s">
+        <v>602</v>
+      </c>
+      <c r="B76" s="58" t="s">
+        <v>628</v>
+      </c>
+      <c r="C76" s="39" t="s">
+        <v>629</v>
+      </c>
+      <c r="D76" s="39" t="s">
+        <v>630</v>
+      </c>
+      <c r="E76" s="39" t="s">
         <v>631</v>
       </c>
-      <c r="B72" s="58" t="s">
+      <c r="F76" s="118" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="42" customHeight="1">
+      <c r="A77" s="105" t="s">
+        <v>602</v>
+      </c>
+      <c r="B77" s="60" t="s">
+        <v>633</v>
+      </c>
+      <c r="C77" s="61" t="s">
+        <v>634</v>
+      </c>
+      <c r="D77" s="61" t="s">
+        <v>635</v>
+      </c>
+      <c r="E77" s="61" t="s">
+        <v>636</v>
+      </c>
+      <c r="F77" s="120" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A78" s="104" t="s">
+        <v>602</v>
+      </c>
+      <c r="B78" s="59" t="s">
+        <v>638</v>
+      </c>
+      <c r="C78" s="47" t="s">
+        <v>639</v>
+      </c>
+      <c r="D78" s="47" t="s">
+        <v>640</v>
+      </c>
+      <c r="E78" s="47" t="s">
+        <v>631</v>
+      </c>
+      <c r="F78" s="119" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="30" customHeight="1">
+      <c r="A79" s="106" t="s">
+        <v>602</v>
+      </c>
+      <c r="B79" s="63" t="s">
+        <v>642</v>
+      </c>
+      <c r="C79" s="20" t="s">
+        <v>643</v>
+      </c>
+      <c r="D79" s="20" t="s">
+        <v>644</v>
+      </c>
+      <c r="E79" s="20" t="s">
+        <v>645</v>
+      </c>
+      <c r="F79" s="121" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="30" customHeight="1">
+      <c r="A80" s="102" t="s">
+        <v>602</v>
+      </c>
+      <c r="B80" s="57" t="s">
+        <v>647</v>
+      </c>
+      <c r="C80" s="33" t="s">
+        <v>648</v>
+      </c>
+      <c r="D80" s="33" t="s">
+        <v>649</v>
+      </c>
+      <c r="E80" s="33" t="s">
+        <v>650</v>
+      </c>
+      <c r="F80" s="117" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="42" customHeight="1">
+      <c r="A81" s="102" t="s">
+        <v>602</v>
+      </c>
+      <c r="B81" s="209" t="s">
+        <v>707</v>
+      </c>
+      <c r="C81" s="33" t="s">
+        <v>959</v>
+      </c>
+      <c r="D81" s="33" t="s">
+        <v>960</v>
+      </c>
+      <c r="E81" s="33" t="s">
+        <v>631</v>
+      </c>
+      <c r="F81" s="117" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="30" customHeight="1">
+      <c r="A82" s="107" t="s">
+        <v>602</v>
+      </c>
+      <c r="B82" s="64" t="s">
+        <v>538</v>
+      </c>
+      <c r="C82" s="36" t="s">
+        <v>651</v>
+      </c>
+      <c r="D82" s="36" t="s">
+        <v>652</v>
+      </c>
+      <c r="E82" s="36" t="s">
+        <v>210</v>
+      </c>
+      <c r="F82" s="122" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="21.75" customHeight="1">
+      <c r="A83" s="101" t="s">
+        <v>602</v>
+      </c>
+      <c r="B83" s="56" t="s">
+        <v>653</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>654</v>
+      </c>
+      <c r="D83" s="10" t="s">
+        <v>655</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="F83" s="116" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="42" customHeight="1">
+      <c r="A84" s="101" t="s">
+        <v>602</v>
+      </c>
+      <c r="B84" s="56" t="s">
+        <v>599</v>
+      </c>
+      <c r="C84" s="10" t="s">
+        <v>656</v>
+      </c>
+      <c r="D84" s="10" t="s">
         <v>657</v>
       </c>
-      <c r="C72" s="39" t="s">
+      <c r="E84" s="10" t="s">
+        <v>601</v>
+      </c>
+      <c r="F84" s="116" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A85" s="103" t="s">
+        <v>602</v>
+      </c>
+      <c r="B85" s="58" t="s">
+        <v>541</v>
+      </c>
+      <c r="C85" s="39" t="s">
         <v>658</v>
       </c>
-      <c r="D72" s="39" t="s">
+      <c r="D85" s="39" t="s">
         <v>659</v>
       </c>
-      <c r="E72" s="39" t="s">
+      <c r="E85" s="39" t="s">
+        <v>544</v>
+      </c>
+      <c r="F85" s="118" t="s">
         <v>660</v>
       </c>
-      <c r="F72" s="118" t="s">
+    </row>
+    <row r="86" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A86" s="103" t="s">
+        <v>602</v>
+      </c>
+      <c r="B86" s="58" t="s">
+        <v>541</v>
+      </c>
+      <c r="C86" s="39" t="s">
         <v>661</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" ht="30" customHeight="1">
-      <c r="A73" s="105" t="s">
+      <c r="D86" s="39" t="s">
+        <v>662</v>
+      </c>
+      <c r="E86" s="39" t="s">
+        <v>544</v>
+      </c>
+      <c r="F86" s="118" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="30" customHeight="1">
+      <c r="A87" s="103" t="s">
+        <v>602</v>
+      </c>
+      <c r="B87" s="58" t="s">
+        <v>541</v>
+      </c>
+      <c r="C87" s="39" t="s">
+        <v>664</v>
+      </c>
+      <c r="D87" s="39" t="s">
+        <v>665</v>
+      </c>
+      <c r="E87" s="39" t="s">
+        <v>544</v>
+      </c>
+      <c r="F87" s="118" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A88" s="108" t="s">
+        <v>602</v>
+      </c>
+      <c r="B88" s="89" t="s">
+        <v>541</v>
+      </c>
+      <c r="C88" s="90" t="s">
+        <v>918</v>
+      </c>
+      <c r="D88" s="95" t="s">
+        <v>919</v>
+      </c>
+      <c r="E88" s="90" t="s">
+        <v>920</v>
+      </c>
+      <c r="F88" s="123" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="42" customHeight="1">
+      <c r="A89" s="108" t="s">
+        <v>602</v>
+      </c>
+      <c r="B89" s="208" t="s">
+        <v>541</v>
+      </c>
+      <c r="C89" s="90" t="s">
+        <v>956</v>
+      </c>
+      <c r="D89" s="95" t="s">
+        <v>957</v>
+      </c>
+      <c r="E89" s="90" t="s">
+        <v>920</v>
+      </c>
+      <c r="F89" s="123" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="30" customHeight="1">
+      <c r="A90" s="155" t="s">
+        <v>983</v>
+      </c>
+      <c r="B90" s="156"/>
+      <c r="C90" s="156"/>
+      <c r="D90" s="156"/>
+      <c r="E90" s="156"/>
+      <c r="F90" s="157"/>
+    </row>
+    <row r="91" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A91" s="101" t="s">
+        <v>667</v>
+      </c>
+      <c r="B91" s="56" t="s">
+        <v>497</v>
+      </c>
+      <c r="C91" s="10" t="s">
+        <v>668</v>
+      </c>
+      <c r="D91" s="10"/>
+      <c r="E91" s="10" t="s">
+        <v>551</v>
+      </c>
+      <c r="F91" s="116" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A92" s="100" t="s">
+        <v>667</v>
+      </c>
+      <c r="B92" s="55" t="s">
+        <v>552</v>
+      </c>
+      <c r="C92" s="50" t="s">
+        <v>669</v>
+      </c>
+      <c r="D92" s="50" t="s">
+        <v>670</v>
+      </c>
+      <c r="E92" s="50" t="s">
+        <v>555</v>
+      </c>
+      <c r="F92" s="115" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="30" customHeight="1">
+      <c r="A93" s="100" t="s">
+        <v>667</v>
+      </c>
+      <c r="B93" s="55" t="s">
+        <v>557</v>
+      </c>
+      <c r="C93" s="50" t="s">
+        <v>672</v>
+      </c>
+      <c r="D93" s="50" t="s">
+        <v>673</v>
+      </c>
+      <c r="E93" s="50" t="s">
+        <v>560</v>
+      </c>
+      <c r="F93" s="115" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="30" customHeight="1">
+      <c r="A94" s="101" t="s">
+        <v>667</v>
+      </c>
+      <c r="B94" s="56" t="s">
+        <v>562</v>
+      </c>
+      <c r="C94" s="10" t="s">
+        <v>675</v>
+      </c>
+      <c r="D94" s="10" t="s">
+        <v>676</v>
+      </c>
+      <c r="E94" s="10" t="s">
+        <v>677</v>
+      </c>
+      <c r="F94" s="116" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="42" customHeight="1">
+      <c r="A95" s="99" t="s">
+        <v>667</v>
+      </c>
+      <c r="B95" s="54" t="s">
+        <v>566</v>
+      </c>
+      <c r="C95" s="15" t="s">
+        <v>679</v>
+      </c>
+      <c r="D95" s="15" t="s">
+        <v>680</v>
+      </c>
+      <c r="E95" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="F95" s="85" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A96" s="105" t="s">
+        <v>667</v>
+      </c>
+      <c r="B96" s="60" t="s">
+        <v>681</v>
+      </c>
+      <c r="C96" s="61" t="s">
+        <v>682</v>
+      </c>
+      <c r="D96" s="61" t="s">
+        <v>683</v>
+      </c>
+      <c r="E96" s="61" t="s">
+        <v>684</v>
+      </c>
+      <c r="F96" s="120" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="45" customHeight="1">
+      <c r="A97" s="105" t="s">
+        <v>667</v>
+      </c>
+      <c r="B97" s="60" t="s">
+        <v>686</v>
+      </c>
+      <c r="C97" s="61" t="s">
+        <v>687</v>
+      </c>
+      <c r="D97" s="61" t="s">
+        <v>688</v>
+      </c>
+      <c r="E97" s="61" t="s">
+        <v>608</v>
+      </c>
+      <c r="F97" s="120" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="30" customHeight="1">
+      <c r="A98" s="105" t="s">
+        <v>667</v>
+      </c>
+      <c r="B98" s="60" t="s">
+        <v>690</v>
+      </c>
+      <c r="C98" s="61" t="s">
+        <v>691</v>
+      </c>
+      <c r="D98" s="61" t="s">
+        <v>692</v>
+      </c>
+      <c r="E98" s="61" t="s">
+        <v>693</v>
+      </c>
+      <c r="F98" s="120" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="21.75" customHeight="1">
+      <c r="A99" s="106" t="s">
+        <v>667</v>
+      </c>
+      <c r="B99" s="63" t="s">
+        <v>695</v>
+      </c>
+      <c r="C99" s="20" t="s">
+        <v>696</v>
+      </c>
+      <c r="D99" s="20" t="s">
+        <v>697</v>
+      </c>
+      <c r="E99" s="20" t="s">
+        <v>698</v>
+      </c>
+      <c r="F99" s="121" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A100" s="105" t="s">
+        <v>667</v>
+      </c>
+      <c r="B100" s="60" t="s">
+        <v>699</v>
+      </c>
+      <c r="C100" s="61" t="s">
+        <v>700</v>
+      </c>
+      <c r="D100" s="61" t="s">
+        <v>701</v>
+      </c>
+      <c r="E100" s="61" t="s">
+        <v>111</v>
+      </c>
+      <c r="F100" s="120" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="42" customHeight="1">
+      <c r="A101" s="105" t="s">
+        <v>667</v>
+      </c>
+      <c r="B101" s="207" t="s">
+        <v>707</v>
+      </c>
+      <c r="C101" s="61" t="s">
+        <v>954</v>
+      </c>
+      <c r="D101" s="61" t="s">
+        <v>955</v>
+      </c>
+      <c r="E101" s="61" t="s">
         <v>631</v>
       </c>
-      <c r="B73" s="60" t="s">
-        <v>662</v>
-      </c>
-      <c r="C73" s="61" t="s">
-        <v>663</v>
-      </c>
-      <c r="D73" s="61" t="s">
-        <v>664</v>
-      </c>
-      <c r="E73" s="61" t="s">
-        <v>665</v>
-      </c>
-      <c r="F73" s="120" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A74" s="104" t="s">
-        <v>631</v>
-      </c>
-      <c r="B74" s="59" t="s">
+      <c r="F101" s="120" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="30" customHeight="1">
+      <c r="A102" s="109" t="s">
         <v>667</v>
       </c>
-      <c r="C74" s="47" t="s">
+      <c r="B102" s="65" t="s">
+        <v>702</v>
+      </c>
+      <c r="C102" s="42" t="s">
+        <v>703</v>
+      </c>
+      <c r="D102" s="42" t="s">
+        <v>704</v>
+      </c>
+      <c r="E102" s="42" t="s">
+        <v>705</v>
+      </c>
+      <c r="F102" s="124" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="45" customHeight="1">
+      <c r="A103" s="111" t="s">
+        <v>667</v>
+      </c>
+      <c r="B103" s="93" t="s">
+        <v>922</v>
+      </c>
+      <c r="C103" s="94" t="s">
+        <v>923</v>
+      </c>
+      <c r="D103" s="94" t="s">
+        <v>924</v>
+      </c>
+      <c r="E103" s="94" t="s">
+        <v>925</v>
+      </c>
+      <c r="F103" s="126" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A104" s="101" t="s">
+        <v>667</v>
+      </c>
+      <c r="B104" s="128" t="s">
+        <v>932</v>
+      </c>
+      <c r="C104" s="10" t="s">
+        <v>931</v>
+      </c>
+      <c r="D104" s="10"/>
+      <c r="E104" s="10" t="s">
+        <v>601</v>
+      </c>
+      <c r="F104" s="116" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="42" customHeight="1">
+      <c r="A105" s="102" t="s">
+        <v>667</v>
+      </c>
+      <c r="B105" s="57" t="s">
+        <v>707</v>
+      </c>
+      <c r="C105" s="33" t="s">
+        <v>708</v>
+      </c>
+      <c r="D105" s="33" t="s">
+        <v>709</v>
+      </c>
+      <c r="E105" s="33" t="s">
+        <v>536</v>
+      </c>
+      <c r="F105" s="117" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="42" customHeight="1">
+      <c r="A106" s="103" t="s">
+        <v>667</v>
+      </c>
+      <c r="B106" s="58" t="s">
+        <v>707</v>
+      </c>
+      <c r="C106" s="39" t="s">
+        <v>977</v>
+      </c>
+      <c r="D106" s="39" t="s">
+        <v>978</v>
+      </c>
+      <c r="E106" s="39" t="s">
+        <v>536</v>
+      </c>
+      <c r="F106" s="118" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="30" customHeight="1">
+      <c r="A107" s="155" t="s">
+        <v>984</v>
+      </c>
+      <c r="B107" s="156"/>
+      <c r="C107" s="156"/>
+      <c r="D107" s="156"/>
+      <c r="E107" s="156"/>
+      <c r="F107" s="157"/>
+    </row>
+    <row r="108" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A108" s="101" t="s">
+        <v>710</v>
+      </c>
+      <c r="B108" s="56" t="s">
+        <v>497</v>
+      </c>
+      <c r="C108" s="10" t="s">
+        <v>603</v>
+      </c>
+      <c r="D108" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="E108" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F108" s="116" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A109" s="105" t="s">
+        <v>710</v>
+      </c>
+      <c r="B109" s="60" t="s">
+        <v>499</v>
+      </c>
+      <c r="C109" s="61" t="s">
+        <v>712</v>
+      </c>
+      <c r="D109" s="61" t="s">
+        <v>713</v>
+      </c>
+      <c r="E109" s="61" t="s">
+        <v>502</v>
+      </c>
+      <c r="F109" s="120" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="30" customHeight="1">
+      <c r="A110" s="105" t="s">
+        <v>710</v>
+      </c>
+      <c r="B110" s="60" t="s">
+        <v>715</v>
+      </c>
+      <c r="C110" s="61" t="s">
+        <v>716</v>
+      </c>
+      <c r="D110" s="61" t="s">
+        <v>717</v>
+      </c>
+      <c r="E110" s="61" t="s">
+        <v>718</v>
+      </c>
+      <c r="F110" s="120" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A111" s="105" t="s">
+        <v>710</v>
+      </c>
+      <c r="B111" s="60" t="s">
+        <v>618</v>
+      </c>
+      <c r="C111" s="61" t="s">
+        <v>720</v>
+      </c>
+      <c r="D111" s="61" t="s">
+        <v>721</v>
+      </c>
+      <c r="E111" s="61" t="s">
+        <v>722</v>
+      </c>
+      <c r="F111" s="120" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="42" customHeight="1">
+      <c r="A112" s="105" t="s">
+        <v>710</v>
+      </c>
+      <c r="B112" s="207" t="s">
+        <v>707</v>
+      </c>
+      <c r="C112" s="61" t="s">
+        <v>950</v>
+      </c>
+      <c r="D112" s="61" t="s">
+        <v>951</v>
+      </c>
+      <c r="E112" s="61" t="s">
+        <v>952</v>
+      </c>
+      <c r="F112" s="120" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="45" customHeight="1">
+      <c r="A113" s="98" t="s">
+        <v>710</v>
+      </c>
+      <c r="B113" s="53" t="s">
+        <v>723</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>724</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>725</v>
+      </c>
+      <c r="E113" s="5" t="s">
+        <v>726</v>
+      </c>
+      <c r="F113" s="86" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A114" s="102" t="s">
+        <v>710</v>
+      </c>
+      <c r="B114" s="57" t="s">
+        <v>628</v>
+      </c>
+      <c r="C114" s="33" t="s">
+        <v>727</v>
+      </c>
+      <c r="D114" s="33" t="s">
+        <v>728</v>
+      </c>
+      <c r="E114" s="33" t="s">
+        <v>729</v>
+      </c>
+      <c r="F114" s="117" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="21.75" customHeight="1">
+      <c r="A115" s="105" t="s">
+        <v>710</v>
+      </c>
+      <c r="B115" s="60" t="s">
+        <v>730</v>
+      </c>
+      <c r="C115" s="61" t="s">
+        <v>731</v>
+      </c>
+      <c r="D115" s="61" t="s">
+        <v>732</v>
+      </c>
+      <c r="E115" s="61" t="s">
+        <v>482</v>
+      </c>
+      <c r="F115" s="120" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A116" s="106" t="s">
+        <v>710</v>
+      </c>
+      <c r="B116" s="63" t="s">
+        <v>734</v>
+      </c>
+      <c r="C116" s="20" t="s">
+        <v>735</v>
+      </c>
+      <c r="D116" s="20" t="s">
+        <v>736</v>
+      </c>
+      <c r="E116" s="20" t="s">
+        <v>531</v>
+      </c>
+      <c r="F116" s="121" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A117" s="109" t="s">
+        <v>710</v>
+      </c>
+      <c r="B117" s="65" t="s">
+        <v>582</v>
+      </c>
+      <c r="C117" s="42" t="s">
+        <v>737</v>
+      </c>
+      <c r="D117" s="42" t="s">
+        <v>738</v>
+      </c>
+      <c r="E117" s="42" t="s">
+        <v>739</v>
+      </c>
+      <c r="F117" s="124" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="30" customHeight="1">
+      <c r="A118" s="99" t="s">
+        <v>710</v>
+      </c>
+      <c r="B118" s="54" t="s">
+        <v>740</v>
+      </c>
+      <c r="C118" s="15" t="s">
+        <v>741</v>
+      </c>
+      <c r="D118" s="15" t="s">
+        <v>742</v>
+      </c>
+      <c r="E118" s="15" t="s">
+        <v>539</v>
+      </c>
+      <c r="F118" s="85" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A119" s="103" t="s">
+        <v>710</v>
+      </c>
+      <c r="B119" s="58" t="s">
+        <v>743</v>
+      </c>
+      <c r="C119" s="39" t="s">
+        <v>744</v>
+      </c>
+      <c r="D119" s="39" t="s">
+        <v>745</v>
+      </c>
+      <c r="E119" s="39" t="s">
+        <v>746</v>
+      </c>
+      <c r="F119" s="118" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="30" customHeight="1">
+      <c r="A120" s="101" t="s">
+        <v>710</v>
+      </c>
+      <c r="B120" s="56" t="s">
+        <v>747</v>
+      </c>
+      <c r="C120" s="10" t="s">
+        <v>748</v>
+      </c>
+      <c r="D120" s="10" t="s">
+        <v>749</v>
+      </c>
+      <c r="E120" s="10" t="s">
+        <v>601</v>
+      </c>
+      <c r="F120" s="116" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A121" s="103" t="s">
+        <v>710</v>
+      </c>
+      <c r="B121" s="58" t="s">
+        <v>541</v>
+      </c>
+      <c r="C121" s="39" t="s">
+        <v>750</v>
+      </c>
+      <c r="D121" s="39" t="s">
+        <v>751</v>
+      </c>
+      <c r="E121" s="39" t="s">
+        <v>544</v>
+      </c>
+      <c r="F121" s="118" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A122" s="103" t="s">
+        <v>710</v>
+      </c>
+      <c r="B122" s="58" t="s">
+        <v>541</v>
+      </c>
+      <c r="C122" s="39" t="s">
+        <v>752</v>
+      </c>
+      <c r="D122" s="39" t="s">
+        <v>753</v>
+      </c>
+      <c r="E122" s="39" t="s">
+        <v>544</v>
+      </c>
+      <c r="F122" s="118" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="42" customHeight="1">
+      <c r="A123" s="104" t="s">
+        <v>710</v>
+      </c>
+      <c r="B123" s="59" t="s">
+        <v>541</v>
+      </c>
+      <c r="C123" s="47" t="s">
+        <v>980</v>
+      </c>
+      <c r="D123" s="47" t="s">
+        <v>981</v>
+      </c>
+      <c r="E123" s="47" t="s">
+        <v>544</v>
+      </c>
+      <c r="F123" s="119" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="30" customHeight="1">
+      <c r="A124" s="158" t="s">
+        <v>756</v>
+      </c>
+      <c r="B124" s="159"/>
+      <c r="C124" s="159"/>
+      <c r="D124" s="159"/>
+      <c r="E124" s="159"/>
+      <c r="F124" s="160"/>
+    </row>
+    <row r="125" spans="1:6" ht="28">
+      <c r="A125" s="101" t="s">
+        <v>757</v>
+      </c>
+      <c r="B125" s="56" t="s">
+        <v>758</v>
+      </c>
+      <c r="C125" s="10" t="s">
         <v>668</v>
       </c>
-      <c r="D74" s="47" t="s">
-        <v>669</v>
-      </c>
-      <c r="E74" s="47" t="s">
-        <v>660</v>
-      </c>
-      <c r="F74" s="119" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="30" customHeight="1">
-      <c r="A75" s="106" t="s">
-        <v>631</v>
-      </c>
-      <c r="B75" s="63" t="s">
-        <v>671</v>
-      </c>
-      <c r="C75" s="20" t="s">
-        <v>672</v>
-      </c>
-      <c r="D75" s="20" t="s">
-        <v>673</v>
-      </c>
-      <c r="E75" s="20" t="s">
-        <v>674</v>
-      </c>
-      <c r="F75" s="121" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="30" customHeight="1">
-      <c r="A76" s="102" t="s">
-        <v>631</v>
-      </c>
-      <c r="B76" s="57" t="s">
-        <v>676</v>
-      </c>
-      <c r="C76" s="33" t="s">
+      <c r="D125" s="10" t="s">
+        <v>759</v>
+      </c>
+      <c r="E125" s="10" t="s">
+        <v>551</v>
+      </c>
+      <c r="F125" s="116" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="28">
+      <c r="A126" s="100" t="s">
+        <v>757</v>
+      </c>
+      <c r="B126" s="55" t="s">
+        <v>760</v>
+      </c>
+      <c r="C126" s="50" t="s">
+        <v>761</v>
+      </c>
+      <c r="D126" s="50" t="s">
+        <v>762</v>
+      </c>
+      <c r="E126" s="50" t="s">
         <v>677</v>
       </c>
-      <c r="D76" s="33" t="s">
-        <v>678</v>
-      </c>
-      <c r="E76" s="33" t="s">
-        <v>679</v>
-      </c>
-      <c r="F76" s="117" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="30" customHeight="1">
-      <c r="A77" s="107" t="s">
-        <v>631</v>
-      </c>
-      <c r="B77" s="64" t="s">
-        <v>561</v>
-      </c>
-      <c r="C77" s="36" t="s">
-        <v>680</v>
-      </c>
-      <c r="D77" s="36" t="s">
-        <v>681</v>
-      </c>
-      <c r="E77" s="36" t="s">
-        <v>210</v>
-      </c>
-      <c r="F77" s="122" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A78" s="101" t="s">
-        <v>631</v>
-      </c>
-      <c r="B78" s="56" t="s">
-        <v>682</v>
-      </c>
-      <c r="C78" s="10" t="s">
-        <v>683</v>
-      </c>
-      <c r="D78" s="10" t="s">
-        <v>684</v>
-      </c>
-      <c r="E78" s="10" t="s">
-        <v>559</v>
-      </c>
-      <c r="F78" s="116" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="30" customHeight="1">
-      <c r="A79" s="101" t="s">
-        <v>631</v>
-      </c>
-      <c r="B79" s="56" t="s">
-        <v>627</v>
-      </c>
-      <c r="C79" s="10" t="s">
-        <v>685</v>
-      </c>
-      <c r="D79" s="10" t="s">
-        <v>686</v>
-      </c>
-      <c r="E79" s="10" t="s">
-        <v>629</v>
-      </c>
-      <c r="F79" s="116" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="30" customHeight="1">
-      <c r="A80" s="103" t="s">
-        <v>631</v>
-      </c>
-      <c r="B80" s="58" t="s">
-        <v>568</v>
-      </c>
-      <c r="C80" s="39" t="s">
-        <v>687</v>
-      </c>
-      <c r="D80" s="39" t="s">
-        <v>688</v>
-      </c>
-      <c r="E80" s="39" t="s">
-        <v>571</v>
-      </c>
-      <c r="F80" s="118" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="30" customHeight="1">
-      <c r="A81" s="103" t="s">
-        <v>631</v>
-      </c>
-      <c r="B81" s="58" t="s">
-        <v>568</v>
-      </c>
-      <c r="C81" s="39" t="s">
-        <v>690</v>
-      </c>
-      <c r="D81" s="39" t="s">
-        <v>691</v>
-      </c>
-      <c r="E81" s="39" t="s">
-        <v>571</v>
-      </c>
-      <c r="F81" s="118" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="30" customHeight="1">
-      <c r="A82" s="103" t="s">
-        <v>631</v>
-      </c>
-      <c r="B82" s="58" t="s">
-        <v>568</v>
-      </c>
-      <c r="C82" s="39" t="s">
-        <v>693</v>
-      </c>
-      <c r="D82" s="39" t="s">
-        <v>694</v>
-      </c>
-      <c r="E82" s="39" t="s">
-        <v>571</v>
-      </c>
-      <c r="F82" s="118" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A83" s="108" t="s">
-        <v>631</v>
-      </c>
-      <c r="B83" s="89" t="s">
-        <v>568</v>
-      </c>
-      <c r="C83" s="90" t="s">
-        <v>954</v>
-      </c>
-      <c r="D83" s="95" t="s">
-        <v>955</v>
-      </c>
-      <c r="E83" s="90" t="s">
-        <v>956</v>
-      </c>
-      <c r="F83" s="123" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A84" s="163" t="s">
-        <v>696</v>
-      </c>
-      <c r="B84" s="164"/>
-      <c r="C84" s="164"/>
-      <c r="D84" s="164"/>
-      <c r="E84" s="164"/>
-      <c r="F84" s="165"/>
-    </row>
-    <row r="85" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A85" s="101" t="s">
-        <v>697</v>
-      </c>
-      <c r="B85" s="56" t="s">
-        <v>517</v>
-      </c>
-      <c r="C85" s="10" t="s">
-        <v>698</v>
-      </c>
-      <c r="D85" s="10"/>
-      <c r="E85" s="10" t="s">
-        <v>579</v>
-      </c>
-      <c r="F85" s="116" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A86" s="100" t="s">
-        <v>697</v>
-      </c>
-      <c r="B86" s="55" t="s">
-        <v>580</v>
-      </c>
-      <c r="C86" s="50" t="s">
-        <v>699</v>
-      </c>
-      <c r="D86" s="50" t="s">
-        <v>700</v>
-      </c>
-      <c r="E86" s="50" t="s">
-        <v>583</v>
-      </c>
-      <c r="F86" s="115" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="30" customHeight="1">
-      <c r="A87" s="100" t="s">
-        <v>697</v>
-      </c>
-      <c r="B87" s="55" t="s">
-        <v>585</v>
-      </c>
-      <c r="C87" s="50" t="s">
-        <v>702</v>
-      </c>
-      <c r="D87" s="50" t="s">
-        <v>703</v>
-      </c>
-      <c r="E87" s="50" t="s">
-        <v>588</v>
-      </c>
-      <c r="F87" s="115" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A88" s="101" t="s">
-        <v>697</v>
-      </c>
-      <c r="B88" s="56" t="s">
-        <v>590</v>
-      </c>
-      <c r="C88" s="10" t="s">
-        <v>705</v>
-      </c>
-      <c r="D88" s="10" t="s">
-        <v>706</v>
-      </c>
-      <c r="E88" s="10" t="s">
-        <v>707</v>
-      </c>
-      <c r="F88" s="116" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="30" customHeight="1">
-      <c r="A89" s="99" t="s">
-        <v>697</v>
-      </c>
-      <c r="B89" s="54" t="s">
-        <v>594</v>
-      </c>
-      <c r="C89" s="15" t="s">
-        <v>709</v>
-      </c>
-      <c r="D89" s="15" t="s">
-        <v>710</v>
-      </c>
-      <c r="E89" s="15" t="s">
-        <v>220</v>
-      </c>
-      <c r="F89" s="85" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="30" customHeight="1">
-      <c r="A90" s="105" t="s">
-        <v>697</v>
-      </c>
-      <c r="B90" s="60" t="s">
-        <v>711</v>
-      </c>
-      <c r="C90" s="61" t="s">
-        <v>712</v>
-      </c>
-      <c r="D90" s="61" t="s">
-        <v>713</v>
-      </c>
-      <c r="E90" s="61" t="s">
-        <v>714</v>
-      </c>
-      <c r="F90" s="120" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A91" s="105" t="s">
-        <v>697</v>
-      </c>
-      <c r="B91" s="60" t="s">
-        <v>716</v>
-      </c>
-      <c r="C91" s="61" t="s">
-        <v>717</v>
-      </c>
-      <c r="D91" s="61" t="s">
-        <v>718</v>
-      </c>
-      <c r="E91" s="61" t="s">
-        <v>637</v>
-      </c>
-      <c r="F91" s="120" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A92" s="105" t="s">
-        <v>697</v>
-      </c>
-      <c r="B92" s="60" t="s">
-        <v>720</v>
-      </c>
-      <c r="C92" s="61" t="s">
-        <v>721</v>
-      </c>
-      <c r="D92" s="61" t="s">
-        <v>722</v>
-      </c>
-      <c r="E92" s="61" t="s">
-        <v>723</v>
-      </c>
-      <c r="F92" s="120" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="30" customHeight="1">
-      <c r="A93" s="106" t="s">
-        <v>697</v>
-      </c>
-      <c r="B93" s="63" t="s">
-        <v>725</v>
-      </c>
-      <c r="C93" s="20" t="s">
-        <v>726</v>
-      </c>
-      <c r="D93" s="20" t="s">
-        <v>727</v>
-      </c>
-      <c r="E93" s="20" t="s">
-        <v>728</v>
-      </c>
-      <c r="F93" s="121" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="30" customHeight="1">
-      <c r="A94" s="105" t="s">
-        <v>697</v>
-      </c>
-      <c r="B94" s="60" t="s">
-        <v>729</v>
-      </c>
-      <c r="C94" s="61" t="s">
-        <v>730</v>
-      </c>
-      <c r="D94" s="61" t="s">
-        <v>731</v>
-      </c>
-      <c r="E94" s="61" t="s">
-        <v>111</v>
-      </c>
-      <c r="F94" s="120" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="30" customHeight="1">
-      <c r="A95" s="109" t="s">
-        <v>697</v>
-      </c>
-      <c r="B95" s="65" t="s">
-        <v>732</v>
-      </c>
-      <c r="C95" s="42" t="s">
-        <v>733</v>
-      </c>
-      <c r="D95" s="42" t="s">
-        <v>734</v>
-      </c>
-      <c r="E95" s="42" t="s">
-        <v>735</v>
-      </c>
-      <c r="F95" s="124" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A96" s="111" t="s">
-        <v>697</v>
-      </c>
-      <c r="B96" s="93" t="s">
-        <v>958</v>
-      </c>
-      <c r="C96" s="94" t="s">
-        <v>959</v>
-      </c>
-      <c r="D96" s="94" t="s">
-        <v>960</v>
-      </c>
-      <c r="E96" s="94" t="s">
-        <v>961</v>
-      </c>
-      <c r="F96" s="126" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="45" customHeight="1">
-      <c r="A97" s="101" t="s">
-        <v>697</v>
-      </c>
-      <c r="B97" s="128" t="s">
-        <v>968</v>
-      </c>
-      <c r="C97" s="10" t="s">
-        <v>967</v>
-      </c>
-      <c r="D97" s="10"/>
-      <c r="E97" s="10" t="s">
-        <v>629</v>
-      </c>
-      <c r="F97" s="116" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="30" customHeight="1">
-      <c r="A98" s="102" t="s">
-        <v>697</v>
-      </c>
-      <c r="B98" s="57" t="s">
-        <v>737</v>
-      </c>
-      <c r="C98" s="33" t="s">
-        <v>738</v>
-      </c>
-      <c r="D98" s="33" t="s">
-        <v>739</v>
-      </c>
-      <c r="E98" s="33" t="s">
-        <v>559</v>
-      </c>
-      <c r="F98" s="117" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A99" s="103" t="s">
-        <v>697</v>
-      </c>
-      <c r="B99" s="58" t="s">
-        <v>737</v>
-      </c>
-      <c r="C99" s="39" t="s">
-        <v>740</v>
-      </c>
-      <c r="D99" s="39" t="s">
-        <v>741</v>
-      </c>
-      <c r="E99" s="39" t="s">
-        <v>559</v>
-      </c>
-      <c r="F99" s="118" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A100" s="163" t="s">
-        <v>743</v>
-      </c>
-      <c r="B100" s="164"/>
-      <c r="C100" s="164"/>
-      <c r="D100" s="164"/>
-      <c r="E100" s="164"/>
-      <c r="F100" s="165"/>
-    </row>
-    <row r="101" spans="1:6" ht="30" customHeight="1">
-      <c r="A101" s="101" t="s">
-        <v>744</v>
-      </c>
-      <c r="B101" s="56" t="s">
-        <v>517</v>
-      </c>
-      <c r="C101" s="10" t="s">
-        <v>632</v>
-      </c>
-      <c r="D101" s="10" t="s">
-        <v>745</v>
-      </c>
-      <c r="E101" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F101" s="116" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" ht="30" customHeight="1">
-      <c r="A102" s="105" t="s">
-        <v>744</v>
-      </c>
-      <c r="B102" s="60" t="s">
-        <v>519</v>
-      </c>
-      <c r="C102" s="61" t="s">
-        <v>746</v>
-      </c>
-      <c r="D102" s="61" t="s">
-        <v>747</v>
-      </c>
-      <c r="E102" s="61" t="s">
-        <v>522</v>
-      </c>
-      <c r="F102" s="120" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" ht="45" customHeight="1">
-      <c r="A103" s="105" t="s">
-        <v>744</v>
-      </c>
-      <c r="B103" s="60" t="s">
-        <v>749</v>
-      </c>
-      <c r="C103" s="61" t="s">
-        <v>750</v>
-      </c>
-      <c r="D103" s="61" t="s">
-        <v>751</v>
-      </c>
-      <c r="E103" s="61" t="s">
-        <v>752</v>
-      </c>
-      <c r="F103" s="120" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A104" s="105" t="s">
-        <v>744</v>
-      </c>
-      <c r="B104" s="60" t="s">
-        <v>647</v>
-      </c>
-      <c r="C104" s="61" t="s">
-        <v>754</v>
-      </c>
-      <c r="D104" s="61" t="s">
-        <v>755</v>
-      </c>
-      <c r="E104" s="61" t="s">
-        <v>756</v>
-      </c>
-      <c r="F104" s="120" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A105" s="98" t="s">
-        <v>744</v>
-      </c>
-      <c r="B105" s="53" t="s">
+      <c r="F126" s="115" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="28">
+      <c r="A127" s="100" t="s">
         <v>757</v>
       </c>
-      <c r="C105" s="5" t="s">
-        <v>758</v>
-      </c>
-      <c r="D105" s="5" t="s">
-        <v>759</v>
-      </c>
-      <c r="E105" s="5" t="s">
-        <v>760</v>
-      </c>
-      <c r="F105" s="86" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" ht="30" customHeight="1">
-      <c r="A106" s="102" t="s">
-        <v>744</v>
-      </c>
-      <c r="B106" s="57" t="s">
-        <v>657</v>
-      </c>
-      <c r="C106" s="33" t="s">
-        <v>761</v>
-      </c>
-      <c r="D106" s="33" t="s">
-        <v>762</v>
-      </c>
-      <c r="E106" s="33" t="s">
-        <v>763</v>
-      </c>
-      <c r="F106" s="117" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A107" s="105" t="s">
-        <v>744</v>
-      </c>
-      <c r="B107" s="60" t="s">
+      <c r="B127" s="55" t="s">
         <v>764</v>
       </c>
-      <c r="C107" s="61" t="s">
+      <c r="C127" s="50" t="s">
         <v>765</v>
       </c>
-      <c r="D107" s="61" t="s">
+      <c r="D127" s="50" t="s">
         <v>766</v>
       </c>
-      <c r="E107" s="61" t="s">
-        <v>495</v>
-      </c>
-      <c r="F107" s="120" t="s">
+      <c r="E127" s="50" t="s">
         <v>767</v>
       </c>
-    </row>
-    <row r="108" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A108" s="106" t="s">
-        <v>744</v>
-      </c>
-      <c r="B108" s="63" t="s">
+      <c r="F127" s="115" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="28">
+      <c r="A128" s="100" t="s">
+        <v>757</v>
+      </c>
+      <c r="B128" s="55" t="s">
         <v>768</v>
       </c>
-      <c r="C108" s="20" t="s">
+      <c r="C128" s="50" t="s">
         <v>769</v>
       </c>
-      <c r="D108" s="20" t="s">
+      <c r="D128" s="50" t="s">
         <v>770</v>
       </c>
-      <c r="E108" s="20" t="s">
-        <v>551</v>
-      </c>
-      <c r="F108" s="121" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A109" s="109" t="s">
-        <v>744</v>
-      </c>
-      <c r="B109" s="65" t="s">
-        <v>610</v>
-      </c>
-      <c r="C109" s="42" t="s">
+      <c r="E128" s="50" t="s">
         <v>771</v>
       </c>
-      <c r="D109" s="42" t="s">
+      <c r="F128" s="115" t="s">
         <v>772</v>
       </c>
-      <c r="E109" s="42" t="s">
+    </row>
+    <row r="129" spans="1:6" ht="28">
+      <c r="A129" s="99" t="s">
+        <v>757</v>
+      </c>
+      <c r="B129" s="54" t="s">
         <v>773</v>
       </c>
-      <c r="F109" s="124" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" ht="30" customHeight="1">
-      <c r="A110" s="99" t="s">
-        <v>744</v>
-      </c>
-      <c r="B110" s="54" t="s">
+      <c r="C129" s="15" t="s">
         <v>774</v>
       </c>
-      <c r="C110" s="15" t="s">
+      <c r="D129" s="15" t="s">
         <v>775</v>
       </c>
-      <c r="D110" s="15" t="s">
+      <c r="E129" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="F129" s="85" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="28">
+      <c r="A130" s="98" t="s">
+        <v>757</v>
+      </c>
+      <c r="B130" s="53" t="s">
         <v>776</v>
       </c>
-      <c r="E110" s="15" t="s">
-        <v>564</v>
-      </c>
-      <c r="F110" s="85" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A111" s="103" t="s">
-        <v>744</v>
-      </c>
-      <c r="B111" s="58" t="s">
+      <c r="C130" s="5" t="s">
         <v>777</v>
       </c>
-      <c r="C111" s="39" t="s">
+      <c r="D130" s="5" t="s">
         <v>778</v>
       </c>
-      <c r="D111" s="39" t="s">
+      <c r="E130" s="5" t="s">
         <v>779</v>
       </c>
-      <c r="E111" s="39" t="s">
+      <c r="F130" s="114" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" ht="28">
+      <c r="A131" s="99" t="s">
+        <v>757</v>
+      </c>
+      <c r="B131" s="54" t="s">
         <v>780</v>
       </c>
-      <c r="F111" s="118" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="30" customHeight="1">
-      <c r="A112" s="101" t="s">
-        <v>744</v>
-      </c>
-      <c r="B112" s="56" t="s">
+      <c r="C131" s="15" t="s">
         <v>781</v>
       </c>
-      <c r="C112" s="10" t="s">
+      <c r="D131" s="15" t="s">
         <v>782</v>
       </c>
-      <c r="D112" s="10" t="s">
+      <c r="E131" s="15" t="s">
         <v>783</v>
       </c>
-      <c r="E112" s="10" t="s">
-        <v>629</v>
-      </c>
-      <c r="F112" s="116" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" ht="45" customHeight="1">
-      <c r="A113" s="103" t="s">
-        <v>744</v>
-      </c>
-      <c r="B113" s="58" t="s">
-        <v>568</v>
-      </c>
-      <c r="C113" s="39" t="s">
+      <c r="F131" s="113" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="28">
+      <c r="A132" s="98" t="s">
+        <v>757</v>
+      </c>
+      <c r="B132" s="53" t="s">
         <v>784</v>
       </c>
-      <c r="D113" s="39" t="s">
+      <c r="C132" s="5" t="s">
         <v>785</v>
       </c>
-      <c r="E113" s="39" t="s">
-        <v>571</v>
-      </c>
-      <c r="F113" s="118" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A114" s="103" t="s">
-        <v>744</v>
-      </c>
-      <c r="B114" s="58" t="s">
-        <v>568</v>
-      </c>
-      <c r="C114" s="39" t="s">
+      <c r="D132" s="5" t="s">
         <v>786</v>
       </c>
-      <c r="D114" s="39" t="s">
+      <c r="E132" s="5" t="s">
         <v>787</v>
       </c>
-      <c r="E114" s="39" t="s">
-        <v>571</v>
-      </c>
-      <c r="F114" s="118" t="s">
+      <c r="F132" s="114" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="29" thickBot="1">
+      <c r="A133" s="112" t="s">
+        <v>757</v>
+      </c>
+      <c r="B133" s="96" t="s">
+        <v>494</v>
+      </c>
+      <c r="C133" s="97" t="s">
         <v>788</v>
       </c>
-    </row>
-    <row r="115" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A115" s="104" t="s">
-        <v>744</v>
-      </c>
-      <c r="B115" s="59" t="s">
-        <v>568</v>
-      </c>
-      <c r="C115" s="47" t="s">
+      <c r="D133" s="97" t="s">
         <v>789</v>
       </c>
-      <c r="D115" s="47" t="s">
+      <c r="E133" s="97" t="s">
         <v>790</v>
       </c>
-      <c r="E115" s="47" t="s">
-        <v>571</v>
-      </c>
-      <c r="F115" s="119" t="s">
+      <c r="F133" s="127" t="s">
         <v>791</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A116" s="166" t="s">
-        <v>792</v>
-      </c>
-      <c r="B116" s="167"/>
-      <c r="C116" s="167"/>
-      <c r="D116" s="167"/>
-      <c r="E116" s="167"/>
-      <c r="F116" s="168"/>
-    </row>
-    <row r="117" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A117" s="101" t="s">
-        <v>793</v>
-      </c>
-      <c r="B117" s="56" t="s">
-        <v>794</v>
-      </c>
-      <c r="C117" s="10" t="s">
-        <v>698</v>
-      </c>
-      <c r="D117" s="10" t="s">
-        <v>795</v>
-      </c>
-      <c r="E117" s="10" t="s">
-        <v>579</v>
-      </c>
-      <c r="F117" s="116" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" ht="30" customHeight="1">
-      <c r="A118" s="100" t="s">
-        <v>793</v>
-      </c>
-      <c r="B118" s="55" t="s">
-        <v>796</v>
-      </c>
-      <c r="C118" s="50" t="s">
-        <v>797</v>
-      </c>
-      <c r="D118" s="50" t="s">
-        <v>798</v>
-      </c>
-      <c r="E118" s="50" t="s">
-        <v>707</v>
-      </c>
-      <c r="F118" s="115" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A119" s="100" t="s">
-        <v>793</v>
-      </c>
-      <c r="B119" s="55" t="s">
-        <v>800</v>
-      </c>
-      <c r="C119" s="50" t="s">
-        <v>801</v>
-      </c>
-      <c r="D119" s="50" t="s">
-        <v>802</v>
-      </c>
-      <c r="E119" s="50" t="s">
-        <v>803</v>
-      </c>
-      <c r="F119" s="115" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" ht="30" customHeight="1">
-      <c r="A120" s="100" t="s">
-        <v>793</v>
-      </c>
-      <c r="B120" s="55" t="s">
-        <v>804</v>
-      </c>
-      <c r="C120" s="50" t="s">
-        <v>805</v>
-      </c>
-      <c r="D120" s="50" t="s">
-        <v>806</v>
-      </c>
-      <c r="E120" s="50" t="s">
-        <v>807</v>
-      </c>
-      <c r="F120" s="115" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A121" s="99" t="s">
-        <v>793</v>
-      </c>
-      <c r="B121" s="54" t="s">
-        <v>809</v>
-      </c>
-      <c r="C121" s="15" t="s">
-        <v>810</v>
-      </c>
-      <c r="D121" s="15" t="s">
-        <v>811</v>
-      </c>
-      <c r="E121" s="15" t="s">
-        <v>408</v>
-      </c>
-      <c r="F121" s="85" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A122" s="98" t="s">
-        <v>793</v>
-      </c>
-      <c r="B122" s="53" t="s">
-        <v>812</v>
-      </c>
-      <c r="C122" s="5" t="s">
-        <v>813</v>
-      </c>
-      <c r="D122" s="5" t="s">
-        <v>814</v>
-      </c>
-      <c r="E122" s="5" t="s">
-        <v>815</v>
-      </c>
-      <c r="F122" s="114" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A123" s="99" t="s">
-        <v>793</v>
-      </c>
-      <c r="B123" s="54" t="s">
-        <v>816</v>
-      </c>
-      <c r="C123" s="15" t="s">
-        <v>817</v>
-      </c>
-      <c r="D123" s="15" t="s">
-        <v>818</v>
-      </c>
-      <c r="E123" s="15" t="s">
-        <v>819</v>
-      </c>
-      <c r="F123" s="113" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A124" s="98" t="s">
-        <v>793</v>
-      </c>
-      <c r="B124" s="53" t="s">
-        <v>820</v>
-      </c>
-      <c r="C124" s="5" t="s">
-        <v>821</v>
-      </c>
-      <c r="D124" s="5" t="s">
-        <v>822</v>
-      </c>
-      <c r="E124" s="5" t="s">
-        <v>823</v>
-      </c>
-      <c r="F124" s="114" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" ht="29" thickBot="1">
-      <c r="A125" s="112" t="s">
-        <v>793</v>
-      </c>
-      <c r="B125" s="96" t="s">
-        <v>513</v>
-      </c>
-      <c r="C125" s="97" t="s">
-        <v>824</v>
-      </c>
-      <c r="D125" s="97" t="s">
-        <v>825</v>
-      </c>
-      <c r="E125" s="97" t="s">
-        <v>826</v>
-      </c>
-      <c r="F125" s="127" t="s">
-        <v>827</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A49:F49"/>
-    <mergeCell ref="A64:F64"/>
-    <mergeCell ref="A84:F84"/>
-    <mergeCell ref="A100:F100"/>
-    <mergeCell ref="A116:F116"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A90:F90"/>
+    <mergeCell ref="A107:F107"/>
+    <mergeCell ref="A124:F124"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -18616,22 +18683,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="176" t="s">
+      <c r="A1" s="177" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="176"/>
-      <c r="C1" s="176"/>
-      <c r="D1" s="176"/>
-      <c r="E1" s="176"/>
+      <c r="B1" s="177"/>
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
     </row>
     <row r="3" spans="1:5" ht="24" customHeight="1">
-      <c r="A3" s="177" t="s">
+      <c r="A3" s="178" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="177"/>
-      <c r="C3" s="177"/>
-      <c r="D3" s="177"/>
-      <c r="E3" s="177"/>
+      <c r="B3" s="178"/>
+      <c r="C3" s="178"/>
+      <c r="D3" s="178"/>
+      <c r="E3" s="178"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="12" t="s">
@@ -18723,13 +18790,13 @@
         <v>53</v>
       </c>
       <c r="B9" s="69" t="s">
-        <v>828</v>
+        <v>792</v>
       </c>
       <c r="C9" s="67" t="s">
-        <v>829</v>
+        <v>793</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>830</v>
+        <v>794</v>
       </c>
       <c r="E9" s="68" t="s">
         <v>185</v>
@@ -18740,13 +18807,13 @@
         <v>53</v>
       </c>
       <c r="B10" s="69" t="s">
-        <v>831</v>
+        <v>795</v>
       </c>
       <c r="C10" s="67" t="s">
         <v>207</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>832</v>
+        <v>796</v>
       </c>
       <c r="E10" s="68" t="s">
         <v>61</v>
@@ -18787,13 +18854,13 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="24" customHeight="1">
-      <c r="A14" s="173" t="s">
+      <c r="A14" s="174" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="173"/>
-      <c r="C14" s="173"/>
-      <c r="D14" s="173"/>
-      <c r="E14" s="173"/>
+      <c r="B14" s="174"/>
+      <c r="C14" s="174"/>
+      <c r="D14" s="174"/>
+      <c r="E14" s="174"/>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="12" t="s">
@@ -18902,13 +18969,13 @@
         <v>90</v>
       </c>
       <c r="B21" s="66" t="s">
-        <v>833</v>
+        <v>797</v>
       </c>
       <c r="C21" s="67" t="s">
-        <v>834</v>
+        <v>798</v>
       </c>
       <c r="D21" s="66" t="s">
-        <v>835</v>
+        <v>799</v>
       </c>
       <c r="E21" s="68" t="s">
         <v>235</v>
@@ -18932,13 +18999,13 @@
       </c>
     </row>
     <row r="24" spans="1:5" ht="24" customHeight="1">
-      <c r="A24" s="175" t="s">
+      <c r="A24" s="176" t="s">
         <v>104</v>
       </c>
-      <c r="B24" s="175"/>
-      <c r="C24" s="175"/>
-      <c r="D24" s="175"/>
-      <c r="E24" s="175"/>
+      <c r="B24" s="176"/>
+      <c r="C24" s="176"/>
+      <c r="D24" s="176"/>
+      <c r="E24" s="176"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="12" t="s">
@@ -19098,13 +19165,13 @@
         <v>67</v>
       </c>
       <c r="B34" s="73" t="s">
-        <v>836</v>
+        <v>800</v>
       </c>
       <c r="C34" s="71" t="s">
         <v>273</v>
       </c>
       <c r="D34" s="70" t="s">
-        <v>837</v>
+        <v>801</v>
       </c>
       <c r="E34" s="72" t="s">
         <v>103</v>
@@ -19156,24 +19223,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
-      <c r="A1" s="178" t="s">
-        <v>878</v>
-      </c>
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="179"/>
-      <c r="F1" s="180"/>
+      <c r="A1" s="191" t="s">
+        <v>842</v>
+      </c>
+      <c r="B1" s="192"/>
+      <c r="C1" s="192"/>
+      <c r="D1" s="192"/>
+      <c r="E1" s="192"/>
+      <c r="F1" s="193"/>
     </row>
     <row r="2" spans="1:6" ht="34" customHeight="1">
-      <c r="A2" s="181" t="s">
-        <v>879</v>
-      </c>
-      <c r="B2" s="182"/>
-      <c r="C2" s="182"/>
-      <c r="D2" s="182"/>
-      <c r="E2" s="182"/>
-      <c r="F2" s="183"/>
+      <c r="A2" s="194" t="s">
+        <v>843</v>
+      </c>
+      <c r="B2" s="195"/>
+      <c r="C2" s="195"/>
+      <c r="D2" s="195"/>
+      <c r="E2" s="195"/>
+      <c r="F2" s="196"/>
     </row>
     <row r="3" spans="1:6" ht="19.5" customHeight="1">
       <c r="A3" s="77" t="s">
@@ -19196,14 +19263,14 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A4" s="184" t="s">
+      <c r="A4" s="188" t="s">
         <v>146</v>
       </c>
-      <c r="B4" s="185"/>
-      <c r="C4" s="185"/>
-      <c r="D4" s="185"/>
-      <c r="E4" s="185"/>
-      <c r="F4" s="186"/>
+      <c r="B4" s="189"/>
+      <c r="C4" s="189"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="189"/>
+      <c r="F4" s="190"/>
     </row>
     <row r="5" spans="1:6" ht="30" customHeight="1">
       <c r="A5" s="78" t="s">
@@ -19267,19 +19334,19 @@
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1">
       <c r="A8" s="81" t="s">
-        <v>838</v>
+        <v>802</v>
       </c>
       <c r="B8" s="75">
         <v>4.5</v>
       </c>
       <c r="C8" s="76" t="s">
-        <v>839</v>
+        <v>803</v>
       </c>
       <c r="D8" s="75" t="s">
-        <v>840</v>
+        <v>804</v>
       </c>
       <c r="E8" s="76" t="s">
-        <v>841</v>
+        <v>805</v>
       </c>
       <c r="F8" s="87" t="s">
         <v>152</v>
@@ -19287,33 +19354,33 @@
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1">
       <c r="A9" s="82" t="s">
-        <v>842</v>
+        <v>806</v>
       </c>
       <c r="B9" s="68">
         <v>4.5</v>
       </c>
       <c r="C9" s="66" t="s">
-        <v>900</v>
+        <v>864</v>
       </c>
       <c r="D9" s="68" t="s">
         <v>107</v>
       </c>
       <c r="E9" s="66" t="s">
-        <v>901</v>
+        <v>865</v>
       </c>
       <c r="F9" s="88" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A10" s="184" t="s">
+      <c r="A10" s="188" t="s">
         <v>162</v>
       </c>
-      <c r="B10" s="185"/>
-      <c r="C10" s="185"/>
-      <c r="D10" s="185"/>
-      <c r="E10" s="185"/>
-      <c r="F10" s="186"/>
+      <c r="B10" s="189"/>
+      <c r="C10" s="189"/>
+      <c r="D10" s="189"/>
+      <c r="E10" s="189"/>
+      <c r="F10" s="190"/>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1">
       <c r="A11" s="78" t="s">
@@ -19377,53 +19444,53 @@
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1">
       <c r="A14" s="81" t="s">
-        <v>838</v>
+        <v>802</v>
       </c>
       <c r="B14" s="75">
         <v>4.8</v>
       </c>
       <c r="C14" s="76" t="s">
-        <v>843</v>
+        <v>807</v>
       </c>
       <c r="D14" s="75" t="s">
         <v>66</v>
       </c>
       <c r="E14" s="76" t="s">
-        <v>844</v>
+        <v>808</v>
       </c>
       <c r="F14" s="87" t="s">
-        <v>845</v>
+        <v>809</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="30" customHeight="1">
       <c r="A15" s="82" t="s">
-        <v>842</v>
+        <v>806</v>
       </c>
       <c r="B15" s="68">
         <v>4.5999999999999996</v>
       </c>
       <c r="C15" s="66" t="s">
-        <v>880</v>
+        <v>844</v>
       </c>
       <c r="D15" s="68" t="s">
         <v>111</v>
       </c>
       <c r="E15" s="66" t="s">
-        <v>881</v>
+        <v>845</v>
       </c>
       <c r="F15" s="88" t="s">
-        <v>882</v>
+        <v>846</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A16" s="184" t="s">
+      <c r="A16" s="188" t="s">
         <v>174</v>
       </c>
-      <c r="B16" s="185"/>
-      <c r="C16" s="185"/>
-      <c r="D16" s="185"/>
-      <c r="E16" s="185"/>
-      <c r="F16" s="186"/>
+      <c r="B16" s="189"/>
+      <c r="C16" s="189"/>
+      <c r="D16" s="189"/>
+      <c r="E16" s="189"/>
+      <c r="F16" s="190"/>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1">
       <c r="A17" s="78" t="s">
@@ -19493,13 +19560,13 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C20" s="76" t="s">
-        <v>902</v>
+        <v>866</v>
       </c>
       <c r="D20" s="75" t="s">
         <v>257</v>
       </c>
       <c r="E20" s="76" t="s">
-        <v>903</v>
+        <v>867</v>
       </c>
       <c r="F20" s="87" t="s">
         <v>303</v>
@@ -19507,33 +19574,33 @@
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
       <c r="A21" s="82" t="s">
-        <v>838</v>
+        <v>802</v>
       </c>
       <c r="B21" s="68">
         <v>4.3</v>
       </c>
       <c r="C21" s="66" t="s">
-        <v>846</v>
+        <v>810</v>
       </c>
       <c r="D21" s="68" t="s">
         <v>257</v>
       </c>
       <c r="E21" s="66" t="s">
-        <v>847</v>
+        <v>811</v>
       </c>
       <c r="F21" s="88" t="s">
-        <v>848</v>
+        <v>812</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A22" s="184" t="s">
+      <c r="A22" s="188" t="s">
         <v>188</v>
       </c>
-      <c r="B22" s="185"/>
-      <c r="C22" s="185"/>
-      <c r="D22" s="185"/>
-      <c r="E22" s="185"/>
-      <c r="F22" s="186"/>
+      <c r="B22" s="189"/>
+      <c r="C22" s="189"/>
+      <c r="D22" s="189"/>
+      <c r="E22" s="189"/>
+      <c r="F22" s="190"/>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1">
       <c r="A23" s="78" t="s">
@@ -19597,53 +19664,53 @@
     </row>
     <row r="26" spans="1:6" ht="30" customHeight="1">
       <c r="A26" s="81" t="s">
-        <v>838</v>
+        <v>802</v>
       </c>
       <c r="B26" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C26" s="76" t="s">
-        <v>849</v>
+        <v>813</v>
       </c>
       <c r="D26" s="75" t="s">
         <v>160</v>
       </c>
       <c r="E26" s="76" t="s">
-        <v>850</v>
+        <v>814</v>
       </c>
       <c r="F26" s="87" t="s">
-        <v>851</v>
+        <v>815</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="30" customHeight="1">
       <c r="A27" s="82" t="s">
-        <v>842</v>
+        <v>806</v>
       </c>
       <c r="B27" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C27" s="66" t="s">
-        <v>883</v>
+        <v>847</v>
       </c>
       <c r="D27" s="68" t="s">
         <v>220</v>
       </c>
       <c r="E27" s="66" t="s">
-        <v>884</v>
+        <v>848</v>
       </c>
       <c r="F27" s="88" t="s">
-        <v>885</v>
+        <v>849</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A28" s="184" t="s">
+      <c r="A28" s="188" t="s">
         <v>201</v>
       </c>
-      <c r="B28" s="185"/>
-      <c r="C28" s="185"/>
-      <c r="D28" s="185"/>
-      <c r="E28" s="185"/>
-      <c r="F28" s="186"/>
+      <c r="B28" s="189"/>
+      <c r="C28" s="189"/>
+      <c r="D28" s="189"/>
+      <c r="E28" s="189"/>
+      <c r="F28" s="190"/>
     </row>
     <row r="29" spans="1:6" ht="30" customHeight="1">
       <c r="A29" s="78" t="s">
@@ -19693,33 +19760,33 @@
         <v>4.3</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>904</v>
+        <v>868</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>866</v>
+        <v>830</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>905</v>
+        <v>869</v>
       </c>
       <c r="F31" s="86" t="s">
-        <v>888</v>
+        <v>852</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="30" customHeight="1">
       <c r="A32" s="81" t="s">
-        <v>838</v>
+        <v>802</v>
       </c>
       <c r="B32" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C32" s="76" t="s">
-        <v>852</v>
+        <v>816</v>
       </c>
       <c r="D32" s="75" t="s">
         <v>167</v>
       </c>
       <c r="E32" s="76" t="s">
-        <v>853</v>
+        <v>817</v>
       </c>
       <c r="F32" s="87" t="s">
         <v>207</v>
@@ -19727,33 +19794,33 @@
     </row>
     <row r="33" spans="1:6" ht="30" customHeight="1">
       <c r="A33" s="82" t="s">
-        <v>842</v>
+        <v>806</v>
       </c>
       <c r="B33" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C33" s="66" t="s">
-        <v>886</v>
+        <v>850</v>
       </c>
       <c r="D33" s="68" t="s">
         <v>61</v>
       </c>
       <c r="E33" s="66" t="s">
-        <v>887</v>
+        <v>851</v>
       </c>
       <c r="F33" s="88" t="s">
-        <v>888</v>
+        <v>852</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A34" s="187" t="s">
+      <c r="A34" s="185" t="s">
         <v>209</v>
       </c>
-      <c r="B34" s="188"/>
-      <c r="C34" s="188"/>
-      <c r="D34" s="188"/>
-      <c r="E34" s="188"/>
-      <c r="F34" s="189"/>
+      <c r="B34" s="186"/>
+      <c r="C34" s="186"/>
+      <c r="D34" s="186"/>
+      <c r="E34" s="186"/>
+      <c r="F34" s="187"/>
     </row>
     <row r="35" spans="1:6" ht="30" customHeight="1">
       <c r="A35" s="78" t="s">
@@ -19763,16 +19830,16 @@
         <v>4.5</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>916</v>
+        <v>880</v>
       </c>
       <c r="D35" s="27" t="s">
         <v>220</v>
       </c>
       <c r="E35" s="28" t="s">
-        <v>917</v>
+        <v>881</v>
       </c>
       <c r="F35" s="84" t="s">
-        <v>918</v>
+        <v>882</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="30" customHeight="1">
@@ -19817,19 +19884,19 @@
     </row>
     <row r="38" spans="1:6" ht="30" customHeight="1">
       <c r="A38" s="81" t="s">
-        <v>838</v>
+        <v>802</v>
       </c>
       <c r="B38" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C38" s="76" t="s">
-        <v>854</v>
+        <v>818</v>
       </c>
       <c r="D38" s="75" t="s">
         <v>216</v>
       </c>
       <c r="E38" s="76" t="s">
-        <v>855</v>
+        <v>819</v>
       </c>
       <c r="F38" s="87" t="s">
         <v>92</v>
@@ -19837,33 +19904,33 @@
     </row>
     <row r="39" spans="1:6" ht="30" customHeight="1">
       <c r="A39" s="82" t="s">
-        <v>842</v>
+        <v>806</v>
       </c>
       <c r="B39" s="68">
         <v>4.3</v>
       </c>
       <c r="C39" s="66" t="s">
-        <v>889</v>
+        <v>853</v>
       </c>
       <c r="D39" s="68" t="s">
         <v>224</v>
       </c>
       <c r="E39" s="66" t="s">
-        <v>890</v>
+        <v>854</v>
       </c>
       <c r="F39" s="88" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A40" s="187" t="s">
+      <c r="A40" s="185" t="s">
         <v>218</v>
       </c>
-      <c r="B40" s="188"/>
-      <c r="C40" s="188"/>
-      <c r="D40" s="188"/>
-      <c r="E40" s="188"/>
-      <c r="F40" s="189"/>
+      <c r="B40" s="186"/>
+      <c r="C40" s="186"/>
+      <c r="D40" s="186"/>
+      <c r="E40" s="186"/>
+      <c r="F40" s="187"/>
     </row>
     <row r="41" spans="1:6" ht="30" customHeight="1">
       <c r="A41" s="78" t="s">
@@ -19927,19 +19994,19 @@
     </row>
     <row r="44" spans="1:6" ht="30" customHeight="1">
       <c r="A44" s="81" t="s">
-        <v>838</v>
+        <v>802</v>
       </c>
       <c r="B44" s="75">
         <v>4.5</v>
       </c>
       <c r="C44" s="76" t="s">
-        <v>856</v>
+        <v>820</v>
       </c>
       <c r="D44" s="75" t="s">
         <v>89</v>
       </c>
       <c r="E44" s="76" t="s">
-        <v>857</v>
+        <v>821</v>
       </c>
       <c r="F44" s="87" t="s">
         <v>226</v>
@@ -19947,33 +20014,33 @@
     </row>
     <row r="45" spans="1:6" ht="30" customHeight="1">
       <c r="A45" s="82" t="s">
-        <v>842</v>
+        <v>806</v>
       </c>
       <c r="B45" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C45" s="66" t="s">
-        <v>858</v>
+        <v>822</v>
       </c>
       <c r="D45" s="68" t="s">
-        <v>859</v>
+        <v>823</v>
       </c>
       <c r="E45" s="66" t="s">
-        <v>860</v>
+        <v>824</v>
       </c>
       <c r="F45" s="88" t="s">
-        <v>861</v>
+        <v>825</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A46" s="187" t="s">
+      <c r="A46" s="185" t="s">
         <v>230</v>
       </c>
-      <c r="B46" s="188"/>
-      <c r="C46" s="188"/>
-      <c r="D46" s="188"/>
-      <c r="E46" s="188"/>
-      <c r="F46" s="189"/>
+      <c r="B46" s="186"/>
+      <c r="C46" s="186"/>
+      <c r="D46" s="186"/>
+      <c r="E46" s="186"/>
+      <c r="F46" s="187"/>
     </row>
     <row r="47" spans="1:6" ht="30" customHeight="1">
       <c r="A47" s="78" t="s">
@@ -20023,67 +20090,67 @@
         <v>4.5</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>906</v>
+        <v>870</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>220</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>907</v>
+        <v>871</v>
       </c>
       <c r="F49" s="86" t="s">
-        <v>908</v>
+        <v>872</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="30" customHeight="1">
       <c r="A50" s="81" t="s">
-        <v>838</v>
+        <v>802</v>
       </c>
       <c r="B50" s="75">
         <v>4.7</v>
       </c>
       <c r="C50" s="76" t="s">
-        <v>862</v>
+        <v>826</v>
       </c>
       <c r="D50" s="75" t="s">
         <v>66</v>
       </c>
       <c r="E50" s="76" t="s">
-        <v>863</v>
+        <v>827</v>
       </c>
       <c r="F50" s="87" t="s">
-        <v>864</v>
+        <v>828</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="30" customHeight="1">
       <c r="A51" s="82" t="s">
-        <v>842</v>
+        <v>806</v>
       </c>
       <c r="B51" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C51" s="66" t="s">
-        <v>865</v>
+        <v>829</v>
       </c>
       <c r="D51" s="68" t="s">
-        <v>866</v>
+        <v>830</v>
       </c>
       <c r="E51" s="66" t="s">
-        <v>867</v>
+        <v>831</v>
       </c>
       <c r="F51" s="88" t="s">
-        <v>868</v>
+        <v>832</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A52" s="187" t="s">
+      <c r="A52" s="185" t="s">
         <v>238</v>
       </c>
-      <c r="B52" s="188"/>
-      <c r="C52" s="188"/>
-      <c r="D52" s="188"/>
-      <c r="E52" s="188"/>
-      <c r="F52" s="189"/>
+      <c r="B52" s="186"/>
+      <c r="C52" s="186"/>
+      <c r="D52" s="186"/>
+      <c r="E52" s="186"/>
+      <c r="F52" s="187"/>
     </row>
     <row r="53" spans="1:6" ht="30" customHeight="1">
       <c r="A53" s="78" t="s">
@@ -20147,53 +20214,53 @@
     </row>
     <row r="56" spans="1:6" ht="30" customHeight="1">
       <c r="A56" s="81" t="s">
-        <v>838</v>
+        <v>802</v>
       </c>
       <c r="B56" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C56" s="74" t="s">
-        <v>891</v>
+        <v>855</v>
       </c>
       <c r="D56" s="75" t="s">
         <v>220</v>
       </c>
       <c r="E56" s="76" t="s">
-        <v>892</v>
+        <v>856</v>
       </c>
       <c r="F56" s="87" t="s">
-        <v>893</v>
+        <v>857</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="30" customHeight="1">
       <c r="A57" s="82" t="s">
-        <v>842</v>
+        <v>806</v>
       </c>
       <c r="B57" s="68">
         <v>4.5999999999999996</v>
       </c>
       <c r="C57" s="69" t="s">
-        <v>869</v>
+        <v>833</v>
       </c>
       <c r="D57" s="68" t="s">
         <v>52</v>
       </c>
       <c r="E57" s="66" t="s">
-        <v>870</v>
+        <v>834</v>
       </c>
       <c r="F57" s="88" t="s">
-        <v>871</v>
+        <v>835</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A58" s="187" t="s">
+      <c r="A58" s="185" t="s">
         <v>247</v>
       </c>
-      <c r="B58" s="188"/>
-      <c r="C58" s="188"/>
-      <c r="D58" s="188"/>
-      <c r="E58" s="188"/>
-      <c r="F58" s="189"/>
+      <c r="B58" s="186"/>
+      <c r="C58" s="186"/>
+      <c r="D58" s="186"/>
+      <c r="E58" s="186"/>
+      <c r="F58" s="187"/>
     </row>
     <row r="59" spans="1:6" ht="30" customHeight="1">
       <c r="A59" s="78" t="s">
@@ -20256,14 +20323,14 @@
       </c>
     </row>
     <row r="62" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A62" s="190" t="s">
+      <c r="A62" s="179" t="s">
         <v>260</v>
       </c>
-      <c r="B62" s="191"/>
-      <c r="C62" s="191"/>
-      <c r="D62" s="191"/>
-      <c r="E62" s="191"/>
-      <c r="F62" s="192"/>
+      <c r="B62" s="180"/>
+      <c r="C62" s="180"/>
+      <c r="D62" s="180"/>
+      <c r="E62" s="180"/>
+      <c r="F62" s="181"/>
     </row>
     <row r="63" spans="1:6" ht="30" customHeight="1">
       <c r="A63" s="78" t="s">
@@ -20293,13 +20360,13 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>894</v>
+        <v>858</v>
       </c>
       <c r="D64" s="18" t="s">
         <v>224</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>911</v>
+        <v>875</v>
       </c>
       <c r="F64" s="85" t="s">
         <v>279</v>
@@ -20327,19 +20394,19 @@
     </row>
     <row r="66" spans="1:6" ht="30" customHeight="1">
       <c r="A66" s="81" t="s">
-        <v>838</v>
+        <v>802</v>
       </c>
       <c r="B66" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C66" s="76" t="s">
-        <v>898</v>
+        <v>862</v>
       </c>
       <c r="D66" s="75" t="s">
-        <v>866</v>
+        <v>830</v>
       </c>
       <c r="E66" s="76" t="s">
-        <v>899</v>
+        <v>863</v>
       </c>
       <c r="F66" s="87" t="s">
         <v>279</v>
@@ -20347,39 +20414,39 @@
     </row>
     <row r="67" spans="1:6" ht="30" customHeight="1">
       <c r="A67" s="82" t="s">
-        <v>842</v>
+        <v>806</v>
       </c>
       <c r="B67" s="68">
         <v>4.3</v>
       </c>
       <c r="C67" s="66" t="s">
-        <v>912</v>
+        <v>876</v>
       </c>
       <c r="D67" s="68" t="s">
-        <v>913</v>
+        <v>877</v>
       </c>
       <c r="E67" s="66" t="s">
-        <v>914</v>
+        <v>878</v>
       </c>
       <c r="F67" s="88" t="s">
-        <v>915</v>
+        <v>879</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="30" customHeight="1">
       <c r="A68" s="81" t="s">
-        <v>928</v>
+        <v>892</v>
       </c>
       <c r="B68" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C68" s="76" t="s">
-        <v>929</v>
+        <v>893</v>
       </c>
       <c r="D68" s="75" t="s">
         <v>123</v>
       </c>
       <c r="E68" s="76" t="s">
-        <v>930</v>
+        <v>894</v>
       </c>
       <c r="F68" s="87" t="s">
         <v>121</v>
@@ -20387,33 +20454,33 @@
     </row>
     <row r="69" spans="1:6" ht="30" customHeight="1">
       <c r="A69" s="82" t="s">
-        <v>931</v>
+        <v>895</v>
       </c>
       <c r="B69" s="68">
         <v>4.5</v>
       </c>
       <c r="C69" s="66" t="s">
-        <v>932</v>
+        <v>896</v>
       </c>
       <c r="D69" s="68" t="s">
         <v>99</v>
       </c>
       <c r="E69" s="66" t="s">
-        <v>933</v>
+        <v>897</v>
       </c>
       <c r="F69" s="88" t="s">
-        <v>934</v>
+        <v>898</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A70" s="190" t="s">
+      <c r="A70" s="179" t="s">
         <v>267</v>
       </c>
-      <c r="B70" s="191"/>
-      <c r="C70" s="191"/>
-      <c r="D70" s="191"/>
-      <c r="E70" s="191"/>
-      <c r="F70" s="192"/>
+      <c r="B70" s="180"/>
+      <c r="C70" s="180"/>
+      <c r="D70" s="180"/>
+      <c r="E70" s="180"/>
+      <c r="F70" s="181"/>
     </row>
     <row r="71" spans="1:6" ht="30" customHeight="1">
       <c r="A71" s="78" t="s">
@@ -20477,19 +20544,19 @@
     </row>
     <row r="74" spans="1:6" ht="30" customHeight="1">
       <c r="A74" s="81" t="s">
-        <v>838</v>
+        <v>802</v>
       </c>
       <c r="B74" s="75">
         <v>4.3</v>
       </c>
       <c r="C74" s="76" t="s">
-        <v>909</v>
+        <v>873</v>
       </c>
       <c r="D74" s="75" t="s">
         <v>220</v>
       </c>
       <c r="E74" s="76" t="s">
-        <v>910</v>
+        <v>874</v>
       </c>
       <c r="F74" s="87" t="s">
         <v>273</v>
@@ -20497,33 +20564,33 @@
     </row>
     <row r="75" spans="1:6" ht="30" customHeight="1">
       <c r="A75" s="82" t="s">
-        <v>842</v>
+        <v>806</v>
       </c>
       <c r="B75" s="68">
         <v>4</v>
       </c>
       <c r="C75" s="66" t="s">
-        <v>873</v>
+        <v>837</v>
       </c>
       <c r="D75" s="68" t="s">
-        <v>874</v>
+        <v>838</v>
       </c>
       <c r="E75" s="66" t="s">
-        <v>875</v>
+        <v>839</v>
       </c>
       <c r="F75" s="88" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A76" s="190" t="s">
+      <c r="A76" s="179" t="s">
         <v>275</v>
       </c>
-      <c r="B76" s="191"/>
-      <c r="C76" s="191"/>
-      <c r="D76" s="191"/>
-      <c r="E76" s="191"/>
-      <c r="F76" s="192"/>
+      <c r="B76" s="180"/>
+      <c r="C76" s="180"/>
+      <c r="D76" s="180"/>
+      <c r="E76" s="180"/>
+      <c r="F76" s="181"/>
     </row>
     <row r="77" spans="1:6" ht="30" customHeight="1">
       <c r="A77" s="78" t="s">
@@ -20553,13 +20620,13 @@
         <v>4.2</v>
       </c>
       <c r="C78" s="16" t="s">
-        <v>896</v>
+        <v>860</v>
       </c>
       <c r="D78" s="18" t="s">
         <v>119</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>897</v>
+        <v>861</v>
       </c>
       <c r="F78" s="85" t="s">
         <v>279</v>
@@ -20573,13 +20640,13 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>919</v>
+        <v>883</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>220</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>920</v>
+        <v>884</v>
       </c>
       <c r="F79" s="86" t="s">
         <v>279</v>
@@ -20587,19 +20654,19 @@
     </row>
     <row r="80" spans="1:6" ht="30" customHeight="1">
       <c r="A80" s="81" t="s">
-        <v>838</v>
+        <v>802</v>
       </c>
       <c r="B80" s="75">
         <v>4.3</v>
       </c>
       <c r="C80" s="76" t="s">
-        <v>872</v>
+        <v>836</v>
       </c>
       <c r="D80" s="75" t="s">
         <v>119</v>
       </c>
       <c r="E80" s="76" t="s">
-        <v>895</v>
+        <v>859</v>
       </c>
       <c r="F80" s="87" t="s">
         <v>279</v>
@@ -20607,19 +20674,19 @@
     </row>
     <row r="81" spans="1:6" ht="30" customHeight="1">
       <c r="A81" s="82" t="s">
-        <v>842</v>
+        <v>806</v>
       </c>
       <c r="B81" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C81" s="66" t="s">
-        <v>921</v>
+        <v>885</v>
       </c>
       <c r="D81" s="68" t="s">
-        <v>922</v>
+        <v>886</v>
       </c>
       <c r="E81" s="66" t="s">
-        <v>923</v>
+        <v>887</v>
       </c>
       <c r="F81" s="88" t="s">
         <v>290</v>
@@ -20627,19 +20694,19 @@
     </row>
     <row r="82" spans="1:6" ht="30" customHeight="1">
       <c r="A82" s="81" t="s">
-        <v>928</v>
+        <v>892</v>
       </c>
       <c r="B82" s="75">
         <v>4.5999999999999996</v>
       </c>
       <c r="C82" s="76" t="s">
-        <v>935</v>
+        <v>899</v>
       </c>
       <c r="D82" s="75" t="s">
         <v>128</v>
       </c>
       <c r="E82" s="76" t="s">
-        <v>936</v>
+        <v>900</v>
       </c>
       <c r="F82" s="87" t="s">
         <v>279</v>
@@ -20647,33 +20714,33 @@
     </row>
     <row r="83" spans="1:6" ht="30" customHeight="1">
       <c r="A83" s="82" t="s">
-        <v>931</v>
+        <v>895</v>
       </c>
       <c r="B83" s="68" t="s">
         <v>255</v>
       </c>
       <c r="C83" s="66" t="s">
-        <v>937</v>
+        <v>901</v>
       </c>
       <c r="D83" s="68" t="s">
         <v>291</v>
       </c>
       <c r="E83" s="66" t="s">
-        <v>938</v>
+        <v>902</v>
       </c>
       <c r="F83" s="88" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A84" s="190" t="s">
+      <c r="A84" s="179" t="s">
         <v>281</v>
       </c>
-      <c r="B84" s="191"/>
-      <c r="C84" s="191"/>
-      <c r="D84" s="191"/>
-      <c r="E84" s="191"/>
-      <c r="F84" s="192"/>
+      <c r="B84" s="180"/>
+      <c r="C84" s="180"/>
+      <c r="D84" s="180"/>
+      <c r="E84" s="180"/>
+      <c r="F84" s="181"/>
     </row>
     <row r="85" spans="1:6" ht="30" customHeight="1">
       <c r="A85" s="78" t="s">
@@ -20737,56 +20804,66 @@
     </row>
     <row r="88" spans="1:6" ht="30" customHeight="1">
       <c r="A88" s="81" t="s">
-        <v>838</v>
+        <v>802</v>
       </c>
       <c r="B88" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C88" s="76" t="s">
-        <v>924</v>
+        <v>888</v>
       </c>
       <c r="D88" s="75" t="s">
-        <v>925</v>
+        <v>889</v>
       </c>
       <c r="E88" s="76" t="s">
-        <v>926</v>
+        <v>890</v>
       </c>
       <c r="F88" s="87" t="s">
-        <v>927</v>
+        <v>891</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="30" customHeight="1">
       <c r="A89" s="82" t="s">
-        <v>842</v>
+        <v>806</v>
       </c>
       <c r="B89" s="68">
         <v>4.5</v>
       </c>
       <c r="C89" s="66" t="s">
-        <v>876</v>
+        <v>840</v>
       </c>
       <c r="D89" s="68" t="s">
         <v>119</v>
       </c>
       <c r="E89" s="66" t="s">
-        <v>877</v>
+        <v>841</v>
       </c>
       <c r="F89" s="88" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="33.75" customHeight="1" thickBot="1">
-      <c r="A90" s="193" t="s">
-        <v>939</v>
-      </c>
-      <c r="B90" s="194"/>
-      <c r="C90" s="194"/>
-      <c r="D90" s="194"/>
-      <c r="E90" s="194"/>
-      <c r="F90" s="195"/>
+      <c r="A90" s="182" t="s">
+        <v>903</v>
+      </c>
+      <c r="B90" s="183"/>
+      <c r="C90" s="183"/>
+      <c r="D90" s="183"/>
+      <c r="E90" s="183"/>
+      <c r="F90" s="184"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A46:F46"/>
     <mergeCell ref="A84:F84"/>
     <mergeCell ref="A90:F90"/>
     <mergeCell ref="A52:F52"/>
@@ -20794,16 +20871,6 @@
     <mergeCell ref="A62:F62"/>
     <mergeCell ref="A70:F70"/>
     <mergeCell ref="A76:F76"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A16:F16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -20825,12 +20892,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="161" t="s">
         <v>292</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="153"/>
+      <c r="B1" s="162"/>
+      <c r="C1" s="162"/>
+      <c r="D1" s="163"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="132"/>
@@ -20839,12 +20906,12 @@
       <c r="D2" s="142"/>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
-      <c r="A3" s="196" t="s">
+      <c r="A3" s="197" t="s">
         <v>293</v>
       </c>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
-      <c r="D3" s="198"/>
+      <c r="B3" s="198"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="199"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="133" t="s">
@@ -20935,13 +21002,13 @@
         <v>326</v>
       </c>
       <c r="B10" s="92" t="s">
-        <v>969</v>
+        <v>933</v>
       </c>
       <c r="C10" s="92" t="s">
-        <v>970</v>
+        <v>934</v>
       </c>
       <c r="D10" s="125" t="s">
-        <v>971</v>
+        <v>935</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -20951,12 +21018,12 @@
       <c r="D11" s="142"/>
     </row>
     <row r="12" spans="1:4" ht="24" customHeight="1">
-      <c r="A12" s="199" t="s">
+      <c r="A12" s="200" t="s">
         <v>316</v>
       </c>
-      <c r="B12" s="200"/>
-      <c r="C12" s="200"/>
-      <c r="D12" s="201"/>
+      <c r="B12" s="201"/>
+      <c r="C12" s="201"/>
+      <c r="D12" s="202"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="133" t="s">
@@ -21061,27 +21128,27 @@
         <v>326</v>
       </c>
       <c r="B20" s="92" t="s">
-        <v>972</v>
+        <v>936</v>
       </c>
       <c r="C20" s="92" t="s">
-        <v>973</v>
+        <v>937</v>
       </c>
       <c r="D20" s="125" t="s">
-        <v>974</v>
+        <v>938</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="30" customHeight="1">
       <c r="A21" s="140" t="s">
-        <v>975</v>
+        <v>939</v>
       </c>
       <c r="B21" s="90" t="s">
-        <v>976</v>
+        <v>940</v>
       </c>
       <c r="C21" s="90" t="s">
-        <v>977</v>
+        <v>941</v>
       </c>
       <c r="D21" s="149" t="s">
-        <v>978</v>
+        <v>942</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="27.75" customHeight="1">
@@ -21133,12 +21200,12 @@
       <c r="D25" s="142"/>
     </row>
     <row r="26" spans="1:4" ht="24" customHeight="1">
-      <c r="A26" s="202" t="s">
+      <c r="A26" s="203" t="s">
         <v>347</v>
       </c>
-      <c r="B26" s="203"/>
-      <c r="C26" s="203"/>
-      <c r="D26" s="204"/>
+      <c r="B26" s="204"/>
+      <c r="C26" s="204"/>
+      <c r="D26" s="205"/>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="133" t="s">
@@ -21293,20 +21360,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1">
-      <c r="A1" s="205" t="s">
+      <c r="A1" s="206" t="s">
         <v>370</v>
       </c>
-      <c r="B1" s="205"/>
-      <c r="C1" s="205"/>
-      <c r="D1" s="205"/>
+      <c r="B1" s="206"/>
+      <c r="C1" s="206"/>
+      <c r="D1" s="206"/>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
-      <c r="A3" s="177" t="s">
+      <c r="A3" s="178" t="s">
         <v>293</v>
       </c>
-      <c r="B3" s="177"/>
-      <c r="C3" s="177"/>
-      <c r="D3" s="177"/>
+      <c r="B3" s="178"/>
+      <c r="C3" s="178"/>
+      <c r="D3" s="178"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="12" t="s">
@@ -21365,12 +21432,12 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="24" customHeight="1">
-      <c r="A9" s="173" t="s">
+      <c r="A9" s="174" t="s">
         <v>316</v>
       </c>
-      <c r="B9" s="173"/>
-      <c r="C9" s="173"/>
-      <c r="D9" s="173"/>
+      <c r="B9" s="174"/>
+      <c r="C9" s="174"/>
+      <c r="D9" s="174"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="12" t="s">
@@ -21415,12 +21482,12 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="24" customHeight="1">
-      <c r="A14" s="175" t="s">
+      <c r="A14" s="176" t="s">
         <v>347</v>
       </c>
-      <c r="B14" s="175"/>
-      <c r="C14" s="175"/>
-      <c r="D14" s="175"/>
+      <c r="B14" s="176"/>
+      <c r="C14" s="176"/>
+      <c r="D14" s="176"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="12" t="s">

--- a/tools/itinerary.xlsx
+++ b/tools/itinerary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jitwei/Library/Mobile Documents/com~apple~CloudDocs/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A39598-DE4D-6B4F-9112-248D58D61379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4BAEC6-A34F-1948-9AEC-08A088BC0738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="17020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="1014">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1591" uniqueCount="1069">
   <si>
     <r>
       <rPr>
@@ -2959,9 +2959,6 @@
     </r>
   </si>
   <si>
-    <t>1848 lakeside icon; vinegar fish, Dongpo pork</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -4661,9 +4658,6 @@
     </r>
   </si>
   <si>
-    <t>250-yr-old; squirrel mandarin fish. 1,350+ reviews</t>
-  </si>
-  <si>
     <t>¥120–200</t>
   </si>
   <si>
@@ -13538,9 +13532,6 @@
     <t>MEAL OPTIONS — 5 top-rated picks per lunch &amp; dinner (by popularity, rating &amp; distance)</t>
   </si>
   <si>
-    <t>Ratings from Trip.com / Dianping / Tripadvisor (2026). Options ranked ①→⑤ by rating, review volume and walking distance from that day’s route. ★ = special. 🏨 = at/near hotel.</t>
-  </si>
-  <si>
     <t>Zhang Sheng Ji 张生记 (Hubin 湖滨)</t>
   </si>
   <si>
@@ -13716,9 +13707,6 @@
   </si>
   <si>
     <t>Order these at 松鹤楼 / 得月楼 — sizzling eel &amp; biluochun shrimp</t>
-  </si>
-  <si>
-    <t>①–⑦ ranked by rating, popularity &amp; distance from the day’s route. ★ 宫宴 = banquet. 🏨 = at/near hotel (incl. Michelin-starred in-hotel at Ritz Nanjing). Suzhou snack specialities (生煎, 糕团, 鲜肉月饼, 响油鳝糊) are folded into the Day 6–7 lists as ⑥/⑦ — grab-and-go or add-on dishes rather than full sit-down meals. Ratings indicative 2026; fine-dining &amp; 宫宴 need booking 3+ days ahead.</t>
   </si>
   <si>
     <t>14:15–14:45</t>
@@ -14391,6 +14379,183 @@
   </si>
   <si>
     <t>DiDi ~20 min from 曙光路 back to the CBD. Pack for Nanjing 南京.</t>
+  </si>
+  <si>
+    <t>⑧</t>
+  </si>
+  <si>
+    <t>评分 71</t>
+  </si>
+  <si>
+    <t>Xiehe Caiguan 协和菜馆 (Fenghuang St 凤凰街)</t>
+  </si>
+  <si>
+    <t>DIANPING #3 苏帮菜 (评分 71) — outranks 松鹤楼 at ⅔ the price; on 凤凰街/十全街 near your coffee stop</t>
+  </si>
+  <si>
+    <t>⑨</t>
+  </si>
+  <si>
+    <t>评分 67</t>
+  </si>
+  <si>
+    <t>Zhenzhu Fandian 珍珠饭店 (Guanqian 观前街)</t>
+  </si>
+  <si>
+    <t>¥80–110</t>
+  </si>
+  <si>
+    <t>DIANPING #7 苏帮菜 (评分 67) — on 珍珠弄 right at your Guanqian lunch spot, half the price of 得月楼</t>
+  </si>
+  <si>
+    <t>姑苏区观前街珍珠弄</t>
+  </si>
+  <si>
+    <t>评分 73</t>
+  </si>
+  <si>
+    <t>Wusa Jiujia 五卅酒家 (Shiquan 十全街)</t>
+  </si>
+  <si>
+    <t>¥70–100</t>
+  </si>
+  <si>
+    <t>DIANPING #1 苏帮菜 2026 (评分 73) — top-scoring Su-bang house in the city, great value</t>
+  </si>
+  <si>
+    <t>评分 70</t>
+  </si>
+  <si>
+    <t>Xiaoyuanlou 小园楼 (Xibei St 西北街)</t>
+  </si>
+  <si>
+    <t>DIANPING #5 苏帮菜 (评分 70) — near Humble Administrator's Garden 拙政园 / 平江路 north end</t>
+  </si>
+  <si>
+    <t>姑苏区西北街</t>
+  </si>
+  <si>
+    <t>评分 82</t>
+  </si>
+  <si>
+    <t>Ye Ma Canting 叶马餐厅</t>
+  </si>
+  <si>
+    <t>DIANPING #4 杭帮菜 2026 (评分 82) — best-value entry in the city top-5; modern Hangzhou cooking</t>
+  </si>
+  <si>
+    <t>评分 77</t>
+  </si>
+  <si>
+    <t>Hangzhou Jiujia 杭州酒家</t>
+  </si>
+  <si>
+    <t>DIANPING #11 杭帮菜 (评分 77) — top-12 ranking at under half 楼外楼's price; old-school 杭帮菜</t>
+  </si>
+  <si>
+    <t>1848 lakeside icon; vinegar fish, Dongpo pork. ⚠️ NOT in the 2026 Dianping 杭帮菜 top-16 — famous &amp; scenic, but locals rank it below its reputation. See ⑥⑦ below.</t>
+  </si>
+  <si>
+    <t>250-yr-old; squirrel mandarin fish. 1,350+ reviews. ⚠️ Ranks LAST (评分 65) among 2026 Dianping 苏帮菜 entries while being the priciest — go for the heritage dish, not value. See ⑧⑨ below.</t>
+  </si>
+  <si>
+    <t>Ratings from Trip.com / Dianping / Tripadvisor (2026). Options ranked ①→⑤ by rating, review volume and walking distance from that day’s route. ★ = special. 🏨 = at/near hotel.  ⚠️ TWO SCALES: plain numbers (e.g. 4.6) are 0–5 star averages; entries marked “评分 NN” are Dianping’s 0–100 composite city-ranking score (taste + environment + service + popularity). They are NOT directly comparable — compare rank position, not the digits.</t>
+  </si>
+  <si>
+    <t>①–⑦ ranked by rating, popularity &amp; distance from the day’s route. ★ 宫宴 = banquet. 🏨 = at/near hotel (incl. Michelin-starred in-hotel at Ritz Nanjing). Suzhou snack specialities (生煎, 糕团, 鲜肉月饼, 响油鳝糊) are folded into the Day 6–7 lists as ⑥/⑦ — grab-and-go or add-on dishes rather than full sit-down meals. Ratings indicative 2026; fine-dining &amp; 宫宴 need booking 3+ days ahead.  ⑧/⑨ entries (added Sep 2026) come from the 2026 Dianping city rankings for 杭帮菜 &amp; 苏帮菜 — each sourced from a single aggregator, so treat as one strong opinion rather than settled fact. No comparable Nanjing restaurant ranking was found, so the Nanjing lists are unchanged.</t>
+  </si>
+  <si>
+    <t>☕ Optional: 羽和铃 Feather Bell coffee</t>
+  </si>
+  <si>
+    <t>Verified on Dianping (~¥53pp). Bamboo-wind-chime courtyard cafe at the foot of Wushan 吴山, a few steps up from Hefang St. Specialty hand-brew, plum-soda, scones &amp; chiffon cake.</t>
+  </si>
+  <si>
+    <t>Opt · ~¥53pp</t>
+  </si>
+  <si>
+    <t>上城区 清河坊/河坊街 (吴山山脚)</t>
+  </si>
+  <si>
+    <t>🍦 Optional: 夏序 SASU Gelato</t>
+  </si>
+  <si>
+    <t>Verified on Dianping (~¥37pp). Called by reviewers Hangzhou's best Italian gelato — pistachio, matcha &amp; chocolate are the standouts. On Guangfu Rd 光复路, ~5 min from Hefang St. Little queuing off-peak.</t>
+  </si>
+  <si>
+    <t>Opt · ~¥37pp</t>
+  </si>
+  <si>
+    <t>上城区光复路 (清河坊/南宋御街)</t>
+  </si>
+  <si>
+    <t>羽和铃 Feather Bell (Day 2 · Opt)</t>
+  </si>
+  <si>
+    <t>Courtyard café at the foot of Wushan 吴山, steps up from Hefang St. Hand-brew Ethiopia, plum soda 梅子露, scones &amp; chiffon cake. Verified on Dianping.</t>
+  </si>
+  <si>
+    <t>¥45–60</t>
+  </si>
+  <si>
+    <t>🍦 Gelato</t>
+  </si>
+  <si>
+    <t>夏序 SASU Gelato (Day 2 · Opt)</t>
+  </si>
+  <si>
+    <t>Reviewers call it Hangzhou's best Italian gelato — pistachio, matcha, chocolate. ~5 min from Hefang St; little queuing off-peak. Verified on Dianping.</t>
+  </si>
+  <si>
+    <t>宫宴 Gongyan Palace Banquet (Day 3)</t>
+  </si>
+  <si>
+    <t>🍵 Optional: 查小文茶客厅 Cha Talk Tea House (四寒茶舍)</t>
+  </si>
+  <si>
+    <t>Award-winning tea house on Dajing Lane 大井巷 (Southern Song lane off Hefang St). Owner 查文 is a Hangzhou tea-culture inheritor. 1F: walk-in tasting + tea/teaware retail — local 西湖龙井 plus Taiwan high-mtn oolong, Fuding white, Wuyi rock tea. Creative tea mocktails (茶逗逗 w/ tea jelly) brewed espresso-style. 2F tatami tea room needs advance booking 预约.</t>
+  </si>
+  <si>
+    <t>Opt · walk-in 1F</t>
+  </si>
+  <si>
+    <t>上城区大井巷7-9号 (近河坊街)</t>
+  </si>
+  <si>
+    <t>🍵 Tea House</t>
+  </si>
+  <si>
+    <t>查小文茶客厅 Cha Talk 四寒茶舍 (Day 2 · Opt)</t>
+  </si>
+  <si>
+    <t>AIR Architects-designed tea house in a Southern Song lane; owner 查文 is a Hangzhou tea-culture inheritor. 1F walk-in tasting &amp; tea/teaware retail (本土西湖龙井, 台湾高山乌龙, 福鼎白茶, 武夷岩茶). Creative tea mocktails 茶逗逗. 2F tatami tea room by reservation only. Gift: 消闲果儿 hamper.</t>
+  </si>
+  <si>
+    <t>¥50–120</t>
+  </si>
+  <si>
+    <t>🥟 Optional breakfast: 泮芳春煎饺 Pan Fang Chun (中山南路店)</t>
+  </si>
+  <si>
+    <t>MICHELIN Bib Gourmand 必比登 3 years running — Hangzhou's most famous pan-fried dumplings 煎饺, ~¥1 each (5 for ¥5). Thin skin, crisp golden base, juicy pork. Verified on Dianping: ~¥17pp, opens 06:00. Queues form early — go before 08:00. Located at the 南宋御街 archway, ~10 min walk from 清河坊/吴山. Also: 鲜肉小馄饨, 葱油拌面, 咸豆花, 现磨豆浆.</t>
+  </si>
+  <si>
+    <t>Opt · ~¥17pp · 06:00开</t>
+  </si>
+  <si>
+    <t>上城区中山南路479号 (中河中路×望江路西南100m)</t>
+  </si>
+  <si>
+    <t>泮芳春煎饺 Pan Fang Chun (Day 3 · Opt)</t>
+  </si>
+  <si>
+    <t>上城区中山南路479号 (吴山广场/河坊街)</t>
+  </si>
+  <si>
+    <t>MICHELIN Bib Gourmand 必比登 3 yrs running. Founder 泮芳春 has run it 18+ yrs. Signature 煎饺 ~¥1 each — thin skin, crisp base, juicy pork. Also 鲜肉小馄饨, 葱油拌面, 咸豆花, 现磨浓豆浆, 龙井茶叶蛋. Opens 06:00; queue before 08:00. Verified on Dianping (~¥17pp). NOTE: family split — 朝晖路 store is now "芳春/芳楠春" (different owners); 中山南路 &amp; 鼓楼 are the founder's own.</t>
+  </si>
+  <si>
+    <t>¥15–25</t>
   </si>
 </sst>
 </file>
@@ -14956,7 +15121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="216">
+  <cellXfs count="219">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -15597,6 +15762,15 @@
     <xf numFmtId="49" fontId="10" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -16086,7 +16260,7 @@
   <sheetPr>
     <tabColor rgb="FFC55A11"/>
   </sheetPr>
-  <dimension ref="A1:F133"/>
+  <dimension ref="A1:F137"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -16099,7 +16273,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
       <c r="A1" s="161" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B1" s="162"/>
       <c r="C1" s="162"/>
@@ -16109,7 +16283,7 @@
     </row>
     <row r="2" spans="1:6" ht="21.75" customHeight="1">
       <c r="A2" s="164" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B2" s="165"/>
       <c r="C2" s="165"/>
@@ -16119,19 +16293,19 @@
     </row>
     <row r="3" spans="1:6" ht="19.5" customHeight="1">
       <c r="A3" s="77" t="s">
+        <v>396</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>397</v>
+      </c>
+      <c r="C3" s="26" t="s">
         <v>398</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="D3" s="26" t="s">
         <v>399</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="E3" s="26" t="s">
         <v>400</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>401</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>402</v>
       </c>
       <c r="F3" s="83" t="s">
         <v>23</v>
@@ -16139,7 +16313,7 @@
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1">
       <c r="A4" s="167" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="B4" s="168"/>
       <c r="C4" s="168"/>
@@ -16149,99 +16323,99 @@
     </row>
     <row r="5" spans="1:6" ht="25.5" customHeight="1">
       <c r="A5" s="98" t="s">
+        <v>401</v>
+      </c>
+      <c r="B5" s="53" t="s">
+        <v>402</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="D5" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="F5" s="86" t="s">
         <v>406</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="F5" s="86" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="25.5" customHeight="1">
       <c r="A6" s="99" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B6" s="54" t="s">
+        <v>407</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="D6" s="15" t="s">
         <v>409</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="E6" s="15" t="s">
         <v>410</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="F6" s="113" t="s">
         <v>411</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>412</v>
-      </c>
-      <c r="F6" s="113" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1">
       <c r="A7" s="100" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B7" s="213" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="C7" s="50" t="s">
+        <v>412</v>
+      </c>
+      <c r="D7" s="50" t="s">
+        <v>982</v>
+      </c>
+      <c r="E7" s="50" t="s">
+        <v>413</v>
+      </c>
+      <c r="F7" s="115" t="s">
         <v>414</v>
-      </c>
-      <c r="D7" s="50" t="s">
-        <v>986</v>
-      </c>
-      <c r="E7" s="50" t="s">
-        <v>415</v>
-      </c>
-      <c r="F7" s="115" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="25.5" customHeight="1">
       <c r="A8" s="100" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B8" s="55" t="s">
+        <v>415</v>
+      </c>
+      <c r="C8" s="50" t="s">
+        <v>416</v>
+      </c>
+      <c r="D8" s="50" t="s">
         <v>417</v>
       </c>
-      <c r="C8" s="50" t="s">
+      <c r="E8" s="50" t="s">
         <v>418</v>
       </c>
-      <c r="D8" s="50" t="s">
+      <c r="F8" s="115" t="s">
         <v>419</v>
-      </c>
-      <c r="E8" s="50" t="s">
-        <v>420</v>
-      </c>
-      <c r="F8" s="115" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="25.5" customHeight="1">
       <c r="A9" s="100" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B9" s="55" t="s">
+        <v>420</v>
+      </c>
+      <c r="C9" s="50" t="s">
+        <v>421</v>
+      </c>
+      <c r="D9" s="50" t="s">
         <v>422</v>
       </c>
-      <c r="C9" s="50" t="s">
+      <c r="E9" s="50" t="s">
         <v>423</v>
-      </c>
-      <c r="D9" s="50" t="s">
-        <v>424</v>
-      </c>
-      <c r="E9" s="50" t="s">
-        <v>425</v>
       </c>
       <c r="F9" s="115" t="s">
         <v>28</v>
@@ -16249,39 +16423,39 @@
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1">
       <c r="A10" s="101" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B10" s="56" t="s">
+        <v>424</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>426</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="E10" s="10" t="s">
         <v>427</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="F10" s="116" t="s">
         <v>428</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="F10" s="116" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1">
       <c r="A11" s="102" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B11" s="57" t="s">
+        <v>429</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>430</v>
+      </c>
+      <c r="D11" s="33" t="s">
         <v>431</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="E11" s="35" t="s">
         <v>432</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>433</v>
-      </c>
-      <c r="E11" s="35" t="s">
-        <v>434</v>
       </c>
       <c r="F11" s="117" t="s">
         <v>152</v>
@@ -16289,47 +16463,47 @@
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1">
       <c r="A12" s="103" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B12" s="58" t="s">
+        <v>433</v>
+      </c>
+      <c r="C12" s="39" t="s">
+        <v>434</v>
+      </c>
+      <c r="D12" s="39" t="s">
         <v>435</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="E12" s="41" t="s">
         <v>436</v>
       </c>
-      <c r="D12" s="39" t="s">
+      <c r="F12" s="118" t="s">
         <v>437</v>
-      </c>
-      <c r="E12" s="41" t="s">
-        <v>438</v>
-      </c>
-      <c r="F12" s="118" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1">
       <c r="A13" s="101" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B13" s="56" t="s">
+        <v>438</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="D13" s="10" t="s">
         <v>440</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="E13" s="10" t="s">
         <v>441</v>
       </c>
-      <c r="D13" s="10" t="s">
-        <v>442</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>443</v>
-      </c>
       <c r="F13" s="116" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="25.5" customHeight="1">
       <c r="A14" s="167" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="B14" s="168"/>
       <c r="C14" s="168"/>
@@ -16339,16 +16513,16 @@
     </row>
     <row r="15" spans="1:6" ht="30" customHeight="1">
       <c r="A15" s="101" t="s">
+        <v>442</v>
+      </c>
+      <c r="B15" s="56" t="s">
+        <v>443</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>444</v>
       </c>
-      <c r="B15" s="56" t="s">
+      <c r="D15" s="10" t="s">
         <v>445</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>446</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>447</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>20</v>
@@ -16359,119 +16533,119 @@
     </row>
     <row r="16" spans="1:6" ht="30" customHeight="1">
       <c r="A16" s="104" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B16" s="59" t="s">
+        <v>446</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>447</v>
+      </c>
+      <c r="D16" s="47" t="s">
         <v>448</v>
       </c>
-      <c r="C16" s="47" t="s">
+      <c r="E16" s="47" t="s">
         <v>449</v>
       </c>
-      <c r="D16" s="47" t="s">
+      <c r="F16" s="119" t="s">
         <v>450</v>
-      </c>
-      <c r="E16" s="47" t="s">
-        <v>451</v>
-      </c>
-      <c r="F16" s="119" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="25.5" customHeight="1">
       <c r="A17" s="105" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B17" s="60" t="s">
+        <v>451</v>
+      </c>
+      <c r="C17" s="61" t="s">
+        <v>452</v>
+      </c>
+      <c r="D17" s="61" t="s">
         <v>453</v>
       </c>
-      <c r="C17" s="61" t="s">
+      <c r="E17" s="61" t="s">
+        <v>449</v>
+      </c>
+      <c r="F17" s="120" t="s">
         <v>454</v>
-      </c>
-      <c r="D17" s="61" t="s">
-        <v>455</v>
-      </c>
-      <c r="E17" s="61" t="s">
-        <v>451</v>
-      </c>
-      <c r="F17" s="120" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="25.5" customHeight="1">
       <c r="A18" s="104" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B18" s="59" t="s">
+        <v>455</v>
+      </c>
+      <c r="C18" s="47" t="s">
+        <v>456</v>
+      </c>
+      <c r="D18" s="47" t="s">
         <v>457</v>
       </c>
-      <c r="C18" s="47" t="s">
+      <c r="E18" s="47" t="s">
+        <v>449</v>
+      </c>
+      <c r="F18" s="119" t="s">
         <v>458</v>
-      </c>
-      <c r="D18" s="47" t="s">
-        <v>459</v>
-      </c>
-      <c r="E18" s="47" t="s">
-        <v>451</v>
-      </c>
-      <c r="F18" s="119" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="25.5" customHeight="1">
       <c r="A19" s="105" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B19" s="60" t="s">
+        <v>459</v>
+      </c>
+      <c r="C19" s="61" t="s">
+        <v>460</v>
+      </c>
+      <c r="D19" s="61" t="s">
         <v>461</v>
       </c>
-      <c r="C19" s="61" t="s">
+      <c r="E19" s="61" t="s">
         <v>462</v>
       </c>
-      <c r="D19" s="61" t="s">
+      <c r="F19" s="120" t="s">
         <v>463</v>
-      </c>
-      <c r="E19" s="61" t="s">
-        <v>464</v>
-      </c>
-      <c r="F19" s="120" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="25.5" customHeight="1">
       <c r="A20" s="105" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B20" s="207" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="C20" s="61" t="s">
+        <v>465</v>
+      </c>
+      <c r="D20" s="61" t="s">
+        <v>466</v>
+      </c>
+      <c r="E20" s="61" t="s">
         <v>467</v>
       </c>
-      <c r="D20" s="61" t="s">
+      <c r="F20" s="120" t="s">
         <v>468</v>
-      </c>
-      <c r="E20" s="61" t="s">
-        <v>469</v>
-      </c>
-      <c r="F20" s="120" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="25.5" customHeight="1">
       <c r="A21" s="106" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B21" s="212" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="C21" s="20" t="s">
+        <v>469</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>470</v>
+      </c>
+      <c r="E21" s="20" t="s">
         <v>471</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>472</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>473</v>
       </c>
       <c r="F21" s="121" t="s">
         <v>69</v>
@@ -16479,36 +16653,36 @@
     </row>
     <row r="22" spans="1:6" ht="42" customHeight="1">
       <c r="A22" s="106" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B22" s="212" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="F22" s="121" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="42" customHeight="1">
       <c r="A23" s="98" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B23" s="214" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>57</v>
@@ -16519,2134 +16693,2214 @@
     </row>
     <row r="24" spans="1:6" ht="25.5" customHeight="1">
       <c r="A24" s="105" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B24" s="207" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="C24" s="61" t="s">
+        <v>474</v>
+      </c>
+      <c r="D24" s="61" t="s">
+        <v>475</v>
+      </c>
+      <c r="E24" s="61" t="s">
         <v>476</v>
       </c>
-      <c r="D24" s="61" t="s">
+      <c r="F24" s="120" t="s">
         <v>477</v>
-      </c>
-      <c r="E24" s="61" t="s">
-        <v>478</v>
-      </c>
-      <c r="F24" s="120" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="25.5" customHeight="1">
       <c r="A25" s="105" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B25" s="207" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="C25" s="61" t="s">
+        <v>478</v>
+      </c>
+      <c r="D25" s="61" t="s">
+        <v>479</v>
+      </c>
+      <c r="E25" s="61" t="s">
         <v>480</v>
       </c>
-      <c r="D25" s="61" t="s">
+      <c r="F25" s="120" t="s">
         <v>481</v>
-      </c>
-      <c r="E25" s="61" t="s">
-        <v>482</v>
-      </c>
-      <c r="F25" s="120" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="25.5" customHeight="1">
       <c r="A26" s="105" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B26" s="207" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="C26" s="61" t="s">
+        <v>482</v>
+      </c>
+      <c r="D26" s="61" t="s">
+        <v>483</v>
+      </c>
+      <c r="E26" s="61" t="s">
         <v>484</v>
       </c>
-      <c r="D26" s="61" t="s">
+      <c r="F26" s="120" t="s">
         <v>485</v>
-      </c>
-      <c r="E26" s="61" t="s">
-        <v>486</v>
-      </c>
-      <c r="F26" s="120" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="42" customHeight="1">
       <c r="A27" s="105" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B27" s="207" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C27" s="61" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="D27" s="61" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="E27" s="61" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="F27" s="120" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="42" customHeight="1">
       <c r="A28" s="107" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B28" s="215" t="s">
+        <v>991</v>
+      </c>
+      <c r="C28" s="36" t="s">
+        <v>994</v>
+      </c>
+      <c r="D28" s="36" t="s">
         <v>995</v>
-      </c>
-      <c r="C28" s="36" t="s">
-        <v>998</v>
-      </c>
-      <c r="D28" s="36" t="s">
-        <v>999</v>
       </c>
       <c r="E28" s="36" t="s">
         <v>61</v>
       </c>
       <c r="F28" s="122" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="28">
       <c r="A29" s="102" t="s">
+        <v>442</v>
+      </c>
+      <c r="B29" s="209" t="s">
+        <v>992</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>486</v>
+      </c>
+      <c r="D29" s="33" t="s">
+        <v>944</v>
+      </c>
+      <c r="E29" s="33" t="s">
+        <v>487</v>
+      </c>
+      <c r="F29" s="117" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="42" customHeight="1">
+      <c r="A30" s="217" t="s">
+        <v>442</v>
+      </c>
+      <c r="B30" s="218" t="s">
+        <v>705</v>
+      </c>
+      <c r="C30" s="61" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D30" s="61" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E30" s="61" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F30" s="120" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="42" customHeight="1">
+      <c r="A31" s="217" t="s">
+        <v>442</v>
+      </c>
+      <c r="B31" s="218" t="s">
+        <v>705</v>
+      </c>
+      <c r="C31" s="61" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D31" s="61" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E31" s="61" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F31" s="120" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="56" customHeight="1">
+      <c r="A32" s="217" t="s">
+        <v>442</v>
+      </c>
+      <c r="B32" s="218" t="s">
+        <v>705</v>
+      </c>
+      <c r="C32" s="61" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D32" s="61" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E32" s="61" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F32" s="120" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A33" s="102" t="s">
+        <v>442</v>
+      </c>
+      <c r="B33" s="57" t="s">
+        <v>939</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>940</v>
+      </c>
+      <c r="D33" s="33" t="s">
+        <v>941</v>
+      </c>
+      <c r="E33" s="33" t="s">
+        <v>942</v>
+      </c>
+      <c r="F33" s="117" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="30" customHeight="1">
+      <c r="A34" s="107" t="s">
+        <v>442</v>
+      </c>
+      <c r="B34" s="64" t="s">
+        <v>945</v>
+      </c>
+      <c r="C34" s="36" t="s">
+        <v>488</v>
+      </c>
+      <c r="D34" s="36" t="s">
+        <v>489</v>
+      </c>
+      <c r="E34" s="36" t="s">
+        <v>490</v>
+      </c>
+      <c r="F34" s="122" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A35" s="101" t="s">
+        <v>442</v>
+      </c>
+      <c r="B35" s="151" t="s">
+        <v>928</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="F35" s="116" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A36" s="167" t="s">
+        <v>971</v>
+      </c>
+      <c r="B36" s="168"/>
+      <c r="C36" s="168"/>
+      <c r="D36" s="168"/>
+      <c r="E36" s="168"/>
+      <c r="F36" s="169"/>
+    </row>
+    <row r="37" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A37" s="101" t="s">
+        <v>494</v>
+      </c>
+      <c r="B37" s="56" t="s">
+        <v>495</v>
+      </c>
+      <c r="C37" s="10" t="s">
         <v>444</v>
       </c>
-      <c r="B29" s="209" t="s">
-        <v>996</v>
-      </c>
-      <c r="C29" s="33" t="s">
-        <v>488</v>
-      </c>
-      <c r="D29" s="33" t="s">
-        <v>948</v>
-      </c>
-      <c r="E29" s="33" t="s">
-        <v>489</v>
-      </c>
-      <c r="F29" s="117" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="25" customHeight="1">
-      <c r="A30" s="102" t="s">
-        <v>444</v>
-      </c>
-      <c r="B30" s="57" t="s">
-        <v>943</v>
-      </c>
-      <c r="C30" s="33" t="s">
-        <v>944</v>
-      </c>
-      <c r="D30" s="33" t="s">
-        <v>945</v>
-      </c>
-      <c r="E30" s="33" t="s">
-        <v>946</v>
-      </c>
-      <c r="F30" s="117" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A31" s="107" t="s">
-        <v>444</v>
-      </c>
-      <c r="B31" s="64" t="s">
-        <v>949</v>
-      </c>
-      <c r="C31" s="36" t="s">
-        <v>490</v>
-      </c>
-      <c r="D31" s="36" t="s">
-        <v>491</v>
-      </c>
-      <c r="E31" s="36" t="s">
-        <v>492</v>
-      </c>
-      <c r="F31" s="122" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A32" s="101" t="s">
-        <v>444</v>
-      </c>
-      <c r="B32" s="151" t="s">
-        <v>932</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>495</v>
-      </c>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10" t="s">
-        <v>443</v>
-      </c>
-      <c r="F32" s="116" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A33" s="167" t="s">
-        <v>975</v>
-      </c>
-      <c r="B33" s="168"/>
-      <c r="C33" s="168"/>
-      <c r="D33" s="168"/>
-      <c r="E33" s="168"/>
-      <c r="F33" s="169"/>
-    </row>
-    <row r="34" spans="1:6" ht="30" customHeight="1">
-      <c r="A34" s="101" t="s">
+      <c r="D37" s="10" t="s">
         <v>496</v>
       </c>
-      <c r="B34" s="56" t="s">
-        <v>497</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>446</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>498</v>
-      </c>
-      <c r="E34" s="10" t="s">
+      <c r="E37" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F34" s="116" t="s">
+      <c r="F37" s="116" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A35" s="105" t="s">
-        <v>496</v>
-      </c>
-      <c r="B35" s="60" t="s">
-        <v>499</v>
-      </c>
-      <c r="C35" s="61" t="s">
-        <v>500</v>
-      </c>
-      <c r="D35" s="61" t="s">
-        <v>501</v>
-      </c>
-      <c r="E35" s="61" t="s">
-        <v>502</v>
-      </c>
-      <c r="F35" s="120" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A36" s="105" t="s">
-        <v>496</v>
-      </c>
-      <c r="B36" s="60" t="s">
-        <v>504</v>
-      </c>
-      <c r="C36" s="61" t="s">
-        <v>505</v>
-      </c>
-      <c r="D36" s="61" t="s">
-        <v>506</v>
-      </c>
-      <c r="E36" s="61" t="s">
-        <v>507</v>
-      </c>
-      <c r="F36" s="120" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A37" s="104" t="s">
-        <v>496</v>
-      </c>
-      <c r="B37" s="59" t="s">
-        <v>509</v>
-      </c>
-      <c r="C37" s="47" t="s">
-        <v>510</v>
-      </c>
-      <c r="D37" s="47" t="s">
-        <v>511</v>
-      </c>
-      <c r="E37" s="47" t="s">
-        <v>451</v>
-      </c>
-      <c r="F37" s="119" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A38" s="99" t="s">
-        <v>496</v>
-      </c>
-      <c r="B38" s="54" t="s">
-        <v>512</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="D38" s="15" t="s">
-        <v>514</v>
-      </c>
-      <c r="E38" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F38" s="85" t="s">
-        <v>515</v>
+    <row r="38" spans="1:6" ht="70" customHeight="1">
+      <c r="A38" s="102" t="s">
+        <v>494</v>
+      </c>
+      <c r="B38" s="209" t="s">
+        <v>705</v>
+      </c>
+      <c r="C38" s="33" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D38" s="33" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E38" s="35" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F38" s="117" t="s">
+        <v>1064</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="30" customHeight="1">
       <c r="A39" s="105" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B39" s="60" t="s">
+        <v>497</v>
+      </c>
+      <c r="C39" s="61" t="s">
+        <v>498</v>
+      </c>
+      <c r="D39" s="61" t="s">
+        <v>499</v>
+      </c>
+      <c r="E39" s="61" t="s">
+        <v>500</v>
+      </c>
+      <c r="F39" s="120" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A40" s="105" t="s">
+        <v>494</v>
+      </c>
+      <c r="B40" s="60" t="s">
+        <v>502</v>
+      </c>
+      <c r="C40" s="61" t="s">
+        <v>503</v>
+      </c>
+      <c r="D40" s="61" t="s">
+        <v>504</v>
+      </c>
+      <c r="E40" s="61" t="s">
+        <v>505</v>
+      </c>
+      <c r="F40" s="120" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A41" s="104" t="s">
+        <v>494</v>
+      </c>
+      <c r="B41" s="59" t="s">
+        <v>507</v>
+      </c>
+      <c r="C41" s="47" t="s">
+        <v>508</v>
+      </c>
+      <c r="D41" s="47" t="s">
+        <v>509</v>
+      </c>
+      <c r="E41" s="47" t="s">
+        <v>449</v>
+      </c>
+      <c r="F41" s="119" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="42" customHeight="1">
+      <c r="A42" s="99" t="s">
+        <v>494</v>
+      </c>
+      <c r="B42" s="54" t="s">
+        <v>510</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>511</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>512</v>
+      </c>
+      <c r="E42" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F42" s="85" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A43" s="105" t="s">
+        <v>494</v>
+      </c>
+      <c r="B43" s="60" t="s">
+        <v>514</v>
+      </c>
+      <c r="C43" s="61" t="s">
+        <v>515</v>
+      </c>
+      <c r="D43" s="61" t="s">
         <v>516</v>
       </c>
-      <c r="C39" s="61" t="s">
+      <c r="E43" s="61" t="s">
+        <v>505</v>
+      </c>
+      <c r="F43" s="120" t="s">
         <v>517</v>
       </c>
-      <c r="D39" s="61" t="s">
+    </row>
+    <row r="44" spans="1:6" ht="42" customHeight="1">
+      <c r="A44" s="103" t="s">
+        <v>494</v>
+      </c>
+      <c r="B44" s="58" t="s">
         <v>518</v>
       </c>
-      <c r="E39" s="61" t="s">
-        <v>507</v>
-      </c>
-      <c r="F39" s="120" t="s">
+      <c r="C44" s="39" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A40" s="103" t="s">
-        <v>496</v>
-      </c>
-      <c r="B40" s="58" t="s">
+      <c r="D44" s="39" t="s">
         <v>520</v>
       </c>
-      <c r="C40" s="39" t="s">
+      <c r="E44" s="39" t="s">
         <v>521</v>
       </c>
-      <c r="D40" s="39" t="s">
+      <c r="F44" s="118" t="s">
         <v>522</v>
       </c>
-      <c r="E40" s="39" t="s">
+    </row>
+    <row r="45" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A45" s="108" t="s">
+        <v>494</v>
+      </c>
+      <c r="B45" s="89" t="s">
+        <v>900</v>
+      </c>
+      <c r="C45" s="90" t="s">
+        <v>901</v>
+      </c>
+      <c r="D45" s="90" t="s">
+        <v>902</v>
+      </c>
+      <c r="E45" s="90" t="s">
+        <v>903</v>
+      </c>
+      <c r="F45" s="123" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A46" s="102" t="s">
+        <v>494</v>
+      </c>
+      <c r="B46" s="57" t="s">
+        <v>631</v>
+      </c>
+      <c r="C46" s="33" t="s">
         <v>523</v>
       </c>
-      <c r="F40" s="118" t="s">
+      <c r="D46" s="33" t="s">
         <v>524</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A41" s="108" t="s">
-        <v>496</v>
-      </c>
-      <c r="B41" s="89" t="s">
-        <v>904</v>
-      </c>
-      <c r="C41" s="90" t="s">
-        <v>905</v>
-      </c>
-      <c r="D41" s="90" t="s">
-        <v>906</v>
-      </c>
-      <c r="E41" s="90" t="s">
-        <v>907</v>
-      </c>
-      <c r="F41" s="123" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="42" customHeight="1">
-      <c r="A42" s="102" t="s">
-        <v>496</v>
-      </c>
-      <c r="B42" s="57" t="s">
-        <v>633</v>
-      </c>
-      <c r="C42" s="33" t="s">
+      <c r="E46" s="35" t="s">
         <v>525</v>
       </c>
-      <c r="D42" s="33" t="s">
+      <c r="F46" s="117" t="s">
         <v>526</v>
       </c>
-      <c r="E42" s="35" t="s">
+    </row>
+    <row r="47" spans="1:6" ht="42" customHeight="1">
+      <c r="A47" s="102" t="s">
+        <v>494</v>
+      </c>
+      <c r="B47" s="209" t="s">
+        <v>705</v>
+      </c>
+      <c r="C47" s="33" t="s">
+        <v>962</v>
+      </c>
+      <c r="D47" s="33" t="s">
+        <v>963</v>
+      </c>
+      <c r="E47" s="35" t="s">
+        <v>629</v>
+      </c>
+      <c r="F47" s="117" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="42" customHeight="1">
+      <c r="A48" s="106" t="s">
+        <v>494</v>
+      </c>
+      <c r="B48" s="63" t="s">
+        <v>922</v>
+      </c>
+      <c r="C48" s="20" t="s">
         <v>527</v>
       </c>
-      <c r="F42" s="117" t="s">
+      <c r="D48" s="20" t="s">
         <v>528</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A43" s="102" t="s">
-        <v>496</v>
-      </c>
-      <c r="B43" s="209" t="s">
-        <v>707</v>
-      </c>
-      <c r="C43" s="33" t="s">
-        <v>966</v>
-      </c>
-      <c r="D43" s="33" t="s">
-        <v>967</v>
-      </c>
-      <c r="E43" s="35" t="s">
-        <v>631</v>
-      </c>
-      <c r="F43" s="117" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="42" customHeight="1">
-      <c r="A44" s="106" t="s">
-        <v>496</v>
-      </c>
-      <c r="B44" s="63" t="s">
-        <v>926</v>
-      </c>
-      <c r="C44" s="20" t="s">
+      <c r="E48" s="20" t="s">
         <v>529</v>
       </c>
-      <c r="D44" s="20" t="s">
+      <c r="F48" s="121" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="42" customHeight="1">
+      <c r="A49" s="105" t="s">
+        <v>494</v>
+      </c>
+      <c r="B49" s="207" t="s">
+        <v>996</v>
+      </c>
+      <c r="C49" s="61" t="s">
         <v>530</v>
       </c>
-      <c r="E44" s="20" t="s">
+      <c r="D49" s="61" t="s">
+        <v>997</v>
+      </c>
+      <c r="E49" s="61" t="s">
         <v>531</v>
       </c>
-      <c r="F44" s="121" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A45" s="105" t="s">
-        <v>496</v>
-      </c>
-      <c r="B45" s="207" t="s">
+      <c r="F49" s="120" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A50" s="103" t="s">
+        <v>494</v>
+      </c>
+      <c r="B50" s="210" t="s">
+        <v>705</v>
+      </c>
+      <c r="C50" s="39" t="s">
+        <v>533</v>
+      </c>
+      <c r="D50" s="39" t="s">
+        <v>998</v>
+      </c>
+      <c r="E50" s="39" t="s">
+        <v>999</v>
+      </c>
+      <c r="F50" s="118" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A51" s="98" t="s">
+        <v>494</v>
+      </c>
+      <c r="B51" s="53" t="s">
         <v>1000</v>
       </c>
-      <c r="C45" s="61" t="s">
-        <v>532</v>
-      </c>
-      <c r="D45" s="61" t="s">
+      <c r="C51" s="5" t="s">
         <v>1001</v>
       </c>
-      <c r="E45" s="61" t="s">
-        <v>533</v>
-      </c>
-      <c r="F45" s="120" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A46" s="103" t="s">
-        <v>496</v>
-      </c>
-      <c r="B46" s="210" t="s">
-        <v>707</v>
-      </c>
-      <c r="C46" s="39" t="s">
-        <v>535</v>
-      </c>
-      <c r="D46" s="39" t="s">
+      <c r="D51" s="5" t="s">
         <v>1002</v>
       </c>
-      <c r="E46" s="39" t="s">
+      <c r="E51" s="5" t="s">
         <v>1003</v>
       </c>
-      <c r="F46" s="118" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="42" customHeight="1">
-      <c r="A47" s="98" t="s">
-        <v>496</v>
-      </c>
-      <c r="B47" s="53" t="s">
+      <c r="F51" s="86" t="s">
         <v>1004</v>
       </c>
-      <c r="C47" s="5" t="s">
+    </row>
+    <row r="52" spans="1:6" ht="42" customHeight="1">
+      <c r="A52" s="98" t="s">
+        <v>494</v>
+      </c>
+      <c r="B52" s="214" t="s">
         <v>1005</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="C52" s="5" t="s">
         <v>1006</v>
       </c>
-      <c r="E47" s="5" t="s">
+      <c r="D52" s="5" t="s">
         <v>1007</v>
       </c>
-      <c r="F47" s="86" t="s">
+      <c r="E52" s="5" t="s">
         <v>1008</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" ht="42" customHeight="1">
-      <c r="A48" s="98" t="s">
-        <v>496</v>
-      </c>
-      <c r="B48" s="214" t="s">
+      <c r="F52" s="86" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="30" customHeight="1">
+      <c r="A53" s="101" t="s">
+        <v>494</v>
+      </c>
+      <c r="B53" s="151" t="s">
+        <v>928</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>538</v>
+      </c>
+      <c r="D53" s="10" t="s">
         <v>1009</v>
       </c>
-      <c r="C48" s="5" t="s">
-        <v>1010</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>1011</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>1012</v>
-      </c>
-      <c r="F48" s="86" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="42" customHeight="1">
-      <c r="A49" s="101" t="s">
-        <v>496</v>
-      </c>
-      <c r="B49" s="151" t="s">
-        <v>932</v>
-      </c>
-      <c r="C49" s="10" t="s">
+      <c r="E53" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="F53" s="116" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A54" s="109" t="s">
+        <v>494</v>
+      </c>
+      <c r="B54" s="65" t="s">
+        <v>539</v>
+      </c>
+      <c r="C54" s="42" t="s">
         <v>540</v>
       </c>
-      <c r="D49" s="10" t="s">
-        <v>1013</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>443</v>
-      </c>
-      <c r="F49" s="116" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A50" s="109" t="s">
-        <v>496</v>
-      </c>
-      <c r="B50" s="65" t="s">
+      <c r="D54" s="42" t="s">
         <v>541</v>
       </c>
-      <c r="C50" s="42" t="s">
+      <c r="E54" s="42" t="s">
         <v>542</v>
       </c>
-      <c r="D50" s="42" t="s">
+      <c r="F54" s="124" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A55" s="103" t="s">
+        <v>494</v>
+      </c>
+      <c r="B55" s="58" t="s">
+        <v>539</v>
+      </c>
+      <c r="C55" s="39" t="s">
         <v>543</v>
       </c>
-      <c r="E50" s="42" t="s">
+      <c r="D55" s="39" t="s">
         <v>544</v>
       </c>
-      <c r="F50" s="124" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A51" s="103" t="s">
-        <v>496</v>
-      </c>
-      <c r="B51" s="58" t="s">
-        <v>541</v>
-      </c>
-      <c r="C51" s="39" t="s">
+      <c r="E55" s="39" t="s">
+        <v>542</v>
+      </c>
+      <c r="F55" s="118" t="s">
         <v>545</v>
       </c>
-      <c r="D51" s="39" t="s">
+    </row>
+    <row r="56" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A56" s="103" t="s">
+        <v>494</v>
+      </c>
+      <c r="B56" s="210" t="s">
+        <v>539</v>
+      </c>
+      <c r="C56" s="39" t="s">
+        <v>958</v>
+      </c>
+      <c r="D56" s="211" t="s">
+        <v>959</v>
+      </c>
+      <c r="E56" s="39" t="s">
+        <v>960</v>
+      </c>
+      <c r="F56" s="118" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A57" s="152" t="s">
+        <v>978</v>
+      </c>
+      <c r="B57" s="153"/>
+      <c r="C57" s="153"/>
+      <c r="D57" s="153"/>
+      <c r="E57" s="153"/>
+      <c r="F57" s="154"/>
+    </row>
+    <row r="58" spans="1:6" ht="45" customHeight="1">
+      <c r="A58" s="101" t="s">
         <v>546</v>
       </c>
-      <c r="E51" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="F51" s="118" t="s">
+      <c r="B58" s="56" t="s">
+        <v>495</v>
+      </c>
+      <c r="C58" s="10" t="s">
         <v>547</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" ht="42" customHeight="1">
-      <c r="A52" s="103" t="s">
-        <v>496</v>
-      </c>
-      <c r="B52" s="210" t="s">
-        <v>541</v>
-      </c>
-      <c r="C52" s="39" t="s">
-        <v>962</v>
-      </c>
-      <c r="D52" s="211" t="s">
-        <v>963</v>
-      </c>
-      <c r="E52" s="39" t="s">
-        <v>964</v>
-      </c>
-      <c r="F52" s="118" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="30" customHeight="1">
-      <c r="A53" s="152" t="s">
-        <v>982</v>
-      </c>
-      <c r="B53" s="153"/>
-      <c r="C53" s="153"/>
-      <c r="D53" s="153"/>
-      <c r="E53" s="153"/>
-      <c r="F53" s="154"/>
-    </row>
-    <row r="54" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A54" s="101" t="s">
+      <c r="D58" s="10" t="s">
         <v>548</v>
       </c>
-      <c r="B54" s="56" t="s">
-        <v>497</v>
-      </c>
-      <c r="C54" s="10" t="s">
+      <c r="E58" s="10" t="s">
         <v>549</v>
       </c>
-      <c r="D54" s="10" t="s">
+      <c r="F58" s="116" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A59" s="100" t="s">
+        <v>546</v>
+      </c>
+      <c r="B59" s="55" t="s">
         <v>550</v>
       </c>
-      <c r="E54" s="10" t="s">
+      <c r="C59" s="50" t="s">
         <v>551</v>
       </c>
-      <c r="F54" s="116" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A55" s="100" t="s">
-        <v>548</v>
-      </c>
-      <c r="B55" s="55" t="s">
+      <c r="D59" s="50" t="s">
         <v>552</v>
       </c>
-      <c r="C55" s="50" t="s">
+      <c r="E59" s="50" t="s">
         <v>553</v>
       </c>
-      <c r="D55" s="50" t="s">
+      <c r="F59" s="115" t="s">
         <v>554</v>
       </c>
-      <c r="E55" s="50" t="s">
+    </row>
+    <row r="60" spans="1:6" ht="30" customHeight="1">
+      <c r="A60" s="100" t="s">
+        <v>546</v>
+      </c>
+      <c r="B60" s="55" t="s">
         <v>555</v>
       </c>
-      <c r="F55" s="115" t="s">
+      <c r="C60" s="50" t="s">
         <v>556</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A56" s="100" t="s">
-        <v>548</v>
-      </c>
-      <c r="B56" s="55" t="s">
+      <c r="D60" s="50" t="s">
         <v>557</v>
       </c>
-      <c r="C56" s="50" t="s">
+      <c r="E60" s="50" t="s">
         <v>558</v>
       </c>
-      <c r="D56" s="50" t="s">
+      <c r="F60" s="115" t="s">
         <v>559</v>
       </c>
-      <c r="E56" s="50" t="s">
+    </row>
+    <row r="61" spans="1:6" ht="30" customHeight="1">
+      <c r="A61" s="101" t="s">
+        <v>546</v>
+      </c>
+      <c r="B61" s="56" t="s">
         <v>560</v>
       </c>
-      <c r="F56" s="115" t="s">
+      <c r="C61" s="10" t="s">
         <v>561</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A57" s="101" t="s">
-        <v>548</v>
-      </c>
-      <c r="B57" s="56" t="s">
+      <c r="D61" s="10" t="s">
         <v>562</v>
       </c>
-      <c r="C57" s="10" t="s">
+      <c r="E61" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="F61" s="116" t="s">
         <v>563</v>
       </c>
-      <c r="D57" s="10" t="s">
+    </row>
+    <row r="62" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A62" s="99" t="s">
+        <v>546</v>
+      </c>
+      <c r="B62" s="54" t="s">
         <v>564</v>
       </c>
-      <c r="E57" s="10" t="s">
-        <v>425</v>
-      </c>
-      <c r="F57" s="116" t="s">
+      <c r="C62" s="15" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" ht="45" customHeight="1">
-      <c r="A58" s="99" t="s">
-        <v>548</v>
-      </c>
-      <c r="B58" s="54" t="s">
+      <c r="D62" s="25" t="s">
         <v>566</v>
       </c>
-      <c r="C58" s="15" t="s">
+      <c r="E62" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="F62" s="85" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="21.75" customHeight="1">
+      <c r="A63" s="105" t="s">
+        <v>546</v>
+      </c>
+      <c r="B63" s="60" t="s">
         <v>567</v>
       </c>
-      <c r="D58" s="25" t="s">
+      <c r="C63" s="61" t="s">
         <v>568</v>
       </c>
-      <c r="E58" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="F58" s="85" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A59" s="105" t="s">
-        <v>548</v>
-      </c>
-      <c r="B59" s="60" t="s">
+      <c r="D63" s="61" t="s">
         <v>569</v>
       </c>
-      <c r="C59" s="61" t="s">
-        <v>570</v>
-      </c>
-      <c r="D59" s="61" t="s">
-        <v>571</v>
-      </c>
-      <c r="E59" s="61" t="s">
-        <v>507</v>
-      </c>
-      <c r="F59" s="120" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="30" customHeight="1">
-      <c r="A60" s="105" t="s">
-        <v>548</v>
-      </c>
-      <c r="B60" s="60" t="s">
-        <v>572</v>
-      </c>
-      <c r="C60" s="61" t="s">
-        <v>573</v>
-      </c>
-      <c r="D60" s="61" t="s">
-        <v>574</v>
-      </c>
-      <c r="E60" s="61" t="s">
-        <v>575</v>
-      </c>
-      <c r="F60" s="120" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="30" customHeight="1">
-      <c r="A61" s="106" t="s">
-        <v>548</v>
-      </c>
-      <c r="B61" s="63" t="s">
-        <v>577</v>
-      </c>
-      <c r="C61" s="20" t="s">
-        <v>578</v>
-      </c>
-      <c r="D61" s="20" t="s">
-        <v>579</v>
-      </c>
-      <c r="E61" s="20" t="s">
-        <v>580</v>
-      </c>
-      <c r="F61" s="121" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A62" s="105" t="s">
-        <v>548</v>
-      </c>
-      <c r="B62" s="60" t="s">
-        <v>582</v>
-      </c>
-      <c r="C62" s="61" t="s">
-        <v>583</v>
-      </c>
-      <c r="D62" s="61" t="s">
-        <v>584</v>
-      </c>
-      <c r="E62" s="61" t="s">
-        <v>575</v>
-      </c>
-      <c r="F62" s="120" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A63" s="110" t="s">
-        <v>548</v>
-      </c>
-      <c r="B63" s="91" t="s">
-        <v>927</v>
-      </c>
-      <c r="C63" s="92" t="s">
-        <v>909</v>
-      </c>
-      <c r="D63" s="92" t="s">
-        <v>910</v>
-      </c>
-      <c r="E63" s="92" t="s">
-        <v>911</v>
-      </c>
-      <c r="F63" s="125" t="s">
-        <v>912</v>
+      <c r="E63" s="61" t="s">
+        <v>505</v>
+      </c>
+      <c r="F63" s="120" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="25.5" customHeight="1">
       <c r="A64" s="105" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B64" s="60" t="s">
+        <v>570</v>
+      </c>
+      <c r="C64" s="61" t="s">
+        <v>571</v>
+      </c>
+      <c r="D64" s="61" t="s">
+        <v>572</v>
+      </c>
+      <c r="E64" s="61" t="s">
+        <v>573</v>
+      </c>
+      <c r="F64" s="120" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A65" s="106" t="s">
+        <v>546</v>
+      </c>
+      <c r="B65" s="63" t="s">
+        <v>575</v>
+      </c>
+      <c r="C65" s="20" t="s">
+        <v>576</v>
+      </c>
+      <c r="D65" s="20" t="s">
+        <v>577</v>
+      </c>
+      <c r="E65" s="20" t="s">
+        <v>578</v>
+      </c>
+      <c r="F65" s="121" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="30" customHeight="1">
+      <c r="A66" s="105" t="s">
+        <v>546</v>
+      </c>
+      <c r="B66" s="60" t="s">
+        <v>580</v>
+      </c>
+      <c r="C66" s="61" t="s">
+        <v>581</v>
+      </c>
+      <c r="D66" s="61" t="s">
+        <v>582</v>
+      </c>
+      <c r="E66" s="61" t="s">
+        <v>573</v>
+      </c>
+      <c r="F66" s="120" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="30" customHeight="1">
+      <c r="A67" s="110" t="s">
+        <v>546</v>
+      </c>
+      <c r="B67" s="91" t="s">
+        <v>923</v>
+      </c>
+      <c r="C67" s="92" t="s">
+        <v>905</v>
+      </c>
+      <c r="D67" s="92" t="s">
+        <v>906</v>
+      </c>
+      <c r="E67" s="92" t="s">
+        <v>907</v>
+      </c>
+      <c r="F67" s="125" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="30" customHeight="1">
+      <c r="A68" s="105" t="s">
+        <v>546</v>
+      </c>
+      <c r="B68" s="60" t="s">
+        <v>588</v>
+      </c>
+      <c r="C68" s="61" t="s">
+        <v>584</v>
+      </c>
+      <c r="D68" s="61" t="s">
+        <v>585</v>
+      </c>
+      <c r="E68" s="61" t="s">
+        <v>586</v>
+      </c>
+      <c r="F68" s="120" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A69" s="107" t="s">
+        <v>546</v>
+      </c>
+      <c r="B69" s="64" t="s">
+        <v>924</v>
+      </c>
+      <c r="C69" s="36" t="s">
+        <v>589</v>
+      </c>
+      <c r="D69" s="36" t="s">
         <v>590</v>
       </c>
-      <c r="C64" s="61" t="s">
-        <v>586</v>
-      </c>
-      <c r="D64" s="61" t="s">
-        <v>587</v>
-      </c>
-      <c r="E64" s="61" t="s">
-        <v>588</v>
-      </c>
-      <c r="F64" s="120" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A65" s="107" t="s">
-        <v>548</v>
-      </c>
-      <c r="B65" s="64" t="s">
+      <c r="E69" s="36" t="s">
+        <v>591</v>
+      </c>
+      <c r="F69" s="122" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A70" s="109" t="s">
+        <v>546</v>
+      </c>
+      <c r="B70" s="65" t="s">
+        <v>925</v>
+      </c>
+      <c r="C70" s="42" t="s">
+        <v>593</v>
+      </c>
+      <c r="D70" s="44" t="s">
+        <v>594</v>
+      </c>
+      <c r="E70" s="42" t="s">
+        <v>595</v>
+      </c>
+      <c r="F70" s="124" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="30" customHeight="1">
+      <c r="A71" s="101" t="s">
+        <v>546</v>
+      </c>
+      <c r="B71" s="128" t="s">
         <v>928</v>
       </c>
-      <c r="C65" s="36" t="s">
-        <v>591</v>
-      </c>
-      <c r="D65" s="36" t="s">
-        <v>592</v>
-      </c>
-      <c r="E65" s="36" t="s">
-        <v>593</v>
-      </c>
-      <c r="F65" s="122" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="30" customHeight="1">
-      <c r="A66" s="109" t="s">
-        <v>548</v>
-      </c>
-      <c r="B66" s="65" t="s">
-        <v>929</v>
-      </c>
-      <c r="C66" s="42" t="s">
-        <v>595</v>
-      </c>
-      <c r="D66" s="44" t="s">
-        <v>596</v>
-      </c>
-      <c r="E66" s="42" t="s">
-        <v>597</v>
-      </c>
-      <c r="F66" s="124" t="s">
+      <c r="C71" s="10" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" ht="30" customHeight="1">
-      <c r="A67" s="101" t="s">
-        <v>548</v>
-      </c>
-      <c r="B67" s="128" t="s">
-        <v>932</v>
-      </c>
-      <c r="C67" s="10" t="s">
+      <c r="D71" s="10"/>
+      <c r="E71" s="10" t="s">
+        <v>599</v>
+      </c>
+      <c r="F71" s="116" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="30" customHeight="1">
+      <c r="A72" s="152" t="s">
+        <v>972</v>
+      </c>
+      <c r="B72" s="153"/>
+      <c r="C72" s="153"/>
+      <c r="D72" s="153"/>
+      <c r="E72" s="153"/>
+      <c r="F72" s="154"/>
+    </row>
+    <row r="73" spans="1:6" ht="30" customHeight="1">
+      <c r="A73" s="101" t="s">
         <v>600</v>
       </c>
-      <c r="D67" s="10"/>
-      <c r="E67" s="10" t="s">
+      <c r="B73" s="56" t="s">
+        <v>495</v>
+      </c>
+      <c r="C73" s="10" t="s">
         <v>601</v>
       </c>
-      <c r="F67" s="116" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="30" customHeight="1">
-      <c r="A68" s="152" t="s">
-        <v>976</v>
-      </c>
-      <c r="B68" s="153"/>
-      <c r="C68" s="153"/>
-      <c r="D68" s="153"/>
-      <c r="E68" s="153"/>
-      <c r="F68" s="154"/>
-    </row>
-    <row r="69" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A69" s="101" t="s">
+      <c r="D73" s="10" t="s">
         <v>602</v>
       </c>
-      <c r="B69" s="56" t="s">
-        <v>497</v>
-      </c>
-      <c r="C69" s="10" t="s">
-        <v>603</v>
-      </c>
-      <c r="D69" s="10" t="s">
-        <v>604</v>
-      </c>
-      <c r="E69" s="10" t="s">
+      <c r="E73" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F69" s="116" t="s">
+      <c r="F73" s="116" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A70" s="105" t="s">
-        <v>602</v>
-      </c>
-      <c r="B70" s="60" t="s">
-        <v>605</v>
-      </c>
-      <c r="C70" s="61" t="s">
-        <v>606</v>
-      </c>
-      <c r="D70" s="62" t="s">
-        <v>607</v>
-      </c>
-      <c r="E70" s="61" t="s">
-        <v>608</v>
-      </c>
-      <c r="F70" s="120" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="30" customHeight="1">
-      <c r="A71" s="108" t="s">
-        <v>602</v>
-      </c>
-      <c r="B71" s="89" t="s">
-        <v>913</v>
-      </c>
-      <c r="C71" s="90" t="s">
-        <v>914</v>
-      </c>
-      <c r="D71" s="90" t="s">
-        <v>915</v>
-      </c>
-      <c r="E71" s="90" t="s">
-        <v>916</v>
-      </c>
-      <c r="F71" s="123" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="30" customHeight="1">
-      <c r="A72" s="103" t="s">
-        <v>602</v>
-      </c>
-      <c r="B72" s="58" t="s">
-        <v>930</v>
-      </c>
-      <c r="C72" s="39" t="s">
-        <v>610</v>
-      </c>
-      <c r="D72" s="39" t="s">
-        <v>611</v>
-      </c>
-      <c r="E72" s="39" t="s">
-        <v>612</v>
-      </c>
-      <c r="F72" s="118" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="30" customHeight="1">
-      <c r="A73" s="104" t="s">
-        <v>602</v>
-      </c>
-      <c r="B73" s="59" t="s">
-        <v>466</v>
-      </c>
-      <c r="C73" s="47" t="s">
-        <v>614</v>
-      </c>
-      <c r="D73" s="47" t="s">
-        <v>615</v>
-      </c>
-      <c r="E73" s="47" t="s">
-        <v>616</v>
-      </c>
-      <c r="F73" s="119" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="25.5" customHeight="1">
       <c r="A74" s="105" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B74" s="60" t="s">
-        <v>618</v>
+        <v>603</v>
       </c>
       <c r="C74" s="61" t="s">
-        <v>619</v>
-      </c>
-      <c r="D74" s="61" t="s">
-        <v>620</v>
+        <v>604</v>
+      </c>
+      <c r="D74" s="62" t="s">
+        <v>605</v>
       </c>
       <c r="E74" s="61" t="s">
-        <v>621</v>
+        <v>606</v>
       </c>
       <c r="F74" s="120" t="s">
-        <v>622</v>
+        <v>607</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="30" customHeight="1">
-      <c r="A75" s="98" t="s">
-        <v>602</v>
-      </c>
-      <c r="B75" s="53" t="s">
-        <v>623</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>624</v>
-      </c>
-      <c r="D75" s="5" t="s">
-        <v>625</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>626</v>
-      </c>
-      <c r="F75" s="86" t="s">
-        <v>627</v>
+      <c r="A75" s="108" t="s">
+        <v>600</v>
+      </c>
+      <c r="B75" s="89" t="s">
+        <v>909</v>
+      </c>
+      <c r="C75" s="90" t="s">
+        <v>910</v>
+      </c>
+      <c r="D75" s="90" t="s">
+        <v>911</v>
+      </c>
+      <c r="E75" s="90" t="s">
+        <v>912</v>
+      </c>
+      <c r="F75" s="123" t="s">
+        <v>913</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="30" customHeight="1">
       <c r="A76" s="103" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B76" s="58" t="s">
+        <v>926</v>
+      </c>
+      <c r="C76" s="39" t="s">
+        <v>608</v>
+      </c>
+      <c r="D76" s="39" t="s">
+        <v>609</v>
+      </c>
+      <c r="E76" s="39" t="s">
+        <v>610</v>
+      </c>
+      <c r="F76" s="118" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="42" customHeight="1">
+      <c r="A77" s="104" t="s">
+        <v>600</v>
+      </c>
+      <c r="B77" s="59" t="s">
+        <v>464</v>
+      </c>
+      <c r="C77" s="47" t="s">
+        <v>612</v>
+      </c>
+      <c r="D77" s="47" t="s">
+        <v>613</v>
+      </c>
+      <c r="E77" s="47" t="s">
+        <v>614</v>
+      </c>
+      <c r="F77" s="119" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A78" s="105" t="s">
+        <v>600</v>
+      </c>
+      <c r="B78" s="60" t="s">
+        <v>616</v>
+      </c>
+      <c r="C78" s="61" t="s">
+        <v>617</v>
+      </c>
+      <c r="D78" s="61" t="s">
+        <v>618</v>
+      </c>
+      <c r="E78" s="61" t="s">
+        <v>619</v>
+      </c>
+      <c r="F78" s="120" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="30" customHeight="1">
+      <c r="A79" s="98" t="s">
+        <v>600</v>
+      </c>
+      <c r="B79" s="53" t="s">
+        <v>621</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>624</v>
+      </c>
+      <c r="F79" s="86" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="30" customHeight="1">
+      <c r="A80" s="103" t="s">
+        <v>600</v>
+      </c>
+      <c r="B80" s="58" t="s">
+        <v>626</v>
+      </c>
+      <c r="C80" s="39" t="s">
+        <v>627</v>
+      </c>
+      <c r="D80" s="39" t="s">
         <v>628</v>
       </c>
-      <c r="C76" s="39" t="s">
+      <c r="E80" s="39" t="s">
         <v>629</v>
       </c>
-      <c r="D76" s="39" t="s">
+      <c r="F80" s="118" t="s">
         <v>630</v>
       </c>
-      <c r="E76" s="39" t="s">
+    </row>
+    <row r="81" spans="1:6" ht="42" customHeight="1">
+      <c r="A81" s="105" t="s">
+        <v>600</v>
+      </c>
+      <c r="B81" s="60" t="s">
         <v>631</v>
       </c>
-      <c r="F76" s="118" t="s">
+      <c r="C81" s="61" t="s">
         <v>632</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" ht="42" customHeight="1">
-      <c r="A77" s="105" t="s">
-        <v>602</v>
-      </c>
-      <c r="B77" s="60" t="s">
+      <c r="D81" s="61" t="s">
         <v>633</v>
       </c>
-      <c r="C77" s="61" t="s">
+      <c r="E81" s="61" t="s">
         <v>634</v>
       </c>
-      <c r="D77" s="61" t="s">
+      <c r="F81" s="120" t="s">
         <v>635</v>
       </c>
-      <c r="E77" s="61" t="s">
+    </row>
+    <row r="82" spans="1:6" ht="30" customHeight="1">
+      <c r="A82" s="104" t="s">
+        <v>600</v>
+      </c>
+      <c r="B82" s="59" t="s">
         <v>636</v>
       </c>
-      <c r="F77" s="120" t="s">
+      <c r="C82" s="47" t="s">
         <v>637</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A78" s="104" t="s">
-        <v>602</v>
-      </c>
-      <c r="B78" s="59" t="s">
+      <c r="D82" s="47" t="s">
         <v>638</v>
       </c>
-      <c r="C78" s="47" t="s">
+      <c r="E82" s="47" t="s">
+        <v>629</v>
+      </c>
+      <c r="F82" s="119" t="s">
         <v>639</v>
       </c>
-      <c r="D78" s="47" t="s">
+    </row>
+    <row r="83" spans="1:6" ht="21.75" customHeight="1">
+      <c r="A83" s="106" t="s">
+        <v>600</v>
+      </c>
+      <c r="B83" s="63" t="s">
         <v>640</v>
       </c>
-      <c r="E78" s="47" t="s">
-        <v>631</v>
-      </c>
-      <c r="F78" s="119" t="s">
+      <c r="C83" s="20" t="s">
         <v>641</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" ht="30" customHeight="1">
-      <c r="A79" s="106" t="s">
-        <v>602</v>
-      </c>
-      <c r="B79" s="63" t="s">
+      <c r="D83" s="20" t="s">
         <v>642</v>
       </c>
-      <c r="C79" s="20" t="s">
+      <c r="E83" s="20" t="s">
         <v>643</v>
       </c>
-      <c r="D79" s="20" t="s">
+      <c r="F83" s="121" t="s">
         <v>644</v>
       </c>
-      <c r="E79" s="20" t="s">
+    </row>
+    <row r="84" spans="1:6" ht="42" customHeight="1">
+      <c r="A84" s="102" t="s">
+        <v>600</v>
+      </c>
+      <c r="B84" s="57" t="s">
         <v>645</v>
       </c>
-      <c r="F79" s="121" t="s">
+      <c r="C84" s="33" t="s">
         <v>646</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" ht="30" customHeight="1">
-      <c r="A80" s="102" t="s">
-        <v>602</v>
-      </c>
-      <c r="B80" s="57" t="s">
+      <c r="D84" s="33" t="s">
         <v>647</v>
       </c>
-      <c r="C80" s="33" t="s">
+      <c r="E84" s="33" t="s">
         <v>648</v>
       </c>
-      <c r="D80" s="33" t="s">
+      <c r="F84" s="117" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A85" s="102" t="s">
+        <v>600</v>
+      </c>
+      <c r="B85" s="209" t="s">
+        <v>705</v>
+      </c>
+      <c r="C85" s="33" t="s">
+        <v>955</v>
+      </c>
+      <c r="D85" s="33" t="s">
+        <v>956</v>
+      </c>
+      <c r="E85" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="F85" s="117" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A86" s="107" t="s">
+        <v>600</v>
+      </c>
+      <c r="B86" s="64" t="s">
+        <v>536</v>
+      </c>
+      <c r="C86" s="36" t="s">
         <v>649</v>
       </c>
-      <c r="E80" s="33" t="s">
+      <c r="D86" s="36" t="s">
         <v>650</v>
       </c>
-      <c r="F80" s="117" t="s">
+      <c r="E86" s="36" t="s">
+        <v>209</v>
+      </c>
+      <c r="F86" s="122" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="30" customHeight="1">
+      <c r="A87" s="101" t="s">
+        <v>600</v>
+      </c>
+      <c r="B87" s="56" t="s">
+        <v>651</v>
+      </c>
+      <c r="C87" s="10" t="s">
+        <v>652</v>
+      </c>
+      <c r="D87" s="10" t="s">
+        <v>653</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>534</v>
+      </c>
+      <c r="F87" s="116" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="42" customHeight="1">
-      <c r="A81" s="102" t="s">
-        <v>602</v>
-      </c>
-      <c r="B81" s="209" t="s">
-        <v>707</v>
-      </c>
-      <c r="C81" s="33" t="s">
-        <v>959</v>
-      </c>
-      <c r="D81" s="33" t="s">
-        <v>960</v>
-      </c>
-      <c r="E81" s="33" t="s">
-        <v>631</v>
-      </c>
-      <c r="F81" s="117" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="30" customHeight="1">
-      <c r="A82" s="107" t="s">
-        <v>602</v>
-      </c>
-      <c r="B82" s="64" t="s">
-        <v>538</v>
-      </c>
-      <c r="C82" s="36" t="s">
-        <v>651</v>
-      </c>
-      <c r="D82" s="36" t="s">
-        <v>652</v>
-      </c>
-      <c r="E82" s="36" t="s">
-        <v>210</v>
-      </c>
-      <c r="F82" s="122" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A83" s="101" t="s">
-        <v>602</v>
-      </c>
-      <c r="B83" s="56" t="s">
-        <v>653</v>
-      </c>
-      <c r="C83" s="10" t="s">
+    <row r="88" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A88" s="101" t="s">
+        <v>600</v>
+      </c>
+      <c r="B88" s="56" t="s">
+        <v>597</v>
+      </c>
+      <c r="C88" s="10" t="s">
         <v>654</v>
       </c>
-      <c r="D83" s="10" t="s">
+      <c r="D88" s="10" t="s">
         <v>655</v>
       </c>
-      <c r="E83" s="10" t="s">
-        <v>536</v>
-      </c>
-      <c r="F83" s="116" t="s">
+      <c r="E88" s="10" t="s">
+        <v>599</v>
+      </c>
+      <c r="F88" s="116" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="42" customHeight="1">
+      <c r="A89" s="103" t="s">
+        <v>600</v>
+      </c>
+      <c r="B89" s="58" t="s">
+        <v>539</v>
+      </c>
+      <c r="C89" s="39" t="s">
+        <v>656</v>
+      </c>
+      <c r="D89" s="39" t="s">
+        <v>657</v>
+      </c>
+      <c r="E89" s="39" t="s">
+        <v>542</v>
+      </c>
+      <c r="F89" s="118" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="30" customHeight="1">
+      <c r="A90" s="103" t="s">
+        <v>600</v>
+      </c>
+      <c r="B90" s="58" t="s">
+        <v>539</v>
+      </c>
+      <c r="C90" s="39" t="s">
+        <v>659</v>
+      </c>
+      <c r="D90" s="39" t="s">
+        <v>660</v>
+      </c>
+      <c r="E90" s="39" t="s">
+        <v>542</v>
+      </c>
+      <c r="F90" s="118" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A91" s="103" t="s">
+        <v>600</v>
+      </c>
+      <c r="B91" s="58" t="s">
+        <v>539</v>
+      </c>
+      <c r="C91" s="39" t="s">
+        <v>662</v>
+      </c>
+      <c r="D91" s="39" t="s">
+        <v>663</v>
+      </c>
+      <c r="E91" s="39" t="s">
+        <v>542</v>
+      </c>
+      <c r="F91" s="118" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A92" s="108" t="s">
+        <v>600</v>
+      </c>
+      <c r="B92" s="89" t="s">
+        <v>539</v>
+      </c>
+      <c r="C92" s="90" t="s">
+        <v>914</v>
+      </c>
+      <c r="D92" s="95" t="s">
+        <v>915</v>
+      </c>
+      <c r="E92" s="90" t="s">
+        <v>916</v>
+      </c>
+      <c r="F92" s="123" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="30" customHeight="1">
+      <c r="A93" s="108" t="s">
+        <v>600</v>
+      </c>
+      <c r="B93" s="208" t="s">
+        <v>539</v>
+      </c>
+      <c r="C93" s="90" t="s">
+        <v>952</v>
+      </c>
+      <c r="D93" s="95" t="s">
+        <v>953</v>
+      </c>
+      <c r="E93" s="90" t="s">
+        <v>916</v>
+      </c>
+      <c r="F93" s="123" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="30" customHeight="1">
+      <c r="A94" s="155" t="s">
+        <v>979</v>
+      </c>
+      <c r="B94" s="156"/>
+      <c r="C94" s="156"/>
+      <c r="D94" s="156"/>
+      <c r="E94" s="156"/>
+      <c r="F94" s="157"/>
+    </row>
+    <row r="95" spans="1:6" ht="42" customHeight="1">
+      <c r="A95" s="101" t="s">
+        <v>665</v>
+      </c>
+      <c r="B95" s="56" t="s">
+        <v>495</v>
+      </c>
+      <c r="C95" s="10" t="s">
+        <v>666</v>
+      </c>
+      <c r="D95" s="10"/>
+      <c r="E95" s="10" t="s">
+        <v>549</v>
+      </c>
+      <c r="F95" s="116" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="42" customHeight="1">
-      <c r="A84" s="101" t="s">
-        <v>602</v>
-      </c>
-      <c r="B84" s="56" t="s">
-        <v>599</v>
-      </c>
-      <c r="C84" s="10" t="s">
-        <v>656</v>
-      </c>
-      <c r="D84" s="10" t="s">
-        <v>657</v>
-      </c>
-      <c r="E84" s="10" t="s">
-        <v>601</v>
-      </c>
-      <c r="F84" s="116" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A85" s="103" t="s">
-        <v>602</v>
-      </c>
-      <c r="B85" s="58" t="s">
-        <v>541</v>
-      </c>
-      <c r="C85" s="39" t="s">
-        <v>658</v>
-      </c>
-      <c r="D85" s="39" t="s">
-        <v>659</v>
-      </c>
-      <c r="E85" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="F85" s="118" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A86" s="103" t="s">
-        <v>602</v>
-      </c>
-      <c r="B86" s="58" t="s">
-        <v>541</v>
-      </c>
-      <c r="C86" s="39" t="s">
-        <v>661</v>
-      </c>
-      <c r="D86" s="39" t="s">
-        <v>662</v>
-      </c>
-      <c r="E86" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="F86" s="118" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="30" customHeight="1">
-      <c r="A87" s="103" t="s">
-        <v>602</v>
-      </c>
-      <c r="B87" s="58" t="s">
-        <v>541</v>
-      </c>
-      <c r="C87" s="39" t="s">
-        <v>664</v>
-      </c>
-      <c r="D87" s="39" t="s">
+    <row r="96" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A96" s="100" t="s">
         <v>665</v>
       </c>
-      <c r="E87" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="F87" s="118" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A88" s="108" t="s">
-        <v>602</v>
-      </c>
-      <c r="B88" s="89" t="s">
-        <v>541</v>
-      </c>
-      <c r="C88" s="90" t="s">
-        <v>918</v>
-      </c>
-      <c r="D88" s="95" t="s">
-        <v>919</v>
-      </c>
-      <c r="E88" s="90" t="s">
-        <v>920</v>
-      </c>
-      <c r="F88" s="123" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="42" customHeight="1">
-      <c r="A89" s="108" t="s">
-        <v>602</v>
-      </c>
-      <c r="B89" s="208" t="s">
-        <v>541</v>
-      </c>
-      <c r="C89" s="90" t="s">
-        <v>956</v>
-      </c>
-      <c r="D89" s="95" t="s">
-        <v>957</v>
-      </c>
-      <c r="E89" s="90" t="s">
-        <v>920</v>
-      </c>
-      <c r="F89" s="123" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="30" customHeight="1">
-      <c r="A90" s="155" t="s">
-        <v>983</v>
-      </c>
-      <c r="B90" s="156"/>
-      <c r="C90" s="156"/>
-      <c r="D90" s="156"/>
-      <c r="E90" s="156"/>
-      <c r="F90" s="157"/>
-    </row>
-    <row r="91" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A91" s="101" t="s">
+      <c r="B96" s="55" t="s">
+        <v>550</v>
+      </c>
+      <c r="C96" s="50" t="s">
         <v>667</v>
       </c>
-      <c r="B91" s="56" t="s">
-        <v>497</v>
-      </c>
-      <c r="C91" s="10" t="s">
+      <c r="D96" s="50" t="s">
         <v>668</v>
       </c>
-      <c r="D91" s="10"/>
-      <c r="E91" s="10" t="s">
-        <v>551</v>
-      </c>
-      <c r="F91" s="116" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A92" s="100" t="s">
-        <v>667</v>
-      </c>
-      <c r="B92" s="55" t="s">
-        <v>552</v>
-      </c>
-      <c r="C92" s="50" t="s">
+      <c r="E96" s="50" t="s">
+        <v>553</v>
+      </c>
+      <c r="F96" s="115" t="s">
         <v>669</v>
       </c>
-      <c r="D92" s="50" t="s">
+    </row>
+    <row r="97" spans="1:6" ht="45" customHeight="1">
+      <c r="A97" s="100" t="s">
+        <v>665</v>
+      </c>
+      <c r="B97" s="55" t="s">
+        <v>555</v>
+      </c>
+      <c r="C97" s="50" t="s">
         <v>670</v>
       </c>
-      <c r="E92" s="50" t="s">
-        <v>555</v>
-      </c>
-      <c r="F92" s="115" t="s">
+      <c r="D97" s="50" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" ht="30" customHeight="1">
-      <c r="A93" s="100" t="s">
-        <v>667</v>
-      </c>
-      <c r="B93" s="55" t="s">
-        <v>557</v>
-      </c>
-      <c r="C93" s="50" t="s">
+      <c r="E97" s="50" t="s">
+        <v>558</v>
+      </c>
+      <c r="F97" s="115" t="s">
         <v>672</v>
       </c>
-      <c r="D93" s="50" t="s">
+    </row>
+    <row r="98" spans="1:6" ht="30" customHeight="1">
+      <c r="A98" s="101" t="s">
+        <v>665</v>
+      </c>
+      <c r="B98" s="56" t="s">
+        <v>560</v>
+      </c>
+      <c r="C98" s="10" t="s">
         <v>673</v>
       </c>
-      <c r="E93" s="50" t="s">
-        <v>560</v>
-      </c>
-      <c r="F93" s="115" t="s">
+      <c r="D98" s="10" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" ht="30" customHeight="1">
-      <c r="A94" s="101" t="s">
-        <v>667</v>
-      </c>
-      <c r="B94" s="56" t="s">
-        <v>562</v>
-      </c>
-      <c r="C94" s="10" t="s">
+      <c r="E98" s="10" t="s">
         <v>675</v>
       </c>
-      <c r="D94" s="10" t="s">
+      <c r="F98" s="116" t="s">
         <v>676</v>
       </c>
-      <c r="E94" s="10" t="s">
+    </row>
+    <row r="99" spans="1:6" ht="21.75" customHeight="1">
+      <c r="A99" s="99" t="s">
+        <v>665</v>
+      </c>
+      <c r="B99" s="54" t="s">
+        <v>564</v>
+      </c>
+      <c r="C99" s="15" t="s">
         <v>677</v>
       </c>
-      <c r="F94" s="116" t="s">
+      <c r="D99" s="15" t="s">
         <v>678</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" ht="42" customHeight="1">
-      <c r="A95" s="99" t="s">
-        <v>667</v>
-      </c>
-      <c r="B95" s="54" t="s">
-        <v>566</v>
-      </c>
-      <c r="C95" s="15" t="s">
-        <v>679</v>
-      </c>
-      <c r="D95" s="15" t="s">
-        <v>680</v>
-      </c>
-      <c r="E95" s="15" t="s">
-        <v>220</v>
-      </c>
-      <c r="F95" s="85" t="s">
+      <c r="E99" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="F99" s="85" t="s">
         <v>131</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A96" s="105" t="s">
-        <v>667</v>
-      </c>
-      <c r="B96" s="60" t="s">
-        <v>681</v>
-      </c>
-      <c r="C96" s="61" t="s">
-        <v>682</v>
-      </c>
-      <c r="D96" s="61" t="s">
-        <v>683</v>
-      </c>
-      <c r="E96" s="61" t="s">
-        <v>684</v>
-      </c>
-      <c r="F96" s="120" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="45" customHeight="1">
-      <c r="A97" s="105" t="s">
-        <v>667</v>
-      </c>
-      <c r="B97" s="60" t="s">
-        <v>686</v>
-      </c>
-      <c r="C97" s="61" t="s">
-        <v>687</v>
-      </c>
-      <c r="D97" s="61" t="s">
-        <v>688</v>
-      </c>
-      <c r="E97" s="61" t="s">
-        <v>608</v>
-      </c>
-      <c r="F97" s="120" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="30" customHeight="1">
-      <c r="A98" s="105" t="s">
-        <v>667</v>
-      </c>
-      <c r="B98" s="60" t="s">
-        <v>690</v>
-      </c>
-      <c r="C98" s="61" t="s">
-        <v>691</v>
-      </c>
-      <c r="D98" s="61" t="s">
-        <v>692</v>
-      </c>
-      <c r="E98" s="61" t="s">
-        <v>693</v>
-      </c>
-      <c r="F98" s="120" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" ht="21.75" customHeight="1">
-      <c r="A99" s="106" t="s">
-        <v>667</v>
-      </c>
-      <c r="B99" s="63" t="s">
-        <v>695</v>
-      </c>
-      <c r="C99" s="20" t="s">
-        <v>696</v>
-      </c>
-      <c r="D99" s="20" t="s">
-        <v>697</v>
-      </c>
-      <c r="E99" s="20" t="s">
-        <v>698</v>
-      </c>
-      <c r="F99" s="121" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="25.5" customHeight="1">
       <c r="A100" s="105" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B100" s="60" t="s">
-        <v>699</v>
+        <v>679</v>
       </c>
       <c r="C100" s="61" t="s">
-        <v>700</v>
+        <v>680</v>
       </c>
       <c r="D100" s="61" t="s">
-        <v>701</v>
+        <v>681</v>
       </c>
       <c r="E100" s="61" t="s">
-        <v>111</v>
+        <v>682</v>
       </c>
       <c r="F100" s="120" t="s">
-        <v>273</v>
+        <v>683</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="42" customHeight="1">
       <c r="A101" s="105" t="s">
-        <v>667</v>
-      </c>
-      <c r="B101" s="207" t="s">
-        <v>707</v>
+        <v>665</v>
+      </c>
+      <c r="B101" s="60" t="s">
+        <v>684</v>
       </c>
       <c r="C101" s="61" t="s">
-        <v>954</v>
+        <v>685</v>
       </c>
       <c r="D101" s="61" t="s">
-        <v>955</v>
+        <v>686</v>
       </c>
       <c r="E101" s="61" t="s">
-        <v>631</v>
+        <v>606</v>
       </c>
       <c r="F101" s="120" t="s">
-        <v>273</v>
+        <v>687</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="30" customHeight="1">
-      <c r="A102" s="109" t="s">
-        <v>667</v>
-      </c>
-      <c r="B102" s="65" t="s">
+      <c r="A102" s="105" t="s">
+        <v>665</v>
+      </c>
+      <c r="B102" s="60" t="s">
+        <v>688</v>
+      </c>
+      <c r="C102" s="61" t="s">
+        <v>689</v>
+      </c>
+      <c r="D102" s="61" t="s">
+        <v>690</v>
+      </c>
+      <c r="E102" s="61" t="s">
+        <v>691</v>
+      </c>
+      <c r="F102" s="120" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="45" customHeight="1">
+      <c r="A103" s="106" t="s">
+        <v>665</v>
+      </c>
+      <c r="B103" s="63" t="s">
+        <v>693</v>
+      </c>
+      <c r="C103" s="20" t="s">
+        <v>694</v>
+      </c>
+      <c r="D103" s="20" t="s">
+        <v>695</v>
+      </c>
+      <c r="E103" s="20" t="s">
+        <v>696</v>
+      </c>
+      <c r="F103" s="121" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A104" s="105" t="s">
+        <v>665</v>
+      </c>
+      <c r="B104" s="60" t="s">
+        <v>697</v>
+      </c>
+      <c r="C104" s="61" t="s">
+        <v>698</v>
+      </c>
+      <c r="D104" s="61" t="s">
+        <v>699</v>
+      </c>
+      <c r="E104" s="61" t="s">
+        <v>111</v>
+      </c>
+      <c r="F104" s="120" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="42" customHeight="1">
+      <c r="A105" s="105" t="s">
+        <v>665</v>
+      </c>
+      <c r="B105" s="207" t="s">
+        <v>705</v>
+      </c>
+      <c r="C105" s="61" t="s">
+        <v>950</v>
+      </c>
+      <c r="D105" s="61" t="s">
+        <v>951</v>
+      </c>
+      <c r="E105" s="61" t="s">
+        <v>629</v>
+      </c>
+      <c r="F105" s="120" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="42" customHeight="1">
+      <c r="A106" s="109" t="s">
+        <v>665</v>
+      </c>
+      <c r="B106" s="65" t="s">
+        <v>700</v>
+      </c>
+      <c r="C106" s="42" t="s">
+        <v>701</v>
+      </c>
+      <c r="D106" s="42" t="s">
         <v>702</v>
       </c>
-      <c r="C102" s="42" t="s">
+      <c r="E106" s="42" t="s">
         <v>703</v>
       </c>
-      <c r="D102" s="42" t="s">
+      <c r="F106" s="124" t="s">
         <v>704</v>
       </c>
-      <c r="E102" s="42" t="s">
-        <v>705</v>
-      </c>
-      <c r="F102" s="124" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" ht="45" customHeight="1">
-      <c r="A103" s="111" t="s">
-        <v>667</v>
-      </c>
-      <c r="B103" s="93" t="s">
-        <v>922</v>
-      </c>
-      <c r="C103" s="94" t="s">
-        <v>923</v>
-      </c>
-      <c r="D103" s="94" t="s">
-        <v>924</v>
-      </c>
-      <c r="E103" s="94" t="s">
-        <v>925</v>
-      </c>
-      <c r="F103" s="126" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A104" s="101" t="s">
-        <v>667</v>
-      </c>
-      <c r="B104" s="128" t="s">
-        <v>932</v>
-      </c>
-      <c r="C104" s="10" t="s">
-        <v>931</v>
-      </c>
-      <c r="D104" s="10"/>
-      <c r="E104" s="10" t="s">
-        <v>601</v>
-      </c>
-      <c r="F104" s="116" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="42" customHeight="1">
-      <c r="A105" s="102" t="s">
-        <v>667</v>
-      </c>
-      <c r="B105" s="57" t="s">
-        <v>707</v>
-      </c>
-      <c r="C105" s="33" t="s">
-        <v>708</v>
-      </c>
-      <c r="D105" s="33" t="s">
-        <v>709</v>
-      </c>
-      <c r="E105" s="33" t="s">
-        <v>536</v>
-      </c>
-      <c r="F105" s="117" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" ht="42" customHeight="1">
-      <c r="A106" s="103" t="s">
-        <v>667</v>
-      </c>
-      <c r="B106" s="58" t="s">
-        <v>707</v>
-      </c>
-      <c r="C106" s="39" t="s">
-        <v>977</v>
-      </c>
-      <c r="D106" s="39" t="s">
-        <v>978</v>
-      </c>
-      <c r="E106" s="39" t="s">
-        <v>536</v>
-      </c>
-      <c r="F106" s="118" t="s">
-        <v>979</v>
-      </c>
     </row>
     <row r="107" spans="1:6" ht="30" customHeight="1">
-      <c r="A107" s="155" t="s">
-        <v>984</v>
-      </c>
-      <c r="B107" s="156"/>
-      <c r="C107" s="156"/>
-      <c r="D107" s="156"/>
-      <c r="E107" s="156"/>
-      <c r="F107" s="157"/>
+      <c r="A107" s="111" t="s">
+        <v>665</v>
+      </c>
+      <c r="B107" s="93" t="s">
+        <v>918</v>
+      </c>
+      <c r="C107" s="94" t="s">
+        <v>919</v>
+      </c>
+      <c r="D107" s="94" t="s">
+        <v>920</v>
+      </c>
+      <c r="E107" s="94" t="s">
+        <v>921</v>
+      </c>
+      <c r="F107" s="126" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="108" spans="1:6" ht="25.5" customHeight="1">
       <c r="A108" s="101" t="s">
+        <v>665</v>
+      </c>
+      <c r="B108" s="128" t="s">
+        <v>928</v>
+      </c>
+      <c r="C108" s="10" t="s">
+        <v>927</v>
+      </c>
+      <c r="D108" s="10"/>
+      <c r="E108" s="10" t="s">
+        <v>599</v>
+      </c>
+      <c r="F108" s="116" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A109" s="102" t="s">
+        <v>665</v>
+      </c>
+      <c r="B109" s="57" t="s">
+        <v>705</v>
+      </c>
+      <c r="C109" s="33" t="s">
+        <v>706</v>
+      </c>
+      <c r="D109" s="33" t="s">
+        <v>707</v>
+      </c>
+      <c r="E109" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="F109" s="117" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="30" customHeight="1">
+      <c r="A110" s="103" t="s">
+        <v>665</v>
+      </c>
+      <c r="B110" s="58" t="s">
+        <v>705</v>
+      </c>
+      <c r="C110" s="39" t="s">
+        <v>973</v>
+      </c>
+      <c r="D110" s="39" t="s">
+        <v>974</v>
+      </c>
+      <c r="E110" s="39" t="s">
+        <v>534</v>
+      </c>
+      <c r="F110" s="118" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A111" s="155" t="s">
+        <v>980</v>
+      </c>
+      <c r="B111" s="156"/>
+      <c r="C111" s="156"/>
+      <c r="D111" s="156"/>
+      <c r="E111" s="156"/>
+      <c r="F111" s="157"/>
+    </row>
+    <row r="112" spans="1:6" ht="42" customHeight="1">
+      <c r="A112" s="101" t="s">
+        <v>708</v>
+      </c>
+      <c r="B112" s="56" t="s">
+        <v>495</v>
+      </c>
+      <c r="C112" s="10" t="s">
+        <v>601</v>
+      </c>
+      <c r="D112" s="10" t="s">
+        <v>709</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F112" s="116" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="45" customHeight="1">
+      <c r="A113" s="105" t="s">
+        <v>708</v>
+      </c>
+      <c r="B113" s="60" t="s">
+        <v>497</v>
+      </c>
+      <c r="C113" s="61" t="s">
         <v>710</v>
       </c>
-      <c r="B108" s="56" t="s">
-        <v>497</v>
-      </c>
-      <c r="C108" s="10" t="s">
-        <v>603</v>
-      </c>
-      <c r="D108" s="10" t="s">
+      <c r="D113" s="61" t="s">
         <v>711</v>
       </c>
-      <c r="E108" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F108" s="116" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A109" s="105" t="s">
-        <v>710</v>
-      </c>
-      <c r="B109" s="60" t="s">
-        <v>499</v>
-      </c>
-      <c r="C109" s="61" t="s">
+      <c r="E113" s="61" t="s">
+        <v>500</v>
+      </c>
+      <c r="F113" s="120" t="s">
         <v>712</v>
       </c>
-      <c r="D109" s="61" t="s">
+    </row>
+    <row r="114" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A114" s="105" t="s">
+        <v>708</v>
+      </c>
+      <c r="B114" s="60" t="s">
         <v>713</v>
       </c>
-      <c r="E109" s="61" t="s">
-        <v>502</v>
-      </c>
-      <c r="F109" s="120" t="s">
+      <c r="C114" s="61" t="s">
         <v>714</v>
       </c>
-    </row>
-    <row r="110" spans="1:6" ht="30" customHeight="1">
-      <c r="A110" s="105" t="s">
-        <v>710</v>
-      </c>
-      <c r="B110" s="60" t="s">
+      <c r="D114" s="61" t="s">
         <v>715</v>
       </c>
-      <c r="C110" s="61" t="s">
+      <c r="E114" s="61" t="s">
         <v>716</v>
       </c>
-      <c r="D110" s="61" t="s">
+      <c r="F114" s="120" t="s">
         <v>717</v>
-      </c>
-      <c r="E110" s="61" t="s">
-        <v>718</v>
-      </c>
-      <c r="F110" s="120" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A111" s="105" t="s">
-        <v>710</v>
-      </c>
-      <c r="B111" s="60" t="s">
-        <v>618</v>
-      </c>
-      <c r="C111" s="61" t="s">
-        <v>720</v>
-      </c>
-      <c r="D111" s="61" t="s">
-        <v>721</v>
-      </c>
-      <c r="E111" s="61" t="s">
-        <v>722</v>
-      </c>
-      <c r="F111" s="120" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="42" customHeight="1">
-      <c r="A112" s="105" t="s">
-        <v>710</v>
-      </c>
-      <c r="B112" s="207" t="s">
-        <v>707</v>
-      </c>
-      <c r="C112" s="61" t="s">
-        <v>950</v>
-      </c>
-      <c r="D112" s="61" t="s">
-        <v>951</v>
-      </c>
-      <c r="E112" s="61" t="s">
-        <v>952</v>
-      </c>
-      <c r="F112" s="120" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" ht="45" customHeight="1">
-      <c r="A113" s="98" t="s">
-        <v>710</v>
-      </c>
-      <c r="B113" s="53" t="s">
-        <v>723</v>
-      </c>
-      <c r="C113" s="5" t="s">
-        <v>724</v>
-      </c>
-      <c r="D113" s="5" t="s">
-        <v>725</v>
-      </c>
-      <c r="E113" s="5" t="s">
-        <v>726</v>
-      </c>
-      <c r="F113" s="86" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A114" s="102" t="s">
-        <v>710</v>
-      </c>
-      <c r="B114" s="57" t="s">
-        <v>628</v>
-      </c>
-      <c r="C114" s="33" t="s">
-        <v>727</v>
-      </c>
-      <c r="D114" s="33" t="s">
-        <v>728</v>
-      </c>
-      <c r="E114" s="33" t="s">
-        <v>729</v>
-      </c>
-      <c r="F114" s="117" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="21.75" customHeight="1">
       <c r="A115" s="105" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B115" s="60" t="s">
+        <v>616</v>
+      </c>
+      <c r="C115" s="61" t="s">
+        <v>718</v>
+      </c>
+      <c r="D115" s="61" t="s">
+        <v>719</v>
+      </c>
+      <c r="E115" s="61" t="s">
+        <v>720</v>
+      </c>
+      <c r="F115" s="120" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A116" s="105" t="s">
+        <v>708</v>
+      </c>
+      <c r="B116" s="207" t="s">
+        <v>705</v>
+      </c>
+      <c r="C116" s="61" t="s">
+        <v>946</v>
+      </c>
+      <c r="D116" s="61" t="s">
+        <v>947</v>
+      </c>
+      <c r="E116" s="61" t="s">
+        <v>948</v>
+      </c>
+      <c r="F116" s="120" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A117" s="98" t="s">
+        <v>708</v>
+      </c>
+      <c r="B117" s="53" t="s">
+        <v>721</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>723</v>
+      </c>
+      <c r="E117" s="5" t="s">
+        <v>724</v>
+      </c>
+      <c r="F117" s="86" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="30" customHeight="1">
+      <c r="A118" s="102" t="s">
+        <v>708</v>
+      </c>
+      <c r="B118" s="57" t="s">
+        <v>626</v>
+      </c>
+      <c r="C118" s="33" t="s">
+        <v>725</v>
+      </c>
+      <c r="D118" s="33" t="s">
+        <v>726</v>
+      </c>
+      <c r="E118" s="33" t="s">
+        <v>727</v>
+      </c>
+      <c r="F118" s="117" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A119" s="105" t="s">
+        <v>708</v>
+      </c>
+      <c r="B119" s="60" t="s">
+        <v>728</v>
+      </c>
+      <c r="C119" s="61" t="s">
+        <v>729</v>
+      </c>
+      <c r="D119" s="61" t="s">
         <v>730</v>
       </c>
-      <c r="C115" s="61" t="s">
+      <c r="E119" s="61" t="s">
+        <v>480</v>
+      </c>
+      <c r="F119" s="120" t="s">
         <v>731</v>
       </c>
-      <c r="D115" s="61" t="s">
+    </row>
+    <row r="120" spans="1:6" ht="30" customHeight="1">
+      <c r="A120" s="106" t="s">
+        <v>708</v>
+      </c>
+      <c r="B120" s="63" t="s">
         <v>732</v>
       </c>
-      <c r="E115" s="61" t="s">
-        <v>482</v>
-      </c>
-      <c r="F115" s="120" t="s">
+      <c r="C120" s="20" t="s">
         <v>733</v>
       </c>
-    </row>
-    <row r="116" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A116" s="106" t="s">
-        <v>710</v>
-      </c>
-      <c r="B116" s="63" t="s">
+      <c r="D120" s="20" t="s">
         <v>734</v>
       </c>
-      <c r="C116" s="20" t="s">
+      <c r="E120" s="20" t="s">
+        <v>529</v>
+      </c>
+      <c r="F120" s="121" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A121" s="109" t="s">
+        <v>708</v>
+      </c>
+      <c r="B121" s="65" t="s">
+        <v>580</v>
+      </c>
+      <c r="C121" s="42" t="s">
         <v>735</v>
       </c>
-      <c r="D116" s="20" t="s">
+      <c r="D121" s="42" t="s">
         <v>736</v>
       </c>
-      <c r="E116" s="20" t="s">
-        <v>531</v>
-      </c>
-      <c r="F116" s="121" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A117" s="109" t="s">
-        <v>710</v>
-      </c>
-      <c r="B117" s="65" t="s">
-        <v>582</v>
-      </c>
-      <c r="C117" s="42" t="s">
+      <c r="E121" s="42" t="s">
         <v>737</v>
       </c>
-      <c r="D117" s="42" t="s">
+      <c r="F121" s="124" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A122" s="99" t="s">
+        <v>708</v>
+      </c>
+      <c r="B122" s="54" t="s">
         <v>738</v>
       </c>
-      <c r="E117" s="42" t="s">
+      <c r="C122" s="15" t="s">
         <v>739</v>
       </c>
-      <c r="F117" s="124" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" ht="30" customHeight="1">
-      <c r="A118" s="99" t="s">
-        <v>710</v>
-      </c>
-      <c r="B118" s="54" t="s">
+      <c r="D122" s="15" t="s">
         <v>740</v>
       </c>
-      <c r="C118" s="15" t="s">
+      <c r="E122" s="15" t="s">
+        <v>537</v>
+      </c>
+      <c r="F122" s="85" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="42" customHeight="1">
+      <c r="A123" s="103" t="s">
+        <v>708</v>
+      </c>
+      <c r="B123" s="58" t="s">
         <v>741</v>
       </c>
-      <c r="D118" s="15" t="s">
+      <c r="C123" s="39" t="s">
         <v>742</v>
       </c>
-      <c r="E118" s="15" t="s">
+      <c r="D123" s="39" t="s">
+        <v>743</v>
+      </c>
+      <c r="E123" s="39" t="s">
+        <v>744</v>
+      </c>
+      <c r="F123" s="118" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="30" customHeight="1">
+      <c r="A124" s="101" t="s">
+        <v>708</v>
+      </c>
+      <c r="B124" s="56" t="s">
+        <v>745</v>
+      </c>
+      <c r="C124" s="10" t="s">
+        <v>746</v>
+      </c>
+      <c r="D124" s="10" t="s">
+        <v>747</v>
+      </c>
+      <c r="E124" s="10" t="s">
+        <v>599</v>
+      </c>
+      <c r="F124" s="116" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="28">
+      <c r="A125" s="103" t="s">
+        <v>708</v>
+      </c>
+      <c r="B125" s="58" t="s">
         <v>539</v>
       </c>
-      <c r="F118" s="85" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A119" s="103" t="s">
-        <v>710</v>
-      </c>
-      <c r="B119" s="58" t="s">
-        <v>743</v>
-      </c>
-      <c r="C119" s="39" t="s">
-        <v>744</v>
-      </c>
-      <c r="D119" s="39" t="s">
-        <v>745</v>
-      </c>
-      <c r="E119" s="39" t="s">
-        <v>746</v>
-      </c>
-      <c r="F119" s="118" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" ht="30" customHeight="1">
-      <c r="A120" s="101" t="s">
-        <v>710</v>
-      </c>
-      <c r="B120" s="56" t="s">
-        <v>747</v>
-      </c>
-      <c r="C120" s="10" t="s">
+      <c r="C125" s="39" t="s">
         <v>748</v>
       </c>
-      <c r="D120" s="10" t="s">
+      <c r="D125" s="39" t="s">
         <v>749</v>
       </c>
-      <c r="E120" s="10" t="s">
-        <v>601</v>
-      </c>
-      <c r="F120" s="116" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A121" s="103" t="s">
-        <v>710</v>
-      </c>
-      <c r="B121" s="58" t="s">
-        <v>541</v>
-      </c>
-      <c r="C121" s="39" t="s">
+      <c r="E125" s="39" t="s">
+        <v>542</v>
+      </c>
+      <c r="F125" s="118" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="28">
+      <c r="A126" s="103" t="s">
+        <v>708</v>
+      </c>
+      <c r="B126" s="58" t="s">
+        <v>539</v>
+      </c>
+      <c r="C126" s="39" t="s">
         <v>750</v>
       </c>
-      <c r="D121" s="39" t="s">
+      <c r="D126" s="39" t="s">
         <v>751</v>
       </c>
-      <c r="E121" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="F121" s="118" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A122" s="103" t="s">
-        <v>710</v>
-      </c>
-      <c r="B122" s="58" t="s">
-        <v>541</v>
-      </c>
-      <c r="C122" s="39" t="s">
+      <c r="E126" s="39" t="s">
+        <v>542</v>
+      </c>
+      <c r="F126" s="118" t="s">
         <v>752</v>
       </c>
-      <c r="D122" s="39" t="s">
+    </row>
+    <row r="127" spans="1:6" ht="31">
+      <c r="A127" s="104" t="s">
+        <v>708</v>
+      </c>
+      <c r="B127" s="59" t="s">
+        <v>539</v>
+      </c>
+      <c r="C127" s="47" t="s">
+        <v>976</v>
+      </c>
+      <c r="D127" s="47" t="s">
+        <v>977</v>
+      </c>
+      <c r="E127" s="47" t="s">
+        <v>542</v>
+      </c>
+      <c r="F127" s="119" t="s">
         <v>753</v>
       </c>
-      <c r="E122" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="F122" s="118" t="s">
+    </row>
+    <row r="128" spans="1:6">
+      <c r="A128" s="158" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="123" spans="1:6" ht="42" customHeight="1">
-      <c r="A123" s="104" t="s">
-        <v>710</v>
-      </c>
-      <c r="B123" s="59" t="s">
-        <v>541</v>
-      </c>
-      <c r="C123" s="47" t="s">
-        <v>980</v>
-      </c>
-      <c r="D123" s="47" t="s">
-        <v>981</v>
-      </c>
-      <c r="E123" s="47" t="s">
-        <v>544</v>
-      </c>
-      <c r="F123" s="119" t="s">
+      <c r="B128" s="159"/>
+      <c r="C128" s="159"/>
+      <c r="D128" s="159"/>
+      <c r="E128" s="159"/>
+      <c r="F128" s="160"/>
+    </row>
+    <row r="129" spans="1:6" ht="28">
+      <c r="A129" s="101" t="s">
         <v>755</v>
       </c>
-    </row>
-    <row r="124" spans="1:6" ht="30" customHeight="1">
-      <c r="A124" s="158" t="s">
+      <c r="B129" s="56" t="s">
         <v>756</v>
       </c>
-      <c r="B124" s="159"/>
-      <c r="C124" s="159"/>
-      <c r="D124" s="159"/>
-      <c r="E124" s="159"/>
-      <c r="F124" s="160"/>
-    </row>
-    <row r="125" spans="1:6" ht="28">
-      <c r="A125" s="101" t="s">
+      <c r="C129" s="10" t="s">
+        <v>666</v>
+      </c>
+      <c r="D129" s="10" t="s">
         <v>757</v>
       </c>
-      <c r="B125" s="56" t="s">
+      <c r="E129" s="10" t="s">
+        <v>549</v>
+      </c>
+      <c r="F129" s="116" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="28">
+      <c r="A130" s="100" t="s">
+        <v>755</v>
+      </c>
+      <c r="B130" s="55" t="s">
         <v>758</v>
       </c>
-      <c r="C125" s="10" t="s">
-        <v>668</v>
-      </c>
-      <c r="D125" s="10" t="s">
+      <c r="C130" s="50" t="s">
         <v>759</v>
       </c>
-      <c r="E125" s="10" t="s">
-        <v>551</v>
-      </c>
-      <c r="F125" s="116" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" ht="28">
-      <c r="A126" s="100" t="s">
-        <v>757</v>
-      </c>
-      <c r="B126" s="55" t="s">
+      <c r="D130" s="50" t="s">
         <v>760</v>
       </c>
-      <c r="C126" s="50" t="s">
+      <c r="E130" s="50" t="s">
+        <v>675</v>
+      </c>
+      <c r="F130" s="115" t="s">
         <v>761</v>
       </c>
-      <c r="D126" s="50" t="s">
+    </row>
+    <row r="131" spans="1:6" ht="28">
+      <c r="A131" s="100" t="s">
+        <v>755</v>
+      </c>
+      <c r="B131" s="55" t="s">
         <v>762</v>
       </c>
-      <c r="E126" s="50" t="s">
-        <v>677</v>
-      </c>
-      <c r="F126" s="115" t="s">
+      <c r="C131" s="50" t="s">
         <v>763</v>
       </c>
-    </row>
-    <row r="127" spans="1:6" ht="28">
-      <c r="A127" s="100" t="s">
-        <v>757</v>
-      </c>
-      <c r="B127" s="55" t="s">
+      <c r="D131" s="50" t="s">
         <v>764</v>
       </c>
-      <c r="C127" s="50" t="s">
+      <c r="E131" s="50" t="s">
         <v>765</v>
       </c>
-      <c r="D127" s="50" t="s">
+      <c r="F131" s="115" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="28">
+      <c r="A132" s="100" t="s">
+        <v>755</v>
+      </c>
+      <c r="B132" s="55" t="s">
         <v>766</v>
       </c>
-      <c r="E127" s="50" t="s">
+      <c r="C132" s="50" t="s">
         <v>767</v>
       </c>
-      <c r="F127" s="115" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" ht="28">
-      <c r="A128" s="100" t="s">
-        <v>757</v>
-      </c>
-      <c r="B128" s="55" t="s">
+      <c r="D132" s="50" t="s">
         <v>768</v>
       </c>
-      <c r="C128" s="50" t="s">
+      <c r="E132" s="50" t="s">
         <v>769</v>
       </c>
-      <c r="D128" s="50" t="s">
+      <c r="F132" s="115" t="s">
         <v>770</v>
       </c>
-      <c r="E128" s="50" t="s">
+    </row>
+    <row r="133" spans="1:6" ht="28">
+      <c r="A133" s="99" t="s">
+        <v>755</v>
+      </c>
+      <c r="B133" s="54" t="s">
         <v>771</v>
       </c>
-      <c r="F128" s="115" t="s">
+      <c r="C133" s="15" t="s">
         <v>772</v>
       </c>
-    </row>
-    <row r="129" spans="1:6" ht="28">
-      <c r="A129" s="99" t="s">
-        <v>757</v>
-      </c>
-      <c r="B129" s="54" t="s">
+      <c r="D133" s="15" t="s">
         <v>773</v>
       </c>
-      <c r="C129" s="15" t="s">
+      <c r="E133" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="F133" s="85" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" ht="28">
+      <c r="A134" s="98" t="s">
+        <v>755</v>
+      </c>
+      <c r="B134" s="53" t="s">
         <v>774</v>
       </c>
-      <c r="D129" s="15" t="s">
+      <c r="C134" s="5" t="s">
         <v>775</v>
       </c>
-      <c r="E129" s="15" t="s">
-        <v>407</v>
-      </c>
-      <c r="F129" s="85" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" ht="28">
-      <c r="A130" s="98" t="s">
-        <v>757</v>
-      </c>
-      <c r="B130" s="53" t="s">
+      <c r="D134" s="5" t="s">
         <v>776</v>
       </c>
-      <c r="C130" s="5" t="s">
+      <c r="E134" s="5" t="s">
         <v>777</v>
       </c>
-      <c r="D130" s="5" t="s">
+      <c r="F134" s="114" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" ht="28">
+      <c r="A135" s="99" t="s">
+        <v>755</v>
+      </c>
+      <c r="B135" s="54" t="s">
         <v>778</v>
       </c>
-      <c r="E130" s="5" t="s">
+      <c r="C135" s="15" t="s">
         <v>779</v>
       </c>
-      <c r="F130" s="114" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" ht="28">
-      <c r="A131" s="99" t="s">
-        <v>757</v>
-      </c>
-      <c r="B131" s="54" t="s">
+      <c r="D135" s="15" t="s">
         <v>780</v>
       </c>
-      <c r="C131" s="15" t="s">
+      <c r="E135" s="15" t="s">
         <v>781</v>
       </c>
-      <c r="D131" s="15" t="s">
+      <c r="F135" s="113" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" ht="28">
+      <c r="A136" s="98" t="s">
+        <v>755</v>
+      </c>
+      <c r="B136" s="53" t="s">
         <v>782</v>
       </c>
-      <c r="E131" s="15" t="s">
+      <c r="C136" s="5" t="s">
         <v>783</v>
       </c>
-      <c r="F131" s="113" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" ht="28">
-      <c r="A132" s="98" t="s">
-        <v>757</v>
-      </c>
-      <c r="B132" s="53" t="s">
+      <c r="D136" s="5" t="s">
         <v>784</v>
       </c>
-      <c r="C132" s="5" t="s">
+      <c r="E136" s="5" t="s">
         <v>785</v>
       </c>
-      <c r="D132" s="5" t="s">
+      <c r="F136" s="114" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="29" thickBot="1">
+      <c r="A137" s="112" t="s">
+        <v>755</v>
+      </c>
+      <c r="B137" s="96" t="s">
+        <v>492</v>
+      </c>
+      <c r="C137" s="97" t="s">
         <v>786</v>
       </c>
-      <c r="E132" s="5" t="s">
+      <c r="D137" s="97" t="s">
         <v>787</v>
       </c>
-      <c r="F132" s="114" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" ht="29" thickBot="1">
-      <c r="A133" s="112" t="s">
-        <v>757</v>
-      </c>
-      <c r="B133" s="96" t="s">
-        <v>494</v>
-      </c>
-      <c r="C133" s="97" t="s">
+      <c r="E137" s="97" t="s">
         <v>788</v>
       </c>
-      <c r="D133" s="97" t="s">
+      <c r="F137" s="127" t="s">
         <v>789</v>
-      </c>
-      <c r="E133" s="97" t="s">
-        <v>790</v>
-      </c>
-      <c r="F133" s="127" t="s">
-        <v>791</v>
       </c>
     </row>
   </sheetData>
@@ -18655,12 +18909,12 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A53:F53"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A90:F90"/>
-    <mergeCell ref="A107:F107"/>
-    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="A94:F94"/>
+    <mergeCell ref="A111:F111"/>
+    <mergeCell ref="A128:F128"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -18672,7 +18926,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -18773,7 +19027,7 @@
         <v>62</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>63</v>
+        <v>1052</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>64</v>
@@ -18790,16 +19044,16 @@
         <v>53</v>
       </c>
       <c r="B9" s="69" t="s">
+        <v>790</v>
+      </c>
+      <c r="C9" s="67" t="s">
+        <v>791</v>
+      </c>
+      <c r="D9" s="66" t="s">
         <v>792</v>
       </c>
-      <c r="C9" s="67" t="s">
-        <v>793</v>
-      </c>
-      <c r="D9" s="66" t="s">
-        <v>794</v>
-      </c>
       <c r="E9" s="68" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="30" customHeight="1">
@@ -18807,13 +19061,13 @@
         <v>53</v>
       </c>
       <c r="B10" s="69" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C10" s="67" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="E10" s="68" t="s">
         <v>61</v>
@@ -18853,344 +19107,414 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="24" customHeight="1">
-      <c r="A14" s="174" t="s">
+    <row r="13" spans="1:5" ht="42" customHeight="1">
+      <c r="A13" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="42" customHeight="1">
+      <c r="A14" s="20" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="56" customHeight="1">
+      <c r="A15" s="20" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="70" customHeight="1">
+      <c r="A16" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="30" customHeight="1"/>
+    <row r="18" spans="1:5" ht="30" customHeight="1">
+      <c r="A18" s="174" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="174"/>
-      <c r="C14" s="174"/>
-      <c r="D14" s="174"/>
-      <c r="E14" s="174"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="12" t="s">
+      <c r="B18" s="174"/>
+      <c r="C18" s="174"/>
+      <c r="D18" s="174"/>
+      <c r="E18" s="174"/>
+    </row>
+    <row r="19" spans="1:5" ht="27.75" customHeight="1">
+      <c r="A19" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B19" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C19" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D19" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E19" s="12" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="45" customHeight="1">
-      <c r="A16" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="E16" s="18" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="30" customHeight="1">
-      <c r="A17" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="30" customHeight="1">
-      <c r="A18" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E18" s="18" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A19" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="30" customHeight="1">
       <c r="A20" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="30" customHeight="1">
+      <c r="A21" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="30" customHeight="1">
+      <c r="A22" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="28">
+      <c r="A23" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="24" customHeight="1">
+      <c r="A24" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B24" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C24" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D24" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E24" s="18" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="30" customHeight="1">
-      <c r="A21" s="66" t="s">
+    <row r="25" spans="1:5" ht="28">
+      <c r="A25" s="66" t="s">
         <v>90</v>
       </c>
-      <c r="B21" s="66" t="s">
+      <c r="B25" s="66" t="s">
+        <v>795</v>
+      </c>
+      <c r="C25" s="67" t="s">
+        <v>796</v>
+      </c>
+      <c r="D25" s="66" t="s">
         <v>797</v>
       </c>
-      <c r="C21" s="67" t="s">
-        <v>798</v>
-      </c>
-      <c r="D21" s="66" t="s">
-        <v>799</v>
-      </c>
-      <c r="E21" s="68" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="30" customHeight="1">
-      <c r="A22" s="20" t="s">
+      <c r="E25" s="68" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="30" customHeight="1">
+      <c r="A26" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B26" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C26" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="D26" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="E22" s="23" t="s">
+      <c r="E26" s="23" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="24" customHeight="1">
-      <c r="A24" s="176" t="s">
+    <row r="27" spans="1:5" ht="30" customHeight="1"/>
+    <row r="28" spans="1:5" ht="27.75" customHeight="1">
+      <c r="A28" s="176" t="s">
         <v>104</v>
       </c>
-      <c r="B24" s="176"/>
-      <c r="C24" s="176"/>
-      <c r="D24" s="176"/>
-      <c r="E24" s="176"/>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="12" t="s">
+      <c r="B28" s="176"/>
+      <c r="C28" s="176"/>
+      <c r="D28" s="176"/>
+      <c r="E28" s="176"/>
+    </row>
+    <row r="29" spans="1:5" ht="30" customHeight="1">
+      <c r="A29" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B29" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C29" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D29" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E29" s="12" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="30" customHeight="1">
-      <c r="A26" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="30" customHeight="1">
-      <c r="A27" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E27" s="18" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A28" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="30" customHeight="1">
-      <c r="A29" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="D29" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="27.75" customHeight="1">
       <c r="A30" s="5" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>121</v>
+        <v>37</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="30" customHeight="1">
       <c r="A31" s="15" t="s">
-        <v>124</v>
+        <v>53</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="27.75" customHeight="1">
       <c r="A32" s="5" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="D32" s="24" t="s">
-        <v>132</v>
+        <v>113</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="30" customHeight="1">
       <c r="A33" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="D33" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="30" customHeight="1">
+      <c r="A34" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="27.75" customHeight="1">
+      <c r="A35" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="28">
+      <c r="A36" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D36" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="28">
+      <c r="A37" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="B33" s="19" t="s">
+      <c r="B37" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C37" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="D37" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="E33" s="18" t="s">
+      <c r="E37" s="18" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="30" customHeight="1">
-      <c r="A34" s="70" t="s">
+    <row r="38" spans="1:5" ht="28">
+      <c r="A38" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="B34" s="73" t="s">
-        <v>800</v>
-      </c>
-      <c r="C34" s="71" t="s">
-        <v>273</v>
-      </c>
-      <c r="D34" s="70" t="s">
-        <v>801</v>
-      </c>
-      <c r="E34" s="72" t="s">
+      <c r="B38" s="73" t="s">
+        <v>798</v>
+      </c>
+      <c r="C38" s="71" t="s">
+        <v>271</v>
+      </c>
+      <c r="D38" s="70" t="s">
+        <v>799</v>
+      </c>
+      <c r="E38" s="72" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A35" s="20" t="s">
+    <row r="39" spans="1:5" ht="28">
+      <c r="A39" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="B35" s="21" t="s">
+      <c r="B39" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="C35" s="22" t="s">
+      <c r="C39" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="D35" s="20" t="s">
+      <c r="D39" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="E35" s="23" t="s">
+      <c r="E39" s="23" t="s">
         <v>103</v>
       </c>
     </row>
@@ -19198,8 +19522,8 @@
   <mergeCells count="4">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A28:E28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -19211,7 +19535,7 @@
   <sheetPr>
     <tabColor rgb="FFE36C09"/>
   </sheetPr>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -19224,7 +19548,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
       <c r="A1" s="191" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B1" s="192"/>
       <c r="C1" s="192"/>
@@ -19232,9 +19556,9 @@
       <c r="E1" s="192"/>
       <c r="F1" s="193"/>
     </row>
-    <row r="2" spans="1:6" ht="34" customHeight="1">
+    <row r="2" spans="1:6" ht="45" customHeight="1">
       <c r="A2" s="194" t="s">
-        <v>843</v>
+        <v>1036</v>
       </c>
       <c r="B2" s="195"/>
       <c r="C2" s="195"/>
@@ -19334,19 +19658,19 @@
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1">
       <c r="A8" s="81" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B8" s="75">
         <v>4.5</v>
       </c>
       <c r="C8" s="76" t="s">
+        <v>801</v>
+      </c>
+      <c r="D8" s="75" t="s">
+        <v>802</v>
+      </c>
+      <c r="E8" s="76" t="s">
         <v>803</v>
-      </c>
-      <c r="D8" s="75" t="s">
-        <v>804</v>
-      </c>
-      <c r="E8" s="76" t="s">
-        <v>805</v>
       </c>
       <c r="F8" s="87" t="s">
         <v>152</v>
@@ -19354,19 +19678,19 @@
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1">
       <c r="A9" s="82" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B9" s="68">
         <v>4.5</v>
       </c>
       <c r="C9" s="66" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="D9" s="68" t="s">
         <v>107</v>
       </c>
       <c r="E9" s="66" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="F9" s="88" t="s">
         <v>152</v>
@@ -19382,7 +19706,7 @@
       <c r="E10" s="189"/>
       <c r="F10" s="190"/>
     </row>
-    <row r="11" spans="1:6" ht="30" customHeight="1">
+    <row r="11" spans="1:6" ht="42" customHeight="1">
       <c r="A11" s="78" t="s">
         <v>147</v>
       </c>
@@ -19396,10 +19720,10 @@
         <v>57</v>
       </c>
       <c r="E11" s="6" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F11" s="84" t="s">
         <v>164</v>
-      </c>
-      <c r="F11" s="84" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1">
@@ -19410,16 +19734,16 @@
         <v>158</v>
       </c>
       <c r="C12" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="D12" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="E12" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="F12" s="85" t="s">
         <v>168</v>
-      </c>
-      <c r="F12" s="85" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1">
@@ -19430,1427 +19754,1547 @@
         <v>154</v>
       </c>
       <c r="C13" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="E13" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="F13" s="86" t="s">
         <v>172</v>
-      </c>
-      <c r="F13" s="86" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1">
       <c r="A14" s="81" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B14" s="75">
         <v>4.8</v>
       </c>
       <c r="C14" s="76" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="D14" s="75" t="s">
         <v>66</v>
       </c>
       <c r="E14" s="76" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="F14" s="87" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="30" customHeight="1">
       <c r="A15" s="82" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B15" s="68">
         <v>4.5999999999999996</v>
       </c>
       <c r="C15" s="66" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="D15" s="68" t="s">
         <v>111</v>
       </c>
       <c r="E15" s="66" t="s">
+        <v>842</v>
+      </c>
+      <c r="F15" s="88" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="30" customHeight="1">
+      <c r="A16" s="82" t="s">
+        <v>889</v>
+      </c>
+      <c r="B16" s="216" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C16" s="66" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D16" s="68" t="s">
+        <v>802</v>
+      </c>
+      <c r="E16" s="66" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F16" s="88" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="30" customHeight="1">
+      <c r="A17" s="82" t="s">
+        <v>892</v>
+      </c>
+      <c r="B17" s="216" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C17" s="66" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D17" s="68" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E17" s="66" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F17" s="88" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="30" customHeight="1">
+      <c r="A18" s="188" t="s">
+        <v>173</v>
+      </c>
+      <c r="B18" s="189"/>
+      <c r="C18" s="189"/>
+      <c r="D18" s="189"/>
+      <c r="E18" s="189"/>
+      <c r="F18" s="190"/>
+    </row>
+    <row r="19" spans="1:6" ht="30" customHeight="1">
+      <c r="A19" s="78" t="s">
+        <v>174</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F19" s="84" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="30" customHeight="1">
+      <c r="A20" s="79" t="s">
+        <v>147</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="F20" s="85" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="30" customHeight="1">
+      <c r="A21" s="80" t="s">
+        <v>153</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="F21" s="86" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A22" s="81" t="s">
+        <v>157</v>
+      </c>
+      <c r="B22" s="75">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C22" s="76" t="s">
+        <v>863</v>
+      </c>
+      <c r="D22" s="75" t="s">
+        <v>256</v>
+      </c>
+      <c r="E22" s="76" t="s">
+        <v>864</v>
+      </c>
+      <c r="F22" s="87" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="30" customHeight="1">
+      <c r="A23" s="82" t="s">
+        <v>800</v>
+      </c>
+      <c r="B23" s="68">
+        <v>4.3</v>
+      </c>
+      <c r="C23" s="66" t="s">
+        <v>808</v>
+      </c>
+      <c r="D23" s="68" t="s">
+        <v>256</v>
+      </c>
+      <c r="E23" s="66" t="s">
+        <v>809</v>
+      </c>
+      <c r="F23" s="88" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="30" customHeight="1">
+      <c r="A24" s="188" t="s">
+        <v>187</v>
+      </c>
+      <c r="B24" s="189"/>
+      <c r="C24" s="189"/>
+      <c r="D24" s="189"/>
+      <c r="E24" s="189"/>
+      <c r="F24" s="190"/>
+    </row>
+    <row r="25" spans="1:6" ht="30" customHeight="1">
+      <c r="A25" s="78" t="s">
+        <v>147</v>
+      </c>
+      <c r="B25" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F25" s="84" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="30" customHeight="1">
+      <c r="A26" s="79" t="s">
+        <v>153</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="F26" s="85" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="30" customHeight="1">
+      <c r="A27" s="80" t="s">
+        <v>157</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="F27" s="86" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A28" s="81" t="s">
+        <v>800</v>
+      </c>
+      <c r="B28" s="75">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C28" s="76" t="s">
+        <v>811</v>
+      </c>
+      <c r="D28" s="75" t="s">
+        <v>160</v>
+      </c>
+      <c r="E28" s="76" t="s">
+        <v>812</v>
+      </c>
+      <c r="F28" s="87" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="30" customHeight="1">
+      <c r="A29" s="82" t="s">
+        <v>804</v>
+      </c>
+      <c r="B29" s="68">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C29" s="66" t="s">
+        <v>844</v>
+      </c>
+      <c r="D29" s="68" t="s">
+        <v>219</v>
+      </c>
+      <c r="E29" s="66" t="s">
         <v>845</v>
       </c>
-      <c r="F15" s="88" t="s">
+      <c r="F29" s="88" t="s">
         <v>846</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A16" s="188" t="s">
-        <v>174</v>
-      </c>
-      <c r="B16" s="189"/>
-      <c r="C16" s="189"/>
-      <c r="D16" s="189"/>
-      <c r="E16" s="189"/>
-      <c r="F16" s="190"/>
-    </row>
-    <row r="17" spans="1:6" ht="30" customHeight="1">
-      <c r="A17" s="78" t="s">
-        <v>175</v>
-      </c>
-      <c r="B17" s="27" t="s">
-        <v>176</v>
-      </c>
-      <c r="C17" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="D17" s="27" t="s">
+    <row r="30" spans="1:6" ht="30" customHeight="1">
+      <c r="A30" s="188" t="s">
+        <v>200</v>
+      </c>
+      <c r="B30" s="189"/>
+      <c r="C30" s="189"/>
+      <c r="D30" s="189"/>
+      <c r="E30" s="189"/>
+      <c r="F30" s="190"/>
+    </row>
+    <row r="31" spans="1:6" ht="30" customHeight="1">
+      <c r="A31" s="78" t="s">
+        <v>147</v>
+      </c>
+      <c r="B31" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D31" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="F31" s="84" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="30" customHeight="1">
+      <c r="A32" s="79" t="s">
+        <v>153</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="F32" s="85" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="30" customHeight="1">
+      <c r="A33" s="80" t="s">
+        <v>157</v>
+      </c>
+      <c r="B33" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>865</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>828</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>866</v>
+      </c>
+      <c r="F33" s="86" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A34" s="81" t="s">
+        <v>800</v>
+      </c>
+      <c r="B34" s="75">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C34" s="76" t="s">
+        <v>814</v>
+      </c>
+      <c r="D34" s="75" t="s">
+        <v>166</v>
+      </c>
+      <c r="E34" s="76" t="s">
+        <v>815</v>
+      </c>
+      <c r="F34" s="87" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="30" customHeight="1">
+      <c r="A35" s="82" t="s">
+        <v>804</v>
+      </c>
+      <c r="B35" s="68">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C35" s="66" t="s">
+        <v>847</v>
+      </c>
+      <c r="D35" s="68" t="s">
+        <v>61</v>
+      </c>
+      <c r="E35" s="66" t="s">
+        <v>848</v>
+      </c>
+      <c r="F35" s="88" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="30" customHeight="1">
+      <c r="A36" s="185" t="s">
+        <v>208</v>
+      </c>
+      <c r="B36" s="186"/>
+      <c r="C36" s="186"/>
+      <c r="D36" s="186"/>
+      <c r="E36" s="186"/>
+      <c r="F36" s="187"/>
+    </row>
+    <row r="37" spans="1:6" ht="30" customHeight="1">
+      <c r="A37" s="78" t="s">
+        <v>147</v>
+      </c>
+      <c r="B37" s="27">
+        <v>4.5</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>877</v>
+      </c>
+      <c r="D37" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="E37" s="28" t="s">
+        <v>878</v>
+      </c>
+      <c r="F37" s="84" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="30" customHeight="1">
+      <c r="A38" s="79" t="s">
+        <v>153</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="F38" s="85" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="30" customHeight="1">
+      <c r="A39" s="80" t="s">
+        <v>157</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="F39" s="86" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A40" s="81" t="s">
+        <v>800</v>
+      </c>
+      <c r="B40" s="75">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C40" s="76" t="s">
+        <v>816</v>
+      </c>
+      <c r="D40" s="75" t="s">
+        <v>215</v>
+      </c>
+      <c r="E40" s="76" t="s">
+        <v>817</v>
+      </c>
+      <c r="F40" s="87" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="30" customHeight="1">
+      <c r="A41" s="82" t="s">
+        <v>804</v>
+      </c>
+      <c r="B41" s="68">
+        <v>4.3</v>
+      </c>
+      <c r="C41" s="66" t="s">
+        <v>850</v>
+      </c>
+      <c r="D41" s="68" t="s">
+        <v>223</v>
+      </c>
+      <c r="E41" s="66" t="s">
+        <v>851</v>
+      </c>
+      <c r="F41" s="88" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="30" customHeight="1">
+      <c r="A42" s="185" t="s">
+        <v>217</v>
+      </c>
+      <c r="B42" s="186"/>
+      <c r="C42" s="186"/>
+      <c r="D42" s="186"/>
+      <c r="E42" s="186"/>
+      <c r="F42" s="187"/>
+    </row>
+    <row r="43" spans="1:6" ht="30" customHeight="1">
+      <c r="A43" s="78" t="s">
+        <v>147</v>
+      </c>
+      <c r="B43" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="D43" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="F43" s="84" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="30" customHeight="1">
+      <c r="A44" s="79" t="s">
+        <v>153</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="D44" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="E44" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="F44" s="85" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="30" customHeight="1">
+      <c r="A45" s="80" t="s">
+        <v>157</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F45" s="86" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A46" s="81" t="s">
+        <v>800</v>
+      </c>
+      <c r="B46" s="75">
+        <v>4.5</v>
+      </c>
+      <c r="C46" s="76" t="s">
+        <v>818</v>
+      </c>
+      <c r="D46" s="75" t="s">
+        <v>89</v>
+      </c>
+      <c r="E46" s="76" t="s">
+        <v>819</v>
+      </c>
+      <c r="F46" s="87" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="30" customHeight="1">
+      <c r="A47" s="82" t="s">
+        <v>804</v>
+      </c>
+      <c r="B47" s="68">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C47" s="66" t="s">
+        <v>820</v>
+      </c>
+      <c r="D47" s="68" t="s">
+        <v>821</v>
+      </c>
+      <c r="E47" s="66" t="s">
+        <v>822</v>
+      </c>
+      <c r="F47" s="88" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="30" customHeight="1">
+      <c r="A48" s="185" t="s">
+        <v>229</v>
+      </c>
+      <c r="B48" s="186"/>
+      <c r="C48" s="186"/>
+      <c r="D48" s="186"/>
+      <c r="E48" s="186"/>
+      <c r="F48" s="187"/>
+    </row>
+    <row r="49" spans="1:6" ht="30" customHeight="1">
+      <c r="A49" s="78" t="s">
+        <v>147</v>
+      </c>
+      <c r="B49" s="27" t="s">
+        <v>213</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="D49" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="F49" s="84" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="30" customHeight="1">
+      <c r="A50" s="79" t="s">
+        <v>153</v>
+      </c>
+      <c r="B50" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="D50" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="E50" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="F50" s="85" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="30" customHeight="1">
+      <c r="A51" s="80" t="s">
+        <v>157</v>
+      </c>
+      <c r="B51" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>867</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="F51" s="86" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A52" s="81" t="s">
+        <v>800</v>
+      </c>
+      <c r="B52" s="75">
+        <v>4.7</v>
+      </c>
+      <c r="C52" s="76" t="s">
+        <v>824</v>
+      </c>
+      <c r="D52" s="75" t="s">
         <v>66</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="F17" s="84" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="30" customHeight="1">
-      <c r="A18" s="79" t="s">
+      <c r="E52" s="76" t="s">
+        <v>825</v>
+      </c>
+      <c r="F52" s="87" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="30" customHeight="1">
+      <c r="A53" s="82" t="s">
+        <v>804</v>
+      </c>
+      <c r="B53" s="68">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C53" s="66" t="s">
+        <v>827</v>
+      </c>
+      <c r="D53" s="68" t="s">
+        <v>828</v>
+      </c>
+      <c r="E53" s="66" t="s">
+        <v>829</v>
+      </c>
+      <c r="F53" s="88" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="30" customHeight="1">
+      <c r="A54" s="185" t="s">
+        <v>237</v>
+      </c>
+      <c r="B54" s="186"/>
+      <c r="C54" s="186"/>
+      <c r="D54" s="186"/>
+      <c r="E54" s="186"/>
+      <c r="F54" s="187"/>
+    </row>
+    <row r="55" spans="1:6" ht="30" customHeight="1">
+      <c r="A55" s="78" t="s">
         <v>147</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B55" s="27" t="s">
         <v>158</v>
       </c>
-      <c r="C18" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="F18" s="85" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="30" customHeight="1">
-      <c r="A19" s="80" t="s">
+      <c r="C55" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="D55" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="F55" s="84" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="30" customHeight="1">
+      <c r="A56" s="79" t="s">
         <v>153</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="F19" s="86" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="30" customHeight="1">
-      <c r="A20" s="81" t="s">
+      <c r="B56" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C56" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="D56" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="E56" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="F56" s="85" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="30" customHeight="1">
+      <c r="A57" s="80" t="s">
         <v>157</v>
       </c>
-      <c r="B20" s="75">
+      <c r="B57" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C57" s="29" t="s">
+        <v>243</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="F57" s="86" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A58" s="81" t="s">
+        <v>800</v>
+      </c>
+      <c r="B58" s="75">
         <v>4.4000000000000004</v>
       </c>
-      <c r="C20" s="76" t="s">
-        <v>866</v>
-      </c>
-      <c r="D20" s="75" t="s">
+      <c r="C58" s="74" t="s">
+        <v>852</v>
+      </c>
+      <c r="D58" s="75" t="s">
+        <v>219</v>
+      </c>
+      <c r="E58" s="76" t="s">
+        <v>853</v>
+      </c>
+      <c r="F58" s="87" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="30" customHeight="1">
+      <c r="A59" s="82" t="s">
+        <v>804</v>
+      </c>
+      <c r="B59" s="68">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="C59" s="69" t="s">
+        <v>831</v>
+      </c>
+      <c r="D59" s="68" t="s">
+        <v>52</v>
+      </c>
+      <c r="E59" s="66" t="s">
+        <v>832</v>
+      </c>
+      <c r="F59" s="88" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="30" customHeight="1">
+      <c r="A60" s="185" t="s">
+        <v>246</v>
+      </c>
+      <c r="B60" s="186"/>
+      <c r="C60" s="186"/>
+      <c r="D60" s="186"/>
+      <c r="E60" s="186"/>
+      <c r="F60" s="187"/>
+    </row>
+    <row r="61" spans="1:6" ht="30" customHeight="1">
+      <c r="A61" s="78" t="s">
+        <v>247</v>
+      </c>
+      <c r="B61" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="C61" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="D61" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="F61" s="84" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A62" s="79" t="s">
+        <v>250</v>
+      </c>
+      <c r="B62" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C62" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="D62" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="E62" s="25" t="s">
+        <v>252</v>
+      </c>
+      <c r="F62" s="85" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="30" customHeight="1">
+      <c r="A63" s="80" t="s">
+        <v>253</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C63" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="E63" s="24" t="s">
         <v>257</v>
       </c>
-      <c r="E20" s="76" t="s">
-        <v>867</v>
-      </c>
-      <c r="F20" s="87" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="30" customHeight="1">
-      <c r="A21" s="82" t="s">
-        <v>802</v>
-      </c>
-      <c r="B21" s="68">
-        <v>4.3</v>
-      </c>
-      <c r="C21" s="66" t="s">
-        <v>810</v>
-      </c>
-      <c r="D21" s="68" t="s">
-        <v>257</v>
-      </c>
-      <c r="E21" s="66" t="s">
-        <v>811</v>
-      </c>
-      <c r="F21" s="88" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A22" s="188" t="s">
-        <v>188</v>
-      </c>
-      <c r="B22" s="189"/>
-      <c r="C22" s="189"/>
-      <c r="D22" s="189"/>
-      <c r="E22" s="189"/>
-      <c r="F22" s="190"/>
-    </row>
-    <row r="23" spans="1:6" ht="30" customHeight="1">
-      <c r="A23" s="78" t="s">
+      <c r="F63" s="86" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="30" customHeight="1">
+      <c r="A64" s="179" t="s">
+        <v>259</v>
+      </c>
+      <c r="B64" s="180"/>
+      <c r="C64" s="180"/>
+      <c r="D64" s="180"/>
+      <c r="E64" s="180"/>
+      <c r="F64" s="181"/>
+    </row>
+    <row r="65" spans="1:6" ht="42" customHeight="1">
+      <c r="A65" s="78" t="s">
         <v>147</v>
       </c>
-      <c r="B23" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="C23" s="6" t="s">
+      <c r="B65" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D65" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F65" s="84" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="30" customHeight="1">
+      <c r="A66" s="79" t="s">
+        <v>153</v>
+      </c>
+      <c r="B66" s="18">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C66" s="16" t="s">
+        <v>855</v>
+      </c>
+      <c r="D66" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="E66" s="15" t="s">
+        <v>872</v>
+      </c>
+      <c r="F66" s="85" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="30" customHeight="1">
+      <c r="A67" s="80" t="s">
+        <v>157</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="D67" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="D23" s="27" t="s">
-        <v>190</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="F23" s="84" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="30" customHeight="1">
-      <c r="A24" s="79" t="s">
-        <v>153</v>
-      </c>
-      <c r="B24" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="F24" s="85" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="30" customHeight="1">
-      <c r="A25" s="80" t="s">
-        <v>157</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="F25" s="86" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="30" customHeight="1">
-      <c r="A26" s="81" t="s">
-        <v>802</v>
-      </c>
-      <c r="B26" s="75">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C26" s="76" t="s">
-        <v>813</v>
-      </c>
-      <c r="D26" s="75" t="s">
-        <v>160</v>
-      </c>
-      <c r="E26" s="76" t="s">
-        <v>814</v>
-      </c>
-      <c r="F26" s="87" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="30" customHeight="1">
-      <c r="A27" s="82" t="s">
-        <v>806</v>
-      </c>
-      <c r="B27" s="68">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C27" s="66" t="s">
-        <v>847</v>
-      </c>
-      <c r="D27" s="68" t="s">
-        <v>220</v>
-      </c>
-      <c r="E27" s="66" t="s">
-        <v>848</v>
-      </c>
-      <c r="F27" s="88" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A28" s="188" t="s">
-        <v>201</v>
-      </c>
-      <c r="B28" s="189"/>
-      <c r="C28" s="189"/>
-      <c r="D28" s="189"/>
-      <c r="E28" s="189"/>
-      <c r="F28" s="190"/>
-    </row>
-    <row r="29" spans="1:6" ht="30" customHeight="1">
-      <c r="A29" s="78" t="s">
-        <v>147</v>
-      </c>
-      <c r="B29" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="D29" s="27" t="s">
-        <v>171</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="F29" s="84" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="30" customHeight="1">
-      <c r="A30" s="79" t="s">
-        <v>153</v>
-      </c>
-      <c r="B30" s="18" t="s">
-        <v>183</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="E30" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="F30" s="85" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="30" customHeight="1">
-      <c r="A31" s="80" t="s">
-        <v>157</v>
-      </c>
-      <c r="B31" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>868</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>830</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>869</v>
-      </c>
-      <c r="F31" s="86" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="30" customHeight="1">
-      <c r="A32" s="81" t="s">
-        <v>802</v>
-      </c>
-      <c r="B32" s="75">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C32" s="76" t="s">
-        <v>816</v>
-      </c>
-      <c r="D32" s="75" t="s">
-        <v>167</v>
-      </c>
-      <c r="E32" s="76" t="s">
-        <v>817</v>
-      </c>
-      <c r="F32" s="87" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="30" customHeight="1">
-      <c r="A33" s="82" t="s">
-        <v>806</v>
-      </c>
-      <c r="B33" s="68">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C33" s="66" t="s">
-        <v>850</v>
-      </c>
-      <c r="D33" s="68" t="s">
-        <v>61</v>
-      </c>
-      <c r="E33" s="66" t="s">
-        <v>851</v>
-      </c>
-      <c r="F33" s="88" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A34" s="185" t="s">
-        <v>209</v>
-      </c>
-      <c r="B34" s="186"/>
-      <c r="C34" s="186"/>
-      <c r="D34" s="186"/>
-      <c r="E34" s="186"/>
-      <c r="F34" s="187"/>
-    </row>
-    <row r="35" spans="1:6" ht="30" customHeight="1">
-      <c r="A35" s="78" t="s">
-        <v>147</v>
-      </c>
-      <c r="B35" s="27">
-        <v>4.5</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>880</v>
-      </c>
-      <c r="D35" s="27" t="s">
-        <v>220</v>
-      </c>
-      <c r="E35" s="28" t="s">
-        <v>881</v>
-      </c>
-      <c r="F35" s="84" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="30" customHeight="1">
-      <c r="A36" s="79" t="s">
-        <v>153</v>
-      </c>
-      <c r="B36" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="D36" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="E36" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="F36" s="85" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="30" customHeight="1">
-      <c r="A37" s="80" t="s">
-        <v>157</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="F37" s="86" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="30" customHeight="1">
-      <c r="A38" s="81" t="s">
-        <v>802</v>
-      </c>
-      <c r="B38" s="75">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C38" s="76" t="s">
-        <v>818</v>
-      </c>
-      <c r="D38" s="75" t="s">
-        <v>216</v>
-      </c>
-      <c r="E38" s="76" t="s">
-        <v>819</v>
-      </c>
-      <c r="F38" s="87" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="30" customHeight="1">
-      <c r="A39" s="82" t="s">
-        <v>806</v>
-      </c>
-      <c r="B39" s="68">
-        <v>4.3</v>
-      </c>
-      <c r="C39" s="66" t="s">
-        <v>853</v>
-      </c>
-      <c r="D39" s="68" t="s">
-        <v>224</v>
-      </c>
-      <c r="E39" s="66" t="s">
-        <v>854</v>
-      </c>
-      <c r="F39" s="88" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A40" s="185" t="s">
-        <v>218</v>
-      </c>
-      <c r="B40" s="186"/>
-      <c r="C40" s="186"/>
-      <c r="D40" s="186"/>
-      <c r="E40" s="186"/>
-      <c r="F40" s="187"/>
-    </row>
-    <row r="41" spans="1:6" ht="30" customHeight="1">
-      <c r="A41" s="78" t="s">
-        <v>147</v>
-      </c>
-      <c r="B41" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="D41" s="27" t="s">
-        <v>220</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="F41" s="84" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="30" customHeight="1">
-      <c r="A42" s="79" t="s">
-        <v>153</v>
-      </c>
-      <c r="B42" s="18" t="s">
-        <v>183</v>
-      </c>
-      <c r="C42" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="D42" s="18" t="s">
-        <v>224</v>
-      </c>
-      <c r="E42" s="15" t="s">
-        <v>225</v>
-      </c>
-      <c r="F42" s="85" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="30" customHeight="1">
-      <c r="A43" s="80" t="s">
-        <v>157</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C43" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="F43" s="86" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="30" customHeight="1">
-      <c r="A44" s="81" t="s">
-        <v>802</v>
-      </c>
-      <c r="B44" s="75">
-        <v>4.5</v>
-      </c>
-      <c r="C44" s="76" t="s">
-        <v>820</v>
-      </c>
-      <c r="D44" s="75" t="s">
-        <v>89</v>
-      </c>
-      <c r="E44" s="76" t="s">
-        <v>821</v>
-      </c>
-      <c r="F44" s="87" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="30" customHeight="1">
-      <c r="A45" s="82" t="s">
-        <v>806</v>
-      </c>
-      <c r="B45" s="68">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C45" s="66" t="s">
-        <v>822</v>
-      </c>
-      <c r="D45" s="68" t="s">
-        <v>823</v>
-      </c>
-      <c r="E45" s="66" t="s">
-        <v>824</v>
-      </c>
-      <c r="F45" s="88" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A46" s="185" t="s">
-        <v>230</v>
-      </c>
-      <c r="B46" s="186"/>
-      <c r="C46" s="186"/>
-      <c r="D46" s="186"/>
-      <c r="E46" s="186"/>
-      <c r="F46" s="187"/>
-    </row>
-    <row r="47" spans="1:6" ht="30" customHeight="1">
-      <c r="A47" s="78" t="s">
-        <v>147</v>
-      </c>
-      <c r="B47" s="27" t="s">
-        <v>214</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="D47" s="27" t="s">
-        <v>160</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="F47" s="84" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="30" customHeight="1">
-      <c r="A48" s="79" t="s">
-        <v>153</v>
-      </c>
-      <c r="B48" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="C48" s="16" t="s">
-        <v>234</v>
-      </c>
-      <c r="D48" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="E48" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="F48" s="85" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="30" customHeight="1">
-      <c r="A49" s="80" t="s">
-        <v>157</v>
-      </c>
-      <c r="B49" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>870</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>871</v>
-      </c>
-      <c r="F49" s="86" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="30" customHeight="1">
-      <c r="A50" s="81" t="s">
-        <v>802</v>
-      </c>
-      <c r="B50" s="75">
-        <v>4.7</v>
-      </c>
-      <c r="C50" s="76" t="s">
-        <v>826</v>
-      </c>
-      <c r="D50" s="75" t="s">
-        <v>66</v>
-      </c>
-      <c r="E50" s="76" t="s">
-        <v>827</v>
-      </c>
-      <c r="F50" s="87" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="30" customHeight="1">
-      <c r="A51" s="82" t="s">
-        <v>806</v>
-      </c>
-      <c r="B51" s="68">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C51" s="66" t="s">
-        <v>829</v>
-      </c>
-      <c r="D51" s="68" t="s">
-        <v>830</v>
-      </c>
-      <c r="E51" s="66" t="s">
-        <v>831</v>
-      </c>
-      <c r="F51" s="88" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A52" s="185" t="s">
-        <v>238</v>
-      </c>
-      <c r="B52" s="186"/>
-      <c r="C52" s="186"/>
-      <c r="D52" s="186"/>
-      <c r="E52" s="186"/>
-      <c r="F52" s="187"/>
-    </row>
-    <row r="53" spans="1:6" ht="30" customHeight="1">
-      <c r="A53" s="78" t="s">
-        <v>147</v>
-      </c>
-      <c r="B53" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="D53" s="27" t="s">
-        <v>210</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="F53" s="84" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="30" customHeight="1">
-      <c r="A54" s="79" t="s">
-        <v>153</v>
-      </c>
-      <c r="B54" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="C54" s="16" t="s">
-        <v>242</v>
-      </c>
-      <c r="D54" s="18" t="s">
-        <v>228</v>
-      </c>
-      <c r="E54" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="F54" s="85" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="30" customHeight="1">
-      <c r="A55" s="80" t="s">
-        <v>157</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C55" s="29" t="s">
-        <v>244</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="F55" s="86" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="30" customHeight="1">
-      <c r="A56" s="81" t="s">
-        <v>802</v>
-      </c>
-      <c r="B56" s="75">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C56" s="74" t="s">
-        <v>855</v>
-      </c>
-      <c r="D56" s="75" t="s">
-        <v>220</v>
-      </c>
-      <c r="E56" s="76" t="s">
-        <v>856</v>
-      </c>
-      <c r="F56" s="87" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="30" customHeight="1">
-      <c r="A57" s="82" t="s">
-        <v>806</v>
-      </c>
-      <c r="B57" s="68">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="C57" s="69" t="s">
-        <v>833</v>
-      </c>
-      <c r="D57" s="68" t="s">
-        <v>52</v>
-      </c>
-      <c r="E57" s="66" t="s">
-        <v>834</v>
-      </c>
-      <c r="F57" s="88" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A58" s="185" t="s">
-        <v>247</v>
-      </c>
-      <c r="B58" s="186"/>
-      <c r="C58" s="186"/>
-      <c r="D58" s="186"/>
-      <c r="E58" s="186"/>
-      <c r="F58" s="187"/>
-    </row>
-    <row r="59" spans="1:6" ht="30" customHeight="1">
-      <c r="A59" s="78" t="s">
-        <v>248</v>
-      </c>
-      <c r="B59" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="C59" s="28" t="s">
-        <v>249</v>
-      </c>
-      <c r="D59" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="F59" s="84" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="30" customHeight="1">
-      <c r="A60" s="79" t="s">
-        <v>251</v>
-      </c>
-      <c r="B60" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="C60" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="D60" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="E60" s="25" t="s">
-        <v>253</v>
-      </c>
-      <c r="F60" s="85" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="30" customHeight="1">
-      <c r="A61" s="80" t="s">
-        <v>254</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="C61" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="E61" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="F61" s="86" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A62" s="179" t="s">
-        <v>260</v>
-      </c>
-      <c r="B62" s="180"/>
-      <c r="C62" s="180"/>
-      <c r="D62" s="180"/>
-      <c r="E62" s="180"/>
-      <c r="F62" s="181"/>
-    </row>
-    <row r="63" spans="1:6" ht="30" customHeight="1">
-      <c r="A63" s="78" t="s">
-        <v>147</v>
-      </c>
-      <c r="B63" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="D63" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="F63" s="84" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="30" customHeight="1">
-      <c r="A64" s="79" t="s">
-        <v>153</v>
-      </c>
-      <c r="B64" s="18">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C64" s="16" t="s">
-        <v>858</v>
-      </c>
-      <c r="D64" s="18" t="s">
-        <v>224</v>
-      </c>
-      <c r="E64" s="15" t="s">
-        <v>875</v>
-      </c>
-      <c r="F64" s="85" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="30" customHeight="1">
-      <c r="A65" s="80" t="s">
-        <v>157</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="C65" s="13" t="s">
+      <c r="E67" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="F67" s="86" t="s">
         <v>264</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="F65" s="86" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="30" customHeight="1">
-      <c r="A66" s="81" t="s">
-        <v>802</v>
-      </c>
-      <c r="B66" s="75">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C66" s="76" t="s">
-        <v>862</v>
-      </c>
-      <c r="D66" s="75" t="s">
-        <v>830</v>
-      </c>
-      <c r="E66" s="76" t="s">
-        <v>863</v>
-      </c>
-      <c r="F66" s="87" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="30" customHeight="1">
-      <c r="A67" s="82" t="s">
-        <v>806</v>
-      </c>
-      <c r="B67" s="68">
-        <v>4.3</v>
-      </c>
-      <c r="C67" s="66" t="s">
-        <v>876</v>
-      </c>
-      <c r="D67" s="68" t="s">
-        <v>877</v>
-      </c>
-      <c r="E67" s="66" t="s">
-        <v>878</v>
-      </c>
-      <c r="F67" s="88" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="30" customHeight="1">
       <c r="A68" s="81" t="s">
-        <v>892</v>
+        <v>800</v>
       </c>
       <c r="B68" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C68" s="76" t="s">
-        <v>893</v>
+        <v>859</v>
       </c>
       <c r="D68" s="75" t="s">
-        <v>123</v>
+        <v>828</v>
       </c>
       <c r="E68" s="76" t="s">
-        <v>894</v>
+        <v>860</v>
       </c>
       <c r="F68" s="87" t="s">
-        <v>121</v>
+        <v>277</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="30" customHeight="1">
       <c r="A69" s="82" t="s">
+        <v>804</v>
+      </c>
+      <c r="B69" s="68">
+        <v>4.3</v>
+      </c>
+      <c r="C69" s="66" t="s">
+        <v>873</v>
+      </c>
+      <c r="D69" s="68" t="s">
+        <v>874</v>
+      </c>
+      <c r="E69" s="66" t="s">
+        <v>875</v>
+      </c>
+      <c r="F69" s="88" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="30" customHeight="1">
+      <c r="A70" s="81" t="s">
+        <v>889</v>
+      </c>
+      <c r="B70" s="75">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C70" s="76" t="s">
+        <v>890</v>
+      </c>
+      <c r="D70" s="75" t="s">
+        <v>123</v>
+      </c>
+      <c r="E70" s="76" t="s">
+        <v>891</v>
+      </c>
+      <c r="F70" s="87" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="30" customHeight="1">
+      <c r="A71" s="82" t="s">
+        <v>892</v>
+      </c>
+      <c r="B71" s="68">
+        <v>4.5</v>
+      </c>
+      <c r="C71" s="66" t="s">
+        <v>893</v>
+      </c>
+      <c r="D71" s="68" t="s">
+        <v>99</v>
+      </c>
+      <c r="E71" s="66" t="s">
+        <v>894</v>
+      </c>
+      <c r="F71" s="88" t="s">
         <v>895</v>
       </c>
-      <c r="B69" s="68">
-        <v>4.5</v>
-      </c>
-      <c r="C69" s="66" t="s">
+    </row>
+    <row r="72" spans="1:6" ht="30" customHeight="1">
+      <c r="A72" s="82" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B72" s="216" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C72" s="66" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D72" s="68" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E72" s="66" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F72" s="88" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="30" customHeight="1">
+      <c r="A73" s="82" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B73" s="216" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C73" s="66" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D73" s="68" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E73" s="66" t="s">
+        <v>1026</v>
+      </c>
+      <c r="F73" s="88" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="30" customHeight="1">
+      <c r="A74" s="179" t="s">
+        <v>265</v>
+      </c>
+      <c r="B74" s="180"/>
+      <c r="C74" s="180"/>
+      <c r="D74" s="180"/>
+      <c r="E74" s="180"/>
+      <c r="F74" s="181"/>
+    </row>
+    <row r="75" spans="1:6" ht="30" customHeight="1">
+      <c r="A75" s="78" t="s">
+        <v>147</v>
+      </c>
+      <c r="B75" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D75" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="F75" s="84" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A76" s="79" t="s">
+        <v>153</v>
+      </c>
+      <c r="B76" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="C76" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="D76" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="E76" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="F76" s="85" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="30" customHeight="1">
+      <c r="A77" s="80" t="s">
+        <v>157</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="F77" s="86" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="30" customHeight="1">
+      <c r="A78" s="81" t="s">
+        <v>800</v>
+      </c>
+      <c r="B78" s="75">
+        <v>4.3</v>
+      </c>
+      <c r="C78" s="76" t="s">
+        <v>870</v>
+      </c>
+      <c r="D78" s="75" t="s">
+        <v>219</v>
+      </c>
+      <c r="E78" s="76" t="s">
+        <v>871</v>
+      </c>
+      <c r="F78" s="87" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="30" customHeight="1">
+      <c r="A79" s="82" t="s">
+        <v>804</v>
+      </c>
+      <c r="B79" s="68">
+        <v>4</v>
+      </c>
+      <c r="C79" s="66" t="s">
+        <v>835</v>
+      </c>
+      <c r="D79" s="68" t="s">
+        <v>836</v>
+      </c>
+      <c r="E79" s="66" t="s">
+        <v>837</v>
+      </c>
+      <c r="F79" s="88" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="30" customHeight="1">
+      <c r="A80" s="179" t="s">
+        <v>273</v>
+      </c>
+      <c r="B80" s="180"/>
+      <c r="C80" s="180"/>
+      <c r="D80" s="180"/>
+      <c r="E80" s="180"/>
+      <c r="F80" s="181"/>
+    </row>
+    <row r="81" spans="1:6" ht="30" customHeight="1">
+      <c r="A81" s="78" t="s">
+        <v>147</v>
+      </c>
+      <c r="B81" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="D81" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="F81" s="84" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="30" customHeight="1">
+      <c r="A82" s="79" t="s">
+        <v>153</v>
+      </c>
+      <c r="B82" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="C82" s="16" t="s">
+        <v>857</v>
+      </c>
+      <c r="D82" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="E82" s="15" t="s">
+        <v>858</v>
+      </c>
+      <c r="F82" s="85" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="30" customHeight="1">
+      <c r="A83" s="80" t="s">
+        <v>157</v>
+      </c>
+      <c r="B83" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C83" s="13" t="s">
+        <v>880</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>881</v>
+      </c>
+      <c r="F83" s="86" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="30" customHeight="1">
+      <c r="A84" s="81" t="s">
+        <v>800</v>
+      </c>
+      <c r="B84" s="75">
+        <v>4.3</v>
+      </c>
+      <c r="C84" s="76" t="s">
+        <v>834</v>
+      </c>
+      <c r="D84" s="75" t="s">
+        <v>119</v>
+      </c>
+      <c r="E84" s="76" t="s">
+        <v>856</v>
+      </c>
+      <c r="F84" s="87" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="30" customHeight="1">
+      <c r="A85" s="82" t="s">
+        <v>804</v>
+      </c>
+      <c r="B85" s="68">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C85" s="66" t="s">
+        <v>882</v>
+      </c>
+      <c r="D85" s="68" t="s">
+        <v>883</v>
+      </c>
+      <c r="E85" s="66" t="s">
+        <v>884</v>
+      </c>
+      <c r="F85" s="88" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="30" customHeight="1">
+      <c r="A86" s="81" t="s">
+        <v>889</v>
+      </c>
+      <c r="B86" s="75">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="C86" s="76" t="s">
         <v>896</v>
       </c>
-      <c r="D69" s="68" t="s">
-        <v>99</v>
-      </c>
-      <c r="E69" s="66" t="s">
+      <c r="D86" s="75" t="s">
+        <v>128</v>
+      </c>
+      <c r="E86" s="76" t="s">
         <v>897</v>
       </c>
-      <c r="F69" s="88" t="s">
+      <c r="F86" s="87" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="30" customHeight="1">
+      <c r="A87" s="82" t="s">
+        <v>892</v>
+      </c>
+      <c r="B87" s="68" t="s">
+        <v>254</v>
+      </c>
+      <c r="C87" s="66" t="s">
         <v>898</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A70" s="179" t="s">
-        <v>267</v>
-      </c>
-      <c r="B70" s="180"/>
-      <c r="C70" s="180"/>
-      <c r="D70" s="180"/>
-      <c r="E70" s="180"/>
-      <c r="F70" s="181"/>
-    </row>
-    <row r="71" spans="1:6" ht="30" customHeight="1">
-      <c r="A71" s="78" t="s">
-        <v>147</v>
-      </c>
-      <c r="B71" s="27" t="s">
-        <v>183</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="D71" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="E71" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="F71" s="84" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="30" customHeight="1">
-      <c r="A72" s="79" t="s">
-        <v>153</v>
-      </c>
-      <c r="B72" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="C72" s="16" t="s">
-        <v>271</v>
-      </c>
-      <c r="D72" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="E72" s="15" t="s">
-        <v>272</v>
-      </c>
-      <c r="F72" s="85" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="30" customHeight="1">
-      <c r="A73" s="80" t="s">
-        <v>157</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C73" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="F73" s="86" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="30" customHeight="1">
-      <c r="A74" s="81" t="s">
-        <v>802</v>
-      </c>
-      <c r="B74" s="75">
-        <v>4.3</v>
-      </c>
-      <c r="C74" s="76" t="s">
-        <v>873</v>
-      </c>
-      <c r="D74" s="75" t="s">
-        <v>220</v>
-      </c>
-      <c r="E74" s="76" t="s">
-        <v>874</v>
-      </c>
-      <c r="F74" s="87" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="30" customHeight="1">
-      <c r="A75" s="82" t="s">
-        <v>806</v>
-      </c>
-      <c r="B75" s="68">
-        <v>4</v>
-      </c>
-      <c r="C75" s="66" t="s">
-        <v>837</v>
-      </c>
-      <c r="D75" s="68" t="s">
-        <v>838</v>
-      </c>
-      <c r="E75" s="66" t="s">
-        <v>839</v>
-      </c>
-      <c r="F75" s="88" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A76" s="179" t="s">
-        <v>275</v>
-      </c>
-      <c r="B76" s="180"/>
-      <c r="C76" s="180"/>
-      <c r="D76" s="180"/>
-      <c r="E76" s="180"/>
-      <c r="F76" s="181"/>
-    </row>
-    <row r="77" spans="1:6" ht="30" customHeight="1">
-      <c r="A77" s="78" t="s">
-        <v>147</v>
-      </c>
-      <c r="B77" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="C77" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="D77" s="27" t="s">
-        <v>263</v>
-      </c>
-      <c r="E77" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="F77" s="84" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="30" customHeight="1">
-      <c r="A78" s="79" t="s">
-        <v>153</v>
-      </c>
-      <c r="B78" s="18">
-        <v>4.2</v>
-      </c>
-      <c r="C78" s="16" t="s">
-        <v>860</v>
-      </c>
-      <c r="D78" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="E78" s="15" t="s">
-        <v>861</v>
-      </c>
-      <c r="F78" s="85" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="30" customHeight="1">
-      <c r="A79" s="80" t="s">
-        <v>157</v>
-      </c>
-      <c r="B79" s="4">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C79" s="13" t="s">
-        <v>883</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>884</v>
-      </c>
-      <c r="F79" s="86" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="30" customHeight="1">
-      <c r="A80" s="81" t="s">
-        <v>802</v>
-      </c>
-      <c r="B80" s="75">
-        <v>4.3</v>
-      </c>
-      <c r="C80" s="76" t="s">
-        <v>836</v>
-      </c>
-      <c r="D80" s="75" t="s">
-        <v>119</v>
-      </c>
-      <c r="E80" s="76" t="s">
-        <v>859</v>
-      </c>
-      <c r="F80" s="87" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="30" customHeight="1">
-      <c r="A81" s="82" t="s">
-        <v>806</v>
-      </c>
-      <c r="B81" s="68">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C81" s="66" t="s">
-        <v>885</v>
-      </c>
-      <c r="D81" s="68" t="s">
-        <v>886</v>
-      </c>
-      <c r="E81" s="66" t="s">
-        <v>887</v>
-      </c>
-      <c r="F81" s="88" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="30" customHeight="1">
-      <c r="A82" s="81" t="s">
-        <v>892</v>
-      </c>
-      <c r="B82" s="75">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="C82" s="76" t="s">
+      <c r="D87" s="68" t="s">
+        <v>289</v>
+      </c>
+      <c r="E87" s="66" t="s">
         <v>899</v>
       </c>
-      <c r="D82" s="75" t="s">
-        <v>128</v>
-      </c>
-      <c r="E82" s="76" t="s">
-        <v>900</v>
-      </c>
-      <c r="F82" s="87" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="30" customHeight="1">
-      <c r="A83" s="82" t="s">
-        <v>895</v>
-      </c>
-      <c r="B83" s="68" t="s">
-        <v>255</v>
-      </c>
-      <c r="C83" s="66" t="s">
-        <v>901</v>
-      </c>
-      <c r="D83" s="68" t="s">
-        <v>291</v>
-      </c>
-      <c r="E83" s="66" t="s">
-        <v>902</v>
-      </c>
-      <c r="F83" s="88" t="s">
+      <c r="F87" s="88" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A84" s="179" t="s">
-        <v>281</v>
-      </c>
-      <c r="B84" s="180"/>
-      <c r="C84" s="180"/>
-      <c r="D84" s="180"/>
-      <c r="E84" s="180"/>
-      <c r="F84" s="181"/>
-    </row>
-    <row r="85" spans="1:6" ht="30" customHeight="1">
-      <c r="A85" s="78" t="s">
-        <v>147</v>
-      </c>
-      <c r="B85" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="D85" s="27" t="s">
-        <v>283</v>
-      </c>
-      <c r="E85" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="F85" s="84" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="30" customHeight="1">
-      <c r="A86" s="79" t="s">
-        <v>153</v>
-      </c>
-      <c r="B86" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="C86" s="16" t="s">
-        <v>285</v>
-      </c>
-      <c r="D86" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="E86" s="15" t="s">
-        <v>286</v>
-      </c>
-      <c r="F86" s="85" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="30" customHeight="1">
-      <c r="A87" s="80" t="s">
-        <v>157</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="C87" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="F87" s="86" t="s">
-        <v>290</v>
-      </c>
-    </row>
     <row r="88" spans="1:6" ht="30" customHeight="1">
-      <c r="A88" s="81" t="s">
-        <v>802</v>
-      </c>
-      <c r="B88" s="75">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C88" s="76" t="s">
-        <v>888</v>
-      </c>
-      <c r="D88" s="75" t="s">
-        <v>889</v>
-      </c>
-      <c r="E88" s="76" t="s">
-        <v>890</v>
-      </c>
-      <c r="F88" s="87" t="s">
-        <v>891</v>
+      <c r="A88" s="82" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B88" s="216" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C88" s="66" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D88" s="68" t="s">
+        <v>189</v>
+      </c>
+      <c r="E88" s="66" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F88" s="88" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="30" customHeight="1">
       <c r="A89" s="82" t="s">
-        <v>806</v>
-      </c>
-      <c r="B89" s="68">
+        <v>1014</v>
+      </c>
+      <c r="B89" s="216" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C89" s="66" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D89" s="68" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E89" s="66" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F89" s="88" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="33.75" customHeight="1">
+      <c r="A90" s="179" t="s">
+        <v>279</v>
+      </c>
+      <c r="B90" s="180"/>
+      <c r="C90" s="180"/>
+      <c r="D90" s="180"/>
+      <c r="E90" s="180"/>
+      <c r="F90" s="181"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91" s="78" t="s">
+        <v>147</v>
+      </c>
+      <c r="B91" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="D91" s="27" t="s">
+        <v>281</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="F91" s="84" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" s="79" t="s">
+        <v>153</v>
+      </c>
+      <c r="B92" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="C92" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="D92" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="E92" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="F92" s="85" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" s="80" t="s">
+        <v>157</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C93" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="F93" s="86" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="28">
+      <c r="A94" s="81" t="s">
+        <v>800</v>
+      </c>
+      <c r="B94" s="75">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C94" s="76" t="s">
+        <v>885</v>
+      </c>
+      <c r="D94" s="75" t="s">
+        <v>886</v>
+      </c>
+      <c r="E94" s="76" t="s">
+        <v>887</v>
+      </c>
+      <c r="F94" s="87" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="28">
+      <c r="A95" s="82" t="s">
+        <v>804</v>
+      </c>
+      <c r="B95" s="68">
         <v>4.5</v>
       </c>
-      <c r="C89" s="66" t="s">
-        <v>840</v>
-      </c>
-      <c r="D89" s="68" t="s">
+      <c r="C95" s="66" t="s">
+        <v>838</v>
+      </c>
+      <c r="D95" s="68" t="s">
         <v>119</v>
       </c>
-      <c r="E89" s="66" t="s">
-        <v>841</v>
-      </c>
-      <c r="F89" s="88" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="33.75" customHeight="1" thickBot="1">
-      <c r="A90" s="182" t="s">
-        <v>903</v>
-      </c>
-      <c r="B90" s="183"/>
-      <c r="C90" s="183"/>
-      <c r="D90" s="183"/>
-      <c r="E90" s="183"/>
-      <c r="F90" s="184"/>
+      <c r="E95" s="66" t="s">
+        <v>839</v>
+      </c>
+      <c r="F95" s="88" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="48" customHeight="1" thickBot="1">
+      <c r="A96" s="182" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B96" s="183"/>
+      <c r="C96" s="183"/>
+      <c r="D96" s="183"/>
+      <c r="E96" s="183"/>
+      <c r="F96" s="184"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -20858,19 +21302,19 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A48:F48"/>
     <mergeCell ref="A90:F90"/>
-    <mergeCell ref="A52:F52"/>
-    <mergeCell ref="A58:F58"/>
-    <mergeCell ref="A62:F62"/>
-    <mergeCell ref="A70:F70"/>
-    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A96:F96"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A60:F60"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A74:F74"/>
+    <mergeCell ref="A80:F80"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -20893,7 +21337,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1">
       <c r="A1" s="161" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B1" s="162"/>
       <c r="C1" s="162"/>
@@ -20907,7 +21351,7 @@
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
       <c r="A3" s="197" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B3" s="198"/>
       <c r="C3" s="198"/>
@@ -20915,100 +21359,100 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="133" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>45</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D4" s="143" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" customHeight="1">
       <c r="A5" s="134" t="s">
+        <v>295</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>296</v>
+      </c>
+      <c r="C5" s="32" t="s">
         <v>297</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="D5" s="144" t="s">
         <v>298</v>
-      </c>
-      <c r="C5" s="32" t="s">
-        <v>299</v>
-      </c>
-      <c r="D5" s="144" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="27.75" customHeight="1">
       <c r="A6" s="135" t="s">
+        <v>299</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="C6" s="35" t="s">
         <v>301</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="D6" s="145" t="s">
         <v>302</v>
-      </c>
-      <c r="C6" s="35" t="s">
-        <v>303</v>
-      </c>
-      <c r="D6" s="145" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="27.75" customHeight="1">
       <c r="A7" s="136" t="s">
+        <v>303</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>304</v>
+      </c>
+      <c r="C7" s="38" t="s">
         <v>305</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="D7" s="146" t="s">
         <v>306</v>
-      </c>
-      <c r="C7" s="38" t="s">
-        <v>307</v>
-      </c>
-      <c r="D7" s="146" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1">
       <c r="A8" s="137" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B8" s="40" t="s">
         <v>63</v>
       </c>
       <c r="C8" s="41" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D8" s="147" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="27.75" customHeight="1">
       <c r="A9" s="138" t="s">
+        <v>310</v>
+      </c>
+      <c r="B9" s="43" t="s">
+        <v>311</v>
+      </c>
+      <c r="C9" s="44" t="s">
         <v>312</v>
       </c>
-      <c r="B9" s="43" t="s">
+      <c r="D9" s="148" t="s">
         <v>313</v>
-      </c>
-      <c r="C9" s="44" t="s">
-        <v>314</v>
-      </c>
-      <c r="D9" s="148" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" customHeight="1">
       <c r="A10" s="139" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B10" s="92" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="C10" s="92" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="D10" s="125" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -21019,7 +21463,7 @@
     </row>
     <row r="12" spans="1:4" ht="24" customHeight="1">
       <c r="A12" s="200" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B12" s="201"/>
       <c r="C12" s="201"/>
@@ -21027,170 +21471,170 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="133" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>45</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D13" s="143" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1">
       <c r="A14" s="135" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B14" s="34" t="s">
+        <v>315</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>316</v>
+      </c>
+      <c r="D14" s="145" t="s">
         <v>317</v>
-      </c>
-      <c r="C14" s="35" t="s">
-        <v>318</v>
-      </c>
-      <c r="D14" s="145" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="27.75" customHeight="1">
       <c r="A15" s="136" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D15" s="146" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="30" customHeight="1">
       <c r="A16" s="136" t="s">
+        <v>320</v>
+      </c>
+      <c r="B16" s="45" t="s">
+        <v>321</v>
+      </c>
+      <c r="C16" s="38" t="s">
         <v>322</v>
       </c>
-      <c r="B16" s="45" t="s">
+      <c r="D16" s="146" t="s">
         <v>323</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>324</v>
-      </c>
-      <c r="D16" s="146" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1">
       <c r="A17" s="137" t="s">
+        <v>324</v>
+      </c>
+      <c r="B17" s="40" t="s">
+        <v>325</v>
+      </c>
+      <c r="C17" s="41" t="s">
         <v>326</v>
       </c>
-      <c r="B17" s="40" t="s">
+      <c r="D17" s="147" t="s">
         <v>327</v>
-      </c>
-      <c r="C17" s="41" t="s">
-        <v>328</v>
-      </c>
-      <c r="D17" s="147" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1">
       <c r="A18" s="137" t="s">
+        <v>328</v>
+      </c>
+      <c r="B18" s="40" t="s">
+        <v>329</v>
+      </c>
+      <c r="C18" s="41" t="s">
         <v>330</v>
       </c>
-      <c r="B18" s="40" t="s">
+      <c r="D18" s="147" t="s">
         <v>331</v>
-      </c>
-      <c r="C18" s="41" t="s">
-        <v>332</v>
-      </c>
-      <c r="D18" s="147" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="30" customHeight="1">
       <c r="A19" s="134" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B19" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>333</v>
+      </c>
+      <c r="D19" s="144" t="s">
         <v>334</v>
-      </c>
-      <c r="C19" s="32" t="s">
-        <v>335</v>
-      </c>
-      <c r="D19" s="144" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="30" customHeight="1">
       <c r="A20" s="139" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B20" s="92" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="C20" s="92" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="D20" s="125" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="30" customHeight="1">
       <c r="A21" s="140" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="B21" s="90" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="C21" s="90" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="D21" s="149" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="27.75" customHeight="1">
       <c r="A22" s="138" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B22" s="43" t="s">
+        <v>335</v>
+      </c>
+      <c r="C22" s="44" t="s">
+        <v>336</v>
+      </c>
+      <c r="D22" s="148" t="s">
         <v>337</v>
-      </c>
-      <c r="C22" s="44" t="s">
-        <v>338</v>
-      </c>
-      <c r="D22" s="148" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="30" customHeight="1">
       <c r="A23" s="137" t="s">
+        <v>338</v>
+      </c>
+      <c r="B23" s="40" t="s">
+        <v>339</v>
+      </c>
+      <c r="C23" s="41" t="s">
         <v>340</v>
       </c>
-      <c r="B23" s="40" t="s">
+      <c r="D23" s="147" t="s">
         <v>341</v>
-      </c>
-      <c r="C23" s="41" t="s">
-        <v>342</v>
-      </c>
-      <c r="D23" s="147" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="30" customHeight="1">
       <c r="A24" s="137" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B24" s="40" t="s">
+        <v>342</v>
+      </c>
+      <c r="C24" s="41" t="s">
+        <v>343</v>
+      </c>
+      <c r="D24" s="147" t="s">
         <v>344</v>
-      </c>
-      <c r="C24" s="41" t="s">
-        <v>345</v>
-      </c>
-      <c r="D24" s="147" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -21201,7 +21645,7 @@
     </row>
     <row r="26" spans="1:4" ht="24" customHeight="1">
       <c r="A26" s="203" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B26" s="204"/>
       <c r="C26" s="204"/>
@@ -21209,128 +21653,128 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="133" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>45</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D27" s="143" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="27.75" customHeight="1">
       <c r="A28" s="135" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B28" s="34" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D28" s="145" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="30" customHeight="1">
       <c r="A29" s="136" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B29" s="37" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D29" s="146" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="27.75" customHeight="1">
       <c r="A30" s="134" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B30" s="31" t="s">
+        <v>350</v>
+      </c>
+      <c r="C30" s="32" t="s">
+        <v>351</v>
+      </c>
+      <c r="D30" s="144" t="s">
         <v>352</v>
-      </c>
-      <c r="C30" s="32" t="s">
-        <v>353</v>
-      </c>
-      <c r="D30" s="144" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="27.75" customHeight="1">
       <c r="A31" s="138" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B31" s="43" t="s">
+        <v>353</v>
+      </c>
+      <c r="C31" s="44" t="s">
+        <v>354</v>
+      </c>
+      <c r="D31" s="148" t="s">
         <v>355</v>
-      </c>
-      <c r="C31" s="44" t="s">
-        <v>356</v>
-      </c>
-      <c r="D31" s="148" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="27.75" customHeight="1">
       <c r="A32" s="138" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B32" s="43" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C32" s="44" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D32" s="148" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="30" customHeight="1">
       <c r="A33" s="135" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B33" s="46" t="s">
+        <v>358</v>
+      </c>
+      <c r="C33" s="35" t="s">
+        <v>359</v>
+      </c>
+      <c r="D33" s="145" t="s">
         <v>360</v>
-      </c>
-      <c r="C33" s="35" t="s">
-        <v>361</v>
-      </c>
-      <c r="D33" s="145" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="30" customHeight="1">
       <c r="A34" s="137" t="s">
+        <v>361</v>
+      </c>
+      <c r="B34" s="40" t="s">
+        <v>362</v>
+      </c>
+      <c r="C34" s="41" t="s">
         <v>363</v>
       </c>
-      <c r="B34" s="40" t="s">
+      <c r="D34" s="147" t="s">
         <v>364</v>
-      </c>
-      <c r="C34" s="41" t="s">
-        <v>365</v>
-      </c>
-      <c r="D34" s="147" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="30" customHeight="1" thickBot="1">
       <c r="A35" s="141" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B35" s="130" t="s">
+        <v>365</v>
+      </c>
+      <c r="C35" s="131" t="s">
+        <v>366</v>
+      </c>
+      <c r="D35" s="150" t="s">
         <v>367</v>
-      </c>
-      <c r="C35" s="131" t="s">
-        <v>368</v>
-      </c>
-      <c r="D35" s="150" t="s">
-        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -21361,7 +21805,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1">
       <c r="A1" s="206" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B1" s="206"/>
       <c r="C1" s="206"/>
@@ -21369,7 +21813,7 @@
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
       <c r="A3" s="178" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B3" s="178"/>
       <c r="C3" s="178"/>
@@ -21377,63 +21821,63 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="12" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B4" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>371</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>372</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="27.75" customHeight="1">
       <c r="A5" s="47" t="s">
+        <v>372</v>
+      </c>
+      <c r="B5" s="48" t="s">
+        <v>373</v>
+      </c>
+      <c r="C5" s="49" t="s">
         <v>374</v>
       </c>
-      <c r="B5" s="48" t="s">
+      <c r="D5" s="47" t="s">
         <v>375</v>
-      </c>
-      <c r="C5" s="49" t="s">
-        <v>376</v>
-      </c>
-      <c r="D5" s="47" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="27.75" customHeight="1">
       <c r="A6" s="47" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D6" s="47" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="27.75" customHeight="1">
       <c r="A7" s="30" t="s">
+        <v>378</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>379</v>
+      </c>
+      <c r="C7" s="32" t="s">
         <v>380</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="D7" s="30" t="s">
         <v>381</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>382</v>
-      </c>
-      <c r="D7" s="30" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="24" customHeight="1">
       <c r="A9" s="174" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B9" s="174"/>
       <c r="C9" s="174"/>
@@ -21441,49 +21885,49 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="12" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B10" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>371</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>372</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="27.75" customHeight="1">
       <c r="A11" s="47" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B11" s="48" t="s">
+        <v>382</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>383</v>
+      </c>
+      <c r="D11" s="47" t="s">
         <v>384</v>
-      </c>
-      <c r="C11" s="49" t="s">
-        <v>385</v>
-      </c>
-      <c r="D11" s="47" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="27.75" customHeight="1">
       <c r="A12" s="47" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B12" s="48" t="s">
+        <v>385</v>
+      </c>
+      <c r="C12" s="49" t="s">
+        <v>386</v>
+      </c>
+      <c r="D12" s="47" t="s">
         <v>387</v>
-      </c>
-      <c r="C12" s="49" t="s">
-        <v>388</v>
-      </c>
-      <c r="D12" s="47" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="24" customHeight="1">
       <c r="A14" s="176" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B14" s="176"/>
       <c r="C14" s="176"/>
@@ -21491,44 +21935,44 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="12" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B15" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="D15" s="12" t="s">
         <v>371</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>372</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="27.75" customHeight="1">
       <c r="A16" s="47" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B16" s="48" t="s">
+        <v>388</v>
+      </c>
+      <c r="C16" s="49" t="s">
+        <v>389</v>
+      </c>
+      <c r="D16" s="47" t="s">
         <v>390</v>
-      </c>
-      <c r="C16" s="49" t="s">
-        <v>391</v>
-      </c>
-      <c r="D16" s="47" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="27.75" customHeight="1">
       <c r="A17" s="50" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B17" s="51" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C17" s="52" t="s">
         <v>117</v>
       </c>
       <c r="D17" s="50" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>

--- a/tools/itinerary.xlsx
+++ b/tools/itinerary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jitwei/Library/Mobile Documents/com~apple~CloudDocs/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4BAEC6-A34F-1948-9AEC-08A088BC0738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1283FF7-42FE-E247-A56C-B529A2C85B5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="17020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="17020" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1591" uniqueCount="1069">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1596" uniqueCount="1075">
   <si>
     <r>
       <rPr>
@@ -8939,9 +8939,6 @@
     <t>18:30–19:45</t>
   </si>
   <si>
-    <t>Dinner</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -12701,12 +12698,6 @@
   </si>
   <si>
     <t>18:00–19:45</t>
-  </si>
-  <si>
-    <t>Farewell dinner — south old town</t>
-  </si>
-  <si>
-    <t>Canal-side dinner near Shiquan/Pingjiang.</t>
   </si>
   <si>
     <t>20:00–21:15</t>
@@ -14556,6 +14547,33 @@
   </si>
   <si>
     <t>¥15–25</t>
+  </si>
+  <si>
+    <t>Farewell dinner — 🦀 HAIRY CRAB: Lao Changmen 老阊门菜馆 (Shantang 山塘街店)</t>
+  </si>
+  <si>
+    <t>Peak 大闸蟹 season — mid-Nov is the 公蟹/蟹膏 window (农历十月). Order 招牌熟醉蟹, 阳澄湖大闸蟹 (market price), 蟹粉豆腐. ~¥100pp, 4.8/5 (small sample, 21 reviews); praised for 物美价廉 &amp; 拒绝料包. ⚠ Queues can exceed 1h at meal times — book or arrive 17:45. ⚠ At ¥100pp the crab is mostly 熟醉蟹, not whole steamed; whole 清蒸 is extra at 时令价. Ask for 现点现炒 蟹粉 and scan the 防伪戒指 QR to verify 阳澄湖 origin. PRESTIGE ALT: 新聚丰菜馆 太监弄店 (est. 1904, 黑珍珠+米其林指南, 清炒蟹粉, ¥215–389) — same lane as today’s lunch, but closes 20:30 and has QC complaints.</t>
+  </si>
+  <si>
+    <t>¥100pp · 山塘街</t>
+  </si>
+  <si>
+    <t>姑苏区山塘街 (老阊门菜馆) · 备选 姑苏区观前街太监弄 (新聚丰)</t>
+  </si>
+  <si>
+    <t>🦀 Crab</t>
+  </si>
+  <si>
+    <t>Lao Changmen 老阊门菜馆 (Day 7 · 山塘街店)</t>
+  </si>
+  <si>
+    <t>姑苏区山塘街 (walkable from the Ritz)</t>
+  </si>
+  <si>
+    <t>HAIRY CRAB 大闸蟹 season pick. 招牌熟醉蟹, 阳澄湖大闸蟹 (时令价), 蟹粉豆腐. 4.8/5 but only 21 reviews; 拒绝料包. Queues &gt;1h at meal times. Prestige alt: 新聚丰菜馆 太监弄店 (1904, 黑珍珠+米其林指南, 清炒蟹粉, ¥215–389, closes 20:30). Lake-view alt: 璞园春舍 on 阳澄湖莲花岛 — boat required, board by 16:30, book 3+ days ahead. Season: 9月下旬–12月; 农历十月 = 公蟹蟹膏. Source: Ctrip reviews via news summary — re-check on Dianping before going.</t>
+  </si>
+  <si>
+    <t>¥100 (蟹另计)</t>
   </si>
 </sst>
 </file>
@@ -16313,7 +16331,7 @@
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1">
       <c r="A4" s="167" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="B4" s="168"/>
       <c r="C4" s="168"/>
@@ -16366,13 +16384,13 @@
         <v>401</v>
       </c>
       <c r="B7" s="213" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="C7" s="50" t="s">
         <v>412</v>
       </c>
       <c r="D7" s="50" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="E7" s="50" t="s">
         <v>413</v>
@@ -16503,7 +16521,7 @@
     </row>
     <row r="14" spans="1:6" ht="25.5" customHeight="1">
       <c r="A14" s="167" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="B14" s="168"/>
       <c r="C14" s="168"/>
@@ -16616,7 +16634,7 @@
         <v>442</v>
       </c>
       <c r="B20" s="207" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="C20" s="61" t="s">
         <v>465</v>
@@ -16636,7 +16654,7 @@
         <v>442</v>
       </c>
       <c r="B21" s="212" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="C21" s="20" t="s">
         <v>469</v>
@@ -16656,19 +16674,19 @@
         <v>442</v>
       </c>
       <c r="B22" s="212" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="F22" s="121" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="42" customHeight="1">
@@ -16676,7 +16694,7 @@
         <v>442</v>
       </c>
       <c r="B23" s="214" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>472</v>
@@ -16696,7 +16714,7 @@
         <v>442</v>
       </c>
       <c r="B24" s="207" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="C24" s="61" t="s">
         <v>474</v>
@@ -16716,7 +16734,7 @@
         <v>442</v>
       </c>
       <c r="B25" s="207" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="C25" s="61" t="s">
         <v>478</v>
@@ -16736,7 +16754,7 @@
         <v>442</v>
       </c>
       <c r="B26" s="207" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="C26" s="61" t="s">
         <v>482</v>
@@ -16756,19 +16774,19 @@
         <v>442</v>
       </c>
       <c r="B27" s="207" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C27" s="61" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="D27" s="61" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="E27" s="61" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F27" s="120" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="42" customHeight="1">
@@ -16776,13 +16794,13 @@
         <v>442</v>
       </c>
       <c r="B28" s="215" t="s">
+        <v>988</v>
+      </c>
+      <c r="C28" s="36" t="s">
         <v>991</v>
       </c>
-      <c r="C28" s="36" t="s">
-        <v>994</v>
-      </c>
       <c r="D28" s="36" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="E28" s="36" t="s">
         <v>61</v>
@@ -16796,13 +16814,13 @@
         <v>442</v>
       </c>
       <c r="B29" s="209" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="C29" s="33" t="s">
         <v>486</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="E29" s="33" t="s">
         <v>487</v>
@@ -16816,19 +16834,19 @@
         <v>442</v>
       </c>
       <c r="B30" s="218" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C30" s="61" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D30" s="61" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E30" s="61" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F30" s="120" t="s">
         <v>1038</v>
-      </c>
-      <c r="D30" s="61" t="s">
-        <v>1039</v>
-      </c>
-      <c r="E30" s="61" t="s">
-        <v>1040</v>
-      </c>
-      <c r="F30" s="120" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="42" customHeight="1">
@@ -16836,19 +16854,19 @@
         <v>442</v>
       </c>
       <c r="B31" s="218" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C31" s="61" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D31" s="61" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E31" s="61" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F31" s="120" t="s">
         <v>1042</v>
-      </c>
-      <c r="D31" s="61" t="s">
-        <v>1043</v>
-      </c>
-      <c r="E31" s="61" t="s">
-        <v>1044</v>
-      </c>
-      <c r="F31" s="120" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="56" customHeight="1">
@@ -16856,19 +16874,19 @@
         <v>442</v>
       </c>
       <c r="B32" s="218" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C32" s="61" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D32" s="61" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E32" s="61" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F32" s="120" t="s">
         <v>1053</v>
-      </c>
-      <c r="D32" s="61" t="s">
-        <v>1054</v>
-      </c>
-      <c r="E32" s="61" t="s">
-        <v>1055</v>
-      </c>
-      <c r="F32" s="120" t="s">
-        <v>1056</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="25.5" customHeight="1">
@@ -16876,19 +16894,19 @@
         <v>442</v>
       </c>
       <c r="B33" s="57" t="s">
+        <v>936</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>937</v>
+      </c>
+      <c r="D33" s="33" t="s">
+        <v>938</v>
+      </c>
+      <c r="E33" s="33" t="s">
         <v>939</v>
       </c>
-      <c r="C33" s="33" t="s">
+      <c r="F33" s="117" t="s">
         <v>940</v>
-      </c>
-      <c r="D33" s="33" t="s">
-        <v>941</v>
-      </c>
-      <c r="E33" s="33" t="s">
-        <v>942</v>
-      </c>
-      <c r="F33" s="117" t="s">
-        <v>943</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="30" customHeight="1">
@@ -16896,7 +16914,7 @@
         <v>442</v>
       </c>
       <c r="B34" s="64" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="C34" s="36" t="s">
         <v>488</v>
@@ -16916,7 +16934,7 @@
         <v>442</v>
       </c>
       <c r="B35" s="151" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="C35" s="10" t="s">
         <v>493</v>
@@ -16931,7 +16949,7 @@
     </row>
     <row r="36" spans="1:6" ht="25.5" customHeight="1">
       <c r="A36" s="167" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="B36" s="168"/>
       <c r="C36" s="168"/>
@@ -16964,19 +16982,19 @@
         <v>494</v>
       </c>
       <c r="B38" s="209" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C38" s="33" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D38" s="33" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E38" s="35" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F38" s="117" t="s">
         <v>1061</v>
-      </c>
-      <c r="D38" s="33" t="s">
-        <v>1062</v>
-      </c>
-      <c r="E38" s="35" t="s">
-        <v>1063</v>
-      </c>
-      <c r="F38" s="117" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="30" customHeight="1">
@@ -17104,19 +17122,19 @@
         <v>494</v>
       </c>
       <c r="B45" s="89" t="s">
+        <v>897</v>
+      </c>
+      <c r="C45" s="90" t="s">
+        <v>898</v>
+      </c>
+      <c r="D45" s="90" t="s">
+        <v>899</v>
+      </c>
+      <c r="E45" s="90" t="s">
         <v>900</v>
       </c>
-      <c r="C45" s="90" t="s">
+      <c r="F45" s="123" t="s">
         <v>901</v>
-      </c>
-      <c r="D45" s="90" t="s">
-        <v>902</v>
-      </c>
-      <c r="E45" s="90" t="s">
-        <v>903</v>
-      </c>
-      <c r="F45" s="123" t="s">
-        <v>904</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="25.5" customHeight="1">
@@ -17124,7 +17142,7 @@
         <v>494</v>
       </c>
       <c r="B46" s="57" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C46" s="33" t="s">
         <v>523</v>
@@ -17144,19 +17162,19 @@
         <v>494</v>
       </c>
       <c r="B47" s="209" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C47" s="33" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="D47" s="33" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="E47" s="35" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F47" s="117" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="42" customHeight="1">
@@ -17164,7 +17182,7 @@
         <v>494</v>
       </c>
       <c r="B48" s="63" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="C48" s="20" t="s">
         <v>527</v>
@@ -17184,13 +17202,13 @@
         <v>494</v>
       </c>
       <c r="B49" s="207" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="C49" s="61" t="s">
         <v>530</v>
       </c>
       <c r="D49" s="61" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="E49" s="61" t="s">
         <v>531</v>
@@ -17204,16 +17222,16 @@
         <v>494</v>
       </c>
       <c r="B50" s="210" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C50" s="39" t="s">
         <v>533</v>
       </c>
       <c r="D50" s="39" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="E50" s="39" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="F50" s="118" t="s">
         <v>535</v>
@@ -17224,19 +17242,19 @@
         <v>494</v>
       </c>
       <c r="B51" s="53" t="s">
+        <v>997</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>998</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>999</v>
+      </c>
+      <c r="E51" s="5" t="s">
         <v>1000</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="F51" s="86" t="s">
         <v>1001</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>1002</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>1003</v>
-      </c>
-      <c r="F51" s="86" t="s">
-        <v>1004</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="42" customHeight="1">
@@ -17244,19 +17262,19 @@
         <v>494</v>
       </c>
       <c r="B52" s="214" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E52" s="5" t="s">
         <v>1005</v>
       </c>
-      <c r="C52" s="5" t="s">
-        <v>1006</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>1007</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>1008</v>
-      </c>
       <c r="F52" s="86" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="30" customHeight="1">
@@ -17264,13 +17282,13 @@
         <v>494</v>
       </c>
       <c r="B53" s="151" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>441</v>
@@ -17284,16 +17302,16 @@
         <v>494</v>
       </c>
       <c r="B54" s="65" t="s">
+        <v>538</v>
+      </c>
+      <c r="C54" s="42" t="s">
         <v>539</v>
       </c>
-      <c r="C54" s="42" t="s">
+      <c r="D54" s="42" t="s">
         <v>540</v>
       </c>
-      <c r="D54" s="42" t="s">
+      <c r="E54" s="42" t="s">
         <v>541</v>
-      </c>
-      <c r="E54" s="42" t="s">
-        <v>542</v>
       </c>
       <c r="F54" s="124" t="s">
         <v>312</v>
@@ -17304,19 +17322,19 @@
         <v>494</v>
       </c>
       <c r="B55" s="58" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C55" s="39" t="s">
+        <v>542</v>
+      </c>
+      <c r="D55" s="39" t="s">
         <v>543</v>
       </c>
-      <c r="D55" s="39" t="s">
+      <c r="E55" s="39" t="s">
+        <v>541</v>
+      </c>
+      <c r="F55" s="118" t="s">
         <v>544</v>
-      </c>
-      <c r="E55" s="39" t="s">
-        <v>542</v>
-      </c>
-      <c r="F55" s="118" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="25.5" customHeight="1">
@@ -17324,24 +17342,24 @@
         <v>494</v>
       </c>
       <c r="B56" s="210" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C56" s="39" t="s">
+        <v>955</v>
+      </c>
+      <c r="D56" s="211" t="s">
+        <v>956</v>
+      </c>
+      <c r="E56" s="39" t="s">
+        <v>957</v>
+      </c>
+      <c r="F56" s="118" t="s">
         <v>958</v>
-      </c>
-      <c r="D56" s="211" t="s">
-        <v>959</v>
-      </c>
-      <c r="E56" s="39" t="s">
-        <v>960</v>
-      </c>
-      <c r="F56" s="118" t="s">
-        <v>961</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="25.5" customHeight="1">
       <c r="A57" s="152" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="B57" s="153"/>
       <c r="C57" s="153"/>
@@ -17351,19 +17369,19 @@
     </row>
     <row r="58" spans="1:6" ht="45" customHeight="1">
       <c r="A58" s="101" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B58" s="56" t="s">
         <v>495</v>
       </c>
       <c r="C58" s="10" t="s">
+        <v>546</v>
+      </c>
+      <c r="D58" s="10" t="s">
         <v>547</v>
       </c>
-      <c r="D58" s="10" t="s">
+      <c r="E58" s="10" t="s">
         <v>548</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>549</v>
       </c>
       <c r="F58" s="116" t="s">
         <v>28</v>
@@ -17371,76 +17389,76 @@
     </row>
     <row r="59" spans="1:6" ht="25.5" customHeight="1">
       <c r="A59" s="100" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B59" s="55" t="s">
+        <v>549</v>
+      </c>
+      <c r="C59" s="50" t="s">
         <v>550</v>
       </c>
-      <c r="C59" s="50" t="s">
+      <c r="D59" s="50" t="s">
         <v>551</v>
       </c>
-      <c r="D59" s="50" t="s">
+      <c r="E59" s="50" t="s">
         <v>552</v>
       </c>
-      <c r="E59" s="50" t="s">
+      <c r="F59" s="115" t="s">
         <v>553</v>
-      </c>
-      <c r="F59" s="115" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="30" customHeight="1">
       <c r="A60" s="100" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B60" s="55" t="s">
+        <v>554</v>
+      </c>
+      <c r="C60" s="50" t="s">
         <v>555</v>
       </c>
-      <c r="C60" s="50" t="s">
+      <c r="D60" s="50" t="s">
         <v>556</v>
       </c>
-      <c r="D60" s="50" t="s">
+      <c r="E60" s="50" t="s">
         <v>557</v>
       </c>
-      <c r="E60" s="50" t="s">
+      <c r="F60" s="115" t="s">
         <v>558</v>
-      </c>
-      <c r="F60" s="115" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="30" customHeight="1">
       <c r="A61" s="101" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B61" s="56" t="s">
+        <v>559</v>
+      </c>
+      <c r="C61" s="10" t="s">
         <v>560</v>
       </c>
-      <c r="C61" s="10" t="s">
+      <c r="D61" s="10" t="s">
         <v>561</v>
-      </c>
-      <c r="D61" s="10" t="s">
-        <v>562</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>423</v>
       </c>
       <c r="F61" s="116" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="25.5" customHeight="1">
       <c r="A62" s="99" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B62" s="54" t="s">
+        <v>563</v>
+      </c>
+      <c r="C62" s="15" t="s">
         <v>564</v>
       </c>
-      <c r="C62" s="15" t="s">
+      <c r="D62" s="25" t="s">
         <v>565</v>
-      </c>
-      <c r="D62" s="25" t="s">
-        <v>566</v>
       </c>
       <c r="E62" s="15" t="s">
         <v>166</v>
@@ -17451,16 +17469,16 @@
     </row>
     <row r="63" spans="1:6" ht="21.75" customHeight="1">
       <c r="A63" s="105" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B63" s="60" t="s">
+        <v>566</v>
+      </c>
+      <c r="C63" s="61" t="s">
         <v>567</v>
       </c>
-      <c r="C63" s="61" t="s">
+      <c r="D63" s="61" t="s">
         <v>568</v>
-      </c>
-      <c r="D63" s="61" t="s">
-        <v>569</v>
       </c>
       <c r="E63" s="61" t="s">
         <v>505</v>
@@ -17471,165 +17489,165 @@
     </row>
     <row r="64" spans="1:6" ht="25.5" customHeight="1">
       <c r="A64" s="105" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B64" s="60" t="s">
+        <v>569</v>
+      </c>
+      <c r="C64" s="61" t="s">
         <v>570</v>
       </c>
-      <c r="C64" s="61" t="s">
+      <c r="D64" s="61" t="s">
         <v>571</v>
       </c>
-      <c r="D64" s="61" t="s">
+      <c r="E64" s="61" t="s">
         <v>572</v>
       </c>
-      <c r="E64" s="61" t="s">
+      <c r="F64" s="120" t="s">
         <v>573</v>
-      </c>
-      <c r="F64" s="120" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="25.5" customHeight="1">
       <c r="A65" s="106" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B65" s="63" t="s">
+        <v>574</v>
+      </c>
+      <c r="C65" s="20" t="s">
         <v>575</v>
       </c>
-      <c r="C65" s="20" t="s">
+      <c r="D65" s="20" t="s">
         <v>576</v>
       </c>
-      <c r="D65" s="20" t="s">
+      <c r="E65" s="20" t="s">
         <v>577</v>
       </c>
-      <c r="E65" s="20" t="s">
+      <c r="F65" s="121" t="s">
         <v>578</v>
-      </c>
-      <c r="F65" s="121" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="30" customHeight="1">
       <c r="A66" s="105" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B66" s="60" t="s">
+        <v>579</v>
+      </c>
+      <c r="C66" s="61" t="s">
         <v>580</v>
       </c>
-      <c r="C66" s="61" t="s">
+      <c r="D66" s="61" t="s">
         <v>581</v>
       </c>
-      <c r="D66" s="61" t="s">
+      <c r="E66" s="61" t="s">
+        <v>572</v>
+      </c>
+      <c r="F66" s="120" t="s">
         <v>582</v>
-      </c>
-      <c r="E66" s="61" t="s">
-        <v>573</v>
-      </c>
-      <c r="F66" s="120" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="30" customHeight="1">
       <c r="A67" s="110" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B67" s="91" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="C67" s="92" t="s">
+        <v>902</v>
+      </c>
+      <c r="D67" s="92" t="s">
+        <v>903</v>
+      </c>
+      <c r="E67" s="92" t="s">
+        <v>904</v>
+      </c>
+      <c r="F67" s="125" t="s">
         <v>905</v>
-      </c>
-      <c r="D67" s="92" t="s">
-        <v>906</v>
-      </c>
-      <c r="E67" s="92" t="s">
-        <v>907</v>
-      </c>
-      <c r="F67" s="125" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="30" customHeight="1">
       <c r="A68" s="105" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B68" s="60" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C68" s="61" t="s">
+        <v>583</v>
+      </c>
+      <c r="D68" s="61" t="s">
         <v>584</v>
       </c>
-      <c r="D68" s="61" t="s">
+      <c r="E68" s="61" t="s">
         <v>585</v>
       </c>
-      <c r="E68" s="61" t="s">
+      <c r="F68" s="120" t="s">
         <v>586</v>
-      </c>
-      <c r="F68" s="120" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="25.5" customHeight="1">
       <c r="A69" s="107" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B69" s="64" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="C69" s="36" t="s">
+        <v>588</v>
+      </c>
+      <c r="D69" s="36" t="s">
         <v>589</v>
       </c>
-      <c r="D69" s="36" t="s">
+      <c r="E69" s="36" t="s">
         <v>590</v>
       </c>
-      <c r="E69" s="36" t="s">
+      <c r="F69" s="122" t="s">
         <v>591</v>
-      </c>
-      <c r="F69" s="122" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="25.5" customHeight="1">
       <c r="A70" s="109" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B70" s="65" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="C70" s="42" t="s">
+        <v>592</v>
+      </c>
+      <c r="D70" s="44" t="s">
         <v>593</v>
       </c>
-      <c r="D70" s="44" t="s">
+      <c r="E70" s="42" t="s">
         <v>594</v>
       </c>
-      <c r="E70" s="42" t="s">
+      <c r="F70" s="124" t="s">
         <v>595</v>
-      </c>
-      <c r="F70" s="124" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="30" customHeight="1">
       <c r="A71" s="101" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B71" s="128" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D71" s="10"/>
       <c r="E71" s="10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="F71" s="116" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="30" customHeight="1">
       <c r="A72" s="152" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="B72" s="153"/>
       <c r="C72" s="153"/>
@@ -17639,16 +17657,16 @@
     </row>
     <row r="73" spans="1:6" ht="30" customHeight="1">
       <c r="A73" s="101" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B73" s="56" t="s">
         <v>495</v>
       </c>
       <c r="C73" s="10" t="s">
+        <v>600</v>
+      </c>
+      <c r="D73" s="10" t="s">
         <v>601</v>
-      </c>
-      <c r="D73" s="10" t="s">
-        <v>602</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>20</v>
@@ -17659,219 +17677,219 @@
     </row>
     <row r="74" spans="1:6" ht="25.5" customHeight="1">
       <c r="A74" s="105" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B74" s="60" t="s">
+        <v>602</v>
+      </c>
+      <c r="C74" s="61" t="s">
         <v>603</v>
       </c>
-      <c r="C74" s="61" t="s">
+      <c r="D74" s="62" t="s">
         <v>604</v>
       </c>
-      <c r="D74" s="62" t="s">
+      <c r="E74" s="61" t="s">
         <v>605</v>
       </c>
-      <c r="E74" s="61" t="s">
+      <c r="F74" s="120" t="s">
         <v>606</v>
-      </c>
-      <c r="F74" s="120" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="30" customHeight="1">
       <c r="A75" s="108" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B75" s="89" t="s">
+        <v>906</v>
+      </c>
+      <c r="C75" s="90" t="s">
+        <v>907</v>
+      </c>
+      <c r="D75" s="90" t="s">
+        <v>908</v>
+      </c>
+      <c r="E75" s="90" t="s">
         <v>909</v>
       </c>
-      <c r="C75" s="90" t="s">
+      <c r="F75" s="123" t="s">
         <v>910</v>
-      </c>
-      <c r="D75" s="90" t="s">
-        <v>911</v>
-      </c>
-      <c r="E75" s="90" t="s">
-        <v>912</v>
-      </c>
-      <c r="F75" s="123" t="s">
-        <v>913</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="30" customHeight="1">
       <c r="A76" s="103" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B76" s="58" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="C76" s="39" t="s">
+        <v>607</v>
+      </c>
+      <c r="D76" s="39" t="s">
         <v>608</v>
       </c>
-      <c r="D76" s="39" t="s">
+      <c r="E76" s="39" t="s">
         <v>609</v>
       </c>
-      <c r="E76" s="39" t="s">
+      <c r="F76" s="118" t="s">
         <v>610</v>
-      </c>
-      <c r="F76" s="118" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="42" customHeight="1">
       <c r="A77" s="104" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B77" s="59" t="s">
         <v>464</v>
       </c>
       <c r="C77" s="47" t="s">
+        <v>611</v>
+      </c>
+      <c r="D77" s="47" t="s">
         <v>612</v>
       </c>
-      <c r="D77" s="47" t="s">
+      <c r="E77" s="47" t="s">
         <v>613</v>
       </c>
-      <c r="E77" s="47" t="s">
+      <c r="F77" s="119" t="s">
         <v>614</v>
-      </c>
-      <c r="F77" s="119" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="25.5" customHeight="1">
       <c r="A78" s="105" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B78" s="60" t="s">
+        <v>615</v>
+      </c>
+      <c r="C78" s="61" t="s">
         <v>616</v>
       </c>
-      <c r="C78" s="61" t="s">
+      <c r="D78" s="61" t="s">
         <v>617</v>
       </c>
-      <c r="D78" s="61" t="s">
+      <c r="E78" s="61" t="s">
         <v>618</v>
       </c>
-      <c r="E78" s="61" t="s">
+      <c r="F78" s="120" t="s">
         <v>619</v>
-      </c>
-      <c r="F78" s="120" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="30" customHeight="1">
       <c r="A79" s="98" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B79" s="53" t="s">
+        <v>620</v>
+      </c>
+      <c r="C79" s="5" t="s">
         <v>621</v>
       </c>
-      <c r="C79" s="5" t="s">
+      <c r="D79" s="5" t="s">
         <v>622</v>
       </c>
-      <c r="D79" s="5" t="s">
+      <c r="E79" s="5" t="s">
         <v>623</v>
       </c>
-      <c r="E79" s="5" t="s">
+      <c r="F79" s="86" t="s">
         <v>624</v>
-      </c>
-      <c r="F79" s="86" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="30" customHeight="1">
       <c r="A80" s="103" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B80" s="58" t="s">
+        <v>625</v>
+      </c>
+      <c r="C80" s="39" t="s">
         <v>626</v>
       </c>
-      <c r="C80" s="39" t="s">
+      <c r="D80" s="39" t="s">
         <v>627</v>
       </c>
-      <c r="D80" s="39" t="s">
+      <c r="E80" s="39" t="s">
         <v>628</v>
       </c>
-      <c r="E80" s="39" t="s">
+      <c r="F80" s="118" t="s">
         <v>629</v>
-      </c>
-      <c r="F80" s="118" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="42" customHeight="1">
       <c r="A81" s="105" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B81" s="60" t="s">
+        <v>630</v>
+      </c>
+      <c r="C81" s="61" t="s">
         <v>631</v>
       </c>
-      <c r="C81" s="61" t="s">
+      <c r="D81" s="61" t="s">
         <v>632</v>
       </c>
-      <c r="D81" s="61" t="s">
+      <c r="E81" s="61" t="s">
         <v>633</v>
       </c>
-      <c r="E81" s="61" t="s">
+      <c r="F81" s="120" t="s">
         <v>634</v>
-      </c>
-      <c r="F81" s="120" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="30" customHeight="1">
       <c r="A82" s="104" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B82" s="59" t="s">
+        <v>635</v>
+      </c>
+      <c r="C82" s="47" t="s">
         <v>636</v>
       </c>
-      <c r="C82" s="47" t="s">
+      <c r="D82" s="47" t="s">
         <v>637</v>
       </c>
-      <c r="D82" s="47" t="s">
+      <c r="E82" s="47" t="s">
+        <v>628</v>
+      </c>
+      <c r="F82" s="119" t="s">
         <v>638</v>
-      </c>
-      <c r="E82" s="47" t="s">
-        <v>629</v>
-      </c>
-      <c r="F82" s="119" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="21.75" customHeight="1">
       <c r="A83" s="106" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B83" s="63" t="s">
+        <v>639</v>
+      </c>
+      <c r="C83" s="20" t="s">
         <v>640</v>
       </c>
-      <c r="C83" s="20" t="s">
+      <c r="D83" s="20" t="s">
         <v>641</v>
       </c>
-      <c r="D83" s="20" t="s">
+      <c r="E83" s="20" t="s">
         <v>642</v>
       </c>
-      <c r="E83" s="20" t="s">
+      <c r="F83" s="121" t="s">
         <v>643</v>
-      </c>
-      <c r="F83" s="121" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="42" customHeight="1">
       <c r="A84" s="102" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B84" s="57" t="s">
+        <v>644</v>
+      </c>
+      <c r="C84" s="33" t="s">
         <v>645</v>
       </c>
-      <c r="C84" s="33" t="s">
+      <c r="D84" s="33" t="s">
         <v>646</v>
       </c>
-      <c r="D84" s="33" t="s">
+      <c r="E84" s="33" t="s">
         <v>647</v>
-      </c>
-      <c r="E84" s="33" t="s">
-        <v>648</v>
       </c>
       <c r="F84" s="117" t="s">
         <v>33</v>
@@ -17879,36 +17897,36 @@
     </row>
     <row r="85" spans="1:6" ht="25.5" customHeight="1">
       <c r="A85" s="102" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B85" s="209" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C85" s="33" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="D85" s="33" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="E85" s="33" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F85" s="117" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="25.5" customHeight="1">
       <c r="A86" s="107" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B86" s="64" t="s">
         <v>536</v>
       </c>
       <c r="C86" s="36" t="s">
+        <v>648</v>
+      </c>
+      <c r="D86" s="36" t="s">
         <v>649</v>
-      </c>
-      <c r="D86" s="36" t="s">
-        <v>650</v>
       </c>
       <c r="E86" s="36" t="s">
         <v>209</v>
@@ -17919,16 +17937,16 @@
     </row>
     <row r="87" spans="1:6" ht="30" customHeight="1">
       <c r="A87" s="101" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B87" s="56" t="s">
+        <v>650</v>
+      </c>
+      <c r="C87" s="10" t="s">
         <v>651</v>
       </c>
-      <c r="C87" s="10" t="s">
+      <c r="D87" s="10" t="s">
         <v>652</v>
-      </c>
-      <c r="D87" s="10" t="s">
-        <v>653</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>534</v>
@@ -17939,127 +17957,127 @@
     </row>
     <row r="88" spans="1:6" ht="25.5" customHeight="1">
       <c r="A88" s="101" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B88" s="56" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C88" s="10" t="s">
+        <v>653</v>
+      </c>
+      <c r="D88" s="10" t="s">
         <v>654</v>
       </c>
-      <c r="D88" s="10" t="s">
-        <v>655</v>
-      </c>
       <c r="E88" s="10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="F88" s="116" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="42" customHeight="1">
       <c r="A89" s="103" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B89" s="58" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C89" s="39" t="s">
+        <v>655</v>
+      </c>
+      <c r="D89" s="39" t="s">
         <v>656</v>
       </c>
-      <c r="D89" s="39" t="s">
+      <c r="E89" s="39" t="s">
+        <v>541</v>
+      </c>
+      <c r="F89" s="118" t="s">
         <v>657</v>
-      </c>
-      <c r="E89" s="39" t="s">
-        <v>542</v>
-      </c>
-      <c r="F89" s="118" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="30" customHeight="1">
       <c r="A90" s="103" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B90" s="58" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C90" s="39" t="s">
+        <v>658</v>
+      </c>
+      <c r="D90" s="39" t="s">
         <v>659</v>
       </c>
-      <c r="D90" s="39" t="s">
+      <c r="E90" s="39" t="s">
+        <v>541</v>
+      </c>
+      <c r="F90" s="118" t="s">
         <v>660</v>
-      </c>
-      <c r="E90" s="39" t="s">
-        <v>542</v>
-      </c>
-      <c r="F90" s="118" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="25.5" customHeight="1">
       <c r="A91" s="103" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B91" s="58" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C91" s="39" t="s">
+        <v>661</v>
+      </c>
+      <c r="D91" s="39" t="s">
         <v>662</v>
       </c>
-      <c r="D91" s="39" t="s">
+      <c r="E91" s="39" t="s">
+        <v>541</v>
+      </c>
+      <c r="F91" s="118" t="s">
         <v>663</v>
-      </c>
-      <c r="E91" s="39" t="s">
-        <v>542</v>
-      </c>
-      <c r="F91" s="118" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="25.5" customHeight="1">
       <c r="A92" s="108" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B92" s="89" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C92" s="90" t="s">
+        <v>911</v>
+      </c>
+      <c r="D92" s="95" t="s">
+        <v>912</v>
+      </c>
+      <c r="E92" s="90" t="s">
+        <v>913</v>
+      </c>
+      <c r="F92" s="123" t="s">
         <v>914</v>
-      </c>
-      <c r="D92" s="95" t="s">
-        <v>915</v>
-      </c>
-      <c r="E92" s="90" t="s">
-        <v>916</v>
-      </c>
-      <c r="F92" s="123" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="30" customHeight="1">
       <c r="A93" s="108" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B93" s="208" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C93" s="90" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="D93" s="95" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="E93" s="90" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="F93" s="123" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="30" customHeight="1">
       <c r="A94" s="155" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="B94" s="156"/>
       <c r="C94" s="156"/>
@@ -18069,17 +18087,17 @@
     </row>
     <row r="95" spans="1:6" ht="42" customHeight="1">
       <c r="A95" s="101" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B95" s="56" t="s">
         <v>495</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D95" s="10"/>
       <c r="E95" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F95" s="116" t="s">
         <v>33</v>
@@ -18087,76 +18105,76 @@
     </row>
     <row r="96" spans="1:6" ht="25.5" customHeight="1">
       <c r="A96" s="100" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B96" s="55" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C96" s="50" t="s">
+        <v>666</v>
+      </c>
+      <c r="D96" s="50" t="s">
         <v>667</v>
       </c>
-      <c r="D96" s="50" t="s">
+      <c r="E96" s="50" t="s">
+        <v>552</v>
+      </c>
+      <c r="F96" s="115" t="s">
         <v>668</v>
-      </c>
-      <c r="E96" s="50" t="s">
-        <v>553</v>
-      </c>
-      <c r="F96" s="115" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="45" customHeight="1">
       <c r="A97" s="100" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B97" s="55" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C97" s="50" t="s">
+        <v>669</v>
+      </c>
+      <c r="D97" s="50" t="s">
         <v>670</v>
       </c>
-      <c r="D97" s="50" t="s">
+      <c r="E97" s="50" t="s">
+        <v>557</v>
+      </c>
+      <c r="F97" s="115" t="s">
         <v>671</v>
-      </c>
-      <c r="E97" s="50" t="s">
-        <v>558</v>
-      </c>
-      <c r="F97" s="115" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="30" customHeight="1">
       <c r="A98" s="101" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B98" s="56" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C98" s="10" t="s">
+        <v>672</v>
+      </c>
+      <c r="D98" s="10" t="s">
         <v>673</v>
       </c>
-      <c r="D98" s="10" t="s">
+      <c r="E98" s="10" t="s">
         <v>674</v>
       </c>
-      <c r="E98" s="10" t="s">
+      <c r="F98" s="116" t="s">
         <v>675</v>
-      </c>
-      <c r="F98" s="116" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="21.75" customHeight="1">
       <c r="A99" s="99" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B99" s="54" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C99" s="15" t="s">
+        <v>676</v>
+      </c>
+      <c r="D99" s="15" t="s">
         <v>677</v>
-      </c>
-      <c r="D99" s="15" t="s">
-        <v>678</v>
       </c>
       <c r="E99" s="15" t="s">
         <v>219</v>
@@ -18167,79 +18185,79 @@
     </row>
     <row r="100" spans="1:6" ht="25.5" customHeight="1">
       <c r="A100" s="105" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B100" s="60" t="s">
+        <v>678</v>
+      </c>
+      <c r="C100" s="61" t="s">
         <v>679</v>
       </c>
-      <c r="C100" s="61" t="s">
+      <c r="D100" s="61" t="s">
         <v>680</v>
       </c>
-      <c r="D100" s="61" t="s">
+      <c r="E100" s="61" t="s">
         <v>681</v>
       </c>
-      <c r="E100" s="61" t="s">
+      <c r="F100" s="120" t="s">
         <v>682</v>
-      </c>
-      <c r="F100" s="120" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="42" customHeight="1">
       <c r="A101" s="105" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B101" s="60" t="s">
+        <v>683</v>
+      </c>
+      <c r="C101" s="61" t="s">
         <v>684</v>
       </c>
-      <c r="C101" s="61" t="s">
+      <c r="D101" s="61" t="s">
         <v>685</v>
       </c>
-      <c r="D101" s="61" t="s">
+      <c r="E101" s="61" t="s">
+        <v>605</v>
+      </c>
+      <c r="F101" s="120" t="s">
         <v>686</v>
-      </c>
-      <c r="E101" s="61" t="s">
-        <v>606</v>
-      </c>
-      <c r="F101" s="120" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="30" customHeight="1">
       <c r="A102" s="105" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B102" s="60" t="s">
+        <v>687</v>
+      </c>
+      <c r="C102" s="61" t="s">
         <v>688</v>
       </c>
-      <c r="C102" s="61" t="s">
+      <c r="D102" s="61" t="s">
         <v>689</v>
       </c>
-      <c r="D102" s="61" t="s">
+      <c r="E102" s="61" t="s">
         <v>690</v>
       </c>
-      <c r="E102" s="61" t="s">
+      <c r="F102" s="120" t="s">
         <v>691</v>
-      </c>
-      <c r="F102" s="120" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="45" customHeight="1">
       <c r="A103" s="106" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B103" s="63" t="s">
+        <v>692</v>
+      </c>
+      <c r="C103" s="20" t="s">
         <v>693</v>
       </c>
-      <c r="C103" s="20" t="s">
+      <c r="D103" s="20" t="s">
         <v>694</v>
       </c>
-      <c r="D103" s="20" t="s">
+      <c r="E103" s="20" t="s">
         <v>695</v>
-      </c>
-      <c r="E103" s="20" t="s">
-        <v>696</v>
       </c>
       <c r="F103" s="121" t="s">
         <v>271</v>
@@ -18247,16 +18265,16 @@
     </row>
     <row r="104" spans="1:6" ht="25.5" customHeight="1">
       <c r="A104" s="105" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B104" s="60" t="s">
+        <v>696</v>
+      </c>
+      <c r="C104" s="61" t="s">
         <v>697</v>
       </c>
-      <c r="C104" s="61" t="s">
+      <c r="D104" s="61" t="s">
         <v>698</v>
-      </c>
-      <c r="D104" s="61" t="s">
-        <v>699</v>
       </c>
       <c r="E104" s="61" t="s">
         <v>111</v>
@@ -18267,19 +18285,19 @@
     </row>
     <row r="105" spans="1:6" ht="42" customHeight="1">
       <c r="A105" s="105" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B105" s="207" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C105" s="61" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="D105" s="61" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="E105" s="61" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F105" s="120" t="s">
         <v>271</v>
@@ -18287,39 +18305,39 @@
     </row>
     <row r="106" spans="1:6" ht="42" customHeight="1">
       <c r="A106" s="109" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B106" s="65" t="s">
+        <v>699</v>
+      </c>
+      <c r="C106" s="42" t="s">
         <v>700</v>
       </c>
-      <c r="C106" s="42" t="s">
+      <c r="D106" s="42" t="s">
         <v>701</v>
       </c>
-      <c r="D106" s="42" t="s">
+      <c r="E106" s="42" t="s">
         <v>702</v>
       </c>
-      <c r="E106" s="42" t="s">
+      <c r="F106" s="124" t="s">
         <v>703</v>
-      </c>
-      <c r="F106" s="124" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="30" customHeight="1">
       <c r="A107" s="111" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B107" s="93" t="s">
+        <v>915</v>
+      </c>
+      <c r="C107" s="94" t="s">
+        <v>916</v>
+      </c>
+      <c r="D107" s="94" t="s">
+        <v>917</v>
+      </c>
+      <c r="E107" s="94" t="s">
         <v>918</v>
-      </c>
-      <c r="C107" s="94" t="s">
-        <v>919</v>
-      </c>
-      <c r="D107" s="94" t="s">
-        <v>920</v>
-      </c>
-      <c r="E107" s="94" t="s">
-        <v>921</v>
       </c>
       <c r="F107" s="126" t="s">
         <v>278</v>
@@ -18327,34 +18345,34 @@
     </row>
     <row r="108" spans="1:6" ht="25.5" customHeight="1">
       <c r="A108" s="101" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B108" s="128" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="D108" s="10"/>
       <c r="E108" s="10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="F108" s="116" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="25.5" customHeight="1">
       <c r="A109" s="102" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B109" s="57" t="s">
+        <v>704</v>
+      </c>
+      <c r="C109" s="33" t="s">
         <v>705</v>
       </c>
-      <c r="C109" s="33" t="s">
+      <c r="D109" s="33" t="s">
         <v>706</v>
-      </c>
-      <c r="D109" s="33" t="s">
-        <v>707</v>
       </c>
       <c r="E109" s="33" t="s">
         <v>534</v>
@@ -18365,27 +18383,27 @@
     </row>
     <row r="110" spans="1:6" ht="30" customHeight="1">
       <c r="A110" s="103" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B110" s="58" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C110" s="39" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="D110" s="39" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="E110" s="39" t="s">
         <v>534</v>
       </c>
       <c r="F110" s="118" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="25.5" customHeight="1">
       <c r="A111" s="155" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="B111" s="156"/>
       <c r="C111" s="156"/>
@@ -18395,16 +18413,16 @@
     </row>
     <row r="112" spans="1:6" ht="42" customHeight="1">
       <c r="A112" s="101" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B112" s="56" t="s">
         <v>495</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>20</v>
@@ -18415,59 +18433,59 @@
     </row>
     <row r="113" spans="1:6" ht="45" customHeight="1">
       <c r="A113" s="105" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B113" s="60" t="s">
         <v>497</v>
       </c>
       <c r="C113" s="61" t="s">
+        <v>709</v>
+      </c>
+      <c r="D113" s="61" t="s">
         <v>710</v>
-      </c>
-      <c r="D113" s="61" t="s">
-        <v>711</v>
       </c>
       <c r="E113" s="61" t="s">
         <v>500</v>
       </c>
       <c r="F113" s="120" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="25.5" customHeight="1">
       <c r="A114" s="105" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B114" s="60" t="s">
+        <v>712</v>
+      </c>
+      <c r="C114" s="61" t="s">
         <v>713</v>
       </c>
-      <c r="C114" s="61" t="s">
+      <c r="D114" s="61" t="s">
         <v>714</v>
       </c>
-      <c r="D114" s="61" t="s">
+      <c r="E114" s="61" t="s">
         <v>715</v>
       </c>
-      <c r="E114" s="61" t="s">
+      <c r="F114" s="120" t="s">
         <v>716</v>
-      </c>
-      <c r="F114" s="120" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="21.75" customHeight="1">
       <c r="A115" s="105" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B115" s="60" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C115" s="61" t="s">
+        <v>717</v>
+      </c>
+      <c r="D115" s="61" t="s">
         <v>718</v>
       </c>
-      <c r="D115" s="61" t="s">
+      <c r="E115" s="61" t="s">
         <v>719</v>
-      </c>
-      <c r="E115" s="61" t="s">
-        <v>720</v>
       </c>
       <c r="F115" s="120" t="s">
         <v>363</v>
@@ -18475,39 +18493,39 @@
     </row>
     <row r="116" spans="1:6" ht="25.5" customHeight="1">
       <c r="A116" s="105" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B116" s="207" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C116" s="61" t="s">
+        <v>943</v>
+      </c>
+      <c r="D116" s="61" t="s">
+        <v>944</v>
+      </c>
+      <c r="E116" s="61" t="s">
+        <v>945</v>
+      </c>
+      <c r="F116" s="120" t="s">
         <v>946</v>
-      </c>
-      <c r="D116" s="61" t="s">
-        <v>947</v>
-      </c>
-      <c r="E116" s="61" t="s">
-        <v>948</v>
-      </c>
-      <c r="F116" s="120" t="s">
-        <v>949</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="25.5" customHeight="1">
       <c r="A117" s="98" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B117" s="53" t="s">
+        <v>720</v>
+      </c>
+      <c r="C117" s="5" t="s">
         <v>721</v>
       </c>
-      <c r="C117" s="5" t="s">
+      <c r="D117" s="5" t="s">
         <v>722</v>
       </c>
-      <c r="D117" s="5" t="s">
+      <c r="E117" s="5" t="s">
         <v>723</v>
-      </c>
-      <c r="E117" s="5" t="s">
-        <v>724</v>
       </c>
       <c r="F117" s="86" t="s">
         <v>113</v>
@@ -18515,19 +18533,19 @@
     </row>
     <row r="118" spans="1:6" ht="30" customHeight="1">
       <c r="A118" s="102" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B118" s="57" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C118" s="33" t="s">
+        <v>724</v>
+      </c>
+      <c r="D118" s="33" t="s">
         <v>725</v>
       </c>
-      <c r="D118" s="33" t="s">
+      <c r="E118" s="33" t="s">
         <v>726</v>
-      </c>
-      <c r="E118" s="33" t="s">
-        <v>727</v>
       </c>
       <c r="F118" s="117" t="s">
         <v>277</v>
@@ -18535,36 +18553,36 @@
     </row>
     <row r="119" spans="1:6" ht="25.5" customHeight="1">
       <c r="A119" s="105" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B119" s="60" t="s">
+        <v>727</v>
+      </c>
+      <c r="C119" s="61" t="s">
         <v>728</v>
       </c>
-      <c r="C119" s="61" t="s">
+      <c r="D119" s="61" t="s">
         <v>729</v>
-      </c>
-      <c r="D119" s="61" t="s">
-        <v>730</v>
       </c>
       <c r="E119" s="61" t="s">
         <v>480</v>
       </c>
       <c r="F119" s="120" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="30" customHeight="1">
       <c r="A120" s="106" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B120" s="63" t="s">
+        <v>731</v>
+      </c>
+      <c r="C120" s="20" t="s">
         <v>732</v>
       </c>
-      <c r="C120" s="20" t="s">
+      <c r="D120" s="20" t="s">
         <v>733</v>
-      </c>
-      <c r="D120" s="20" t="s">
-        <v>734</v>
       </c>
       <c r="E120" s="20" t="s">
         <v>529</v>
@@ -18575,99 +18593,99 @@
     </row>
     <row r="121" spans="1:6" ht="25.5" customHeight="1">
       <c r="A121" s="109" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B121" s="65" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C121" s="42" t="s">
+        <v>734</v>
+      </c>
+      <c r="D121" s="42" t="s">
         <v>735</v>
       </c>
-      <c r="D121" s="42" t="s">
+      <c r="E121" s="42" t="s">
         <v>736</v>
-      </c>
-      <c r="E121" s="42" t="s">
-        <v>737</v>
       </c>
       <c r="F121" s="124" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="25.5" customHeight="1">
+    <row r="122" spans="1:6" ht="110" customHeight="1">
       <c r="A122" s="99" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B122" s="54" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>739</v>
+        <v>1066</v>
       </c>
       <c r="D122" s="15" t="s">
-        <v>740</v>
+        <v>1067</v>
       </c>
       <c r="E122" s="15" t="s">
-        <v>537</v>
+        <v>1068</v>
       </c>
       <c r="F122" s="85" t="s">
-        <v>131</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="42" customHeight="1">
       <c r="A123" s="103" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B123" s="58" t="s">
+        <v>738</v>
+      </c>
+      <c r="C123" s="39" t="s">
+        <v>739</v>
+      </c>
+      <c r="D123" s="39" t="s">
+        <v>740</v>
+      </c>
+      <c r="E123" s="39" t="s">
         <v>741</v>
       </c>
-      <c r="C123" s="39" t="s">
-        <v>742</v>
-      </c>
-      <c r="D123" s="39" t="s">
-        <v>743</v>
-      </c>
-      <c r="E123" s="39" t="s">
-        <v>744</v>
-      </c>
       <c r="F123" s="118" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="30" customHeight="1">
       <c r="A124" s="101" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B124" s="56" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="D124" s="10" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="E124" s="10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="F124" s="116" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="28">
       <c r="A125" s="103" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B125" s="58" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C125" s="39" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="D125" s="39" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="E125" s="39" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F125" s="118" t="s">
         <v>351</v>
@@ -18675,47 +18693,47 @@
     </row>
     <row r="126" spans="1:6" ht="28">
       <c r="A126" s="103" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B126" s="58" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C126" s="39" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="D126" s="39" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="E126" s="39" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F126" s="118" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="31">
       <c r="A127" s="104" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B127" s="59" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C127" s="47" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="D127" s="47" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="E127" s="47" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F127" s="119" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="158" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="B128" s="159"/>
       <c r="C128" s="159"/>
@@ -18725,19 +18743,19 @@
     </row>
     <row r="129" spans="1:6" ht="28">
       <c r="A129" s="101" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B129" s="56" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F129" s="116" t="s">
         <v>37</v>
@@ -18745,39 +18763,39 @@
     </row>
     <row r="130" spans="1:6" ht="28">
       <c r="A130" s="100" t="s">
+        <v>752</v>
+      </c>
+      <c r="B130" s="55" t="s">
         <v>755</v>
       </c>
-      <c r="B130" s="55" t="s">
+      <c r="C130" s="50" t="s">
+        <v>756</v>
+      </c>
+      <c r="D130" s="50" t="s">
+        <v>757</v>
+      </c>
+      <c r="E130" s="50" t="s">
+        <v>674</v>
+      </c>
+      <c r="F130" s="115" t="s">
         <v>758</v>
-      </c>
-      <c r="C130" s="50" t="s">
-        <v>759</v>
-      </c>
-      <c r="D130" s="50" t="s">
-        <v>760</v>
-      </c>
-      <c r="E130" s="50" t="s">
-        <v>675</v>
-      </c>
-      <c r="F130" s="115" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="28">
       <c r="A131" s="100" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B131" s="55" t="s">
+        <v>759</v>
+      </c>
+      <c r="C131" s="50" t="s">
+        <v>760</v>
+      </c>
+      <c r="D131" s="50" t="s">
+        <v>761</v>
+      </c>
+      <c r="E131" s="50" t="s">
         <v>762</v>
-      </c>
-      <c r="C131" s="50" t="s">
-        <v>763</v>
-      </c>
-      <c r="D131" s="50" t="s">
-        <v>764</v>
-      </c>
-      <c r="E131" s="50" t="s">
-        <v>765</v>
       </c>
       <c r="F131" s="115" t="s">
         <v>406</v>
@@ -18785,99 +18803,99 @@
     </row>
     <row r="132" spans="1:6" ht="28">
       <c r="A132" s="100" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B132" s="55" t="s">
+        <v>763</v>
+      </c>
+      <c r="C132" s="50" t="s">
+        <v>764</v>
+      </c>
+      <c r="D132" s="50" t="s">
+        <v>765</v>
+      </c>
+      <c r="E132" s="50" t="s">
         <v>766</v>
       </c>
-      <c r="C132" s="50" t="s">
+      <c r="F132" s="115" t="s">
         <v>767</v>
-      </c>
-      <c r="D132" s="50" t="s">
-        <v>768</v>
-      </c>
-      <c r="E132" s="50" t="s">
-        <v>769</v>
-      </c>
-      <c r="F132" s="115" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="28">
       <c r="A133" s="99" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B133" s="54" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="D133" s="15" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="E133" s="15" t="s">
         <v>405</v>
       </c>
       <c r="F133" s="85" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="28">
       <c r="A134" s="98" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B134" s="53" t="s">
+        <v>771</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>772</v>
+      </c>
+      <c r="D134" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="E134" s="5" t="s">
         <v>774</v>
       </c>
-      <c r="C134" s="5" t="s">
-        <v>775</v>
-      </c>
-      <c r="D134" s="5" t="s">
-        <v>776</v>
-      </c>
-      <c r="E134" s="5" t="s">
-        <v>777</v>
-      </c>
       <c r="F134" s="114" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="28">
       <c r="A135" s="99" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B135" s="54" t="s">
+        <v>775</v>
+      </c>
+      <c r="C135" s="15" t="s">
+        <v>776</v>
+      </c>
+      <c r="D135" s="15" t="s">
+        <v>777</v>
+      </c>
+      <c r="E135" s="15" t="s">
         <v>778</v>
       </c>
-      <c r="C135" s="15" t="s">
-        <v>779</v>
-      </c>
-      <c r="D135" s="15" t="s">
-        <v>780</v>
-      </c>
-      <c r="E135" s="15" t="s">
-        <v>781</v>
-      </c>
       <c r="F135" s="113" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="28">
       <c r="A136" s="98" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B136" s="53" t="s">
+        <v>779</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>780</v>
+      </c>
+      <c r="D136" s="5" t="s">
+        <v>781</v>
+      </c>
+      <c r="E136" s="5" t="s">
         <v>782</v>
-      </c>
-      <c r="C136" s="5" t="s">
-        <v>783</v>
-      </c>
-      <c r="D136" s="5" t="s">
-        <v>784</v>
-      </c>
-      <c r="E136" s="5" t="s">
-        <v>785</v>
       </c>
       <c r="F136" s="114" t="s">
         <v>254</v>
@@ -18885,22 +18903,22 @@
     </row>
     <row r="137" spans="1:6" ht="29" thickBot="1">
       <c r="A137" s="112" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B137" s="96" t="s">
         <v>492</v>
       </c>
       <c r="C137" s="97" t="s">
+        <v>783</v>
+      </c>
+      <c r="D137" s="97" t="s">
+        <v>784</v>
+      </c>
+      <c r="E137" s="97" t="s">
+        <v>785</v>
+      </c>
+      <c r="F137" s="127" t="s">
         <v>786</v>
-      </c>
-      <c r="D137" s="97" t="s">
-        <v>787</v>
-      </c>
-      <c r="E137" s="97" t="s">
-        <v>788</v>
-      </c>
-      <c r="F137" s="127" t="s">
-        <v>789</v>
       </c>
     </row>
   </sheetData>
@@ -18926,7 +18944,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -19027,7 +19045,7 @@
         <v>62</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>64</v>
@@ -19044,13 +19062,13 @@
         <v>53</v>
       </c>
       <c r="B9" s="69" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="C9" s="67" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="E9" s="68" t="s">
         <v>184</v>
@@ -19061,13 +19079,13 @@
         <v>53</v>
       </c>
       <c r="B10" s="69" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="C10" s="67" t="s">
         <v>206</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="E10" s="68" t="s">
         <v>61</v>
@@ -19112,30 +19130,30 @@
         <v>67</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="42" customHeight="1">
       <c r="A14" s="20" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="E14" s="23" t="s">
         <v>71</v>
@@ -19143,19 +19161,19 @@
     </row>
     <row r="15" spans="1:5" ht="56" customHeight="1">
       <c r="A15" s="20" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E15" s="23" t="s">
         <v>1057</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>1058</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>1056</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>1059</v>
-      </c>
-      <c r="E15" s="23" t="s">
-        <v>1060</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="70" customHeight="1">
@@ -19163,16 +19181,16 @@
         <v>90</v>
       </c>
       <c r="B16" s="20" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E16" s="23" t="s">
         <v>1065</v>
-      </c>
-      <c r="C16" s="22" t="s">
-        <v>1066</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>1067</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>1068</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" customHeight="1"/>
@@ -19292,13 +19310,13 @@
         <v>90</v>
       </c>
       <c r="B25" s="66" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C25" s="67" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="D25" s="66" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="E25" s="68" t="s">
         <v>234</v>
@@ -19489,13 +19507,13 @@
         <v>67</v>
       </c>
       <c r="B38" s="73" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="C38" s="71" t="s">
         <v>271</v>
       </c>
       <c r="D38" s="70" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="E38" s="72" t="s">
         <v>103</v>
@@ -19516,6 +19534,23 @@
       </c>
       <c r="E39" s="23" t="s">
         <v>103</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="110" customHeight="1">
+      <c r="A40" s="20" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C40" s="22" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D40" s="20" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E40" s="23" t="s">
+        <v>1074</v>
       </c>
     </row>
   </sheetData>
@@ -19548,7 +19583,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
       <c r="A1" s="191" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="B1" s="192"/>
       <c r="C1" s="192"/>
@@ -19558,7 +19593,7 @@
     </row>
     <row r="2" spans="1:6" ht="45" customHeight="1">
       <c r="A2" s="194" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="B2" s="195"/>
       <c r="C2" s="195"/>
@@ -19658,19 +19693,19 @@
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1">
       <c r="A8" s="81" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="B8" s="75">
         <v>4.5</v>
       </c>
       <c r="C8" s="76" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="D8" s="75" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="E8" s="76" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="F8" s="87" t="s">
         <v>152</v>
@@ -19678,19 +19713,19 @@
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1">
       <c r="A9" s="82" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B9" s="68">
         <v>4.5</v>
       </c>
       <c r="C9" s="66" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="D9" s="68" t="s">
         <v>107</v>
       </c>
       <c r="E9" s="66" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="F9" s="88" t="s">
         <v>152</v>
@@ -19720,7 +19755,7 @@
         <v>57</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="F11" s="84" t="s">
         <v>164</v>
@@ -19768,59 +19803,59 @@
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1">
       <c r="A14" s="81" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="B14" s="75">
         <v>4.8</v>
       </c>
       <c r="C14" s="76" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="D14" s="75" t="s">
         <v>66</v>
       </c>
       <c r="E14" s="76" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="F14" s="87" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="30" customHeight="1">
       <c r="A15" s="82" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B15" s="68">
         <v>4.5999999999999996</v>
       </c>
       <c r="C15" s="66" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="D15" s="68" t="s">
         <v>111</v>
       </c>
       <c r="E15" s="66" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="F15" s="88" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="30" customHeight="1">
       <c r="A16" s="82" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="B16" s="216" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="C16" s="66" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="D16" s="68" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="E16" s="66" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="F16" s="88" t="s">
         <v>477</v>
@@ -19828,22 +19863,22 @@
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1">
       <c r="A17" s="82" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="B17" s="216" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="C17" s="66" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="D17" s="68" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="E17" s="66" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="F17" s="88" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
@@ -19924,13 +19959,13 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C22" s="76" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="D22" s="75" t="s">
         <v>256</v>
       </c>
       <c r="E22" s="76" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="F22" s="87" t="s">
         <v>301</v>
@@ -19938,22 +19973,22 @@
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1">
       <c r="A23" s="82" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="B23" s="68">
         <v>4.3</v>
       </c>
       <c r="C23" s="66" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D23" s="68" t="s">
         <v>256</v>
       </c>
       <c r="E23" s="66" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="F23" s="88" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1">
@@ -20028,42 +20063,42 @@
     </row>
     <row r="28" spans="1:6" ht="19.5" customHeight="1">
       <c r="A28" s="81" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="B28" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C28" s="76" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="D28" s="75" t="s">
         <v>160</v>
       </c>
       <c r="E28" s="76" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="F28" s="87" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="30" customHeight="1">
       <c r="A29" s="82" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B29" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C29" s="66" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="D29" s="68" t="s">
         <v>219</v>
       </c>
       <c r="E29" s="66" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="F29" s="88" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="30" customHeight="1">
@@ -20124,33 +20159,33 @@
         <v>4.3</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="F33" s="86" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="19.5" customHeight="1">
       <c r="A34" s="81" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="B34" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C34" s="76" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="D34" s="75" t="s">
         <v>166</v>
       </c>
       <c r="E34" s="76" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="F34" s="87" t="s">
         <v>206</v>
@@ -20158,22 +20193,22 @@
     </row>
     <row r="35" spans="1:6" ht="30" customHeight="1">
       <c r="A35" s="82" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B35" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C35" s="66" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="D35" s="68" t="s">
         <v>61</v>
       </c>
       <c r="E35" s="66" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="F35" s="88" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="30" customHeight="1">
@@ -20194,16 +20229,16 @@
         <v>4.5</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="D37" s="27" t="s">
         <v>219</v>
       </c>
       <c r="E37" s="28" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="F37" s="84" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="30" customHeight="1">
@@ -20248,19 +20283,19 @@
     </row>
     <row r="40" spans="1:6" ht="19.5" customHeight="1">
       <c r="A40" s="81" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="B40" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C40" s="76" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="D40" s="75" t="s">
         <v>215</v>
       </c>
       <c r="E40" s="76" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="F40" s="87" t="s">
         <v>92</v>
@@ -20268,19 +20303,19 @@
     </row>
     <row r="41" spans="1:6" ht="30" customHeight="1">
       <c r="A41" s="82" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B41" s="68">
         <v>4.3</v>
       </c>
       <c r="C41" s="66" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="D41" s="68" t="s">
         <v>223</v>
       </c>
       <c r="E41" s="66" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="F41" s="88" t="s">
         <v>92</v>
@@ -20358,19 +20393,19 @@
     </row>
     <row r="46" spans="1:6" ht="19.5" customHeight="1">
       <c r="A46" s="81" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="B46" s="75">
         <v>4.5</v>
       </c>
       <c r="C46" s="76" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="D46" s="75" t="s">
         <v>89</v>
       </c>
       <c r="E46" s="76" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="F46" s="87" t="s">
         <v>225</v>
@@ -20378,22 +20413,22 @@
     </row>
     <row r="47" spans="1:6" ht="30" customHeight="1">
       <c r="A47" s="82" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B47" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C47" s="66" t="s">
+        <v>817</v>
+      </c>
+      <c r="D47" s="68" t="s">
+        <v>818</v>
+      </c>
+      <c r="E47" s="66" t="s">
+        <v>819</v>
+      </c>
+      <c r="F47" s="88" t="s">
         <v>820</v>
-      </c>
-      <c r="D47" s="68" t="s">
-        <v>821</v>
-      </c>
-      <c r="E47" s="66" t="s">
-        <v>822</v>
-      </c>
-      <c r="F47" s="88" t="s">
-        <v>823</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="30" customHeight="1">
@@ -20454,56 +20489,56 @@
         <v>4.5</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>219</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="F51" s="86" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="19.5" customHeight="1">
       <c r="A52" s="81" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="B52" s="75">
         <v>4.7</v>
       </c>
       <c r="C52" s="76" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="D52" s="75" t="s">
         <v>66</v>
       </c>
       <c r="E52" s="76" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="F52" s="87" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="30" customHeight="1">
       <c r="A53" s="82" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B53" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C53" s="66" t="s">
+        <v>824</v>
+      </c>
+      <c r="D53" s="68" t="s">
+        <v>825</v>
+      </c>
+      <c r="E53" s="66" t="s">
+        <v>826</v>
+      </c>
+      <c r="F53" s="88" t="s">
         <v>827</v>
-      </c>
-      <c r="D53" s="68" t="s">
-        <v>828</v>
-      </c>
-      <c r="E53" s="66" t="s">
-        <v>829</v>
-      </c>
-      <c r="F53" s="88" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="30" customHeight="1">
@@ -20578,42 +20613,42 @@
     </row>
     <row r="58" spans="1:6" ht="19.5" customHeight="1">
       <c r="A58" s="81" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="B58" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C58" s="74" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="D58" s="75" t="s">
         <v>219</v>
       </c>
       <c r="E58" s="76" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="F58" s="87" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="30" customHeight="1">
       <c r="A59" s="82" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B59" s="68">
         <v>4.5999999999999996</v>
       </c>
       <c r="C59" s="69" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="D59" s="68" t="s">
         <v>52</v>
       </c>
       <c r="E59" s="66" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="F59" s="88" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="30" customHeight="1">
@@ -20710,7 +20745,7 @@
         <v>115</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="F65" s="84" t="s">
         <v>113</v>
@@ -20724,13 +20759,13 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="D66" s="18" t="s">
         <v>223</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="F66" s="85" t="s">
         <v>277</v>
@@ -20758,19 +20793,19 @@
     </row>
     <row r="68" spans="1:6" ht="30" customHeight="1">
       <c r="A68" s="81" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="B68" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C68" s="76" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="D68" s="75" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="E68" s="76" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="F68" s="87" t="s">
         <v>277</v>
@@ -20778,39 +20813,39 @@
     </row>
     <row r="69" spans="1:6" ht="30" customHeight="1">
       <c r="A69" s="82" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B69" s="68">
         <v>4.3</v>
       </c>
       <c r="C69" s="66" t="s">
+        <v>870</v>
+      </c>
+      <c r="D69" s="68" t="s">
+        <v>871</v>
+      </c>
+      <c r="E69" s="66" t="s">
+        <v>872</v>
+      </c>
+      <c r="F69" s="88" t="s">
         <v>873</v>
-      </c>
-      <c r="D69" s="68" t="s">
-        <v>874</v>
-      </c>
-      <c r="E69" s="66" t="s">
-        <v>875</v>
-      </c>
-      <c r="F69" s="88" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="30" customHeight="1">
       <c r="A70" s="81" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="B70" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C70" s="76" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="D70" s="75" t="s">
         <v>123</v>
       </c>
       <c r="E70" s="76" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="F70" s="87" t="s">
         <v>121</v>
@@ -20818,39 +20853,39 @@
     </row>
     <row r="71" spans="1:6" ht="30" customHeight="1">
       <c r="A71" s="82" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="B71" s="68">
         <v>4.5</v>
       </c>
       <c r="C71" s="66" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="D71" s="68" t="s">
         <v>99</v>
       </c>
       <c r="E71" s="66" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="F71" s="88" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="30" customHeight="1">
       <c r="A72" s="82" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="B72" s="216" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C72" s="66" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D72" s="68" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E72" s="66" t="s">
         <v>1020</v>
-      </c>
-      <c r="C72" s="66" t="s">
-        <v>1021</v>
-      </c>
-      <c r="D72" s="68" t="s">
-        <v>1022</v>
-      </c>
-      <c r="E72" s="66" t="s">
-        <v>1023</v>
       </c>
       <c r="F72" s="88" t="s">
         <v>288</v>
@@ -20858,22 +20893,22 @@
     </row>
     <row r="73" spans="1:6" ht="30" customHeight="1">
       <c r="A73" s="82" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B73" s="216" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C73" s="66" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D73" s="68" t="s">
         <v>1014</v>
       </c>
-      <c r="B73" s="216" t="s">
+      <c r="E73" s="66" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F73" s="88" t="s">
         <v>1024</v>
-      </c>
-      <c r="C73" s="66" t="s">
-        <v>1025</v>
-      </c>
-      <c r="D73" s="68" t="s">
-        <v>1017</v>
-      </c>
-      <c r="E73" s="66" t="s">
-        <v>1026</v>
-      </c>
-      <c r="F73" s="88" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="30" customHeight="1">
@@ -20948,19 +20983,19 @@
     </row>
     <row r="78" spans="1:6" ht="30" customHeight="1">
       <c r="A78" s="81" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="B78" s="75">
         <v>4.3</v>
       </c>
       <c r="C78" s="76" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="D78" s="75" t="s">
         <v>219</v>
       </c>
       <c r="E78" s="76" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="F78" s="87" t="s">
         <v>271</v>
@@ -20968,19 +21003,19 @@
     </row>
     <row r="79" spans="1:6" ht="30" customHeight="1">
       <c r="A79" s="82" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B79" s="68">
         <v>4</v>
       </c>
       <c r="C79" s="66" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="D79" s="68" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="E79" s="66" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="F79" s="88" t="s">
         <v>271</v>
@@ -21024,13 +21059,13 @@
         <v>4.2</v>
       </c>
       <c r="C82" s="16" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="D82" s="18" t="s">
         <v>119</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="F82" s="85" t="s">
         <v>277</v>
@@ -21044,13 +21079,13 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>219</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="F83" s="86" t="s">
         <v>277</v>
@@ -21058,19 +21093,19 @@
     </row>
     <row r="84" spans="1:6" ht="30" customHeight="1">
       <c r="A84" s="81" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="B84" s="75">
         <v>4.3</v>
       </c>
       <c r="C84" s="76" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="D84" s="75" t="s">
         <v>119</v>
       </c>
       <c r="E84" s="76" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="F84" s="87" t="s">
         <v>277</v>
@@ -21078,19 +21113,19 @@
     </row>
     <row r="85" spans="1:6" ht="30" customHeight="1">
       <c r="A85" s="82" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B85" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C85" s="66" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="D85" s="68" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="E85" s="66" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="F85" s="88" t="s">
         <v>288</v>
@@ -21098,19 +21133,19 @@
     </row>
     <row r="86" spans="1:6" ht="30" customHeight="1">
       <c r="A86" s="81" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="B86" s="75">
         <v>4.5999999999999996</v>
       </c>
       <c r="C86" s="76" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="D86" s="75" t="s">
         <v>128</v>
       </c>
       <c r="E86" s="76" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="F86" s="87" t="s">
         <v>277</v>
@@ -21118,19 +21153,19 @@
     </row>
     <row r="87" spans="1:6" ht="30" customHeight="1">
       <c r="A87" s="82" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="B87" s="68" t="s">
         <v>254</v>
       </c>
       <c r="C87" s="66" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="D87" s="68" t="s">
         <v>289</v>
       </c>
       <c r="E87" s="66" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="F87" s="88" t="s">
         <v>113</v>
@@ -21138,19 +21173,19 @@
     </row>
     <row r="88" spans="1:6" ht="30" customHeight="1">
       <c r="A88" s="82" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="B88" s="216" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="C88" s="66" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="D88" s="68" t="s">
         <v>189</v>
       </c>
       <c r="E88" s="66" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="F88" s="88" t="s">
         <v>264</v>
@@ -21158,22 +21193,22 @@
     </row>
     <row r="89" spans="1:6" ht="30" customHeight="1">
       <c r="A89" s="82" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B89" s="216" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C89" s="66" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D89" s="68" t="s">
         <v>1014</v>
       </c>
-      <c r="B89" s="216" t="s">
+      <c r="E89" s="66" t="s">
         <v>1015</v>
       </c>
-      <c r="C89" s="66" t="s">
+      <c r="F89" s="88" t="s">
         <v>1016</v>
-      </c>
-      <c r="D89" s="68" t="s">
-        <v>1017</v>
-      </c>
-      <c r="E89" s="66" t="s">
-        <v>1018</v>
-      </c>
-      <c r="F89" s="88" t="s">
-        <v>1019</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="33.75" customHeight="1">
@@ -21248,39 +21283,39 @@
     </row>
     <row r="94" spans="1:6" ht="28">
       <c r="A94" s="81" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="B94" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C94" s="76" t="s">
+        <v>882</v>
+      </c>
+      <c r="D94" s="75" t="s">
+        <v>883</v>
+      </c>
+      <c r="E94" s="76" t="s">
+        <v>884</v>
+      </c>
+      <c r="F94" s="87" t="s">
         <v>885</v>
-      </c>
-      <c r="D94" s="75" t="s">
-        <v>886</v>
-      </c>
-      <c r="E94" s="76" t="s">
-        <v>887</v>
-      </c>
-      <c r="F94" s="87" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="28">
       <c r="A95" s="82" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B95" s="68">
         <v>4.5</v>
       </c>
       <c r="C95" s="66" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="D95" s="68" t="s">
         <v>119</v>
       </c>
       <c r="E95" s="66" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="F95" s="88" t="s">
         <v>278</v>
@@ -21288,7 +21323,7 @@
     </row>
     <row r="96" spans="1:6" ht="48" customHeight="1" thickBot="1">
       <c r="A96" s="182" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="B96" s="183"/>
       <c r="C96" s="183"/>
@@ -21446,13 +21481,13 @@
         <v>324</v>
       </c>
       <c r="B10" s="92" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="C10" s="92" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D10" s="125" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -21572,27 +21607,27 @@
         <v>324</v>
       </c>
       <c r="B20" s="92" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="C20" s="92" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="D20" s="125" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="30" customHeight="1">
       <c r="A21" s="140" t="s">
+        <v>932</v>
+      </c>
+      <c r="B21" s="90" t="s">
+        <v>933</v>
+      </c>
+      <c r="C21" s="90" t="s">
+        <v>934</v>
+      </c>
+      <c r="D21" s="149" t="s">
         <v>935</v>
-      </c>
-      <c r="B21" s="90" t="s">
-        <v>936</v>
-      </c>
-      <c r="C21" s="90" t="s">
-        <v>937</v>
-      </c>
-      <c r="D21" s="149" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="27.75" customHeight="1">

--- a/tools/itinerary.xlsx
+++ b/tools/itinerary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jitwei/Library/Mobile Documents/com~apple~CloudDocs/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1283FF7-42FE-E247-A56C-B529A2C85B5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{FCD1244A-421E-DA43-B9DC-C68901FA4525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51231A84-60FF-3346-80AA-8A8C1F1C5813}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="17020" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="17020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1596" uniqueCount="1075">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="1092">
   <si>
     <r>
       <rPr>
@@ -3811,32 +3811,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Li Bai Xie Crab-Roe Noodles </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>李白蟹</t>
-    </r>
-  </si>
-  <si>
     <t>¥60–120</t>
-  </si>
-  <si>
-    <t>Qinhuai river-view; crab-roe noodles</t>
   </si>
   <si>
     <t>秦淮区夫子庙</t>
@@ -14574,6 +14549,63 @@
   </si>
   <si>
     <t>¥100 (蟹另计)</t>
+  </si>
+  <si>
+    <t>☕ ALT half-day: Taihu Dongshan 太湖东山 lake-view cafés (sunset)</t>
+  </si>
+  <si>
+    <t>From a 苏州文旅 post. DONGSHAN IS THE CLOSER/EASIER SIDE: ~30km &amp; bus 502/621 direct from the city (vs Xishan 45km, needs 太湖大桥 + awkward 地铁5号线→快线11号→岛内公交). ① 望听café·零湖落日 — white walls + wood-fired kiln, floor-to-ceiling Taihu view; 果木窑烤玛格丽塔 pizza, 碧螺春拿铁, 东山大米咖啡; also a 4.8/59 guesthouse (吴中区东山镇莫厘村尚锦2号, 08:00–22:00, 13564174956). ② ATE·阿缇依湖景咖啡 — sunset seats + the red-and-white lighthouse landmark; a Wuzhong day-trip guide names it THE Dongshan sunset stop. ③ 橙色计划 NO.1 露营咖啡 — camping base w/ 巨轮咖啡, BBQ, 篝火DJ. ⚠ NOT a detour you can slot into Day 7 — this REPLACES the afternoon (网师园/十全街/观前街). ⚠ Bonus: mid-Nov is peak 银杏 at 陆巷古村 on the same peninsula. XISHAN ALT (pick one side only, ~1h apart): 湖与Cafe 270° (缥纱路20x, 大众点评4.2, #1 太湖西山热门榜), 树下茶咖 (罗汉坞千年古樟), 野隐·松簧 (风铃溪谷金铎岭半山腰).</t>
+  </si>
+  <si>
+    <t>Alt · ~1h each way</t>
+  </si>
+  <si>
+    <t>吴中区东山镇莫厘村尚锦2号 (望听) · 东山镇 (ATE/橙色计划)</t>
+  </si>
+  <si>
+    <t>Wangting 望听café·零湖落日 (Day 7 · Alt)</t>
+  </si>
+  <si>
+    <t>吴中区东山镇莫厘村尚锦2号 (太湖东山, ~30km)</t>
+  </si>
+  <si>
+    <t>TAIHU SUNSET. White walls + traditional wood-fired kiln; floor-to-ceiling windows onto the lake. 果木窑烤玛格丽塔 pizza, 碧螺春拿铁, 东山大米咖啡, 开心果巴斯克. Also a guesthouse: 4.8/5 (59 reviews), 08:00–22:00, 13564174956. Nearby same-side picks: ATE·阿缇依湖景咖啡 (sunset + red/white lighthouse) and 橙色计划 NO.1 露营咖啡 (camping base, BBQ, 篝火DJ). Source: 苏州文旅 post + Dianping/Ctrip. DONGSHAN = the closer, bus-served side (502/621).</t>
+  </si>
+  <si>
+    <t>Hu Yu 湖与Cafe 270° (Xishan — only if you swap sides)</t>
+  </si>
+  <si>
+    <t>吴中区金庭镇缥纱路20x (太湖西山岛, ~45km)</t>
+  </si>
+  <si>
+    <t>XISHAN ALTERNATIVE — 270° lake view, 2 floors. 大众点评 4.2, ranked #1 on 太湖西山美食热门榜 (Ctrip shows a lower 3.7 on only 3 reviews). Try 西山拿铁, 黑松露薯条, 栗子巴斯克. Same-side extras: 树下茶咖 (under the 千年古樟 at 罗汉坞 — coffee or a pot of 碧螺春) and 野隐·松簧 (风铃溪谷·金铎岭半山腰, terrace w/ pine-wind + lake view). ⚠ Xishan needs 太湖大桥; public transport is weak (地铁5号线→快线11号→岛内公交) and the bridge jams at weekends. Dongshan and Xishan are ~1h apart — choose ONE.</t>
+  </si>
+  <si>
+    <t>🦀 Optional: Li Bai Xie 李百蟹·蟹黄面 (Pingjiang 平江路总店)</t>
+  </si>
+  <si>
+    <t>NOTE THE SPELLING: 李百蟹 (bǎi 百), not 李白蟹. ZERO DETOUR — it is ON Pingjiang Rd 平江路, which you already walk 18:00–19:15 (row above). Crab-roe noodles 蟹黄面 &amp; 蟹黄拌饭 — golden 蟹粉/蟹膏, FREE noodle &amp; rice refills; also 江南花雕熟醉蟹, 蟹膏, and photogenic Suzhou desserts (草莓奶盖冰, 抹茶豆花, 桂花奶酪). Riverside seats look onto the canal, bridges &amp; boats. ⚠ Queues at meal times — take a queue number on arrival (reported to move fast). Open 10:00–21:30. Trip.com 5.0/5 but only 2 reviews — thin sample, re-check on Dianping. Other branches: 观前街店 (beside Day 7 lunch), 山塘街店 (河景船宴, near hotel).</t>
+  </si>
+  <si>
+    <t>Opt · 10:00–21:30</t>
+  </si>
+  <si>
+    <t>姑苏区狮林寺巷99号 琵琶语评弹茶馆·北馆1层 (平江路)</t>
+  </si>
+  <si>
+    <t>Li Bai Xie 李百蟹·蟹黄面 (Day 6 · Opt · 平江路总店)</t>
+  </si>
+  <si>
+    <t>姑苏区狮林寺巷99号 琵琶语评弹茶馆·北馆1层 (on 平江路)</t>
+  </si>
+  <si>
+    <t>CRAB-ROE NOODLES, zero detour — sits on the Pingjiang Rd 平江路 stretch already in Day 6. 蟹黄面 / 蟹黄拌饭 with free noodle &amp; rice refills; 江南花雕熟醉蟹, 蟹膏; Suzhou desserts (草莓奶盖冰, 抹茶豆花, 桂花奶酪). Canal-side windows over bridges &amp; boats. Open 10:00–21:30; take a queue number on arrival. Spelling is 李百蟹 (百), not 李白蟹. Branches also at 观前街 and 山塘街 (河景船宴). Trip.com 5.0/5 on only 2 reviews — thin sample; re-check on Dianping.</t>
+  </si>
+  <si>
+    <t>李百蟹·蟹黄面 Li Bai Xie Crab-Roe Noodles (夫子庙店)</t>
+  </si>
+  <si>
+    <t>Crab-roe noodles 蟹黄面 &amp; 蟹黄拌饭 with free noodle/rice refills; Qinhuai river-view. NOTE: correct spelling is 李百蟹 (百 "hundred"), not 李白蟹 — it has nothing to do with the poet 李白. Same chain also has 4 Suzhou branches (see Day 6 Opt).</t>
   </si>
 </sst>
 </file>
@@ -16278,7 +16310,7 @@
   <sheetPr>
     <tabColor rgb="FFC55A11"/>
   </sheetPr>
-  <dimension ref="A1:F137"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -16291,7 +16323,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
       <c r="A1" s="161" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B1" s="162"/>
       <c r="C1" s="162"/>
@@ -16301,7 +16333,7 @@
     </row>
     <row r="2" spans="1:6" ht="21.75" customHeight="1">
       <c r="A2" s="164" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B2" s="165"/>
       <c r="C2" s="165"/>
@@ -16311,19 +16343,19 @@
     </row>
     <row r="3" spans="1:6" ht="19.5" customHeight="1">
       <c r="A3" s="77" t="s">
+        <v>394</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>395</v>
+      </c>
+      <c r="C3" s="26" t="s">
         <v>396</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="D3" s="26" t="s">
         <v>397</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="E3" s="26" t="s">
         <v>398</v>
-      </c>
-      <c r="D3" s="26" t="s">
-        <v>399</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>400</v>
       </c>
       <c r="F3" s="83" t="s">
         <v>23</v>
@@ -16331,7 +16363,7 @@
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1">
       <c r="A4" s="167" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="B4" s="168"/>
       <c r="C4" s="168"/>
@@ -16341,99 +16373,99 @@
     </row>
     <row r="5" spans="1:6" ht="25.5" customHeight="1">
       <c r="A5" s="98" t="s">
+        <v>399</v>
+      </c>
+      <c r="B5" s="53" t="s">
+        <v>400</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="D5" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="F5" s="86" t="s">
         <v>404</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>405</v>
-      </c>
-      <c r="F5" s="86" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="25.5" customHeight="1">
       <c r="A6" s="99" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B6" s="54" t="s">
+        <v>405</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="D6" s="15" t="s">
         <v>407</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="E6" s="15" t="s">
         <v>408</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="F6" s="113" t="s">
         <v>409</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>410</v>
-      </c>
-      <c r="F6" s="113" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1">
       <c r="A7" s="100" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B7" s="213" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="C7" s="50" t="s">
+        <v>410</v>
+      </c>
+      <c r="D7" s="50" t="s">
+        <v>977</v>
+      </c>
+      <c r="E7" s="50" t="s">
+        <v>411</v>
+      </c>
+      <c r="F7" s="115" t="s">
         <v>412</v>
-      </c>
-      <c r="D7" s="50" t="s">
-        <v>979</v>
-      </c>
-      <c r="E7" s="50" t="s">
-        <v>413</v>
-      </c>
-      <c r="F7" s="115" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="25.5" customHeight="1">
       <c r="A8" s="100" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B8" s="55" t="s">
+        <v>413</v>
+      </c>
+      <c r="C8" s="50" t="s">
+        <v>414</v>
+      </c>
+      <c r="D8" s="50" t="s">
         <v>415</v>
       </c>
-      <c r="C8" s="50" t="s">
+      <c r="E8" s="50" t="s">
         <v>416</v>
       </c>
-      <c r="D8" s="50" t="s">
+      <c r="F8" s="115" t="s">
         <v>417</v>
-      </c>
-      <c r="E8" s="50" t="s">
-        <v>418</v>
-      </c>
-      <c r="F8" s="115" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="25.5" customHeight="1">
       <c r="A9" s="100" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B9" s="55" t="s">
+        <v>418</v>
+      </c>
+      <c r="C9" s="50" t="s">
+        <v>419</v>
+      </c>
+      <c r="D9" s="50" t="s">
         <v>420</v>
       </c>
-      <c r="C9" s="50" t="s">
+      <c r="E9" s="50" t="s">
         <v>421</v>
-      </c>
-      <c r="D9" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="E9" s="50" t="s">
-        <v>423</v>
       </c>
       <c r="F9" s="115" t="s">
         <v>28</v>
@@ -16441,39 +16473,39 @@
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1">
       <c r="A10" s="101" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B10" s="56" t="s">
+        <v>422</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="E10" s="10" t="s">
         <v>425</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="F10" s="116" t="s">
         <v>426</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>427</v>
-      </c>
-      <c r="F10" s="116" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1">
       <c r="A11" s="102" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B11" s="57" t="s">
+        <v>427</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>428</v>
+      </c>
+      <c r="D11" s="33" t="s">
         <v>429</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="E11" s="35" t="s">
         <v>430</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>431</v>
-      </c>
-      <c r="E11" s="35" t="s">
-        <v>432</v>
       </c>
       <c r="F11" s="117" t="s">
         <v>152</v>
@@ -16481,47 +16513,47 @@
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1">
       <c r="A12" s="103" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B12" s="58" t="s">
+        <v>431</v>
+      </c>
+      <c r="C12" s="39" t="s">
+        <v>432</v>
+      </c>
+      <c r="D12" s="39" t="s">
         <v>433</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="E12" s="41" t="s">
         <v>434</v>
       </c>
-      <c r="D12" s="39" t="s">
+      <c r="F12" s="118" t="s">
         <v>435</v>
-      </c>
-      <c r="E12" s="41" t="s">
-        <v>436</v>
-      </c>
-      <c r="F12" s="118" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1">
       <c r="A13" s="101" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B13" s="56" t="s">
+        <v>436</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="D13" s="10" t="s">
         <v>438</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="E13" s="10" t="s">
         <v>439</v>
       </c>
-      <c r="D13" s="10" t="s">
-        <v>440</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>441</v>
-      </c>
       <c r="F13" s="116" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="25.5" customHeight="1">
       <c r="A14" s="167" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="B14" s="168"/>
       <c r="C14" s="168"/>
@@ -16531,16 +16563,16 @@
     </row>
     <row r="15" spans="1:6" ht="30" customHeight="1">
       <c r="A15" s="101" t="s">
+        <v>440</v>
+      </c>
+      <c r="B15" s="56" t="s">
+        <v>441</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>442</v>
       </c>
-      <c r="B15" s="56" t="s">
+      <c r="D15" s="10" t="s">
         <v>443</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>444</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>445</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>20</v>
@@ -16551,119 +16583,119 @@
     </row>
     <row r="16" spans="1:6" ht="30" customHeight="1">
       <c r="A16" s="104" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B16" s="59" t="s">
+        <v>444</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>445</v>
+      </c>
+      <c r="D16" s="47" t="s">
         <v>446</v>
       </c>
-      <c r="C16" s="47" t="s">
+      <c r="E16" s="47" t="s">
         <v>447</v>
       </c>
-      <c r="D16" s="47" t="s">
+      <c r="F16" s="119" t="s">
         <v>448</v>
-      </c>
-      <c r="E16" s="47" t="s">
-        <v>449</v>
-      </c>
-      <c r="F16" s="119" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="25.5" customHeight="1">
       <c r="A17" s="105" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B17" s="60" t="s">
+        <v>449</v>
+      </c>
+      <c r="C17" s="61" t="s">
+        <v>450</v>
+      </c>
+      <c r="D17" s="61" t="s">
         <v>451</v>
       </c>
-      <c r="C17" s="61" t="s">
+      <c r="E17" s="61" t="s">
+        <v>447</v>
+      </c>
+      <c r="F17" s="120" t="s">
         <v>452</v>
-      </c>
-      <c r="D17" s="61" t="s">
-        <v>453</v>
-      </c>
-      <c r="E17" s="61" t="s">
-        <v>449</v>
-      </c>
-      <c r="F17" s="120" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="25.5" customHeight="1">
       <c r="A18" s="104" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B18" s="59" t="s">
+        <v>453</v>
+      </c>
+      <c r="C18" s="47" t="s">
+        <v>454</v>
+      </c>
+      <c r="D18" s="47" t="s">
         <v>455</v>
       </c>
-      <c r="C18" s="47" t="s">
+      <c r="E18" s="47" t="s">
+        <v>447</v>
+      </c>
+      <c r="F18" s="119" t="s">
         <v>456</v>
-      </c>
-      <c r="D18" s="47" t="s">
-        <v>457</v>
-      </c>
-      <c r="E18" s="47" t="s">
-        <v>449</v>
-      </c>
-      <c r="F18" s="119" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="25.5" customHeight="1">
       <c r="A19" s="105" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B19" s="60" t="s">
+        <v>457</v>
+      </c>
+      <c r="C19" s="61" t="s">
+        <v>458</v>
+      </c>
+      <c r="D19" s="61" t="s">
         <v>459</v>
       </c>
-      <c r="C19" s="61" t="s">
+      <c r="E19" s="61" t="s">
         <v>460</v>
       </c>
-      <c r="D19" s="61" t="s">
+      <c r="F19" s="120" t="s">
         <v>461</v>
-      </c>
-      <c r="E19" s="61" t="s">
-        <v>462</v>
-      </c>
-      <c r="F19" s="120" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="25.5" customHeight="1">
       <c r="A20" s="105" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B20" s="207" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="C20" s="61" t="s">
+        <v>463</v>
+      </c>
+      <c r="D20" s="61" t="s">
+        <v>464</v>
+      </c>
+      <c r="E20" s="61" t="s">
         <v>465</v>
       </c>
-      <c r="D20" s="61" t="s">
+      <c r="F20" s="120" t="s">
         <v>466</v>
-      </c>
-      <c r="E20" s="61" t="s">
-        <v>467</v>
-      </c>
-      <c r="F20" s="120" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="25.5" customHeight="1">
       <c r="A21" s="106" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B21" s="212" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="C21" s="20" t="s">
+        <v>467</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>468</v>
+      </c>
+      <c r="E21" s="20" t="s">
         <v>469</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>470</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>471</v>
       </c>
       <c r="F21" s="121" t="s">
         <v>69</v>
@@ -16671,36 +16703,36 @@
     </row>
     <row r="22" spans="1:6" ht="42" customHeight="1">
       <c r="A22" s="106" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B22" s="212" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C22" s="20" t="s">
+        <v>978</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>979</v>
+      </c>
+      <c r="E22" s="20" t="s">
         <v>980</v>
       </c>
-      <c r="D22" s="20" t="s">
-        <v>981</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>982</v>
-      </c>
       <c r="F22" s="121" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="42" customHeight="1">
       <c r="A23" s="98" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B23" s="214" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>57</v>
@@ -16711,245 +16743,245 @@
     </row>
     <row r="24" spans="1:6" ht="25.5" customHeight="1">
       <c r="A24" s="105" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B24" s="207" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="C24" s="61" t="s">
+        <v>472</v>
+      </c>
+      <c r="D24" s="61" t="s">
+        <v>473</v>
+      </c>
+      <c r="E24" s="61" t="s">
         <v>474</v>
       </c>
-      <c r="D24" s="61" t="s">
+      <c r="F24" s="120" t="s">
         <v>475</v>
-      </c>
-      <c r="E24" s="61" t="s">
-        <v>476</v>
-      </c>
-      <c r="F24" s="120" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="25.5" customHeight="1">
       <c r="A25" s="105" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B25" s="207" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="C25" s="61" t="s">
+        <v>476</v>
+      </c>
+      <c r="D25" s="61" t="s">
+        <v>477</v>
+      </c>
+      <c r="E25" s="61" t="s">
         <v>478</v>
       </c>
-      <c r="D25" s="61" t="s">
+      <c r="F25" s="120" t="s">
         <v>479</v>
-      </c>
-      <c r="E25" s="61" t="s">
-        <v>480</v>
-      </c>
-      <c r="F25" s="120" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="25.5" customHeight="1">
       <c r="A26" s="105" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B26" s="207" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="C26" s="61" t="s">
+        <v>480</v>
+      </c>
+      <c r="D26" s="61" t="s">
+        <v>481</v>
+      </c>
+      <c r="E26" s="61" t="s">
         <v>482</v>
       </c>
-      <c r="D26" s="61" t="s">
+      <c r="F26" s="120" t="s">
         <v>483</v>
-      </c>
-      <c r="E26" s="61" t="s">
-        <v>484</v>
-      </c>
-      <c r="F26" s="120" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="42" customHeight="1">
       <c r="A27" s="105" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B27" s="207" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C27" s="61" t="s">
+        <v>960</v>
+      </c>
+      <c r="D27" s="61" t="s">
+        <v>961</v>
+      </c>
+      <c r="E27" s="61" t="s">
+        <v>626</v>
+      </c>
+      <c r="F27" s="120" t="s">
         <v>962</v>
-      </c>
-      <c r="D27" s="61" t="s">
-        <v>963</v>
-      </c>
-      <c r="E27" s="61" t="s">
-        <v>628</v>
-      </c>
-      <c r="F27" s="120" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="42" customHeight="1">
       <c r="A28" s="107" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B28" s="215" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="C28" s="36" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="D28" s="36" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="E28" s="36" t="s">
         <v>61</v>
       </c>
       <c r="F28" s="122" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="28">
       <c r="A29" s="102" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B29" s="209" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F29" s="117" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="42" customHeight="1">
       <c r="A30" s="217" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B30" s="218" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C30" s="61" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D30" s="61" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E30" s="61" t="s">
         <v>1035</v>
       </c>
-      <c r="D30" s="61" t="s">
+      <c r="F30" s="120" t="s">
         <v>1036</v>
-      </c>
-      <c r="E30" s="61" t="s">
-        <v>1037</v>
-      </c>
-      <c r="F30" s="120" t="s">
-        <v>1038</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="42" customHeight="1">
       <c r="A31" s="217" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B31" s="218" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C31" s="61" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D31" s="61" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E31" s="61" t="s">
         <v>1039</v>
       </c>
-      <c r="D31" s="61" t="s">
+      <c r="F31" s="120" t="s">
         <v>1040</v>
-      </c>
-      <c r="E31" s="61" t="s">
-        <v>1041</v>
-      </c>
-      <c r="F31" s="120" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="56" customHeight="1">
       <c r="A32" s="217" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B32" s="218" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C32" s="61" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D32" s="61" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E32" s="61" t="s">
         <v>1050</v>
       </c>
-      <c r="D32" s="61" t="s">
+      <c r="F32" s="120" t="s">
         <v>1051</v>
-      </c>
-      <c r="E32" s="61" t="s">
-        <v>1052</v>
-      </c>
-      <c r="F32" s="120" t="s">
-        <v>1053</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="25.5" customHeight="1">
       <c r="A33" s="102" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B33" s="57" t="s">
+        <v>934</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>935</v>
+      </c>
+      <c r="D33" s="33" t="s">
         <v>936</v>
       </c>
-      <c r="C33" s="33" t="s">
+      <c r="E33" s="33" t="s">
         <v>937</v>
       </c>
-      <c r="D33" s="33" t="s">
+      <c r="F33" s="117" t="s">
         <v>938</v>
-      </c>
-      <c r="E33" s="33" t="s">
-        <v>939</v>
-      </c>
-      <c r="F33" s="117" t="s">
-        <v>940</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="30" customHeight="1">
       <c r="A34" s="107" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B34" s="64" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="C34" s="36" t="s">
+        <v>486</v>
+      </c>
+      <c r="D34" s="36" t="s">
+        <v>487</v>
+      </c>
+      <c r="E34" s="36" t="s">
         <v>488</v>
       </c>
-      <c r="D34" s="36" t="s">
+      <c r="F34" s="122" t="s">
         <v>489</v>
-      </c>
-      <c r="E34" s="36" t="s">
-        <v>490</v>
-      </c>
-      <c r="F34" s="122" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="25.5" customHeight="1">
       <c r="A35" s="101" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B35" s="151" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D35" s="10"/>
       <c r="E35" s="10" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F35" s="116" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="25.5" customHeight="1">
       <c r="A36" s="167" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="B36" s="168"/>
       <c r="C36" s="168"/>
@@ -16959,16 +16991,16 @@
     </row>
     <row r="37" spans="1:6" ht="25.5" customHeight="1">
       <c r="A37" s="101" t="s">
+        <v>492</v>
+      </c>
+      <c r="B37" s="56" t="s">
+        <v>493</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="D37" s="10" t="s">
         <v>494</v>
-      </c>
-      <c r="B37" s="56" t="s">
-        <v>495</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>444</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>496</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>20</v>
@@ -16979,79 +17011,79 @@
     </row>
     <row r="38" spans="1:6" ht="70" customHeight="1">
       <c r="A38" s="102" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B38" s="209" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C38" s="33" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D38" s="33" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E38" s="35" t="s">
         <v>1058</v>
       </c>
-      <c r="D38" s="33" t="s">
+      <c r="F38" s="117" t="s">
         <v>1059</v>
-      </c>
-      <c r="E38" s="35" t="s">
-        <v>1060</v>
-      </c>
-      <c r="F38" s="117" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="30" customHeight="1">
       <c r="A39" s="105" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B39" s="60" t="s">
+        <v>495</v>
+      </c>
+      <c r="C39" s="61" t="s">
+        <v>496</v>
+      </c>
+      <c r="D39" s="61" t="s">
         <v>497</v>
       </c>
-      <c r="C39" s="61" t="s">
+      <c r="E39" s="61" t="s">
         <v>498</v>
       </c>
-      <c r="D39" s="61" t="s">
+      <c r="F39" s="120" t="s">
         <v>499</v>
-      </c>
-      <c r="E39" s="61" t="s">
-        <v>500</v>
-      </c>
-      <c r="F39" s="120" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="25.5" customHeight="1">
       <c r="A40" s="105" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B40" s="60" t="s">
+        <v>500</v>
+      </c>
+      <c r="C40" s="61" t="s">
+        <v>501</v>
+      </c>
+      <c r="D40" s="61" t="s">
         <v>502</v>
       </c>
-      <c r="C40" s="61" t="s">
+      <c r="E40" s="61" t="s">
         <v>503</v>
       </c>
-      <c r="D40" s="61" t="s">
+      <c r="F40" s="120" t="s">
         <v>504</v>
-      </c>
-      <c r="E40" s="61" t="s">
-        <v>505</v>
-      </c>
-      <c r="F40" s="120" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="25.5" customHeight="1">
       <c r="A41" s="104" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B41" s="59" t="s">
+        <v>505</v>
+      </c>
+      <c r="C41" s="47" t="s">
+        <v>506</v>
+      </c>
+      <c r="D41" s="47" t="s">
         <v>507</v>
       </c>
-      <c r="C41" s="47" t="s">
-        <v>508</v>
-      </c>
-      <c r="D41" s="47" t="s">
-        <v>509</v>
-      </c>
       <c r="E41" s="47" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F41" s="119" t="s">
         <v>199</v>
@@ -17059,139 +17091,139 @@
     </row>
     <row r="42" spans="1:6" ht="42" customHeight="1">
       <c r="A42" s="99" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B42" s="54" t="s">
+        <v>508</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>509</v>
+      </c>
+      <c r="D42" s="15" t="s">
         <v>510</v>
-      </c>
-      <c r="C42" s="15" t="s">
-        <v>511</v>
-      </c>
-      <c r="D42" s="15" t="s">
-        <v>512</v>
       </c>
       <c r="E42" s="15" t="s">
         <v>61</v>
       </c>
       <c r="F42" s="85" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="25.5" customHeight="1">
       <c r="A43" s="105" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B43" s="60" t="s">
+        <v>512</v>
+      </c>
+      <c r="C43" s="61" t="s">
+        <v>513</v>
+      </c>
+      <c r="D43" s="61" t="s">
         <v>514</v>
       </c>
-      <c r="C43" s="61" t="s">
+      <c r="E43" s="61" t="s">
+        <v>503</v>
+      </c>
+      <c r="F43" s="120" t="s">
         <v>515</v>
-      </c>
-      <c r="D43" s="61" t="s">
-        <v>516</v>
-      </c>
-      <c r="E43" s="61" t="s">
-        <v>505</v>
-      </c>
-      <c r="F43" s="120" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="42" customHeight="1">
       <c r="A44" s="103" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B44" s="58" t="s">
+        <v>516</v>
+      </c>
+      <c r="C44" s="39" t="s">
+        <v>517</v>
+      </c>
+      <c r="D44" s="39" t="s">
         <v>518</v>
       </c>
-      <c r="C44" s="39" t="s">
+      <c r="E44" s="39" t="s">
         <v>519</v>
       </c>
-      <c r="D44" s="39" t="s">
+      <c r="F44" s="118" t="s">
         <v>520</v>
-      </c>
-      <c r="E44" s="39" t="s">
-        <v>521</v>
-      </c>
-      <c r="F44" s="118" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="25.5" customHeight="1">
       <c r="A45" s="108" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B45" s="89" t="s">
+        <v>895</v>
+      </c>
+      <c r="C45" s="90" t="s">
+        <v>896</v>
+      </c>
+      <c r="D45" s="90" t="s">
         <v>897</v>
       </c>
-      <c r="C45" s="90" t="s">
+      <c r="E45" s="90" t="s">
         <v>898</v>
       </c>
-      <c r="D45" s="90" t="s">
+      <c r="F45" s="123" t="s">
         <v>899</v>
-      </c>
-      <c r="E45" s="90" t="s">
-        <v>900</v>
-      </c>
-      <c r="F45" s="123" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="25.5" customHeight="1">
       <c r="A46" s="102" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B46" s="57" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C46" s="33" t="s">
+        <v>521</v>
+      </c>
+      <c r="D46" s="33" t="s">
+        <v>522</v>
+      </c>
+      <c r="E46" s="35" t="s">
         <v>523</v>
       </c>
-      <c r="D46" s="33" t="s">
+      <c r="F46" s="117" t="s">
         <v>524</v>
-      </c>
-      <c r="E46" s="35" t="s">
-        <v>525</v>
-      </c>
-      <c r="F46" s="117" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="42" customHeight="1">
       <c r="A47" s="102" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B47" s="209" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C47" s="33" t="s">
+        <v>957</v>
+      </c>
+      <c r="D47" s="33" t="s">
+        <v>958</v>
+      </c>
+      <c r="E47" s="35" t="s">
+        <v>626</v>
+      </c>
+      <c r="F47" s="117" t="s">
         <v>959</v>
-      </c>
-      <c r="D47" s="33" t="s">
-        <v>960</v>
-      </c>
-      <c r="E47" s="35" t="s">
-        <v>628</v>
-      </c>
-      <c r="F47" s="117" t="s">
-        <v>961</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="42" customHeight="1">
       <c r="A48" s="106" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B48" s="63" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="C48" s="20" t="s">
+        <v>525</v>
+      </c>
+      <c r="D48" s="20" t="s">
+        <v>526</v>
+      </c>
+      <c r="E48" s="20" t="s">
         <v>527</v>
-      </c>
-      <c r="D48" s="20" t="s">
-        <v>528</v>
-      </c>
-      <c r="E48" s="20" t="s">
-        <v>529</v>
       </c>
       <c r="F48" s="121" t="s">
         <v>73</v>
@@ -17199,167 +17231,167 @@
     </row>
     <row r="49" spans="1:6" ht="42" customHeight="1">
       <c r="A49" s="105" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B49" s="207" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="C49" s="61" t="s">
+        <v>528</v>
+      </c>
+      <c r="D49" s="61" t="s">
+        <v>992</v>
+      </c>
+      <c r="E49" s="61" t="s">
+        <v>529</v>
+      </c>
+      <c r="F49" s="120" t="s">
         <v>530</v>
-      </c>
-      <c r="D49" s="61" t="s">
-        <v>994</v>
-      </c>
-      <c r="E49" s="61" t="s">
-        <v>531</v>
-      </c>
-      <c r="F49" s="120" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="25.5" customHeight="1">
       <c r="A50" s="103" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B50" s="210" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C50" s="39" t="s">
+        <v>531</v>
+      </c>
+      <c r="D50" s="39" t="s">
+        <v>993</v>
+      </c>
+      <c r="E50" s="39" t="s">
+        <v>994</v>
+      </c>
+      <c r="F50" s="118" t="s">
         <v>533</v>
-      </c>
-      <c r="D50" s="39" t="s">
-        <v>995</v>
-      </c>
-      <c r="E50" s="39" t="s">
-        <v>996</v>
-      </c>
-      <c r="F50" s="118" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="25.5" customHeight="1">
       <c r="A51" s="98" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B51" s="53" t="s">
+        <v>995</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>996</v>
+      </c>
+      <c r="D51" s="5" t="s">
         <v>997</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="E51" s="5" t="s">
         <v>998</v>
       </c>
-      <c r="D51" s="5" t="s">
+      <c r="F51" s="86" t="s">
         <v>999</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F51" s="86" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="42" customHeight="1">
       <c r="A52" s="98" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B52" s="214" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D52" s="5" t="s">
         <v>1002</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="E52" s="5" t="s">
         <v>1003</v>
       </c>
-      <c r="D52" s="5" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>1005</v>
-      </c>
       <c r="F52" s="86" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="30" customHeight="1">
       <c r="A53" s="101" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B53" s="151" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F53" s="116" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="25.5" customHeight="1">
       <c r="A54" s="109" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B54" s="65" t="s">
+        <v>536</v>
+      </c>
+      <c r="C54" s="42" t="s">
+        <v>537</v>
+      </c>
+      <c r="D54" s="42" t="s">
         <v>538</v>
       </c>
-      <c r="C54" s="42" t="s">
+      <c r="E54" s="42" t="s">
         <v>539</v>
       </c>
-      <c r="D54" s="42" t="s">
-        <v>540</v>
-      </c>
-      <c r="E54" s="42" t="s">
-        <v>541</v>
-      </c>
       <c r="F54" s="124" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="25.5" customHeight="1">
       <c r="A55" s="103" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B55" s="58" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C55" s="39" t="s">
+        <v>540</v>
+      </c>
+      <c r="D55" s="39" t="s">
+        <v>541</v>
+      </c>
+      <c r="E55" s="39" t="s">
+        <v>539</v>
+      </c>
+      <c r="F55" s="118" t="s">
         <v>542</v>
-      </c>
-      <c r="D55" s="39" t="s">
-        <v>543</v>
-      </c>
-      <c r="E55" s="39" t="s">
-        <v>541</v>
-      </c>
-      <c r="F55" s="118" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="25.5" customHeight="1">
       <c r="A56" s="103" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B56" s="210" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C56" s="39" t="s">
+        <v>953</v>
+      </c>
+      <c r="D56" s="211" t="s">
+        <v>954</v>
+      </c>
+      <c r="E56" s="39" t="s">
         <v>955</v>
       </c>
-      <c r="D56" s="211" t="s">
+      <c r="F56" s="118" t="s">
         <v>956</v>
-      </c>
-      <c r="E56" s="39" t="s">
-        <v>957</v>
-      </c>
-      <c r="F56" s="118" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="25.5" customHeight="1">
       <c r="A57" s="152" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="B57" s="153"/>
       <c r="C57" s="153"/>
@@ -17369,19 +17401,19 @@
     </row>
     <row r="58" spans="1:6" ht="45" customHeight="1">
       <c r="A58" s="101" t="s">
+        <v>543</v>
+      </c>
+      <c r="B58" s="56" t="s">
+        <v>493</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>544</v>
+      </c>
+      <c r="D58" s="10" t="s">
         <v>545</v>
       </c>
-      <c r="B58" s="56" t="s">
-        <v>495</v>
-      </c>
-      <c r="C58" s="10" t="s">
+      <c r="E58" s="10" t="s">
         <v>546</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>547</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>548</v>
       </c>
       <c r="F58" s="116" t="s">
         <v>28</v>
@@ -17389,265 +17421,265 @@
     </row>
     <row r="59" spans="1:6" ht="25.5" customHeight="1">
       <c r="A59" s="100" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B59" s="55" t="s">
+        <v>547</v>
+      </c>
+      <c r="C59" s="50" t="s">
+        <v>548</v>
+      </c>
+      <c r="D59" s="50" t="s">
         <v>549</v>
       </c>
-      <c r="C59" s="50" t="s">
+      <c r="E59" s="50" t="s">
         <v>550</v>
       </c>
-      <c r="D59" s="50" t="s">
+      <c r="F59" s="115" t="s">
         <v>551</v>
-      </c>
-      <c r="E59" s="50" t="s">
-        <v>552</v>
-      </c>
-      <c r="F59" s="115" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="30" customHeight="1">
       <c r="A60" s="100" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B60" s="55" t="s">
+        <v>552</v>
+      </c>
+      <c r="C60" s="50" t="s">
+        <v>553</v>
+      </c>
+      <c r="D60" s="50" t="s">
         <v>554</v>
       </c>
-      <c r="C60" s="50" t="s">
+      <c r="E60" s="50" t="s">
         <v>555</v>
       </c>
-      <c r="D60" s="50" t="s">
+      <c r="F60" s="115" t="s">
         <v>556</v>
-      </c>
-      <c r="E60" s="50" t="s">
-        <v>557</v>
-      </c>
-      <c r="F60" s="115" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="30" customHeight="1">
       <c r="A61" s="101" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B61" s="56" t="s">
+        <v>557</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>558</v>
+      </c>
+      <c r="D61" s="10" t="s">
         <v>559</v>
       </c>
-      <c r="C61" s="10" t="s">
+      <c r="E61" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="F61" s="116" t="s">
         <v>560</v>
-      </c>
-      <c r="D61" s="10" t="s">
-        <v>561</v>
-      </c>
-      <c r="E61" s="10" t="s">
-        <v>423</v>
-      </c>
-      <c r="F61" s="116" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="25.5" customHeight="1">
       <c r="A62" s="99" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B62" s="54" t="s">
+        <v>561</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>562</v>
+      </c>
+      <c r="D62" s="25" t="s">
         <v>563</v>
-      </c>
-      <c r="C62" s="15" t="s">
-        <v>564</v>
-      </c>
-      <c r="D62" s="25" t="s">
-        <v>565</v>
       </c>
       <c r="E62" s="15" t="s">
         <v>166</v>
       </c>
       <c r="F62" s="85" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="21.75" customHeight="1">
       <c r="A63" s="105" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B63" s="60" t="s">
+        <v>564</v>
+      </c>
+      <c r="C63" s="61" t="s">
+        <v>565</v>
+      </c>
+      <c r="D63" s="61" t="s">
         <v>566</v>
       </c>
-      <c r="C63" s="61" t="s">
-        <v>567</v>
-      </c>
-      <c r="D63" s="61" t="s">
-        <v>568</v>
-      </c>
       <c r="E63" s="61" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F63" s="120" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="25.5" customHeight="1">
       <c r="A64" s="105" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B64" s="60" t="s">
+        <v>567</v>
+      </c>
+      <c r="C64" s="61" t="s">
+        <v>568</v>
+      </c>
+      <c r="D64" s="61" t="s">
         <v>569</v>
       </c>
-      <c r="C64" s="61" t="s">
+      <c r="E64" s="61" t="s">
         <v>570</v>
       </c>
-      <c r="D64" s="61" t="s">
+      <c r="F64" s="120" t="s">
         <v>571</v>
-      </c>
-      <c r="E64" s="61" t="s">
-        <v>572</v>
-      </c>
-      <c r="F64" s="120" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="25.5" customHeight="1">
       <c r="A65" s="106" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B65" s="63" t="s">
+        <v>572</v>
+      </c>
+      <c r="C65" s="20" t="s">
+        <v>573</v>
+      </c>
+      <c r="D65" s="20" t="s">
         <v>574</v>
       </c>
-      <c r="C65" s="20" t="s">
+      <c r="E65" s="20" t="s">
         <v>575</v>
       </c>
-      <c r="D65" s="20" t="s">
+      <c r="F65" s="121" t="s">
         <v>576</v>
-      </c>
-      <c r="E65" s="20" t="s">
-        <v>577</v>
-      </c>
-      <c r="F65" s="121" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="30" customHeight="1">
       <c r="A66" s="105" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B66" s="60" t="s">
+        <v>577</v>
+      </c>
+      <c r="C66" s="61" t="s">
+        <v>578</v>
+      </c>
+      <c r="D66" s="61" t="s">
         <v>579</v>
       </c>
-      <c r="C66" s="61" t="s">
+      <c r="E66" s="61" t="s">
+        <v>570</v>
+      </c>
+      <c r="F66" s="120" t="s">
         <v>580</v>
-      </c>
-      <c r="D66" s="61" t="s">
-        <v>581</v>
-      </c>
-      <c r="E66" s="61" t="s">
-        <v>572</v>
-      </c>
-      <c r="F66" s="120" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="30" customHeight="1">
       <c r="A67" s="110" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B67" s="91" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="C67" s="92" t="s">
+        <v>900</v>
+      </c>
+      <c r="D67" s="92" t="s">
+        <v>901</v>
+      </c>
+      <c r="E67" s="92" t="s">
         <v>902</v>
       </c>
-      <c r="D67" s="92" t="s">
+      <c r="F67" s="125" t="s">
         <v>903</v>
-      </c>
-      <c r="E67" s="92" t="s">
-        <v>904</v>
-      </c>
-      <c r="F67" s="125" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="30" customHeight="1">
       <c r="A68" s="105" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B68" s="60" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C68" s="61" t="s">
+        <v>581</v>
+      </c>
+      <c r="D68" s="61" t="s">
+        <v>582</v>
+      </c>
+      <c r="E68" s="61" t="s">
         <v>583</v>
       </c>
-      <c r="D68" s="61" t="s">
+      <c r="F68" s="120" t="s">
         <v>584</v>
-      </c>
-      <c r="E68" s="61" t="s">
-        <v>585</v>
-      </c>
-      <c r="F68" s="120" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="25.5" customHeight="1">
       <c r="A69" s="107" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B69" s="64" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="C69" s="36" t="s">
+        <v>586</v>
+      </c>
+      <c r="D69" s="36" t="s">
+        <v>587</v>
+      </c>
+      <c r="E69" s="36" t="s">
         <v>588</v>
       </c>
-      <c r="D69" s="36" t="s">
+      <c r="F69" s="122" t="s">
         <v>589</v>
-      </c>
-      <c r="E69" s="36" t="s">
-        <v>590</v>
-      </c>
-      <c r="F69" s="122" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="25.5" customHeight="1">
       <c r="A70" s="109" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B70" s="65" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="C70" s="42" t="s">
+        <v>590</v>
+      </c>
+      <c r="D70" s="44" t="s">
+        <v>591</v>
+      </c>
+      <c r="E70" s="42" t="s">
         <v>592</v>
       </c>
-      <c r="D70" s="44" t="s">
+      <c r="F70" s="124" t="s">
         <v>593</v>
-      </c>
-      <c r="E70" s="42" t="s">
-        <v>594</v>
-      </c>
-      <c r="F70" s="124" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="30" customHeight="1">
       <c r="A71" s="101" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B71" s="128" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="D71" s="10"/>
       <c r="E71" s="10" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="F71" s="116" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="30" customHeight="1">
       <c r="A72" s="152" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="B72" s="153"/>
       <c r="C72" s="153"/>
@@ -17657,16 +17689,16 @@
     </row>
     <row r="73" spans="1:6" ht="30" customHeight="1">
       <c r="A73" s="101" t="s">
+        <v>597</v>
+      </c>
+      <c r="B73" s="56" t="s">
+        <v>493</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>598</v>
+      </c>
+      <c r="D73" s="10" t="s">
         <v>599</v>
-      </c>
-      <c r="B73" s="56" t="s">
-        <v>495</v>
-      </c>
-      <c r="C73" s="10" t="s">
-        <v>600</v>
-      </c>
-      <c r="D73" s="10" t="s">
-        <v>601</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>20</v>
@@ -17677,219 +17709,219 @@
     </row>
     <row r="74" spans="1:6" ht="25.5" customHeight="1">
       <c r="A74" s="105" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B74" s="60" t="s">
+        <v>600</v>
+      </c>
+      <c r="C74" s="61" t="s">
+        <v>601</v>
+      </c>
+      <c r="D74" s="62" t="s">
         <v>602</v>
       </c>
-      <c r="C74" s="61" t="s">
+      <c r="E74" s="61" t="s">
         <v>603</v>
       </c>
-      <c r="D74" s="62" t="s">
+      <c r="F74" s="120" t="s">
         <v>604</v>
-      </c>
-      <c r="E74" s="61" t="s">
-        <v>605</v>
-      </c>
-      <c r="F74" s="120" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="30" customHeight="1">
       <c r="A75" s="108" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B75" s="89" t="s">
+        <v>904</v>
+      </c>
+      <c r="C75" s="90" t="s">
+        <v>905</v>
+      </c>
+      <c r="D75" s="90" t="s">
         <v>906</v>
       </c>
-      <c r="C75" s="90" t="s">
+      <c r="E75" s="90" t="s">
         <v>907</v>
       </c>
-      <c r="D75" s="90" t="s">
+      <c r="F75" s="123" t="s">
         <v>908</v>
-      </c>
-      <c r="E75" s="90" t="s">
-        <v>909</v>
-      </c>
-      <c r="F75" s="123" t="s">
-        <v>910</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="30" customHeight="1">
       <c r="A76" s="103" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B76" s="58" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C76" s="39" t="s">
+        <v>605</v>
+      </c>
+      <c r="D76" s="39" t="s">
+        <v>606</v>
+      </c>
+      <c r="E76" s="39" t="s">
         <v>607</v>
       </c>
-      <c r="D76" s="39" t="s">
+      <c r="F76" s="118" t="s">
         <v>608</v>
-      </c>
-      <c r="E76" s="39" t="s">
-        <v>609</v>
-      </c>
-      <c r="F76" s="118" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="42" customHeight="1">
       <c r="A77" s="104" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B77" s="59" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C77" s="47" t="s">
+        <v>609</v>
+      </c>
+      <c r="D77" s="47" t="s">
+        <v>610</v>
+      </c>
+      <c r="E77" s="47" t="s">
         <v>611</v>
       </c>
-      <c r="D77" s="47" t="s">
+      <c r="F77" s="119" t="s">
         <v>612</v>
-      </c>
-      <c r="E77" s="47" t="s">
-        <v>613</v>
-      </c>
-      <c r="F77" s="119" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="25.5" customHeight="1">
       <c r="A78" s="105" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B78" s="60" t="s">
+        <v>613</v>
+      </c>
+      <c r="C78" s="61" t="s">
+        <v>614</v>
+      </c>
+      <c r="D78" s="61" t="s">
         <v>615</v>
       </c>
-      <c r="C78" s="61" t="s">
+      <c r="E78" s="61" t="s">
         <v>616</v>
       </c>
-      <c r="D78" s="61" t="s">
+      <c r="F78" s="120" t="s">
         <v>617</v>
-      </c>
-      <c r="E78" s="61" t="s">
-        <v>618</v>
-      </c>
-      <c r="F78" s="120" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="30" customHeight="1">
       <c r="A79" s="98" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B79" s="53" t="s">
+        <v>618</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>619</v>
+      </c>
+      <c r="D79" s="5" t="s">
         <v>620</v>
       </c>
-      <c r="C79" s="5" t="s">
+      <c r="E79" s="5" t="s">
         <v>621</v>
       </c>
-      <c r="D79" s="5" t="s">
+      <c r="F79" s="86" t="s">
         <v>622</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>623</v>
-      </c>
-      <c r="F79" s="86" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="30" customHeight="1">
       <c r="A80" s="103" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B80" s="58" t="s">
+        <v>623</v>
+      </c>
+      <c r="C80" s="39" t="s">
+        <v>624</v>
+      </c>
+      <c r="D80" s="39" t="s">
         <v>625</v>
       </c>
-      <c r="C80" s="39" t="s">
+      <c r="E80" s="39" t="s">
         <v>626</v>
       </c>
-      <c r="D80" s="39" t="s">
+      <c r="F80" s="118" t="s">
         <v>627</v>
-      </c>
-      <c r="E80" s="39" t="s">
-        <v>628</v>
-      </c>
-      <c r="F80" s="118" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="42" customHeight="1">
       <c r="A81" s="105" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B81" s="60" t="s">
+        <v>628</v>
+      </c>
+      <c r="C81" s="61" t="s">
+        <v>629</v>
+      </c>
+      <c r="D81" s="61" t="s">
         <v>630</v>
       </c>
-      <c r="C81" s="61" t="s">
+      <c r="E81" s="61" t="s">
         <v>631</v>
       </c>
-      <c r="D81" s="61" t="s">
+      <c r="F81" s="120" t="s">
         <v>632</v>
-      </c>
-      <c r="E81" s="61" t="s">
-        <v>633</v>
-      </c>
-      <c r="F81" s="120" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="30" customHeight="1">
       <c r="A82" s="104" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B82" s="59" t="s">
+        <v>633</v>
+      </c>
+      <c r="C82" s="47" t="s">
+        <v>634</v>
+      </c>
+      <c r="D82" s="47" t="s">
         <v>635</v>
       </c>
-      <c r="C82" s="47" t="s">
+      <c r="E82" s="47" t="s">
+        <v>626</v>
+      </c>
+      <c r="F82" s="119" t="s">
         <v>636</v>
-      </c>
-      <c r="D82" s="47" t="s">
-        <v>637</v>
-      </c>
-      <c r="E82" s="47" t="s">
-        <v>628</v>
-      </c>
-      <c r="F82" s="119" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="21.75" customHeight="1">
       <c r="A83" s="106" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B83" s="63" t="s">
+        <v>637</v>
+      </c>
+      <c r="C83" s="20" t="s">
+        <v>638</v>
+      </c>
+      <c r="D83" s="20" t="s">
         <v>639</v>
       </c>
-      <c r="C83" s="20" t="s">
+      <c r="E83" s="20" t="s">
         <v>640</v>
       </c>
-      <c r="D83" s="20" t="s">
+      <c r="F83" s="121" t="s">
         <v>641</v>
-      </c>
-      <c r="E83" s="20" t="s">
-        <v>642</v>
-      </c>
-      <c r="F83" s="121" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="42" customHeight="1">
       <c r="A84" s="102" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B84" s="57" t="s">
+        <v>642</v>
+      </c>
+      <c r="C84" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="D84" s="33" t="s">
         <v>644</v>
       </c>
-      <c r="C84" s="33" t="s">
+      <c r="E84" s="33" t="s">
         <v>645</v>
-      </c>
-      <c r="D84" s="33" t="s">
-        <v>646</v>
-      </c>
-      <c r="E84" s="33" t="s">
-        <v>647</v>
       </c>
       <c r="F84" s="117" t="s">
         <v>33</v>
@@ -17897,59 +17929,59 @@
     </row>
     <row r="85" spans="1:6" ht="25.5" customHeight="1">
       <c r="A85" s="102" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B85" s="209" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C85" s="33" t="s">
+        <v>950</v>
+      </c>
+      <c r="D85" s="33" t="s">
+        <v>951</v>
+      </c>
+      <c r="E85" s="33" t="s">
+        <v>626</v>
+      </c>
+      <c r="F85" s="117" t="s">
         <v>952</v>
-      </c>
-      <c r="D85" s="33" t="s">
-        <v>953</v>
-      </c>
-      <c r="E85" s="33" t="s">
-        <v>628</v>
-      </c>
-      <c r="F85" s="117" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="25.5" customHeight="1">
       <c r="A86" s="107" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B86" s="64" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C86" s="36" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="D86" s="36" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E86" s="36" t="s">
         <v>209</v>
       </c>
       <c r="F86" s="122" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="30" customHeight="1">
       <c r="A87" s="101" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B87" s="56" t="s">
+        <v>648</v>
+      </c>
+      <c r="C87" s="10" t="s">
+        <v>649</v>
+      </c>
+      <c r="D87" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="C87" s="10" t="s">
-        <v>651</v>
-      </c>
-      <c r="D87" s="10" t="s">
-        <v>652</v>
-      </c>
       <c r="E87" s="10" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F87" s="116" t="s">
         <v>33</v>
@@ -17957,127 +17989,127 @@
     </row>
     <row r="88" spans="1:6" ht="25.5" customHeight="1">
       <c r="A88" s="101" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B88" s="56" t="s">
+        <v>594</v>
+      </c>
+      <c r="C88" s="10" t="s">
+        <v>651</v>
+      </c>
+      <c r="D88" s="10" t="s">
+        <v>652</v>
+      </c>
+      <c r="E88" s="10" t="s">
         <v>596</v>
       </c>
-      <c r="C88" s="10" t="s">
-        <v>653</v>
-      </c>
-      <c r="D88" s="10" t="s">
-        <v>654</v>
-      </c>
-      <c r="E88" s="10" t="s">
-        <v>598</v>
-      </c>
       <c r="F88" s="116" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="42" customHeight="1">
       <c r="A89" s="103" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B89" s="58" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C89" s="39" t="s">
+        <v>653</v>
+      </c>
+      <c r="D89" s="39" t="s">
+        <v>654</v>
+      </c>
+      <c r="E89" s="39" t="s">
+        <v>539</v>
+      </c>
+      <c r="F89" s="118" t="s">
         <v>655</v>
-      </c>
-      <c r="D89" s="39" t="s">
-        <v>656</v>
-      </c>
-      <c r="E89" s="39" t="s">
-        <v>541</v>
-      </c>
-      <c r="F89" s="118" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="30" customHeight="1">
       <c r="A90" s="103" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B90" s="58" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C90" s="39" t="s">
+        <v>656</v>
+      </c>
+      <c r="D90" s="39" t="s">
+        <v>657</v>
+      </c>
+      <c r="E90" s="39" t="s">
+        <v>539</v>
+      </c>
+      <c r="F90" s="118" t="s">
         <v>658</v>
-      </c>
-      <c r="D90" s="39" t="s">
-        <v>659</v>
-      </c>
-      <c r="E90" s="39" t="s">
-        <v>541</v>
-      </c>
-      <c r="F90" s="118" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="25.5" customHeight="1">
       <c r="A91" s="103" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B91" s="58" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C91" s="39" t="s">
+        <v>659</v>
+      </c>
+      <c r="D91" s="39" t="s">
+        <v>660</v>
+      </c>
+      <c r="E91" s="39" t="s">
+        <v>539</v>
+      </c>
+      <c r="F91" s="118" t="s">
         <v>661</v>
-      </c>
-      <c r="D91" s="39" t="s">
-        <v>662</v>
-      </c>
-      <c r="E91" s="39" t="s">
-        <v>541</v>
-      </c>
-      <c r="F91" s="118" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="25.5" customHeight="1">
       <c r="A92" s="108" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B92" s="89" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C92" s="90" t="s">
+        <v>909</v>
+      </c>
+      <c r="D92" s="95" t="s">
+        <v>910</v>
+      </c>
+      <c r="E92" s="90" t="s">
         <v>911</v>
       </c>
-      <c r="D92" s="95" t="s">
+      <c r="F92" s="123" t="s">
         <v>912</v>
-      </c>
-      <c r="E92" s="90" t="s">
-        <v>913</v>
-      </c>
-      <c r="F92" s="123" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="30" customHeight="1">
       <c r="A93" s="108" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B93" s="208" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C93" s="90" t="s">
+        <v>947</v>
+      </c>
+      <c r="D93" s="95" t="s">
+        <v>948</v>
+      </c>
+      <c r="E93" s="90" t="s">
+        <v>911</v>
+      </c>
+      <c r="F93" s="123" t="s">
         <v>949</v>
-      </c>
-      <c r="D93" s="95" t="s">
-        <v>950</v>
-      </c>
-      <c r="E93" s="90" t="s">
-        <v>913</v>
-      </c>
-      <c r="F93" s="123" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="30" customHeight="1">
       <c r="A94" s="155" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B94" s="156"/>
       <c r="C94" s="156"/>
@@ -18087,17 +18119,17 @@
     </row>
     <row r="95" spans="1:6" ht="42" customHeight="1">
       <c r="A95" s="101" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B95" s="56" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="D95" s="10"/>
       <c r="E95" s="10" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="F95" s="116" t="s">
         <v>33</v>
@@ -18105,79 +18137,79 @@
     </row>
     <row r="96" spans="1:6" ht="25.5" customHeight="1">
       <c r="A96" s="100" t="s">
+        <v>662</v>
+      </c>
+      <c r="B96" s="55" t="s">
+        <v>547</v>
+      </c>
+      <c r="C96" s="50" t="s">
         <v>664</v>
       </c>
-      <c r="B96" s="55" t="s">
-        <v>549</v>
-      </c>
-      <c r="C96" s="50" t="s">
+      <c r="D96" s="50" t="s">
+        <v>665</v>
+      </c>
+      <c r="E96" s="50" t="s">
+        <v>550</v>
+      </c>
+      <c r="F96" s="115" t="s">
         <v>666</v>
-      </c>
-      <c r="D96" s="50" t="s">
-        <v>667</v>
-      </c>
-      <c r="E96" s="50" t="s">
-        <v>552</v>
-      </c>
-      <c r="F96" s="115" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="45" customHeight="1">
       <c r="A97" s="100" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B97" s="55" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C97" s="50" t="s">
+        <v>667</v>
+      </c>
+      <c r="D97" s="50" t="s">
+        <v>668</v>
+      </c>
+      <c r="E97" s="50" t="s">
+        <v>555</v>
+      </c>
+      <c r="F97" s="115" t="s">
         <v>669</v>
-      </c>
-      <c r="D97" s="50" t="s">
-        <v>670</v>
-      </c>
-      <c r="E97" s="50" t="s">
-        <v>557</v>
-      </c>
-      <c r="F97" s="115" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="30" customHeight="1">
       <c r="A98" s="101" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B98" s="56" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C98" s="10" t="s">
+        <v>670</v>
+      </c>
+      <c r="D98" s="10" t="s">
+        <v>671</v>
+      </c>
+      <c r="E98" s="10" t="s">
         <v>672</v>
       </c>
-      <c r="D98" s="10" t="s">
+      <c r="F98" s="116" t="s">
         <v>673</v>
-      </c>
-      <c r="E98" s="10" t="s">
-        <v>674</v>
-      </c>
-      <c r="F98" s="116" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="21.75" customHeight="1">
       <c r="A99" s="99" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B99" s="54" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D99" s="15" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E99" s="15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F99" s="85" t="s">
         <v>131</v>
@@ -18185,740 +18217,780 @@
     </row>
     <row r="100" spans="1:6" ht="25.5" customHeight="1">
       <c r="A100" s="105" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B100" s="60" t="s">
+        <v>676</v>
+      </c>
+      <c r="C100" s="61" t="s">
+        <v>677</v>
+      </c>
+      <c r="D100" s="61" t="s">
         <v>678</v>
       </c>
-      <c r="C100" s="61" t="s">
+      <c r="E100" s="61" t="s">
         <v>679</v>
       </c>
-      <c r="D100" s="61" t="s">
+      <c r="F100" s="120" t="s">
         <v>680</v>
-      </c>
-      <c r="E100" s="61" t="s">
-        <v>681</v>
-      </c>
-      <c r="F100" s="120" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="42" customHeight="1">
       <c r="A101" s="105" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B101" s="60" t="s">
+        <v>681</v>
+      </c>
+      <c r="C101" s="61" t="s">
+        <v>682</v>
+      </c>
+      <c r="D101" s="61" t="s">
         <v>683</v>
       </c>
-      <c r="C101" s="61" t="s">
+      <c r="E101" s="61" t="s">
+        <v>603</v>
+      </c>
+      <c r="F101" s="120" t="s">
         <v>684</v>
-      </c>
-      <c r="D101" s="61" t="s">
-        <v>685</v>
-      </c>
-      <c r="E101" s="61" t="s">
-        <v>605</v>
-      </c>
-      <c r="F101" s="120" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="30" customHeight="1">
       <c r="A102" s="105" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B102" s="60" t="s">
+        <v>685</v>
+      </c>
+      <c r="C102" s="61" t="s">
+        <v>686</v>
+      </c>
+      <c r="D102" s="61" t="s">
         <v>687</v>
       </c>
-      <c r="C102" s="61" t="s">
+      <c r="E102" s="61" t="s">
         <v>688</v>
       </c>
-      <c r="D102" s="61" t="s">
+      <c r="F102" s="120" t="s">
         <v>689</v>
-      </c>
-      <c r="E102" s="61" t="s">
-        <v>690</v>
-      </c>
-      <c r="F102" s="120" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="45" customHeight="1">
       <c r="A103" s="106" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B103" s="63" t="s">
+        <v>690</v>
+      </c>
+      <c r="C103" s="20" t="s">
+        <v>691</v>
+      </c>
+      <c r="D103" s="20" t="s">
         <v>692</v>
       </c>
-      <c r="C103" s="20" t="s">
+      <c r="E103" s="20" t="s">
         <v>693</v>
       </c>
-      <c r="D103" s="20" t="s">
-        <v>694</v>
-      </c>
-      <c r="E103" s="20" t="s">
-        <v>695</v>
-      </c>
       <c r="F103" s="121" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="25.5" customHeight="1">
       <c r="A104" s="105" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B104" s="60" t="s">
+        <v>694</v>
+      </c>
+      <c r="C104" s="61" t="s">
+        <v>695</v>
+      </c>
+      <c r="D104" s="61" t="s">
         <v>696</v>
-      </c>
-      <c r="C104" s="61" t="s">
-        <v>697</v>
-      </c>
-      <c r="D104" s="61" t="s">
-        <v>698</v>
       </c>
       <c r="E104" s="61" t="s">
         <v>111</v>
       </c>
       <c r="F104" s="120" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="42" customHeight="1">
       <c r="A105" s="105" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B105" s="207" t="s">
+        <v>702</v>
+      </c>
+      <c r="C105" s="61" t="s">
+        <v>945</v>
+      </c>
+      <c r="D105" s="61" t="s">
+        <v>946</v>
+      </c>
+      <c r="E105" s="61" t="s">
+        <v>626</v>
+      </c>
+      <c r="F105" s="120" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="130" customHeight="1">
+      <c r="A106" s="105" t="s">
+        <v>662</v>
+      </c>
+      <c r="B106" s="207" t="s">
+        <v>702</v>
+      </c>
+      <c r="C106" s="61" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D106" s="61" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E106" s="61" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F106" s="120" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="30" customHeight="1">
+      <c r="A107" s="109" t="s">
+        <v>662</v>
+      </c>
+      <c r="B107" s="65" t="s">
+        <v>697</v>
+      </c>
+      <c r="C107" s="42" t="s">
+        <v>698</v>
+      </c>
+      <c r="D107" s="42" t="s">
+        <v>699</v>
+      </c>
+      <c r="E107" s="42" t="s">
+        <v>700</v>
+      </c>
+      <c r="F107" s="124" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A108" s="111" t="s">
+        <v>662</v>
+      </c>
+      <c r="B108" s="93" t="s">
+        <v>913</v>
+      </c>
+      <c r="C108" s="94" t="s">
+        <v>914</v>
+      </c>
+      <c r="D108" s="94" t="s">
+        <v>915</v>
+      </c>
+      <c r="E108" s="94" t="s">
+        <v>916</v>
+      </c>
+      <c r="F108" s="126" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A109" s="101" t="s">
+        <v>662</v>
+      </c>
+      <c r="B109" s="128" t="s">
+        <v>923</v>
+      </c>
+      <c r="C109" s="10" t="s">
+        <v>922</v>
+      </c>
+      <c r="D109" s="10"/>
+      <c r="E109" s="10" t="s">
+        <v>596</v>
+      </c>
+      <c r="F109" s="116" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="30" customHeight="1">
+      <c r="A110" s="102" t="s">
+        <v>662</v>
+      </c>
+      <c r="B110" s="57" t="s">
+        <v>702</v>
+      </c>
+      <c r="C110" s="33" t="s">
+        <v>703</v>
+      </c>
+      <c r="D110" s="33" t="s">
         <v>704</v>
       </c>
-      <c r="C105" s="61" t="s">
-        <v>947</v>
-      </c>
-      <c r="D105" s="61" t="s">
-        <v>948</v>
-      </c>
-      <c r="E105" s="61" t="s">
-        <v>628</v>
-      </c>
-      <c r="F105" s="120" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" ht="42" customHeight="1">
-      <c r="A106" s="109" t="s">
-        <v>664</v>
-      </c>
-      <c r="B106" s="65" t="s">
-        <v>699</v>
-      </c>
-      <c r="C106" s="42" t="s">
-        <v>700</v>
-      </c>
-      <c r="D106" s="42" t="s">
-        <v>701</v>
-      </c>
-      <c r="E106" s="42" t="s">
+      <c r="E110" s="33" t="s">
+        <v>532</v>
+      </c>
+      <c r="F110" s="117" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A111" s="103" t="s">
+        <v>662</v>
+      </c>
+      <c r="B111" s="58" t="s">
         <v>702</v>
       </c>
-      <c r="F106" s="124" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" ht="30" customHeight="1">
-      <c r="A107" s="111" t="s">
-        <v>664</v>
-      </c>
-      <c r="B107" s="93" t="s">
-        <v>915</v>
-      </c>
-      <c r="C107" s="94" t="s">
-        <v>916</v>
-      </c>
-      <c r="D107" s="94" t="s">
-        <v>917</v>
-      </c>
-      <c r="E107" s="94" t="s">
-        <v>918</v>
-      </c>
-      <c r="F107" s="126" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A108" s="101" t="s">
-        <v>664</v>
-      </c>
-      <c r="B108" s="128" t="s">
-        <v>925</v>
-      </c>
-      <c r="C108" s="10" t="s">
-        <v>924</v>
-      </c>
-      <c r="D108" s="10"/>
-      <c r="E108" s="10" t="s">
+      <c r="C111" s="39" t="s">
+        <v>968</v>
+      </c>
+      <c r="D111" s="39" t="s">
+        <v>969</v>
+      </c>
+      <c r="E111" s="39" t="s">
+        <v>532</v>
+      </c>
+      <c r="F111" s="118" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="42" customHeight="1">
+      <c r="A112" s="155" t="s">
+        <v>975</v>
+      </c>
+      <c r="B112" s="156"/>
+      <c r="C112" s="156"/>
+      <c r="D112" s="156"/>
+      <c r="E112" s="156"/>
+      <c r="F112" s="157"/>
+    </row>
+    <row r="113" spans="1:6" ht="45" customHeight="1">
+      <c r="A113" s="101" t="s">
+        <v>705</v>
+      </c>
+      <c r="B113" s="56" t="s">
+        <v>493</v>
+      </c>
+      <c r="C113" s="10" t="s">
         <v>598</v>
       </c>
-      <c r="F108" s="116" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A109" s="102" t="s">
-        <v>664</v>
-      </c>
-      <c r="B109" s="57" t="s">
-        <v>704</v>
-      </c>
-      <c r="C109" s="33" t="s">
-        <v>705</v>
-      </c>
-      <c r="D109" s="33" t="s">
+      <c r="D113" s="10" t="s">
         <v>706</v>
       </c>
-      <c r="E109" s="33" t="s">
-        <v>534</v>
-      </c>
-      <c r="F109" s="117" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" ht="30" customHeight="1">
-      <c r="A110" s="103" t="s">
-        <v>664</v>
-      </c>
-      <c r="B110" s="58" t="s">
-        <v>704</v>
-      </c>
-      <c r="C110" s="39" t="s">
-        <v>970</v>
-      </c>
-      <c r="D110" s="39" t="s">
-        <v>971</v>
-      </c>
-      <c r="E110" s="39" t="s">
-        <v>534</v>
-      </c>
-      <c r="F110" s="118" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A111" s="155" t="s">
-        <v>977</v>
-      </c>
-      <c r="B111" s="156"/>
-      <c r="C111" s="156"/>
-      <c r="D111" s="156"/>
-      <c r="E111" s="156"/>
-      <c r="F111" s="157"/>
-    </row>
-    <row r="112" spans="1:6" ht="42" customHeight="1">
-      <c r="A112" s="101" t="s">
-        <v>707</v>
-      </c>
-      <c r="B112" s="56" t="s">
-        <v>495</v>
-      </c>
-      <c r="C112" s="10" t="s">
-        <v>600</v>
-      </c>
-      <c r="D112" s="10" t="s">
-        <v>708</v>
-      </c>
-      <c r="E112" s="10" t="s">
+      <c r="E113" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F112" s="116" t="s">
+      <c r="F113" s="116" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" ht="45" customHeight="1">
-      <c r="A113" s="105" t="s">
-        <v>707</v>
-      </c>
-      <c r="B113" s="60" t="s">
-        <v>497</v>
-      </c>
-      <c r="C113" s="61" t="s">
-        <v>709</v>
-      </c>
-      <c r="D113" s="61" t="s">
-        <v>710</v>
-      </c>
-      <c r="E113" s="61" t="s">
-        <v>500</v>
-      </c>
-      <c r="F113" s="120" t="s">
-        <v>711</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="25.5" customHeight="1">
       <c r="A114" s="105" t="s">
+        <v>705</v>
+      </c>
+      <c r="B114" s="60" t="s">
+        <v>495</v>
+      </c>
+      <c r="C114" s="61" t="s">
         <v>707</v>
       </c>
-      <c r="B114" s="60" t="s">
-        <v>712</v>
-      </c>
-      <c r="C114" s="61" t="s">
-        <v>713</v>
-      </c>
       <c r="D114" s="61" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="E114" s="61" t="s">
-        <v>715</v>
+        <v>498</v>
       </c>
       <c r="F114" s="120" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="21.75" customHeight="1">
       <c r="A115" s="105" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B115" s="60" t="s">
-        <v>615</v>
+        <v>710</v>
       </c>
       <c r="C115" s="61" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="D115" s="61" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="E115" s="61" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="F115" s="120" t="s">
-        <v>363</v>
+        <v>714</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="25.5" customHeight="1">
       <c r="A116" s="105" t="s">
-        <v>707</v>
-      </c>
-      <c r="B116" s="207" t="s">
-        <v>704</v>
+        <v>705</v>
+      </c>
+      <c r="B116" s="60" t="s">
+        <v>613</v>
       </c>
       <c r="C116" s="61" t="s">
+        <v>715</v>
+      </c>
+      <c r="D116" s="61" t="s">
+        <v>716</v>
+      </c>
+      <c r="E116" s="61" t="s">
+        <v>717</v>
+      </c>
+      <c r="F116" s="120" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A117" s="105" t="s">
+        <v>705</v>
+      </c>
+      <c r="B117" s="207" t="s">
+        <v>702</v>
+      </c>
+      <c r="C117" s="61" t="s">
+        <v>941</v>
+      </c>
+      <c r="D117" s="61" t="s">
+        <v>942</v>
+      </c>
+      <c r="E117" s="61" t="s">
         <v>943</v>
       </c>
-      <c r="D116" s="61" t="s">
+      <c r="F117" s="120" t="s">
         <v>944</v>
       </c>
-      <c r="E116" s="61" t="s">
-        <v>945</v>
-      </c>
-      <c r="F116" s="120" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A117" s="98" t="s">
-        <v>707</v>
-      </c>
-      <c r="B117" s="53" t="s">
+    </row>
+    <row r="118" spans="1:6" ht="30" customHeight="1">
+      <c r="A118" s="98" t="s">
+        <v>705</v>
+      </c>
+      <c r="B118" s="53" t="s">
+        <v>718</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>719</v>
+      </c>
+      <c r="D118" s="5" t="s">
         <v>720</v>
       </c>
-      <c r="C117" s="5" t="s">
+      <c r="E118" s="5" t="s">
         <v>721</v>
       </c>
-      <c r="D117" s="5" t="s">
+      <c r="F118" s="86" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A119" s="102" t="s">
+        <v>705</v>
+      </c>
+      <c r="B119" s="57" t="s">
+        <v>623</v>
+      </c>
+      <c r="C119" s="33" t="s">
         <v>722</v>
       </c>
-      <c r="E117" s="5" t="s">
+      <c r="D119" s="33" t="s">
         <v>723</v>
       </c>
-      <c r="F117" s="86" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" ht="30" customHeight="1">
-      <c r="A118" s="102" t="s">
-        <v>707</v>
-      </c>
-      <c r="B118" s="57" t="s">
-        <v>625</v>
-      </c>
-      <c r="C118" s="33" t="s">
+      <c r="E119" s="33" t="s">
         <v>724</v>
       </c>
-      <c r="D118" s="33" t="s">
+      <c r="F119" s="117" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="30" customHeight="1">
+      <c r="A120" s="105" t="s">
+        <v>705</v>
+      </c>
+      <c r="B120" s="60" t="s">
         <v>725</v>
       </c>
-      <c r="E118" s="33" t="s">
+      <c r="C120" s="61" t="s">
         <v>726</v>
       </c>
-      <c r="F118" s="117" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A119" s="105" t="s">
-        <v>707</v>
-      </c>
-      <c r="B119" s="60" t="s">
+      <c r="D120" s="61" t="s">
         <v>727</v>
       </c>
-      <c r="C119" s="61" t="s">
+      <c r="E120" s="61" t="s">
+        <v>478</v>
+      </c>
+      <c r="F120" s="120" t="s">
         <v>728</v>
       </c>
-      <c r="D119" s="61" t="s">
+    </row>
+    <row r="121" spans="1:6" ht="25.5" customHeight="1">
+      <c r="A121" s="106" t="s">
+        <v>705</v>
+      </c>
+      <c r="B121" s="63" t="s">
         <v>729</v>
       </c>
-      <c r="E119" s="61" t="s">
-        <v>480</v>
-      </c>
-      <c r="F119" s="120" t="s">
+      <c r="C121" s="20" t="s">
         <v>730</v>
       </c>
-    </row>
-    <row r="120" spans="1:6" ht="30" customHeight="1">
-      <c r="A120" s="106" t="s">
-        <v>707</v>
-      </c>
-      <c r="B120" s="63" t="s">
+      <c r="D121" s="20" t="s">
         <v>731</v>
       </c>
-      <c r="C120" s="20" t="s">
+      <c r="E121" s="20" t="s">
+        <v>527</v>
+      </c>
+      <c r="F121" s="121" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="110" customHeight="1">
+      <c r="A122" s="109" t="s">
+        <v>705</v>
+      </c>
+      <c r="B122" s="65" t="s">
+        <v>577</v>
+      </c>
+      <c r="C122" s="42" t="s">
         <v>732</v>
       </c>
-      <c r="D120" s="20" t="s">
+      <c r="D122" s="42" t="s">
         <v>733</v>
       </c>
-      <c r="E120" s="20" t="s">
-        <v>529</v>
-      </c>
-      <c r="F120" s="121" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" ht="25.5" customHeight="1">
-      <c r="A121" s="109" t="s">
-        <v>707</v>
-      </c>
-      <c r="B121" s="65" t="s">
-        <v>579</v>
-      </c>
-      <c r="C121" s="42" t="s">
+      <c r="E122" s="42" t="s">
         <v>734</v>
       </c>
-      <c r="D121" s="42" t="s">
+      <c r="F122" s="124" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="42" customHeight="1">
+      <c r="A123" s="99" t="s">
+        <v>705</v>
+      </c>
+      <c r="B123" s="54" t="s">
         <v>735</v>
       </c>
-      <c r="E121" s="42" t="s">
+      <c r="C123" s="15" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D123" s="15" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E123" s="15" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F123" s="85" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" ht="30" customHeight="1">
+      <c r="A124" s="103" t="s">
+        <v>705</v>
+      </c>
+      <c r="B124" s="58" t="s">
         <v>736</v>
       </c>
-      <c r="F121" s="124" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" ht="110" customHeight="1">
-      <c r="A122" s="99" t="s">
-        <v>707</v>
-      </c>
-      <c r="B122" s="54" t="s">
+      <c r="C124" s="39" t="s">
         <v>737</v>
       </c>
-      <c r="C122" s="15" t="s">
-        <v>1066</v>
-      </c>
-      <c r="D122" s="15" t="s">
-        <v>1067</v>
-      </c>
-      <c r="E122" s="15" t="s">
-        <v>1068</v>
-      </c>
-      <c r="F122" s="85" t="s">
-        <v>1069</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" ht="42" customHeight="1">
-      <c r="A123" s="103" t="s">
-        <v>707</v>
-      </c>
-      <c r="B123" s="58" t="s">
+      <c r="D124" s="39" t="s">
         <v>738</v>
       </c>
-      <c r="C123" s="39" t="s">
+      <c r="E124" s="39" t="s">
         <v>739</v>
       </c>
-      <c r="D123" s="39" t="s">
+      <c r="F124" s="118" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="28">
+      <c r="A125" s="101" t="s">
+        <v>705</v>
+      </c>
+      <c r="B125" s="56" t="s">
         <v>740</v>
       </c>
-      <c r="E123" s="39" t="s">
+      <c r="C125" s="10" t="s">
         <v>741</v>
       </c>
-      <c r="F123" s="118" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" ht="30" customHeight="1">
-      <c r="A124" s="101" t="s">
-        <v>707</v>
-      </c>
-      <c r="B124" s="56" t="s">
+      <c r="D125" s="10" t="s">
         <v>742</v>
       </c>
-      <c r="C124" s="10" t="s">
-        <v>743</v>
-      </c>
-      <c r="D124" s="10" t="s">
-        <v>744</v>
-      </c>
-      <c r="E124" s="10" t="s">
-        <v>598</v>
-      </c>
-      <c r="F124" s="116" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" ht="28">
-      <c r="A125" s="103" t="s">
-        <v>707</v>
-      </c>
-      <c r="B125" s="58" t="s">
-        <v>538</v>
-      </c>
-      <c r="C125" s="39" t="s">
-        <v>745</v>
-      </c>
-      <c r="D125" s="39" t="s">
-        <v>746</v>
-      </c>
-      <c r="E125" s="39" t="s">
-        <v>541</v>
-      </c>
-      <c r="F125" s="118" t="s">
-        <v>351</v>
+      <c r="E125" s="10" t="s">
+        <v>596</v>
+      </c>
+      <c r="F125" s="116" t="s">
+        <v>673</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="28">
       <c r="A126" s="103" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B126" s="58" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C126" s="39" t="s">
+        <v>743</v>
+      </c>
+      <c r="D126" s="39" t="s">
+        <v>744</v>
+      </c>
+      <c r="E126" s="39" t="s">
+        <v>539</v>
+      </c>
+      <c r="F126" s="118" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="150" customHeight="1">
+      <c r="A127" s="103" t="s">
+        <v>705</v>
+      </c>
+      <c r="B127" s="58" t="s">
+        <v>536</v>
+      </c>
+      <c r="C127" s="39" t="s">
+        <v>745</v>
+      </c>
+      <c r="D127" s="39" t="s">
+        <v>746</v>
+      </c>
+      <c r="E127" s="39" t="s">
+        <v>539</v>
+      </c>
+      <c r="F127" s="118" t="s">
         <v>747</v>
       </c>
-      <c r="D126" s="39" t="s">
+    </row>
+    <row r="128" spans="1:6" ht="238">
+      <c r="A128" s="103" t="s">
+        <v>705</v>
+      </c>
+      <c r="B128" s="210" t="s">
+        <v>536</v>
+      </c>
+      <c r="C128" s="39" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D128" s="39" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E128" s="39" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F128" s="118" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="31">
+      <c r="A129" s="104" t="s">
+        <v>705</v>
+      </c>
+      <c r="B129" s="59" t="s">
+        <v>536</v>
+      </c>
+      <c r="C129" s="47" t="s">
+        <v>971</v>
+      </c>
+      <c r="D129" s="47" t="s">
+        <v>972</v>
+      </c>
+      <c r="E129" s="47" t="s">
+        <v>539</v>
+      </c>
+      <c r="F129" s="119" t="s">
         <v>748</v>
       </c>
-      <c r="E126" s="39" t="s">
-        <v>541</v>
-      </c>
-      <c r="F126" s="118" t="s">
+    </row>
+    <row r="130" spans="1:6">
+      <c r="A130" s="158" t="s">
         <v>749</v>
       </c>
-    </row>
-    <row r="127" spans="1:6" ht="31">
-      <c r="A127" s="104" t="s">
-        <v>707</v>
-      </c>
-      <c r="B127" s="59" t="s">
-        <v>538</v>
-      </c>
-      <c r="C127" s="47" t="s">
-        <v>973</v>
-      </c>
-      <c r="D127" s="47" t="s">
-        <v>974</v>
-      </c>
-      <c r="E127" s="47" t="s">
-        <v>541</v>
-      </c>
-      <c r="F127" s="119" t="s">
+      <c r="B130" s="159"/>
+      <c r="C130" s="159"/>
+      <c r="D130" s="159"/>
+      <c r="E130" s="159"/>
+      <c r="F130" s="160"/>
+    </row>
+    <row r="131" spans="1:6" ht="28">
+      <c r="A131" s="101" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128" s="158" t="s">
+      <c r="B131" s="56" t="s">
         <v>751</v>
       </c>
-      <c r="B128" s="159"/>
-      <c r="C128" s="159"/>
-      <c r="D128" s="159"/>
-      <c r="E128" s="159"/>
-      <c r="F128" s="160"/>
-    </row>
-    <row r="129" spans="1:6" ht="28">
-      <c r="A129" s="101" t="s">
+      <c r="C131" s="10" t="s">
+        <v>663</v>
+      </c>
+      <c r="D131" s="10" t="s">
         <v>752</v>
       </c>
-      <c r="B129" s="56" t="s">
-        <v>753</v>
-      </c>
-      <c r="C129" s="10" t="s">
-        <v>665</v>
-      </c>
-      <c r="D129" s="10" t="s">
-        <v>754</v>
-      </c>
-      <c r="E129" s="10" t="s">
-        <v>548</v>
-      </c>
-      <c r="F129" s="116" t="s">
+      <c r="E131" s="10" t="s">
+        <v>546</v>
+      </c>
+      <c r="F131" s="116" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" ht="28">
-      <c r="A130" s="100" t="s">
-        <v>752</v>
-      </c>
-      <c r="B130" s="55" t="s">
-        <v>755</v>
-      </c>
-      <c r="C130" s="50" t="s">
-        <v>756</v>
-      </c>
-      <c r="D130" s="50" t="s">
-        <v>757</v>
-      </c>
-      <c r="E130" s="50" t="s">
-        <v>674</v>
-      </c>
-      <c r="F130" s="115" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" ht="28">
-      <c r="A131" s="100" t="s">
-        <v>752</v>
-      </c>
-      <c r="B131" s="55" t="s">
-        <v>759</v>
-      </c>
-      <c r="C131" s="50" t="s">
-        <v>760</v>
-      </c>
-      <c r="D131" s="50" t="s">
-        <v>761</v>
-      </c>
-      <c r="E131" s="50" t="s">
-        <v>762</v>
-      </c>
-      <c r="F131" s="115" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="28">
       <c r="A132" s="100" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B132" s="55" t="s">
+        <v>753</v>
+      </c>
+      <c r="C132" s="50" t="s">
+        <v>754</v>
+      </c>
+      <c r="D132" s="50" t="s">
+        <v>755</v>
+      </c>
+      <c r="E132" s="50" t="s">
+        <v>672</v>
+      </c>
+      <c r="F132" s="115" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="28">
+      <c r="A133" s="100" t="s">
+        <v>750</v>
+      </c>
+      <c r="B133" s="55" t="s">
+        <v>757</v>
+      </c>
+      <c r="C133" s="50" t="s">
+        <v>758</v>
+      </c>
+      <c r="D133" s="50" t="s">
+        <v>759</v>
+      </c>
+      <c r="E133" s="50" t="s">
+        <v>760</v>
+      </c>
+      <c r="F133" s="115" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" ht="28">
+      <c r="A134" s="100" t="s">
+        <v>750</v>
+      </c>
+      <c r="B134" s="55" t="s">
+        <v>761</v>
+      </c>
+      <c r="C134" s="50" t="s">
+        <v>762</v>
+      </c>
+      <c r="D134" s="50" t="s">
         <v>763</v>
       </c>
-      <c r="C132" s="50" t="s">
+      <c r="E134" s="50" t="s">
         <v>764</v>
       </c>
-      <c r="D132" s="50" t="s">
+      <c r="F134" s="115" t="s">
         <v>765</v>
-      </c>
-      <c r="E132" s="50" t="s">
-        <v>766</v>
-      </c>
-      <c r="F132" s="115" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" ht="28">
-      <c r="A133" s="99" t="s">
-        <v>752</v>
-      </c>
-      <c r="B133" s="54" t="s">
-        <v>768</v>
-      </c>
-      <c r="C133" s="15" t="s">
-        <v>769</v>
-      </c>
-      <c r="D133" s="15" t="s">
-        <v>770</v>
-      </c>
-      <c r="E133" s="15" t="s">
-        <v>405</v>
-      </c>
-      <c r="F133" s="85" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" ht="28">
-      <c r="A134" s="98" t="s">
-        <v>752</v>
-      </c>
-      <c r="B134" s="53" t="s">
-        <v>771</v>
-      </c>
-      <c r="C134" s="5" t="s">
-        <v>772</v>
-      </c>
-      <c r="D134" s="5" t="s">
-        <v>773</v>
-      </c>
-      <c r="E134" s="5" t="s">
-        <v>774</v>
-      </c>
-      <c r="F134" s="114" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="28">
       <c r="A135" s="99" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B135" s="54" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
       <c r="C135" s="15" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
       <c r="D135" s="15" t="s">
-        <v>777</v>
+        <v>768</v>
       </c>
       <c r="E135" s="15" t="s">
-        <v>778</v>
-      </c>
-      <c r="F135" s="113" t="s">
-        <v>766</v>
+        <v>403</v>
+      </c>
+      <c r="F135" s="85" t="s">
+        <v>765</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="28">
       <c r="A136" s="98" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B136" s="53" t="s">
+        <v>769</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>770</v>
+      </c>
+      <c r="D136" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="E136" s="5" t="s">
+        <v>772</v>
+      </c>
+      <c r="F136" s="114" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="28">
+      <c r="A137" s="99" t="s">
+        <v>750</v>
+      </c>
+      <c r="B137" s="54" t="s">
+        <v>773</v>
+      </c>
+      <c r="C137" s="15" t="s">
+        <v>774</v>
+      </c>
+      <c r="D137" s="15" t="s">
+        <v>775</v>
+      </c>
+      <c r="E137" s="15" t="s">
+        <v>776</v>
+      </c>
+      <c r="F137" s="113" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="28">
+      <c r="A138" s="98" t="s">
+        <v>750</v>
+      </c>
+      <c r="B138" s="53" t="s">
+        <v>777</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>778</v>
+      </c>
+      <c r="D138" s="5" t="s">
         <v>779</v>
       </c>
-      <c r="C136" s="5" t="s">
+      <c r="E138" s="5" t="s">
         <v>780</v>
       </c>
-      <c r="D136" s="5" t="s">
+      <c r="F138" s="114" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" ht="29" thickBot="1">
+      <c r="A139" s="112" t="s">
+        <v>750</v>
+      </c>
+      <c r="B139" s="96" t="s">
+        <v>490</v>
+      </c>
+      <c r="C139" s="97" t="s">
         <v>781</v>
       </c>
-      <c r="E136" s="5" t="s">
+      <c r="D139" s="97" t="s">
         <v>782</v>
       </c>
-      <c r="F136" s="114" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" ht="29" thickBot="1">
-      <c r="A137" s="112" t="s">
-        <v>752</v>
-      </c>
-      <c r="B137" s="96" t="s">
-        <v>492</v>
-      </c>
-      <c r="C137" s="97" t="s">
+      <c r="E139" s="97" t="s">
         <v>783</v>
       </c>
-      <c r="D137" s="97" t="s">
+      <c r="F139" s="127" t="s">
         <v>784</v>
-      </c>
-      <c r="E137" s="97" t="s">
-        <v>785</v>
-      </c>
-      <c r="F137" s="127" t="s">
-        <v>786</v>
       </c>
     </row>
   </sheetData>
@@ -18931,8 +19003,8 @@
     <mergeCell ref="A57:F57"/>
     <mergeCell ref="A72:F72"/>
     <mergeCell ref="A94:F94"/>
-    <mergeCell ref="A111:F111"/>
-    <mergeCell ref="A128:F128"/>
+    <mergeCell ref="A112:F112"/>
+    <mergeCell ref="A130:F130"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -18944,7 +19016,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -19045,7 +19117,7 @@
         <v>62</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>64</v>
@@ -19062,13 +19134,13 @@
         <v>53</v>
       </c>
       <c r="B9" s="69" t="s">
+        <v>785</v>
+      </c>
+      <c r="C9" s="67" t="s">
+        <v>786</v>
+      </c>
+      <c r="D9" s="66" t="s">
         <v>787</v>
-      </c>
-      <c r="C9" s="67" t="s">
-        <v>788</v>
-      </c>
-      <c r="D9" s="66" t="s">
-        <v>789</v>
       </c>
       <c r="E9" s="68" t="s">
         <v>184</v>
@@ -19079,13 +19151,13 @@
         <v>53</v>
       </c>
       <c r="B10" s="69" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C10" s="67" t="s">
         <v>206</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="E10" s="68" t="s">
         <v>61</v>
@@ -19130,30 +19202,30 @@
         <v>67</v>
       </c>
       <c r="B13" s="20" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E13" s="23" t="s">
         <v>1043</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>1038</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>1044</v>
-      </c>
-      <c r="E13" s="23" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="42" customHeight="1">
       <c r="A14" s="20" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D14" s="20" t="s">
         <v>1046</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>1042</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>1048</v>
       </c>
       <c r="E14" s="23" t="s">
         <v>71</v>
@@ -19161,19 +19233,19 @@
     </row>
     <row r="15" spans="1:5" ht="56" customHeight="1">
       <c r="A15" s="20" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D15" s="20" t="s">
         <v>1054</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="E15" s="23" t="s">
         <v>1055</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>1053</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>1056</v>
-      </c>
-      <c r="E15" s="23" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="70" customHeight="1">
@@ -19181,16 +19253,16 @@
         <v>90</v>
       </c>
       <c r="B16" s="20" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D16" s="20" t="s">
         <v>1062</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="E16" s="23" t="s">
         <v>1063</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="30" customHeight="1"/>
@@ -19310,16 +19382,16 @@
         <v>90</v>
       </c>
       <c r="B25" s="66" t="s">
+        <v>790</v>
+      </c>
+      <c r="C25" s="67" t="s">
+        <v>791</v>
+      </c>
+      <c r="D25" s="66" t="s">
         <v>792</v>
       </c>
-      <c r="C25" s="67" t="s">
-        <v>793</v>
-      </c>
-      <c r="D25" s="66" t="s">
-        <v>794</v>
-      </c>
       <c r="E25" s="68" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="30" customHeight="1">
@@ -19507,13 +19579,13 @@
         <v>67</v>
       </c>
       <c r="B38" s="73" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C38" s="71" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D38" s="70" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="E38" s="72" t="s">
         <v>103</v>
@@ -19538,19 +19610,70 @@
     </row>
     <row r="40" spans="1:5" ht="110" customHeight="1">
       <c r="A40" s="20" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C40" s="22" t="s">
         <v>1070</v>
       </c>
-      <c r="B40" s="21" t="s">
+      <c r="D40" s="20" t="s">
         <v>1071</v>
       </c>
-      <c r="C40" s="22" t="s">
+      <c r="E40" s="23" t="s">
         <v>1072</v>
       </c>
-      <c r="D40" s="20" t="s">
-        <v>1073</v>
-      </c>
-      <c r="E40" s="23" t="s">
-        <v>1074</v>
+    </row>
+    <row r="41" spans="1:5" ht="130" customHeight="1">
+      <c r="A41" s="20" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C41" s="22" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D41" s="20" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E41" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="150" customHeight="1">
+      <c r="A42" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C42" s="22" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D42" s="20" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E42" s="23" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="168">
+      <c r="A43" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C43" s="22" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D43" s="20" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E43" s="23" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -19583,7 +19706,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
       <c r="A1" s="191" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="B1" s="192"/>
       <c r="C1" s="192"/>
@@ -19593,7 +19716,7 @@
     </row>
     <row r="2" spans="1:6" ht="45" customHeight="1">
       <c r="A2" s="194" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="B2" s="195"/>
       <c r="C2" s="195"/>
@@ -19693,19 +19816,19 @@
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1">
       <c r="A8" s="81" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B8" s="75">
         <v>4.5</v>
       </c>
       <c r="C8" s="76" t="s">
+        <v>796</v>
+      </c>
+      <c r="D8" s="75" t="s">
+        <v>797</v>
+      </c>
+      <c r="E8" s="76" t="s">
         <v>798</v>
-      </c>
-      <c r="D8" s="75" t="s">
-        <v>799</v>
-      </c>
-      <c r="E8" s="76" t="s">
-        <v>800</v>
       </c>
       <c r="F8" s="87" t="s">
         <v>152</v>
@@ -19713,19 +19836,19 @@
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1">
       <c r="A9" s="82" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B9" s="68">
         <v>4.5</v>
       </c>
       <c r="C9" s="66" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="D9" s="68" t="s">
         <v>107</v>
       </c>
       <c r="E9" s="66" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="F9" s="88" t="s">
         <v>152</v>
@@ -19755,7 +19878,7 @@
         <v>57</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="F11" s="84" t="s">
         <v>164</v>
@@ -19803,82 +19926,82 @@
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1">
       <c r="A14" s="81" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B14" s="75">
         <v>4.8</v>
       </c>
       <c r="C14" s="76" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="D14" s="75" t="s">
         <v>66</v>
       </c>
       <c r="E14" s="76" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="F14" s="87" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="30" customHeight="1">
       <c r="A15" s="82" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B15" s="68">
         <v>4.5999999999999996</v>
       </c>
       <c r="C15" s="66" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="D15" s="68" t="s">
         <v>111</v>
       </c>
       <c r="E15" s="66" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="F15" s="88" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="30" customHeight="1">
       <c r="A16" s="82" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B16" s="216" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C16" s="66" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D16" s="68" t="s">
+        <v>797</v>
+      </c>
+      <c r="E16" s="66" t="s">
         <v>1025</v>
       </c>
-      <c r="C16" s="66" t="s">
-        <v>1026</v>
-      </c>
-      <c r="D16" s="68" t="s">
-        <v>799</v>
-      </c>
-      <c r="E16" s="66" t="s">
-        <v>1027</v>
-      </c>
       <c r="F16" s="88" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1">
       <c r="A17" s="82" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B17" s="216" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C17" s="66" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D17" s="68" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E17" s="66" t="s">
         <v>1028</v>
       </c>
-      <c r="C17" s="66" t="s">
-        <v>1029</v>
-      </c>
-      <c r="D17" s="68" t="s">
-        <v>1014</v>
-      </c>
-      <c r="E17" s="66" t="s">
-        <v>1030</v>
-      </c>
       <c r="F17" s="88" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1">
@@ -19959,36 +20082,36 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C22" s="76" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="D22" s="75" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E22" s="76" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="F22" s="87" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1">
       <c r="A23" s="82" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B23" s="68">
         <v>4.3</v>
       </c>
       <c r="C23" s="66" t="s">
+        <v>803</v>
+      </c>
+      <c r="D23" s="68" t="s">
+        <v>254</v>
+      </c>
+      <c r="E23" s="66" t="s">
+        <v>804</v>
+      </c>
+      <c r="F23" s="88" t="s">
         <v>805</v>
-      </c>
-      <c r="D23" s="68" t="s">
-        <v>256</v>
-      </c>
-      <c r="E23" s="66" t="s">
-        <v>806</v>
-      </c>
-      <c r="F23" s="88" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1">
@@ -20063,42 +20186,42 @@
     </row>
     <row r="28" spans="1:6" ht="19.5" customHeight="1">
       <c r="A28" s="81" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B28" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C28" s="76" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D28" s="75" t="s">
         <v>160</v>
       </c>
       <c r="E28" s="76" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="F28" s="87" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="30" customHeight="1">
       <c r="A29" s="82" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B29" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C29" s="66" t="s">
+        <v>839</v>
+      </c>
+      <c r="D29" s="68" t="s">
+        <v>218</v>
+      </c>
+      <c r="E29" s="66" t="s">
+        <v>840</v>
+      </c>
+      <c r="F29" s="88" t="s">
         <v>841</v>
-      </c>
-      <c r="D29" s="68" t="s">
-        <v>219</v>
-      </c>
-      <c r="E29" s="66" t="s">
-        <v>842</v>
-      </c>
-      <c r="F29" s="88" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="30" customHeight="1">
@@ -20159,33 +20282,33 @@
         <v>4.3</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="F33" s="86" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="19.5" customHeight="1">
       <c r="A34" s="81" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B34" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C34" s="76" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="D34" s="75" t="s">
         <v>166</v>
       </c>
       <c r="E34" s="76" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="F34" s="87" t="s">
         <v>206</v>
@@ -20193,22 +20316,22 @@
     </row>
     <row r="35" spans="1:6" ht="30" customHeight="1">
       <c r="A35" s="82" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B35" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C35" s="66" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="D35" s="68" t="s">
         <v>61</v>
       </c>
       <c r="E35" s="66" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="F35" s="88" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="30" customHeight="1">
@@ -20229,16 +20352,16 @@
         <v>4.5</v>
       </c>
       <c r="C37" s="6" t="s">
+        <v>872</v>
+      </c>
+      <c r="D37" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="E37" s="28" t="s">
+        <v>873</v>
+      </c>
+      <c r="F37" s="84" t="s">
         <v>874</v>
-      </c>
-      <c r="D37" s="27" t="s">
-        <v>219</v>
-      </c>
-      <c r="E37" s="28" t="s">
-        <v>875</v>
-      </c>
-      <c r="F37" s="84" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="30" customHeight="1">
@@ -20283,19 +20406,19 @@
     </row>
     <row r="40" spans="1:6" ht="19.5" customHeight="1">
       <c r="A40" s="81" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B40" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C40" s="76" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="D40" s="75" t="s">
         <v>215</v>
       </c>
       <c r="E40" s="76" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="F40" s="87" t="s">
         <v>92</v>
@@ -20303,19 +20426,19 @@
     </row>
     <row r="41" spans="1:6" ht="30" customHeight="1">
       <c r="A41" s="82" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B41" s="68">
         <v>4.3</v>
       </c>
       <c r="C41" s="66" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="D41" s="68" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E41" s="66" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="F41" s="88" t="s">
         <v>92</v>
@@ -20339,16 +20462,16 @@
         <v>154</v>
       </c>
       <c r="C43" s="6" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D43" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="D43" s="27" t="s">
+      <c r="E43" s="6" t="s">
+        <v>1091</v>
+      </c>
+      <c r="F43" s="84" t="s">
         <v>219</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="F43" s="84" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="30" customHeight="1">
@@ -20359,16 +20482,16 @@
         <v>182</v>
       </c>
       <c r="C44" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="D44" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="E44" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="D44" s="18" t="s">
+      <c r="F44" s="85" t="s">
         <v>223</v>
-      </c>
-      <c r="E44" s="15" t="s">
-        <v>224</v>
-      </c>
-      <c r="F44" s="85" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="30" customHeight="1">
@@ -20379,13 +20502,13 @@
         <v>148</v>
       </c>
       <c r="C45" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="E45" s="5" t="s">
         <v>226</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>228</v>
       </c>
       <c r="F45" s="86" t="s">
         <v>33</v>
@@ -20393,47 +20516,47 @@
     </row>
     <row r="46" spans="1:6" ht="19.5" customHeight="1">
       <c r="A46" s="81" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B46" s="75">
         <v>4.5</v>
       </c>
       <c r="C46" s="76" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="D46" s="75" t="s">
         <v>89</v>
       </c>
       <c r="E46" s="76" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="F46" s="87" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="30" customHeight="1">
       <c r="A47" s="82" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B47" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C47" s="66" t="s">
+        <v>815</v>
+      </c>
+      <c r="D47" s="68" t="s">
+        <v>816</v>
+      </c>
+      <c r="E47" s="66" t="s">
         <v>817</v>
       </c>
-      <c r="D47" s="68" t="s">
+      <c r="F47" s="88" t="s">
         <v>818</v>
-      </c>
-      <c r="E47" s="66" t="s">
-        <v>819</v>
-      </c>
-      <c r="F47" s="88" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="30" customHeight="1">
       <c r="A48" s="185" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B48" s="186"/>
       <c r="C48" s="186"/>
@@ -20449,16 +20572,16 @@
         <v>213</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D49" s="27" t="s">
         <v>160</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F49" s="84" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="30" customHeight="1">
@@ -20469,16 +20592,16 @@
         <v>154</v>
       </c>
       <c r="C50" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="D50" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="E50" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="D50" s="18" t="s">
+      <c r="F50" s="85" t="s">
         <v>234</v>
-      </c>
-      <c r="E50" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="F50" s="85" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="30" customHeight="1">
@@ -20489,61 +20612,61 @@
         <v>4.5</v>
       </c>
       <c r="C51" s="13" t="s">
+        <v>862</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="F51" s="86" t="s">
         <v>864</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>865</v>
-      </c>
-      <c r="F51" s="86" t="s">
-        <v>866</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="19.5" customHeight="1">
       <c r="A52" s="81" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B52" s="75">
         <v>4.7</v>
       </c>
       <c r="C52" s="76" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="D52" s="75" t="s">
         <v>66</v>
       </c>
       <c r="E52" s="76" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="F52" s="87" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="30" customHeight="1">
       <c r="A53" s="82" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B53" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C53" s="66" t="s">
+        <v>822</v>
+      </c>
+      <c r="D53" s="68" t="s">
+        <v>823</v>
+      </c>
+      <c r="E53" s="66" t="s">
         <v>824</v>
       </c>
-      <c r="D53" s="68" t="s">
+      <c r="F53" s="88" t="s">
         <v>825</v>
-      </c>
-      <c r="E53" s="66" t="s">
-        <v>826</v>
-      </c>
-      <c r="F53" s="88" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="30" customHeight="1">
       <c r="A54" s="185" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B54" s="186"/>
       <c r="C54" s="186"/>
@@ -20559,16 +20682,16 @@
         <v>158</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D55" s="27" t="s">
         <v>209</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F55" s="84" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="30" customHeight="1">
@@ -20579,13 +20702,13 @@
         <v>148</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D56" s="18" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F56" s="85" t="s">
         <v>33</v>
@@ -20599,61 +20722,61 @@
         <v>158</v>
       </c>
       <c r="C57" s="29" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>160</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F57" s="86" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="19.5" customHeight="1">
       <c r="A58" s="81" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B58" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C58" s="74" t="s">
+        <v>847</v>
+      </c>
+      <c r="D58" s="75" t="s">
+        <v>218</v>
+      </c>
+      <c r="E58" s="76" t="s">
+        <v>848</v>
+      </c>
+      <c r="F58" s="87" t="s">
         <v>849</v>
-      </c>
-      <c r="D58" s="75" t="s">
-        <v>219</v>
-      </c>
-      <c r="E58" s="76" t="s">
-        <v>850</v>
-      </c>
-      <c r="F58" s="87" t="s">
-        <v>851</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="30" customHeight="1">
       <c r="A59" s="82" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B59" s="68">
         <v>4.5999999999999996</v>
       </c>
       <c r="C59" s="69" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="D59" s="68" t="s">
         <v>52</v>
       </c>
       <c r="E59" s="66" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="F59" s="88" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="30" customHeight="1">
       <c r="A60" s="185" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B60" s="186"/>
       <c r="C60" s="186"/>
@@ -20663,19 +20786,19 @@
     </row>
     <row r="61" spans="1:6" ht="30" customHeight="1">
       <c r="A61" s="78" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B61" s="27" t="s">
         <v>158</v>
       </c>
       <c r="C61" s="28" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D61" s="27" t="s">
         <v>89</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F61" s="84" t="s">
         <v>87</v>
@@ -20683,19 +20806,19 @@
     </row>
     <row r="62" spans="1:6" ht="19.5" customHeight="1">
       <c r="A62" s="79" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B62" s="18" t="s">
         <v>154</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D62" s="18" t="s">
         <v>99</v>
       </c>
       <c r="E62" s="25" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F62" s="85" t="s">
         <v>97</v>
@@ -20703,27 +20826,27 @@
     </row>
     <row r="63" spans="1:6" ht="30" customHeight="1">
       <c r="A63" s="80" t="s">
+        <v>251</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="C63" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="D63" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="C63" s="13" t="s">
+      <c r="E63" s="24" t="s">
         <v>255</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="F63" s="86" t="s">
         <v>256</v>
-      </c>
-      <c r="E63" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="F63" s="86" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="30" customHeight="1">
       <c r="A64" s="179" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B64" s="180"/>
       <c r="C64" s="180"/>
@@ -20739,13 +20862,13 @@
         <v>158</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D65" s="27" t="s">
         <v>115</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="F65" s="84" t="s">
         <v>113</v>
@@ -20759,16 +20882,16 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="D66" s="18" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="F66" s="85" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="30" customHeight="1">
@@ -20779,73 +20902,73 @@
         <v>207</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>189</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F67" s="86" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="30" customHeight="1">
       <c r="A68" s="81" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B68" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C68" s="76" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="D68" s="75" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="E68" s="76" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="F68" s="87" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="30" customHeight="1">
       <c r="A69" s="82" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B69" s="68">
         <v>4.3</v>
       </c>
       <c r="C69" s="66" t="s">
+        <v>868</v>
+      </c>
+      <c r="D69" s="68" t="s">
+        <v>869</v>
+      </c>
+      <c r="E69" s="66" t="s">
         <v>870</v>
       </c>
-      <c r="D69" s="68" t="s">
+      <c r="F69" s="88" t="s">
         <v>871</v>
-      </c>
-      <c r="E69" s="66" t="s">
-        <v>872</v>
-      </c>
-      <c r="F69" s="88" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="30" customHeight="1">
       <c r="A70" s="81" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B70" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C70" s="76" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="D70" s="75" t="s">
         <v>123</v>
       </c>
       <c r="E70" s="76" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="F70" s="87" t="s">
         <v>121</v>
@@ -20853,67 +20976,67 @@
     </row>
     <row r="71" spans="1:6" ht="30" customHeight="1">
       <c r="A71" s="82" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B71" s="68">
         <v>4.5</v>
       </c>
       <c r="C71" s="66" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="D71" s="68" t="s">
         <v>99</v>
       </c>
       <c r="E71" s="66" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="F71" s="88" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="30" customHeight="1">
       <c r="A72" s="82" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="B72" s="216" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C72" s="66" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D72" s="68" t="s">
         <v>1017</v>
       </c>
-      <c r="C72" s="66" t="s">
+      <c r="E72" s="66" t="s">
         <v>1018</v>
       </c>
-      <c r="D72" s="68" t="s">
-        <v>1019</v>
-      </c>
-      <c r="E72" s="66" t="s">
-        <v>1020</v>
-      </c>
       <c r="F72" s="88" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="30" customHeight="1">
       <c r="A73" s="82" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="B73" s="216" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C73" s="66" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D73" s="68" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E73" s="66" t="s">
         <v>1021</v>
       </c>
-      <c r="C73" s="66" t="s">
+      <c r="F73" s="88" t="s">
         <v>1022</v>
-      </c>
-      <c r="D73" s="68" t="s">
-        <v>1014</v>
-      </c>
-      <c r="E73" s="66" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F73" s="88" t="s">
-        <v>1024</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="30" customHeight="1">
       <c r="A74" s="179" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B74" s="180"/>
       <c r="C74" s="180"/>
@@ -20929,16 +21052,16 @@
         <v>182</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D75" s="27" t="s">
         <v>111</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F75" s="84" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="19.5" customHeight="1">
@@ -20949,16 +21072,16 @@
         <v>207</v>
       </c>
       <c r="C76" s="16" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D76" s="18" t="s">
         <v>189</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F76" s="85" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="30" customHeight="1">
@@ -20975,7 +21098,7 @@
         <v>107</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F77" s="86" t="s">
         <v>37</v>
@@ -20983,47 +21106,47 @@
     </row>
     <row r="78" spans="1:6" ht="30" customHeight="1">
       <c r="A78" s="81" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B78" s="75">
         <v>4.3</v>
       </c>
       <c r="C78" s="76" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="D78" s="75" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E78" s="76" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="F78" s="87" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="30" customHeight="1">
       <c r="A79" s="82" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B79" s="68">
         <v>4</v>
       </c>
       <c r="C79" s="66" t="s">
+        <v>830</v>
+      </c>
+      <c r="D79" s="68" t="s">
+        <v>831</v>
+      </c>
+      <c r="E79" s="66" t="s">
         <v>832</v>
       </c>
-      <c r="D79" s="68" t="s">
-        <v>833</v>
-      </c>
-      <c r="E79" s="66" t="s">
-        <v>834</v>
-      </c>
       <c r="F79" s="88" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="30" customHeight="1">
       <c r="A80" s="179" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B80" s="180"/>
       <c r="C80" s="180"/>
@@ -21039,16 +21162,16 @@
         <v>158</v>
       </c>
       <c r="C81" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="D81" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="F81" s="84" t="s">
         <v>274</v>
-      </c>
-      <c r="D81" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="E81" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="F81" s="84" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="30" customHeight="1">
@@ -21059,16 +21182,16 @@
         <v>4.2</v>
       </c>
       <c r="C82" s="16" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="D82" s="18" t="s">
         <v>119</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="F82" s="85" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="30" customHeight="1">
@@ -21079,93 +21202,93 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="F83" s="86" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="30" customHeight="1">
       <c r="A84" s="81" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B84" s="75">
         <v>4.3</v>
       </c>
       <c r="C84" s="76" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="D84" s="75" t="s">
         <v>119</v>
       </c>
       <c r="E84" s="76" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="F84" s="87" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="30" customHeight="1">
       <c r="A85" s="82" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B85" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C85" s="66" t="s">
+        <v>877</v>
+      </c>
+      <c r="D85" s="68" t="s">
+        <v>878</v>
+      </c>
+      <c r="E85" s="66" t="s">
         <v>879</v>
       </c>
-      <c r="D85" s="68" t="s">
-        <v>880</v>
-      </c>
-      <c r="E85" s="66" t="s">
-        <v>881</v>
-      </c>
       <c r="F85" s="88" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="30" customHeight="1">
       <c r="A86" s="81" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B86" s="75">
         <v>4.5999999999999996</v>
       </c>
       <c r="C86" s="76" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="D86" s="75" t="s">
         <v>128</v>
       </c>
       <c r="E86" s="76" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="F86" s="87" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="30" customHeight="1">
       <c r="A87" s="82" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B87" s="68" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C87" s="66" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="D87" s="68" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E87" s="66" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="F87" s="88" t="s">
         <v>113</v>
@@ -21173,47 +21296,47 @@
     </row>
     <row r="88" spans="1:6" ht="30" customHeight="1">
       <c r="A88" s="82" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B88" s="216" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C88" s="66" t="s">
         <v>1007</v>
-      </c>
-      <c r="B88" s="216" t="s">
-        <v>1008</v>
-      </c>
-      <c r="C88" s="66" t="s">
-        <v>1009</v>
       </c>
       <c r="D88" s="68" t="s">
         <v>189</v>
       </c>
       <c r="E88" s="66" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="F88" s="88" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="30" customHeight="1">
       <c r="A89" s="82" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B89" s="216" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C89" s="66" t="s">
         <v>1011</v>
       </c>
-      <c r="B89" s="216" t="s">
+      <c r="D89" s="68" t="s">
         <v>1012</v>
       </c>
-      <c r="C89" s="66" t="s">
+      <c r="E89" s="66" t="s">
         <v>1013</v>
       </c>
-      <c r="D89" s="68" t="s">
+      <c r="F89" s="88" t="s">
         <v>1014</v>
-      </c>
-      <c r="E89" s="66" t="s">
-        <v>1015</v>
-      </c>
-      <c r="F89" s="88" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="33.75" customHeight="1">
       <c r="A90" s="179" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B90" s="180"/>
       <c r="C90" s="180"/>
@@ -21229,16 +21352,16 @@
         <v>158</v>
       </c>
       <c r="C91" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D91" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="E91" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="D91" s="27" t="s">
-        <v>281</v>
-      </c>
-      <c r="E91" s="6" t="s">
-        <v>282</v>
-      </c>
       <c r="F91" s="84" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -21249,16 +21372,16 @@
         <v>175</v>
       </c>
       <c r="C92" s="16" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D92" s="18" t="s">
         <v>66</v>
       </c>
       <c r="E92" s="15" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F92" s="85" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -21269,61 +21392,61 @@
         <v>207</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>189</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F93" s="86" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="28">
       <c r="A94" s="81" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B94" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C94" s="76" t="s">
+        <v>880</v>
+      </c>
+      <c r="D94" s="75" t="s">
+        <v>881</v>
+      </c>
+      <c r="E94" s="76" t="s">
         <v>882</v>
       </c>
-      <c r="D94" s="75" t="s">
+      <c r="F94" s="87" t="s">
         <v>883</v>
-      </c>
-      <c r="E94" s="76" t="s">
-        <v>884</v>
-      </c>
-      <c r="F94" s="87" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="28">
       <c r="A95" s="82" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B95" s="68">
         <v>4.5</v>
       </c>
       <c r="C95" s="66" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D95" s="68" t="s">
         <v>119</v>
       </c>
       <c r="E95" s="66" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="F95" s="88" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="48" customHeight="1" thickBot="1">
       <c r="A96" s="182" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="B96" s="183"/>
       <c r="C96" s="183"/>
@@ -21372,7 +21495,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1">
       <c r="A1" s="161" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B1" s="162"/>
       <c r="C1" s="162"/>
@@ -21386,7 +21509,7 @@
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
       <c r="A3" s="197" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B3" s="198"/>
       <c r="C3" s="198"/>
@@ -21394,100 +21517,100 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="133" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>45</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D4" s="143" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" customHeight="1">
       <c r="A5" s="134" t="s">
+        <v>293</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="C5" s="32" t="s">
         <v>295</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="D5" s="144" t="s">
         <v>296</v>
-      </c>
-      <c r="C5" s="32" t="s">
-        <v>297</v>
-      </c>
-      <c r="D5" s="144" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="27.75" customHeight="1">
       <c r="A6" s="135" t="s">
+        <v>297</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>298</v>
+      </c>
+      <c r="C6" s="35" t="s">
         <v>299</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="D6" s="145" t="s">
         <v>300</v>
-      </c>
-      <c r="C6" s="35" t="s">
-        <v>301</v>
-      </c>
-      <c r="D6" s="145" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="27.75" customHeight="1">
       <c r="A7" s="136" t="s">
+        <v>301</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>302</v>
+      </c>
+      <c r="C7" s="38" t="s">
         <v>303</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="D7" s="146" t="s">
         <v>304</v>
-      </c>
-      <c r="C7" s="38" t="s">
-        <v>305</v>
-      </c>
-      <c r="D7" s="146" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1">
       <c r="A8" s="137" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B8" s="40" t="s">
         <v>63</v>
       </c>
       <c r="C8" s="41" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D8" s="147" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="27.75" customHeight="1">
       <c r="A9" s="138" t="s">
+        <v>308</v>
+      </c>
+      <c r="B9" s="43" t="s">
+        <v>309</v>
+      </c>
+      <c r="C9" s="44" t="s">
         <v>310</v>
       </c>
-      <c r="B9" s="43" t="s">
+      <c r="D9" s="148" t="s">
         <v>311</v>
-      </c>
-      <c r="C9" s="44" t="s">
-        <v>312</v>
-      </c>
-      <c r="D9" s="148" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" customHeight="1">
       <c r="A10" s="139" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B10" s="92" t="s">
+        <v>924</v>
+      </c>
+      <c r="C10" s="92" t="s">
+        <v>925</v>
+      </c>
+      <c r="D10" s="125" t="s">
         <v>926</v>
-      </c>
-      <c r="C10" s="92" t="s">
-        <v>927</v>
-      </c>
-      <c r="D10" s="125" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -21498,7 +21621,7 @@
     </row>
     <row r="12" spans="1:4" ht="24" customHeight="1">
       <c r="A12" s="200" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B12" s="201"/>
       <c r="C12" s="201"/>
@@ -21506,170 +21629,170 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="133" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>45</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D13" s="143" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1">
       <c r="A14" s="135" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B14" s="34" t="s">
+        <v>313</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>314</v>
+      </c>
+      <c r="D14" s="145" t="s">
         <v>315</v>
-      </c>
-      <c r="C14" s="35" t="s">
-        <v>316</v>
-      </c>
-      <c r="D14" s="145" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="27.75" customHeight="1">
       <c r="A15" s="136" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D15" s="146" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="30" customHeight="1">
       <c r="A16" s="136" t="s">
+        <v>318</v>
+      </c>
+      <c r="B16" s="45" t="s">
+        <v>319</v>
+      </c>
+      <c r="C16" s="38" t="s">
         <v>320</v>
       </c>
-      <c r="B16" s="45" t="s">
+      <c r="D16" s="146" t="s">
         <v>321</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>322</v>
-      </c>
-      <c r="D16" s="146" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1">
       <c r="A17" s="137" t="s">
+        <v>322</v>
+      </c>
+      <c r="B17" s="40" t="s">
+        <v>323</v>
+      </c>
+      <c r="C17" s="41" t="s">
         <v>324</v>
       </c>
-      <c r="B17" s="40" t="s">
+      <c r="D17" s="147" t="s">
         <v>325</v>
-      </c>
-      <c r="C17" s="41" t="s">
-        <v>326</v>
-      </c>
-      <c r="D17" s="147" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1">
       <c r="A18" s="137" t="s">
+        <v>326</v>
+      </c>
+      <c r="B18" s="40" t="s">
+        <v>327</v>
+      </c>
+      <c r="C18" s="41" t="s">
         <v>328</v>
       </c>
-      <c r="B18" s="40" t="s">
+      <c r="D18" s="147" t="s">
         <v>329</v>
-      </c>
-      <c r="C18" s="41" t="s">
-        <v>330</v>
-      </c>
-      <c r="D18" s="147" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="30" customHeight="1">
       <c r="A19" s="134" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B19" s="31" t="s">
+        <v>330</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>331</v>
+      </c>
+      <c r="D19" s="144" t="s">
         <v>332</v>
-      </c>
-      <c r="C19" s="32" t="s">
-        <v>333</v>
-      </c>
-      <c r="D19" s="144" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="30" customHeight="1">
       <c r="A20" s="139" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B20" s="92" t="s">
+        <v>927</v>
+      </c>
+      <c r="C20" s="92" t="s">
+        <v>928</v>
+      </c>
+      <c r="D20" s="125" t="s">
         <v>929</v>
-      </c>
-      <c r="C20" s="92" t="s">
-        <v>930</v>
-      </c>
-      <c r="D20" s="125" t="s">
-        <v>931</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="30" customHeight="1">
       <c r="A21" s="140" t="s">
+        <v>930</v>
+      </c>
+      <c r="B21" s="90" t="s">
+        <v>931</v>
+      </c>
+      <c r="C21" s="90" t="s">
         <v>932</v>
       </c>
-      <c r="B21" s="90" t="s">
+      <c r="D21" s="149" t="s">
         <v>933</v>
-      </c>
-      <c r="C21" s="90" t="s">
-        <v>934</v>
-      </c>
-      <c r="D21" s="149" t="s">
-        <v>935</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="27.75" customHeight="1">
       <c r="A22" s="138" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B22" s="43" t="s">
+        <v>333</v>
+      </c>
+      <c r="C22" s="44" t="s">
+        <v>334</v>
+      </c>
+      <c r="D22" s="148" t="s">
         <v>335</v>
-      </c>
-      <c r="C22" s="44" t="s">
-        <v>336</v>
-      </c>
-      <c r="D22" s="148" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="30" customHeight="1">
       <c r="A23" s="137" t="s">
+        <v>336</v>
+      </c>
+      <c r="B23" s="40" t="s">
+        <v>337</v>
+      </c>
+      <c r="C23" s="41" t="s">
         <v>338</v>
       </c>
-      <c r="B23" s="40" t="s">
+      <c r="D23" s="147" t="s">
         <v>339</v>
-      </c>
-      <c r="C23" s="41" t="s">
-        <v>340</v>
-      </c>
-      <c r="D23" s="147" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="30" customHeight="1">
       <c r="A24" s="137" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B24" s="40" t="s">
+        <v>340</v>
+      </c>
+      <c r="C24" s="41" t="s">
+        <v>341</v>
+      </c>
+      <c r="D24" s="147" t="s">
         <v>342</v>
-      </c>
-      <c r="C24" s="41" t="s">
-        <v>343</v>
-      </c>
-      <c r="D24" s="147" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -21680,7 +21803,7 @@
     </row>
     <row r="26" spans="1:4" ht="24" customHeight="1">
       <c r="A26" s="203" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B26" s="204"/>
       <c r="C26" s="204"/>
@@ -21688,128 +21811,128 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="133" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>45</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D27" s="143" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="27.75" customHeight="1">
       <c r="A28" s="135" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B28" s="34" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D28" s="145" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="30" customHeight="1">
       <c r="A29" s="136" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B29" s="37" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D29" s="146" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="27.75" customHeight="1">
       <c r="A30" s="134" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B30" s="31" t="s">
+        <v>348</v>
+      </c>
+      <c r="C30" s="32" t="s">
+        <v>349</v>
+      </c>
+      <c r="D30" s="144" t="s">
         <v>350</v>
-      </c>
-      <c r="C30" s="32" t="s">
-        <v>351</v>
-      </c>
-      <c r="D30" s="144" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="27.75" customHeight="1">
       <c r="A31" s="138" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B31" s="43" t="s">
+        <v>351</v>
+      </c>
+      <c r="C31" s="44" t="s">
+        <v>352</v>
+      </c>
+      <c r="D31" s="148" t="s">
         <v>353</v>
-      </c>
-      <c r="C31" s="44" t="s">
-        <v>354</v>
-      </c>
-      <c r="D31" s="148" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="27.75" customHeight="1">
       <c r="A32" s="138" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B32" s="43" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C32" s="44" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D32" s="148" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="30" customHeight="1">
       <c r="A33" s="135" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B33" s="46" t="s">
+        <v>356</v>
+      </c>
+      <c r="C33" s="35" t="s">
+        <v>357</v>
+      </c>
+      <c r="D33" s="145" t="s">
         <v>358</v>
-      </c>
-      <c r="C33" s="35" t="s">
-        <v>359</v>
-      </c>
-      <c r="D33" s="145" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="30" customHeight="1">
       <c r="A34" s="137" t="s">
+        <v>359</v>
+      </c>
+      <c r="B34" s="40" t="s">
+        <v>360</v>
+      </c>
+      <c r="C34" s="41" t="s">
         <v>361</v>
       </c>
-      <c r="B34" s="40" t="s">
+      <c r="D34" s="147" t="s">
         <v>362</v>
-      </c>
-      <c r="C34" s="41" t="s">
-        <v>363</v>
-      </c>
-      <c r="D34" s="147" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="30" customHeight="1" thickBot="1">
       <c r="A35" s="141" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B35" s="130" t="s">
+        <v>363</v>
+      </c>
+      <c r="C35" s="131" t="s">
+        <v>364</v>
+      </c>
+      <c r="D35" s="150" t="s">
         <v>365</v>
-      </c>
-      <c r="C35" s="131" t="s">
-        <v>366</v>
-      </c>
-      <c r="D35" s="150" t="s">
-        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -21840,7 +21963,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1">
       <c r="A1" s="206" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B1" s="206"/>
       <c r="C1" s="206"/>
@@ -21848,7 +21971,7 @@
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
       <c r="A3" s="178" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B3" s="178"/>
       <c r="C3" s="178"/>
@@ -21856,63 +21979,63 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="12" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B4" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>369</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="27.75" customHeight="1">
       <c r="A5" s="47" t="s">
+        <v>370</v>
+      </c>
+      <c r="B5" s="48" t="s">
+        <v>371</v>
+      </c>
+      <c r="C5" s="49" t="s">
         <v>372</v>
       </c>
-      <c r="B5" s="48" t="s">
+      <c r="D5" s="47" t="s">
         <v>373</v>
-      </c>
-      <c r="C5" s="49" t="s">
-        <v>374</v>
-      </c>
-      <c r="D5" s="47" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="27.75" customHeight="1">
       <c r="A6" s="47" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C6" s="49" t="s">
         <v>199</v>
       </c>
       <c r="D6" s="47" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="27.75" customHeight="1">
       <c r="A7" s="30" t="s">
+        <v>376</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>377</v>
+      </c>
+      <c r="C7" s="32" t="s">
         <v>378</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="D7" s="30" t="s">
         <v>379</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>380</v>
-      </c>
-      <c r="D7" s="30" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="24" customHeight="1">
       <c r="A9" s="174" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B9" s="174"/>
       <c r="C9" s="174"/>
@@ -21920,49 +22043,49 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="12" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B10" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>369</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="27.75" customHeight="1">
       <c r="A11" s="47" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B11" s="48" t="s">
+        <v>380</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>381</v>
+      </c>
+      <c r="D11" s="47" t="s">
         <v>382</v>
-      </c>
-      <c r="C11" s="49" t="s">
-        <v>383</v>
-      </c>
-      <c r="D11" s="47" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="27.75" customHeight="1">
       <c r="A12" s="47" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B12" s="48" t="s">
+        <v>383</v>
+      </c>
+      <c r="C12" s="49" t="s">
+        <v>384</v>
+      </c>
+      <c r="D12" s="47" t="s">
         <v>385</v>
-      </c>
-      <c r="C12" s="49" t="s">
-        <v>386</v>
-      </c>
-      <c r="D12" s="47" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="24" customHeight="1">
       <c r="A14" s="176" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B14" s="176"/>
       <c r="C14" s="176"/>
@@ -21970,44 +22093,44 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="12" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B15" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D15" s="12" t="s">
         <v>369</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="27.75" customHeight="1">
       <c r="A16" s="47" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B16" s="48" t="s">
+        <v>386</v>
+      </c>
+      <c r="C16" s="49" t="s">
+        <v>387</v>
+      </c>
+      <c r="D16" s="47" t="s">
         <v>388</v>
-      </c>
-      <c r="C16" s="49" t="s">
-        <v>389</v>
-      </c>
-      <c r="D16" s="47" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="27.75" customHeight="1">
       <c r="A17" s="50" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B17" s="51" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C17" s="52" t="s">
         <v>117</v>
       </c>
       <c r="D17" s="50" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>

--- a/tools/itinerary.xlsx
+++ b/tools/itinerary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jitwei/Library/Mobile Documents/com~apple~CloudDocs/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{FCD1244A-421E-DA43-B9DC-C68901FA4525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51231A84-60FF-3346-80AA-8A8C1F1C5813}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A830E94F-BF89-7049-9200-E77F80738451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="17020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="1092">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1685" uniqueCount="1126">
   <si>
     <r>
       <rPr>
@@ -864,9 +864,6 @@
     <t>👉 'ALL DAYS (merged)' combines every day into one table with a Day/Date column. 'Meal Options' gives 3 rated picks per lunch/dinner. Optional items shaded lilac.</t>
   </si>
   <si>
-    <t>DINING &amp; SPECIALTY COFFEE (also slotted into day tabs)</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -1136,28 +1133,6 @@
   <si>
     <r>
       <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">宫宴 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Gongyan Palace Banquet (Day 2)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Noto Sans CJK SC"/>
@@ -1325,53 +1300,6 @@
     <t>Ritz Nanjing dining (38–62F)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Pin Ning Fu </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">品宁府 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&amp; Dai Yuet Heen </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">帝粤轩 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(both Michelin 1★ 2026); FLAIR rooftop 62F.</t>
-    </r>
-  </si>
-  <si>
     <t>¥300–600</t>
   </si>
   <si>
@@ -1645,116 +1573,6 @@
     <t>秦淮区贡院街</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鸭血粉丝汤 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>小潘记</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>叶新</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">牛肉锅贴 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>蒋有记</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>汤包</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
     <t>¥10–35</t>
   </si>
   <si>
@@ -1784,71 +1602,6 @@
   </si>
   <si>
     <t>秦淮区</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Queue for </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>乌饭团</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>卤蛋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">桂花糖芋苗 — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>beloved Jinling sweets.</t>
-    </r>
   </si>
   <si>
     <t>¥8–25</t>
@@ -3158,28 +2911,6 @@
         <b/>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">宫宴 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Gongyan — Song Palace Banquet</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -3435,9 +3166,6 @@
     <t>¥700+</t>
   </si>
   <si>
-    <t>Michelin ⭐⭐; the ceiling (splurge)</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -3676,35 +3404,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">90-yr-old; beef potstickers </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">牛肉锅贴 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Halal)</t>
-    </r>
-  </si>
-  <si>
     <t>秦淮区大顶巷</t>
   </si>
   <si>
@@ -3919,9 +3618,6 @@
     <t>¥400+</t>
   </si>
   <si>
-    <t>In-hotel Cantonese, starred; skyline views (splurge)</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -4006,9 +3702,6 @@
     </r>
   </si>
   <si>
-    <t>Rated Nanjing's best Chinese; Huaiyang (splurge)</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -4191,9 +3884,6 @@
     </r>
   </si>
   <si>
-    <t>In-hotel Chinese, starred; easy luxury</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -4213,53 +3903,6 @@
         <family val="2"/>
       </rPr>
       <t>Plum Garden (Jinling Hotel)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Rated top </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>盐水鸭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>烤鸭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>; refined</t>
     </r>
   </si>
   <si>
@@ -4397,62 +4040,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>乌饭团</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>卤蛋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">桂花糖芋苗 — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>queue-worthy Jinling sweets</t>
-    </r>
-  </si>
-  <si>
     <t>🌃</t>
   </si>
   <si>
@@ -4911,79 +4498,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Pingjiangsong </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">平江宋 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Platinum)</t>
-    </r>
-  </si>
-  <si>
-    <t>¥180–350</t>
-  </si>
-  <si>
-    <t>Reviving traditional Suzhou cuisine</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">SU Yan </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">苏宴 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(W Suzhou, Jinji Lake)</t>
-    </r>
-  </si>
-  <si>
-    <t>5.0-rated; lakeside fine dining (if SIP)</t>
-  </si>
-  <si>
     <t>工业园区苏绣路</t>
   </si>
   <si>
@@ -13411,9 +12925,6 @@
     <t>Longjing Caotang 龙井草堂</t>
   </si>
   <si>
-    <t>Slow-food courtyard in the tea village — pairs with the Longjing 龙井 stop</t>
-  </si>
-  <si>
     <t>西湖区龙井路399号</t>
   </si>
   <si>
@@ -13432,9 +12943,6 @@
     <t>Xiao Pan Ji 小潘记 鸭血粉丝汤</t>
   </si>
   <si>
-    <t>Nanjing's signature duck-blood vermicelli soup — steps from Laomendong 老门东</t>
-  </si>
-  <si>
     <t>Lan Jia Shan 蓝家山 (Laomendong)</t>
   </si>
   <si>
@@ -13495,9 +13003,6 @@
     <t>Shrimp shengjian by the lanterns — closest to the Ritz for a late finish</t>
   </si>
   <si>
-    <t>MEAL OPTIONS — 5 top-rated picks per lunch &amp; dinner (by popularity, rating &amp; distance)</t>
-  </si>
-  <si>
     <t>Zhang Sheng Ji 张生记 (Hubin 湖滨)</t>
   </si>
   <si>
@@ -13561,9 +13066,6 @@
     <t>Xin Rong Ji 新荣记 (Raffles City 来福士)</t>
   </si>
   <si>
-    <t>Taizhou-style seafood, nationally acclaimed — in the connected mall</t>
-  </si>
-  <si>
     <t>Kuiyuan Wangzhuang / Hefang snack lanes 河坊街小吃</t>
   </si>
   <si>
@@ -13595,15 +13097,6 @@
   </si>
   <si>
     <t>Tongdexing 同得兴 (Suzhou noodles 苏式面)</t>
-  </si>
-  <si>
-    <t>¥30–80</t>
-  </si>
-  <si>
-    <t>Renowned 枫镇大肉面 / 焖肉面 — a Suzhou noodle pilgrimage</t>
-  </si>
-  <si>
-    <t>姑苏区嘉馀坊</t>
   </si>
   <si>
     <t>Qinhuai Renjia 秦淮人家 (夫子庙)</t>
@@ -14425,12 +13918,6 @@
     <t>250-yr-old; squirrel mandarin fish. 1,350+ reviews. ⚠️ Ranks LAST (评分 65) among 2026 Dianping 苏帮菜 entries while being the priciest — go for the heritage dish, not value. See ⑧⑨ below.</t>
   </si>
   <si>
-    <t>Ratings from Trip.com / Dianping / Tripadvisor (2026). Options ranked ①→⑤ by rating, review volume and walking distance from that day’s route. ★ = special. 🏨 = at/near hotel.  ⚠️ TWO SCALES: plain numbers (e.g. 4.6) are 0–5 star averages; entries marked “评分 NN” are Dianping’s 0–100 composite city-ranking score (taste + environment + service + popularity). They are NOT directly comparable — compare rank position, not the digits.</t>
-  </si>
-  <si>
-    <t>①–⑦ ranked by rating, popularity &amp; distance from the day’s route. ★ 宫宴 = banquet. 🏨 = at/near hotel (incl. Michelin-starred in-hotel at Ritz Nanjing). Suzhou snack specialities (生煎, 糕团, 鲜肉月饼, 响油鳝糊) are folded into the Day 6–7 lists as ⑥/⑦ — grab-and-go or add-on dishes rather than full sit-down meals. Ratings indicative 2026; fine-dining &amp; 宫宴 need booking 3+ days ahead.  ⑧/⑨ entries (added Sep 2026) come from the 2026 Dianping city rankings for 杭帮菜 &amp; 苏帮菜 — each sourced from a single aggregator, so treat as one strong opinion rather than settled fact. No comparable Nanjing restaurant ranking was found, so the Nanjing lists are unchanged.</t>
-  </si>
-  <si>
     <t>☕ Optional: 羽和铃 Feather Bell coffee</t>
   </si>
   <si>
@@ -14606,12 +14093,198 @@
   </si>
   <si>
     <t>Crab-roe noodles 蟹黄面 &amp; 蟹黄拌饭 with free noodle/rice refills; Qinhuai river-view. NOTE: correct spelling is 李百蟹 (百 "hundred"), not 李白蟹 — it has nothing to do with the poet 李白. Same chain also has 4 Suzhou branches (see Day 6 Opt).</t>
+  </si>
+  <si>
+    <t>Taizhou-style seafood — MICHELIN ⭐ 1-STAR 2026 (沪苏浙指南). In the connected Raffles City 来福士 mall.</t>
+  </si>
+  <si>
+    <t>MICHELIN ⭐ 1-STAR 2026 (沪苏浙指南) — Four Seasons Chinese; the ceiling (splurge). Was previously listed as 2-star; 2026 guide lists it at 1 star.</t>
+  </si>
+  <si>
+    <t>MICHELIN ⭐ 1-STAR 2026 (沪苏浙指南) — slow-food courtyard in the tea village; pairs with the Longjing 龙井 stop.</t>
+  </si>
+  <si>
+    <t>In-hotel Cantonese — MICHELIN ⭐ 1-STAR 2026 (蝉联/retained); skyline views (splurge).</t>
+  </si>
+  <si>
+    <t>In-hotel Huaiyang — MICHELIN ⭐ 1-STAR 2026 (新晋/NEW, promoted from 指南入选). 醋粒水晶肴肉, 蟹肉文思豆腐羹.</t>
+  </si>
+  <si>
+    <t>MICHELIN 指南入选 2026 (Selected). Huaiyang at Shangri-La. NOTE: the ⭐ 1-star is the separate sister restaurant 江南灶·云府.</t>
+  </si>
+  <si>
+    <t>MICHELIN 指南入选 2026 (Selected) — rated top 盐水鸭/烤鸭; refined.</t>
+  </si>
+  <si>
+    <t>MICHELIN 必比登 BIB GOURMAND 2026 — 乌饭团, 卤蛋, 桂花糖芋苗. Among Nanjing's cheapest Bib entries (~¥13pp).</t>
+  </si>
+  <si>
+    <t>MICHELIN 必比登 BIB GOURMAND 2026 (~¥28pp) — 90-yr-old Halal house; beef potstickers 牛肉锅贴.</t>
+  </si>
+  <si>
+    <t>MICHELIN 必比登 BIB GOURMAND 2026 — Nanjing's signature duck-blood vermicelli soup; steps from Laomendong 老门东.</t>
+  </si>
+  <si>
+    <t>MICHELIN 必比登 BIB GOURMAND 2026 — 2nd year running (嘉馀坊店 is the listed branch). 枫镇大肉面 (summer only) / 焖肉面 / 爆鱼面. Opens 07:00–13:00 &amp; 16:30–19:00 — CLOSED mid-afternoon.</t>
+  </si>
+  <si>
+    <t>姑苏区嘉馀坊6号</t>
+  </si>
+  <si>
+    <t>~¥57</t>
+  </si>
+  <si>
+    <t>Pin Ning Fu 品宁府 — MICHELIN ⭐ 1★ 2026 (NEW 新晋); Dai Yuet Heen 帝粤轩 — MICHELIN ⭐ 1★ 2026 (retained 蝉联). Plus FLAIR rooftop 62F.</t>
+  </si>
+  <si>
+    <t>MICHELIN 必比登 BIB GOURMAND 2026. Queue for 乌饭团, 卤蛋, 桂花糖芋苗 — beloved Jinling sweets, ~¥13pp.</t>
+  </si>
+  <si>
+    <t>鸭血粉丝汤 (小潘记 — 必比登 2026), 牛肉锅贴 (蒋有记), 汤包. Also nearby: 李记清真馆 &amp; 致和老鸭粉丝汤, both 必比登 2026.</t>
+  </si>
+  <si>
+    <t>Tongdexing 同得兴 (嘉馀坊店) (Day 7 · Michelin)</t>
+  </si>
+  <si>
+    <t>姑苏区嘉馀坊6号 (near 观前街)</t>
+  </si>
+  <si>
+    <t>MICHELIN 必比登 BIB GOURMAND 2026 — 2nd year running. Suzhou's benchmark 苏式面; 枫镇大肉面 featured on 《舌尖上的中国》 S2. 焖肉面 / 爆鱼面 / 鳝糊面. ⚠ Opens 07:00–13:00 &amp; 16:30–19:00 — CLOSED mid-afternoon, so it fits Day 7 LUNCH, not the coffee slot.</t>
+  </si>
+  <si>
+    <t>⭐ Michelin</t>
+  </si>
+  <si>
+    <t>(not verified)</t>
+  </si>
+  <si>
+    <t>正清牛肉锅贴店 Zhengqing (NEW 必比登 2026)</t>
+  </si>
+  <si>
+    <t>鼓楼区江西路</t>
+  </si>
+  <si>
+    <t>MICHELIN 必比登 BIB GOURMAND 2026 (新晋). Locals rate its 牛肉锅贴 above the 夫子庙 tourist names — crisp shell, juicy filling; 牛肉小馄饨 too. Alternative to 蒋有记 on Day 4.</t>
+  </si>
+  <si>
+    <t>致和老鸭粉丝汤 Zhihe (NEW 必比登 2026)</t>
+  </si>
+  <si>
+    <t>秦淮区 (residential lanes)</t>
+  </si>
+  <si>
+    <t>MICHELIN 必比登 BIB GOURMAND 2026 (新晋) — ~¥20pp. Duck-carcass broth; 鸭血/鸭肠/鸭肝, the chilli oil is the soul. Qinhuai = same district as your Day 4 evening.</t>
+  </si>
+  <si>
+    <t>~¥20</t>
+  </si>
+  <si>
+    <t>Xin Rong Ji 新荣记 (Day 1 · Raffles City 来福士)</t>
+  </si>
+  <si>
+    <t>上城区钱江新城 来福士 (at the Conrad)</t>
+  </si>
+  <si>
+    <t>MICHELIN ⭐ 1-STAR 2026 (沪苏浙指南). Taizhou-style seafood, nationally acclaimed — inside the mall your hotel connects to. The easiest starred meal of the whole trip.</t>
+  </si>
+  <si>
+    <t>湉园 Tianyuan (NEW 指南入选 2026)</t>
+  </si>
+  <si>
+    <t>西湖区杨公堤 花港观鱼10号</t>
+  </si>
+  <si>
+    <t>MICHELIN 指南入选 2026 (NEW Selected). Address is literally INSIDE 花港观鱼 — your Day 2 14:25–15:10 stop. Zero detour for a garden-set meal on the West Lake west side.</t>
+  </si>
+  <si>
+    <t>金丝·听海 (NEW 指南入选 2026)</t>
+  </si>
+  <si>
+    <t>西湖区北山街78号 (香格里拉·水知心居一楼)</t>
+  </si>
+  <si>
+    <t>MICHELIN 指南入选 2026 (NEW Selected). On 北山街 — your Day 2 08:15 ginkgo avenue — and ~4 doors from 印象西湖 at 北山路82号. Strong pre-show dinner candidate.</t>
+  </si>
+  <si>
+    <t>DINING &amp; SPECIALTY COFFEE (also slotted into day tabs) — MICHELIN 2026 沪苏浙指南 status labelled (⭐ star / 必比登 Bib / 指南入选 Selected). Cafés are never Michelin-rated: the guide covers restaurants only.</t>
+  </si>
+  <si>
+    <t>MEAL OPTIONS — top-rated picks per lunch &amp; dinner (by popularity, rating &amp; distance), with MICHELIN 2026 status</t>
+  </si>
+  <si>
+    <t>Ratings from Trip.com / Dianping / Tripadvisor (2026). Dianping 评分 is a 0–100 scale — NOT comparable to the 0–5 star ratings in column B; compare rank position only. MICHELIN labels are from the 2026 沪苏浙米其林指南 (released 9 Apr 2026, 409 restaurants).</t>
+  </si>
+  <si>
+    <t>Options ranked by rating, popularity &amp; distance from the day's route. ★ 宫宴 = banquet. 🏨 = at/near hotel. MICHELIN 2026: Hangzhou 88 listings (34 必比登) · Nanjing 41 (21 必比登, 4 ⭐) · Suzhou 38 (18 必比登, 3 ⭐).</t>
+  </si>
+  <si>
+    <t>宫宴 Gongyan — Song Palace Banquet (Day 3)</t>
+  </si>
+  <si>
+    <t>姑苏区平江街道大儒巷54号 (丁宅)</t>
+  </si>
+  <si>
+    <t>金海华·平江颂 Pingjiang Song (Day 7 · Michelin 1★)</t>
+  </si>
+  <si>
+    <t>姑苏区平江街道大儒巷54号 (丁宅, off 平江路)</t>
+  </si>
+  <si>
+    <t>MICHELIN ⭐ 1-STAR 2026. Address CONFIRMED — 大儒巷54号, a lane off 平江路, so it IS walkable from your Day 6 Pingjiang Rd evening. Ming-dynasty 丁宅 relocated here in 2011; garden setting with 评弹. 新苏州菜, 不时不食. Trip.com 4.8, #1 Suzhou fine dining. ⚠ Book ~1 week ahead — very few tables; set menu from 2 pax. 11:30–14:00 / 17:30–21:00.</t>
+  </si>
+  <si>
+    <t>李百蟹·蟹黄面 Li Bai Xie (平江路总店)</t>
+  </si>
+  <si>
+    <t>CRAB-ROE NOODLES with zero detour — inside 琵琶语评弹茶馆 on the Pingjiang Rd 平江路 stretch you already walk. 蟹黄面 / 蟹黄拌饭, free noodle &amp; rice refills. Nov = peak hairy-crab season.</t>
+  </si>
+  <si>
+    <t>姑苏区狮林寺巷99号 琵琶语评弹茶馆·北馆1层</t>
+  </si>
+  <si>
+    <t>湉园 Tianyuan (Michelin 指南入选 2026)</t>
+  </si>
+  <si>
+    <t>MICHELIN 指南入选 2026 (NEW Selected). Sits INSIDE 花港观鱼 — your Day 2 14:25 stop — so it is a zero-detour garden lunch. Price &amp; hours not yet verified; call ahead.</t>
+  </si>
+  <si>
+    <t>金丝·听海 (Michelin 指南入选 2026)</t>
+  </si>
+  <si>
+    <t>MICHELIN 指南入选 2026 (NEW Selected). On 北山街 — your Day 2 08:15 ginkgo avenue — and ~4 doors from 印象西湖 (北山路82号). Best used as the PRE-SHOW dinner. Price &amp; hours not verified.</t>
+  </si>
+  <si>
+    <t>致和老鸭粉丝汤 Zhihe (Michelin 必比登 2026)</t>
+  </si>
+  <si>
+    <t>MICHELIN 必比登 BIB GOURMAND 2026 (新晋/NEW) — ~¥20pp. Duck-carcass broth with 鸭血/鸭肠/鸭肝; the chilli oil is the soul. 秦淮区 = same district as this evening. Exact lane address not published — locate on Amap before going.</t>
+  </si>
+  <si>
+    <t>正清牛肉锅贴店 Zhengqing (Michelin 必比登 2026)</t>
+  </si>
+  <si>
+    <t>MICHELIN 必比登 BIB GOURMAND 2026 (新晋/NEW). Locals rate its 牛肉锅贴 above the 夫子庙 tourist names — crisp shell, juicy filling; 牛肉小馄饨 too. 鼓楼区江西路, the same western side as 马祥兴 — a cheap alternative on this block.</t>
+  </si>
+  <si>
+    <t>金海华·平江颂 Pingjiang Song (Michelin ⭐ 1★)</t>
+  </si>
+  <si>
+    <t>MICHELIN ⭐ 1-STAR 2026 — 大儒巷54号 is a lane just OFF 平江路, so it is walkable from tonight's canal stroll. 丁宅, a Ming mansion relocated here in 2011; garden setting with 评弹. 新苏州菜, 不时不食 — 松鼠黄鱼, 碧螺虾仁, 响油蟹䰾. Trip.com 4.8, #1 Suzhou fine dining. ⚠ BOOK ~1 WEEK AHEAD — very few tables; set menu from 2 pax. 11:30–14:00 / 17:30–21:00. Tel +86 512 6610 9177.</t>
+  </si>
+  <si>
+    <t>SU Yan 苏宴 (W Suzhou, Jinji Lake 金鸡湖)</t>
+  </si>
+  <si>
+    <t>5.0-rated lakeside fine dining — the splurge choice IF you head to Jinji Lake 金鸡湖 / SIP on the last night. (Note: 平江颂 has moved to Day 6 Dinner — 大儒巷54号 sits off 平江路, so it belongs with that evening.)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="19">
     <font>
       <sz val="11"/>
@@ -15171,7 +14844,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="219">
+  <cellXfs count="241">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -15812,6 +15485,18 @@
     <xf numFmtId="49" fontId="10" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -15819,6 +15504,60 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -16323,7 +16062,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
       <c r="A1" s="161" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="B1" s="162"/>
       <c r="C1" s="162"/>
@@ -16333,7 +16072,7 @@
     </row>
     <row r="2" spans="1:6" ht="21.75" customHeight="1">
       <c r="A2" s="164" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="B2" s="165"/>
       <c r="C2" s="165"/>
@@ -16343,19 +16082,19 @@
     </row>
     <row r="3" spans="1:6" ht="19.5" customHeight="1">
       <c r="A3" s="77" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="F3" s="83" t="s">
         <v>23</v>
@@ -16363,7 +16102,7 @@
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1">
       <c r="A4" s="167" t="s">
-        <v>964</v>
+        <v>939</v>
       </c>
       <c r="B4" s="168"/>
       <c r="C4" s="168"/>
@@ -16373,99 +16112,99 @@
     </row>
     <row r="5" spans="1:6" ht="25.5" customHeight="1">
       <c r="A5" s="98" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>401</v>
+        <v>383</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
       <c r="F5" s="86" t="s">
-        <v>404</v>
+        <v>386</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="25.5" customHeight="1">
       <c r="A6" s="99" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="B6" s="54" t="s">
-        <v>405</v>
+        <v>387</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>408</v>
+        <v>390</v>
       </c>
       <c r="F6" s="113" t="s">
-        <v>409</v>
+        <v>391</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1">
       <c r="A7" s="100" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="B7" s="213" t="s">
-        <v>976</v>
+        <v>951</v>
       </c>
       <c r="C7" s="50" t="s">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="D7" s="50" t="s">
-        <v>977</v>
+        <v>952</v>
       </c>
       <c r="E7" s="50" t="s">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="F7" s="115" t="s">
-        <v>412</v>
+        <v>394</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="25.5" customHeight="1">
       <c r="A8" s="100" t="s">
+        <v>381</v>
+      </c>
+      <c r="B8" s="55" t="s">
+        <v>395</v>
+      </c>
+      <c r="C8" s="50" t="s">
+        <v>396</v>
+      </c>
+      <c r="D8" s="50" t="s">
+        <v>397</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>398</v>
+      </c>
+      <c r="F8" s="115" t="s">
         <v>399</v>
-      </c>
-      <c r="B8" s="55" t="s">
-        <v>413</v>
-      </c>
-      <c r="C8" s="50" t="s">
-        <v>414</v>
-      </c>
-      <c r="D8" s="50" t="s">
-        <v>415</v>
-      </c>
-      <c r="E8" s="50" t="s">
-        <v>416</v>
-      </c>
-      <c r="F8" s="115" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="25.5" customHeight="1">
       <c r="A9" s="100" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="B9" s="55" t="s">
-        <v>418</v>
+        <v>400</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>419</v>
+        <v>401</v>
       </c>
       <c r="D9" s="50" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="E9" s="50" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="F9" s="115" t="s">
         <v>28</v>
@@ -16473,87 +16212,87 @@
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1">
       <c r="A10" s="101" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="F10" s="116" t="s">
-        <v>426</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1">
       <c r="A11" s="102" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>427</v>
+        <v>409</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
       <c r="F11" s="117" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1">
       <c r="A12" s="103" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>431</v>
+        <v>413</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>432</v>
+        <v>414</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="E12" s="41" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="F12" s="118" t="s">
-        <v>435</v>
+        <v>417</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1">
       <c r="A13" s="101" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="B13" s="56" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="F13" s="116" t="s">
-        <v>426</v>
+        <v>408</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="25.5" customHeight="1">
       <c r="A14" s="167" t="s">
-        <v>965</v>
+        <v>940</v>
       </c>
       <c r="B14" s="168"/>
       <c r="C14" s="168"/>
@@ -16563,16 +16302,16 @@
     </row>
     <row r="15" spans="1:6" ht="30" customHeight="1">
       <c r="A15" s="101" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="B15" s="56" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>443</v>
+        <v>425</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>20</v>
@@ -16583,405 +16322,405 @@
     </row>
     <row r="16" spans="1:6" ht="30" customHeight="1">
       <c r="A16" s="104" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="B16" s="59" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="D16" s="47" t="s">
-        <v>446</v>
+        <v>428</v>
       </c>
       <c r="E16" s="47" t="s">
-        <v>447</v>
+        <v>429</v>
       </c>
       <c r="F16" s="119" t="s">
-        <v>448</v>
+        <v>430</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="25.5" customHeight="1">
       <c r="A17" s="105" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="B17" s="60" t="s">
-        <v>449</v>
+        <v>431</v>
       </c>
       <c r="C17" s="61" t="s">
-        <v>450</v>
+        <v>432</v>
       </c>
       <c r="D17" s="61" t="s">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="E17" s="61" t="s">
-        <v>447</v>
+        <v>429</v>
       </c>
       <c r="F17" s="120" t="s">
-        <v>452</v>
+        <v>434</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="25.5" customHeight="1">
       <c r="A18" s="104" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>453</v>
+        <v>435</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>454</v>
+        <v>436</v>
       </c>
       <c r="D18" s="47" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="E18" s="47" t="s">
-        <v>447</v>
+        <v>429</v>
       </c>
       <c r="F18" s="119" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="25.5" customHeight="1">
       <c r="A19" s="105" t="s">
+        <v>422</v>
+      </c>
+      <c r="B19" s="60" t="s">
+        <v>439</v>
+      </c>
+      <c r="C19" s="61" t="s">
         <v>440</v>
       </c>
-      <c r="B19" s="60" t="s">
-        <v>457</v>
-      </c>
-      <c r="C19" s="61" t="s">
-        <v>458</v>
-      </c>
       <c r="D19" s="61" t="s">
-        <v>459</v>
+        <v>441</v>
       </c>
       <c r="E19" s="61" t="s">
-        <v>460</v>
+        <v>442</v>
       </c>
       <c r="F19" s="120" t="s">
-        <v>461</v>
+        <v>443</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="25.5" customHeight="1">
       <c r="A20" s="105" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="B20" s="207" t="s">
-        <v>988</v>
+        <v>963</v>
       </c>
       <c r="C20" s="61" t="s">
-        <v>463</v>
+        <v>445</v>
       </c>
       <c r="D20" s="61" t="s">
-        <v>464</v>
+        <v>446</v>
       </c>
       <c r="E20" s="61" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="F20" s="120" t="s">
-        <v>466</v>
+        <v>448</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="25.5" customHeight="1">
       <c r="A21" s="106" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="B21" s="212" t="s">
-        <v>981</v>
+        <v>956</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>469</v>
+        <v>451</v>
       </c>
       <c r="F21" s="121" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="42" customHeight="1">
       <c r="A22" s="106" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="B22" s="212" t="s">
-        <v>557</v>
+        <v>539</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>978</v>
+        <v>953</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>979</v>
+        <v>954</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>980</v>
+        <v>955</v>
       </c>
       <c r="F22" s="121" t="s">
-        <v>963</v>
+        <v>938</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="42" customHeight="1">
       <c r="A23" s="98" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="B23" s="214" t="s">
-        <v>982</v>
+        <v>957</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>470</v>
+        <v>452</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>471</v>
+        <v>453</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F23" s="86" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="25.5" customHeight="1">
       <c r="A24" s="105" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="B24" s="207" t="s">
-        <v>983</v>
+        <v>958</v>
       </c>
       <c r="C24" s="61" t="s">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="D24" s="61" t="s">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="E24" s="61" t="s">
-        <v>474</v>
+        <v>456</v>
       </c>
       <c r="F24" s="120" t="s">
-        <v>475</v>
+        <v>457</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="25.5" customHeight="1">
       <c r="A25" s="105" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="B25" s="207" t="s">
-        <v>984</v>
+        <v>959</v>
       </c>
       <c r="C25" s="61" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="D25" s="61" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="E25" s="61" t="s">
-        <v>478</v>
+        <v>460</v>
       </c>
       <c r="F25" s="120" t="s">
-        <v>479</v>
+        <v>461</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="25.5" customHeight="1">
       <c r="A26" s="105" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="B26" s="207" t="s">
-        <v>985</v>
+        <v>960</v>
       </c>
       <c r="C26" s="61" t="s">
-        <v>480</v>
+        <v>462</v>
       </c>
       <c r="D26" s="61" t="s">
-        <v>481</v>
+        <v>463</v>
       </c>
       <c r="E26" s="61" t="s">
-        <v>482</v>
+        <v>464</v>
       </c>
       <c r="F26" s="120" t="s">
-        <v>483</v>
+        <v>465</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="42" customHeight="1">
       <c r="A27" s="105" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="B27" s="207" t="s">
-        <v>702</v>
+        <v>684</v>
       </c>
       <c r="C27" s="61" t="s">
-        <v>960</v>
+        <v>935</v>
       </c>
       <c r="D27" s="61" t="s">
-        <v>961</v>
+        <v>936</v>
       </c>
       <c r="E27" s="61" t="s">
-        <v>626</v>
+        <v>608</v>
       </c>
       <c r="F27" s="120" t="s">
-        <v>962</v>
+        <v>937</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="42" customHeight="1">
       <c r="A28" s="107" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="B28" s="215" t="s">
-        <v>986</v>
+        <v>961</v>
       </c>
       <c r="C28" s="36" t="s">
-        <v>989</v>
+        <v>964</v>
       </c>
       <c r="D28" s="36" t="s">
-        <v>990</v>
+        <v>965</v>
       </c>
       <c r="E28" s="36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F28" s="122" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="28">
       <c r="A29" s="102" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="B29" s="209" t="s">
-        <v>987</v>
+        <v>962</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>484</v>
+        <v>466</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>939</v>
+        <v>914</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>485</v>
+        <v>467</v>
       </c>
       <c r="F29" s="117" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="42" customHeight="1">
-      <c r="A30" s="217" t="s">
-        <v>440</v>
-      </c>
-      <c r="B30" s="218" t="s">
-        <v>702</v>
+      <c r="A30" s="221" t="s">
+        <v>422</v>
+      </c>
+      <c r="B30" s="222" t="s">
+        <v>684</v>
       </c>
       <c r="C30" s="61" t="s">
-        <v>1033</v>
+        <v>1006</v>
       </c>
       <c r="D30" s="61" t="s">
-        <v>1034</v>
+        <v>1007</v>
       </c>
       <c r="E30" s="61" t="s">
-        <v>1035</v>
+        <v>1008</v>
       </c>
       <c r="F30" s="120" t="s">
-        <v>1036</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="42" customHeight="1">
-      <c r="A31" s="217" t="s">
-        <v>440</v>
-      </c>
-      <c r="B31" s="218" t="s">
-        <v>702</v>
+      <c r="A31" s="221" t="s">
+        <v>422</v>
+      </c>
+      <c r="B31" s="222" t="s">
+        <v>684</v>
       </c>
       <c r="C31" s="61" t="s">
-        <v>1037</v>
+        <v>1010</v>
       </c>
       <c r="D31" s="61" t="s">
-        <v>1038</v>
+        <v>1011</v>
       </c>
       <c r="E31" s="61" t="s">
-        <v>1039</v>
+        <v>1012</v>
       </c>
       <c r="F31" s="120" t="s">
-        <v>1040</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="56" customHeight="1">
-      <c r="A32" s="217" t="s">
-        <v>440</v>
-      </c>
-      <c r="B32" s="218" t="s">
-        <v>702</v>
+      <c r="A32" s="221" t="s">
+        <v>422</v>
+      </c>
+      <c r="B32" s="222" t="s">
+        <v>684</v>
       </c>
       <c r="C32" s="61" t="s">
-        <v>1048</v>
+        <v>1021</v>
       </c>
       <c r="D32" s="61" t="s">
-        <v>1049</v>
+        <v>1022</v>
       </c>
       <c r="E32" s="61" t="s">
-        <v>1050</v>
+        <v>1023</v>
       </c>
       <c r="F32" s="120" t="s">
-        <v>1051</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="25.5" customHeight="1">
       <c r="A33" s="102" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="B33" s="57" t="s">
-        <v>934</v>
+        <v>909</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>935</v>
+        <v>910</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>936</v>
+        <v>911</v>
       </c>
       <c r="E33" s="33" t="s">
-        <v>937</v>
+        <v>912</v>
       </c>
       <c r="F33" s="117" t="s">
-        <v>938</v>
+        <v>913</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="30" customHeight="1">
       <c r="A34" s="107" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="B34" s="64" t="s">
-        <v>940</v>
+        <v>915</v>
       </c>
       <c r="C34" s="36" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="D34" s="36" t="s">
-        <v>487</v>
+        <v>469</v>
       </c>
       <c r="E34" s="36" t="s">
-        <v>488</v>
+        <v>470</v>
       </c>
       <c r="F34" s="122" t="s">
-        <v>489</v>
+        <v>471</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="25.5" customHeight="1">
       <c r="A35" s="101" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="B35" s="151" t="s">
-        <v>923</v>
+        <v>898</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>491</v>
+        <v>473</v>
       </c>
       <c r="D35" s="10"/>
       <c r="E35" s="10" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="F35" s="116" t="s">
-        <v>426</v>
+        <v>408</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="25.5" customHeight="1">
       <c r="A36" s="167" t="s">
-        <v>966</v>
+        <v>941</v>
       </c>
       <c r="B36" s="168"/>
       <c r="C36" s="168"/>
@@ -16991,16 +16730,16 @@
     </row>
     <row r="37" spans="1:6" ht="25.5" customHeight="1">
       <c r="A37" s="101" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="B37" s="56" t="s">
-        <v>493</v>
+        <v>475</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>494</v>
+        <v>476</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>20</v>
@@ -17011,387 +16750,387 @@
     </row>
     <row r="38" spans="1:6" ht="70" customHeight="1">
       <c r="A38" s="102" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="B38" s="209" t="s">
-        <v>702</v>
+        <v>684</v>
       </c>
       <c r="C38" s="33" t="s">
-        <v>1056</v>
+        <v>1029</v>
       </c>
       <c r="D38" s="33" t="s">
-        <v>1057</v>
+        <v>1030</v>
       </c>
       <c r="E38" s="35" t="s">
-        <v>1058</v>
+        <v>1031</v>
       </c>
       <c r="F38" s="117" t="s">
-        <v>1059</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="30" customHeight="1">
       <c r="A39" s="105" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="B39" s="60" t="s">
-        <v>495</v>
+        <v>477</v>
       </c>
       <c r="C39" s="61" t="s">
-        <v>496</v>
+        <v>478</v>
       </c>
       <c r="D39" s="61" t="s">
-        <v>497</v>
+        <v>479</v>
       </c>
       <c r="E39" s="61" t="s">
-        <v>498</v>
+        <v>480</v>
       </c>
       <c r="F39" s="120" t="s">
-        <v>499</v>
+        <v>481</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="25.5" customHeight="1">
       <c r="A40" s="105" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="B40" s="60" t="s">
-        <v>500</v>
+        <v>482</v>
       </c>
       <c r="C40" s="61" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="D40" s="61" t="s">
-        <v>502</v>
+        <v>484</v>
       </c>
       <c r="E40" s="61" t="s">
-        <v>503</v>
+        <v>485</v>
       </c>
       <c r="F40" s="120" t="s">
-        <v>504</v>
+        <v>486</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="25.5" customHeight="1">
       <c r="A41" s="104" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="B41" s="59" t="s">
-        <v>505</v>
+        <v>487</v>
       </c>
       <c r="C41" s="47" t="s">
-        <v>506</v>
+        <v>488</v>
       </c>
       <c r="D41" s="47" t="s">
-        <v>507</v>
+        <v>489</v>
       </c>
       <c r="E41" s="47" t="s">
-        <v>447</v>
+        <v>429</v>
       </c>
       <c r="F41" s="119" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="42" customHeight="1">
       <c r="A42" s="99" t="s">
+        <v>474</v>
+      </c>
+      <c r="B42" s="54" t="s">
+        <v>490</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>491</v>
+      </c>
+      <c r="D42" s="15" t="s">
         <v>492</v>
       </c>
-      <c r="B42" s="54" t="s">
-        <v>508</v>
-      </c>
-      <c r="C42" s="15" t="s">
-        <v>509</v>
-      </c>
-      <c r="D42" s="15" t="s">
-        <v>510</v>
-      </c>
       <c r="E42" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F42" s="85" t="s">
-        <v>511</v>
+        <v>493</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="25.5" customHeight="1">
       <c r="A43" s="105" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="B43" s="60" t="s">
-        <v>512</v>
+        <v>494</v>
       </c>
       <c r="C43" s="61" t="s">
-        <v>513</v>
+        <v>495</v>
       </c>
       <c r="D43" s="61" t="s">
-        <v>514</v>
+        <v>496</v>
       </c>
       <c r="E43" s="61" t="s">
-        <v>503</v>
+        <v>485</v>
       </c>
       <c r="F43" s="120" t="s">
-        <v>515</v>
+        <v>497</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="42" customHeight="1">
       <c r="A44" s="103" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="B44" s="58" t="s">
-        <v>516</v>
+        <v>498</v>
       </c>
       <c r="C44" s="39" t="s">
-        <v>517</v>
+        <v>499</v>
       </c>
       <c r="D44" s="39" t="s">
-        <v>518</v>
+        <v>500</v>
       </c>
       <c r="E44" s="39" t="s">
-        <v>519</v>
+        <v>501</v>
       </c>
       <c r="F44" s="118" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="25.5" customHeight="1">
       <c r="A45" s="108" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="B45" s="89" t="s">
-        <v>895</v>
+        <v>870</v>
       </c>
       <c r="C45" s="90" t="s">
-        <v>896</v>
+        <v>871</v>
       </c>
       <c r="D45" s="90" t="s">
-        <v>897</v>
+        <v>872</v>
       </c>
       <c r="E45" s="90" t="s">
-        <v>898</v>
+        <v>873</v>
       </c>
       <c r="F45" s="123" t="s">
-        <v>899</v>
+        <v>874</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="25.5" customHeight="1">
       <c r="A46" s="102" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="B46" s="57" t="s">
-        <v>628</v>
+        <v>610</v>
       </c>
       <c r="C46" s="33" t="s">
-        <v>521</v>
+        <v>503</v>
       </c>
       <c r="D46" s="33" t="s">
-        <v>522</v>
+        <v>504</v>
       </c>
       <c r="E46" s="35" t="s">
-        <v>523</v>
+        <v>505</v>
       </c>
       <c r="F46" s="117" t="s">
-        <v>524</v>
+        <v>506</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="42" customHeight="1">
       <c r="A47" s="102" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="B47" s="209" t="s">
-        <v>702</v>
+        <v>684</v>
       </c>
       <c r="C47" s="33" t="s">
-        <v>957</v>
+        <v>932</v>
       </c>
       <c r="D47" s="33" t="s">
-        <v>958</v>
+        <v>933</v>
       </c>
       <c r="E47" s="35" t="s">
-        <v>626</v>
+        <v>608</v>
       </c>
       <c r="F47" s="117" t="s">
-        <v>959</v>
+        <v>934</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="42" customHeight="1">
       <c r="A48" s="106" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="B48" s="63" t="s">
-        <v>917</v>
+        <v>892</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>525</v>
+        <v>507</v>
       </c>
       <c r="D48" s="20" t="s">
-        <v>526</v>
+        <v>508</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>527</v>
+        <v>509</v>
       </c>
       <c r="F48" s="121" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="42" customHeight="1">
       <c r="A49" s="105" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="B49" s="207" t="s">
-        <v>991</v>
+        <v>966</v>
       </c>
       <c r="C49" s="61" t="s">
-        <v>528</v>
+        <v>510</v>
       </c>
       <c r="D49" s="61" t="s">
-        <v>992</v>
+        <v>967</v>
       </c>
       <c r="E49" s="61" t="s">
-        <v>529</v>
+        <v>511</v>
       </c>
       <c r="F49" s="120" t="s">
-        <v>530</v>
+        <v>512</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="25.5" customHeight="1">
       <c r="A50" s="103" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="B50" s="210" t="s">
-        <v>702</v>
+        <v>684</v>
       </c>
       <c r="C50" s="39" t="s">
-        <v>531</v>
+        <v>513</v>
       </c>
       <c r="D50" s="39" t="s">
-        <v>993</v>
+        <v>968</v>
       </c>
       <c r="E50" s="39" t="s">
-        <v>994</v>
+        <v>969</v>
       </c>
       <c r="F50" s="118" t="s">
-        <v>533</v>
+        <v>515</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="25.5" customHeight="1">
       <c r="A51" s="98" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="B51" s="53" t="s">
-        <v>995</v>
+        <v>970</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>996</v>
+        <v>971</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>997</v>
+        <v>972</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>998</v>
+        <v>973</v>
       </c>
       <c r="F51" s="86" t="s">
-        <v>999</v>
+        <v>974</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="42" customHeight="1">
       <c r="A52" s="98" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="B52" s="214" t="s">
-        <v>1000</v>
+        <v>975</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>1001</v>
+        <v>976</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>1002</v>
+        <v>977</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>1003</v>
+        <v>978</v>
       </c>
       <c r="F52" s="86" t="s">
-        <v>999</v>
+        <v>974</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="30" customHeight="1">
       <c r="A53" s="101" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="B53" s="151" t="s">
-        <v>923</v>
+        <v>898</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>535</v>
+        <v>517</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>1004</v>
+        <v>979</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="F53" s="116" t="s">
-        <v>426</v>
+        <v>408</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="25.5" customHeight="1">
       <c r="A54" s="109" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="B54" s="65" t="s">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="C54" s="42" t="s">
-        <v>537</v>
+        <v>519</v>
       </c>
       <c r="D54" s="42" t="s">
-        <v>538</v>
+        <v>520</v>
       </c>
       <c r="E54" s="42" t="s">
-        <v>539</v>
+        <v>521</v>
       </c>
       <c r="F54" s="124" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="25.5" customHeight="1">
       <c r="A55" s="103" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="B55" s="58" t="s">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="C55" s="39" t="s">
-        <v>540</v>
+        <v>522</v>
       </c>
       <c r="D55" s="39" t="s">
-        <v>541</v>
+        <v>523</v>
       </c>
       <c r="E55" s="39" t="s">
-        <v>539</v>
+        <v>521</v>
       </c>
       <c r="F55" s="118" t="s">
-        <v>542</v>
+        <v>524</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="25.5" customHeight="1">
       <c r="A56" s="103" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="B56" s="210" t="s">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="C56" s="39" t="s">
-        <v>953</v>
+        <v>928</v>
       </c>
       <c r="D56" s="211" t="s">
-        <v>954</v>
+        <v>929</v>
       </c>
       <c r="E56" s="39" t="s">
-        <v>955</v>
+        <v>930</v>
       </c>
       <c r="F56" s="118" t="s">
-        <v>956</v>
+        <v>931</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="25.5" customHeight="1">
       <c r="A57" s="152" t="s">
-        <v>973</v>
+        <v>948</v>
       </c>
       <c r="B57" s="153"/>
       <c r="C57" s="153"/>
@@ -17401,19 +17140,19 @@
     </row>
     <row r="58" spans="1:6" ht="45" customHeight="1">
       <c r="A58" s="101" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="B58" s="56" t="s">
-        <v>493</v>
+        <v>475</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>544</v>
+        <v>526</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>545</v>
+        <v>527</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="F58" s="116" t="s">
         <v>28</v>
@@ -17421,265 +17160,265 @@
     </row>
     <row r="59" spans="1:6" ht="25.5" customHeight="1">
       <c r="A59" s="100" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="B59" s="55" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="C59" s="50" t="s">
-        <v>548</v>
+        <v>530</v>
       </c>
       <c r="D59" s="50" t="s">
-        <v>549</v>
+        <v>531</v>
       </c>
       <c r="E59" s="50" t="s">
-        <v>550</v>
+        <v>532</v>
       </c>
       <c r="F59" s="115" t="s">
-        <v>551</v>
+        <v>533</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="30" customHeight="1">
       <c r="A60" s="100" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="B60" s="55" t="s">
-        <v>552</v>
+        <v>534</v>
       </c>
       <c r="C60" s="50" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="D60" s="50" t="s">
-        <v>554</v>
+        <v>536</v>
       </c>
       <c r="E60" s="50" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F60" s="115" t="s">
-        <v>556</v>
+        <v>538</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="30" customHeight="1">
       <c r="A61" s="101" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="B61" s="56" t="s">
-        <v>557</v>
+        <v>539</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>558</v>
+        <v>540</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>559</v>
+        <v>541</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="F61" s="116" t="s">
-        <v>560</v>
+        <v>542</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="25.5" customHeight="1">
       <c r="A62" s="99" t="s">
+        <v>525</v>
+      </c>
+      <c r="B62" s="54" t="s">
         <v>543</v>
       </c>
-      <c r="B62" s="54" t="s">
-        <v>561</v>
-      </c>
       <c r="C62" s="15" t="s">
-        <v>562</v>
+        <v>544</v>
       </c>
       <c r="D62" s="25" t="s">
-        <v>563</v>
+        <v>545</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="F62" s="85" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="21.75" customHeight="1">
       <c r="A63" s="105" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="B63" s="60" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="C63" s="61" t="s">
-        <v>565</v>
+        <v>547</v>
       </c>
       <c r="D63" s="61" t="s">
-        <v>566</v>
+        <v>548</v>
       </c>
       <c r="E63" s="61" t="s">
-        <v>503</v>
+        <v>485</v>
       </c>
       <c r="F63" s="120" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="25.5" customHeight="1">
       <c r="A64" s="105" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="B64" s="60" t="s">
-        <v>567</v>
+        <v>549</v>
       </c>
       <c r="C64" s="61" t="s">
-        <v>568</v>
+        <v>550</v>
       </c>
       <c r="D64" s="61" t="s">
-        <v>569</v>
+        <v>551</v>
       </c>
       <c r="E64" s="61" t="s">
-        <v>570</v>
+        <v>552</v>
       </c>
       <c r="F64" s="120" t="s">
-        <v>571</v>
+        <v>553</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="25.5" customHeight="1">
       <c r="A65" s="106" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="B65" s="63" t="s">
-        <v>572</v>
+        <v>554</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>573</v>
+        <v>555</v>
       </c>
       <c r="D65" s="20" t="s">
-        <v>574</v>
+        <v>556</v>
       </c>
       <c r="E65" s="20" t="s">
-        <v>575</v>
+        <v>557</v>
       </c>
       <c r="F65" s="121" t="s">
-        <v>576</v>
+        <v>558</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="30" customHeight="1">
       <c r="A66" s="105" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="B66" s="60" t="s">
-        <v>577</v>
+        <v>559</v>
       </c>
       <c r="C66" s="61" t="s">
-        <v>578</v>
+        <v>560</v>
       </c>
       <c r="D66" s="61" t="s">
-        <v>579</v>
+        <v>561</v>
       </c>
       <c r="E66" s="61" t="s">
-        <v>570</v>
+        <v>552</v>
       </c>
       <c r="F66" s="120" t="s">
-        <v>580</v>
+        <v>562</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="30" customHeight="1">
       <c r="A67" s="110" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="B67" s="91" t="s">
-        <v>918</v>
+        <v>893</v>
       </c>
       <c r="C67" s="92" t="s">
-        <v>900</v>
+        <v>875</v>
       </c>
       <c r="D67" s="92" t="s">
-        <v>901</v>
+        <v>876</v>
       </c>
       <c r="E67" s="92" t="s">
-        <v>902</v>
+        <v>877</v>
       </c>
       <c r="F67" s="125" t="s">
-        <v>903</v>
+        <v>878</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="30" customHeight="1">
       <c r="A68" s="105" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="B68" s="60" t="s">
-        <v>585</v>
+        <v>567</v>
       </c>
       <c r="C68" s="61" t="s">
-        <v>581</v>
+        <v>563</v>
       </c>
       <c r="D68" s="61" t="s">
-        <v>582</v>
+        <v>564</v>
       </c>
       <c r="E68" s="61" t="s">
-        <v>583</v>
+        <v>565</v>
       </c>
       <c r="F68" s="120" t="s">
-        <v>584</v>
+        <v>566</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="25.5" customHeight="1">
       <c r="A69" s="107" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="B69" s="64" t="s">
-        <v>919</v>
+        <v>894</v>
       </c>
       <c r="C69" s="36" t="s">
-        <v>586</v>
+        <v>568</v>
       </c>
       <c r="D69" s="36" t="s">
-        <v>587</v>
+        <v>569</v>
       </c>
       <c r="E69" s="36" t="s">
-        <v>588</v>
+        <v>570</v>
       </c>
       <c r="F69" s="122" t="s">
-        <v>589</v>
+        <v>571</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="25.5" customHeight="1">
       <c r="A70" s="109" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="B70" s="65" t="s">
-        <v>920</v>
+        <v>895</v>
       </c>
       <c r="C70" s="42" t="s">
-        <v>590</v>
+        <v>572</v>
       </c>
       <c r="D70" s="44" t="s">
-        <v>591</v>
+        <v>573</v>
       </c>
       <c r="E70" s="42" t="s">
-        <v>592</v>
+        <v>574</v>
       </c>
       <c r="F70" s="124" t="s">
-        <v>593</v>
+        <v>575</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="30" customHeight="1">
       <c r="A71" s="101" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="B71" s="128" t="s">
-        <v>923</v>
+        <v>898</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>595</v>
+        <v>577</v>
       </c>
       <c r="D71" s="10"/>
       <c r="E71" s="10" t="s">
-        <v>596</v>
+        <v>578</v>
       </c>
       <c r="F71" s="116" t="s">
-        <v>560</v>
+        <v>542</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="30" customHeight="1">
       <c r="A72" s="152" t="s">
-        <v>967</v>
+        <v>942</v>
       </c>
       <c r="B72" s="153"/>
       <c r="C72" s="153"/>
@@ -17689,16 +17428,16 @@
     </row>
     <row r="73" spans="1:6" ht="30" customHeight="1">
       <c r="A73" s="101" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="B73" s="56" t="s">
-        <v>493</v>
+        <v>475</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>598</v>
+        <v>580</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>599</v>
+        <v>581</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>20</v>
@@ -17709,219 +17448,219 @@
     </row>
     <row r="74" spans="1:6" ht="25.5" customHeight="1">
       <c r="A74" s="105" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="B74" s="60" t="s">
-        <v>600</v>
+        <v>582</v>
       </c>
       <c r="C74" s="61" t="s">
-        <v>601</v>
+        <v>583</v>
       </c>
       <c r="D74" s="62" t="s">
-        <v>602</v>
+        <v>584</v>
       </c>
       <c r="E74" s="61" t="s">
-        <v>603</v>
+        <v>585</v>
       </c>
       <c r="F74" s="120" t="s">
-        <v>604</v>
+        <v>586</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="30" customHeight="1">
       <c r="A75" s="108" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="B75" s="89" t="s">
-        <v>904</v>
+        <v>879</v>
       </c>
       <c r="C75" s="90" t="s">
-        <v>905</v>
+        <v>880</v>
       </c>
       <c r="D75" s="90" t="s">
-        <v>906</v>
+        <v>881</v>
       </c>
       <c r="E75" s="90" t="s">
-        <v>907</v>
+        <v>882</v>
       </c>
       <c r="F75" s="123" t="s">
-        <v>908</v>
+        <v>883</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="30" customHeight="1">
       <c r="A76" s="103" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="B76" s="58" t="s">
-        <v>921</v>
+        <v>896</v>
       </c>
       <c r="C76" s="39" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="D76" s="39" t="s">
-        <v>606</v>
+        <v>588</v>
       </c>
       <c r="E76" s="39" t="s">
-        <v>607</v>
+        <v>589</v>
       </c>
       <c r="F76" s="118" t="s">
-        <v>608</v>
+        <v>590</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="42" customHeight="1">
       <c r="A77" s="104" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="B77" s="59" t="s">
-        <v>462</v>
+        <v>444</v>
       </c>
       <c r="C77" s="47" t="s">
-        <v>609</v>
+        <v>591</v>
       </c>
       <c r="D77" s="47" t="s">
-        <v>610</v>
+        <v>592</v>
       </c>
       <c r="E77" s="47" t="s">
-        <v>611</v>
+        <v>593</v>
       </c>
       <c r="F77" s="119" t="s">
-        <v>612</v>
+        <v>594</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="25.5" customHeight="1">
       <c r="A78" s="105" t="s">
+        <v>579</v>
+      </c>
+      <c r="B78" s="60" t="s">
+        <v>595</v>
+      </c>
+      <c r="C78" s="61" t="s">
+        <v>596</v>
+      </c>
+      <c r="D78" s="61" t="s">
         <v>597</v>
       </c>
-      <c r="B78" s="60" t="s">
-        <v>613</v>
-      </c>
-      <c r="C78" s="61" t="s">
-        <v>614</v>
-      </c>
-      <c r="D78" s="61" t="s">
-        <v>615</v>
-      </c>
       <c r="E78" s="61" t="s">
-        <v>616</v>
+        <v>598</v>
       </c>
       <c r="F78" s="120" t="s">
-        <v>617</v>
+        <v>599</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="30" customHeight="1">
       <c r="A79" s="98" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="B79" s="53" t="s">
-        <v>618</v>
+        <v>600</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>619</v>
+        <v>601</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>620</v>
+        <v>602</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>621</v>
+        <v>603</v>
       </c>
       <c r="F79" s="86" t="s">
-        <v>622</v>
+        <v>604</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="30" customHeight="1">
       <c r="A80" s="103" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="B80" s="58" t="s">
-        <v>623</v>
+        <v>605</v>
       </c>
       <c r="C80" s="39" t="s">
-        <v>624</v>
+        <v>606</v>
       </c>
       <c r="D80" s="39" t="s">
-        <v>625</v>
+        <v>607</v>
       </c>
       <c r="E80" s="39" t="s">
-        <v>626</v>
+        <v>608</v>
       </c>
       <c r="F80" s="118" t="s">
-        <v>627</v>
+        <v>609</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="42" customHeight="1">
       <c r="A81" s="105" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="B81" s="60" t="s">
-        <v>628</v>
+        <v>610</v>
       </c>
       <c r="C81" s="61" t="s">
-        <v>629</v>
+        <v>611</v>
       </c>
       <c r="D81" s="61" t="s">
-        <v>630</v>
+        <v>612</v>
       </c>
       <c r="E81" s="61" t="s">
-        <v>631</v>
+        <v>613</v>
       </c>
       <c r="F81" s="120" t="s">
-        <v>632</v>
+        <v>614</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="30" customHeight="1">
       <c r="A82" s="104" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="B82" s="59" t="s">
-        <v>633</v>
+        <v>615</v>
       </c>
       <c r="C82" s="47" t="s">
-        <v>634</v>
+        <v>616</v>
       </c>
       <c r="D82" s="47" t="s">
-        <v>635</v>
+        <v>617</v>
       </c>
       <c r="E82" s="47" t="s">
-        <v>626</v>
+        <v>608</v>
       </c>
       <c r="F82" s="119" t="s">
-        <v>636</v>
+        <v>618</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="21.75" customHeight="1">
       <c r="A83" s="106" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="B83" s="63" t="s">
-        <v>637</v>
+        <v>619</v>
       </c>
       <c r="C83" s="20" t="s">
-        <v>638</v>
+        <v>620</v>
       </c>
       <c r="D83" s="20" t="s">
-        <v>639</v>
+        <v>621</v>
       </c>
       <c r="E83" s="20" t="s">
-        <v>640</v>
+        <v>622</v>
       </c>
       <c r="F83" s="121" t="s">
-        <v>641</v>
+        <v>623</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="42" customHeight="1">
       <c r="A84" s="102" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="B84" s="57" t="s">
-        <v>642</v>
+        <v>624</v>
       </c>
       <c r="C84" s="33" t="s">
-        <v>643</v>
+        <v>625</v>
       </c>
       <c r="D84" s="33" t="s">
-        <v>644</v>
+        <v>626</v>
       </c>
       <c r="E84" s="33" t="s">
-        <v>645</v>
+        <v>627</v>
       </c>
       <c r="F84" s="117" t="s">
         <v>33</v>
@@ -17929,59 +17668,59 @@
     </row>
     <row r="85" spans="1:6" ht="25.5" customHeight="1">
       <c r="A85" s="102" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="B85" s="209" t="s">
-        <v>702</v>
+        <v>684</v>
       </c>
       <c r="C85" s="33" t="s">
-        <v>950</v>
+        <v>925</v>
       </c>
       <c r="D85" s="33" t="s">
-        <v>951</v>
+        <v>926</v>
       </c>
       <c r="E85" s="33" t="s">
-        <v>626</v>
+        <v>608</v>
       </c>
       <c r="F85" s="117" t="s">
-        <v>952</v>
+        <v>927</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="25.5" customHeight="1">
       <c r="A86" s="107" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="B86" s="64" t="s">
-        <v>534</v>
+        <v>516</v>
       </c>
       <c r="C86" s="36" t="s">
-        <v>646</v>
+        <v>628</v>
       </c>
       <c r="D86" s="36" t="s">
-        <v>647</v>
+        <v>629</v>
       </c>
       <c r="E86" s="36" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="F86" s="122" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="30" customHeight="1">
       <c r="A87" s="101" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="B87" s="56" t="s">
-        <v>648</v>
+        <v>630</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>649</v>
+        <v>631</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>650</v>
+        <v>632</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>532</v>
+        <v>514</v>
       </c>
       <c r="F87" s="116" t="s">
         <v>33</v>
@@ -17989,127 +17728,127 @@
     </row>
     <row r="88" spans="1:6" ht="25.5" customHeight="1">
       <c r="A88" s="101" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="B88" s="56" t="s">
-        <v>594</v>
+        <v>576</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>651</v>
+        <v>633</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>652</v>
+        <v>634</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>596</v>
+        <v>578</v>
       </c>
       <c r="F88" s="116" t="s">
-        <v>560</v>
+        <v>542</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="42" customHeight="1">
       <c r="A89" s="103" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="B89" s="58" t="s">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="C89" s="39" t="s">
-        <v>653</v>
+        <v>635</v>
       </c>
       <c r="D89" s="39" t="s">
-        <v>654</v>
+        <v>636</v>
       </c>
       <c r="E89" s="39" t="s">
-        <v>539</v>
+        <v>521</v>
       </c>
       <c r="F89" s="118" t="s">
-        <v>655</v>
+        <v>637</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="30" customHeight="1">
       <c r="A90" s="103" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="B90" s="58" t="s">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="C90" s="39" t="s">
-        <v>656</v>
+        <v>638</v>
       </c>
       <c r="D90" s="39" t="s">
-        <v>657</v>
+        <v>639</v>
       </c>
       <c r="E90" s="39" t="s">
-        <v>539</v>
+        <v>521</v>
       </c>
       <c r="F90" s="118" t="s">
-        <v>658</v>
+        <v>640</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="25.5" customHeight="1">
       <c r="A91" s="103" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="B91" s="58" t="s">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="C91" s="39" t="s">
-        <v>659</v>
+        <v>641</v>
       </c>
       <c r="D91" s="39" t="s">
-        <v>660</v>
+        <v>642</v>
       </c>
       <c r="E91" s="39" t="s">
-        <v>539</v>
+        <v>521</v>
       </c>
       <c r="F91" s="118" t="s">
-        <v>661</v>
+        <v>643</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="25.5" customHeight="1">
       <c r="A92" s="108" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="B92" s="89" t="s">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="C92" s="90" t="s">
-        <v>909</v>
+        <v>884</v>
       </c>
       <c r="D92" s="95" t="s">
-        <v>910</v>
+        <v>885</v>
       </c>
       <c r="E92" s="90" t="s">
-        <v>911</v>
+        <v>886</v>
       </c>
       <c r="F92" s="123" t="s">
-        <v>912</v>
+        <v>887</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="30" customHeight="1">
       <c r="A93" s="108" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="B93" s="208" t="s">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="C93" s="90" t="s">
-        <v>947</v>
+        <v>922</v>
       </c>
       <c r="D93" s="95" t="s">
-        <v>948</v>
+        <v>923</v>
       </c>
       <c r="E93" s="90" t="s">
-        <v>911</v>
+        <v>886</v>
       </c>
       <c r="F93" s="123" t="s">
-        <v>949</v>
+        <v>924</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="30" customHeight="1">
       <c r="A94" s="155" t="s">
-        <v>974</v>
+        <v>949</v>
       </c>
       <c r="B94" s="156"/>
       <c r="C94" s="156"/>
@@ -18119,17 +17858,17 @@
     </row>
     <row r="95" spans="1:6" ht="42" customHeight="1">
       <c r="A95" s="101" t="s">
-        <v>662</v>
+        <v>644</v>
       </c>
       <c r="B95" s="56" t="s">
-        <v>493</v>
+        <v>475</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>663</v>
+        <v>645</v>
       </c>
       <c r="D95" s="10"/>
       <c r="E95" s="10" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="F95" s="116" t="s">
         <v>33</v>
@@ -18137,325 +17876,325 @@
     </row>
     <row r="96" spans="1:6" ht="25.5" customHeight="1">
       <c r="A96" s="100" t="s">
-        <v>662</v>
+        <v>644</v>
       </c>
       <c r="B96" s="55" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="C96" s="50" t="s">
-        <v>664</v>
+        <v>646</v>
       </c>
       <c r="D96" s="50" t="s">
-        <v>665</v>
+        <v>647</v>
       </c>
       <c r="E96" s="50" t="s">
-        <v>550</v>
+        <v>532</v>
       </c>
       <c r="F96" s="115" t="s">
-        <v>666</v>
+        <v>648</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="45" customHeight="1">
       <c r="A97" s="100" t="s">
-        <v>662</v>
+        <v>644</v>
       </c>
       <c r="B97" s="55" t="s">
-        <v>552</v>
+        <v>534</v>
       </c>
       <c r="C97" s="50" t="s">
-        <v>667</v>
+        <v>649</v>
       </c>
       <c r="D97" s="50" t="s">
-        <v>668</v>
+        <v>650</v>
       </c>
       <c r="E97" s="50" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F97" s="115" t="s">
-        <v>669</v>
+        <v>651</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="30" customHeight="1">
       <c r="A98" s="101" t="s">
-        <v>662</v>
+        <v>644</v>
       </c>
       <c r="B98" s="56" t="s">
-        <v>557</v>
+        <v>539</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>670</v>
+        <v>652</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>671</v>
+        <v>653</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>672</v>
+        <v>654</v>
       </c>
       <c r="F98" s="116" t="s">
-        <v>673</v>
+        <v>655</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="21.75" customHeight="1">
       <c r="A99" s="99" t="s">
-        <v>662</v>
+        <v>644</v>
       </c>
       <c r="B99" s="54" t="s">
-        <v>561</v>
+        <v>543</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>674</v>
+        <v>656</v>
       </c>
       <c r="D99" s="15" t="s">
-        <v>675</v>
+        <v>657</v>
       </c>
       <c r="E99" s="15" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F99" s="85" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="25.5" customHeight="1">
       <c r="A100" s="105" t="s">
+        <v>644</v>
+      </c>
+      <c r="B100" s="60" t="s">
+        <v>658</v>
+      </c>
+      <c r="C100" s="61" t="s">
+        <v>659</v>
+      </c>
+      <c r="D100" s="61" t="s">
+        <v>660</v>
+      </c>
+      <c r="E100" s="61" t="s">
+        <v>661</v>
+      </c>
+      <c r="F100" s="120" t="s">
         <v>662</v>
-      </c>
-      <c r="B100" s="60" t="s">
-        <v>676</v>
-      </c>
-      <c r="C100" s="61" t="s">
-        <v>677</v>
-      </c>
-      <c r="D100" s="61" t="s">
-        <v>678</v>
-      </c>
-      <c r="E100" s="61" t="s">
-        <v>679</v>
-      </c>
-      <c r="F100" s="120" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="42" customHeight="1">
       <c r="A101" s="105" t="s">
-        <v>662</v>
+        <v>644</v>
       </c>
       <c r="B101" s="60" t="s">
-        <v>681</v>
+        <v>663</v>
       </c>
       <c r="C101" s="61" t="s">
-        <v>682</v>
+        <v>664</v>
       </c>
       <c r="D101" s="61" t="s">
-        <v>683</v>
+        <v>665</v>
       </c>
       <c r="E101" s="61" t="s">
-        <v>603</v>
+        <v>585</v>
       </c>
       <c r="F101" s="120" t="s">
-        <v>684</v>
+        <v>666</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="30" customHeight="1">
       <c r="A102" s="105" t="s">
-        <v>662</v>
+        <v>644</v>
       </c>
       <c r="B102" s="60" t="s">
-        <v>685</v>
+        <v>667</v>
       </c>
       <c r="C102" s="61" t="s">
-        <v>686</v>
+        <v>668</v>
       </c>
       <c r="D102" s="61" t="s">
-        <v>687</v>
+        <v>669</v>
       </c>
       <c r="E102" s="61" t="s">
-        <v>688</v>
+        <v>670</v>
       </c>
       <c r="F102" s="120" t="s">
-        <v>689</v>
+        <v>671</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="45" customHeight="1">
       <c r="A103" s="106" t="s">
-        <v>662</v>
+        <v>644</v>
       </c>
       <c r="B103" s="63" t="s">
-        <v>690</v>
+        <v>672</v>
       </c>
       <c r="C103" s="20" t="s">
-        <v>691</v>
+        <v>673</v>
       </c>
       <c r="D103" s="20" t="s">
-        <v>692</v>
+        <v>674</v>
       </c>
       <c r="E103" s="20" t="s">
-        <v>693</v>
+        <v>675</v>
       </c>
       <c r="F103" s="121" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="25.5" customHeight="1">
       <c r="A104" s="105" t="s">
-        <v>662</v>
+        <v>644</v>
       </c>
       <c r="B104" s="60" t="s">
-        <v>694</v>
+        <v>676</v>
       </c>
       <c r="C104" s="61" t="s">
-        <v>695</v>
+        <v>677</v>
       </c>
       <c r="D104" s="61" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="E104" s="61" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F104" s="120" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="42" customHeight="1">
       <c r="A105" s="105" t="s">
-        <v>662</v>
+        <v>644</v>
       </c>
       <c r="B105" s="207" t="s">
-        <v>702</v>
+        <v>684</v>
       </c>
       <c r="C105" s="61" t="s">
-        <v>945</v>
+        <v>920</v>
       </c>
       <c r="D105" s="61" t="s">
-        <v>946</v>
+        <v>921</v>
       </c>
       <c r="E105" s="61" t="s">
-        <v>626</v>
+        <v>608</v>
       </c>
       <c r="F105" s="120" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="130" customHeight="1">
       <c r="A106" s="105" t="s">
-        <v>662</v>
+        <v>644</v>
       </c>
       <c r="B106" s="207" t="s">
-        <v>702</v>
+        <v>684</v>
       </c>
       <c r="C106" s="61" t="s">
-        <v>1083</v>
+        <v>1056</v>
       </c>
       <c r="D106" s="61" t="s">
-        <v>1084</v>
+        <v>1057</v>
       </c>
       <c r="E106" s="61" t="s">
-        <v>1085</v>
+        <v>1058</v>
       </c>
       <c r="F106" s="120" t="s">
-        <v>1086</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="30" customHeight="1">
       <c r="A107" s="109" t="s">
-        <v>662</v>
+        <v>644</v>
       </c>
       <c r="B107" s="65" t="s">
-        <v>697</v>
+        <v>679</v>
       </c>
       <c r="C107" s="42" t="s">
-        <v>698</v>
+        <v>680</v>
       </c>
       <c r="D107" s="42" t="s">
-        <v>699</v>
+        <v>681</v>
       </c>
       <c r="E107" s="42" t="s">
-        <v>700</v>
+        <v>682</v>
       </c>
       <c r="F107" s="124" t="s">
-        <v>701</v>
+        <v>683</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="25.5" customHeight="1">
       <c r="A108" s="111" t="s">
-        <v>662</v>
+        <v>644</v>
       </c>
       <c r="B108" s="93" t="s">
-        <v>913</v>
+        <v>888</v>
       </c>
       <c r="C108" s="94" t="s">
-        <v>914</v>
+        <v>889</v>
       </c>
       <c r="D108" s="94" t="s">
-        <v>915</v>
+        <v>890</v>
       </c>
       <c r="E108" s="94" t="s">
-        <v>916</v>
+        <v>891</v>
       </c>
       <c r="F108" s="126" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="25.5" customHeight="1">
       <c r="A109" s="101" t="s">
-        <v>662</v>
+        <v>644</v>
       </c>
       <c r="B109" s="128" t="s">
-        <v>923</v>
+        <v>898</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>922</v>
+        <v>897</v>
       </c>
       <c r="D109" s="10"/>
       <c r="E109" s="10" t="s">
-        <v>596</v>
+        <v>578</v>
       </c>
       <c r="F109" s="116" t="s">
-        <v>673</v>
+        <v>655</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="30" customHeight="1">
       <c r="A110" s="102" t="s">
-        <v>662</v>
+        <v>644</v>
       </c>
       <c r="B110" s="57" t="s">
-        <v>702</v>
+        <v>684</v>
       </c>
       <c r="C110" s="33" t="s">
-        <v>703</v>
+        <v>685</v>
       </c>
       <c r="D110" s="33" t="s">
-        <v>704</v>
+        <v>686</v>
       </c>
       <c r="E110" s="33" t="s">
-        <v>532</v>
+        <v>514</v>
       </c>
       <c r="F110" s="117" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="25.5" customHeight="1">
       <c r="A111" s="103" t="s">
-        <v>662</v>
+        <v>644</v>
       </c>
       <c r="B111" s="58" t="s">
-        <v>702</v>
+        <v>684</v>
       </c>
       <c r="C111" s="39" t="s">
-        <v>968</v>
+        <v>943</v>
       </c>
       <c r="D111" s="39" t="s">
-        <v>969</v>
+        <v>944</v>
       </c>
       <c r="E111" s="39" t="s">
-        <v>532</v>
+        <v>514</v>
       </c>
       <c r="F111" s="118" t="s">
-        <v>970</v>
+        <v>945</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="42" customHeight="1">
       <c r="A112" s="155" t="s">
-        <v>975</v>
+        <v>950</v>
       </c>
       <c r="B112" s="156"/>
       <c r="C112" s="156"/>
@@ -18465,16 +18204,16 @@
     </row>
     <row r="113" spans="1:6" ht="45" customHeight="1">
       <c r="A113" s="101" t="s">
-        <v>705</v>
+        <v>687</v>
       </c>
       <c r="B113" s="56" t="s">
-        <v>493</v>
+        <v>475</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>598</v>
+        <v>580</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>706</v>
+        <v>688</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>20</v>
@@ -18485,327 +18224,327 @@
     </row>
     <row r="114" spans="1:6" ht="25.5" customHeight="1">
       <c r="A114" s="105" t="s">
-        <v>705</v>
+        <v>687</v>
       </c>
       <c r="B114" s="60" t="s">
-        <v>495</v>
+        <v>477</v>
       </c>
       <c r="C114" s="61" t="s">
-        <v>707</v>
+        <v>689</v>
       </c>
       <c r="D114" s="61" t="s">
-        <v>708</v>
+        <v>690</v>
       </c>
       <c r="E114" s="61" t="s">
-        <v>498</v>
+        <v>480</v>
       </c>
       <c r="F114" s="120" t="s">
-        <v>709</v>
+        <v>691</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="21.75" customHeight="1">
       <c r="A115" s="105" t="s">
-        <v>705</v>
+        <v>687</v>
       </c>
       <c r="B115" s="60" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
       <c r="C115" s="61" t="s">
-        <v>711</v>
+        <v>693</v>
       </c>
       <c r="D115" s="61" t="s">
-        <v>712</v>
+        <v>694</v>
       </c>
       <c r="E115" s="61" t="s">
-        <v>713</v>
+        <v>695</v>
       </c>
       <c r="F115" s="120" t="s">
-        <v>714</v>
+        <v>696</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="25.5" customHeight="1">
       <c r="A116" s="105" t="s">
-        <v>705</v>
+        <v>687</v>
       </c>
       <c r="B116" s="60" t="s">
-        <v>613</v>
+        <v>595</v>
       </c>
       <c r="C116" s="61" t="s">
-        <v>715</v>
+        <v>697</v>
       </c>
       <c r="D116" s="61" t="s">
-        <v>716</v>
+        <v>698</v>
       </c>
       <c r="E116" s="61" t="s">
-        <v>717</v>
+        <v>699</v>
       </c>
       <c r="F116" s="120" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="25.5" customHeight="1">
       <c r="A117" s="105" t="s">
-        <v>705</v>
+        <v>687</v>
       </c>
       <c r="B117" s="207" t="s">
-        <v>702</v>
+        <v>684</v>
       </c>
       <c r="C117" s="61" t="s">
-        <v>941</v>
+        <v>916</v>
       </c>
       <c r="D117" s="61" t="s">
-        <v>942</v>
+        <v>917</v>
       </c>
       <c r="E117" s="61" t="s">
-        <v>943</v>
+        <v>918</v>
       </c>
       <c r="F117" s="120" t="s">
-        <v>944</v>
+        <v>919</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="30" customHeight="1">
       <c r="A118" s="98" t="s">
-        <v>705</v>
+        <v>687</v>
       </c>
       <c r="B118" s="53" t="s">
-        <v>718</v>
+        <v>700</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>719</v>
+        <v>701</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>720</v>
+        <v>702</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>721</v>
+        <v>703</v>
       </c>
       <c r="F118" s="86" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="25.5" customHeight="1">
       <c r="A119" s="102" t="s">
+        <v>687</v>
+      </c>
+      <c r="B119" s="57" t="s">
+        <v>605</v>
+      </c>
+      <c r="C119" s="33" t="s">
+        <v>704</v>
+      </c>
+      <c r="D119" s="33" t="s">
         <v>705</v>
       </c>
-      <c r="B119" s="57" t="s">
-        <v>623</v>
-      </c>
-      <c r="C119" s="33" t="s">
-        <v>722</v>
-      </c>
-      <c r="D119" s="33" t="s">
-        <v>723</v>
-      </c>
       <c r="E119" s="33" t="s">
-        <v>724</v>
+        <v>706</v>
       </c>
       <c r="F119" s="117" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="30" customHeight="1">
       <c r="A120" s="105" t="s">
-        <v>705</v>
+        <v>687</v>
       </c>
       <c r="B120" s="60" t="s">
-        <v>725</v>
+        <v>707</v>
       </c>
       <c r="C120" s="61" t="s">
-        <v>726</v>
+        <v>708</v>
       </c>
       <c r="D120" s="61" t="s">
-        <v>727</v>
+        <v>709</v>
       </c>
       <c r="E120" s="61" t="s">
-        <v>478</v>
+        <v>460</v>
       </c>
       <c r="F120" s="120" t="s">
-        <v>728</v>
+        <v>710</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="25.5" customHeight="1">
       <c r="A121" s="106" t="s">
-        <v>705</v>
+        <v>687</v>
       </c>
       <c r="B121" s="63" t="s">
-        <v>729</v>
+        <v>711</v>
       </c>
       <c r="C121" s="20" t="s">
-        <v>730</v>
+        <v>712</v>
       </c>
       <c r="D121" s="20" t="s">
-        <v>731</v>
+        <v>713</v>
       </c>
       <c r="E121" s="20" t="s">
-        <v>527</v>
+        <v>509</v>
       </c>
       <c r="F121" s="121" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="110" customHeight="1">
       <c r="A122" s="109" t="s">
-        <v>705</v>
+        <v>687</v>
       </c>
       <c r="B122" s="65" t="s">
-        <v>577</v>
+        <v>559</v>
       </c>
       <c r="C122" s="42" t="s">
-        <v>732</v>
+        <v>714</v>
       </c>
       <c r="D122" s="42" t="s">
-        <v>733</v>
+        <v>715</v>
       </c>
       <c r="E122" s="42" t="s">
-        <v>734</v>
+        <v>716</v>
       </c>
       <c r="F122" s="124" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="42" customHeight="1">
       <c r="A123" s="99" t="s">
-        <v>705</v>
+        <v>687</v>
       </c>
       <c r="B123" s="54" t="s">
-        <v>735</v>
+        <v>717</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>1064</v>
+        <v>1037</v>
       </c>
       <c r="D123" s="15" t="s">
-        <v>1065</v>
+        <v>1038</v>
       </c>
       <c r="E123" s="15" t="s">
-        <v>1066</v>
+        <v>1039</v>
       </c>
       <c r="F123" s="85" t="s">
-        <v>1067</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="30" customHeight="1">
       <c r="A124" s="103" t="s">
-        <v>705</v>
+        <v>687</v>
       </c>
       <c r="B124" s="58" t="s">
-        <v>736</v>
+        <v>718</v>
       </c>
       <c r="C124" s="39" t="s">
-        <v>737</v>
+        <v>719</v>
       </c>
       <c r="D124" s="39" t="s">
-        <v>738</v>
+        <v>720</v>
       </c>
       <c r="E124" s="39" t="s">
-        <v>739</v>
+        <v>721</v>
       </c>
       <c r="F124" s="118" t="s">
-        <v>728</v>
+        <v>710</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="28">
       <c r="A125" s="101" t="s">
-        <v>705</v>
+        <v>687</v>
       </c>
       <c r="B125" s="56" t="s">
-        <v>740</v>
+        <v>722</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>741</v>
+        <v>723</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>742</v>
+        <v>724</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>596</v>
+        <v>578</v>
       </c>
       <c r="F125" s="116" t="s">
-        <v>673</v>
+        <v>655</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="28">
       <c r="A126" s="103" t="s">
-        <v>705</v>
+        <v>687</v>
       </c>
       <c r="B126" s="58" t="s">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="C126" s="39" t="s">
-        <v>743</v>
+        <v>725</v>
       </c>
       <c r="D126" s="39" t="s">
-        <v>744</v>
+        <v>726</v>
       </c>
       <c r="E126" s="39" t="s">
-        <v>539</v>
+        <v>521</v>
       </c>
       <c r="F126" s="118" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="150" customHeight="1">
       <c r="A127" s="103" t="s">
-        <v>705</v>
+        <v>687</v>
       </c>
       <c r="B127" s="58" t="s">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="C127" s="39" t="s">
-        <v>745</v>
+        <v>727</v>
       </c>
       <c r="D127" s="39" t="s">
-        <v>746</v>
+        <v>728</v>
       </c>
       <c r="E127" s="39" t="s">
-        <v>539</v>
+        <v>521</v>
       </c>
       <c r="F127" s="118" t="s">
-        <v>747</v>
+        <v>729</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="238">
       <c r="A128" s="103" t="s">
-        <v>705</v>
+        <v>687</v>
       </c>
       <c r="B128" s="210" t="s">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="C128" s="39" t="s">
-        <v>1073</v>
+        <v>1046</v>
       </c>
       <c r="D128" s="39" t="s">
-        <v>1074</v>
+        <v>1047</v>
       </c>
       <c r="E128" s="39" t="s">
-        <v>1075</v>
+        <v>1048</v>
       </c>
       <c r="F128" s="118" t="s">
-        <v>1076</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="31">
       <c r="A129" s="104" t="s">
-        <v>705</v>
+        <v>687</v>
       </c>
       <c r="B129" s="59" t="s">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="C129" s="47" t="s">
-        <v>971</v>
+        <v>946</v>
       </c>
       <c r="D129" s="47" t="s">
-        <v>972</v>
+        <v>947</v>
       </c>
       <c r="E129" s="47" t="s">
-        <v>539</v>
+        <v>521</v>
       </c>
       <c r="F129" s="119" t="s">
-        <v>748</v>
+        <v>730</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="158" t="s">
-        <v>749</v>
+        <v>731</v>
       </c>
       <c r="B130" s="159"/>
       <c r="C130" s="159"/>
@@ -18815,19 +18554,19 @@
     </row>
     <row r="131" spans="1:6" ht="28">
       <c r="A131" s="101" t="s">
-        <v>750</v>
+        <v>732</v>
       </c>
       <c r="B131" s="56" t="s">
-        <v>751</v>
+        <v>733</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>663</v>
+        <v>645</v>
       </c>
       <c r="D131" s="10" t="s">
-        <v>752</v>
+        <v>734</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="F131" s="116" t="s">
         <v>37</v>
@@ -18835,162 +18574,162 @@
     </row>
     <row r="132" spans="1:6" ht="28">
       <c r="A132" s="100" t="s">
-        <v>750</v>
+        <v>732</v>
       </c>
       <c r="B132" s="55" t="s">
-        <v>753</v>
+        <v>735</v>
       </c>
       <c r="C132" s="50" t="s">
-        <v>754</v>
+        <v>736</v>
       </c>
       <c r="D132" s="50" t="s">
-        <v>755</v>
+        <v>737</v>
       </c>
       <c r="E132" s="50" t="s">
-        <v>672</v>
+        <v>654</v>
       </c>
       <c r="F132" s="115" t="s">
-        <v>756</v>
+        <v>738</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="28">
       <c r="A133" s="100" t="s">
-        <v>750</v>
+        <v>732</v>
       </c>
       <c r="B133" s="55" t="s">
-        <v>757</v>
+        <v>739</v>
       </c>
       <c r="C133" s="50" t="s">
-        <v>758</v>
+        <v>740</v>
       </c>
       <c r="D133" s="50" t="s">
-        <v>759</v>
+        <v>741</v>
       </c>
       <c r="E133" s="50" t="s">
-        <v>760</v>
+        <v>742</v>
       </c>
       <c r="F133" s="115" t="s">
-        <v>404</v>
+        <v>386</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="28">
       <c r="A134" s="100" t="s">
-        <v>750</v>
+        <v>732</v>
       </c>
       <c r="B134" s="55" t="s">
-        <v>761</v>
+        <v>743</v>
       </c>
       <c r="C134" s="50" t="s">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="D134" s="50" t="s">
-        <v>763</v>
+        <v>745</v>
       </c>
       <c r="E134" s="50" t="s">
-        <v>764</v>
+        <v>746</v>
       </c>
       <c r="F134" s="115" t="s">
-        <v>765</v>
+        <v>747</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="28">
       <c r="A135" s="99" t="s">
+        <v>732</v>
+      </c>
+      <c r="B135" s="54" t="s">
+        <v>748</v>
+      </c>
+      <c r="C135" s="15" t="s">
+        <v>749</v>
+      </c>
+      <c r="D135" s="15" t="s">
         <v>750</v>
       </c>
-      <c r="B135" s="54" t="s">
-        <v>766</v>
-      </c>
-      <c r="C135" s="15" t="s">
-        <v>767</v>
-      </c>
-      <c r="D135" s="15" t="s">
-        <v>768</v>
-      </c>
       <c r="E135" s="15" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
       <c r="F135" s="85" t="s">
-        <v>765</v>
+        <v>747</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="28">
       <c r="A136" s="98" t="s">
-        <v>750</v>
+        <v>732</v>
       </c>
       <c r="B136" s="53" t="s">
-        <v>769</v>
+        <v>751</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>771</v>
+        <v>753</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>772</v>
+        <v>754</v>
       </c>
       <c r="F136" s="114" t="s">
-        <v>764</v>
+        <v>746</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="28">
       <c r="A137" s="99" t="s">
-        <v>750</v>
+        <v>732</v>
       </c>
       <c r="B137" s="54" t="s">
-        <v>773</v>
+        <v>755</v>
       </c>
       <c r="C137" s="15" t="s">
-        <v>774</v>
+        <v>756</v>
       </c>
       <c r="D137" s="15" t="s">
-        <v>775</v>
+        <v>757</v>
       </c>
       <c r="E137" s="15" t="s">
-        <v>776</v>
+        <v>758</v>
       </c>
       <c r="F137" s="113" t="s">
-        <v>764</v>
+        <v>746</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="28">
       <c r="A138" s="98" t="s">
-        <v>750</v>
+        <v>732</v>
       </c>
       <c r="B138" s="53" t="s">
-        <v>777</v>
+        <v>759</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>778</v>
+        <v>760</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>779</v>
+        <v>761</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>780</v>
+        <v>762</v>
       </c>
       <c r="F138" s="114" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="29" thickBot="1">
       <c r="A139" s="112" t="s">
-        <v>750</v>
+        <v>732</v>
       </c>
       <c r="B139" s="96" t="s">
-        <v>490</v>
+        <v>472</v>
       </c>
       <c r="C139" s="97" t="s">
-        <v>781</v>
+        <v>763</v>
       </c>
       <c r="D139" s="97" t="s">
-        <v>782</v>
+        <v>764</v>
       </c>
       <c r="E139" s="97" t="s">
-        <v>783</v>
+        <v>765</v>
       </c>
       <c r="F139" s="127" t="s">
-        <v>784</v>
+        <v>766</v>
       </c>
     </row>
   </sheetData>
@@ -19016,7 +18755,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -19028,7 +18767,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
       <c r="A1" s="177" t="s">
-        <v>42</v>
+        <v>1102</v>
       </c>
       <c r="B1" s="177"/>
       <c r="C1" s="177"/>
@@ -19037,7 +18776,7 @@
     </row>
     <row r="3" spans="1:5" ht="24" customHeight="1">
       <c r="A3" s="178" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3" s="178"/>
       <c r="C3" s="178"/>
@@ -19046,642 +18785,761 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="C4" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="D4" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="E4" s="12" t="s">
         <v>47</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="30" customHeight="1">
       <c r="A5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="13" t="s">
         <v>49</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>50</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="30" customHeight="1">
       <c r="A6" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="C6" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="D6" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="E6" s="18" t="s">
         <v>56</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="30" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B7" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="D7" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="30" customHeight="1">
       <c r="A8" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C8" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="19" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C8" s="17" t="s">
+      <c r="D8" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="18" t="s">
         <v>64</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="30" customHeight="1">
       <c r="A9" s="66" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B9" s="69" t="s">
-        <v>785</v>
+        <v>767</v>
       </c>
       <c r="C9" s="67" t="s">
-        <v>786</v>
+        <v>768</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>787</v>
+        <v>769</v>
       </c>
       <c r="E9" s="68" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="30" customHeight="1">
       <c r="A10" s="66" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B10" s="69" t="s">
-        <v>788</v>
+        <v>770</v>
       </c>
       <c r="C10" s="67" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>789</v>
+        <v>771</v>
       </c>
       <c r="E10" s="68" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="27.75" customHeight="1">
       <c r="A11" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="D11" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="E11" s="23" t="s">
         <v>69</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="27.75" customHeight="1">
       <c r="A12" s="20" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B12" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="E12" s="23" t="s">
         <v>73</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="42" customHeight="1">
       <c r="A13" s="20" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>1041</v>
+        <v>1014</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>1036</v>
+        <v>1009</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>1042</v>
+        <v>1015</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>1043</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="42" customHeight="1">
       <c r="A14" s="20" t="s">
-        <v>1044</v>
+        <v>1017</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>1045</v>
+        <v>1018</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>1040</v>
+        <v>1013</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>1046</v>
+        <v>1019</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="56" customHeight="1">
       <c r="A15" s="20" t="s">
-        <v>1052</v>
+        <v>1025</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>1053</v>
+        <v>1026</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>1051</v>
+        <v>1024</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>1054</v>
+        <v>1027</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>1055</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="70" customHeight="1">
       <c r="A16" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="62" customHeight="1">
+      <c r="A17" s="20" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="62" customHeight="1">
+      <c r="A18" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="62" customHeight="1">
+      <c r="A19" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E19" s="23" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="30" customHeight="1"/>
+    <row r="21" spans="1:5" ht="30" customHeight="1">
+      <c r="A21" s="174" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="174"/>
+      <c r="C21" s="174"/>
+      <c r="D21" s="174"/>
+      <c r="E21" s="174"/>
+    </row>
+    <row r="22" spans="1:5" ht="30" customHeight="1">
+      <c r="A22" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="56">
+      <c r="A23" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="24" customHeight="1">
+      <c r="A24" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="28">
+      <c r="A25" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="30" customHeight="1">
+      <c r="A26" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B16" s="20" t="s">
+    </row>
+    <row r="27" spans="1:5" ht="30" customHeight="1">
+      <c r="A27" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="27.75" customHeight="1">
+      <c r="A28" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="66" t="s">
+        <v>772</v>
+      </c>
+      <c r="C28" s="67" t="s">
+        <v>773</v>
+      </c>
+      <c r="D28" s="66" t="s">
+        <v>774</v>
+      </c>
+      <c r="E28" s="68" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="30" customHeight="1">
+      <c r="A29" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="D29" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="E29" s="23" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="62" customHeight="1">
+      <c r="A30" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C30" s="17" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="62" customHeight="1">
+      <c r="A31" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="27.75" customHeight="1"/>
+    <row r="33" spans="1:5" ht="30" customHeight="1">
+      <c r="A33" s="176" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" s="176"/>
+      <c r="C33" s="176"/>
+      <c r="D33" s="176"/>
+      <c r="E33" s="176"/>
+    </row>
+    <row r="34" spans="1:5" ht="30" customHeight="1">
+      <c r="A34" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="27.75" customHeight="1">
+      <c r="A35" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="28">
+      <c r="A38" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="D38" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="28">
+      <c r="A39" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="110" customHeight="1">
+      <c r="A40" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="130" customHeight="1">
+      <c r="A41" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D41" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="150" customHeight="1">
+      <c r="A42" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="E42" s="18" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="28">
+      <c r="A43" s="70" t="s">
+        <v>65</v>
+      </c>
+      <c r="B43" s="73" t="s">
+        <v>775</v>
+      </c>
+      <c r="C43" s="71" t="s">
+        <v>256</v>
+      </c>
+      <c r="D43" s="70" t="s">
+        <v>776</v>
+      </c>
+      <c r="E43" s="72" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="28">
+      <c r="A44" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B44" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="C44" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="D44" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="E44" s="23" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="140">
+      <c r="A45" s="20" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C45" s="22" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D45" s="20" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E45" s="23" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="154">
+      <c r="A46" s="20" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B46" s="21" t="s">
         <v>1060</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C46" s="22" t="s">
         <v>1061</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D46" s="20" t="s">
         <v>1062</v>
       </c>
-      <c r="E16" s="23" t="s">
-        <v>1063</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="30" customHeight="1"/>
-    <row r="18" spans="1:5" ht="30" customHeight="1">
-      <c r="A18" s="174" t="s">
-        <v>76</v>
-      </c>
-      <c r="B18" s="174"/>
-      <c r="C18" s="174"/>
-      <c r="D18" s="174"/>
-      <c r="E18" s="174"/>
-    </row>
-    <row r="19" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A19" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="30" customHeight="1">
-      <c r="A20" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="30" customHeight="1">
-      <c r="A21" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" s="14" t="s">
+      <c r="E46" s="23" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="154">
+      <c r="A47" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C47" s="22" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D47" s="20" t="s">
+        <v>1052</v>
+      </c>
+      <c r="E47" s="23" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="168">
+      <c r="A48" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B48" s="21" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C48" s="22" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D48" s="20" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E48" s="23" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="62" customHeight="1">
+      <c r="A49" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="30" customHeight="1">
-      <c r="A22" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="E22" s="18" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="28">
-      <c r="A23" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="24" customHeight="1">
-      <c r="A24" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="E24" s="18" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="28">
-      <c r="A25" s="66" t="s">
-        <v>90</v>
-      </c>
-      <c r="B25" s="66" t="s">
-        <v>790</v>
-      </c>
-      <c r="C25" s="67" t="s">
-        <v>791</v>
-      </c>
-      <c r="D25" s="66" t="s">
-        <v>792</v>
-      </c>
-      <c r="E25" s="68" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="30" customHeight="1">
-      <c r="A26" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="B26" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="C26" s="22" t="s">
-        <v>101</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="E26" s="23" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="30" customHeight="1"/>
-    <row r="28" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A28" s="176" t="s">
-        <v>104</v>
-      </c>
-      <c r="B28" s="176"/>
-      <c r="C28" s="176"/>
-      <c r="D28" s="176"/>
-      <c r="E28" s="176"/>
-    </row>
-    <row r="29" spans="1:5" ht="30" customHeight="1">
-      <c r="A29" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A30" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="30" customHeight="1">
-      <c r="A31" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E31" s="18" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A32" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="30" customHeight="1">
-      <c r="A33" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="C33" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="D33" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="30" customHeight="1">
-      <c r="A34" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A35" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="B35" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="C35" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="E35" s="18" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="28">
-      <c r="A36" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="D36" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="28">
-      <c r="A37" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="B37" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="C37" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="E37" s="18" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="28">
-      <c r="A38" s="70" t="s">
-        <v>67</v>
-      </c>
-      <c r="B38" s="73" t="s">
-        <v>793</v>
-      </c>
-      <c r="C38" s="71" t="s">
-        <v>269</v>
-      </c>
-      <c r="D38" s="70" t="s">
-        <v>794</v>
-      </c>
-      <c r="E38" s="72" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="28">
-      <c r="A39" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="B39" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="C39" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="E39" s="23" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="110" customHeight="1">
-      <c r="A40" s="20" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B40" s="21" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C40" s="22" t="s">
-        <v>1070</v>
-      </c>
-      <c r="D40" s="20" t="s">
-        <v>1071</v>
-      </c>
-      <c r="E40" s="23" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="130" customHeight="1">
-      <c r="A41" s="20" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B41" s="21" t="s">
-        <v>1087</v>
-      </c>
-      <c r="C41" s="22" t="s">
-        <v>1088</v>
-      </c>
-      <c r="D41" s="20" t="s">
-        <v>1089</v>
-      </c>
-      <c r="E41" s="23" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="150" customHeight="1">
-      <c r="A42" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="B42" s="21" t="s">
+      <c r="B49" s="21" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C49" s="22" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D49" s="20" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E49" s="23" t="s">
         <v>1077</v>
       </c>
-      <c r="C42" s="22" t="s">
-        <v>1078</v>
-      </c>
-      <c r="D42" s="20" t="s">
-        <v>1079</v>
-      </c>
-      <c r="E42" s="23" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="168">
-      <c r="A43" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="B43" s="21" t="s">
-        <v>1080</v>
-      </c>
-      <c r="C43" s="22" t="s">
-        <v>1081</v>
-      </c>
-      <c r="D43" s="20" t="s">
-        <v>1082</v>
-      </c>
-      <c r="E43" s="23" t="s">
-        <v>218</v>
+    </row>
+    <row r="50" spans="1:5" ht="62" customHeight="1">
+      <c r="A50" s="20" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B50" s="21" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C50" s="22" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D50" s="20" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E50" s="23" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A33:E33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -19693,7 +19551,7 @@
   <sheetPr>
     <tabColor rgb="FFE36C09"/>
   </sheetPr>
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -19706,7 +19564,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
       <c r="A1" s="191" t="s">
-        <v>835</v>
+        <v>1103</v>
       </c>
       <c r="B1" s="192"/>
       <c r="C1" s="192"/>
@@ -19716,7 +19574,7 @@
     </row>
     <row r="2" spans="1:6" ht="45" customHeight="1">
       <c r="A2" s="194" t="s">
-        <v>1031</v>
+        <v>1104</v>
       </c>
       <c r="B2" s="195"/>
       <c r="C2" s="195"/>
@@ -19726,19 +19584,19 @@
     </row>
     <row r="3" spans="1:6" ht="19.5" customHeight="1">
       <c r="A3" s="77" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F3" s="83" t="s">
         <v>23</v>
@@ -19746,7 +19604,7 @@
     </row>
     <row r="4" spans="1:6" ht="19.5" customHeight="1">
       <c r="A4" s="188" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B4" s="189"/>
       <c r="C4" s="189"/>
@@ -19756,39 +19614,39 @@
     </row>
     <row r="5" spans="1:6" ht="30" customHeight="1">
       <c r="A5" s="78" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F5" s="84" t="s">
         <v>147</v>
-      </c>
-      <c r="B5" s="27" t="s">
-        <v>148</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="F5" s="84" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1">
       <c r="A6" s="79" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="F6" s="85" t="s">
         <v>28</v>
@@ -19796,19 +19654,19 @@
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1">
       <c r="A7" s="80" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F7" s="86" t="s">
         <v>28</v>
@@ -19816,47 +19674,47 @@
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1">
       <c r="A8" s="81" t="s">
-        <v>795</v>
+        <v>777</v>
       </c>
       <c r="B8" s="75">
         <v>4.5</v>
       </c>
       <c r="C8" s="76" t="s">
-        <v>796</v>
+        <v>778</v>
       </c>
       <c r="D8" s="75" t="s">
-        <v>797</v>
+        <v>779</v>
       </c>
       <c r="E8" s="76" t="s">
-        <v>798</v>
+        <v>780</v>
       </c>
       <c r="F8" s="87" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1">
       <c r="A9" s="82" t="s">
-        <v>799</v>
+        <v>781</v>
       </c>
       <c r="B9" s="68">
         <v>4.5</v>
       </c>
       <c r="C9" s="66" t="s">
-        <v>856</v>
+        <v>835</v>
       </c>
       <c r="D9" s="68" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E9" s="66" t="s">
-        <v>857</v>
+        <v>1065</v>
       </c>
       <c r="F9" s="88" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="19.5" customHeight="1">
       <c r="A10" s="188" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B10" s="189"/>
       <c r="C10" s="189"/>
@@ -19866,1593 +19724,1693 @@
     </row>
     <row r="11" spans="1:6" ht="42" customHeight="1">
       <c r="A11" s="78" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>1029</v>
+        <v>1004</v>
       </c>
       <c r="F11" s="84" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1">
       <c r="A12" s="79" t="s">
+        <v>148</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>158</v>
-      </c>
       <c r="C12" s="16" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F12" s="85" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1">
       <c r="A13" s="80" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F13" s="86" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1">
       <c r="A14" s="81" t="s">
-        <v>795</v>
+        <v>777</v>
       </c>
       <c r="B14" s="75">
         <v>4.8</v>
       </c>
       <c r="C14" s="76" t="s">
-        <v>800</v>
+        <v>782</v>
       </c>
       <c r="D14" s="75" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E14" s="76" t="s">
-        <v>801</v>
+        <v>783</v>
       </c>
       <c r="F14" s="87" t="s">
-        <v>802</v>
+        <v>784</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="30" customHeight="1">
       <c r="A15" s="82" t="s">
-        <v>799</v>
+        <v>781</v>
       </c>
       <c r="B15" s="68">
         <v>4.5999999999999996</v>
       </c>
       <c r="C15" s="66" t="s">
-        <v>836</v>
+        <v>815</v>
       </c>
       <c r="D15" s="68" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E15" s="66" t="s">
-        <v>837</v>
+        <v>816</v>
       </c>
       <c r="F15" s="88" t="s">
-        <v>838</v>
+        <v>817</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="30" customHeight="1">
       <c r="A16" s="82" t="s">
-        <v>884</v>
-      </c>
-      <c r="B16" s="216" t="s">
-        <v>1023</v>
+        <v>859</v>
+      </c>
+      <c r="B16" s="220" t="s">
+        <v>998</v>
       </c>
       <c r="C16" s="66" t="s">
-        <v>1024</v>
+        <v>999</v>
       </c>
       <c r="D16" s="68" t="s">
-        <v>797</v>
+        <v>779</v>
       </c>
       <c r="E16" s="66" t="s">
-        <v>1025</v>
+        <v>1000</v>
       </c>
       <c r="F16" s="88" t="s">
-        <v>475</v>
+        <v>457</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1">
       <c r="A17" s="82" t="s">
-        <v>887</v>
-      </c>
-      <c r="B17" s="216" t="s">
-        <v>1026</v>
+        <v>862</v>
+      </c>
+      <c r="B17" s="220" t="s">
+        <v>1001</v>
       </c>
       <c r="C17" s="66" t="s">
-        <v>1027</v>
+        <v>1002</v>
       </c>
       <c r="D17" s="68" t="s">
-        <v>1012</v>
+        <v>987</v>
       </c>
       <c r="E17" s="66" t="s">
-        <v>1028</v>
+        <v>1003</v>
       </c>
       <c r="F17" s="88" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="44" customHeight="1">
+      <c r="A18" s="223" t="s">
+        <v>980</v>
+      </c>
+      <c r="B18" s="224" t="s">
+        <v>239</v>
+      </c>
+      <c r="C18" s="225" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D18" s="226" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E18" s="225" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F18" s="227" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="44" customHeight="1">
+      <c r="A19" s="223" t="s">
+        <v>984</v>
+      </c>
+      <c r="B19" s="224" t="s">
+        <v>239</v>
+      </c>
+      <c r="C19" s="225" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D19" s="226" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E19" s="225" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F19" s="227" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="30" customHeight="1">
+      <c r="A20" s="188" t="s">
+        <v>168</v>
+      </c>
+      <c r="B20" s="189"/>
+      <c r="C20" s="189"/>
+      <c r="D20" s="189"/>
+      <c r="E20" s="189"/>
+      <c r="F20" s="190"/>
+    </row>
+    <row r="21" spans="1:6" ht="30" customHeight="1">
+      <c r="A21" s="78" t="s">
+        <v>169</v>
+      </c>
+      <c r="B21" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="F21" s="84" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A22" s="79" t="s">
+        <v>142</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="F22" s="85" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="30" customHeight="1">
+      <c r="A23" s="80" t="s">
+        <v>148</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="F23" s="86" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="30" customHeight="1">
+      <c r="A24" s="81" t="s">
+        <v>152</v>
+      </c>
+      <c r="B24" s="75">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C24" s="76" t="s">
+        <v>836</v>
+      </c>
+      <c r="D24" s="75" t="s">
+        <v>241</v>
+      </c>
+      <c r="E24" s="76" t="s">
+        <v>837</v>
+      </c>
+      <c r="F24" s="87" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="30" customHeight="1">
+      <c r="A25" s="82" t="s">
+        <v>777</v>
+      </c>
+      <c r="B25" s="68">
+        <v>4.3</v>
+      </c>
+      <c r="C25" s="66" t="s">
+        <v>785</v>
+      </c>
+      <c r="D25" s="68" t="s">
+        <v>241</v>
+      </c>
+      <c r="E25" s="66" t="s">
+        <v>786</v>
+      </c>
+      <c r="F25" s="88" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="30" customHeight="1">
+      <c r="A26" s="188" t="s">
+        <v>181</v>
+      </c>
+      <c r="B26" s="189"/>
+      <c r="C26" s="189"/>
+      <c r="D26" s="189"/>
+      <c r="E26" s="189"/>
+      <c r="F26" s="190"/>
+    </row>
+    <row r="27" spans="1:6" ht="30" customHeight="1">
+      <c r="A27" s="78" t="s">
+        <v>142</v>
+      </c>
+      <c r="B27" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="D27" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F27" s="84" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A28" s="79" t="s">
+        <v>148</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F28" s="85" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="30" customHeight="1">
+      <c r="A29" s="80" t="s">
+        <v>152</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F29" s="86" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="30" customHeight="1">
+      <c r="A30" s="81" t="s">
+        <v>777</v>
+      </c>
+      <c r="B30" s="75">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C30" s="76" t="s">
+        <v>788</v>
+      </c>
+      <c r="D30" s="75" t="s">
+        <v>155</v>
+      </c>
+      <c r="E30" s="76" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F30" s="87" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="30" customHeight="1">
+      <c r="A31" s="82" t="s">
+        <v>781</v>
+      </c>
+      <c r="B31" s="68">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C31" s="66" t="s">
+        <v>818</v>
+      </c>
+      <c r="D31" s="68" t="s">
+        <v>210</v>
+      </c>
+      <c r="E31" s="66" t="s">
+        <v>819</v>
+      </c>
+      <c r="F31" s="88" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="30" customHeight="1">
+      <c r="A32" s="188" t="s">
+        <v>193</v>
+      </c>
+      <c r="B32" s="189"/>
+      <c r="C32" s="189"/>
+      <c r="D32" s="189"/>
+      <c r="E32" s="189"/>
+      <c r="F32" s="190"/>
+    </row>
+    <row r="33" spans="1:6" ht="30" customHeight="1">
+      <c r="A33" s="78" t="s">
+        <v>142</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D33" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F33" s="84" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A34" s="79" t="s">
+        <v>148</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="F34" s="85" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="30" customHeight="1">
+      <c r="A35" s="80" t="s">
+        <v>152</v>
+      </c>
+      <c r="B35" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="C35" s="13" t="s">
         <v>838</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="30" customHeight="1">
-      <c r="A18" s="188" t="s">
-        <v>173</v>
-      </c>
-      <c r="B18" s="189"/>
-      <c r="C18" s="189"/>
-      <c r="D18" s="189"/>
-      <c r="E18" s="189"/>
-      <c r="F18" s="190"/>
-    </row>
-    <row r="19" spans="1:6" ht="30" customHeight="1">
-      <c r="A19" s="78" t="s">
-        <v>174</v>
-      </c>
-      <c r="B19" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="C19" s="28" t="s">
+      <c r="D35" s="4" t="s">
+        <v>803</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="F35" s="86" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="30" customHeight="1">
+      <c r="A36" s="81" t="s">
+        <v>777</v>
+      </c>
+      <c r="B36" s="75">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C36" s="76" t="s">
+        <v>790</v>
+      </c>
+      <c r="D36" s="75" t="s">
+        <v>161</v>
+      </c>
+      <c r="E36" s="76" t="s">
+        <v>791</v>
+      </c>
+      <c r="F36" s="87" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="30" customHeight="1">
+      <c r="A37" s="82" t="s">
+        <v>781</v>
+      </c>
+      <c r="B37" s="68">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C37" s="66" t="s">
+        <v>821</v>
+      </c>
+      <c r="D37" s="68" t="s">
+        <v>60</v>
+      </c>
+      <c r="E37" s="66" t="s">
+        <v>822</v>
+      </c>
+      <c r="F37" s="88" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="30" customHeight="1">
+      <c r="A38" s="185" t="s">
+        <v>201</v>
+      </c>
+      <c r="B38" s="186"/>
+      <c r="C38" s="186"/>
+      <c r="D38" s="186"/>
+      <c r="E38" s="186"/>
+      <c r="F38" s="187"/>
+    </row>
+    <row r="39" spans="1:6" ht="30" customHeight="1">
+      <c r="A39" s="78" t="s">
+        <v>142</v>
+      </c>
+      <c r="B39" s="27">
+        <v>4.5</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>847</v>
+      </c>
+      <c r="D39" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="E39" s="28" t="s">
+        <v>848</v>
+      </c>
+      <c r="F39" s="84" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A40" s="79" t="s">
+        <v>148</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="D40" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F40" s="85" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="30" customHeight="1">
+      <c r="A41" s="80" t="s">
+        <v>152</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F41" s="86" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="30" customHeight="1">
+      <c r="A42" s="81" t="s">
+        <v>777</v>
+      </c>
+      <c r="B42" s="75">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C42" s="76" t="s">
+        <v>792</v>
+      </c>
+      <c r="D42" s="75" t="s">
+        <v>207</v>
+      </c>
+      <c r="E42" s="76" t="s">
+        <v>793</v>
+      </c>
+      <c r="F42" s="87" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="30" customHeight="1">
+      <c r="A43" s="82" t="s">
+        <v>781</v>
+      </c>
+      <c r="B43" s="68">
+        <v>4.3</v>
+      </c>
+      <c r="C43" s="66" t="s">
+        <v>824</v>
+      </c>
+      <c r="D43" s="68" t="s">
+        <v>213</v>
+      </c>
+      <c r="E43" s="66" t="s">
+        <v>825</v>
+      </c>
+      <c r="F43" s="88" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="30" customHeight="1">
+      <c r="A44" s="185" t="s">
+        <v>209</v>
+      </c>
+      <c r="B44" s="186"/>
+      <c r="C44" s="186"/>
+      <c r="D44" s="186"/>
+      <c r="E44" s="186"/>
+      <c r="F44" s="187"/>
+    </row>
+    <row r="45" spans="1:6" ht="30" customHeight="1">
+      <c r="A45" s="78" t="s">
+        <v>142</v>
+      </c>
+      <c r="B45" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D45" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F45" s="84" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A46" s="79" t="s">
+        <v>148</v>
+      </c>
+      <c r="B46" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="D19" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="F19" s="84" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="30" customHeight="1">
-      <c r="A20" s="79" t="s">
-        <v>147</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="F20" s="85" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="30" customHeight="1">
-      <c r="A21" s="80" t="s">
+      <c r="C46" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="D46" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="E46" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="F46" s="85" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="30" customHeight="1">
+      <c r="A47" s="80" t="s">
+        <v>152</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F47" s="86" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="30" customHeight="1">
+      <c r="A48" s="81" t="s">
+        <v>777</v>
+      </c>
+      <c r="B48" s="75">
+        <v>4.5</v>
+      </c>
+      <c r="C48" s="76" t="s">
+        <v>794</v>
+      </c>
+      <c r="D48" s="75" t="s">
+        <v>86</v>
+      </c>
+      <c r="E48" s="76" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F48" s="87" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="30" customHeight="1">
+      <c r="A49" s="82" t="s">
+        <v>781</v>
+      </c>
+      <c r="B49" s="68">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C49" s="66" t="s">
+        <v>795</v>
+      </c>
+      <c r="D49" s="68" t="s">
+        <v>796</v>
+      </c>
+      <c r="E49" s="66" t="s">
+        <v>797</v>
+      </c>
+      <c r="F49" s="88" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="44" customHeight="1">
+      <c r="A50" s="223" t="s">
+        <v>859</v>
+      </c>
+      <c r="B50" s="226" t="s">
+        <v>239</v>
+      </c>
+      <c r="C50" s="225" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D50" s="226" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E50" s="225" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F50" s="227" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="30" customHeight="1">
+      <c r="A51" s="185" t="s">
+        <v>218</v>
+      </c>
+      <c r="B51" s="186"/>
+      <c r="C51" s="186"/>
+      <c r="D51" s="186"/>
+      <c r="E51" s="186"/>
+      <c r="F51" s="187"/>
+    </row>
+    <row r="52" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A52" s="78" t="s">
+        <v>142</v>
+      </c>
+      <c r="B52" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D52" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F52" s="84" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="30" customHeight="1">
+      <c r="A53" s="79" t="s">
+        <v>148</v>
+      </c>
+      <c r="B53" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C53" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="D53" s="18" t="s">
+        <v>222</v>
+      </c>
+      <c r="E53" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="F53" s="85" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="30" customHeight="1">
+      <c r="A54" s="80" t="s">
+        <v>152</v>
+      </c>
+      <c r="B54" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>840</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>841</v>
+      </c>
+      <c r="F54" s="86" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="30" customHeight="1">
+      <c r="A55" s="81" t="s">
+        <v>777</v>
+      </c>
+      <c r="B55" s="75">
+        <v>4.7</v>
+      </c>
+      <c r="C55" s="76" t="s">
+        <v>799</v>
+      </c>
+      <c r="D55" s="75" t="s">
+        <v>64</v>
+      </c>
+      <c r="E55" s="76" t="s">
+        <v>800</v>
+      </c>
+      <c r="F55" s="87" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="30" customHeight="1">
+      <c r="A56" s="81" t="s">
+        <v>781</v>
+      </c>
+      <c r="B56" s="75">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C56" s="76" t="s">
+        <v>802</v>
+      </c>
+      <c r="D56" s="75" t="s">
+        <v>803</v>
+      </c>
+      <c r="E56" s="76" t="s">
+        <v>804</v>
+      </c>
+      <c r="F56" s="87" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="44" customHeight="1">
+      <c r="A57" s="228" t="s">
+        <v>859</v>
+      </c>
+      <c r="B57" s="229" t="s">
+        <v>239</v>
+      </c>
+      <c r="C57" s="230" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D57" s="229" t="s">
+        <v>207</v>
+      </c>
+      <c r="E57" s="230" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F57" s="231" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A58" s="185" t="s">
+        <v>225</v>
+      </c>
+      <c r="B58" s="186"/>
+      <c r="C58" s="186"/>
+      <c r="D58" s="186"/>
+      <c r="E58" s="186"/>
+      <c r="F58" s="187"/>
+    </row>
+    <row r="59" spans="1:6" ht="30" customHeight="1">
+      <c r="A59" s="78" t="s">
+        <v>142</v>
+      </c>
+      <c r="B59" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="F21" s="86" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A22" s="81" t="s">
-        <v>157</v>
-      </c>
-      <c r="B22" s="75">
+      <c r="C59" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D59" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="F59" s="84" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="30" customHeight="1">
+      <c r="A60" s="79" t="s">
+        <v>148</v>
+      </c>
+      <c r="B60" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="C60" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="D60" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="E60" s="15" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F60" s="85" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="30" customHeight="1">
+      <c r="A61" s="80" t="s">
+        <v>152</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C61" s="29" t="s">
+        <v>230</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F61" s="86" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A62" s="81" t="s">
+        <v>777</v>
+      </c>
+      <c r="B62" s="75">
         <v>4.4000000000000004</v>
       </c>
-      <c r="C22" s="76" t="s">
-        <v>858</v>
-      </c>
-      <c r="D22" s="75" t="s">
-        <v>254</v>
-      </c>
-      <c r="E22" s="76" t="s">
-        <v>859</v>
-      </c>
-      <c r="F22" s="87" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="30" customHeight="1">
-      <c r="A23" s="82" t="s">
-        <v>795</v>
-      </c>
-      <c r="B23" s="68">
-        <v>4.3</v>
-      </c>
-      <c r="C23" s="66" t="s">
-        <v>803</v>
-      </c>
-      <c r="D23" s="68" t="s">
-        <v>254</v>
-      </c>
-      <c r="E23" s="66" t="s">
-        <v>804</v>
-      </c>
-      <c r="F23" s="88" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="30" customHeight="1">
-      <c r="A24" s="188" t="s">
-        <v>187</v>
-      </c>
-      <c r="B24" s="189"/>
-      <c r="C24" s="189"/>
-      <c r="D24" s="189"/>
-      <c r="E24" s="189"/>
-      <c r="F24" s="190"/>
-    </row>
-    <row r="25" spans="1:6" ht="30" customHeight="1">
-      <c r="A25" s="78" t="s">
-        <v>147</v>
-      </c>
-      <c r="B25" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="D25" s="27" t="s">
-        <v>189</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="F25" s="84" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="30" customHeight="1">
-      <c r="A26" s="79" t="s">
-        <v>153</v>
-      </c>
-      <c r="B26" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="D26" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>194</v>
-      </c>
-      <c r="F26" s="85" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="30" customHeight="1">
-      <c r="A27" s="80" t="s">
-        <v>157</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="F27" s="86" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A28" s="81" t="s">
-        <v>795</v>
-      </c>
-      <c r="B28" s="75">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C28" s="76" t="s">
+      <c r="C62" s="74" t="s">
+        <v>826</v>
+      </c>
+      <c r="D62" s="75" t="s">
+        <v>210</v>
+      </c>
+      <c r="E62" s="76" t="s">
+        <v>827</v>
+      </c>
+      <c r="F62" s="87" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="30" customHeight="1">
+      <c r="A63" s="82" t="s">
+        <v>781</v>
+      </c>
+      <c r="B63" s="68">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="C63" s="69" t="s">
         <v>806</v>
       </c>
-      <c r="D28" s="75" t="s">
-        <v>160</v>
-      </c>
-      <c r="E28" s="76" t="s">
+      <c r="D63" s="68" t="s">
+        <v>51</v>
+      </c>
+      <c r="E63" s="66" t="s">
         <v>807</v>
       </c>
-      <c r="F28" s="87" t="s">
+      <c r="F63" s="88" t="s">
         <v>808</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="30" customHeight="1">
-      <c r="A29" s="82" t="s">
-        <v>799</v>
-      </c>
-      <c r="B29" s="68">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C29" s="66" t="s">
-        <v>839</v>
-      </c>
-      <c r="D29" s="68" t="s">
-        <v>218</v>
-      </c>
-      <c r="E29" s="66" t="s">
-        <v>840</v>
-      </c>
-      <c r="F29" s="88" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="30" customHeight="1">
-      <c r="A30" s="188" t="s">
-        <v>200</v>
-      </c>
-      <c r="B30" s="189"/>
-      <c r="C30" s="189"/>
-      <c r="D30" s="189"/>
-      <c r="E30" s="189"/>
-      <c r="F30" s="190"/>
-    </row>
-    <row r="31" spans="1:6" ht="30" customHeight="1">
-      <c r="A31" s="78" t="s">
-        <v>147</v>
-      </c>
-      <c r="B31" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D31" s="27" t="s">
-        <v>170</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="F31" s="84" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="30" customHeight="1">
-      <c r="A32" s="79" t="s">
-        <v>153</v>
-      </c>
-      <c r="B32" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="D32" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="E32" s="15" t="s">
-        <v>205</v>
-      </c>
-      <c r="F32" s="85" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="30" customHeight="1">
-      <c r="A33" s="80" t="s">
-        <v>157</v>
-      </c>
-      <c r="B33" s="4">
-        <v>4.3</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>860</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>823</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>861</v>
-      </c>
-      <c r="F33" s="86" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A34" s="81" t="s">
-        <v>795</v>
-      </c>
-      <c r="B34" s="75">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C34" s="76" t="s">
-        <v>809</v>
-      </c>
-      <c r="D34" s="75" t="s">
-        <v>166</v>
-      </c>
-      <c r="E34" s="76" t="s">
-        <v>810</v>
-      </c>
-      <c r="F34" s="87" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="30" customHeight="1">
-      <c r="A35" s="82" t="s">
-        <v>799</v>
-      </c>
-      <c r="B35" s="68">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C35" s="66" t="s">
-        <v>842</v>
-      </c>
-      <c r="D35" s="68" t="s">
-        <v>61</v>
-      </c>
-      <c r="E35" s="66" t="s">
-        <v>843</v>
-      </c>
-      <c r="F35" s="88" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="30" customHeight="1">
-      <c r="A36" s="185" t="s">
-        <v>208</v>
-      </c>
-      <c r="B36" s="186"/>
-      <c r="C36" s="186"/>
-      <c r="D36" s="186"/>
-      <c r="E36" s="186"/>
-      <c r="F36" s="187"/>
-    </row>
-    <row r="37" spans="1:6" ht="30" customHeight="1">
-      <c r="A37" s="78" t="s">
-        <v>147</v>
-      </c>
-      <c r="B37" s="27">
-        <v>4.5</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="D37" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="E37" s="28" t="s">
-        <v>873</v>
-      </c>
-      <c r="F37" s="84" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="30" customHeight="1">
-      <c r="A38" s="79" t="s">
-        <v>153</v>
-      </c>
-      <c r="B38" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="C38" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="D38" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="E38" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="F38" s="85" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="30" customHeight="1">
-      <c r="A39" s="80" t="s">
-        <v>157</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="F39" s="86" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A40" s="81" t="s">
-        <v>795</v>
-      </c>
-      <c r="B40" s="75">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C40" s="76" t="s">
-        <v>811</v>
-      </c>
-      <c r="D40" s="75" t="s">
-        <v>215</v>
-      </c>
-      <c r="E40" s="76" t="s">
-        <v>812</v>
-      </c>
-      <c r="F40" s="87" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="30" customHeight="1">
-      <c r="A41" s="82" t="s">
-        <v>799</v>
-      </c>
-      <c r="B41" s="68">
-        <v>4.3</v>
-      </c>
-      <c r="C41" s="66" t="s">
-        <v>845</v>
-      </c>
-      <c r="D41" s="68" t="s">
-        <v>221</v>
-      </c>
-      <c r="E41" s="66" t="s">
-        <v>846</v>
-      </c>
-      <c r="F41" s="88" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="30" customHeight="1">
-      <c r="A42" s="185" t="s">
-        <v>217</v>
-      </c>
-      <c r="B42" s="186"/>
-      <c r="C42" s="186"/>
-      <c r="D42" s="186"/>
-      <c r="E42" s="186"/>
-      <c r="F42" s="187"/>
-    </row>
-    <row r="43" spans="1:6" ht="30" customHeight="1">
-      <c r="A43" s="78" t="s">
-        <v>147</v>
-      </c>
-      <c r="B43" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>1090</v>
-      </c>
-      <c r="D43" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>1091</v>
-      </c>
-      <c r="F43" s="84" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="30" customHeight="1">
-      <c r="A44" s="79" t="s">
-        <v>153</v>
-      </c>
-      <c r="B44" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="C44" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="D44" s="18" t="s">
-        <v>221</v>
-      </c>
-      <c r="E44" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="F44" s="85" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="30" customHeight="1">
-      <c r="A45" s="80" t="s">
-        <v>157</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="F45" s="86" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A46" s="81" t="s">
-        <v>795</v>
-      </c>
-      <c r="B46" s="75">
-        <v>4.5</v>
-      </c>
-      <c r="C46" s="76" t="s">
-        <v>813</v>
-      </c>
-      <c r="D46" s="75" t="s">
-        <v>89</v>
-      </c>
-      <c r="E46" s="76" t="s">
-        <v>814</v>
-      </c>
-      <c r="F46" s="87" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="30" customHeight="1">
-      <c r="A47" s="82" t="s">
-        <v>799</v>
-      </c>
-      <c r="B47" s="68">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C47" s="66" t="s">
-        <v>815</v>
-      </c>
-      <c r="D47" s="68" t="s">
-        <v>816</v>
-      </c>
-      <c r="E47" s="66" t="s">
-        <v>817</v>
-      </c>
-      <c r="F47" s="88" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="30" customHeight="1">
-      <c r="A48" s="185" t="s">
-        <v>227</v>
-      </c>
-      <c r="B48" s="186"/>
-      <c r="C48" s="186"/>
-      <c r="D48" s="186"/>
-      <c r="E48" s="186"/>
-      <c r="F48" s="187"/>
-    </row>
-    <row r="49" spans="1:6" ht="30" customHeight="1">
-      <c r="A49" s="78" t="s">
-        <v>147</v>
-      </c>
-      <c r="B49" s="27" t="s">
-        <v>213</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="D49" s="27" t="s">
-        <v>160</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="F49" s="84" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="30" customHeight="1">
-      <c r="A50" s="79" t="s">
-        <v>153</v>
-      </c>
-      <c r="B50" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="D50" s="18" t="s">
+    <row r="64" spans="1:6" ht="30" customHeight="1">
+      <c r="A64" s="185" t="s">
         <v>232</v>
       </c>
-      <c r="E50" s="15" t="s">
-        <v>233</v>
-      </c>
-      <c r="F50" s="85" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="30" customHeight="1">
-      <c r="A51" s="80" t="s">
-        <v>157</v>
-      </c>
-      <c r="B51" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>862</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>863</v>
-      </c>
-      <c r="F51" s="86" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A52" s="81" t="s">
-        <v>795</v>
-      </c>
-      <c r="B52" s="75">
-        <v>4.7</v>
-      </c>
-      <c r="C52" s="76" t="s">
-        <v>819</v>
-      </c>
-      <c r="D52" s="75" t="s">
-        <v>66</v>
-      </c>
-      <c r="E52" s="76" t="s">
-        <v>820</v>
-      </c>
-      <c r="F52" s="87" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="30" customHeight="1">
-      <c r="A53" s="82" t="s">
-        <v>799</v>
-      </c>
-      <c r="B53" s="68">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C53" s="66" t="s">
-        <v>822</v>
-      </c>
-      <c r="D53" s="68" t="s">
-        <v>823</v>
-      </c>
-      <c r="E53" s="66" t="s">
-        <v>824</v>
-      </c>
-      <c r="F53" s="88" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="30" customHeight="1">
-      <c r="A54" s="185" t="s">
-        <v>235</v>
-      </c>
-      <c r="B54" s="186"/>
-      <c r="C54" s="186"/>
-      <c r="D54" s="186"/>
-      <c r="E54" s="186"/>
-      <c r="F54" s="187"/>
-    </row>
-    <row r="55" spans="1:6" ht="30" customHeight="1">
-      <c r="A55" s="78" t="s">
-        <v>147</v>
-      </c>
-      <c r="B55" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="D55" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="F55" s="84" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="30" customHeight="1">
-      <c r="A56" s="79" t="s">
-        <v>153</v>
-      </c>
-      <c r="B56" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="C56" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="D56" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E56" s="15" t="s">
-        <v>240</v>
-      </c>
-      <c r="F56" s="85" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="30" customHeight="1">
-      <c r="A57" s="80" t="s">
-        <v>157</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C57" s="29" t="s">
-        <v>241</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="F57" s="86" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A58" s="81" t="s">
-        <v>795</v>
-      </c>
-      <c r="B58" s="75">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C58" s="74" t="s">
-        <v>847</v>
-      </c>
-      <c r="D58" s="75" t="s">
-        <v>218</v>
-      </c>
-      <c r="E58" s="76" t="s">
-        <v>848</v>
-      </c>
-      <c r="F58" s="87" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="30" customHeight="1">
-      <c r="A59" s="82" t="s">
-        <v>799</v>
-      </c>
-      <c r="B59" s="68">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="C59" s="69" t="s">
-        <v>826</v>
-      </c>
-      <c r="D59" s="68" t="s">
-        <v>52</v>
-      </c>
-      <c r="E59" s="66" t="s">
-        <v>827</v>
-      </c>
-      <c r="F59" s="88" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="30" customHeight="1">
-      <c r="A60" s="185" t="s">
-        <v>244</v>
-      </c>
-      <c r="B60" s="186"/>
-      <c r="C60" s="186"/>
-      <c r="D60" s="186"/>
-      <c r="E60" s="186"/>
-      <c r="F60" s="187"/>
-    </row>
-    <row r="61" spans="1:6" ht="30" customHeight="1">
-      <c r="A61" s="78" t="s">
-        <v>245</v>
-      </c>
-      <c r="B61" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="C61" s="28" t="s">
-        <v>246</v>
-      </c>
-      <c r="D61" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="F61" s="84" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A62" s="79" t="s">
-        <v>248</v>
-      </c>
-      <c r="B62" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="C62" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="D62" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="E62" s="25" t="s">
-        <v>250</v>
-      </c>
-      <c r="F62" s="85" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="30" customHeight="1">
-      <c r="A63" s="80" t="s">
-        <v>251</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="C63" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="E63" s="24" t="s">
-        <v>255</v>
-      </c>
-      <c r="F63" s="86" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="30" customHeight="1">
-      <c r="A64" s="179" t="s">
-        <v>257</v>
-      </c>
-      <c r="B64" s="180"/>
-      <c r="C64" s="180"/>
-      <c r="D64" s="180"/>
-      <c r="E64" s="180"/>
-      <c r="F64" s="181"/>
+      <c r="B64" s="186"/>
+      <c r="C64" s="186"/>
+      <c r="D64" s="186"/>
+      <c r="E64" s="186"/>
+      <c r="F64" s="187"/>
     </row>
     <row r="65" spans="1:6" ht="42" customHeight="1">
       <c r="A65" s="78" t="s">
-        <v>147</v>
+        <v>233</v>
       </c>
       <c r="B65" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>258</v>
+        <v>153</v>
+      </c>
+      <c r="C65" s="28" t="s">
+        <v>234</v>
       </c>
       <c r="D65" s="27" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>1030</v>
+        <v>235</v>
       </c>
       <c r="F65" s="84" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="30" customHeight="1">
       <c r="A66" s="79" t="s">
-        <v>153</v>
-      </c>
-      <c r="B66" s="18">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C66" s="16" t="s">
-        <v>850</v>
+        <v>236</v>
+      </c>
+      <c r="B66" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C66" s="19" t="s">
+        <v>237</v>
       </c>
       <c r="D66" s="18" t="s">
-        <v>221</v>
-      </c>
-      <c r="E66" s="15" t="s">
-        <v>867</v>
+        <v>94</v>
+      </c>
+      <c r="E66" s="25" t="s">
+        <v>1072</v>
       </c>
       <c r="F66" s="85" t="s">
-        <v>275</v>
+        <v>93</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="30" customHeight="1">
       <c r="A67" s="80" t="s">
-        <v>157</v>
+        <v>238</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>261</v>
+        <v>241</v>
+      </c>
+      <c r="E67" s="24" t="s">
+        <v>242</v>
       </c>
       <c r="F67" s="86" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="30" customHeight="1">
+      <c r="A68" s="179" t="s">
+        <v>244</v>
+      </c>
+      <c r="B68" s="180"/>
+      <c r="C68" s="180"/>
+      <c r="D68" s="180"/>
+      <c r="E68" s="180"/>
+      <c r="F68" s="181"/>
+    </row>
+    <row r="69" spans="1:6" ht="30" customHeight="1">
+      <c r="A69" s="78" t="s">
+        <v>142</v>
+      </c>
+      <c r="B69" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D69" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F69" s="84" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="30" customHeight="1">
+      <c r="A70" s="79" t="s">
+        <v>148</v>
+      </c>
+      <c r="B70" s="18">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C70" s="16" t="s">
+        <v>829</v>
+      </c>
+      <c r="D70" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="E70" s="15" t="s">
+        <v>845</v>
+      </c>
+      <c r="F70" s="85" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="30" customHeight="1">
-      <c r="A68" s="81" t="s">
-        <v>795</v>
-      </c>
-      <c r="B68" s="75">
+    <row r="71" spans="1:6" ht="30" customHeight="1">
+      <c r="A71" s="80" t="s">
+        <v>152</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="F71" s="86" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="30" customHeight="1">
+      <c r="A72" s="81" t="s">
+        <v>777</v>
+      </c>
+      <c r="B72" s="75">
         <v>4.4000000000000004</v>
       </c>
-      <c r="C68" s="76" t="s">
-        <v>854</v>
-      </c>
-      <c r="D68" s="75" t="s">
-        <v>823</v>
-      </c>
-      <c r="E68" s="76" t="s">
-        <v>855</v>
-      </c>
-      <c r="F68" s="87" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="30" customHeight="1">
-      <c r="A69" s="82" t="s">
-        <v>799</v>
-      </c>
-      <c r="B69" s="68">
-        <v>4.3</v>
-      </c>
-      <c r="C69" s="66" t="s">
-        <v>868</v>
-      </c>
-      <c r="D69" s="68" t="s">
-        <v>869</v>
-      </c>
-      <c r="E69" s="66" t="s">
-        <v>870</v>
-      </c>
-      <c r="F69" s="88" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="30" customHeight="1">
-      <c r="A70" s="81" t="s">
-        <v>884</v>
-      </c>
-      <c r="B70" s="75">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C70" s="76" t="s">
-        <v>885</v>
-      </c>
-      <c r="D70" s="75" t="s">
-        <v>123</v>
-      </c>
-      <c r="E70" s="76" t="s">
-        <v>886</v>
-      </c>
-      <c r="F70" s="87" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="30" customHeight="1">
-      <c r="A71" s="82" t="s">
-        <v>887</v>
-      </c>
-      <c r="B71" s="68">
-        <v>4.5</v>
-      </c>
-      <c r="C71" s="66" t="s">
-        <v>888</v>
-      </c>
-      <c r="D71" s="68" t="s">
-        <v>99</v>
-      </c>
-      <c r="E71" s="66" t="s">
-        <v>889</v>
-      </c>
-      <c r="F71" s="88" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="30" customHeight="1">
-      <c r="A72" s="82" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B72" s="216" t="s">
-        <v>1015</v>
-      </c>
-      <c r="C72" s="66" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D72" s="68" t="s">
-        <v>1017</v>
-      </c>
-      <c r="E72" s="66" t="s">
-        <v>1018</v>
-      </c>
-      <c r="F72" s="88" t="s">
-        <v>286</v>
+      <c r="C72" s="76" t="s">
+        <v>833</v>
+      </c>
+      <c r="D72" s="75" t="s">
+        <v>803</v>
+      </c>
+      <c r="E72" s="76" t="s">
+        <v>834</v>
+      </c>
+      <c r="F72" s="87" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="30" customHeight="1">
       <c r="A73" s="82" t="s">
-        <v>1009</v>
-      </c>
-      <c r="B73" s="216" t="s">
-        <v>1019</v>
+        <v>781</v>
+      </c>
+      <c r="B73" s="68">
+        <v>4.3</v>
       </c>
       <c r="C73" s="66" t="s">
-        <v>1020</v>
+        <v>846</v>
       </c>
       <c r="D73" s="68" t="s">
-        <v>1012</v>
+        <v>1077</v>
       </c>
       <c r="E73" s="66" t="s">
-        <v>1021</v>
+        <v>1075</v>
       </c>
       <c r="F73" s="88" t="s">
-        <v>1022</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="30" customHeight="1">
-      <c r="A74" s="179" t="s">
+      <c r="A74" s="81" t="s">
+        <v>859</v>
+      </c>
+      <c r="B74" s="75">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C74" s="76" t="s">
+        <v>860</v>
+      </c>
+      <c r="D74" s="75" t="s">
+        <v>118</v>
+      </c>
+      <c r="E74" s="76" t="s">
+        <v>861</v>
+      </c>
+      <c r="F74" s="87" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="30" customHeight="1">
+      <c r="A75" s="82" t="s">
+        <v>862</v>
+      </c>
+      <c r="B75" s="68">
+        <v>4.5</v>
+      </c>
+      <c r="C75" s="66" t="s">
+        <v>863</v>
+      </c>
+      <c r="D75" s="68" t="s">
+        <v>94</v>
+      </c>
+      <c r="E75" s="66" t="s">
+        <v>864</v>
+      </c>
+      <c r="F75" s="88" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="19.5" customHeight="1">
+      <c r="A76" s="82" t="s">
+        <v>980</v>
+      </c>
+      <c r="B76" s="220" t="s">
+        <v>990</v>
+      </c>
+      <c r="C76" s="66" t="s">
+        <v>991</v>
+      </c>
+      <c r="D76" s="68" t="s">
+        <v>992</v>
+      </c>
+      <c r="E76" s="66" t="s">
+        <v>993</v>
+      </c>
+      <c r="F76" s="88" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="30" customHeight="1">
+      <c r="A77" s="82" t="s">
+        <v>984</v>
+      </c>
+      <c r="B77" s="220" t="s">
+        <v>994</v>
+      </c>
+      <c r="C77" s="66" t="s">
+        <v>995</v>
+      </c>
+      <c r="D77" s="68" t="s">
+        <v>987</v>
+      </c>
+      <c r="E77" s="66" t="s">
+        <v>996</v>
+      </c>
+      <c r="F77" s="88" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="30" customHeight="1">
+      <c r="A78" s="179" t="s">
+        <v>250</v>
+      </c>
+      <c r="B78" s="180"/>
+      <c r="C78" s="180"/>
+      <c r="D78" s="180"/>
+      <c r="E78" s="180"/>
+      <c r="F78" s="181"/>
+    </row>
+    <row r="79" spans="1:6" ht="30" customHeight="1">
+      <c r="A79" s="78" t="s">
+        <v>142</v>
+      </c>
+      <c r="B79" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="D79" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="F79" s="84" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="30" customHeight="1">
+      <c r="A80" s="79" t="s">
+        <v>148</v>
+      </c>
+      <c r="B80" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="C80" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="D80" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="E80" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="F80" s="85" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="44" customHeight="1">
+      <c r="A81" s="232" t="s">
+        <v>152</v>
+      </c>
+      <c r="B81" s="233" t="s">
+        <v>143</v>
+      </c>
+      <c r="C81" s="234" t="s">
+        <v>100</v>
+      </c>
+      <c r="D81" s="233" t="s">
+        <v>102</v>
+      </c>
+      <c r="E81" s="234" t="s">
+        <v>257</v>
+      </c>
+      <c r="F81" s="235" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="30" customHeight="1">
+      <c r="A82" s="81" t="s">
+        <v>777</v>
+      </c>
+      <c r="B82" s="75">
+        <v>4.3</v>
+      </c>
+      <c r="C82" s="76" t="s">
+        <v>843</v>
+      </c>
+      <c r="D82" s="75" t="s">
+        <v>210</v>
+      </c>
+      <c r="E82" s="76" t="s">
+        <v>844</v>
+      </c>
+      <c r="F82" s="87" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="30" customHeight="1">
+      <c r="A83" s="82" t="s">
+        <v>781</v>
+      </c>
+      <c r="B83" s="68">
+        <v>4</v>
+      </c>
+      <c r="C83" s="66" t="s">
+        <v>810</v>
+      </c>
+      <c r="D83" s="68" t="s">
+        <v>811</v>
+      </c>
+      <c r="E83" s="66" t="s">
+        <v>812</v>
+      </c>
+      <c r="F83" s="88" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="30" customHeight="1">
+      <c r="A84" s="216" t="s">
+        <v>859</v>
+      </c>
+      <c r="B84" s="217">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="C84" s="218" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D84" s="217" t="s">
+        <v>183</v>
+      </c>
+      <c r="E84" s="218" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F84" s="219" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="44" customHeight="1">
+      <c r="A85" s="236" t="s">
+        <v>169</v>
+      </c>
+      <c r="B85" s="237">
+        <v>4.8</v>
+      </c>
+      <c r="C85" s="238" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D85" s="237" t="s">
+        <v>64</v>
+      </c>
+      <c r="E85" s="238" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F85" s="239" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="30" customHeight="1">
+      <c r="A86" s="179" t="s">
+        <v>258</v>
+      </c>
+      <c r="B86" s="180"/>
+      <c r="C86" s="180"/>
+      <c r="D86" s="180"/>
+      <c r="E86" s="180"/>
+      <c r="F86" s="181"/>
+    </row>
+    <row r="87" spans="1:6" ht="30" customHeight="1">
+      <c r="A87" s="78" t="s">
+        <v>142</v>
+      </c>
+      <c r="B87" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="D87" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="F87" s="84" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="30" customHeight="1">
+      <c r="A88" s="79" t="s">
+        <v>148</v>
+      </c>
+      <c r="B88" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="C88" s="16" t="s">
+        <v>831</v>
+      </c>
+      <c r="D88" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="E88" s="15" t="s">
+        <v>832</v>
+      </c>
+      <c r="F88" s="85" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="30" customHeight="1">
+      <c r="A89" s="80" t="s">
+        <v>152</v>
+      </c>
+      <c r="B89" s="4">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C89" s="13" t="s">
+        <v>850</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>851</v>
+      </c>
+      <c r="F89" s="86" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="33.75" customHeight="1">
+      <c r="A90" s="81" t="s">
+        <v>777</v>
+      </c>
+      <c r="B90" s="75">
+        <v>4.3</v>
+      </c>
+      <c r="C90" s="76" t="s">
+        <v>809</v>
+      </c>
+      <c r="D90" s="75" t="s">
+        <v>114</v>
+      </c>
+      <c r="E90" s="76" t="s">
+        <v>830</v>
+      </c>
+      <c r="F90" s="87" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="28">
+      <c r="A91" s="82" t="s">
+        <v>781</v>
+      </c>
+      <c r="B91" s="68">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C91" s="66" t="s">
+        <v>852</v>
+      </c>
+      <c r="D91" s="68" t="s">
+        <v>853</v>
+      </c>
+      <c r="E91" s="66" t="s">
+        <v>854</v>
+      </c>
+      <c r="F91" s="88" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="44" customHeight="1">
+      <c r="A92" s="81" t="s">
+        <v>859</v>
+      </c>
+      <c r="B92" s="75">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="C92" s="76" t="s">
+        <v>866</v>
+      </c>
+      <c r="D92" s="75" t="s">
+        <v>123</v>
+      </c>
+      <c r="E92" s="76" t="s">
+        <v>867</v>
+      </c>
+      <c r="F92" s="87" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="28">
+      <c r="A93" s="223" t="s">
+        <v>862</v>
+      </c>
+      <c r="B93" s="226" t="s">
+        <v>239</v>
+      </c>
+      <c r="C93" s="225" t="s">
+        <v>868</v>
+      </c>
+      <c r="D93" s="226" t="s">
+        <v>269</v>
+      </c>
+      <c r="E93" s="225" t="s">
+        <v>869</v>
+      </c>
+      <c r="F93" s="227" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="42">
+      <c r="A94" s="82" t="s">
+        <v>980</v>
+      </c>
+      <c r="B94" s="220" t="s">
+        <v>981</v>
+      </c>
+      <c r="C94" s="66" t="s">
+        <v>982</v>
+      </c>
+      <c r="D94" s="68" t="s">
+        <v>183</v>
+      </c>
+      <c r="E94" s="66" t="s">
+        <v>983</v>
+      </c>
+      <c r="F94" s="88" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="42">
+      <c r="A95" s="82" t="s">
+        <v>984</v>
+      </c>
+      <c r="B95" s="220" t="s">
+        <v>985</v>
+      </c>
+      <c r="C95" s="66" t="s">
+        <v>986</v>
+      </c>
+      <c r="D95" s="68" t="s">
+        <v>987</v>
+      </c>
+      <c r="E95" s="66" t="s">
+        <v>988</v>
+      </c>
+      <c r="F95" s="88" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="48" customHeight="1">
+      <c r="A96" s="179" t="s">
+        <v>264</v>
+      </c>
+      <c r="B96" s="180"/>
+      <c r="C96" s="180"/>
+      <c r="D96" s="180"/>
+      <c r="E96" s="180"/>
+      <c r="F96" s="181"/>
+    </row>
+    <row r="97" spans="1:6" ht="84">
+      <c r="A97" s="78" t="s">
+        <v>142</v>
+      </c>
+      <c r="B97" s="240">
+        <v>5</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D97" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F97" s="84" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" s="80" t="s">
+        <v>148</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C98" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="F98" s="86" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="28">
+      <c r="A99" s="81" t="s">
+        <v>152</v>
+      </c>
+      <c r="B99" s="75">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="C99" s="76" t="s">
+        <v>855</v>
+      </c>
+      <c r="D99" s="75" t="s">
+        <v>856</v>
+      </c>
+      <c r="E99" s="76" t="s">
+        <v>857</v>
+      </c>
+      <c r="F99" s="87" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="28">
+      <c r="A100" s="82" t="s">
+        <v>777</v>
+      </c>
+      <c r="B100" s="68">
+        <v>4.5</v>
+      </c>
+      <c r="C100" s="66" t="s">
+        <v>813</v>
+      </c>
+      <c r="D100" s="68" t="s">
+        <v>114</v>
+      </c>
+      <c r="E100" s="66" t="s">
+        <v>814</v>
+      </c>
+      <c r="F100" s="88" t="s">
         <v>263</v>
       </c>
-      <c r="B74" s="180"/>
-      <c r="C74" s="180"/>
-      <c r="D74" s="180"/>
-      <c r="E74" s="180"/>
-      <c r="F74" s="181"/>
-    </row>
-    <row r="75" spans="1:6" ht="30" customHeight="1">
-      <c r="A75" s="78" t="s">
-        <v>147</v>
-      </c>
-      <c r="B75" s="27" t="s">
-        <v>182</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="D75" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="E75" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="F75" s="84" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="19.5" customHeight="1">
-      <c r="A76" s="79" t="s">
-        <v>153</v>
-      </c>
-      <c r="B76" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="C76" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="D76" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="E76" s="15" t="s">
-        <v>268</v>
-      </c>
-      <c r="F76" s="85" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="30" customHeight="1">
-      <c r="A77" s="80" t="s">
-        <v>157</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C77" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="F77" s="86" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="30" customHeight="1">
-      <c r="A78" s="81" t="s">
-        <v>795</v>
-      </c>
-      <c r="B78" s="75">
-        <v>4.3</v>
-      </c>
-      <c r="C78" s="76" t="s">
-        <v>865</v>
-      </c>
-      <c r="D78" s="75" t="s">
-        <v>218</v>
-      </c>
-      <c r="E78" s="76" t="s">
-        <v>866</v>
-      </c>
-      <c r="F78" s="87" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="30" customHeight="1">
-      <c r="A79" s="82" t="s">
-        <v>799</v>
-      </c>
-      <c r="B79" s="68">
-        <v>4</v>
-      </c>
-      <c r="C79" s="66" t="s">
-        <v>830</v>
-      </c>
-      <c r="D79" s="68" t="s">
-        <v>831</v>
-      </c>
-      <c r="E79" s="66" t="s">
-        <v>832</v>
-      </c>
-      <c r="F79" s="88" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="30" customHeight="1">
-      <c r="A80" s="179" t="s">
-        <v>271</v>
-      </c>
-      <c r="B80" s="180"/>
-      <c r="C80" s="180"/>
-      <c r="D80" s="180"/>
-      <c r="E80" s="180"/>
-      <c r="F80" s="181"/>
-    </row>
-    <row r="81" spans="1:6" ht="30" customHeight="1">
-      <c r="A81" s="78" t="s">
-        <v>147</v>
-      </c>
-      <c r="B81" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="D81" s="27" t="s">
-        <v>259</v>
-      </c>
-      <c r="E81" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="F81" s="84" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="30" customHeight="1">
-      <c r="A82" s="79" t="s">
-        <v>153</v>
-      </c>
-      <c r="B82" s="18">
-        <v>4.2</v>
-      </c>
-      <c r="C82" s="16" t="s">
-        <v>852</v>
-      </c>
-      <c r="D82" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="E82" s="15" t="s">
-        <v>853</v>
-      </c>
-      <c r="F82" s="85" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="30" customHeight="1">
-      <c r="A83" s="80" t="s">
-        <v>157</v>
-      </c>
-      <c r="B83" s="4">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C83" s="13" t="s">
-        <v>875</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>876</v>
-      </c>
-      <c r="F83" s="86" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="30" customHeight="1">
-      <c r="A84" s="81" t="s">
-        <v>795</v>
-      </c>
-      <c r="B84" s="75">
-        <v>4.3</v>
-      </c>
-      <c r="C84" s="76" t="s">
-        <v>829</v>
-      </c>
-      <c r="D84" s="75" t="s">
-        <v>119</v>
-      </c>
-      <c r="E84" s="76" t="s">
-        <v>851</v>
-      </c>
-      <c r="F84" s="87" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="30" customHeight="1">
-      <c r="A85" s="82" t="s">
-        <v>799</v>
-      </c>
-      <c r="B85" s="68">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C85" s="66" t="s">
-        <v>877</v>
-      </c>
-      <c r="D85" s="68" t="s">
-        <v>878</v>
-      </c>
-      <c r="E85" s="66" t="s">
-        <v>879</v>
-      </c>
-      <c r="F85" s="88" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="30" customHeight="1">
-      <c r="A86" s="81" t="s">
-        <v>884</v>
-      </c>
-      <c r="B86" s="75">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="C86" s="76" t="s">
-        <v>891</v>
-      </c>
-      <c r="D86" s="75" t="s">
-        <v>128</v>
-      </c>
-      <c r="E86" s="76" t="s">
-        <v>892</v>
-      </c>
-      <c r="F86" s="87" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="30" customHeight="1">
-      <c r="A87" s="82" t="s">
-        <v>887</v>
-      </c>
-      <c r="B87" s="68" t="s">
-        <v>252</v>
-      </c>
-      <c r="C87" s="66" t="s">
-        <v>893</v>
-      </c>
-      <c r="D87" s="68" t="s">
-        <v>287</v>
-      </c>
-      <c r="E87" s="66" t="s">
-        <v>894</v>
-      </c>
-      <c r="F87" s="88" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="30" customHeight="1">
-      <c r="A88" s="82" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B88" s="216" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C88" s="66" t="s">
-        <v>1007</v>
-      </c>
-      <c r="D88" s="68" t="s">
-        <v>189</v>
-      </c>
-      <c r="E88" s="66" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F88" s="88" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="30" customHeight="1">
-      <c r="A89" s="82" t="s">
-        <v>1009</v>
-      </c>
-      <c r="B89" s="216" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C89" s="66" t="s">
-        <v>1011</v>
-      </c>
-      <c r="D89" s="68" t="s">
-        <v>1012</v>
-      </c>
-      <c r="E89" s="66" t="s">
-        <v>1013</v>
-      </c>
-      <c r="F89" s="88" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="33.75" customHeight="1">
-      <c r="A90" s="179" t="s">
-        <v>277</v>
-      </c>
-      <c r="B90" s="180"/>
-      <c r="C90" s="180"/>
-      <c r="D90" s="180"/>
-      <c r="E90" s="180"/>
-      <c r="F90" s="181"/>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91" s="78" t="s">
-        <v>147</v>
-      </c>
-      <c r="B91" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="D91" s="27" t="s">
-        <v>279</v>
-      </c>
-      <c r="E91" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="F91" s="84" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92" s="79" t="s">
-        <v>153</v>
-      </c>
-      <c r="B92" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="C92" s="16" t="s">
-        <v>281</v>
-      </c>
-      <c r="D92" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="E92" s="15" t="s">
-        <v>282</v>
-      </c>
-      <c r="F92" s="85" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93" s="80" t="s">
-        <v>157</v>
-      </c>
-      <c r="B93" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C93" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="D93" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="F93" s="86" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="28">
-      <c r="A94" s="81" t="s">
-        <v>795</v>
-      </c>
-      <c r="B94" s="75">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="C94" s="76" t="s">
-        <v>880</v>
-      </c>
-      <c r="D94" s="75" t="s">
-        <v>881</v>
-      </c>
-      <c r="E94" s="76" t="s">
-        <v>882</v>
-      </c>
-      <c r="F94" s="87" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="28">
-      <c r="A95" s="82" t="s">
-        <v>799</v>
-      </c>
-      <c r="B95" s="68">
-        <v>4.5</v>
-      </c>
-      <c r="C95" s="66" t="s">
-        <v>833</v>
-      </c>
-      <c r="D95" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="E95" s="66" t="s">
-        <v>834</v>
-      </c>
-      <c r="F95" s="88" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="48" customHeight="1" thickBot="1">
-      <c r="A96" s="182" t="s">
-        <v>1032</v>
-      </c>
-      <c r="B96" s="183"/>
-      <c r="C96" s="183"/>
-      <c r="D96" s="183"/>
-      <c r="E96" s="183"/>
-      <c r="F96" s="184"/>
+    </row>
+    <row r="101" spans="1:6" ht="16" thickBot="1">
+      <c r="A101" s="182" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B101" s="183"/>
+      <c r="C101" s="183"/>
+      <c r="D101" s="183"/>
+      <c r="E101" s="183"/>
+      <c r="F101" s="184"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -21460,19 +21418,19 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="A42:F42"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A90:F90"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A51:F51"/>
     <mergeCell ref="A96:F96"/>
-    <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A60:F60"/>
+    <mergeCell ref="A101:F101"/>
+    <mergeCell ref="A58:F58"/>
     <mergeCell ref="A64:F64"/>
-    <mergeCell ref="A74:F74"/>
-    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="A86:F86"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -21495,7 +21453,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1">
       <c r="A1" s="161" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="B1" s="162"/>
       <c r="C1" s="162"/>
@@ -21509,7 +21467,7 @@
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
       <c r="A3" s="197" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="B3" s="198"/>
       <c r="C3" s="198"/>
@@ -21517,100 +21475,100 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="133" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="D4" s="143" t="s">
-        <v>292</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" customHeight="1">
       <c r="A5" s="134" t="s">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="D5" s="144" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="27.75" customHeight="1">
       <c r="A6" s="135" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="D6" s="145" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="27.75" customHeight="1">
       <c r="A7" s="136" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="D7" s="146" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1">
       <c r="A8" s="137" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>63</v>
+        <v>1020</v>
       </c>
       <c r="C8" s="41" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="D8" s="147" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="27.75" customHeight="1">
       <c r="A9" s="138" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="C9" s="44" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="D9" s="148" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" customHeight="1">
       <c r="A10" s="139" t="s">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="B10" s="92" t="s">
-        <v>924</v>
+        <v>899</v>
       </c>
       <c r="C10" s="92" t="s">
-        <v>925</v>
+        <v>900</v>
       </c>
       <c r="D10" s="125" t="s">
-        <v>926</v>
+        <v>901</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -21621,7 +21579,7 @@
     </row>
     <row r="12" spans="1:4" ht="24" customHeight="1">
       <c r="A12" s="200" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="B12" s="201"/>
       <c r="C12" s="201"/>
@@ -21629,170 +21587,170 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="133" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="D13" s="143" t="s">
-        <v>292</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1">
       <c r="A14" s="135" t="s">
+        <v>279</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>295</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>296</v>
+      </c>
+      <c r="D14" s="145" t="s">
         <v>297</v>
-      </c>
-      <c r="B14" s="34" t="s">
-        <v>313</v>
-      </c>
-      <c r="C14" s="35" t="s">
-        <v>314</v>
-      </c>
-      <c r="D14" s="145" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="27.75" customHeight="1">
       <c r="A15" s="136" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="D15" s="146" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="30" customHeight="1">
       <c r="A16" s="136" t="s">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="B16" s="45" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="D16" s="146" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1">
       <c r="A17" s="137" t="s">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="D17" s="147" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1">
       <c r="A18" s="137" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
       <c r="C18" s="41" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="D18" s="147" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="30" customHeight="1">
       <c r="A19" s="134" t="s">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="D19" s="144" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="30" customHeight="1">
       <c r="A20" s="139" t="s">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="B20" s="92" t="s">
-        <v>927</v>
+        <v>902</v>
       </c>
       <c r="C20" s="92" t="s">
-        <v>928</v>
+        <v>903</v>
       </c>
       <c r="D20" s="125" t="s">
-        <v>929</v>
+        <v>904</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="30" customHeight="1">
       <c r="A21" s="140" t="s">
-        <v>930</v>
+        <v>905</v>
       </c>
       <c r="B21" s="90" t="s">
-        <v>931</v>
+        <v>906</v>
       </c>
       <c r="C21" s="90" t="s">
-        <v>932</v>
+        <v>907</v>
       </c>
       <c r="D21" s="149" t="s">
-        <v>933</v>
+        <v>908</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="27.75" customHeight="1">
       <c r="A22" s="138" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="B22" s="43" t="s">
-        <v>333</v>
+        <v>315</v>
       </c>
       <c r="C22" s="44" t="s">
-        <v>334</v>
+        <v>316</v>
       </c>
       <c r="D22" s="148" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="30" customHeight="1">
       <c r="A23" s="137" t="s">
-        <v>336</v>
+        <v>318</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="C23" s="41" t="s">
-        <v>338</v>
+        <v>320</v>
       </c>
       <c r="D23" s="147" t="s">
-        <v>339</v>
+        <v>321</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="30" customHeight="1">
       <c r="A24" s="137" t="s">
-        <v>336</v>
+        <v>318</v>
       </c>
       <c r="B24" s="40" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="C24" s="41" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="D24" s="147" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -21803,7 +21761,7 @@
     </row>
     <row r="26" spans="1:4" ht="24" customHeight="1">
       <c r="A26" s="203" t="s">
-        <v>343</v>
+        <v>325</v>
       </c>
       <c r="B26" s="204"/>
       <c r="C26" s="204"/>
@@ -21811,128 +21769,128 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="133" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="D27" s="143" t="s">
-        <v>292</v>
+        <v>274</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="27.75" customHeight="1">
       <c r="A28" s="135" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B28" s="34" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="D28" s="145" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="30" customHeight="1">
       <c r="A29" s="136" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="B29" s="37" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="D29" s="146" t="s">
-        <v>347</v>
+        <v>329</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="27.75" customHeight="1">
       <c r="A30" s="134" t="s">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="B30" s="31" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="C30" s="32" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="D30" s="144" t="s">
-        <v>350</v>
+        <v>332</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="27.75" customHeight="1">
       <c r="A31" s="138" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="B31" s="43" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="C31" s="44" t="s">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="D31" s="148" t="s">
-        <v>353</v>
+        <v>335</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="27.75" customHeight="1">
       <c r="A32" s="138" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="B32" s="43" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="C32" s="44" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="D32" s="148" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="30" customHeight="1">
       <c r="A33" s="135" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B33" s="46" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="C33" s="35" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="D33" s="145" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="30" customHeight="1">
       <c r="A34" s="137" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="B34" s="40" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="C34" s="41" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="D34" s="147" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="30" customHeight="1" thickBot="1">
       <c r="A35" s="141" t="s">
-        <v>336</v>
+        <v>318</v>
       </c>
       <c r="B35" s="130" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="C35" s="131" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="D35" s="150" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>
@@ -21963,7 +21921,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1">
       <c r="A1" s="206" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="B1" s="206"/>
       <c r="C1" s="206"/>
@@ -21971,7 +21929,7 @@
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
       <c r="A3" s="178" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="B3" s="178"/>
       <c r="C3" s="178"/>
@@ -21979,63 +21937,63 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="12" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="27.75" customHeight="1">
       <c r="A5" s="47" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="B5" s="48" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="C5" s="49" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="D5" s="47" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="27.75" customHeight="1">
       <c r="A6" s="47" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="D6" s="47" t="s">
-        <v>375</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="27.75" customHeight="1">
       <c r="A7" s="30" t="s">
-        <v>376</v>
+        <v>358</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="24" customHeight="1">
       <c r="A9" s="174" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="B9" s="174"/>
       <c r="C9" s="174"/>
@@ -22043,49 +22001,49 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="12" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="27.75" customHeight="1">
       <c r="A11" s="47" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="B11" s="48" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="D11" s="47" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="27.75" customHeight="1">
       <c r="A12" s="47" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="B12" s="48" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="C12" s="49" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="D12" s="47" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="24" customHeight="1">
       <c r="A14" s="176" t="s">
-        <v>343</v>
+        <v>325</v>
       </c>
       <c r="B14" s="176"/>
       <c r="C14" s="176"/>
@@ -22093,44 +22051,44 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="12" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="27.75" customHeight="1">
       <c r="A16" s="47" t="s">
+        <v>352</v>
+      </c>
+      <c r="B16" s="48" t="s">
+        <v>368</v>
+      </c>
+      <c r="C16" s="49" t="s">
+        <v>369</v>
+      </c>
+      <c r="D16" s="47" t="s">
         <v>370</v>
-      </c>
-      <c r="B16" s="48" t="s">
-        <v>386</v>
-      </c>
-      <c r="C16" s="49" t="s">
-        <v>387</v>
-      </c>
-      <c r="D16" s="47" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="27.75" customHeight="1">
       <c r="A17" s="50" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="B17" s="51" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="C17" s="52" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D17" s="50" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>

--- a/tools/itinerary.xlsx
+++ b/tools/itinerary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jitwei/Library/Mobile Documents/com~apple~CloudDocs/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A830E94F-BF89-7049-9200-E77F80738451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF6D92BA-07DB-AB45-AB44-B5E561C7B00A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="17020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="17020" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1685" uniqueCount="1126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1695" uniqueCount="1133">
   <si>
     <r>
       <rPr>
@@ -1579,28 +1579,6 @@
     <t>🍡 Dessert</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Fangpo Cake Shop </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>芳婆糕团店</t>
-    </r>
-  </si>
-  <si>
     <t>秦淮区</t>
   </si>
   <si>
@@ -3131,38 +3109,6 @@
     <t>西湖区龙井路</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Jin Sha </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">金沙厅 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Four Seasons)</t>
-    </r>
-  </si>
-  <si>
     <t>¥700+</t>
   </si>
   <si>
@@ -3372,38 +3318,6 @@
     <t>¥80–120</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Li Ji </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">李记清真 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Dading Lane)</t>
-    </r>
-  </si>
-  <si>
     <t>秦淮区大顶巷</t>
   </si>
   <si>
@@ -3583,38 +3497,6 @@
     <t>秦淮区老门东</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Ritz — Dai Yuet Heen </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">帝粤轩 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Michelin 1★)</t>
-    </r>
-  </si>
-  <si>
     <t>¥400+</t>
   </si>
   <si>
@@ -3675,38 +3557,6 @@
         <b/>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Jiangnan Wok </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">江南灶 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Shangri-La)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -3854,60 +3704,6 @@
   <si>
     <r>
       <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Ritz — Pin Ning Fu </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">品宁府 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Michelin 1★)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">梅苑 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Plum Garden (Jinling Hotel)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Noto Sans CJK SC"/>
@@ -4008,38 +3804,6 @@
     <t>🍡</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">糕团甜品 — </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Fangpo </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>芳婆糕团店</t>
-    </r>
-  </si>
-  <si>
     <t>🌃</t>
   </si>
   <si>
@@ -12922,9 +12686,6 @@
     <t>上城区仁和路 (近龙翔桥)</t>
   </si>
   <si>
-    <t>Longjing Caotang 龙井草堂</t>
-  </si>
-  <si>
     <t>西湖区龙井路399号</t>
   </si>
   <si>
@@ -12940,9 +12701,6 @@
     <t>Fuzimiao institution — chicken-broth soup dumplings; fast on an arrival day</t>
   </si>
   <si>
-    <t>Xiao Pan Ji 小潘记 鸭血粉丝汤</t>
-  </si>
-  <si>
     <t>Lan Jia Shan 蓝家山 (Laomendong)</t>
   </si>
   <si>
@@ -13063,9 +12821,6 @@
     <t>Famous 三虾面 / 枫镇大肉面 — Suzhou noodle institution near Guanqian</t>
   </si>
   <si>
-    <t>Xin Rong Ji 新荣记 (Raffles City 来福士)</t>
-  </si>
-  <si>
     <t>Kuiyuan Wangzhuang / Hefang snack lanes 河坊街小吃</t>
   </si>
   <si>
@@ -13094,9 +12849,6 @@
   </si>
   <si>
     <t>Fast Su-style zongzi 粽子 &amp; snacks — easy arrival-day lunch</t>
-  </si>
-  <si>
-    <t>Tongdexing 同得兴 (Suzhou noodles 苏式面)</t>
   </si>
   <si>
     <t>Qinhuai Renjia 秦淮人家 (夫子庙)</t>
@@ -13999,9 +13751,6 @@
     <t>上城区中山南路479号 (中河中路×望江路西南100m)</t>
   </si>
   <si>
-    <t>泮芳春煎饺 Pan Fang Chun (Day 3 · Opt)</t>
-  </si>
-  <si>
     <t>上城区中山南路479号 (吴山广场/河坊街)</t>
   </si>
   <si>
@@ -14143,9 +13892,6 @@
     <t>鸭血粉丝汤 (小潘记 — 必比登 2026), 牛肉锅贴 (蒋有记), 汤包. Also nearby: 李记清真馆 &amp; 致和老鸭粉丝汤, both 必比登 2026.</t>
   </si>
   <si>
-    <t>Tongdexing 同得兴 (嘉馀坊店) (Day 7 · Michelin)</t>
-  </si>
-  <si>
     <t>姑苏区嘉馀坊6号 (near 观前街)</t>
   </si>
   <si>
@@ -14158,18 +13904,12 @@
     <t>(not verified)</t>
   </si>
   <si>
-    <t>正清牛肉锅贴店 Zhengqing (NEW 必比登 2026)</t>
-  </si>
-  <si>
     <t>鼓楼区江西路</t>
   </si>
   <si>
     <t>MICHELIN 必比登 BIB GOURMAND 2026 (新晋). Locals rate its 牛肉锅贴 above the 夫子庙 tourist names — crisp shell, juicy filling; 牛肉小馄饨 too. Alternative to 蒋有记 on Day 4.</t>
   </si>
   <si>
-    <t>致和老鸭粉丝汤 Zhihe (NEW 必比登 2026)</t>
-  </si>
-  <si>
     <t>秦淮区 (residential lanes)</t>
   </si>
   <si>
@@ -14179,54 +13919,36 @@
     <t>~¥20</t>
   </si>
   <si>
-    <t>Xin Rong Ji 新荣记 (Day 1 · Raffles City 来福士)</t>
-  </si>
-  <si>
     <t>上城区钱江新城 来福士 (at the Conrad)</t>
   </si>
   <si>
     <t>MICHELIN ⭐ 1-STAR 2026 (沪苏浙指南). Taizhou-style seafood, nationally acclaimed — inside the mall your hotel connects to. The easiest starred meal of the whole trip.</t>
   </si>
   <si>
-    <t>湉园 Tianyuan (NEW 指南入选 2026)</t>
-  </si>
-  <si>
     <t>西湖区杨公堤 花港观鱼10号</t>
   </si>
   <si>
     <t>MICHELIN 指南入选 2026 (NEW Selected). Address is literally INSIDE 花港观鱼 — your Day 2 14:25–15:10 stop. Zero detour for a garden-set meal on the West Lake west side.</t>
   </si>
   <si>
-    <t>金丝·听海 (NEW 指南入选 2026)</t>
-  </si>
-  <si>
     <t>西湖区北山街78号 (香格里拉·水知心居一楼)</t>
   </si>
   <si>
     <t>MICHELIN 指南入选 2026 (NEW Selected). On 北山街 — your Day 2 08:15 ginkgo avenue — and ~4 doors from 印象西湖 at 北山路82号. Strong pre-show dinner candidate.</t>
   </si>
   <si>
-    <t>DINING &amp; SPECIALTY COFFEE (also slotted into day tabs) — MICHELIN 2026 沪苏浙指南 status labelled (⭐ star / 必比登 Bib / 指南入选 Selected). Cafés are never Michelin-rated: the guide covers restaurants only.</t>
-  </si>
-  <si>
     <t>MEAL OPTIONS — top-rated picks per lunch &amp; dinner (by popularity, rating &amp; distance), with MICHELIN 2026 status</t>
   </si>
   <si>
     <t>Ratings from Trip.com / Dianping / Tripadvisor (2026). Dianping 评分 is a 0–100 scale — NOT comparable to the 0–5 star ratings in column B; compare rank position only. MICHELIN labels are from the 2026 沪苏浙米其林指南 (released 9 Apr 2026, 409 restaurants).</t>
   </si>
   <si>
-    <t>Options ranked by rating, popularity &amp; distance from the day's route. ★ 宫宴 = banquet. 🏨 = at/near hotel. MICHELIN 2026: Hangzhou 88 listings (34 必比登) · Nanjing 41 (21 必比登, 4 ⭐) · Suzhou 38 (18 必比登, 3 ⭐).</t>
-  </si>
-  <si>
     <t>宫宴 Gongyan — Song Palace Banquet (Day 3)</t>
   </si>
   <si>
     <t>姑苏区平江街道大儒巷54号 (丁宅)</t>
   </si>
   <si>
-    <t>金海华·平江颂 Pingjiang Song (Day 7 · Michelin 1★)</t>
-  </si>
-  <si>
     <t>姑苏区平江街道大儒巷54号 (丁宅, off 平江路)</t>
   </si>
   <si>
@@ -14242,33 +13964,18 @@
     <t>姑苏区狮林寺巷99号 琵琶语评弹茶馆·北馆1层</t>
   </si>
   <si>
-    <t>湉园 Tianyuan (Michelin 指南入选 2026)</t>
-  </si>
-  <si>
     <t>MICHELIN 指南入选 2026 (NEW Selected). Sits INSIDE 花港观鱼 — your Day 2 14:25 stop — so it is a zero-detour garden lunch. Price &amp; hours not yet verified; call ahead.</t>
   </si>
   <si>
-    <t>金丝·听海 (Michelin 指南入选 2026)</t>
-  </si>
-  <si>
     <t>MICHELIN 指南入选 2026 (NEW Selected). On 北山街 — your Day 2 08:15 ginkgo avenue — and ~4 doors from 印象西湖 (北山路82号). Best used as the PRE-SHOW dinner. Price &amp; hours not verified.</t>
   </si>
   <si>
-    <t>致和老鸭粉丝汤 Zhihe (Michelin 必比登 2026)</t>
-  </si>
-  <si>
     <t>MICHELIN 必比登 BIB GOURMAND 2026 (新晋/NEW) — ~¥20pp. Duck-carcass broth with 鸭血/鸭肠/鸭肝; the chilli oil is the soul. 秦淮区 = same district as this evening. Exact lane address not published — locate on Amap before going.</t>
   </si>
   <si>
-    <t>正清牛肉锅贴店 Zhengqing (Michelin 必比登 2026)</t>
-  </si>
-  <si>
     <t>MICHELIN 必比登 BIB GOURMAND 2026 (新晋/NEW). Locals rate its 牛肉锅贴 above the 夫子庙 tourist names — crisp shell, juicy filling; 牛肉小馄饨 too. 鼓楼区江西路, the same western side as 马祥兴 — a cheap alternative on this block.</t>
   </si>
   <si>
-    <t>金海华·平江颂 Pingjiang Song (Michelin ⭐ 1★)</t>
-  </si>
-  <si>
     <t>MICHELIN ⭐ 1-STAR 2026 — 大儒巷54号 is a lane just OFF 平江路, so it is walkable from tonight's canal stroll. 丁宅, a Ming mansion relocated here in 2011; garden setting with 评弹. 新苏州菜, 不时不食 — 松鼠黄鱼, 碧螺虾仁, 响油蟹䰾. Trip.com 4.8, #1 Suzhou fine dining. ⚠ BOOK ~1 WEEK AHEAD — very few tables; set menu from 2 pax. 11:30–14:00 / 17:30–21:00. Tel +86 512 6610 9177.</t>
   </si>
   <si>
@@ -14276,6 +13983,108 @@
   </si>
   <si>
     <t>5.0-rated lakeside fine dining — the splurge choice IF you head to Jinji Lake 金鸡湖 / SIP on the last night. (Note: 平江颂 has moved to Day 6 Dinner — 大儒巷54号 sits off 平江路, so it belongs with that evening.)</t>
+  </si>
+  <si>
+    <t>姑苏区虎丘街道山塘街方基上38号楼 (白居易码头对面)</t>
+  </si>
+  <si>
+    <t>2026 Bib Gourmand. Noodle sub-brand of Michelin 1★ 鼎膳. Red or white broth simmered 6–8 hrs; 21 hot + 12 cold 浇头. Try 烟熏青鱼面 (signature carried over from 鼎膳), 焖肉面, 塘园五虾面. Verified via 姑苏发布 (区委宣传部) &amp; 苏州市文广旅局.</t>
+  </si>
+  <si>
+    <t>~¥40–80</t>
+  </si>
+  <si>
+    <t>⑩</t>
+  </si>
+  <si>
+    <t>MICHELIN 2026 必比登. Noodle house by Michelin 1★ 鼎膳 — red/white broth simmered 6–8 hrs, 21 hot + 12 cold 浇头. Try 烟熏青鱼面, 焖肉面, 塘园五虾面. Walkable from the Ritz.</t>
+  </si>
+  <si>
+    <t>🔴 泮芳春煎饺 Pan Fang Chun (Day 3 · Opt)</t>
+  </si>
+  <si>
+    <t>⭐ Xin Rong Ji 新荣记 (Day 1 · Raffles City 来福士)</t>
+  </si>
+  <si>
+    <t>◆ 湉园 Tianyuan (NEW 指南入选 2026)</t>
+  </si>
+  <si>
+    <t>◆ 金丝·听海 (NEW 指南入选 2026)</t>
+  </si>
+  <si>
+    <t>🔴 Fangpo Cake Shop 芳婆糕团店</t>
+  </si>
+  <si>
+    <t>🔴 正清牛肉锅贴店 Zhengqing (NEW 必比登 2026)</t>
+  </si>
+  <si>
+    <t>🔴 致和老鸭粉丝汤 Zhihe (NEW 必比登 2026)</t>
+  </si>
+  <si>
+    <t>🔴 Tongdexing 同得兴 (嘉馀坊店) (Day 7 · Michelin)</t>
+  </si>
+  <si>
+    <t>⭐ 金海华·平江颂 Pingjiang Song (Day 6 · Michelin 1★)</t>
+  </si>
+  <si>
+    <t>🔴 Tangyuan 塘园·苏式面菜馆 (Day 7 · Michelin Bib)</t>
+  </si>
+  <si>
+    <t>⭐ Xin Rong Ji 新荣记 (Raffles City 来福士)</t>
+  </si>
+  <si>
+    <t>◆ 湉园 Tianyuan (Michelin 指南入选 2026)</t>
+  </si>
+  <si>
+    <t>◆ 金丝·听海 (Michelin 指南入选 2026)</t>
+  </si>
+  <si>
+    <t>⭐ Jin Sha 金沙厅 (Four Seasons)</t>
+  </si>
+  <si>
+    <t>⭐ Longjing Caotang 龙井草堂</t>
+  </si>
+  <si>
+    <t>🔴 Li Ji 李记清真 (Dading Lane)</t>
+  </si>
+  <si>
+    <t>⭐ Ritz — Dai Yuet Heen 帝粤轩 (Michelin 1★)</t>
+  </si>
+  <si>
+    <t>🔴 Xiao Pan Ji 小潘记 鸭血粉丝汤</t>
+  </si>
+  <si>
+    <t>🔴 致和老鸭粉丝汤 Zhihe (Michelin 必比登 2026)</t>
+  </si>
+  <si>
+    <t>◆ Jiangnan Wok 江南灶 (Shangri-La)</t>
+  </si>
+  <si>
+    <t>🔴 正清牛肉锅贴店 Zhengqing (Michelin 必比登 2026)</t>
+  </si>
+  <si>
+    <t>⭐ Ritz — Pin Ning Fu 品宁府 (Michelin 1★)</t>
+  </si>
+  <si>
+    <t>◆ 梅苑 Plum Garden (Jinling Hotel)</t>
+  </si>
+  <si>
+    <t>🔴 糕团甜品 — Fangpo 芳婆糕团店</t>
+  </si>
+  <si>
+    <t>🔴 Tongdexing 同得兴 (Suzhou noodles 苏式面)</t>
+  </si>
+  <si>
+    <t>⭐ 金海华·平江颂 Pingjiang Song (Michelin ⭐ 1★)</t>
+  </si>
+  <si>
+    <t>🔴 Tangyuan 塘园·苏式面菜馆 (Shantang 山塘街)</t>
+  </si>
+  <si>
+    <t>DINING &amp; CAFÉS — Hangzhou 杭州 · Nanjing 南京 · Suzhou 苏州 · 15–22 Nov 2026. MICHELIN 2026 (沪苏浙) key: ⭐ = Star 星级 · 🔴 = Bib Gourmand 必比登 · ◆ = Selected 指南入选 — icon appears in front of the venue name. Nanjing's full 必比登 list is published; Hangzhou &amp; Suzhou published only new entrants — route-relevant ones are included here. Addresses verified against official/municipal sources; unverified items are labelled.</t>
+  </si>
+  <si>
+    <t>Options ranked by rating, popularity &amp; distance from the day's route. ★ 宫宴 = banquet. 🏨 = at/near hotel. MICHELIN 2026 (沪苏浙, released 9 Apr 2026) key: ⭐ = Star 星级 · 🔴 = Bib Gourmand 必比登 · ◆ = Selected 指南入选 — icon appears in front of the restaurant name. Totals: Hangzhou 88 listings (34 必比登) · Nanjing 41 (21 必比登, 4 ⭐) · Suzhou 38 (18 必比登, 3 ⭐). Nanjing's 21 必比登 are fully published; Hangzhou &amp; Suzhou released only the new entrants by name — remaining 必比登 names are unpublished.</t>
   </si>
 </sst>
 </file>
@@ -14844,7 +14653,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="241">
+  <cellXfs count="242">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -15558,6 +15367,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -16062,7 +15874,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
       <c r="A1" s="161" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="B1" s="162"/>
       <c r="C1" s="162"/>
@@ -16072,7 +15884,7 @@
     </row>
     <row r="2" spans="1:6" ht="21.75" customHeight="1">
       <c r="A2" s="164" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="B2" s="165"/>
       <c r="C2" s="165"/>
@@ -16082,19 +15894,19 @@
     </row>
     <row r="3" spans="1:6" ht="19.5" customHeight="1">
       <c r="A3" s="77" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="F3" s="83" t="s">
         <v>23</v>
@@ -16102,7 +15914,7 @@
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1">
       <c r="A4" s="167" t="s">
-        <v>939</v>
+        <v>927</v>
       </c>
       <c r="B4" s="168"/>
       <c r="C4" s="168"/>
@@ -16112,99 +15924,99 @@
     </row>
     <row r="5" spans="1:6" ht="25.5" customHeight="1">
       <c r="A5" s="98" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="B5" s="53" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="F5" s="86" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="25.5" customHeight="1">
       <c r="A6" s="99" t="s">
+        <v>373</v>
+      </c>
+      <c r="B6" s="54" t="s">
+        <v>379</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="D6" s="15" t="s">
         <v>381</v>
       </c>
-      <c r="B6" s="54" t="s">
-        <v>387</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>388</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>389</v>
-      </c>
       <c r="E6" s="15" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="F6" s="113" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1">
       <c r="A7" s="100" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="B7" s="213" t="s">
-        <v>951</v>
+        <v>939</v>
       </c>
       <c r="C7" s="50" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="D7" s="50" t="s">
-        <v>952</v>
+        <v>940</v>
       </c>
       <c r="E7" s="50" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="F7" s="115" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="25.5" customHeight="1">
       <c r="A8" s="100" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="B8" s="55" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="C8" s="50" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="D8" s="50" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="E8" s="50" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="F8" s="115" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="25.5" customHeight="1">
       <c r="A9" s="100" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="B9" s="55" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="D9" s="50" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="E9" s="50" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="F9" s="115" t="s">
         <v>28</v>
@@ -16212,87 +16024,87 @@
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1">
       <c r="A10" s="101" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="F10" s="116" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1">
       <c r="A11" s="102" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="F11" s="117" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1">
       <c r="A12" s="103" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="E12" s="41" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="F12" s="118" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1">
       <c r="A13" s="101" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="B13" s="56" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="F13" s="116" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="25.5" customHeight="1">
       <c r="A14" s="167" t="s">
-        <v>940</v>
+        <v>928</v>
       </c>
       <c r="B14" s="168"/>
       <c r="C14" s="168"/>
@@ -16302,16 +16114,16 @@
     </row>
     <row r="15" spans="1:6" ht="30" customHeight="1">
       <c r="A15" s="101" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B15" s="56" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>20</v>
@@ -16322,119 +16134,119 @@
     </row>
     <row r="16" spans="1:6" ht="30" customHeight="1">
       <c r="A16" s="104" t="s">
+        <v>414</v>
+      </c>
+      <c r="B16" s="59" t="s">
+        <v>418</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>419</v>
+      </c>
+      <c r="D16" s="47" t="s">
+        <v>420</v>
+      </c>
+      <c r="E16" s="47" t="s">
+        <v>421</v>
+      </c>
+      <c r="F16" s="119" t="s">
         <v>422</v>
-      </c>
-      <c r="B16" s="59" t="s">
-        <v>426</v>
-      </c>
-      <c r="C16" s="47" t="s">
-        <v>427</v>
-      </c>
-      <c r="D16" s="47" t="s">
-        <v>428</v>
-      </c>
-      <c r="E16" s="47" t="s">
-        <v>429</v>
-      </c>
-      <c r="F16" s="119" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="25.5" customHeight="1">
       <c r="A17" s="105" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B17" s="60" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="C17" s="61" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="D17" s="61" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="E17" s="61" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="F17" s="120" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="25.5" customHeight="1">
       <c r="A18" s="104" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="D18" s="47" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="E18" s="47" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="F18" s="119" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="25.5" customHeight="1">
       <c r="A19" s="105" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B19" s="60" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="C19" s="61" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="D19" s="61" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="E19" s="61" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="F19" s="120" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="25.5" customHeight="1">
       <c r="A20" s="105" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B20" s="207" t="s">
-        <v>963</v>
+        <v>951</v>
       </c>
       <c r="C20" s="61" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="D20" s="61" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="E20" s="61" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="F20" s="120" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="25.5" customHeight="1">
       <c r="A21" s="106" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B21" s="212" t="s">
-        <v>956</v>
+        <v>944</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="F21" s="121" t="s">
         <v>67</v>
@@ -16442,36 +16254,36 @@
     </row>
     <row r="22" spans="1:6" ht="42" customHeight="1">
       <c r="A22" s="106" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B22" s="212" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>953</v>
+        <v>941</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>954</v>
+        <v>942</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>955</v>
+        <v>943</v>
       </c>
       <c r="F22" s="121" t="s">
-        <v>938</v>
+        <v>926</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="42" customHeight="1">
       <c r="A23" s="98" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B23" s="214" t="s">
-        <v>957</v>
+        <v>945</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>56</v>
@@ -16482,245 +16294,245 @@
     </row>
     <row r="24" spans="1:6" ht="25.5" customHeight="1">
       <c r="A24" s="105" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B24" s="207" t="s">
-        <v>958</v>
+        <v>946</v>
       </c>
       <c r="C24" s="61" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="D24" s="61" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="E24" s="61" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="F24" s="120" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="25.5" customHeight="1">
       <c r="A25" s="105" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B25" s="207" t="s">
-        <v>959</v>
+        <v>947</v>
       </c>
       <c r="C25" s="61" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="D25" s="61" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="E25" s="61" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="F25" s="120" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="25.5" customHeight="1">
       <c r="A26" s="105" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B26" s="207" t="s">
-        <v>960</v>
+        <v>948</v>
       </c>
       <c r="C26" s="61" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="D26" s="61" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="E26" s="61" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="F26" s="120" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="42" customHeight="1">
       <c r="A27" s="105" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B27" s="207" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="C27" s="61" t="s">
-        <v>935</v>
+        <v>923</v>
       </c>
       <c r="D27" s="61" t="s">
-        <v>936</v>
+        <v>924</v>
       </c>
       <c r="E27" s="61" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="F27" s="120" t="s">
-        <v>937</v>
+        <v>925</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="42" customHeight="1">
       <c r="A28" s="107" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B28" s="215" t="s">
-        <v>961</v>
+        <v>949</v>
       </c>
       <c r="C28" s="36" t="s">
-        <v>964</v>
+        <v>952</v>
       </c>
       <c r="D28" s="36" t="s">
-        <v>965</v>
+        <v>953</v>
       </c>
       <c r="E28" s="36" t="s">
         <v>60</v>
       </c>
       <c r="F28" s="122" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="28">
       <c r="A29" s="102" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B29" s="209" t="s">
-        <v>962</v>
+        <v>950</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>914</v>
+        <v>902</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="F29" s="117" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="42" customHeight="1">
       <c r="A30" s="221" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B30" s="222" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="C30" s="61" t="s">
-        <v>1006</v>
+        <v>994</v>
       </c>
       <c r="D30" s="61" t="s">
-        <v>1007</v>
+        <v>995</v>
       </c>
       <c r="E30" s="61" t="s">
-        <v>1008</v>
+        <v>996</v>
       </c>
       <c r="F30" s="120" t="s">
-        <v>1009</v>
+        <v>997</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="42" customHeight="1">
       <c r="A31" s="221" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B31" s="222" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="C31" s="61" t="s">
-        <v>1010</v>
+        <v>998</v>
       </c>
       <c r="D31" s="61" t="s">
-        <v>1011</v>
+        <v>999</v>
       </c>
       <c r="E31" s="61" t="s">
-        <v>1012</v>
+        <v>1000</v>
       </c>
       <c r="F31" s="120" t="s">
-        <v>1013</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="56" customHeight="1">
       <c r="A32" s="221" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B32" s="222" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="C32" s="61" t="s">
-        <v>1021</v>
+        <v>1009</v>
       </c>
       <c r="D32" s="61" t="s">
-        <v>1022</v>
+        <v>1010</v>
       </c>
       <c r="E32" s="61" t="s">
-        <v>1023</v>
+        <v>1011</v>
       </c>
       <c r="F32" s="120" t="s">
-        <v>1024</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="25.5" customHeight="1">
       <c r="A33" s="102" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B33" s="57" t="s">
-        <v>909</v>
+        <v>897</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>910</v>
+        <v>898</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>911</v>
+        <v>899</v>
       </c>
       <c r="E33" s="33" t="s">
-        <v>912</v>
+        <v>900</v>
       </c>
       <c r="F33" s="117" t="s">
-        <v>913</v>
+        <v>901</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="30" customHeight="1">
       <c r="A34" s="107" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B34" s="64" t="s">
-        <v>915</v>
+        <v>903</v>
       </c>
       <c r="C34" s="36" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="D34" s="36" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="E34" s="36" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="F34" s="122" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="25.5" customHeight="1">
       <c r="A35" s="101" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B35" s="151" t="s">
-        <v>898</v>
+        <v>886</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="D35" s="10"/>
       <c r="E35" s="10" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="F35" s="116" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="25.5" customHeight="1">
       <c r="A36" s="167" t="s">
-        <v>941</v>
+        <v>929</v>
       </c>
       <c r="B36" s="168"/>
       <c r="C36" s="168"/>
@@ -16730,16 +16542,16 @@
     </row>
     <row r="37" spans="1:6" ht="25.5" customHeight="1">
       <c r="A37" s="101" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B37" s="56" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>20</v>
@@ -16750,219 +16562,219 @@
     </row>
     <row r="38" spans="1:6" ht="70" customHeight="1">
       <c r="A38" s="102" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B38" s="209" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="C38" s="33" t="s">
-        <v>1029</v>
+        <v>1017</v>
       </c>
       <c r="D38" s="33" t="s">
-        <v>1030</v>
+        <v>1018</v>
       </c>
       <c r="E38" s="35" t="s">
-        <v>1031</v>
+        <v>1019</v>
       </c>
       <c r="F38" s="117" t="s">
-        <v>1032</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="30" customHeight="1">
       <c r="A39" s="105" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B39" s="60" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="C39" s="61" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="D39" s="61" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="E39" s="61" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="F39" s="120" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="25.5" customHeight="1">
       <c r="A40" s="105" t="s">
+        <v>466</v>
+      </c>
+      <c r="B40" s="60" t="s">
         <v>474</v>
       </c>
-      <c r="B40" s="60" t="s">
-        <v>482</v>
-      </c>
       <c r="C40" s="61" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="D40" s="61" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="E40" s="61" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="F40" s="120" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="25.5" customHeight="1">
       <c r="A41" s="104" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B41" s="59" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="C41" s="47" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="D41" s="47" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="E41" s="47" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="F41" s="119" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="42" customHeight="1">
       <c r="A42" s="99" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B42" s="54" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="E42" s="15" t="s">
         <v>60</v>
       </c>
       <c r="F42" s="85" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="25.5" customHeight="1">
       <c r="A43" s="105" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B43" s="60" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="C43" s="61" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="D43" s="61" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="E43" s="61" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="F43" s="120" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="42" customHeight="1">
       <c r="A44" s="103" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B44" s="58" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="C44" s="39" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="D44" s="39" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="E44" s="39" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="F44" s="118" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="25.5" customHeight="1">
       <c r="A45" s="108" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B45" s="89" t="s">
-        <v>870</v>
+        <v>858</v>
       </c>
       <c r="C45" s="90" t="s">
-        <v>871</v>
+        <v>859</v>
       </c>
       <c r="D45" s="90" t="s">
-        <v>872</v>
+        <v>860</v>
       </c>
       <c r="E45" s="90" t="s">
-        <v>873</v>
+        <v>861</v>
       </c>
       <c r="F45" s="123" t="s">
-        <v>874</v>
+        <v>862</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="25.5" customHeight="1">
       <c r="A46" s="102" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B46" s="57" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="C46" s="33" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="D46" s="33" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="E46" s="35" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="F46" s="117" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="42" customHeight="1">
       <c r="A47" s="102" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B47" s="209" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="C47" s="33" t="s">
-        <v>932</v>
+        <v>920</v>
       </c>
       <c r="D47" s="33" t="s">
-        <v>933</v>
+        <v>921</v>
       </c>
       <c r="E47" s="35" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="F47" s="117" t="s">
-        <v>934</v>
+        <v>922</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="42" customHeight="1">
       <c r="A48" s="106" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B48" s="63" t="s">
-        <v>892</v>
+        <v>880</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="D48" s="20" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="F48" s="121" t="s">
         <v>71</v>
@@ -16970,167 +16782,167 @@
     </row>
     <row r="49" spans="1:6" ht="42" customHeight="1">
       <c r="A49" s="105" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B49" s="207" t="s">
-        <v>966</v>
+        <v>954</v>
       </c>
       <c r="C49" s="61" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="D49" s="61" t="s">
-        <v>967</v>
+        <v>955</v>
       </c>
       <c r="E49" s="61" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="F49" s="120" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="25.5" customHeight="1">
       <c r="A50" s="103" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B50" s="210" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="C50" s="39" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="D50" s="39" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
       <c r="E50" s="39" t="s">
-        <v>969</v>
+        <v>957</v>
       </c>
       <c r="F50" s="118" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="25.5" customHeight="1">
       <c r="A51" s="98" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B51" s="53" t="s">
-        <v>970</v>
+        <v>958</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>971</v>
+        <v>959</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>972</v>
+        <v>960</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>973</v>
+        <v>961</v>
       </c>
       <c r="F51" s="86" t="s">
-        <v>974</v>
+        <v>962</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="42" customHeight="1">
       <c r="A52" s="98" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B52" s="214" t="s">
-        <v>975</v>
+        <v>963</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>976</v>
+        <v>964</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>977</v>
+        <v>965</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>978</v>
+        <v>966</v>
       </c>
       <c r="F52" s="86" t="s">
-        <v>974</v>
+        <v>962</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="30" customHeight="1">
       <c r="A53" s="101" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B53" s="151" t="s">
-        <v>898</v>
+        <v>886</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>979</v>
+        <v>967</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="F53" s="116" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="25.5" customHeight="1">
       <c r="A54" s="109" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B54" s="65" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="C54" s="42" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="D54" s="42" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="E54" s="42" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="F54" s="124" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="25.5" customHeight="1">
       <c r="A55" s="103" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B55" s="58" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="C55" s="39" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="D55" s="39" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="E55" s="39" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="F55" s="118" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="25.5" customHeight="1">
       <c r="A56" s="103" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B56" s="210" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="C56" s="39" t="s">
-        <v>928</v>
+        <v>916</v>
       </c>
       <c r="D56" s="211" t="s">
-        <v>929</v>
+        <v>917</v>
       </c>
       <c r="E56" s="39" t="s">
-        <v>930</v>
+        <v>918</v>
       </c>
       <c r="F56" s="118" t="s">
-        <v>931</v>
+        <v>919</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="25.5" customHeight="1">
       <c r="A57" s="152" t="s">
-        <v>948</v>
+        <v>936</v>
       </c>
       <c r="B57" s="153"/>
       <c r="C57" s="153"/>
@@ -17140,19 +16952,19 @@
     </row>
     <row r="58" spans="1:6" ht="45" customHeight="1">
       <c r="A58" s="101" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="B58" s="56" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="F58" s="116" t="s">
         <v>28</v>
@@ -17160,265 +16972,265 @@
     </row>
     <row r="59" spans="1:6" ht="25.5" customHeight="1">
       <c r="A59" s="100" t="s">
+        <v>517</v>
+      </c>
+      <c r="B59" s="55" t="s">
+        <v>521</v>
+      </c>
+      <c r="C59" s="50" t="s">
+        <v>522</v>
+      </c>
+      <c r="D59" s="50" t="s">
+        <v>523</v>
+      </c>
+      <c r="E59" s="50" t="s">
+        <v>524</v>
+      </c>
+      <c r="F59" s="115" t="s">
         <v>525</v>
-      </c>
-      <c r="B59" s="55" t="s">
-        <v>529</v>
-      </c>
-      <c r="C59" s="50" t="s">
-        <v>530</v>
-      </c>
-      <c r="D59" s="50" t="s">
-        <v>531</v>
-      </c>
-      <c r="E59" s="50" t="s">
-        <v>532</v>
-      </c>
-      <c r="F59" s="115" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="30" customHeight="1">
       <c r="A60" s="100" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="B60" s="55" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="C60" s="50" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="D60" s="50" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="E60" s="50" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="F60" s="115" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="30" customHeight="1">
       <c r="A61" s="101" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="B61" s="56" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="F61" s="116" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="25.5" customHeight="1">
       <c r="A62" s="99" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="B62" s="54" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="D62" s="25" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F62" s="85" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="21.75" customHeight="1">
       <c r="A63" s="105" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="B63" s="60" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="C63" s="61" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="D63" s="61" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="E63" s="61" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="F63" s="120" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="25.5" customHeight="1">
       <c r="A64" s="105" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="B64" s="60" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="C64" s="61" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="D64" s="61" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="E64" s="61" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="F64" s="120" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="25.5" customHeight="1">
       <c r="A65" s="106" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="B65" s="63" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="D65" s="20" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="E65" s="20" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="F65" s="121" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="30" customHeight="1">
       <c r="A66" s="105" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="B66" s="60" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="C66" s="61" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="D66" s="61" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="E66" s="61" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="F66" s="120" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="30" customHeight="1">
       <c r="A67" s="110" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="B67" s="91" t="s">
-        <v>893</v>
+        <v>881</v>
       </c>
       <c r="C67" s="92" t="s">
-        <v>875</v>
+        <v>863</v>
       </c>
       <c r="D67" s="92" t="s">
-        <v>876</v>
+        <v>864</v>
       </c>
       <c r="E67" s="92" t="s">
-        <v>877</v>
+        <v>865</v>
       </c>
       <c r="F67" s="125" t="s">
-        <v>878</v>
+        <v>866</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="30" customHeight="1">
       <c r="A68" s="105" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="B68" s="60" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="C68" s="61" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="D68" s="61" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="E68" s="61" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="F68" s="120" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="25.5" customHeight="1">
       <c r="A69" s="107" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="B69" s="64" t="s">
-        <v>894</v>
+        <v>882</v>
       </c>
       <c r="C69" s="36" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="D69" s="36" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="E69" s="36" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="F69" s="122" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="25.5" customHeight="1">
       <c r="A70" s="109" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="B70" s="65" t="s">
-        <v>895</v>
+        <v>883</v>
       </c>
       <c r="C70" s="42" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="D70" s="44" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="E70" s="42" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="F70" s="124" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="30" customHeight="1">
       <c r="A71" s="101" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="B71" s="128" t="s">
-        <v>898</v>
+        <v>886</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="D71" s="10"/>
       <c r="E71" s="10" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="F71" s="116" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="30" customHeight="1">
       <c r="A72" s="152" t="s">
-        <v>942</v>
+        <v>930</v>
       </c>
       <c r="B72" s="153"/>
       <c r="C72" s="153"/>
@@ -17428,16 +17240,16 @@
     </row>
     <row r="73" spans="1:6" ht="30" customHeight="1">
       <c r="A73" s="101" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B73" s="56" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>20</v>
@@ -17448,219 +17260,219 @@
     </row>
     <row r="74" spans="1:6" ht="25.5" customHeight="1">
       <c r="A74" s="105" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B74" s="60" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="C74" s="61" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="D74" s="62" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="E74" s="61" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="F74" s="120" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="30" customHeight="1">
       <c r="A75" s="108" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B75" s="89" t="s">
-        <v>879</v>
+        <v>867</v>
       </c>
       <c r="C75" s="90" t="s">
-        <v>880</v>
+        <v>868</v>
       </c>
       <c r="D75" s="90" t="s">
-        <v>881</v>
+        <v>869</v>
       </c>
       <c r="E75" s="90" t="s">
-        <v>882</v>
+        <v>870</v>
       </c>
       <c r="F75" s="123" t="s">
-        <v>883</v>
+        <v>871</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="30" customHeight="1">
       <c r="A76" s="103" t="s">
+        <v>571</v>
+      </c>
+      <c r="B76" s="58" t="s">
+        <v>884</v>
+      </c>
+      <c r="C76" s="39" t="s">
         <v>579</v>
       </c>
-      <c r="B76" s="58" t="s">
-        <v>896</v>
-      </c>
-      <c r="C76" s="39" t="s">
-        <v>587</v>
-      </c>
       <c r="D76" s="39" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="E76" s="39" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="F76" s="118" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="42" customHeight="1">
       <c r="A77" s="104" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B77" s="59" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="C77" s="47" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="D77" s="47" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="E77" s="47" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="F77" s="119" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="25.5" customHeight="1">
       <c r="A78" s="105" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B78" s="60" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="C78" s="61" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="D78" s="61" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="E78" s="61" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="F78" s="120" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="30" customHeight="1">
       <c r="A79" s="98" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B79" s="53" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="F79" s="86" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="30" customHeight="1">
       <c r="A80" s="103" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B80" s="58" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="C80" s="39" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="D80" s="39" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="E80" s="39" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="F80" s="118" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="42" customHeight="1">
       <c r="A81" s="105" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B81" s="60" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="C81" s="61" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="D81" s="61" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="E81" s="61" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="F81" s="120" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="30" customHeight="1">
       <c r="A82" s="104" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B82" s="59" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="C82" s="47" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="D82" s="47" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="E82" s="47" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="F82" s="119" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="21.75" customHeight="1">
       <c r="A83" s="106" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B83" s="63" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="C83" s="20" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="D83" s="20" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="E83" s="20" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="F83" s="121" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="42" customHeight="1">
       <c r="A84" s="102" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B84" s="57" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="C84" s="33" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="D84" s="33" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="E84" s="33" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="F84" s="117" t="s">
         <v>33</v>
@@ -17668,59 +17480,59 @@
     </row>
     <row r="85" spans="1:6" ht="25.5" customHeight="1">
       <c r="A85" s="102" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B85" s="209" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="C85" s="33" t="s">
-        <v>925</v>
+        <v>913</v>
       </c>
       <c r="D85" s="33" t="s">
-        <v>926</v>
+        <v>914</v>
       </c>
       <c r="E85" s="33" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="F85" s="117" t="s">
-        <v>927</v>
+        <v>915</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="25.5" customHeight="1">
       <c r="A86" s="107" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B86" s="64" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="C86" s="36" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="D86" s="36" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="E86" s="36" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F86" s="122" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="30" customHeight="1">
       <c r="A87" s="101" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B87" s="56" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="F87" s="116" t="s">
         <v>33</v>
@@ -17728,127 +17540,127 @@
     </row>
     <row r="88" spans="1:6" ht="25.5" customHeight="1">
       <c r="A88" s="101" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B88" s="56" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="E88" s="10" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="F88" s="116" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="42" customHeight="1">
       <c r="A89" s="103" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B89" s="58" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="C89" s="39" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="D89" s="39" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="E89" s="39" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="F89" s="118" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="30" customHeight="1">
       <c r="A90" s="103" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B90" s="58" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="C90" s="39" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="D90" s="39" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="E90" s="39" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="F90" s="118" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="25.5" customHeight="1">
       <c r="A91" s="103" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B91" s="58" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="C91" s="39" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="D91" s="39" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="E91" s="39" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="F91" s="118" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="25.5" customHeight="1">
       <c r="A92" s="108" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B92" s="89" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="C92" s="90" t="s">
-        <v>884</v>
+        <v>872</v>
       </c>
       <c r="D92" s="95" t="s">
-        <v>885</v>
+        <v>873</v>
       </c>
       <c r="E92" s="90" t="s">
-        <v>886</v>
+        <v>874</v>
       </c>
       <c r="F92" s="123" t="s">
-        <v>887</v>
+        <v>875</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="30" customHeight="1">
       <c r="A93" s="108" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B93" s="208" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="C93" s="90" t="s">
-        <v>922</v>
+        <v>910</v>
       </c>
       <c r="D93" s="95" t="s">
-        <v>923</v>
+        <v>911</v>
       </c>
       <c r="E93" s="90" t="s">
-        <v>886</v>
+        <v>874</v>
       </c>
       <c r="F93" s="123" t="s">
-        <v>924</v>
+        <v>912</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="30" customHeight="1">
       <c r="A94" s="155" t="s">
-        <v>949</v>
+        <v>937</v>
       </c>
       <c r="B94" s="156"/>
       <c r="C94" s="156"/>
@@ -17858,17 +17670,17 @@
     </row>
     <row r="95" spans="1:6" ht="42" customHeight="1">
       <c r="A95" s="101" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="B95" s="56" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="D95" s="10"/>
       <c r="E95" s="10" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="F95" s="116" t="s">
         <v>33</v>
@@ -17876,325 +17688,325 @@
     </row>
     <row r="96" spans="1:6" ht="25.5" customHeight="1">
       <c r="A96" s="100" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="B96" s="55" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="C96" s="50" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="D96" s="50" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="E96" s="50" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="F96" s="115" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="45" customHeight="1">
       <c r="A97" s="100" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="B97" s="55" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="C97" s="50" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="D97" s="50" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="E97" s="50" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="F97" s="115" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="30" customHeight="1">
       <c r="A98" s="101" t="s">
+        <v>636</v>
+      </c>
+      <c r="B98" s="56" t="s">
+        <v>531</v>
+      </c>
+      <c r="C98" s="10" t="s">
         <v>644</v>
       </c>
-      <c r="B98" s="56" t="s">
-        <v>539</v>
-      </c>
-      <c r="C98" s="10" t="s">
-        <v>652</v>
-      </c>
       <c r="D98" s="10" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="F98" s="116" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="21.75" customHeight="1">
       <c r="A99" s="99" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="B99" s="54" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="D99" s="15" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="E99" s="15" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F99" s="85" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="25.5" customHeight="1">
       <c r="A100" s="105" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="B100" s="60" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="C100" s="61" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="D100" s="61" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="E100" s="61" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="F100" s="120" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="42" customHeight="1">
       <c r="A101" s="105" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="B101" s="60" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="C101" s="61" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="D101" s="61" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="E101" s="61" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="F101" s="120" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="30" customHeight="1">
       <c r="A102" s="105" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="B102" s="60" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="C102" s="61" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="D102" s="61" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="E102" s="61" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="F102" s="120" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="45" customHeight="1">
       <c r="A103" s="106" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="B103" s="63" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="C103" s="20" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="D103" s="20" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="E103" s="20" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="F103" s="121" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="25.5" customHeight="1">
       <c r="A104" s="105" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="B104" s="60" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="C104" s="61" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="D104" s="61" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="E104" s="61" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F104" s="120" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="42" customHeight="1">
       <c r="A105" s="105" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="B105" s="207" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="C105" s="61" t="s">
-        <v>920</v>
+        <v>908</v>
       </c>
       <c r="D105" s="61" t="s">
-        <v>921</v>
+        <v>909</v>
       </c>
       <c r="E105" s="61" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="F105" s="120" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="130" customHeight="1">
       <c r="A106" s="105" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="B106" s="207" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="C106" s="61" t="s">
-        <v>1056</v>
+        <v>1043</v>
       </c>
       <c r="D106" s="61" t="s">
-        <v>1057</v>
+        <v>1044</v>
       </c>
       <c r="E106" s="61" t="s">
-        <v>1058</v>
+        <v>1045</v>
       </c>
       <c r="F106" s="120" t="s">
-        <v>1059</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="30" customHeight="1">
       <c r="A107" s="109" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="B107" s="65" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="C107" s="42" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="D107" s="42" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="E107" s="42" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="F107" s="124" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="25.5" customHeight="1">
       <c r="A108" s="111" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="B108" s="93" t="s">
-        <v>888</v>
+        <v>876</v>
       </c>
       <c r="C108" s="94" t="s">
-        <v>889</v>
+        <v>877</v>
       </c>
       <c r="D108" s="94" t="s">
-        <v>890</v>
+        <v>878</v>
       </c>
       <c r="E108" s="94" t="s">
-        <v>891</v>
+        <v>879</v>
       </c>
       <c r="F108" s="126" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="25.5" customHeight="1">
       <c r="A109" s="101" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="B109" s="128" t="s">
-        <v>898</v>
+        <v>886</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>897</v>
+        <v>885</v>
       </c>
       <c r="D109" s="10"/>
       <c r="E109" s="10" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="F109" s="116" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="30" customHeight="1">
       <c r="A110" s="102" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="B110" s="57" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="C110" s="33" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="D110" s="33" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="E110" s="33" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="F110" s="117" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="25.5" customHeight="1">
       <c r="A111" s="103" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="B111" s="58" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="C111" s="39" t="s">
-        <v>943</v>
+        <v>931</v>
       </c>
       <c r="D111" s="39" t="s">
-        <v>944</v>
+        <v>932</v>
       </c>
       <c r="E111" s="39" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="F111" s="118" t="s">
-        <v>945</v>
+        <v>933</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="42" customHeight="1">
       <c r="A112" s="155" t="s">
-        <v>950</v>
+        <v>938</v>
       </c>
       <c r="B112" s="156"/>
       <c r="C112" s="156"/>
@@ -18204,16 +18016,16 @@
     </row>
     <row r="113" spans="1:6" ht="45" customHeight="1">
       <c r="A113" s="101" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="B113" s="56" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>20</v>
@@ -18224,327 +18036,327 @@
     </row>
     <row r="114" spans="1:6" ht="25.5" customHeight="1">
       <c r="A114" s="105" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="B114" s="60" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="C114" s="61" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="D114" s="61" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="E114" s="61" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="F114" s="120" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="21.75" customHeight="1">
       <c r="A115" s="105" t="s">
+        <v>679</v>
+      </c>
+      <c r="B115" s="60" t="s">
+        <v>684</v>
+      </c>
+      <c r="C115" s="61" t="s">
+        <v>685</v>
+      </c>
+      <c r="D115" s="61" t="s">
+        <v>686</v>
+      </c>
+      <c r="E115" s="61" t="s">
         <v>687</v>
       </c>
-      <c r="B115" s="60" t="s">
-        <v>692</v>
-      </c>
-      <c r="C115" s="61" t="s">
-        <v>693</v>
-      </c>
-      <c r="D115" s="61" t="s">
-        <v>694</v>
-      </c>
-      <c r="E115" s="61" t="s">
-        <v>695</v>
-      </c>
       <c r="F115" s="120" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="25.5" customHeight="1">
       <c r="A116" s="105" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="B116" s="60" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="C116" s="61" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="D116" s="61" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="E116" s="61" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="F116" s="120" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="25.5" customHeight="1">
       <c r="A117" s="105" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="B117" s="207" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="C117" s="61" t="s">
-        <v>916</v>
+        <v>904</v>
       </c>
       <c r="D117" s="61" t="s">
-        <v>917</v>
+        <v>905</v>
       </c>
       <c r="E117" s="61" t="s">
-        <v>918</v>
+        <v>906</v>
       </c>
       <c r="F117" s="120" t="s">
-        <v>919</v>
+        <v>907</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="30" customHeight="1">
       <c r="A118" s="98" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="B118" s="53" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="F118" s="86" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="25.5" customHeight="1">
       <c r="A119" s="102" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="B119" s="57" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="C119" s="33" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="D119" s="33" t="s">
-        <v>705</v>
+        <v>697</v>
       </c>
       <c r="E119" s="33" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="F119" s="117" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="30" customHeight="1">
       <c r="A120" s="105" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="B120" s="60" t="s">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="C120" s="61" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="D120" s="61" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
       <c r="E120" s="61" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="F120" s="120" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="25.5" customHeight="1">
       <c r="A121" s="106" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="B121" s="63" t="s">
-        <v>711</v>
+        <v>703</v>
       </c>
       <c r="C121" s="20" t="s">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="D121" s="20" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="E121" s="20" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="F121" s="121" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="110" customHeight="1">
       <c r="A122" s="109" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="B122" s="65" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="C122" s="42" t="s">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="D122" s="42" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="E122" s="42" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
       <c r="F122" s="124" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="42" customHeight="1">
       <c r="A123" s="99" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="B123" s="54" t="s">
-        <v>717</v>
+        <v>709</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>1037</v>
+        <v>1024</v>
       </c>
       <c r="D123" s="15" t="s">
-        <v>1038</v>
+        <v>1025</v>
       </c>
       <c r="E123" s="15" t="s">
-        <v>1039</v>
+        <v>1026</v>
       </c>
       <c r="F123" s="85" t="s">
-        <v>1040</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="30" customHeight="1">
       <c r="A124" s="103" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="B124" s="58" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
       <c r="C124" s="39" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="D124" s="39" t="s">
-        <v>720</v>
+        <v>712</v>
       </c>
       <c r="E124" s="39" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="F124" s="118" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="28">
       <c r="A125" s="101" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="B125" s="56" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="F125" s="116" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="28">
       <c r="A126" s="103" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="B126" s="58" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="C126" s="39" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="D126" s="39" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="E126" s="39" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="F126" s="118" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="150" customHeight="1">
       <c r="A127" s="103" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="B127" s="58" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="C127" s="39" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="D127" s="39" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="E127" s="39" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="F127" s="118" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="238">
       <c r="A128" s="103" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="B128" s="210" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="C128" s="39" t="s">
-        <v>1046</v>
+        <v>1033</v>
       </c>
       <c r="D128" s="39" t="s">
-        <v>1047</v>
+        <v>1034</v>
       </c>
       <c r="E128" s="39" t="s">
-        <v>1048</v>
+        <v>1035</v>
       </c>
       <c r="F128" s="118" t="s">
-        <v>1049</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="31">
       <c r="A129" s="104" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="B129" s="59" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="C129" s="47" t="s">
-        <v>946</v>
+        <v>934</v>
       </c>
       <c r="D129" s="47" t="s">
-        <v>947</v>
+        <v>935</v>
       </c>
       <c r="E129" s="47" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="F129" s="119" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="158" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
       <c r="B130" s="159"/>
       <c r="C130" s="159"/>
@@ -18554,19 +18366,19 @@
     </row>
     <row r="131" spans="1:6" ht="28">
       <c r="A131" s="101" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="B131" s="56" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="D131" s="10" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
       <c r="E131" s="10" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="F131" s="116" t="s">
         <v>37</v>
@@ -18574,162 +18386,162 @@
     </row>
     <row r="132" spans="1:6" ht="28">
       <c r="A132" s="100" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="B132" s="55" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="C132" s="50" t="s">
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="D132" s="50" t="s">
-        <v>737</v>
+        <v>729</v>
       </c>
       <c r="E132" s="50" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="F132" s="115" t="s">
-        <v>738</v>
+        <v>730</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="28">
       <c r="A133" s="100" t="s">
+        <v>724</v>
+      </c>
+      <c r="B133" s="55" t="s">
+        <v>731</v>
+      </c>
+      <c r="C133" s="50" t="s">
         <v>732</v>
       </c>
-      <c r="B133" s="55" t="s">
-        <v>739</v>
-      </c>
-      <c r="C133" s="50" t="s">
-        <v>740</v>
-      </c>
       <c r="D133" s="50" t="s">
-        <v>741</v>
+        <v>733</v>
       </c>
       <c r="E133" s="50" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
       <c r="F133" s="115" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="28">
       <c r="A134" s="100" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="B134" s="55" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="C134" s="50" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="D134" s="50" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
       <c r="E134" s="50" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="F134" s="115" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="28">
       <c r="A135" s="99" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="B135" s="54" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
       <c r="C135" s="15" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
       <c r="D135" s="15" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="E135" s="15" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="F135" s="85" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="28">
       <c r="A136" s="98" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="B136" s="53" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="F136" s="114" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
     </row>
     <row r="137" spans="1:6" ht="28">
       <c r="A137" s="99" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="B137" s="54" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="C137" s="15" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="D137" s="15" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="E137" s="15" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="F137" s="113" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="28">
       <c r="A138" s="98" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="B138" s="53" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>762</v>
+        <v>754</v>
       </c>
       <c r="F138" s="114" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="29" thickBot="1">
       <c r="A139" s="112" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="B139" s="96" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="C139" s="97" t="s">
-        <v>763</v>
+        <v>755</v>
       </c>
       <c r="D139" s="97" t="s">
-        <v>764</v>
+        <v>756</v>
       </c>
       <c r="E139" s="97" t="s">
-        <v>765</v>
+        <v>757</v>
       </c>
       <c r="F139" s="127" t="s">
-        <v>766</v>
+        <v>758</v>
       </c>
     </row>
   </sheetData>
@@ -18755,7 +18567,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -18767,7 +18579,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
       <c r="A1" s="177" t="s">
-        <v>1102</v>
+        <v>1131</v>
       </c>
       <c r="B1" s="177"/>
       <c r="C1" s="177"/>
@@ -18856,7 +18668,7 @@
         <v>61</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>1020</v>
+        <v>1008</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>62</v>
@@ -18873,16 +18685,16 @@
         <v>52</v>
       </c>
       <c r="B9" s="69" t="s">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="C9" s="67" t="s">
-        <v>768</v>
+        <v>760</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>769</v>
+        <v>761</v>
       </c>
       <c r="E9" s="68" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="30" customHeight="1">
@@ -18890,13 +18702,13 @@
         <v>52</v>
       </c>
       <c r="B10" s="69" t="s">
-        <v>770</v>
+        <v>762</v>
       </c>
       <c r="C10" s="67" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>771</v>
+        <v>763</v>
       </c>
       <c r="E10" s="68" t="s">
         <v>60</v>
@@ -18941,30 +18753,30 @@
         <v>65</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>1014</v>
+        <v>1002</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>1009</v>
+        <v>997</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>1015</v>
+        <v>1003</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>1016</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="42" customHeight="1">
       <c r="A14" s="20" t="s">
-        <v>1017</v>
+        <v>1005</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>1018</v>
+        <v>1006</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>1013</v>
+        <v>1001</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>1019</v>
+        <v>1007</v>
       </c>
       <c r="E14" s="23" t="s">
         <v>69</v>
@@ -18972,19 +18784,19 @@
     </row>
     <row r="15" spans="1:5" ht="56" customHeight="1">
       <c r="A15" s="20" t="s">
-        <v>1025</v>
+        <v>1013</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>1026</v>
+        <v>1014</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>1024</v>
+        <v>1012</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>1027</v>
+        <v>1015</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>1028</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="70" customHeight="1">
@@ -18992,33 +18804,33 @@
         <v>87</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>1033</v>
+        <v>1104</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>1034</v>
+        <v>1021</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>1035</v>
+        <v>1022</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>1036</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="62" customHeight="1">
       <c r="A17" s="20" t="s">
-        <v>1084</v>
+        <v>1070</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>1093</v>
+        <v>1105</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>1094</v>
+        <v>1077</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>1095</v>
+        <v>1078</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="62" customHeight="1">
@@ -19026,16 +18838,16 @@
         <v>52</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>1096</v>
+        <v>1106</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>1097</v>
+        <v>1079</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>1098</v>
+        <v>1080</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>1085</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="62" customHeight="1">
@@ -19043,16 +18855,16 @@
         <v>52</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>1099</v>
+        <v>1107</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>1100</v>
+        <v>1081</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>1101</v>
+        <v>1082</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>1085</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="30" customHeight="1"/>
@@ -19093,7 +18905,7 @@
         <v>33</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>1078</v>
+        <v>1065</v>
       </c>
       <c r="E23" s="18" t="s">
         <v>76</v>
@@ -19144,7 +18956,7 @@
         <v>89</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>1080</v>
+        <v>1067</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>90</v>
@@ -19155,16 +18967,16 @@
         <v>91</v>
       </c>
       <c r="B27" s="16" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C27" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="D27" s="15" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E27" s="18" t="s">
         <v>93</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>1079</v>
-      </c>
-      <c r="E27" s="18" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="27.75" customHeight="1">
@@ -19172,16 +18984,16 @@
         <v>87</v>
       </c>
       <c r="B28" s="66" t="s">
-        <v>772</v>
+        <v>764</v>
       </c>
       <c r="C28" s="67" t="s">
-        <v>773</v>
+        <v>765</v>
       </c>
       <c r="D28" s="66" t="s">
-        <v>774</v>
+        <v>766</v>
       </c>
       <c r="E28" s="68" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="30" customHeight="1">
@@ -19189,16 +19001,16 @@
         <v>65</v>
       </c>
       <c r="B29" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="C29" s="22" t="s">
+      <c r="D29" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="D29" s="20" t="s">
+      <c r="E29" s="23" t="s">
         <v>97</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="62" customHeight="1">
@@ -19206,16 +19018,16 @@
         <v>82</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>1086</v>
+        <v>1109</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>1087</v>
+        <v>1072</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>1088</v>
+        <v>1073</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="62" customHeight="1">
@@ -19223,22 +19035,22 @@
         <v>82</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>1089</v>
+        <v>1110</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>1090</v>
+        <v>1074</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>1091</v>
+        <v>1075</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>1092</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="27.75" customHeight="1"/>
     <row r="33" spans="1:5" ht="30" customHeight="1">
       <c r="A33" s="176" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B33" s="176"/>
       <c r="C33" s="176"/>
@@ -19267,16 +19079,16 @@
         <v>48</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C35" s="14" t="s">
         <v>37</v>
       </c>
       <c r="D35" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E35" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -19284,16 +19096,16 @@
         <v>52</v>
       </c>
       <c r="B36" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C36" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="D36" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="D36" s="15" t="s">
+      <c r="E36" s="18" t="s">
         <v>105</v>
-      </c>
-      <c r="E36" s="18" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -19301,16 +19113,16 @@
         <v>52</v>
       </c>
       <c r="B37" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C37" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="D37" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="E37" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="28">
@@ -19318,16 +19130,16 @@
         <v>82</v>
       </c>
       <c r="B38" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="C38" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="D38" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="D38" s="25" t="s">
+      <c r="E38" s="18" t="s">
         <v>113</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="28">
@@ -19335,67 +19147,67 @@
         <v>87</v>
       </c>
       <c r="B39" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="C39" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="D39" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="E39" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="110" customHeight="1">
       <c r="A40" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="C40" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="D40" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="E40" s="18" t="s">
         <v>122</v>
-      </c>
-      <c r="E40" s="18" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="130" customHeight="1">
       <c r="A41" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B41" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="C41" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="D41" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="D41" s="24" t="s">
-        <v>127</v>
-      </c>
       <c r="E41" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="150" customHeight="1">
       <c r="A42" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="B42" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="B42" s="19" t="s">
+      <c r="C42" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="D42" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="E42" s="18" t="s">
         <v>131</v>
-      </c>
-      <c r="E42" s="18" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="28">
@@ -19403,16 +19215,16 @@
         <v>65</v>
       </c>
       <c r="B43" s="73" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="C43" s="71" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="D43" s="70" t="s">
-        <v>776</v>
+        <v>768</v>
       </c>
       <c r="E43" s="72" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="28">
@@ -19420,50 +19232,50 @@
         <v>65</v>
       </c>
       <c r="B44" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="C44" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="C44" s="22" t="s">
+      <c r="D44" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="D44" s="20" t="s">
-        <v>135</v>
-      </c>
       <c r="E44" s="23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="140">
       <c r="A45" s="20" t="s">
-        <v>1041</v>
+        <v>1028</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>1042</v>
+        <v>1029</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>1043</v>
+        <v>1030</v>
       </c>
       <c r="D45" s="20" t="s">
-        <v>1044</v>
+        <v>1031</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>1045</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="154">
       <c r="A46" s="20" t="s">
-        <v>1041</v>
+        <v>1028</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>1060</v>
+        <v>1047</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>1061</v>
+        <v>1048</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>1062</v>
+        <v>1049</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="154">
@@ -19471,16 +19283,16 @@
         <v>65</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>1050</v>
+        <v>1037</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>1051</v>
+        <v>1038</v>
       </c>
       <c r="D47" s="20" t="s">
-        <v>1052</v>
+        <v>1039</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="168">
@@ -19488,16 +19300,16 @@
         <v>65</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>1053</v>
+        <v>1040</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>1054</v>
+        <v>1041</v>
       </c>
       <c r="D48" s="20" t="s">
-        <v>1055</v>
+        <v>1042</v>
       </c>
       <c r="E48" s="23" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="62" customHeight="1">
@@ -19505,35 +19317,53 @@
         <v>82</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>1081</v>
+        <v>1111</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>1082</v>
+        <v>1068</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>1083</v>
+        <v>1069</v>
       </c>
       <c r="E49" s="23" t="s">
-        <v>1077</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="62" customHeight="1">
       <c r="A50" s="20" t="s">
-        <v>1084</v>
+        <v>1070</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>1109</v>
+        <v>1087</v>
       </c>
       <c r="D50" s="20" t="s">
-        <v>1110</v>
+        <v>1088</v>
       </c>
       <c r="E50" s="23" t="s">
         <v>64</v>
       </c>
     </row>
+    <row r="51" spans="1:5" ht="62" customHeight="1">
+      <c r="A51" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C51" s="22" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D51" s="20" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E51" s="23" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="62" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:E1"/>
@@ -19551,7 +19381,7 @@
   <sheetPr>
     <tabColor rgb="FFE36C09"/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -19564,7 +19394,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="27.75" customHeight="1">
       <c r="A1" s="191" t="s">
-        <v>1103</v>
+        <v>1083</v>
       </c>
       <c r="B1" s="192"/>
       <c r="C1" s="192"/>
@@ -19574,7 +19404,7 @@
     </row>
     <row r="2" spans="1:6" ht="45" customHeight="1">
       <c r="A2" s="194" t="s">
-        <v>1104</v>
+        <v>1084</v>
       </c>
       <c r="B2" s="195"/>
       <c r="C2" s="195"/>
@@ -19584,19 +19414,19 @@
     </row>
     <row r="3" spans="1:6" ht="19.5" customHeight="1">
       <c r="A3" s="77" t="s">
+        <v>135</v>
+      </c>
+      <c r="B3" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="C3" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="D3" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="E3" s="26" t="s">
         <v>139</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>140</v>
       </c>
       <c r="F3" s="83" t="s">
         <v>23</v>
@@ -19604,7 +19434,7 @@
     </row>
     <row r="4" spans="1:6" ht="19.5" customHeight="1">
       <c r="A4" s="188" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B4" s="189"/>
       <c r="C4" s="189"/>
@@ -19614,39 +19444,39 @@
     </row>
     <row r="5" spans="1:6" ht="30" customHeight="1">
       <c r="A5" s="78" t="s">
+        <v>141</v>
+      </c>
+      <c r="B5" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="C5" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="27" t="s">
         <v>144</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="E5" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="84" t="s">
         <v>146</v>
-      </c>
-      <c r="F5" s="84" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30" customHeight="1">
       <c r="A6" s="79" t="s">
+        <v>147</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="C6" s="16" t="s">
         <v>149</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>150</v>
       </c>
       <c r="D6" s="18" t="s">
         <v>51</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F6" s="85" t="s">
         <v>28</v>
@@ -19654,19 +19484,19 @@
     </row>
     <row r="7" spans="1:6" ht="30" customHeight="1">
       <c r="A7" s="80" t="s">
+        <v>151</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="D7" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>155</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>156</v>
       </c>
       <c r="F7" s="86" t="s">
         <v>28</v>
@@ -19674,47 +19504,47 @@
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1">
       <c r="A8" s="81" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="B8" s="75">
         <v>4.5</v>
       </c>
       <c r="C8" s="76" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="D8" s="75" t="s">
-        <v>779</v>
+        <v>771</v>
       </c>
       <c r="E8" s="76" t="s">
-        <v>780</v>
+        <v>772</v>
       </c>
       <c r="F8" s="87" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1">
       <c r="A9" s="82" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="B9" s="68">
         <v>4.5</v>
       </c>
       <c r="C9" s="66" t="s">
-        <v>835</v>
+        <v>1114</v>
       </c>
       <c r="D9" s="68" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E9" s="66" t="s">
-        <v>1065</v>
+        <v>1052</v>
       </c>
       <c r="F9" s="88" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="19.5" customHeight="1">
       <c r="A10" s="188" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B10" s="189"/>
       <c r="C10" s="189"/>
@@ -19724,187 +19554,187 @@
     </row>
     <row r="11" spans="1:6" ht="42" customHeight="1">
       <c r="A11" s="78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D11" s="27" t="s">
         <v>56</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>1004</v>
+        <v>992</v>
       </c>
       <c r="F11" s="84" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1">
       <c r="A12" s="79" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C12" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D12" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="E12" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="F12" s="85" t="s">
         <v>162</v>
-      </c>
-      <c r="F12" s="85" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1">
       <c r="A13" s="80" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C13" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="E13" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="F13" s="86" t="s">
         <v>166</v>
-      </c>
-      <c r="F13" s="86" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1">
       <c r="A14" s="81" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="B14" s="75">
         <v>4.8</v>
       </c>
       <c r="C14" s="76" t="s">
-        <v>782</v>
+        <v>774</v>
       </c>
       <c r="D14" s="75" t="s">
         <v>64</v>
       </c>
       <c r="E14" s="76" t="s">
-        <v>783</v>
+        <v>775</v>
       </c>
       <c r="F14" s="87" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="30" customHeight="1">
       <c r="A15" s="82" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="B15" s="68">
         <v>4.5999999999999996</v>
       </c>
       <c r="C15" s="66" t="s">
-        <v>815</v>
+        <v>805</v>
       </c>
       <c r="D15" s="68" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E15" s="66" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="F15" s="88" t="s">
-        <v>817</v>
+        <v>807</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="30" customHeight="1">
       <c r="A16" s="82" t="s">
-        <v>859</v>
+        <v>847</v>
       </c>
       <c r="B16" s="220" t="s">
-        <v>998</v>
+        <v>986</v>
       </c>
       <c r="C16" s="66" t="s">
-        <v>999</v>
+        <v>987</v>
       </c>
       <c r="D16" s="68" t="s">
-        <v>779</v>
+        <v>771</v>
       </c>
       <c r="E16" s="66" t="s">
-        <v>1000</v>
+        <v>988</v>
       </c>
       <c r="F16" s="88" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1">
       <c r="A17" s="82" t="s">
-        <v>862</v>
+        <v>850</v>
       </c>
       <c r="B17" s="220" t="s">
-        <v>1001</v>
+        <v>989</v>
       </c>
       <c r="C17" s="66" t="s">
-        <v>1002</v>
+        <v>990</v>
       </c>
       <c r="D17" s="68" t="s">
-        <v>987</v>
+        <v>975</v>
       </c>
       <c r="E17" s="66" t="s">
-        <v>1003</v>
+        <v>991</v>
       </c>
       <c r="F17" s="88" t="s">
-        <v>817</v>
+        <v>807</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="44" customHeight="1">
       <c r="A18" s="223" t="s">
-        <v>980</v>
+        <v>968</v>
       </c>
       <c r="B18" s="224" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C18" s="225" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D18" s="226" t="s">
-        <v>1085</v>
+        <v>1071</v>
       </c>
       <c r="E18" s="225" t="s">
-        <v>1115</v>
+        <v>1092</v>
       </c>
       <c r="F18" s="227" t="s">
-        <v>1097</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="44" customHeight="1">
       <c r="A19" s="223" t="s">
-        <v>984</v>
+        <v>972</v>
       </c>
       <c r="B19" s="224" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C19" s="225" t="s">
         <v>1116</v>
       </c>
       <c r="D19" s="226" t="s">
-        <v>1085</v>
+        <v>1071</v>
       </c>
       <c r="E19" s="225" t="s">
-        <v>1117</v>
+        <v>1093</v>
       </c>
       <c r="F19" s="227" t="s">
-        <v>1100</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30" customHeight="1">
       <c r="A20" s="188" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B20" s="189"/>
       <c r="C20" s="189"/>
@@ -19914,107 +19744,107 @@
     </row>
     <row r="21" spans="1:6" ht="30" customHeight="1">
       <c r="A21" s="78" t="s">
+        <v>168</v>
+      </c>
+      <c r="B21" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="B21" s="27" t="s">
-        <v>170</v>
-      </c>
       <c r="C21" s="28" t="s">
-        <v>1106</v>
+        <v>1085</v>
       </c>
       <c r="D21" s="27" t="s">
         <v>64</v>
       </c>
       <c r="E21" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="F21" s="84" t="s">
         <v>171</v>
-      </c>
-      <c r="F21" s="84" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="19.5" customHeight="1">
       <c r="A22" s="79" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D22" s="18" t="s">
         <v>60</v>
       </c>
       <c r="E22" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="F22" s="85" t="s">
         <v>174</v>
-      </c>
-      <c r="F22" s="85" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1">
       <c r="A23" s="80" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="D23" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="E23" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="F23" s="86" t="s">
         <v>179</v>
-      </c>
-      <c r="F23" s="86" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1">
       <c r="A24" s="81" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B24" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C24" s="76" t="s">
-        <v>836</v>
+        <v>825</v>
       </c>
       <c r="D24" s="75" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="E24" s="76" t="s">
-        <v>837</v>
+        <v>826</v>
       </c>
       <c r="F24" s="87" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1">
       <c r="A25" s="82" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="B25" s="68">
         <v>4.3</v>
       </c>
       <c r="C25" s="66" t="s">
-        <v>785</v>
+        <v>777</v>
       </c>
       <c r="D25" s="68" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="E25" s="66" t="s">
-        <v>786</v>
+        <v>778</v>
       </c>
       <c r="F25" s="88" t="s">
-        <v>787</v>
+        <v>779</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="30" customHeight="1">
       <c r="A26" s="188" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B26" s="189"/>
       <c r="C26" s="189"/>
@@ -20024,107 +19854,107 @@
     </row>
     <row r="27" spans="1:6" ht="30" customHeight="1">
       <c r="A27" s="78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C27" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D27" s="27" t="s">
         <v>182</v>
       </c>
-      <c r="D27" s="27" t="s">
+      <c r="E27" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="F27" s="84" t="s">
         <v>184</v>
-      </c>
-      <c r="F27" s="84" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="19.5" customHeight="1">
       <c r="A28" s="79" t="s">
+        <v>147</v>
+      </c>
+      <c r="B28" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="B28" s="18" t="s">
-        <v>149</v>
-      </c>
       <c r="C28" s="16" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>1053</v>
+      </c>
+      <c r="F28" s="85" t="s">
         <v>186</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>1066</v>
-      </c>
-      <c r="F28" s="85" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="30" customHeight="1">
       <c r="A29" s="80" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="F29" s="86" t="s">
         <v>190</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="F29" s="86" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="30" customHeight="1">
       <c r="A30" s="81" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="B30" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C30" s="76" t="s">
-        <v>788</v>
+        <v>1118</v>
       </c>
       <c r="D30" s="75" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E30" s="76" t="s">
-        <v>1067</v>
+        <v>1054</v>
       </c>
       <c r="F30" s="87" t="s">
-        <v>789</v>
+        <v>780</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="30" customHeight="1">
       <c r="A31" s="82" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="B31" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C31" s="66" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
       <c r="D31" s="68" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E31" s="66" t="s">
-        <v>819</v>
+        <v>809</v>
       </c>
       <c r="F31" s="88" t="s">
-        <v>820</v>
+        <v>810</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="30" customHeight="1">
       <c r="A32" s="188" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B32" s="189"/>
       <c r="C32" s="189"/>
@@ -20134,107 +19964,107 @@
     </row>
     <row r="33" spans="1:6" ht="30" customHeight="1">
       <c r="A33" s="78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C33" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="D33" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F33" s="84" t="s">
         <v>194</v>
-      </c>
-      <c r="D33" s="27" t="s">
-        <v>165</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="F33" s="84" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="19.5" customHeight="1">
       <c r="A34" s="79" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D34" s="18" t="s">
         <v>60</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F34" s="85" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="30" customHeight="1">
       <c r="A35" s="80" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B35" s="4">
         <v>4.3</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>838</v>
+        <v>827</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>803</v>
+        <v>793</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>839</v>
+        <v>828</v>
       </c>
       <c r="F35" s="86" t="s">
-        <v>823</v>
+        <v>813</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="30" customHeight="1">
       <c r="A36" s="81" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="B36" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C36" s="76" t="s">
-        <v>790</v>
+        <v>781</v>
       </c>
       <c r="D36" s="75" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E36" s="76" t="s">
-        <v>791</v>
+        <v>782</v>
       </c>
       <c r="F36" s="87" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="30" customHeight="1">
       <c r="A37" s="82" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="B37" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C37" s="66" t="s">
-        <v>821</v>
+        <v>811</v>
       </c>
       <c r="D37" s="68" t="s">
         <v>60</v>
       </c>
       <c r="E37" s="66" t="s">
-        <v>822</v>
+        <v>812</v>
       </c>
       <c r="F37" s="88" t="s">
-        <v>823</v>
+        <v>813</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="30" customHeight="1">
       <c r="A38" s="185" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B38" s="186"/>
       <c r="C38" s="186"/>
@@ -20244,59 +20074,59 @@
     </row>
     <row r="39" spans="1:6" ht="30" customHeight="1">
       <c r="A39" s="78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B39" s="27">
         <v>4.5</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>847</v>
+        <v>835</v>
       </c>
       <c r="D39" s="27" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E39" s="28" t="s">
-        <v>848</v>
+        <v>836</v>
       </c>
       <c r="F39" s="84" t="s">
-        <v>849</v>
+        <v>837</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="19.5" customHeight="1">
       <c r="A40" s="79" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>203</v>
+        <v>1119</v>
       </c>
       <c r="D40" s="18" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>1073</v>
+        <v>1060</v>
       </c>
       <c r="F40" s="85" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="30" customHeight="1">
       <c r="A41" s="80" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B41" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="E41" s="5" t="s">
         <v>205</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>208</v>
       </c>
       <c r="F41" s="86" t="s">
         <v>89</v>
@@ -20304,19 +20134,19 @@
     </row>
     <row r="42" spans="1:6" ht="30" customHeight="1">
       <c r="A42" s="81" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="B42" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C42" s="76" t="s">
-        <v>792</v>
+        <v>783</v>
       </c>
       <c r="D42" s="75" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E42" s="76" t="s">
-        <v>793</v>
+        <v>784</v>
       </c>
       <c r="F42" s="87" t="s">
         <v>89</v>
@@ -20324,19 +20154,19 @@
     </row>
     <row r="43" spans="1:6" ht="30" customHeight="1">
       <c r="A43" s="82" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="B43" s="68">
         <v>4.3</v>
       </c>
       <c r="C43" s="66" t="s">
-        <v>824</v>
+        <v>814</v>
       </c>
       <c r="D43" s="68" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E43" s="66" t="s">
-        <v>825</v>
+        <v>815</v>
       </c>
       <c r="F43" s="88" t="s">
         <v>89</v>
@@ -20344,7 +20174,7 @@
     </row>
     <row r="44" spans="1:6" ht="30" customHeight="1">
       <c r="A44" s="185" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B44" s="186"/>
       <c r="C44" s="186"/>
@@ -20354,59 +20184,59 @@
     </row>
     <row r="45" spans="1:6" ht="30" customHeight="1">
       <c r="A45" s="78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>1063</v>
+        <v>1050</v>
       </c>
       <c r="D45" s="27" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>1064</v>
+        <v>1051</v>
       </c>
       <c r="F45" s="84" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="19.5" customHeight="1">
       <c r="A46" s="79" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C46" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="D46" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="E46" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="F46" s="85" t="s">
         <v>212</v>
-      </c>
-      <c r="D46" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="E46" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="F46" s="85" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="30" customHeight="1">
       <c r="A47" s="80" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>216</v>
+        <v>1120</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>1068</v>
+        <v>1055</v>
       </c>
       <c r="F47" s="86" t="s">
         <v>33</v>
@@ -20414,67 +20244,67 @@
     </row>
     <row r="48" spans="1:6" ht="30" customHeight="1">
       <c r="A48" s="81" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="B48" s="75">
         <v>4.5</v>
       </c>
       <c r="C48" s="76" t="s">
-        <v>794</v>
+        <v>1121</v>
       </c>
       <c r="D48" s="75" t="s">
         <v>86</v>
       </c>
       <c r="E48" s="76" t="s">
-        <v>1074</v>
+        <v>1061</v>
       </c>
       <c r="F48" s="87" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="30" customHeight="1">
       <c r="A49" s="82" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="B49" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C49" s="66" t="s">
-        <v>795</v>
+        <v>785</v>
       </c>
       <c r="D49" s="68" t="s">
-        <v>796</v>
+        <v>786</v>
       </c>
       <c r="E49" s="66" t="s">
-        <v>797</v>
+        <v>787</v>
       </c>
       <c r="F49" s="88" t="s">
-        <v>798</v>
+        <v>788</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="44" customHeight="1">
       <c r="A50" s="223" t="s">
-        <v>859</v>
+        <v>847</v>
       </c>
       <c r="B50" s="226" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C50" s="225" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="D50" s="226" t="s">
-        <v>1092</v>
+        <v>1076</v>
       </c>
       <c r="E50" s="225" t="s">
-        <v>1119</v>
+        <v>1094</v>
       </c>
       <c r="F50" s="227" t="s">
-        <v>1090</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="30" customHeight="1">
       <c r="A51" s="185" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B51" s="186"/>
       <c r="C51" s="186"/>
@@ -20484,127 +20314,127 @@
     </row>
     <row r="52" spans="1:6" ht="19.5" customHeight="1">
       <c r="A52" s="78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B52" s="27" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>219</v>
+        <v>1123</v>
       </c>
       <c r="D52" s="27" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>1070</v>
+        <v>1057</v>
       </c>
       <c r="F52" s="84" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="30" customHeight="1">
       <c r="A53" s="79" t="s">
+        <v>147</v>
+      </c>
+      <c r="B53" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="B53" s="18" t="s">
-        <v>149</v>
-      </c>
       <c r="C53" s="16" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="F53" s="85" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="30" customHeight="1">
       <c r="A54" s="80" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B54" s="4">
         <v>4.5</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>840</v>
+        <v>829</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>841</v>
+        <v>830</v>
       </c>
       <c r="F54" s="86" t="s">
-        <v>842</v>
+        <v>831</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="30" customHeight="1">
       <c r="A55" s="81" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="B55" s="75">
         <v>4.7</v>
       </c>
       <c r="C55" s="76" t="s">
-        <v>799</v>
+        <v>789</v>
       </c>
       <c r="D55" s="75" t="s">
         <v>64</v>
       </c>
       <c r="E55" s="76" t="s">
-        <v>800</v>
+        <v>790</v>
       </c>
       <c r="F55" s="87" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="30" customHeight="1">
       <c r="A56" s="81" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="B56" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C56" s="76" t="s">
-        <v>802</v>
+        <v>792</v>
       </c>
       <c r="D56" s="75" t="s">
-        <v>803</v>
+        <v>793</v>
       </c>
       <c r="E56" s="76" t="s">
-        <v>804</v>
+        <v>794</v>
       </c>
       <c r="F56" s="87" t="s">
-        <v>805</v>
+        <v>795</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="44" customHeight="1">
       <c r="A57" s="228" t="s">
-        <v>859</v>
+        <v>847</v>
       </c>
       <c r="B57" s="229" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C57" s="230" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="D57" s="229" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E57" s="230" t="s">
-        <v>1121</v>
+        <v>1095</v>
       </c>
       <c r="F57" s="231" t="s">
-        <v>1087</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="19.5" customHeight="1">
       <c r="A58" s="185" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B58" s="186"/>
       <c r="C58" s="186"/>
@@ -20614,39 +20444,39 @@
     </row>
     <row r="59" spans="1:6" ht="30" customHeight="1">
       <c r="A59" s="78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D59" s="27" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="F59" s="84" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="30" customHeight="1">
       <c r="A60" s="79" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B60" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>229</v>
+        <v>1125</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>1069</v>
+        <v>1056</v>
       </c>
       <c r="F60" s="85" t="s">
         <v>33</v>
@@ -20654,67 +20484,67 @@
     </row>
     <row r="61" spans="1:6" ht="30" customHeight="1">
       <c r="A61" s="80" t="s">
+        <v>151</v>
+      </c>
+      <c r="B61" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B61" s="4" t="s">
-        <v>153</v>
-      </c>
       <c r="C61" s="29" t="s">
-        <v>230</v>
+        <v>1126</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>1071</v>
+        <v>1058</v>
       </c>
       <c r="F61" s="86" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="19.5" customHeight="1">
       <c r="A62" s="81" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="B62" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C62" s="74" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="D62" s="75" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E62" s="76" t="s">
-        <v>827</v>
+        <v>817</v>
       </c>
       <c r="F62" s="87" t="s">
-        <v>828</v>
+        <v>818</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="30" customHeight="1">
       <c r="A63" s="82" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="B63" s="68">
         <v>4.5999999999999996</v>
       </c>
       <c r="C63" s="69" t="s">
-        <v>806</v>
+        <v>796</v>
       </c>
       <c r="D63" s="68" t="s">
         <v>51</v>
       </c>
       <c r="E63" s="66" t="s">
-        <v>807</v>
+        <v>797</v>
       </c>
       <c r="F63" s="88" t="s">
-        <v>808</v>
+        <v>798</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="30" customHeight="1">
       <c r="A64" s="185" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="B64" s="186"/>
       <c r="C64" s="186"/>
@@ -20724,19 +20554,19 @@
     </row>
     <row r="65" spans="1:6" ht="42" customHeight="1">
       <c r="A65" s="78" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B65" s="27" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C65" s="28" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D65" s="27" t="s">
         <v>86</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="F65" s="84" t="s">
         <v>84</v>
@@ -20744,47 +20574,47 @@
     </row>
     <row r="66" spans="1:6" ht="30" customHeight="1">
       <c r="A66" s="79" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="B66" s="18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>237</v>
+        <v>1127</v>
       </c>
       <c r="D66" s="18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E66" s="25" t="s">
-        <v>1072</v>
+        <v>1059</v>
       </c>
       <c r="F66" s="85" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="30" customHeight="1">
       <c r="A67" s="80" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="E67" s="24" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="F67" s="86" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="30" customHeight="1">
       <c r="A68" s="179" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="B68" s="180"/>
       <c r="C68" s="180"/>
@@ -20794,187 +20624,187 @@
     </row>
     <row r="69" spans="1:6" ht="30" customHeight="1">
       <c r="A69" s="78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B69" s="27" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="D69" s="27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>1005</v>
+        <v>993</v>
       </c>
       <c r="F69" s="84" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="30" customHeight="1">
       <c r="A70" s="79" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B70" s="18">
         <v>4.4000000000000004</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>829</v>
+        <v>819</v>
       </c>
       <c r="D70" s="18" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>845</v>
+        <v>834</v>
       </c>
       <c r="F70" s="85" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="30" customHeight="1">
       <c r="A71" s="80" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="F71" s="86" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="30" customHeight="1">
       <c r="A72" s="81" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="B72" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C72" s="76" t="s">
-        <v>833</v>
+        <v>823</v>
       </c>
       <c r="D72" s="75" t="s">
-        <v>803</v>
+        <v>793</v>
       </c>
       <c r="E72" s="76" t="s">
-        <v>834</v>
+        <v>824</v>
       </c>
       <c r="F72" s="87" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="30" customHeight="1">
       <c r="A73" s="82" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="B73" s="68">
         <v>4.3</v>
       </c>
       <c r="C73" s="66" t="s">
-        <v>846</v>
+        <v>1128</v>
       </c>
       <c r="D73" s="68" t="s">
-        <v>1077</v>
+        <v>1064</v>
       </c>
       <c r="E73" s="66" t="s">
-        <v>1075</v>
+        <v>1062</v>
       </c>
       <c r="F73" s="88" t="s">
-        <v>1076</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="30" customHeight="1">
       <c r="A74" s="81" t="s">
-        <v>859</v>
+        <v>847</v>
       </c>
       <c r="B74" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C74" s="76" t="s">
-        <v>860</v>
+        <v>848</v>
       </c>
       <c r="D74" s="75" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E74" s="76" t="s">
-        <v>861</v>
+        <v>849</v>
       </c>
       <c r="F74" s="87" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="30" customHeight="1">
       <c r="A75" s="82" t="s">
-        <v>862</v>
+        <v>850</v>
       </c>
       <c r="B75" s="68">
         <v>4.5</v>
       </c>
       <c r="C75" s="66" t="s">
-        <v>863</v>
+        <v>851</v>
       </c>
       <c r="D75" s="68" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E75" s="66" t="s">
-        <v>864</v>
+        <v>852</v>
       </c>
       <c r="F75" s="88" t="s">
-        <v>865</v>
+        <v>853</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="19.5" customHeight="1">
       <c r="A76" s="82" t="s">
+        <v>968</v>
+      </c>
+      <c r="B76" s="220" t="s">
+        <v>978</v>
+      </c>
+      <c r="C76" s="66" t="s">
+        <v>979</v>
+      </c>
+      <c r="D76" s="68" t="s">
         <v>980</v>
       </c>
-      <c r="B76" s="220" t="s">
-        <v>990</v>
-      </c>
-      <c r="C76" s="66" t="s">
-        <v>991</v>
-      </c>
-      <c r="D76" s="68" t="s">
-        <v>992</v>
-      </c>
       <c r="E76" s="66" t="s">
-        <v>993</v>
+        <v>981</v>
       </c>
       <c r="F76" s="88" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="30" customHeight="1">
       <c r="A77" s="82" t="s">
+        <v>972</v>
+      </c>
+      <c r="B77" s="220" t="s">
+        <v>982</v>
+      </c>
+      <c r="C77" s="66" t="s">
+        <v>983</v>
+      </c>
+      <c r="D77" s="68" t="s">
+        <v>975</v>
+      </c>
+      <c r="E77" s="66" t="s">
         <v>984</v>
       </c>
-      <c r="B77" s="220" t="s">
-        <v>994</v>
-      </c>
-      <c r="C77" s="66" t="s">
-        <v>995</v>
-      </c>
-      <c r="D77" s="68" t="s">
-        <v>987</v>
-      </c>
-      <c r="E77" s="66" t="s">
-        <v>996</v>
-      </c>
       <c r="F77" s="88" t="s">
-        <v>997</v>
+        <v>985</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="30" customHeight="1">
       <c r="A78" s="179" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="B78" s="180"/>
       <c r="C78" s="180"/>
@@ -20984,59 +20814,59 @@
     </row>
     <row r="79" spans="1:6" ht="30" customHeight="1">
       <c r="A79" s="78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B79" s="27" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="D79" s="27" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="F79" s="84" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="30" customHeight="1">
       <c r="A80" s="79" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B80" s="18" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C80" s="16" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D80" s="18" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="F80" s="85" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="44" customHeight="1">
       <c r="A81" s="232" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B81" s="233" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C81" s="234" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D81" s="233" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E81" s="234" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="F81" s="235" t="s">
         <v>37</v>
@@ -21044,87 +20874,87 @@
     </row>
     <row r="82" spans="1:6" ht="30" customHeight="1">
       <c r="A82" s="81" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="B82" s="75">
         <v>4.3</v>
       </c>
       <c r="C82" s="76" t="s">
-        <v>843</v>
+        <v>832</v>
       </c>
       <c r="D82" s="75" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E82" s="76" t="s">
-        <v>844</v>
+        <v>833</v>
       </c>
       <c r="F82" s="87" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="30" customHeight="1">
       <c r="A83" s="82" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="B83" s="68">
         <v>4</v>
       </c>
       <c r="C83" s="66" t="s">
-        <v>810</v>
+        <v>800</v>
       </c>
       <c r="D83" s="68" t="s">
-        <v>811</v>
+        <v>801</v>
       </c>
       <c r="E83" s="66" t="s">
-        <v>812</v>
+        <v>802</v>
       </c>
       <c r="F83" s="88" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="30" customHeight="1">
       <c r="A84" s="216" t="s">
-        <v>859</v>
+        <v>847</v>
       </c>
       <c r="B84" s="217">
         <v>4.5999999999999996</v>
       </c>
       <c r="C84" s="218" t="s">
-        <v>1111</v>
+        <v>1089</v>
       </c>
       <c r="D84" s="217" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E84" s="218" t="s">
-        <v>1112</v>
+        <v>1090</v>
       </c>
       <c r="F84" s="219" t="s">
-        <v>1113</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="44" customHeight="1">
       <c r="A85" s="236" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B85" s="237">
         <v>4.8</v>
       </c>
       <c r="C85" s="238" t="s">
-        <v>1122</v>
+        <v>1129</v>
       </c>
       <c r="D85" s="237" t="s">
         <v>64</v>
       </c>
       <c r="E85" s="238" t="s">
-        <v>1123</v>
+        <v>1096</v>
       </c>
       <c r="F85" s="239" t="s">
-        <v>1107</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="30" customHeight="1">
       <c r="A86" s="179" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="B86" s="180"/>
       <c r="C86" s="180"/>
@@ -21134,283 +20964,303 @@
     </row>
     <row r="87" spans="1:6" ht="30" customHeight="1">
       <c r="A87" s="78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B87" s="27" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="D87" s="27" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="F87" s="84" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="30" customHeight="1">
       <c r="A88" s="79" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B88" s="18">
         <v>4.2</v>
       </c>
       <c r="C88" s="16" t="s">
-        <v>831</v>
+        <v>821</v>
       </c>
       <c r="D88" s="18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>832</v>
+        <v>822</v>
       </c>
       <c r="F88" s="85" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="30" customHeight="1">
       <c r="A89" s="80" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B89" s="4">
         <v>4.4000000000000004</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>850</v>
+        <v>838</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>851</v>
+        <v>839</v>
       </c>
       <c r="F89" s="86" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="33.75" customHeight="1">
       <c r="A90" s="81" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="B90" s="75">
         <v>4.3</v>
       </c>
       <c r="C90" s="76" t="s">
-        <v>809</v>
+        <v>799</v>
       </c>
       <c r="D90" s="75" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E90" s="76" t="s">
-        <v>830</v>
+        <v>820</v>
       </c>
       <c r="F90" s="87" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="28">
       <c r="A91" s="82" t="s">
-        <v>781</v>
+        <v>773</v>
       </c>
       <c r="B91" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C91" s="66" t="s">
-        <v>852</v>
+        <v>840</v>
       </c>
       <c r="D91" s="68" t="s">
-        <v>853</v>
+        <v>841</v>
       </c>
       <c r="E91" s="66" t="s">
-        <v>854</v>
+        <v>842</v>
       </c>
       <c r="F91" s="88" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="44" customHeight="1">
       <c r="A92" s="81" t="s">
-        <v>859</v>
+        <v>847</v>
       </c>
       <c r="B92" s="75">
         <v>4.5999999999999996</v>
       </c>
       <c r="C92" s="76" t="s">
-        <v>866</v>
+        <v>854</v>
       </c>
       <c r="D92" s="75" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E92" s="76" t="s">
-        <v>867</v>
+        <v>855</v>
       </c>
       <c r="F92" s="87" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="28">
       <c r="A93" s="223" t="s">
-        <v>862</v>
+        <v>850</v>
       </c>
       <c r="B93" s="226" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C93" s="225" t="s">
-        <v>868</v>
+        <v>856</v>
       </c>
       <c r="D93" s="226" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="E93" s="225" t="s">
-        <v>869</v>
+        <v>857</v>
       </c>
       <c r="F93" s="227" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="42">
       <c r="A94" s="82" t="s">
-        <v>980</v>
+        <v>968</v>
       </c>
       <c r="B94" s="220" t="s">
-        <v>981</v>
+        <v>969</v>
       </c>
       <c r="C94" s="66" t="s">
-        <v>982</v>
+        <v>970</v>
       </c>
       <c r="D94" s="68" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E94" s="66" t="s">
-        <v>983</v>
+        <v>971</v>
       </c>
       <c r="F94" s="88" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="42">
       <c r="A95" s="82" t="s">
-        <v>984</v>
+        <v>972</v>
       </c>
       <c r="B95" s="220" t="s">
-        <v>985</v>
+        <v>973</v>
       </c>
       <c r="C95" s="66" t="s">
-        <v>986</v>
+        <v>974</v>
       </c>
       <c r="D95" s="68" t="s">
-        <v>987</v>
+        <v>975</v>
       </c>
       <c r="E95" s="66" t="s">
-        <v>988</v>
+        <v>976</v>
       </c>
       <c r="F95" s="88" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="48" customHeight="1">
-      <c r="A96" s="179" t="s">
-        <v>264</v>
-      </c>
-      <c r="B96" s="180"/>
-      <c r="C96" s="180"/>
-      <c r="D96" s="180"/>
-      <c r="E96" s="180"/>
-      <c r="F96" s="181"/>
-    </row>
-    <row r="97" spans="1:6" ht="84">
-      <c r="A97" s="78" t="s">
-        <v>142</v>
-      </c>
-      <c r="B97" s="240">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="44" customHeight="1">
+      <c r="A96" s="82" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B96" s="241">
+        <v>4.5</v>
+      </c>
+      <c r="C96" s="66" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D96" s="68" t="s">
+        <v>160</v>
+      </c>
+      <c r="E96" s="66" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F96" s="88" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" s="179" t="s">
+        <v>256</v>
+      </c>
+      <c r="B97" s="180"/>
+      <c r="C97" s="180"/>
+      <c r="D97" s="180"/>
+      <c r="E97" s="180"/>
+      <c r="F97" s="181"/>
+    </row>
+    <row r="98" spans="1:6" ht="84">
+      <c r="A98" s="78" t="s">
+        <v>141</v>
+      </c>
+      <c r="B98" s="240">
         <v>5</v>
       </c>
-      <c r="C97" s="6" t="s">
-        <v>1124</v>
-      </c>
-      <c r="D97" s="27" t="s">
+      <c r="C98" s="6" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D98" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="E97" s="6" t="s">
-        <v>1125</v>
-      </c>
-      <c r="F97" s="84" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98" s="80" t="s">
-        <v>148</v>
-      </c>
-      <c r="B98" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="C98" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="F98" s="86" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" ht="28">
-      <c r="A99" s="81" t="s">
-        <v>152</v>
-      </c>
-      <c r="B99" s="75">
+      <c r="E98" s="6" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F98" s="84" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" s="80" t="s">
+        <v>147</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C99" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="F99" s="86" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="28">
+      <c r="A100" s="81" t="s">
+        <v>151</v>
+      </c>
+      <c r="B100" s="75">
         <v>4.4000000000000004</v>
       </c>
-      <c r="C99" s="76" t="s">
-        <v>855</v>
-      </c>
-      <c r="D99" s="75" t="s">
-        <v>856</v>
-      </c>
-      <c r="E99" s="76" t="s">
-        <v>857</v>
-      </c>
-      <c r="F99" s="87" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" ht="28">
-      <c r="A100" s="82" t="s">
-        <v>777</v>
-      </c>
-      <c r="B100" s="68">
+      <c r="C100" s="76" t="s">
+        <v>843</v>
+      </c>
+      <c r="D100" s="75" t="s">
+        <v>844</v>
+      </c>
+      <c r="E100" s="76" t="s">
+        <v>845</v>
+      </c>
+      <c r="F100" s="87" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="28">
+      <c r="A101" s="82" t="s">
+        <v>769</v>
+      </c>
+      <c r="B101" s="68">
         <v>4.5</v>
       </c>
-      <c r="C100" s="66" t="s">
-        <v>813</v>
-      </c>
-      <c r="D100" s="68" t="s">
-        <v>114</v>
-      </c>
-      <c r="E100" s="66" t="s">
-        <v>814</v>
-      </c>
-      <c r="F100" s="88" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" ht="16" thickBot="1">
-      <c r="A101" s="182" t="s">
-        <v>1105</v>
-      </c>
-      <c r="B101" s="183"/>
-      <c r="C101" s="183"/>
-      <c r="D101" s="183"/>
-      <c r="E101" s="183"/>
-      <c r="F101" s="184"/>
+      <c r="C101" s="66" t="s">
+        <v>803</v>
+      </c>
+      <c r="D101" s="68" t="s">
+        <v>113</v>
+      </c>
+      <c r="E101" s="66" t="s">
+        <v>804</v>
+      </c>
+      <c r="F101" s="88" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="16" thickBot="1">
+      <c r="A102" s="182" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B102" s="183"/>
+      <c r="C102" s="183"/>
+      <c r="D102" s="183"/>
+      <c r="E102" s="183"/>
+      <c r="F102" s="184"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -21424,8 +21274,8 @@
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A51:F51"/>
-    <mergeCell ref="A96:F96"/>
-    <mergeCell ref="A101:F101"/>
+    <mergeCell ref="A97:F97"/>
+    <mergeCell ref="A102:F102"/>
     <mergeCell ref="A58:F58"/>
     <mergeCell ref="A64:F64"/>
     <mergeCell ref="A68:F68"/>
@@ -21453,7 +21303,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1">
       <c r="A1" s="161" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="B1" s="162"/>
       <c r="C1" s="162"/>
@@ -21467,7 +21317,7 @@
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
       <c r="A3" s="197" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="B3" s="198"/>
       <c r="C3" s="198"/>
@@ -21475,100 +21325,100 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="133" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>44</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="D4" s="143" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" customHeight="1">
       <c r="A5" s="134" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="D5" s="144" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="27.75" customHeight="1">
       <c r="A6" s="135" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="D6" s="145" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="27.75" customHeight="1">
       <c r="A7" s="136" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="D7" s="146" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1">
       <c r="A8" s="137" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>1020</v>
+        <v>1008</v>
       </c>
       <c r="C8" s="41" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="D8" s="147" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="27.75" customHeight="1">
       <c r="A9" s="138" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="C9" s="44" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="D9" s="148" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" customHeight="1">
       <c r="A10" s="139" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="B10" s="92" t="s">
-        <v>899</v>
+        <v>887</v>
       </c>
       <c r="C10" s="92" t="s">
-        <v>900</v>
+        <v>888</v>
       </c>
       <c r="D10" s="125" t="s">
-        <v>901</v>
+        <v>889</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -21579,7 +21429,7 @@
     </row>
     <row r="12" spans="1:4" ht="24" customHeight="1">
       <c r="A12" s="200" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="B12" s="201"/>
       <c r="C12" s="201"/>
@@ -21587,170 +21437,170 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="133" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>44</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="D13" s="143" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1">
       <c r="A14" s="135" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="D14" s="145" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="27.75" customHeight="1">
       <c r="A15" s="136" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D15" s="146" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="30" customHeight="1">
       <c r="A16" s="136" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="B16" s="45" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="D16" s="146" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1">
       <c r="A17" s="137" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="D17" s="147" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1">
       <c r="A18" s="137" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C18" s="41" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="D18" s="147" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="30" customHeight="1">
       <c r="A19" s="134" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="D19" s="144" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="30" customHeight="1">
       <c r="A20" s="139" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="B20" s="92" t="s">
-        <v>902</v>
+        <v>890</v>
       </c>
       <c r="C20" s="92" t="s">
-        <v>903</v>
+        <v>891</v>
       </c>
       <c r="D20" s="125" t="s">
-        <v>904</v>
+        <v>892</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="30" customHeight="1">
       <c r="A21" s="140" t="s">
-        <v>905</v>
+        <v>893</v>
       </c>
       <c r="B21" s="90" t="s">
-        <v>906</v>
+        <v>894</v>
       </c>
       <c r="C21" s="90" t="s">
-        <v>907</v>
+        <v>895</v>
       </c>
       <c r="D21" s="149" t="s">
-        <v>908</v>
+        <v>896</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="27.75" customHeight="1">
       <c r="A22" s="138" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="B22" s="43" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="C22" s="44" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="D22" s="148" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="30" customHeight="1">
       <c r="A23" s="137" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="C23" s="41" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="D23" s="147" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="30" customHeight="1">
       <c r="A24" s="137" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="B24" s="40" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="C24" s="41" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="D24" s="147" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -21761,7 +21611,7 @@
     </row>
     <row r="26" spans="1:4" ht="24" customHeight="1">
       <c r="A26" s="203" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="B26" s="204"/>
       <c r="C26" s="204"/>
@@ -21769,128 +21619,128 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="133" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>44</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="D27" s="143" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="27.75" customHeight="1">
       <c r="A28" s="135" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="B28" s="34" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="D28" s="145" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="30" customHeight="1">
       <c r="A29" s="136" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="B29" s="37" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="D29" s="146" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="27.75" customHeight="1">
       <c r="A30" s="134" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="B30" s="31" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="C30" s="32" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="D30" s="144" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="27.75" customHeight="1">
       <c r="A31" s="138" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="B31" s="43" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="C31" s="44" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="D31" s="148" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="27.75" customHeight="1">
       <c r="A32" s="138" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="B32" s="43" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="C32" s="44" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="D32" s="148" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="30" customHeight="1">
       <c r="A33" s="135" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="B33" s="46" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="C33" s="35" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="D33" s="145" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="30" customHeight="1">
       <c r="A34" s="137" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B34" s="40" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="C34" s="41" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="D34" s="147" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="30" customHeight="1" thickBot="1">
       <c r="A35" s="141" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="B35" s="130" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="C35" s="131" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="D35" s="150" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -21921,7 +21771,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1">
       <c r="A1" s="206" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="B1" s="206"/>
       <c r="C1" s="206"/>
@@ -21929,7 +21779,7 @@
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
       <c r="A3" s="178" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="B3" s="178"/>
       <c r="C3" s="178"/>
@@ -21937,63 +21787,63 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="12" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="27.75" customHeight="1">
       <c r="A5" s="47" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="B5" s="48" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="C5" s="49" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="D5" s="47" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="27.75" customHeight="1">
       <c r="A6" s="47" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D6" s="47" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="27.75" customHeight="1">
       <c r="A7" s="30" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="24" customHeight="1">
       <c r="A9" s="174" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="B9" s="174"/>
       <c r="C9" s="174"/>
@@ -22001,49 +21851,49 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="12" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="27.75" customHeight="1">
       <c r="A11" s="47" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="B11" s="48" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="D11" s="47" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="27.75" customHeight="1">
       <c r="A12" s="47" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="B12" s="48" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="C12" s="49" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="D12" s="47" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="24" customHeight="1">
       <c r="A14" s="176" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="B14" s="176"/>
       <c r="C14" s="176"/>
@@ -22051,44 +21901,44 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="12" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="27.75" customHeight="1">
       <c r="A16" s="47" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="B16" s="48" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="C16" s="49" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="D16" s="47" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="27.75" customHeight="1">
       <c r="A17" s="50" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="B17" s="51" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="C17" s="52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D17" s="50" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>

--- a/tools/itinerary.xlsx
+++ b/tools/itinerary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jitwei/Library/Mobile Documents/com~apple~CloudDocs/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA017CA-BD5E-3449-B7AB-7C0B6B1BBFB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26598332-B75E-E346-A5B3-C345DDAEBA4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-6080" yWindow="-21000" windowWidth="38400" windowHeight="21000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11491,9 +11491,6 @@
     <t>🆕 TRENDY alt: Yuniaoji 玉鸟集 &amp; Da Wuding 大屋顶 (良渚)</t>
   </si>
   <si>
-    <t>Hangzhou's art ceiling' — Tadao Ando 安藤忠雄 大屋顶 + 柳亦春 大谷仓 with 单向空间 bookstore; 128 boutiques, 85% independent. Metro L2 to 良渚 — needs a half-day, so swap for 西溪湿地.</t>
-  </si>
-  <si>
     <t>Optional alt · 余杭</t>
   </si>
   <si>
@@ -11788,9 +11785,6 @@
     <t>☕ Optional: 羽和铃 Feather Bell coffee</t>
   </si>
   <si>
-    <t>Verified on Dianping (~¥53pp). Bamboo-wind-chime courtyard cafe at the foot of Wushan 吴山, a few steps up from Hefang St. Specialty hand-brew, plum-soda, scones &amp; chiffon cake.</t>
-  </si>
-  <si>
     <t>Opt · ~¥53pp</t>
   </si>
   <si>
@@ -11800,9 +11794,6 @@
     <t>🍦 Optional: 夏序 SASU Gelato</t>
   </si>
   <si>
-    <t>Verified on Dianping (~¥37pp). Called by reviewers Hangzhou's best Italian gelato — pistachio, matcha &amp; chocolate are the standouts. On Guangfu Rd 光复路, ~5 min from Hefang St. Little queuing off-peak.</t>
-  </si>
-  <si>
     <t>Opt · ~¥37pp</t>
   </si>
   <si>
@@ -11833,9 +11824,6 @@
     <t>🍵 Optional: 查小文茶客厅 Cha Talk Tea House (四寒茶舍)</t>
   </si>
   <si>
-    <t>Award-winning tea house on Dajing Lane 大井巷 (Southern Song lane off Hefang St). Owner 查文 is a Hangzhou tea-culture inheritor. 1F: walk-in tasting + tea/teaware retail — local 西湖龙井 plus Taiwan high-mtn oolong, Fuding white, Wuyi rock tea. Creative tea mocktails (茶逗逗 w/ tea jelly) brewed espresso-style. 2F tatami tea room needs advance booking 预约.</t>
-  </si>
-  <si>
     <t>Opt · walk-in 1F</t>
   </si>
   <si>
@@ -12226,9 +12214,6 @@
     <t>Dinner + SHOP: Hubin in77 湖滨银泰 (at hotel)</t>
   </si>
   <si>
-    <t>Canopy sits beside the 湖滨 waterfront strip — flagship stores, food halls &amp; easy first-night dinner, all within a 5-min walk. Replaces the old Raffles City 来福士 plan (that was next to the Conrad).</t>
-  </si>
-  <si>
     <t>湖滨in77 · 5 min</t>
   </si>
   <si>
@@ -12238,9 +12223,6 @@
     <t>MUST-SEE: West Lake Music Fountain 西湖音乐喷泉</t>
   </si>
   <si>
-    <t>~5-min walk from the hotel at 湖滨三公园 — nightly shows on the lake. Perfect low-effort arrival night. (The 钱江新城灯光秀 is now ~8km east by the Conrad — see the Day 3 Opt row.)</t>
-  </si>
-  <si>
     <t>湖滨 · 5 min</t>
   </si>
   <si>
@@ -12286,9 +12268,6 @@
     <t>🏨 HOTEL MOVE: collect bags at Canopy 康铂 → check in Conrad 康莱德</t>
   </si>
   <si>
-    <t>Per your plan — sightsee first, move after lunch. DiDi from 灵隐 to Canopy 国货路 (~20 min), grab the stored luggage, then DiDi to the Conrad in 钱江新城 (~15 min). Drop bags / check in, then head back to 吴山 for the afternoon. Conrad connects directly to Raffles City 来福士.</t>
-  </si>
-  <si>
     <t>DiDi ~35–40 min total</t>
   </si>
   <si>
@@ -12439,21 +12418,12 @@
     <t>15:00–15:50</t>
   </si>
   <si>
-    <t>Silk, tea, fans, snack stalls — now a relaxed 50 min with the museums dropped.</t>
-  </si>
-  <si>
     <t>15:50–16:20</t>
   </si>
   <si>
-    <t>Old-city roaster — back to a proper 30-min sit-down (the museum drop undid the earlier squeeze), then Metro L5 north.</t>
-  </si>
-  <si>
     <t>16:35–17:30</t>
   </si>
   <si>
-    <t>③ Metro L5 north. Canal museum &amp; Xiaohe Direct St 小河直街. Now ~55 min — the lantern-lit canal frontage, 拱宸桥 and 小河直街 without rushing. Still leave by 17:30 sharp for 宫宴.</t>
-  </si>
-  <si>
     <t>14:30–15:30</t>
   </si>
   <si>
@@ -12469,15 +12439,9 @@
     <t>打卡 highlight — illuminated glazed pagoda 琉璃塔 &amp; ruins light show 光影秀. ~1.2km from 中华门. Comfortable buffer now before the 19:00 cruise.</t>
   </si>
   <si>
-    <t>Iconic yellow temple (求姻缘); climb 台城 明城墙 overlooking Xuanwu Lake. Now a full hour with 南京博物院 dropped.</t>
-  </si>
-  <si>
     <t>14:40–16:30</t>
   </si>
   <si>
-    <t>Jiangnan's largest royal lake park; the 十里长堤 causeway is a stunning sunset spot — now ~1h50m to walk it properly rather than rush.</t>
-  </si>
-  <si>
     <t>16:40–17:15</t>
   </si>
   <si>
@@ -12487,9 +12451,6 @@
     <t>14:30–16:00</t>
   </si>
   <si>
-    <t>④ SOUTH old town. The most exquisite small garden — now ~1h30m to linger, the garden most worth it.</t>
-  </si>
-  <si>
     <t>Tsutaya Books 茑屋书店 (天目里店) (Day 3 alt)</t>
   </si>
   <si>
@@ -12619,9 +12580,6 @@
     <t>🍵 MUST-SEE: Longjing Tea Village 龙井茶村 (2h block)</t>
   </si>
   <si>
-    <t>SW-hills half-day, capped at 2h. Dragon Well spring 龙井泉 (the "dragon whisker" waterline), Longjing Temple 龙井寺, and the Eighteen Royal Tea Trees 十八棵御茶树 at the foot of Lion Peak 狮峰山. Tasting with a local tea family + buy fresh 龙井. Village is free &amp; open 24h, but the terraces are a DAYLIGHT sight — sunset 16 Nov is 17:02. Note: official suggested visit is 2–3h; this 2h cap covers well/temple/tea trees + one tasting, NOT the 十里琅珰 ridge walk.</t>
-  </si>
-  <si>
     <t>Free · DiDi ~20 min</t>
   </si>
   <si>
@@ -12631,9 +12589,6 @@
     <t>🍁 Jiuxi 九溪烟树 · Manjuelong 满觉陇 (foliage leg)</t>
   </si>
   <si>
-    <t>Downhill continuation of the same SW-hills corridor — no lake crossing. Classic NOVEMBER maples 九溪 &amp; 十八涧 stream; 满觉陇 osmanthus lane. Peak-season 打卡 while light holds. DROP THIS LEG if the 龙井 transfer runs long and give the time to 雷峰塔.</t>
-  </si>
-  <si>
     <t>Free · short hop</t>
   </si>
   <si>
@@ -12643,52 +12598,97 @@
     <t>MUST-SEE: Leifeng Pagoda 雷峰塔 (sunset slot)</t>
   </si>
   <si>
-    <t>雷峰夕照 — one of the West Lake Ten Scenes, and the reason this stop now sits here. Sunset 16 Nov is 17:02, so you get golden hour on the way up and the floodlit lake on the way down. Escalators to the top. Pagoda is lit after dark, so the late slot is an upgrade, not a compromise.</t>
-  </si>
-  <si>
     <t>西湖区南山路15号</t>
   </si>
   <si>
-    <t>Optional: Huagang Guanyu 花港观鱼 (dropped from main run)</t>
-  </si>
-  <si>
-    <t>Removed from the fixed schedule to fund the 2h 龙井 block. Peony garden &amp; red-carp ponds; autumn colour. It sits right by 苏堤 south end — bolt it on before lunch only if you are running ahead of time.</t>
-  </si>
-  <si>
     <t>18:05–19:05</t>
   </si>
   <si>
-    <t>Home-style Hangzhou near Hefang 河坊街. Now a full hour — 河坊街 was dropped tonight to protect the show buffer. (宫宴 banquet is on Day 3 — it clashes with tonight's 印象西湖 show.)</t>
-  </si>
-  <si>
     <t>19:05–19:20</t>
   </si>
   <si>
     <t>Transfer: dinner → 岳湖 show entrance (北山路82号)</t>
   </si>
   <si>
-    <t>河坊街 DROPPED from Day 2 at your request — you cover 清河坊 &amp; 大井巷 properly on Day 3 (14:00–15:50). DiDi to the 岳湖景区 gate opposite 岳王庙. Arrive ~19:20 for a 19:40 curtain: ticket collection +检票 + the walk to the seats. Official guidance is to arrive 45 min early; this gives ~20, so do not linger over dinner.</t>
-  </si>
-  <si>
     <t>DiDi ~15 min</t>
   </si>
   <si>
     <t>19:40–20:35</t>
   </si>
   <si>
-    <t>MANDATORY — outdoor water-stage show on West Lake itself (Zhang Yimou 张艺谋 / 王潮歌 / 樊跃; music by Kitaro 喜多郎). ~50–55 min. CONFIRMED START IS 19:40, not 19:30. There is a second 21:10 session but it runs mainly Fri/Sat &amp; public holidays — 16 Nov 2026 is a MONDAY, so expect the 19:40 show ONLY. Outdoor &amp; weather-dependent: re-confirm the session list on the official channel the day before. Entrance 北山路82号, opposite 岳王庙; seating by zone; book ahead.</t>
-  </si>
-  <si>
     <t>Lunch — 28 Hubin Road 湖滨28 (Hyatt Regency 凯悦)</t>
   </si>
   <si>
-    <t>Top-rated lakeside Hangzhou fine dining (Dianping 4.8, 600+ reviews) — famous Dongpo pork 东坡肉. Inside the Hyatt Regency on 湖滨路, so it flows straight on from the in77/湖滨步行街 stop right before it — zero detour. ⚠️ FINE DINING: book ahead, and note the 55-min slot here is tight for this style of meal — allow longer or push the 龙井 departure if you want a relaxed sitting. (Replaces 楼外楼, which is scenic but not in the 2026 Dianping 杭帮菜 top-16.)</t>
-  </si>
-  <si>
     <t>¥300–500 · book ahead</t>
   </si>
   <si>
     <t>上城区湖滨路28号 (凯悦酒店)</t>
+  </si>
+  <si>
+    <t>Top-rated lakeside Hangzhou fine dining (Dianping 4.8, 600+ reviews) — famous Dongpo pork 东坡肉. Inside the Hyatt Regency on 湖滨路, a short walk on from 湖滨步行街/in77. Book ahead; fine-dining pace, so keep an eye on the 13:35 finish.</t>
+  </si>
+  <si>
+    <t>Dragon Well spring 龙井泉 (the "dragon whisker" waterline), Longjing Temple 龙井寺, and the Eighteen Royal Tea Trees 十八棵御茶树 at the foot of Lion Peak 狮峰山. Tasting with a local tea family + buy fresh 龙井. Free &amp; open 24h, but the terraces are a daylight sight — sunset 16 Nov is 17:02. This 2h covers well/temple/tea trees + one tasting, not the 十里琅珰 ridge walk.</t>
+  </si>
+  <si>
+    <t>Classic November foliage in the SW hills — 九溪 maples &amp; 十八涧 stream; 满觉陇 osmanthus lane. Downhill continuation from 龙井, no lake crossing. Skippable if the 龙井 transfer runs long.</t>
+  </si>
+  <si>
+    <t>雷峰夕照 — one of the West Lake Ten Scenes. Sunset 16 Nov is 17:02: golden hour on the way up, floodlit lake on the way down. Escalators to the top; pagoda lit after dark.</t>
+  </si>
+  <si>
+    <t>Optional: Huagang Guanyu 花港观鱼</t>
+  </si>
+  <si>
+    <t>Peony garden &amp; red-carp ponds; autumn colour. Right by the 苏堤 south end — bolt on before lunch only if running ahead of time.</t>
+  </si>
+  <si>
+    <t>Home-style Hangzhou near Hefang 河坊街. Queue early. Keep to the hour — the show gate is a 15-min ride away.</t>
+  </si>
+  <si>
+    <t>DiDi to the 岳湖景区 gate opposite 岳王庙. Arrive ~19:20 for the 19:40 curtain: ticket collection, 检票 and the walk to the seats. Official guidance is 45 min early, so do not linger over dinner.</t>
+  </si>
+  <si>
+    <t>Outdoor water-stage show on West Lake itself (Zhang Yimou 张艺谋 / 王潮歌 / 樊跃; music by Kitaro 喜多郎). ~50–55 min. Starts 19:40. A second 21:10 session runs mainly Fri/Sat &amp; public holidays — 16 Nov is a Monday, so expect the 19:40 show only. Outdoor &amp; weather-dependent: re-confirm the session on the official channel the day before. Entrance 北山路82号, opposite 岳王庙; seating by zone; book ahead.</t>
+  </si>
+  <si>
+    <t>Canopy sits beside the 湖滨 waterfront strip — flagship stores, food halls &amp; easy first-night dinner, all within a 5-min walk.</t>
+  </si>
+  <si>
+    <t>~5-min walk from the hotel at 湖滨三公园 — nightly shows on the lake. Perfect low-effort arrival night.</t>
+  </si>
+  <si>
+    <t>Sightsee first, move after lunch. DiDi from 灵隐 to Canopy 国货路 (~20 min), grab the stored luggage, then DiDi to the Conrad in 钱江新城 (~15 min). Drop bags / check in, then head back to 吴山 for the afternoon. Conrad connects directly to Raffles City 来福士.</t>
+  </si>
+  <si>
+    <t>Silk, tea, fans, snack stalls — a relaxed 50-min browse.</t>
+  </si>
+  <si>
+    <t>Old-city roaster — a proper 30-min sit-down, then Metro L5 north.</t>
+  </si>
+  <si>
+    <t>③ Metro L5 north. Canal museum &amp; Xiaohe Direct St 小河直街 — the lantern-lit canal frontage and 拱宸桥 at an unhurried pace. Leave by 17:30 sharp for 宫宴.</t>
+  </si>
+  <si>
+    <t>Hangzhou's "art ceiling" — Tadao Ando 安藤忠雄 大屋顶 + 柳亦春 大谷仓 with 单向空间 bookstore; 128 boutiques, 85% independent. Metro L2 to 良渚; needs a half-day.</t>
+  </si>
+  <si>
+    <t>Iconic yellow temple (求姻缘); climb 台城 明城墙 overlooking Xuanwu Lake.</t>
+  </si>
+  <si>
+    <t>Jiangnan's largest royal lake park; the 十里长堤 causeway is a stunning sunset spot — allow the full stretch to walk it properly.</t>
+  </si>
+  <si>
+    <t>④ SOUTH old town. The most exquisite of the small gardens and the one most worth lingering in.</t>
+  </si>
+  <si>
+    <t>Verified on Dianping (~¥53pp). Bamboo-wind-chime courtyard cafe at the foot of Wushan 吴山, a few steps up from Hefang St — directly below the 14:15 吴山/城隍阁 stop and beside the 15:00 清河坊 browse. Specialty hand-brew, plum-soda, scones &amp; chiffon cake.</t>
+  </si>
+  <si>
+    <t>Verified on Dianping (~¥37pp). Called by reviewers Hangzhou's best Italian gelato — pistachio, matcha &amp; chocolate are the standouts. On Guangfu Rd 光复路, ~5 min from 清河坊 and right off 南宋御街. Little queuing off-peak.</t>
+  </si>
+  <si>
+    <t>Award-winning tea house on Dajing Lane 大井巷 — the Southern Song lane you walk at 15:00, so it is a zero-detour stop. Owner 查文 is a Hangzhou tea-culture inheritor. 1F: walk-in tasting + tea/teaware retail — local 西湖龙井 plus Taiwan high-mtn oolong, Fuding white, Wuyi rock tea. Creative tea mocktails (茶逗逗 w/ tea jelly) brewed espresso-style. 2F tatami tea room needs advance booking 预约.</t>
   </si>
 </sst>
 </file>
@@ -13257,7 +13257,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="243">
+  <cellXfs count="241">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -13746,12 +13746,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="21" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -14257,31 +14251,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="31.5" customHeight="1">
-      <c r="A1" s="207" t="s">
+      <c r="A1" s="205" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="207"/>
-      <c r="C1" s="207"/>
-      <c r="D1" s="207"/>
-      <c r="E1" s="207"/>
+      <c r="B1" s="205"/>
+      <c r="C1" s="205"/>
+      <c r="D1" s="205"/>
+      <c r="E1" s="205"/>
     </row>
     <row r="2" spans="1:5" ht="21.75" customHeight="1">
-      <c r="A2" s="208" t="s">
+      <c r="A2" s="206" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="208"/>
-      <c r="C2" s="208"/>
-      <c r="D2" s="208"/>
-      <c r="E2" s="208"/>
+      <c r="B2" s="206"/>
+      <c r="C2" s="206"/>
+      <c r="D2" s="206"/>
+      <c r="E2" s="206"/>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1">
-      <c r="A4" s="209" t="s">
+      <c r="A4" s="207" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="209"/>
-      <c r="C4" s="209"/>
-      <c r="D4" s="209"/>
-      <c r="E4" s="209"/>
+      <c r="B4" s="207"/>
+      <c r="C4" s="207"/>
+      <c r="D4" s="207"/>
+      <c r="E4" s="207"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
@@ -14335,13 +14329,13 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1">
-      <c r="A9" s="210" t="s">
+      <c r="A9" s="208" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="210"/>
-      <c r="C9" s="210"/>
-      <c r="D9" s="210"/>
-      <c r="E9" s="210"/>
+      <c r="B9" s="208"/>
+      <c r="C9" s="208"/>
+      <c r="D9" s="208"/>
+      <c r="E9" s="208"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
@@ -14362,36 +14356,36 @@
     </row>
     <row r="11" spans="1:5" ht="55" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>1043</v>
+        <v>1036</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1044</v>
+        <v>1037</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1045</v>
+        <v>1038</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>1046</v>
+        <v>1039</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="55" customHeight="1">
       <c r="A12" s="6" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>1043</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>1048</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>1049</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="45.75" customHeight="1">
@@ -14430,41 +14424,41 @@
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1"/>
     <row r="16" spans="1:5" ht="72" customHeight="1">
-      <c r="A16" s="211" t="s">
+      <c r="A16" s="209" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="211"/>
-      <c r="C16" s="211"/>
-      <c r="D16" s="211"/>
-      <c r="E16" s="211"/>
+      <c r="B16" s="209"/>
+      <c r="C16" s="209"/>
+      <c r="D16" s="209"/>
+      <c r="E16" s="209"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="205" t="s">
+      <c r="A17" s="203" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="205"/>
-      <c r="C17" s="205"/>
-      <c r="D17" s="205"/>
-      <c r="E17" s="205"/>
+      <c r="B17" s="203"/>
+      <c r="C17" s="203"/>
+      <c r="D17" s="203"/>
+      <c r="E17" s="203"/>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1"/>
     <row r="19" spans="1:5" ht="31.5" customHeight="1">
-      <c r="A19" s="206" t="s">
+      <c r="A19" s="204" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="206"/>
-      <c r="C19" s="206"/>
-      <c r="D19" s="206"/>
-      <c r="E19" s="206"/>
+      <c r="B19" s="204"/>
+      <c r="C19" s="204"/>
+      <c r="D19" s="204"/>
+      <c r="E19" s="204"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="205" t="s">
+      <c r="A20" s="203" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="205"/>
-      <c r="C20" s="205"/>
-      <c r="D20" s="205"/>
-      <c r="E20" s="205"/>
+      <c r="B20" s="203"/>
+      <c r="C20" s="203"/>
+      <c r="D20" s="203"/>
+      <c r="E20" s="203"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -14499,24 +14493,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18">
-      <c r="A1" s="212" t="s">
-        <v>1008</v>
-      </c>
-      <c r="B1" s="213"/>
-      <c r="C1" s="213"/>
-      <c r="D1" s="213"/>
-      <c r="E1" s="213"/>
-      <c r="F1" s="214"/>
+      <c r="A1" s="210" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B1" s="211"/>
+      <c r="C1" s="211"/>
+      <c r="D1" s="211"/>
+      <c r="E1" s="211"/>
+      <c r="F1" s="212"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="215" t="s">
+      <c r="A2" s="213" t="s">
         <v>344</v>
       </c>
-      <c r="B2" s="216"/>
-      <c r="C2" s="216"/>
-      <c r="D2" s="216"/>
-      <c r="E2" s="216"/>
-      <c r="F2" s="217"/>
+      <c r="B2" s="214"/>
+      <c r="C2" s="214"/>
+      <c r="D2" s="214"/>
+      <c r="E2" s="214"/>
+      <c r="F2" s="215"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="77" t="s">
@@ -14539,14 +14533,14 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="218" t="s">
-        <v>1009</v>
-      </c>
-      <c r="B4" s="219"/>
-      <c r="C4" s="219"/>
-      <c r="D4" s="219"/>
-      <c r="E4" s="219"/>
-      <c r="F4" s="220"/>
+      <c r="A4" s="216" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B4" s="217"/>
+      <c r="C4" s="217"/>
+      <c r="D4" s="217"/>
+      <c r="E4" s="217"/>
+      <c r="F4" s="218"/>
     </row>
     <row r="5" spans="1:6" ht="28">
       <c r="A5" s="98" t="s">
@@ -14593,13 +14587,13 @@
         <v>350</v>
       </c>
       <c r="B7" s="158" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C7" s="50" t="s">
         <v>361</v>
       </c>
       <c r="D7" s="50" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E7" s="50" t="s">
         <v>362</v>
@@ -14636,16 +14630,16 @@
         <v>369</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="D9" s="50" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="E9" s="50" t="s">
         <v>370</v>
       </c>
       <c r="F9" s="115" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28">
@@ -14656,19 +14650,19 @@
         <v>371</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="F10" s="116" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="56">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="28">
       <c r="A11" s="102" t="s">
         <v>350</v>
       </c>
@@ -14676,19 +14670,19 @@
         <v>373</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>1018</v>
+        <v>1160</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="F11" s="117" t="s">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="42">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="28">
       <c r="A12" s="103" t="s">
         <v>350</v>
       </c>
@@ -14696,16 +14690,16 @@
         <v>374</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>1022</v>
+        <v>1161</v>
       </c>
       <c r="E12" s="41" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="F12" s="118" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28">
@@ -14722,21 +14716,21 @@
         <v>377</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="F13" s="116" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="218" t="s">
-        <v>1026</v>
-      </c>
-      <c r="B14" s="219"/>
-      <c r="C14" s="219"/>
-      <c r="D14" s="219"/>
-      <c r="E14" s="219"/>
-      <c r="F14" s="220"/>
+      <c r="A14" s="216" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B14" s="217"/>
+      <c r="C14" s="217"/>
+      <c r="D14" s="217"/>
+      <c r="E14" s="217"/>
+      <c r="F14" s="218"/>
     </row>
     <row r="15" spans="1:6" ht="28">
       <c r="A15" s="101" t="s">
@@ -14746,16 +14740,16 @@
         <v>380</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>1027</v>
+        <v>1021</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="F15" s="116" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="28">
@@ -14809,7 +14803,7 @@
         <v>391</v>
       </c>
       <c r="D18" s="47" t="s">
-        <v>1077</v>
+        <v>1070</v>
       </c>
       <c r="E18" s="47" t="s">
         <v>384</v>
@@ -14843,7 +14837,7 @@
         <v>379</v>
       </c>
       <c r="B20" s="152" t="s">
-        <v>1143</v>
+        <v>1130</v>
       </c>
       <c r="C20" s="61" t="s">
         <v>399</v>
@@ -14863,7 +14857,7 @@
         <v>379</v>
       </c>
       <c r="B21" s="157" t="s">
-        <v>1144</v>
+        <v>1131</v>
       </c>
       <c r="C21" s="20" t="s">
         <v>403</v>
@@ -14883,102 +14877,102 @@
         <v>379</v>
       </c>
       <c r="B22" s="157" t="s">
-        <v>1145</v>
+        <v>1132</v>
       </c>
       <c r="C22" s="20" t="s">
+        <v>827</v>
+      </c>
+      <c r="D22" s="20" t="s">
         <v>828</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="E22" s="20" t="s">
         <v>829</v>
       </c>
-      <c r="E22" s="20" t="s">
-        <v>830</v>
-      </c>
       <c r="F22" s="121" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="112">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="56">
       <c r="A23" s="98" t="s">
         <v>379</v>
       </c>
       <c r="B23" s="159" t="s">
-        <v>1146</v>
+        <v>1133</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>1169</v>
+        <v>1148</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>1170</v>
+        <v>1151</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>1171</v>
+        <v>1149</v>
       </c>
       <c r="F23" s="86" t="s">
-        <v>1172</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="112">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="98">
       <c r="A24" s="105" t="s">
         <v>379</v>
       </c>
       <c r="B24" s="152" t="s">
-        <v>1147</v>
+        <v>1134</v>
       </c>
       <c r="C24" s="61" t="s">
-        <v>1148</v>
+        <v>1135</v>
       </c>
       <c r="D24" s="61" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="E24" s="61" t="s">
-        <v>1150</v>
+        <v>1136</v>
       </c>
       <c r="F24" s="120" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="70">
+    <row r="25" spans="1:6" ht="56">
       <c r="A25" s="105" t="s">
         <v>379</v>
       </c>
       <c r="B25" s="152" t="s">
-        <v>1151</v>
+        <v>1137</v>
       </c>
       <c r="C25" s="61" t="s">
-        <v>1152</v>
+        <v>1138</v>
       </c>
       <c r="D25" s="61" t="s">
         <v>1153</v>
       </c>
       <c r="E25" s="61" t="s">
-        <v>1154</v>
+        <v>1139</v>
       </c>
       <c r="F25" s="120" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="70">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="42">
       <c r="A26" s="105" t="s">
         <v>379</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>1155</v>
+        <v>1140</v>
       </c>
       <c r="C26" s="61" t="s">
-        <v>1156</v>
+        <v>1141</v>
       </c>
       <c r="D26" s="61" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="E26" s="61" t="s">
         <v>407</v>
       </c>
       <c r="F26" s="120" t="s">
-        <v>1158</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="56">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="42">
       <c r="A27" s="105" t="s">
         <v>379</v>
       </c>
@@ -14986,10 +14980,10 @@
         <v>592</v>
       </c>
       <c r="C27" s="61" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
       <c r="D27" s="61" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="E27" s="61" t="s">
         <v>529</v>
@@ -14998,18 +14992,18 @@
         <v>406</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="42">
+    <row r="28" spans="1:6" ht="28">
       <c r="A28" s="107" t="s">
         <v>379</v>
       </c>
       <c r="B28" s="160" t="s">
-        <v>1161</v>
+        <v>1143</v>
       </c>
       <c r="C28" s="36" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="D28" s="36" t="s">
-        <v>1162</v>
+        <v>1157</v>
       </c>
       <c r="E28" s="36" t="s">
         <v>53</v>
@@ -15018,337 +15012,337 @@
         <v>255</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="84">
+    <row r="29" spans="1:6" ht="42">
       <c r="A29" s="102" t="s">
         <v>379</v>
       </c>
       <c r="B29" s="154" t="s">
-        <v>1163</v>
+        <v>1144</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>1164</v>
+        <v>1145</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>1165</v>
+        <v>1158</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>1166</v>
+        <v>1146</v>
       </c>
       <c r="F29" s="117" t="s">
         <v>798</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="42">
-      <c r="A30" s="166" t="s">
+    <row r="30" spans="1:6" ht="98">
+      <c r="A30" s="102" t="s">
         <v>379</v>
       </c>
-      <c r="B30" s="167" t="s">
+      <c r="B30" s="154" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>796</v>
+      </c>
+      <c r="D30" s="33" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E30" s="33" t="s">
+        <v>797</v>
+      </c>
+      <c r="F30" s="117" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="28">
+      <c r="A31" s="107" t="s">
+        <v>379</v>
+      </c>
+      <c r="B31" s="160" t="s">
+        <v>799</v>
+      </c>
+      <c r="C31" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="D31" s="36" t="s">
+        <v>410</v>
+      </c>
+      <c r="E31" s="36" t="s">
+        <v>411</v>
+      </c>
+      <c r="F31" s="122" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="28">
+      <c r="A32" s="101" t="s">
+        <v>379</v>
+      </c>
+      <c r="B32" s="151" t="s">
+        <v>788</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F32" s="116" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="216" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B33" s="217"/>
+      <c r="C33" s="217"/>
+      <c r="D33" s="217"/>
+      <c r="E33" s="217"/>
+      <c r="F33" s="218"/>
+    </row>
+    <row r="34" spans="1:6" ht="42">
+      <c r="A34" s="101" t="s">
+        <v>414</v>
+      </c>
+      <c r="B34" s="56" t="s">
+        <v>415</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F34" s="116" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="84">
+      <c r="A35" s="102" t="s">
+        <v>414</v>
+      </c>
+      <c r="B35" s="154" t="s">
         <v>592</v>
       </c>
-      <c r="C30" s="61" t="s">
+      <c r="C35" s="33" t="s">
+        <v>890</v>
+      </c>
+      <c r="D35" s="33" t="s">
+        <v>891</v>
+      </c>
+      <c r="E35" s="35" t="s">
+        <v>892</v>
+      </c>
+      <c r="F35" s="117" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="28">
+      <c r="A36" s="105" t="s">
+        <v>414</v>
+      </c>
+      <c r="B36" s="60" t="s">
+        <v>416</v>
+      </c>
+      <c r="C36" s="61" t="s">
+        <v>417</v>
+      </c>
+      <c r="D36" s="61" t="s">
+        <v>418</v>
+      </c>
+      <c r="E36" s="61" t="s">
+        <v>419</v>
+      </c>
+      <c r="F36" s="120" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="28">
+      <c r="A37" s="105" t="s">
+        <v>414</v>
+      </c>
+      <c r="B37" s="60" t="s">
+        <v>421</v>
+      </c>
+      <c r="C37" s="61" t="s">
+        <v>422</v>
+      </c>
+      <c r="D37" s="61" t="s">
+        <v>423</v>
+      </c>
+      <c r="E37" s="61" t="s">
+        <v>424</v>
+      </c>
+      <c r="F37" s="120" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="28">
+      <c r="A38" s="104" t="s">
+        <v>414</v>
+      </c>
+      <c r="B38" s="59" t="s">
+        <v>426</v>
+      </c>
+      <c r="C38" s="47" t="s">
+        <v>427</v>
+      </c>
+      <c r="D38" s="47" t="s">
+        <v>428</v>
+      </c>
+      <c r="E38" s="47" t="s">
+        <v>384</v>
+      </c>
+      <c r="F38" s="119" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="28">
+      <c r="A39" s="99" t="s">
+        <v>414</v>
+      </c>
+      <c r="B39" s="54" t="s">
+        <v>429</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F39" s="85" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="70">
+      <c r="A40" s="99" t="s">
+        <v>414</v>
+      </c>
+      <c r="B40" s="54" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F40" s="85" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="28">
+      <c r="A41" s="105" t="s">
+        <v>414</v>
+      </c>
+      <c r="B41" s="60" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C41" s="61" t="s">
+        <v>433</v>
+      </c>
+      <c r="D41" s="61" t="s">
+        <v>434</v>
+      </c>
+      <c r="E41" s="61" t="s">
+        <v>424</v>
+      </c>
+      <c r="F41" s="120" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="28">
+      <c r="A42" s="102" t="s">
+        <v>414</v>
+      </c>
+      <c r="B42" s="57" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C42" s="33" t="s">
+        <v>436</v>
+      </c>
+      <c r="D42" s="33" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E42" s="35" t="s">
+        <v>437</v>
+      </c>
+      <c r="F42" s="117" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="28">
+      <c r="A43" s="102" t="s">
+        <v>414</v>
+      </c>
+      <c r="B43" s="154" t="s">
+        <v>592</v>
+      </c>
+      <c r="C43" s="33" t="s">
+        <v>815</v>
+      </c>
+      <c r="D43" s="33" t="s">
+        <v>816</v>
+      </c>
+      <c r="E43" s="35" t="s">
+        <v>529</v>
+      </c>
+      <c r="F43" s="117" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="70">
+      <c r="A44" s="102" t="s">
+        <v>414</v>
+      </c>
+      <c r="B44" s="154" t="s">
+        <v>592</v>
+      </c>
+      <c r="C44" s="33" t="s">
+        <v>870</v>
+      </c>
+      <c r="D44" s="33" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E44" s="35" t="s">
         <v>871</v>
       </c>
-      <c r="D30" s="61" t="s">
+      <c r="F44" s="117" t="s">
         <v>872</v>
       </c>
-      <c r="E30" s="61" t="s">
-        <v>873</v>
-      </c>
-      <c r="F30" s="120" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="56">
-      <c r="A31" s="166" t="s">
-        <v>379</v>
-      </c>
-      <c r="B31" s="167" t="s">
-        <v>592</v>
-      </c>
-      <c r="C31" s="61" t="s">
-        <v>875</v>
-      </c>
-      <c r="D31" s="61" t="s">
-        <v>876</v>
-      </c>
-      <c r="E31" s="61" t="s">
-        <v>877</v>
-      </c>
-      <c r="F31" s="120" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="84">
-      <c r="A32" s="166" t="s">
-        <v>379</v>
-      </c>
-      <c r="B32" s="167" t="s">
-        <v>592</v>
-      </c>
-      <c r="C32" s="61" t="s">
-        <v>886</v>
-      </c>
-      <c r="D32" s="61" t="s">
-        <v>887</v>
-      </c>
-      <c r="E32" s="61" t="s">
-        <v>888</v>
-      </c>
-      <c r="F32" s="120" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="112">
-      <c r="A33" s="102" t="s">
-        <v>379</v>
-      </c>
-      <c r="B33" s="154" t="s">
-        <v>1167</v>
-      </c>
-      <c r="C33" s="33" t="s">
-        <v>796</v>
-      </c>
-      <c r="D33" s="33" t="s">
-        <v>1168</v>
-      </c>
-      <c r="E33" s="33" t="s">
-        <v>797</v>
-      </c>
-      <c r="F33" s="117" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="28">
-      <c r="A34" s="107" t="s">
-        <v>379</v>
-      </c>
-      <c r="B34" s="160" t="s">
-        <v>799</v>
-      </c>
-      <c r="C34" s="36" t="s">
-        <v>409</v>
-      </c>
-      <c r="D34" s="36" t="s">
-        <v>410</v>
-      </c>
-      <c r="E34" s="36" t="s">
-        <v>411</v>
-      </c>
-      <c r="F34" s="122" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="28">
-      <c r="A35" s="101" t="s">
-        <v>379</v>
-      </c>
-      <c r="B35" s="151" t="s">
-        <v>788</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>1030</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>1031</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>1025</v>
-      </c>
-      <c r="F35" s="116" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="218" t="s">
-        <v>1032</v>
-      </c>
-      <c r="B36" s="219"/>
-      <c r="C36" s="219"/>
-      <c r="D36" s="219"/>
-      <c r="E36" s="219"/>
-      <c r="F36" s="220"/>
-    </row>
-    <row r="37" spans="1:6" ht="42">
-      <c r="A37" s="101" t="s">
-        <v>414</v>
-      </c>
-      <c r="B37" s="56" t="s">
-        <v>415</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>1033</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>1034</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>1035</v>
-      </c>
-      <c r="F37" s="116" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="84">
-      <c r="A38" s="102" t="s">
-        <v>414</v>
-      </c>
-      <c r="B38" s="154" t="s">
-        <v>592</v>
-      </c>
-      <c r="C38" s="33" t="s">
-        <v>894</v>
-      </c>
-      <c r="D38" s="33" t="s">
-        <v>895</v>
-      </c>
-      <c r="E38" s="35" t="s">
-        <v>896</v>
-      </c>
-      <c r="F38" s="117" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="28">
-      <c r="A39" s="105" t="s">
-        <v>414</v>
-      </c>
-      <c r="B39" s="60" t="s">
-        <v>416</v>
-      </c>
-      <c r="C39" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="D39" s="61" t="s">
-        <v>418</v>
-      </c>
-      <c r="E39" s="61" t="s">
-        <v>419</v>
-      </c>
-      <c r="F39" s="120" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="28">
-      <c r="A40" s="105" t="s">
-        <v>414</v>
-      </c>
-      <c r="B40" s="60" t="s">
-        <v>421</v>
-      </c>
-      <c r="C40" s="61" t="s">
-        <v>422</v>
-      </c>
-      <c r="D40" s="61" t="s">
-        <v>423</v>
-      </c>
-      <c r="E40" s="61" t="s">
-        <v>424</v>
-      </c>
-      <c r="F40" s="120" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="28">
-      <c r="A41" s="104" t="s">
-        <v>414</v>
-      </c>
-      <c r="B41" s="59" t="s">
-        <v>426</v>
-      </c>
-      <c r="C41" s="47" t="s">
-        <v>427</v>
-      </c>
-      <c r="D41" s="47" t="s">
-        <v>428</v>
-      </c>
-      <c r="E41" s="47" t="s">
-        <v>384</v>
-      </c>
-      <c r="F41" s="119" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="28">
-      <c r="A42" s="99" t="s">
-        <v>414</v>
-      </c>
-      <c r="B42" s="54" t="s">
-        <v>429</v>
-      </c>
-      <c r="C42" s="15" t="s">
-        <v>430</v>
-      </c>
-      <c r="D42" s="15" t="s">
-        <v>431</v>
-      </c>
-      <c r="E42" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="F42" s="85" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="70">
-      <c r="A43" s="99" t="s">
-        <v>414</v>
-      </c>
-      <c r="B43" s="54" t="s">
-        <v>1036</v>
-      </c>
-      <c r="C43" s="15" t="s">
-        <v>1037</v>
-      </c>
-      <c r="D43" s="15" t="s">
-        <v>1038</v>
-      </c>
-      <c r="E43" s="15" t="s">
-        <v>1039</v>
-      </c>
-      <c r="F43" s="85" t="s">
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="28">
-      <c r="A44" s="105" t="s">
-        <v>414</v>
-      </c>
-      <c r="B44" s="60" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C44" s="61" t="s">
-        <v>433</v>
-      </c>
-      <c r="D44" s="61" t="s">
-        <v>434</v>
-      </c>
-      <c r="E44" s="61" t="s">
-        <v>424</v>
-      </c>
-      <c r="F44" s="120" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="28">
+    </row>
+    <row r="45" spans="1:6" ht="56">
       <c r="A45" s="102" t="s">
         <v>414</v>
       </c>
-      <c r="B45" s="57" t="s">
-        <v>1088</v>
+      <c r="B45" s="154" t="s">
+        <v>592</v>
       </c>
       <c r="C45" s="33" t="s">
-        <v>436</v>
+        <v>873</v>
       </c>
       <c r="D45" s="33" t="s">
-        <v>1089</v>
+        <v>1171</v>
       </c>
       <c r="E45" s="35" t="s">
-        <v>437</v>
+        <v>874</v>
       </c>
       <c r="F45" s="117" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="28">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="45" customHeight="1">
       <c r="A46" s="102" t="s">
         <v>414</v>
       </c>
@@ -15356,16 +15350,16 @@
         <v>592</v>
       </c>
       <c r="C46" s="33" t="s">
-        <v>816</v>
+        <v>883</v>
       </c>
       <c r="D46" s="33" t="s">
-        <v>817</v>
+        <v>1172</v>
       </c>
       <c r="E46" s="35" t="s">
-        <v>529</v>
+        <v>884</v>
       </c>
       <c r="F46" s="117" t="s">
-        <v>818</v>
+        <v>885</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="28">
@@ -15373,13 +15367,13 @@
         <v>414</v>
       </c>
       <c r="B47" s="63" t="s">
-        <v>1090</v>
+        <v>1082</v>
       </c>
       <c r="C47" s="20" t="s">
         <v>439</v>
       </c>
       <c r="D47" s="20" t="s">
-        <v>1091</v>
+        <v>1164</v>
       </c>
       <c r="E47" s="20" t="s">
         <v>440</v>
@@ -15393,13 +15387,13 @@
         <v>414</v>
       </c>
       <c r="B48" s="152" t="s">
-        <v>1092</v>
+        <v>1083</v>
       </c>
       <c r="C48" s="61" t="s">
         <v>441</v>
       </c>
       <c r="D48" s="61" t="s">
-        <v>1093</v>
+        <v>1165</v>
       </c>
       <c r="E48" s="61" t="s">
         <v>442</v>
@@ -15419,10 +15413,10 @@
         <v>444</v>
       </c>
       <c r="D49" s="39" t="s">
+        <v>832</v>
+      </c>
+      <c r="E49" s="39" t="s">
         <v>833</v>
-      </c>
-      <c r="E49" s="39" t="s">
-        <v>834</v>
       </c>
       <c r="F49" s="118" t="s">
         <v>446</v>
@@ -15433,19 +15427,19 @@
         <v>414</v>
       </c>
       <c r="B50" s="53" t="s">
+        <v>834</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>835</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="D50" s="5" t="s">
         <v>836</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="E50" s="5" t="s">
         <v>837</v>
       </c>
-      <c r="E50" s="5" t="s">
+      <c r="F50" s="86" t="s">
         <v>838</v>
-      </c>
-      <c r="F50" s="86" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="56">
@@ -15453,19 +15447,19 @@
         <v>414</v>
       </c>
       <c r="B51" s="159" t="s">
+        <v>839</v>
+      </c>
+      <c r="C51" s="5" t="s">
         <v>840</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="D51" s="5" t="s">
         <v>841</v>
       </c>
-      <c r="D51" s="5" t="s">
+      <c r="E51" s="5" t="s">
         <v>842</v>
       </c>
-      <c r="E51" s="5" t="s">
-        <v>843</v>
-      </c>
       <c r="F51" s="86" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="28">
@@ -15479,7 +15473,7 @@
         <v>448</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>378</v>
@@ -15528,7 +15522,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="56">
+    <row r="55" spans="1:6" ht="42">
       <c r="A55" s="103" t="s">
         <v>414</v>
       </c>
@@ -15539,24 +15533,24 @@
         <v>812</v>
       </c>
       <c r="D55" s="156" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E55" s="39" t="s">
         <v>813</v>
       </c>
-      <c r="E55" s="39" t="s">
+      <c r="F55" s="118" t="s">
         <v>814</v>
       </c>
-      <c r="F55" s="118" t="s">
-        <v>815</v>
-      </c>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="221" t="s">
-        <v>1073</v>
-      </c>
-      <c r="B56" s="222"/>
-      <c r="C56" s="222"/>
-      <c r="D56" s="222"/>
-      <c r="E56" s="222"/>
-      <c r="F56" s="223"/>
+      <c r="A56" s="219" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B56" s="220"/>
+      <c r="C56" s="220"/>
+      <c r="D56" s="220"/>
+      <c r="E56" s="220"/>
+      <c r="F56" s="221"/>
     </row>
     <row r="57" spans="1:6" ht="28">
       <c r="A57" s="101" t="s">
@@ -15663,13 +15657,13 @@
         <v>456</v>
       </c>
       <c r="B62" s="60" t="s">
-        <v>1094</v>
+        <v>1084</v>
       </c>
       <c r="C62" s="61" t="s">
         <v>477</v>
       </c>
       <c r="D62" s="61" t="s">
-        <v>1095</v>
+        <v>1085</v>
       </c>
       <c r="E62" s="61" t="s">
         <v>424</v>
@@ -15683,7 +15677,7 @@
         <v>456</v>
       </c>
       <c r="B63" s="63" t="s">
-        <v>1042</v>
+        <v>1035</v>
       </c>
       <c r="C63" s="20" t="s">
         <v>479</v>
@@ -15703,13 +15697,13 @@
         <v>456</v>
       </c>
       <c r="B64" s="60" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C64" s="61" t="s">
         <v>484</v>
       </c>
       <c r="D64" s="61" t="s">
-        <v>1096</v>
+        <v>1086</v>
       </c>
       <c r="E64" s="61" t="s">
         <v>478</v>
@@ -15723,13 +15717,13 @@
         <v>456</v>
       </c>
       <c r="B65" s="91" t="s">
-        <v>1097</v>
+        <v>1087</v>
       </c>
       <c r="C65" s="92" t="s">
         <v>768</v>
       </c>
       <c r="D65" s="92" t="s">
-        <v>1098</v>
+        <v>1088</v>
       </c>
       <c r="E65" s="92" t="s">
         <v>769</v>
@@ -15817,14 +15811,14 @@
       </c>
     </row>
     <row r="70" spans="1:6">
-      <c r="A70" s="221" t="s">
-        <v>1074</v>
-      </c>
-      <c r="B70" s="222"/>
-      <c r="C70" s="222"/>
-      <c r="D70" s="222"/>
-      <c r="E70" s="222"/>
-      <c r="F70" s="223"/>
+      <c r="A70" s="219" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B70" s="220"/>
+      <c r="C70" s="220"/>
+      <c r="D70" s="220"/>
+      <c r="E70" s="220"/>
+      <c r="F70" s="221"/>
     </row>
     <row r="71" spans="1:6" ht="28">
       <c r="A71" s="101" t="s">
@@ -15977,7 +15971,7 @@
         <v>530</v>
       </c>
       <c r="D78" s="61" t="s">
-        <v>1099</v>
+        <v>1167</v>
       </c>
       <c r="E78" s="61" t="s">
         <v>531</v>
@@ -15986,18 +15980,18 @@
         <v>532</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="42">
+    <row r="79" spans="1:6" ht="28">
       <c r="A79" s="104" t="s">
         <v>502</v>
       </c>
       <c r="B79" s="59" t="s">
-        <v>1100</v>
+        <v>1089</v>
       </c>
       <c r="C79" s="47" t="s">
         <v>533</v>
       </c>
       <c r="D79" s="47" t="s">
-        <v>1101</v>
+        <v>1168</v>
       </c>
       <c r="E79" s="47" t="s">
         <v>529</v>
@@ -16011,7 +16005,7 @@
         <v>502</v>
       </c>
       <c r="B80" s="63" t="s">
-        <v>1102</v>
+        <v>1090</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>535</v>
@@ -16227,14 +16221,14 @@
       </c>
     </row>
     <row r="91" spans="1:6">
-      <c r="A91" s="224" t="s">
-        <v>1075</v>
-      </c>
-      <c r="B91" s="225"/>
-      <c r="C91" s="225"/>
-      <c r="D91" s="225"/>
-      <c r="E91" s="225"/>
-      <c r="F91" s="226"/>
+      <c r="A91" s="222" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B91" s="223"/>
+      <c r="C91" s="223"/>
+      <c r="D91" s="223"/>
+      <c r="E91" s="223"/>
+      <c r="F91" s="224"/>
     </row>
     <row r="92" spans="1:6" ht="28">
       <c r="A92" s="101" t="s">
@@ -16359,16 +16353,16 @@
         <v>559</v>
       </c>
       <c r="B98" s="60" t="s">
-        <v>1083</v>
+        <v>1076</v>
       </c>
       <c r="C98" s="61" t="s">
-        <v>1080</v>
+        <v>1073</v>
       </c>
       <c r="D98" s="61" t="s">
-        <v>1081</v>
+        <v>1074</v>
       </c>
       <c r="E98" s="61" t="s">
-        <v>1082</v>
+        <v>1075</v>
       </c>
       <c r="F98" s="120" t="s">
         <v>578</v>
@@ -16379,13 +16373,13 @@
         <v>559</v>
       </c>
       <c r="B99" s="60" t="s">
-        <v>1084</v>
+        <v>1077</v>
       </c>
       <c r="C99" s="61" t="s">
         <v>579</v>
       </c>
       <c r="D99" s="61" t="s">
-        <v>1085</v>
+        <v>1078</v>
       </c>
       <c r="E99" s="61" t="s">
         <v>580</v>
@@ -16399,13 +16393,13 @@
         <v>559</v>
       </c>
       <c r="B100" s="63" t="s">
-        <v>1086</v>
+        <v>1079</v>
       </c>
       <c r="C100" s="20" t="s">
         <v>582</v>
       </c>
       <c r="D100" s="20" t="s">
-        <v>1087</v>
+        <v>1080</v>
       </c>
       <c r="E100" s="20" t="s">
         <v>583</v>
@@ -16462,16 +16456,16 @@
         <v>592</v>
       </c>
       <c r="C103" s="61" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="D103" s="61" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="E103" s="61" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="F103" s="120" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="28">
@@ -16560,27 +16554,27 @@
         <v>592</v>
       </c>
       <c r="C108" s="39" t="s">
+        <v>820</v>
+      </c>
+      <c r="D108" s="39" t="s">
         <v>821</v>
-      </c>
-      <c r="D108" s="39" t="s">
-        <v>822</v>
       </c>
       <c r="E108" s="39" t="s">
         <v>445</v>
       </c>
       <c r="F108" s="118" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="109" spans="1:6">
-      <c r="A109" s="224" t="s">
-        <v>1076</v>
-      </c>
-      <c r="B109" s="225"/>
-      <c r="C109" s="225"/>
-      <c r="D109" s="225"/>
-      <c r="E109" s="225"/>
-      <c r="F109" s="226"/>
+      <c r="A109" s="222" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B109" s="223"/>
+      <c r="C109" s="223"/>
+      <c r="D109" s="223"/>
+      <c r="E109" s="223"/>
+      <c r="F109" s="224"/>
     </row>
     <row r="110" spans="1:6" ht="28">
       <c r="A110" s="101" t="s">
@@ -16707,13 +16701,13 @@
         <v>595</v>
       </c>
       <c r="B116" s="57" t="s">
-        <v>1103</v>
+        <v>1091</v>
       </c>
       <c r="C116" s="33" t="s">
-        <v>1078</v>
+        <v>1071</v>
       </c>
       <c r="D116" s="33" t="s">
-        <v>1079</v>
+        <v>1072</v>
       </c>
       <c r="E116" s="33" t="s">
         <v>612</v>
@@ -16727,13 +16721,13 @@
         <v>595</v>
       </c>
       <c r="B117" s="60" t="s">
-        <v>1104</v>
+        <v>1092</v>
       </c>
       <c r="C117" s="61" t="s">
         <v>613</v>
       </c>
       <c r="D117" s="61" t="s">
-        <v>1105</v>
+        <v>1169</v>
       </c>
       <c r="E117" s="61" t="s">
         <v>407</v>
@@ -16790,16 +16784,16 @@
         <v>621</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="D120" s="15" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="E120" s="15" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="F120" s="85" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="28">
@@ -16890,16 +16884,16 @@
         <v>449</v>
       </c>
       <c r="C125" s="39" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="D125" s="39" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="E125" s="39" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="F125" s="118" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="32">
@@ -16910,10 +16904,10 @@
         <v>449</v>
       </c>
       <c r="C126" s="47" t="s">
+        <v>823</v>
+      </c>
+      <c r="D126" s="47" t="s">
         <v>824</v>
-      </c>
-      <c r="D126" s="47" t="s">
-        <v>825</v>
       </c>
       <c r="E126" s="47" t="s">
         <v>452</v>
@@ -16923,14 +16917,14 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="A127" s="227" t="s">
+      <c r="A127" s="225" t="s">
         <v>635</v>
       </c>
-      <c r="B127" s="228"/>
-      <c r="C127" s="228"/>
-      <c r="D127" s="228"/>
-      <c r="E127" s="228"/>
-      <c r="F127" s="229"/>
+      <c r="B127" s="226"/>
+      <c r="C127" s="226"/>
+      <c r="D127" s="226"/>
+      <c r="E127" s="226"/>
+      <c r="F127" s="227"/>
     </row>
     <row r="128" spans="1:6" ht="28">
       <c r="A128" s="101" t="s">
@@ -17123,7 +17117,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A33:F33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -17146,22 +17140,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="230" t="s">
-        <v>1006</v>
-      </c>
-      <c r="B1" s="230"/>
-      <c r="C1" s="230"/>
-      <c r="D1" s="230"/>
-      <c r="E1" s="230"/>
+      <c r="A1" s="228" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B1" s="228"/>
+      <c r="C1" s="228"/>
+      <c r="D1" s="228"/>
+      <c r="E1" s="228"/>
     </row>
     <row r="3" spans="1:5" ht="24" customHeight="1">
-      <c r="A3" s="231" t="s">
-        <v>1051</v>
-      </c>
-      <c r="B3" s="231"/>
-      <c r="C3" s="231"/>
-      <c r="D3" s="231"/>
-      <c r="E3" s="231"/>
+      <c r="A3" s="229" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B3" s="229"/>
+      <c r="C3" s="229"/>
+      <c r="D3" s="229"/>
+      <c r="E3" s="229"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="12" t="s">
@@ -17185,13 +17179,13 @@
         <v>43</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1052</v>
+        <v>1045</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>1050</v>
+        <v>1043</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>1053</v>
+        <v>1046</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>44</v>
@@ -17236,7 +17230,7 @@
         <v>54</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>55</v>
@@ -17321,30 +17315,30 @@
         <v>58</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="42" customHeight="1">
       <c r="A14" s="20" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="E14" s="23" t="s">
         <v>62</v>
@@ -17352,19 +17346,19 @@
     </row>
     <row r="15" spans="1:5" ht="56" customHeight="1">
       <c r="A15" s="20" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="C15" s="22" t="s">
+        <v>885</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>888</v>
+      </c>
+      <c r="E15" s="23" t="s">
         <v>889</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>892</v>
-      </c>
-      <c r="E15" s="23" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="70" customHeight="1">
@@ -17372,30 +17366,30 @@
         <v>80</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="62" customHeight="1">
       <c r="A17" s="20" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="E17" s="23" t="s">
         <v>94</v>
@@ -17406,16 +17400,16 @@
         <v>45</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="62" customHeight="1">
@@ -17423,27 +17417,27 @@
         <v>45</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="30" customHeight="1"/>
     <row r="21" spans="1:5" ht="30" customHeight="1">
-      <c r="A21" s="209" t="s">
+      <c r="A21" s="207" t="s">
         <v>67</v>
       </c>
-      <c r="B21" s="209"/>
-      <c r="C21" s="209"/>
-      <c r="D21" s="209"/>
-      <c r="E21" s="209"/>
+      <c r="B21" s="207"/>
+      <c r="C21" s="207"/>
+      <c r="D21" s="207"/>
+      <c r="E21" s="207"/>
     </row>
     <row r="22" spans="1:5" ht="30" customHeight="1">
       <c r="A22" s="12" t="s">
@@ -17473,7 +17467,7 @@
         <v>29</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="E23" s="18" t="s">
         <v>69</v>
@@ -17524,7 +17518,7 @@
         <v>82</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>83</v>
@@ -17535,13 +17529,13 @@
         <v>84</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>85</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="E27" s="18" t="s">
         <v>86</v>
@@ -17586,13 +17580,13 @@
         <v>75</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="E30" s="18" t="s">
         <v>189</v>
@@ -17603,27 +17597,27 @@
         <v>75</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="27.75" customHeight="1"/>
     <row r="33" spans="1:5" ht="30" customHeight="1">
-      <c r="A33" s="211" t="s">
+      <c r="A33" s="209" t="s">
         <v>91</v>
       </c>
-      <c r="B33" s="211"/>
-      <c r="C33" s="211"/>
-      <c r="D33" s="211"/>
-      <c r="E33" s="211"/>
+      <c r="B33" s="209"/>
+      <c r="C33" s="209"/>
+      <c r="D33" s="209"/>
+      <c r="E33" s="209"/>
     </row>
     <row r="34" spans="1:5" ht="30" customHeight="1">
       <c r="A34" s="12" t="s">
@@ -17814,33 +17808,33 @@
     </row>
     <row r="45" spans="1:5" ht="140">
       <c r="A45" s="20" t="s">
+        <v>901</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>902</v>
+      </c>
+      <c r="C45" s="22" t="s">
+        <v>903</v>
+      </c>
+      <c r="D45" s="20" t="s">
+        <v>904</v>
+      </c>
+      <c r="E45" s="23" t="s">
         <v>905</v>
-      </c>
-      <c r="B45" s="21" t="s">
-        <v>906</v>
-      </c>
-      <c r="C45" s="22" t="s">
-        <v>907</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>908</v>
-      </c>
-      <c r="E45" s="23" t="s">
-        <v>909</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="154">
       <c r="A46" s="20" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="E46" s="23" t="s">
         <v>167</v>
@@ -17851,13 +17845,13 @@
         <v>58</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="D47" s="20" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="E47" s="23" t="s">
         <v>192</v>
@@ -17868,13 +17862,13 @@
         <v>58</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="D48" s="20" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="E48" s="23" t="s">
         <v>192</v>
@@ -17885,30 +17879,30 @@
         <v>75</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="E49" s="23" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="62" customHeight="1">
       <c r="A50" s="20" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="D50" s="20" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="E50" s="23" t="s">
         <v>57</v>
@@ -17919,16 +17913,16 @@
         <v>75</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="D51" s="20" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="E51" s="23" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="62" customHeight="1"/>
@@ -17961,24 +17955,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18">
-      <c r="A1" s="187" t="s">
-        <v>959</v>
-      </c>
-      <c r="B1" s="188"/>
-      <c r="C1" s="188"/>
-      <c r="D1" s="188"/>
-      <c r="E1" s="188"/>
-      <c r="F1" s="189"/>
+      <c r="A1" s="185" t="s">
+        <v>955</v>
+      </c>
+      <c r="B1" s="186"/>
+      <c r="C1" s="186"/>
+      <c r="D1" s="186"/>
+      <c r="E1" s="186"/>
+      <c r="F1" s="187"/>
     </row>
     <row r="2" spans="1:6" ht="41" customHeight="1">
-      <c r="A2" s="190" t="s">
-        <v>960</v>
-      </c>
-      <c r="B2" s="191"/>
-      <c r="C2" s="191"/>
-      <c r="D2" s="191"/>
-      <c r="E2" s="191"/>
-      <c r="F2" s="192"/>
+      <c r="A2" s="188" t="s">
+        <v>956</v>
+      </c>
+      <c r="B2" s="189"/>
+      <c r="C2" s="189"/>
+      <c r="D2" s="189"/>
+      <c r="E2" s="189"/>
+      <c r="F2" s="190"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="77" t="s">
@@ -18001,14 +17995,14 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="193" t="s">
-        <v>1054</v>
-      </c>
-      <c r="B4" s="194"/>
-      <c r="C4" s="194"/>
-      <c r="D4" s="194"/>
-      <c r="E4" s="194"/>
-      <c r="F4" s="195"/>
+      <c r="A4" s="191" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B4" s="192"/>
+      <c r="C4" s="192"/>
+      <c r="D4" s="192"/>
+      <c r="E4" s="192"/>
+      <c r="F4" s="193"/>
     </row>
     <row r="5" spans="1:6" ht="28">
       <c r="A5" s="78" t="s">
@@ -18018,16 +18012,16 @@
         <v>134</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1055</v>
+        <v>1048</v>
       </c>
       <c r="D5" s="27" t="s">
         <v>135</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>1056</v>
+        <v>1049</v>
       </c>
       <c r="F5" s="84" t="s">
-        <v>1057</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="28">
@@ -18038,16 +18032,16 @@
         <v>137</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>1058</v>
+        <v>1051</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>1059</v>
+        <v>1052</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>1060</v>
+        <v>1053</v>
       </c>
       <c r="F6" s="85" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28">
@@ -18058,16 +18052,16 @@
         <v>139</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>1061</v>
+        <v>1054</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>53</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>1062</v>
+        <v>1055</v>
       </c>
       <c r="F7" s="86" t="s">
-        <v>1063</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="28">
@@ -18078,16 +18072,16 @@
         <v>4.5</v>
       </c>
       <c r="C8" s="76" t="s">
-        <v>1064</v>
+        <v>1057</v>
       </c>
       <c r="D8" s="75" t="s">
         <v>682</v>
       </c>
       <c r="E8" s="76" t="s">
-        <v>1065</v>
+        <v>1058</v>
       </c>
       <c r="F8" s="87" t="s">
-        <v>1066</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="28">
@@ -18098,27 +18092,27 @@
         <v>4.5</v>
       </c>
       <c r="C9" s="66" t="s">
-        <v>1067</v>
+        <v>1060</v>
       </c>
       <c r="D9" s="68" t="s">
         <v>526</v>
       </c>
       <c r="E9" s="66" t="s">
-        <v>1068</v>
+        <v>1061</v>
       </c>
       <c r="F9" s="88" t="s">
-        <v>1069</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="193" t="s">
+      <c r="A10" s="191" t="s">
         <v>141</v>
       </c>
-      <c r="B10" s="194"/>
-      <c r="C10" s="194"/>
-      <c r="D10" s="194"/>
-      <c r="E10" s="194"/>
-      <c r="F10" s="195"/>
+      <c r="B10" s="192"/>
+      <c r="C10" s="192"/>
+      <c r="D10" s="192"/>
+      <c r="E10" s="192"/>
+      <c r="F10" s="193"/>
     </row>
     <row r="11" spans="1:6" ht="70">
       <c r="A11" s="78" t="s">
@@ -18134,7 +18128,7 @@
         <v>49</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F11" s="84" t="s">
         <v>143</v>
@@ -18225,16 +18219,16 @@
         <v>757</v>
       </c>
       <c r="B16" s="165" t="s">
+        <v>862</v>
+      </c>
+      <c r="C16" s="66" t="s">
         <v>863</v>
-      </c>
-      <c r="C16" s="66" t="s">
-        <v>864</v>
       </c>
       <c r="D16" s="68" t="s">
         <v>682</v>
       </c>
       <c r="E16" s="66" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F16" s="88" t="s">
         <v>406</v>
@@ -18245,70 +18239,70 @@
         <v>760</v>
       </c>
       <c r="B17" s="165" t="s">
+        <v>865</v>
+      </c>
+      <c r="C17" s="66" t="s">
         <v>866</v>
       </c>
-      <c r="C17" s="66" t="s">
+      <c r="D17" s="68" t="s">
+        <v>851</v>
+      </c>
+      <c r="E17" s="66" t="s">
         <v>867</v>
-      </c>
-      <c r="D17" s="68" t="s">
-        <v>852</v>
-      </c>
-      <c r="E17" s="66" t="s">
-        <v>868</v>
       </c>
       <c r="F17" s="88" t="s">
         <v>717</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="56">
-      <c r="A18" s="168" t="s">
-        <v>845</v>
-      </c>
-      <c r="B18" s="169" t="s">
+      <c r="A18" s="166" t="s">
+        <v>844</v>
+      </c>
+      <c r="B18" s="167" t="s">
         <v>216</v>
       </c>
-      <c r="C18" s="170" t="s">
-        <v>990</v>
-      </c>
-      <c r="D18" s="171" t="s">
-        <v>947</v>
-      </c>
-      <c r="E18" s="170" t="s">
-        <v>968</v>
-      </c>
-      <c r="F18" s="172" t="s">
-        <v>955</v>
+      <c r="C18" s="168" t="s">
+        <v>986</v>
+      </c>
+      <c r="D18" s="169" t="s">
+        <v>943</v>
+      </c>
+      <c r="E18" s="168" t="s">
+        <v>964</v>
+      </c>
+      <c r="F18" s="170" t="s">
+        <v>951</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="70">
-      <c r="A19" s="168" t="s">
-        <v>849</v>
-      </c>
-      <c r="B19" s="169" t="s">
+      <c r="A19" s="166" t="s">
+        <v>848</v>
+      </c>
+      <c r="B19" s="167" t="s">
         <v>216</v>
       </c>
-      <c r="C19" s="170" t="s">
-        <v>991</v>
-      </c>
-      <c r="D19" s="171" t="s">
-        <v>947</v>
-      </c>
-      <c r="E19" s="170" t="s">
-        <v>969</v>
-      </c>
-      <c r="F19" s="172" t="s">
-        <v>957</v>
+      <c r="C19" s="168" t="s">
+        <v>987</v>
+      </c>
+      <c r="D19" s="169" t="s">
+        <v>943</v>
+      </c>
+      <c r="E19" s="168" t="s">
+        <v>965</v>
+      </c>
+      <c r="F19" s="170" t="s">
+        <v>953</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="193" t="s">
+      <c r="A20" s="191" t="s">
         <v>152</v>
       </c>
-      <c r="B20" s="194"/>
-      <c r="C20" s="194"/>
-      <c r="D20" s="194"/>
-      <c r="E20" s="194"/>
-      <c r="F20" s="195"/>
+      <c r="B20" s="192"/>
+      <c r="C20" s="192"/>
+      <c r="D20" s="192"/>
+      <c r="E20" s="192"/>
+      <c r="F20" s="193"/>
     </row>
     <row r="21" spans="1:6" ht="28">
       <c r="A21" s="78" t="s">
@@ -18318,7 +18312,7 @@
         <v>154</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="D21" s="27" t="s">
         <v>57</v>
@@ -18411,14 +18405,14 @@
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="193" t="s">
+      <c r="A26" s="191" t="s">
         <v>165</v>
       </c>
-      <c r="B26" s="194"/>
-      <c r="C26" s="194"/>
-      <c r="D26" s="194"/>
-      <c r="E26" s="194"/>
-      <c r="F26" s="195"/>
+      <c r="B26" s="192"/>
+      <c r="C26" s="192"/>
+      <c r="D26" s="192"/>
+      <c r="E26" s="192"/>
+      <c r="F26" s="193"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="78" t="s">
@@ -18448,13 +18442,13 @@
         <v>137</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="D28" s="18" t="s">
         <v>170</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="F28" s="85" t="s">
         <v>171</v>
@@ -18488,13 +18482,13 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C30" s="76" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="D30" s="75" t="s">
         <v>140</v>
       </c>
       <c r="E30" s="76" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="F30" s="87" t="s">
         <v>690</v>
@@ -18521,14 +18515,14 @@
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="193" t="s">
+      <c r="A32" s="191" t="s">
         <v>176</v>
       </c>
-      <c r="B32" s="194"/>
-      <c r="C32" s="194"/>
-      <c r="D32" s="194"/>
-      <c r="E32" s="194"/>
-      <c r="F32" s="195"/>
+      <c r="B32" s="192"/>
+      <c r="C32" s="192"/>
+      <c r="D32" s="192"/>
+      <c r="E32" s="192"/>
+      <c r="F32" s="193"/>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="78" t="s">
@@ -18631,14 +18625,14 @@
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="196" t="s">
+      <c r="A38" s="194" t="s">
         <v>184</v>
       </c>
-      <c r="B38" s="197"/>
-      <c r="C38" s="197"/>
-      <c r="D38" s="197"/>
-      <c r="E38" s="197"/>
-      <c r="F38" s="198"/>
+      <c r="B38" s="195"/>
+      <c r="C38" s="195"/>
+      <c r="D38" s="195"/>
+      <c r="E38" s="195"/>
+      <c r="F38" s="196"/>
     </row>
     <row r="39" spans="1:6" ht="28">
       <c r="A39" s="78" t="s">
@@ -18668,13 +18662,13 @@
         <v>139</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="D40" s="18" t="s">
         <v>162</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="F40" s="85" t="s">
         <v>186</v>
@@ -18741,14 +18735,14 @@
       </c>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="196" t="s">
+      <c r="A44" s="194" t="s">
         <v>191</v>
       </c>
-      <c r="B44" s="197"/>
-      <c r="C44" s="197"/>
-      <c r="D44" s="197"/>
-      <c r="E44" s="197"/>
-      <c r="F44" s="198"/>
+      <c r="B44" s="195"/>
+      <c r="C44" s="195"/>
+      <c r="D44" s="195"/>
+      <c r="E44" s="195"/>
+      <c r="F44" s="196"/>
     </row>
     <row r="45" spans="1:6" ht="84">
       <c r="A45" s="78" t="s">
@@ -18758,13 +18752,13 @@
         <v>137</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D45" s="27" t="s">
         <v>192</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="F45" s="84" t="s">
         <v>193</v>
@@ -18798,13 +18792,13 @@
         <v>134</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>198</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="F47" s="86" t="s">
         <v>29</v>
@@ -18818,13 +18812,13 @@
         <v>4.5</v>
       </c>
       <c r="C48" s="76" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="D48" s="75" t="s">
         <v>79</v>
       </c>
       <c r="E48" s="76" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="F48" s="87" t="s">
         <v>197</v>
@@ -18851,34 +18845,34 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="84">
-      <c r="A50" s="168" t="s">
+      <c r="A50" s="166" t="s">
         <v>757</v>
       </c>
-      <c r="B50" s="171" t="s">
+      <c r="B50" s="169" t="s">
         <v>216</v>
       </c>
-      <c r="C50" s="170" t="s">
-        <v>997</v>
-      </c>
-      <c r="D50" s="171" t="s">
-        <v>952</v>
-      </c>
-      <c r="E50" s="170" t="s">
-        <v>970</v>
-      </c>
-      <c r="F50" s="172" t="s">
-        <v>950</v>
+      <c r="C50" s="168" t="s">
+        <v>993</v>
+      </c>
+      <c r="D50" s="169" t="s">
+        <v>948</v>
+      </c>
+      <c r="E50" s="168" t="s">
+        <v>966</v>
+      </c>
+      <c r="F50" s="170" t="s">
+        <v>946</v>
       </c>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="196" t="s">
+      <c r="A51" s="194" t="s">
         <v>199</v>
       </c>
-      <c r="B51" s="197"/>
-      <c r="C51" s="197"/>
-      <c r="D51" s="197"/>
-      <c r="E51" s="197"/>
-      <c r="F51" s="198"/>
+      <c r="B51" s="195"/>
+      <c r="C51" s="195"/>
+      <c r="D51" s="195"/>
+      <c r="E51" s="195"/>
+      <c r="F51" s="196"/>
     </row>
     <row r="52" spans="1:6" ht="56">
       <c r="A52" s="78" t="s">
@@ -18888,13 +18882,13 @@
         <v>187</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="D52" s="27" t="s">
         <v>140</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="F52" s="84" t="s">
         <v>200</v>
@@ -18981,34 +18975,34 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="84">
-      <c r="A57" s="173" t="s">
+      <c r="A57" s="171" t="s">
         <v>757</v>
       </c>
-      <c r="B57" s="174" t="s">
+      <c r="B57" s="172" t="s">
         <v>216</v>
       </c>
-      <c r="C57" s="175" t="s">
-        <v>999</v>
-      </c>
-      <c r="D57" s="174" t="s">
+      <c r="C57" s="173" t="s">
+        <v>995</v>
+      </c>
+      <c r="D57" s="172" t="s">
         <v>189</v>
       </c>
-      <c r="E57" s="175" t="s">
-        <v>971</v>
-      </c>
-      <c r="F57" s="176" t="s">
-        <v>948</v>
+      <c r="E57" s="173" t="s">
+        <v>967</v>
+      </c>
+      <c r="F57" s="174" t="s">
+        <v>944</v>
       </c>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="196" t="s">
+      <c r="A58" s="194" t="s">
         <v>205</v>
       </c>
-      <c r="B58" s="197"/>
-      <c r="C58" s="197"/>
-      <c r="D58" s="197"/>
-      <c r="E58" s="197"/>
-      <c r="F58" s="198"/>
+      <c r="B58" s="195"/>
+      <c r="C58" s="195"/>
+      <c r="D58" s="195"/>
+      <c r="E58" s="195"/>
+      <c r="F58" s="196"/>
     </row>
     <row r="59" spans="1:6" ht="28">
       <c r="A59" s="78" t="s">
@@ -19038,13 +19032,13 @@
         <v>134</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="D60" s="18" t="s">
         <v>198</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="F60" s="85" t="s">
         <v>29</v>
@@ -19058,13 +19052,13 @@
         <v>139</v>
       </c>
       <c r="C61" s="29" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>140</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="F61" s="86" t="s">
         <v>209</v>
@@ -19111,14 +19105,14 @@
       </c>
     </row>
     <row r="64" spans="1:6">
-      <c r="A64" s="196" t="s">
+      <c r="A64" s="194" t="s">
         <v>210</v>
       </c>
-      <c r="B64" s="197"/>
-      <c r="C64" s="197"/>
-      <c r="D64" s="197"/>
-      <c r="E64" s="197"/>
-      <c r="F64" s="198"/>
+      <c r="B64" s="195"/>
+      <c r="C64" s="195"/>
+      <c r="D64" s="195"/>
+      <c r="E64" s="195"/>
+      <c r="F64" s="196"/>
     </row>
     <row r="65" spans="1:6" ht="28">
       <c r="A65" s="78" t="s">
@@ -19148,13 +19142,13 @@
         <v>137</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="D66" s="18" t="s">
         <v>86</v>
       </c>
       <c r="E66" s="25" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="F66" s="85" t="s">
         <v>85</v>
@@ -19181,14 +19175,14 @@
       </c>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="199" t="s">
+      <c r="A68" s="197" t="s">
         <v>221</v>
       </c>
-      <c r="B68" s="200"/>
-      <c r="C68" s="200"/>
-      <c r="D68" s="200"/>
-      <c r="E68" s="200"/>
-      <c r="F68" s="201"/>
+      <c r="B68" s="198"/>
+      <c r="C68" s="198"/>
+      <c r="D68" s="198"/>
+      <c r="E68" s="198"/>
+      <c r="F68" s="199"/>
     </row>
     <row r="69" spans="1:6" ht="70">
       <c r="A69" s="78" t="s">
@@ -19204,7 +19198,7 @@
         <v>102</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="F69" s="84" t="s">
         <v>100</v>
@@ -19278,16 +19272,16 @@
         <v>4.3</v>
       </c>
       <c r="C73" s="66" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="D73" s="68" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="E73" s="66" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="F73" s="88" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="28">
@@ -19332,19 +19326,19 @@
     </row>
     <row r="76" spans="1:6" ht="42">
       <c r="A76" s="82" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B76" s="165" t="s">
+        <v>854</v>
+      </c>
+      <c r="C76" s="66" t="s">
         <v>855</v>
       </c>
-      <c r="C76" s="66" t="s">
+      <c r="D76" s="68" t="s">
         <v>856</v>
       </c>
-      <c r="D76" s="68" t="s">
+      <c r="E76" s="66" t="s">
         <v>857</v>
-      </c>
-      <c r="E76" s="66" t="s">
-        <v>858</v>
       </c>
       <c r="F76" s="88" t="s">
         <v>245</v>
@@ -19352,33 +19346,33 @@
     </row>
     <row r="77" spans="1:6" ht="42">
       <c r="A77" s="82" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B77" s="165" t="s">
+        <v>858</v>
+      </c>
+      <c r="C77" s="66" t="s">
         <v>859</v>
       </c>
-      <c r="C77" s="66" t="s">
+      <c r="D77" s="68" t="s">
+        <v>851</v>
+      </c>
+      <c r="E77" s="66" t="s">
         <v>860</v>
       </c>
-      <c r="D77" s="68" t="s">
-        <v>852</v>
-      </c>
-      <c r="E77" s="66" t="s">
+      <c r="F77" s="88" t="s">
         <v>861</v>
       </c>
-      <c r="F77" s="88" t="s">
-        <v>862</v>
-      </c>
     </row>
     <row r="78" spans="1:6">
-      <c r="A78" s="199" t="s">
+      <c r="A78" s="197" t="s">
         <v>227</v>
       </c>
-      <c r="B78" s="200"/>
-      <c r="C78" s="200"/>
-      <c r="D78" s="200"/>
-      <c r="E78" s="200"/>
-      <c r="F78" s="201"/>
+      <c r="B78" s="198"/>
+      <c r="C78" s="198"/>
+      <c r="D78" s="198"/>
+      <c r="E78" s="198"/>
+      <c r="F78" s="199"/>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="78" t="s">
@@ -19421,22 +19415,22 @@
       </c>
     </row>
     <row r="81" spans="1:6">
-      <c r="A81" s="177" t="s">
+      <c r="A81" s="175" t="s">
         <v>138</v>
       </c>
-      <c r="B81" s="178" t="s">
+      <c r="B81" s="176" t="s">
         <v>134</v>
       </c>
-      <c r="C81" s="179" t="s">
+      <c r="C81" s="177" t="s">
         <v>92</v>
       </c>
-      <c r="D81" s="178" t="s">
+      <c r="D81" s="176" t="s">
         <v>94</v>
       </c>
-      <c r="E81" s="179" t="s">
+      <c r="E81" s="177" t="s">
         <v>234</v>
       </c>
-      <c r="F81" s="180" t="s">
+      <c r="F81" s="178" t="s">
         <v>33</v>
       </c>
     </row>
@@ -19488,47 +19482,47 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="C84" s="163" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="D84" s="162" t="s">
         <v>167</v>
       </c>
       <c r="E84" s="163" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="F84" s="164" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="140">
-      <c r="A85" s="181" t="s">
+      <c r="A85" s="179" t="s">
         <v>153</v>
       </c>
-      <c r="B85" s="182">
+      <c r="B85" s="180">
         <v>4.8</v>
       </c>
-      <c r="C85" s="183" t="s">
-        <v>1004</v>
-      </c>
-      <c r="D85" s="182" t="s">
+      <c r="C85" s="181" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D85" s="180" t="s">
         <v>57</v>
       </c>
-      <c r="E85" s="183" t="s">
-        <v>972</v>
-      </c>
-      <c r="F85" s="184" t="s">
-        <v>962</v>
+      <c r="E85" s="181" t="s">
+        <v>968</v>
+      </c>
+      <c r="F85" s="182" t="s">
+        <v>958</v>
       </c>
     </row>
     <row r="86" spans="1:6">
-      <c r="A86" s="199" t="s">
+      <c r="A86" s="197" t="s">
         <v>235</v>
       </c>
-      <c r="B86" s="200"/>
-      <c r="C86" s="200"/>
-      <c r="D86" s="200"/>
-      <c r="E86" s="200"/>
-      <c r="F86" s="201"/>
+      <c r="B86" s="198"/>
+      <c r="C86" s="198"/>
+      <c r="D86" s="198"/>
+      <c r="E86" s="198"/>
+      <c r="F86" s="199"/>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="78" t="s">
@@ -19651,40 +19645,40 @@
       </c>
     </row>
     <row r="93" spans="1:6" ht="28">
-      <c r="A93" s="168" t="s">
+      <c r="A93" s="166" t="s">
         <v>760</v>
       </c>
-      <c r="B93" s="171" t="s">
+      <c r="B93" s="169" t="s">
         <v>216</v>
       </c>
-      <c r="C93" s="170" t="s">
+      <c r="C93" s="168" t="s">
         <v>766</v>
       </c>
-      <c r="D93" s="171" t="s">
+      <c r="D93" s="169" t="s">
         <v>246</v>
       </c>
-      <c r="E93" s="170" t="s">
+      <c r="E93" s="168" t="s">
         <v>767</v>
       </c>
-      <c r="F93" s="172" t="s">
+      <c r="F93" s="170" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="42">
       <c r="A94" s="82" t="s">
+        <v>844</v>
+      </c>
+      <c r="B94" s="165" t="s">
         <v>845</v>
       </c>
-      <c r="B94" s="165" t="s">
+      <c r="C94" s="66" t="s">
         <v>846</v>
-      </c>
-      <c r="C94" s="66" t="s">
-        <v>847</v>
       </c>
       <c r="D94" s="68" t="s">
         <v>167</v>
       </c>
       <c r="E94" s="66" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="F94" s="88" t="s">
         <v>226</v>
@@ -19692,69 +19686,69 @@
     </row>
     <row r="95" spans="1:6" ht="42">
       <c r="A95" s="82" t="s">
+        <v>848</v>
+      </c>
+      <c r="B95" s="165" t="s">
         <v>849</v>
       </c>
-      <c r="B95" s="165" t="s">
+      <c r="C95" s="66" t="s">
         <v>850</v>
       </c>
-      <c r="C95" s="66" t="s">
+      <c r="D95" s="68" t="s">
         <v>851</v>
       </c>
-      <c r="D95" s="68" t="s">
+      <c r="E95" s="66" t="s">
         <v>852</v>
       </c>
-      <c r="E95" s="66" t="s">
+      <c r="F95" s="88" t="s">
         <v>853</v>
-      </c>
-      <c r="F95" s="88" t="s">
-        <v>854</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="70">
       <c r="A96" s="82" t="s">
-        <v>978</v>
-      </c>
-      <c r="B96" s="186">
+        <v>974</v>
+      </c>
+      <c r="B96" s="184">
         <v>4.5</v>
       </c>
       <c r="C96" s="66" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D96" s="68" t="s">
         <v>145</v>
       </c>
       <c r="E96" s="66" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="F96" s="88" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
     </row>
     <row r="97" spans="1:6">
-      <c r="A97" s="199" t="s">
+      <c r="A97" s="197" t="s">
         <v>241</v>
       </c>
-      <c r="B97" s="200"/>
-      <c r="C97" s="200"/>
-      <c r="D97" s="200"/>
-      <c r="E97" s="200"/>
-      <c r="F97" s="201"/>
+      <c r="B97" s="198"/>
+      <c r="C97" s="198"/>
+      <c r="D97" s="198"/>
+      <c r="E97" s="198"/>
+      <c r="F97" s="199"/>
     </row>
     <row r="98" spans="1:6" ht="84">
       <c r="A98" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="B98" s="185">
+      <c r="B98" s="183">
         <v>5</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="D98" s="27" t="s">
         <v>57</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="F98" s="84" t="s">
         <v>242</v>
@@ -19821,14 +19815,14 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="68" customHeight="1" thickBot="1">
-      <c r="A102" s="202" t="s">
-        <v>1007</v>
-      </c>
-      <c r="B102" s="203"/>
-      <c r="C102" s="203"/>
-      <c r="D102" s="203"/>
-      <c r="E102" s="203"/>
-      <c r="F102" s="204"/>
+      <c r="A102" s="200" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B102" s="201"/>
+      <c r="C102" s="201"/>
+      <c r="D102" s="201"/>
+      <c r="E102" s="201"/>
+      <c r="F102" s="202"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -19870,12 +19864,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1">
-      <c r="A1" s="212" t="s">
+      <c r="A1" s="210" t="s">
         <v>247</v>
       </c>
-      <c r="B1" s="213"/>
-      <c r="C1" s="213"/>
-      <c r="D1" s="214"/>
+      <c r="B1" s="211"/>
+      <c r="C1" s="211"/>
+      <c r="D1" s="212"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="132"/>
@@ -19884,12 +19878,12 @@
       <c r="D2" s="142"/>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
-      <c r="A3" s="232" t="s">
+      <c r="A3" s="230" t="s">
         <v>248</v>
       </c>
-      <c r="B3" s="233"/>
-      <c r="C3" s="233"/>
-      <c r="D3" s="234"/>
+      <c r="B3" s="231"/>
+      <c r="C3" s="231"/>
+      <c r="D3" s="232"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="133" t="s">
@@ -19910,13 +19904,13 @@
         <v>252</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>1070</v>
+        <v>1063</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>1071</v>
+        <v>1064</v>
       </c>
       <c r="D5" s="144" t="s">
-        <v>1072</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="27.75" customHeight="1">
@@ -19952,7 +19946,7 @@
         <v>261</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="C8" s="41" t="s">
         <v>262</v>
@@ -19980,13 +19974,13 @@
         <v>792</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>1106</v>
+        <v>1093</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>1107</v>
+        <v>1094</v>
       </c>
       <c r="D10" s="148" t="s">
-        <v>1108</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="45" customHeight="1">
@@ -19994,13 +19988,13 @@
         <v>264</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>1109</v>
+        <v>1096</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>1110</v>
+        <v>1097</v>
       </c>
       <c r="D11" s="148" t="s">
-        <v>1111</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="45" customHeight="1">
@@ -20008,13 +20002,13 @@
         <v>253</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>1112</v>
+        <v>1099</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>1113</v>
+        <v>1100</v>
       </c>
       <c r="D12" s="148" t="s">
-        <v>1114</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="45" customHeight="1">
@@ -20022,13 +20016,13 @@
         <v>288</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>1115</v>
+        <v>1102</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>1116</v>
+        <v>1103</v>
       </c>
       <c r="D13" s="148" t="s">
-        <v>1117</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1">
@@ -20038,12 +20032,12 @@
       <c r="D14" s="142"/>
     </row>
     <row r="15" spans="1:4" ht="16">
-      <c r="A15" s="235" t="s">
+      <c r="A15" s="233" t="s">
         <v>268</v>
       </c>
-      <c r="B15" s="236"/>
-      <c r="C15" s="236"/>
-      <c r="D15" s="237"/>
+      <c r="B15" s="234"/>
+      <c r="C15" s="234"/>
+      <c r="D15" s="235"/>
     </row>
     <row r="16" spans="1:4" ht="24" customHeight="1">
       <c r="A16" s="133" t="s">
@@ -20069,8 +20063,8 @@
       <c r="C17" s="35" t="s">
         <v>270</v>
       </c>
-      <c r="D17" s="242" t="s">
-        <v>1142</v>
+      <c r="D17" s="240" t="s">
+        <v>1129</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1">
@@ -20173,30 +20167,30 @@
     </row>
     <row r="25" spans="1:4" ht="70">
       <c r="A25" s="138" t="s">
-        <v>1118</v>
+        <v>1105</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>1119</v>
+        <v>1106</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>1120</v>
+        <v>1107</v>
       </c>
       <c r="D25" s="148" t="s">
-        <v>1121</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="45" customHeight="1">
       <c r="A26" s="138" t="s">
-        <v>1122</v>
+        <v>1109</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>1123</v>
+        <v>1110</v>
       </c>
       <c r="C26" s="44" t="s">
-        <v>1124</v>
+        <v>1111</v>
       </c>
       <c r="D26" s="148" t="s">
-        <v>1125</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="45" customHeight="1">
@@ -20204,13 +20198,13 @@
         <v>253</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>1126</v>
+        <v>1113</v>
       </c>
       <c r="C27" s="44" t="s">
-        <v>1127</v>
+        <v>1114</v>
       </c>
       <c r="D27" s="148" t="s">
-        <v>1128</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="45" customHeight="1">
@@ -20218,13 +20212,13 @@
         <v>252</v>
       </c>
       <c r="B28" s="43" t="s">
-        <v>1129</v>
+        <v>1116</v>
       </c>
       <c r="C28" s="44" t="s">
-        <v>1130</v>
+        <v>1117</v>
       </c>
       <c r="D28" s="148" t="s">
-        <v>1131</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="30" customHeight="1">
@@ -20262,12 +20256,12 @@
       <c r="D31" s="142"/>
     </row>
     <row r="32" spans="1:4" ht="30" customHeight="1">
-      <c r="A32" s="238" t="s">
+      <c r="A32" s="236" t="s">
         <v>295</v>
       </c>
-      <c r="B32" s="239"/>
-      <c r="C32" s="239"/>
-      <c r="D32" s="240"/>
+      <c r="B32" s="237"/>
+      <c r="C32" s="237"/>
+      <c r="D32" s="238"/>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="133" t="s">
@@ -20358,13 +20352,13 @@
         <v>792</v>
       </c>
       <c r="B39" s="43" t="s">
-        <v>1132</v>
+        <v>1119</v>
       </c>
       <c r="C39" s="44" t="s">
-        <v>1133</v>
+        <v>1120</v>
       </c>
       <c r="D39" s="148" t="s">
-        <v>1134</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="45" customHeight="1">
@@ -20372,27 +20366,27 @@
         <v>257</v>
       </c>
       <c r="B40" s="43" t="s">
-        <v>1135</v>
+        <v>1122</v>
       </c>
       <c r="C40" s="44" t="s">
-        <v>1136</v>
+        <v>1123</v>
       </c>
       <c r="D40" s="148" t="s">
-        <v>1137</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="45" customHeight="1">
       <c r="A41" s="138" t="s">
-        <v>1138</v>
+        <v>1125</v>
       </c>
       <c r="B41" s="43" t="s">
-        <v>1141</v>
+        <v>1128</v>
       </c>
       <c r="C41" s="44" t="s">
-        <v>1139</v>
+        <v>1126</v>
       </c>
       <c r="D41" s="148" t="s">
-        <v>1140</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="27.75" customHeight="1">
@@ -20466,20 +20460,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1">
-      <c r="A1" s="241" t="s">
+      <c r="A1" s="239" t="s">
         <v>318</v>
       </c>
-      <c r="B1" s="241"/>
-      <c r="C1" s="241"/>
-      <c r="D1" s="241"/>
+      <c r="B1" s="239"/>
+      <c r="C1" s="239"/>
+      <c r="D1" s="239"/>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
-      <c r="A3" s="231" t="s">
+      <c r="A3" s="229" t="s">
         <v>248</v>
       </c>
-      <c r="B3" s="231"/>
-      <c r="C3" s="231"/>
-      <c r="D3" s="231"/>
+      <c r="B3" s="229"/>
+      <c r="C3" s="229"/>
+      <c r="D3" s="229"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="12" t="s">
@@ -20538,12 +20532,12 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="24" customHeight="1">
-      <c r="A9" s="209" t="s">
+      <c r="A9" s="207" t="s">
         <v>268</v>
       </c>
-      <c r="B9" s="209"/>
-      <c r="C9" s="209"/>
-      <c r="D9" s="209"/>
+      <c r="B9" s="207"/>
+      <c r="C9" s="207"/>
+      <c r="D9" s="207"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="12" t="s">
@@ -20588,12 +20582,12 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="24" customHeight="1">
-      <c r="A14" s="211" t="s">
+      <c r="A14" s="209" t="s">
         <v>295</v>
       </c>
-      <c r="B14" s="211"/>
-      <c r="C14" s="211"/>
-      <c r="D14" s="211"/>
+      <c r="B14" s="209"/>
+      <c r="C14" s="209"/>
+      <c r="D14" s="209"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="12" t="s">

--- a/tools/itinerary.xlsx
+++ b/tools/itinerary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jitwei/Library/Mobile Documents/com~apple~CloudDocs/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26598332-B75E-E346-A5B3-C345DDAEBA4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F572039E-4B6A-964F-8403-04F370DCD010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-6080" yWindow="-21000" windowWidth="38400" windowHeight="21000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1719" uniqueCount="1173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1725" uniqueCount="1185">
   <si>
     <r>
       <rPr>
@@ -6150,9 +6150,6 @@
     </r>
   </si>
   <si>
-    <t>20:00–21:00</t>
-  </si>
-  <si>
     <t>21:00–21:45</t>
   </si>
   <si>
@@ -6224,53 +6221,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Golden ginkgo </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">银杏 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">with Baochu Pagoda </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">保俶塔 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>backdrop.</t>
-    </r>
-  </si>
-  <si>
     <t>Walk</t>
   </si>
   <si>
@@ -6318,223 +6268,16 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Walk to Pinghu Qiuyue </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">平湖秋月 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>toward Gushan.</t>
-    </r>
-  </si>
-  <si>
     <t>西湖区白堤</t>
   </si>
   <si>
-    <t>09:45–10:30</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">🍁 Gushan </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">孤山 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&amp; Xiling Seal Society </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>西泠印社</t>
-    </r>
-  </si>
-  <si>
     <t>西湖区孤山路</t>
   </si>
   <si>
-    <t>10:30–11:15</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">MUST-SEE: Su Causeway </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">苏堤 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(north)</t>
-    </r>
-  </si>
-  <si>
-    <t>Willow-and-bridge dyke; walk or bike.</t>
-  </si>
-  <si>
-    <t>Walk/bike</t>
-  </si>
-  <si>
     <t>西湖区苏堤</t>
   </si>
   <si>
     <t>11:15–12:15</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">MUST-SEE: Three Pools </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三潭印月 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(boat)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Ferry from Huagang </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">花港码头 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>to the ¥1-note island.</t>
-    </r>
-  </si>
-  <si>
-    <t>Ferry ~¥55</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">西湖三潭印月 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>小瀛洲</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
   </si>
   <si>
     <t>Coffee — % Arabica lakeside</t>
@@ -9744,9 +9487,6 @@
       </rPr>
       <t>)</t>
     </r>
-  </si>
-  <si>
-    <t>Opt</t>
   </si>
   <si>
     <r>
@@ -11650,9 +11390,6 @@
     <t>15:15–16:20</t>
   </si>
   <si>
-    <t>Metro L2 (~60–75 min) or DiDi (~50–70 min). Earlier start = comfortable buffer at Hongqiao.</t>
-  </si>
-  <si>
     <t>🛍 SHOP: Hubin Pedestrian St 湖滨步行街 &amp; 湖滨银泰 in77</t>
   </si>
   <si>
@@ -11662,9 +11399,6 @@
     <t>湖滨 · Walk</t>
   </si>
   <si>
-    <t>Dinner — Grandma's Kitchen 外婆家</t>
-  </si>
-  <si>
     <t>16:15–17:30</t>
   </si>
   <si>
@@ -12211,9 +11945,6 @@
     <t>上城区国货路2号 (Canopy 康铂·西湖)</t>
   </si>
   <si>
-    <t>Dinner + SHOP: Hubin in77 湖滨银泰 (at hotel)</t>
-  </si>
-  <si>
     <t>湖滨in77 · 5 min</t>
   </si>
   <si>
@@ -12382,9 +12113,6 @@
     <t>Day 7 — Sat 21 Nov  ·  Suzhou Gardens &amp; Canals · west gardens AT THE HOTEL → centre → south · overnight Ritz 丽思</t>
   </si>
   <si>
-    <t>Red-leaf corner by the lake — quiet causeway end.</t>
-  </si>
-  <si>
     <t>SHOP: Guanqian Street 观前街</t>
   </si>
   <si>
@@ -12406,9 +12134,6 @@
     <t>16:35–17:15</t>
   </si>
   <si>
-    <t>Labyrinthine rockery nearby — now has a relaxed 40 min instead of a rushed 30.</t>
-  </si>
-  <si>
     <t>17:15–18:00</t>
   </si>
   <si>
@@ -12427,9 +12152,6 @@
     <t>14:30–15:30</t>
   </si>
   <si>
-    <t>Metro L3 ~2km south. Dacheng Hall 大成殿 — extra time now the 江南贡院 museum is dropped.</t>
-  </si>
-  <si>
     <t>World's largest fortified city-gate complex — now 1h15m to climb the tiers properly.</t>
   </si>
   <si>
@@ -12562,15 +12284,6 @@
     <t>No.1 mall' — global flagships + the ¥16M themed washrooms (free, no booking). The Deji Art Museum on 8F is a SEPARATE ticketed visit needing advance 实名预约 — see the dedicated row below.</t>
   </si>
   <si>
-    <t>11:15–11:50</t>
-  </si>
-  <si>
-    <t>11:50–12:05</t>
-  </si>
-  <si>
-    <t>12:05–12:40</t>
-  </si>
-  <si>
     <t>12:40–13:35</t>
   </si>
   <si>
@@ -12580,9 +12293,6 @@
     <t>🍵 MUST-SEE: Longjing Tea Village 龙井茶村 (2h block)</t>
   </si>
   <si>
-    <t>Free · DiDi ~20 min</t>
-  </si>
-  <si>
     <t>15:55–16:35</t>
   </si>
   <si>
@@ -12601,18 +12311,6 @@
     <t>西湖区南山路15号</t>
   </si>
   <si>
-    <t>18:05–19:05</t>
-  </si>
-  <si>
-    <t>19:05–19:20</t>
-  </si>
-  <si>
-    <t>Transfer: dinner → 岳湖 show entrance (北山路82号)</t>
-  </si>
-  <si>
-    <t>DiDi ~15 min</t>
-  </si>
-  <si>
     <t>19:40–20:35</t>
   </si>
   <si>
@@ -12628,9 +12326,6 @@
     <t>Top-rated lakeside Hangzhou fine dining (Dianping 4.8, 600+ reviews) — famous Dongpo pork 东坡肉. Inside the Hyatt Regency on 湖滨路, a short walk on from 湖滨步行街/in77. Book ahead; fine-dining pace, so keep an eye on the 13:35 finish.</t>
   </si>
   <si>
-    <t>Dragon Well spring 龙井泉 (the "dragon whisker" waterline), Longjing Temple 龙井寺, and the Eighteen Royal Tea Trees 十八棵御茶树 at the foot of Lion Peak 狮峰山. Tasting with a local tea family + buy fresh 龙井. Free &amp; open 24h, but the terraces are a daylight sight — sunset 16 Nov is 17:02. This 2h covers well/temple/tea trees + one tasting, not the 十里琅珰 ridge walk.</t>
-  </si>
-  <si>
     <t>Classic November foliage in the SW hills — 九溪 maples &amp; 十八涧 stream; 满觉陇 osmanthus lane. Downhill continuation from 龙井, no lake crossing. Skippable if the 龙井 transfer runs long.</t>
   </si>
   <si>
@@ -12640,21 +12335,6 @@
     <t>Optional: Huagang Guanyu 花港观鱼</t>
   </si>
   <si>
-    <t>Peony garden &amp; red-carp ponds; autumn colour. Right by the 苏堤 south end — bolt on before lunch only if running ahead of time.</t>
-  </si>
-  <si>
-    <t>Home-style Hangzhou near Hefang 河坊街. Queue early. Keep to the hour — the show gate is a 15-min ride away.</t>
-  </si>
-  <si>
-    <t>DiDi to the 岳湖景区 gate opposite 岳王庙. Arrive ~19:20 for the 19:40 curtain: ticket collection, 检票 and the walk to the seats. Official guidance is 45 min early, so do not linger over dinner.</t>
-  </si>
-  <si>
-    <t>Outdoor water-stage show on West Lake itself (Zhang Yimou 张艺谋 / 王潮歌 / 樊跃; music by Kitaro 喜多郎). ~50–55 min. Starts 19:40. A second 21:10 session runs mainly Fri/Sat &amp; public holidays — 16 Nov is a Monday, so expect the 19:40 show only. Outdoor &amp; weather-dependent: re-confirm the session on the official channel the day before. Entrance 北山路82号, opposite 岳王庙; seating by zone; book ahead.</t>
-  </si>
-  <si>
-    <t>Canopy sits beside the 湖滨 waterfront strip — flagship stores, food halls &amp; easy first-night dinner, all within a 5-min walk.</t>
-  </si>
-  <si>
     <t>~5-min walk from the hotel at 湖滨三公园 — nightly shows on the lake. Perfect low-effort arrival night.</t>
   </si>
   <si>
@@ -12689,6 +12369,157 @@
   </si>
   <si>
     <t>Award-winning tea house on Dajing Lane 大井巷 — the Southern Song lane you walk at 15:00, so it is a zero-detour stop. Owner 查文 is a Hangzhou tea-culture inheritor. 1F: walk-in tasting + tea/teaware retail — local 西湖龙井 plus Taiwan high-mtn oolong, Fuding white, Wuyi rock tea. Creative tea mocktails (茶逗逗 w/ tea jelly) brewed espresso-style. 2F tatami tea room needs advance booking 预约.</t>
+  </si>
+  <si>
+    <t>Dinner — Grandma's Kitchen 外婆家 (in77 E区店)</t>
+  </si>
+  <si>
+    <t>Signature 外婆茶香鸡, 龙井虾仁, 东坡肉. Inside 湖滨银泰in77 E区 B1 — no transfer from the hotel. Open till 21:30; no reservations, expect a queue.</t>
+  </si>
+  <si>
+    <t>¥77 · 5-min walk</t>
+  </si>
+  <si>
+    <t>上城区延安路185号 (湖滨银泰in77 E区 B1)</t>
+  </si>
+  <si>
+    <t>20:50–21:00</t>
+  </si>
+  <si>
+    <t>SHOP: Hubin in77 湖滨银泰 (at hotel)</t>
+  </si>
+  <si>
+    <t>Flagship stores and food halls on the walk out toward the waterfront.</t>
+  </si>
+  <si>
+    <t>17:50–18:20</t>
+  </si>
+  <si>
+    <t>Transfer: 雷峰塔 → 北山街 78号 (dinner)</t>
+  </si>
+  <si>
+    <t>DiDi around the north shore to the Shangri-La 水知心居. Books the table before the 17:00–20:30 service fills up.</t>
+  </si>
+  <si>
+    <t>DiDi ~25 min</t>
+  </si>
+  <si>
+    <t>18:20–19:20</t>
+  </si>
+  <si>
+    <t>◆ Dinner — Golden Silk 金丝·听海 (Michelin selected)</t>
+  </si>
+  <si>
+    <t>Zhejiang coastal seafood at the Shangri-La 水知心居 — 招牌江蟹生 (Wenzhou raw marinated crab), 脆皮盐香清远鸡, 头水紫菜海鲜石榴包. Kitchen serves 17:00–20:30. Book ahead; smart-casual dress. ~4 doors from the show gate, so the walk out is 5 min.</t>
+  </si>
+  <si>
+    <t>¥518 · 4.6★</t>
+  </si>
+  <si>
+    <t>Golden ginkgo 银杏 with Baochu Pagoda 保俶塔 backdrop.
+🚶 From the hotel: exit onto 国货路, head west to the lake (~6 min, 500m), then turn right (north) along the waterfront to 北山街. Walk the avenue westward with the lake on your left — the ginkgo run is between 断桥 and 葛岭. Flat pavement throughout.</t>
+  </si>
+  <si>
+    <t>Walk ~1.3km total</t>
+  </si>
+  <si>
+    <t>Walk 987m · ~15 min</t>
+  </si>
+  <si>
+    <t>MUST-SEE: Gushan 孤山 &amp; Xiling Seal Society 西泠印社</t>
+  </si>
+  <si>
+    <t>MUST-SEE: Three Pools 三潭印月 (boat)</t>
+  </si>
+  <si>
+    <t>Ferry ~¥55 · 中山公园码头</t>
+  </si>
+  <si>
+    <t>西湖三潭印月 (小瀛洲)</t>
+  </si>
+  <si>
+    <t>Optional: Su Causeway 苏堤 (苏堤春晓)</t>
+  </si>
+  <si>
+    <t>09:45–11:00</t>
+  </si>
+  <si>
+    <t>Free · 75 min</t>
+  </si>
+  <si>
+    <t>11:05–12:00</t>
+  </si>
+  <si>
+    <t>12:00–12:15</t>
+  </si>
+  <si>
+    <t>12:15–12:40</t>
+  </si>
+  <si>
+    <t>The ¥1-note island 小瀛洲 — three stone pagodas standing in the water.
+⛴ Board at 中山公园码头 on 孤山 — a ~5 min walk from 西泠印社, no causeway traverse needed. Round trip incl. time on the island runs ~45–55 min.</t>
+  </si>
+  <si>
+    <t>A natural island in the lake, 20 hectares, 38m high — 文物胜迹荟萃之地, and the lake's cultural heart since the Tang.
+① 西泠印社 (founded 1904, first president 吴昌硕) — terraced hillside garden of pavilions, cliff-face stone inscriptions &amp; the 印藏. Allow 30–40 min.
+② 放鹤亭 — Song poet 林逋 (林和靖) lived as a recluse and is buried here, ringed by plum trees. NE slope.
+③ 秋瑾墓 (revolutionary, executed 1907) on the W slope; 浙江省博物馆 &amp; 文澜阁 (imperial 四库全书 library); 中山公园.
+🚶 白堤 lands you at 平湖秋月 — the single best spot for photographing 保俶塔 across the water. 孤山 begins right behind it; continue W on 孤山路 ~500m to 西泠印社, which climbs to your right (stone steps).</t>
+  </si>
+  <si>
+    <t>苏堤春晓 — 2,797m dyke with six bridges N→S: 跨虹桥 · 东浦桥 · 压堤桥 · 望山桥 · 锁澜桥 · 映波桥. Full walk 40–50 min; bike ~15 min. 孤山 and 苏堤 are not joined on foot: cross 西泠桥 to 北山路, then ~1km west to the 跨虹桥 north entrance.</t>
+  </si>
+  <si>
+    <t>Peony garden &amp; red-carp ponds; autumn colour. At the 苏堤 south end, beside 映波桥 and 花港码头.</t>
+  </si>
+  <si>
+    <t>断桥残雪 &amp; the causeway to 平湖秋月.
+🚶 白堤 is 987m end to end, east (断桥) to west (平湖秋月) — about 15 min at a slow pace, crossing 锦带桥 at the midpoint. Flat, car-free walk with the lake on both sides.</t>
+  </si>
+  <si>
+    <t>Metro L2 (~60–75 min) or DiDi (~50–70 min).</t>
+  </si>
+  <si>
+    <t>Metro L3 ~2km south. Dacheng Hall 大成殿.</t>
+  </si>
+  <si>
+    <t>Labyrinthine rockery nearby — allow ~40 min.</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>15:50</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free · ¥10 御茶园 · DiDi ~20 min
+</t>
+  </si>
+  <si>
+    <t>2H FLOW (W→E, downhill finish):
+· 13:50–14:05 — 龙井村牌坊 (the arch) → walk the main street.
+· 14:05–14:35 — 十八棵御茶园 (老龙井). Ticket ¥10 — the only paid spot.
+· 14:35–15:00 — Tea-garden terraces. ~200m in from the arch, stone path up on the RIGHT.
+· 15:00–15:35 — Tea tasting at a farmer's house. Buy here if buying.
+· 15:35–15:50 — 龙井泉 &amp; 龙井寺 at the E end.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outdoor water-stage show on West Lake itself (Zhang Yimou 张艺谋 / 王潮歌 / 樊跃; music by Kitaro 喜多郎). ~50–55 min. Starts 19:40. Walk 5 min east along 北山街 from dinner — arrive ~19:25 for ticket collection and 检票. </t>
   </si>
 </sst>
 </file>
@@ -13257,7 +13088,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="241">
+  <cellXfs count="244">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -13805,6 +13636,126 @@
     <xf numFmtId="164" fontId="7" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -13823,123 +13774,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -13970,8 +13804,14 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -14251,31 +14091,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="31.5" customHeight="1">
-      <c r="A1" s="205" t="s">
+      <c r="A1" s="206" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="205"/>
-      <c r="C1" s="205"/>
-      <c r="D1" s="205"/>
-      <c r="E1" s="205"/>
+      <c r="B1" s="206"/>
+      <c r="C1" s="206"/>
+      <c r="D1" s="206"/>
+      <c r="E1" s="206"/>
     </row>
     <row r="2" spans="1:5" ht="21.75" customHeight="1">
-      <c r="A2" s="206" t="s">
+      <c r="A2" s="207" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="206"/>
-      <c r="C2" s="206"/>
-      <c r="D2" s="206"/>
-      <c r="E2" s="206"/>
+      <c r="B2" s="207"/>
+      <c r="C2" s="207"/>
+      <c r="D2" s="207"/>
+      <c r="E2" s="207"/>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1">
-      <c r="A4" s="207" t="s">
+      <c r="A4" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="207"/>
-      <c r="C4" s="207"/>
-      <c r="D4" s="207"/>
-      <c r="E4" s="207"/>
+      <c r="B4" s="208"/>
+      <c r="C4" s="208"/>
+      <c r="D4" s="208"/>
+      <c r="E4" s="208"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
@@ -14329,13 +14169,13 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1">
-      <c r="A9" s="208" t="s">
+      <c r="A9" s="209" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="208"/>
-      <c r="C9" s="208"/>
-      <c r="D9" s="208"/>
-      <c r="E9" s="208"/>
+      <c r="B9" s="209"/>
+      <c r="C9" s="209"/>
+      <c r="D9" s="209"/>
+      <c r="E9" s="209"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
@@ -14356,36 +14196,36 @@
     </row>
     <row r="11" spans="1:5" ht="55" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>1036</v>
+        <v>1019</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1037</v>
+        <v>1020</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1038</v>
+        <v>1021</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>1039</v>
+        <v>1022</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>1008</v>
+        <v>992</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="55" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>1036</v>
+        <v>1019</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1040</v>
+        <v>1023</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1041</v>
+        <v>1024</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1042</v>
+        <v>1025</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>1043</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="45.75" customHeight="1">
@@ -14424,41 +14264,41 @@
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1"/>
     <row r="16" spans="1:5" ht="72" customHeight="1">
-      <c r="A16" s="209" t="s">
+      <c r="A16" s="210" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="209"/>
-      <c r="C16" s="209"/>
-      <c r="D16" s="209"/>
-      <c r="E16" s="209"/>
+      <c r="B16" s="210"/>
+      <c r="C16" s="210"/>
+      <c r="D16" s="210"/>
+      <c r="E16" s="210"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="203" t="s">
+      <c r="A17" s="204" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="203"/>
-      <c r="C17" s="203"/>
-      <c r="D17" s="203"/>
-      <c r="E17" s="203"/>
+      <c r="B17" s="204"/>
+      <c r="C17" s="204"/>
+      <c r="D17" s="204"/>
+      <c r="E17" s="204"/>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1"/>
     <row r="19" spans="1:5" ht="31.5" customHeight="1">
-      <c r="A19" s="204" t="s">
+      <c r="A19" s="205" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="204"/>
-      <c r="C19" s="204"/>
-      <c r="D19" s="204"/>
-      <c r="E19" s="204"/>
+      <c r="B19" s="205"/>
+      <c r="C19" s="205"/>
+      <c r="D19" s="205"/>
+      <c r="E19" s="205"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="203" t="s">
+      <c r="A20" s="204" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="203"/>
-      <c r="C20" s="203"/>
-      <c r="D20" s="203"/>
-      <c r="E20" s="203"/>
+      <c r="B20" s="204"/>
+      <c r="C20" s="204"/>
+      <c r="D20" s="204"/>
+      <c r="E20" s="204"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -14481,7 +14321,7 @@
   <sheetPr>
     <tabColor rgb="FFC55A11"/>
   </sheetPr>
-  <dimension ref="A1:F136"/>
+  <dimension ref="A1:F137"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -14493,24 +14333,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18">
-      <c r="A1" s="210" t="s">
-        <v>1004</v>
-      </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="212"/>
+      <c r="A1" s="195" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1" s="196"/>
+      <c r="C1" s="196"/>
+      <c r="D1" s="196"/>
+      <c r="E1" s="196"/>
+      <c r="F1" s="197"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="213" t="s">
+      <c r="A2" s="198" t="s">
         <v>344</v>
       </c>
-      <c r="B2" s="214"/>
-      <c r="C2" s="214"/>
-      <c r="D2" s="214"/>
-      <c r="E2" s="214"/>
-      <c r="F2" s="215"/>
+      <c r="B2" s="199"/>
+      <c r="C2" s="199"/>
+      <c r="D2" s="199"/>
+      <c r="E2" s="199"/>
+      <c r="F2" s="200"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="77" t="s">
@@ -14533,14 +14373,14 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="216" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B4" s="217"/>
-      <c r="C4" s="217"/>
-      <c r="D4" s="217"/>
-      <c r="E4" s="217"/>
-      <c r="F4" s="218"/>
+      <c r="A4" s="201" t="s">
+        <v>989</v>
+      </c>
+      <c r="B4" s="202"/>
+      <c r="C4" s="202"/>
+      <c r="D4" s="202"/>
+      <c r="E4" s="202"/>
+      <c r="F4" s="203"/>
     </row>
     <row r="5" spans="1:6" ht="28">
       <c r="A5" s="98" t="s">
@@ -14587,13 +14427,13 @@
         <v>350</v>
       </c>
       <c r="B7" s="158" t="s">
-        <v>825</v>
+        <v>811</v>
       </c>
       <c r="C7" s="50" t="s">
         <v>361</v>
       </c>
       <c r="D7" s="50" t="s">
-        <v>826</v>
+        <v>1172</v>
       </c>
       <c r="E7" s="50" t="s">
         <v>362</v>
@@ -14630,16 +14470,16 @@
         <v>369</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>1006</v>
+        <v>990</v>
       </c>
       <c r="D9" s="50" t="s">
-        <v>1007</v>
+        <v>991</v>
       </c>
       <c r="E9" s="50" t="s">
         <v>370</v>
       </c>
       <c r="F9" s="115" t="s">
-        <v>1008</v>
+        <v>992</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28">
@@ -14650,2474 +14490,2494 @@
         <v>371</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>1009</v>
+        <v>993</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>1010</v>
+        <v>994</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>1011</v>
+        <v>995</v>
       </c>
       <c r="F10" s="116" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="28">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="45" customHeight="1">
       <c r="A11" s="102" t="s">
         <v>350</v>
       </c>
-      <c r="B11" s="57" t="s">
+      <c r="B11" s="154" t="s">
+        <v>770</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E11" s="35" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F11" s="117" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="45" customHeight="1">
+      <c r="A12" s="102" t="s">
+        <v>350</v>
+      </c>
+      <c r="B12" s="154" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D12" s="33" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E12" s="35" t="s">
+        <v>997</v>
+      </c>
+      <c r="F12" s="117" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="28">
+      <c r="A13" s="103" t="s">
+        <v>350</v>
+      </c>
+      <c r="B13" s="58" t="s">
         <v>373</v>
       </c>
-      <c r="C11" s="33" t="s">
-        <v>1013</v>
-      </c>
-      <c r="D11" s="33" t="s">
+      <c r="C13" s="39" t="s">
+        <v>999</v>
+      </c>
+      <c r="D13" s="39" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E13" s="41" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F13" s="118" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="28">
+      <c r="A14" s="101" t="s">
+        <v>350</v>
+      </c>
+      <c r="B14" s="56" t="s">
+        <v>374</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F14" s="116" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="201" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B15" s="202"/>
+      <c r="C15" s="202"/>
+      <c r="D15" s="202"/>
+      <c r="E15" s="202"/>
+      <c r="F15" s="203"/>
+    </row>
+    <row r="16" spans="1:6" ht="28">
+      <c r="A16" s="101" t="s">
+        <v>378</v>
+      </c>
+      <c r="B16" s="56" t="s">
+        <v>379</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F16" s="116" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="90" customHeight="1">
+      <c r="A17" s="104" t="s">
+        <v>378</v>
+      </c>
+      <c r="B17" s="59" t="s">
+        <v>380</v>
+      </c>
+      <c r="C17" s="47" t="s">
+        <v>381</v>
+      </c>
+      <c r="D17" s="47" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E17" s="241" t="s">
+        <v>1155</v>
+      </c>
+      <c r="F17" s="119" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="56">
+      <c r="A18" s="105" t="s">
+        <v>378</v>
+      </c>
+      <c r="B18" s="60" t="s">
+        <v>384</v>
+      </c>
+      <c r="C18" s="61" t="s">
+        <v>385</v>
+      </c>
+      <c r="D18" s="61" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E18" s="242" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F18" s="120" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="182">
+      <c r="A19" s="104" t="s">
+        <v>378</v>
+      </c>
+      <c r="B19" s="243" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C19" s="47" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D19" s="47" t="s">
+        <v>1168</v>
+      </c>
+      <c r="E19" s="241" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F19" s="119" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="70">
+      <c r="A20" s="105" t="s">
+        <v>378</v>
+      </c>
+      <c r="B20" s="152" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C20" s="61" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D20" s="61" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E20" s="242" t="s">
+        <v>1159</v>
+      </c>
+      <c r="F20" s="120" t="s">
         <v>1160</v>
       </c>
-      <c r="E11" s="35" t="s">
-        <v>1014</v>
-      </c>
-      <c r="F11" s="117" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="28">
-      <c r="A12" s="103" t="s">
-        <v>350</v>
-      </c>
-      <c r="B12" s="58" t="s">
-        <v>374</v>
-      </c>
-      <c r="C12" s="39" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D12" s="39" t="s">
+    </row>
+    <row r="21" spans="1:6" ht="28" customHeight="1">
+      <c r="A21" s="105" t="s">
+        <v>378</v>
+      </c>
+      <c r="B21" s="152" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C21" s="61" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D21" s="61" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E21" s="61" t="s">
+        <v>516</v>
+      </c>
+      <c r="F21" s="120" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="56" customHeight="1">
+      <c r="A22" s="105" t="s">
+        <v>378</v>
+      </c>
+      <c r="B22" s="152" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C22" s="61" t="s">
         <v>1161</v>
       </c>
-      <c r="E12" s="41" t="s">
-        <v>1017</v>
-      </c>
-      <c r="F12" s="118" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="28">
-      <c r="A13" s="101" t="s">
-        <v>350</v>
-      </c>
-      <c r="B13" s="56" t="s">
-        <v>375</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>377</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>1019</v>
-      </c>
-      <c r="F13" s="116" t="s">
+      <c r="D22" s="61" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E22" s="61" t="s">
+        <v>516</v>
+      </c>
+      <c r="F22" s="120" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="28">
+      <c r="A23" s="106" t="s">
+        <v>378</v>
+      </c>
+      <c r="B23" s="157" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>390</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>391</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>392</v>
+      </c>
+      <c r="F23" s="121" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="42">
+      <c r="A24" s="106" t="s">
+        <v>378</v>
+      </c>
+      <c r="B24" s="157" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>812</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>813</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>814</v>
+      </c>
+      <c r="F24" s="121" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="56">
+      <c r="A25" s="98" t="s">
+        <v>378</v>
+      </c>
+      <c r="B25" s="159" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F25" s="86" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="110" customHeight="1">
+      <c r="A26" s="105" t="s">
+        <v>378</v>
+      </c>
+      <c r="B26" s="152" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C26" s="61" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D26" s="242" t="s">
+        <v>1183</v>
+      </c>
+      <c r="E26" s="242" t="s">
+        <v>1182</v>
+      </c>
+      <c r="F26" s="120" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="56">
+      <c r="A27" s="105" t="s">
+        <v>378</v>
+      </c>
+      <c r="B27" s="152" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C27" s="61" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D27" s="61" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E27" s="61" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F27" s="120" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="42">
+      <c r="A28" s="105" t="s">
+        <v>378</v>
+      </c>
+      <c r="B28" s="152" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C28" s="61" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D28" s="61" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E28" s="61" t="s">
+        <v>394</v>
+      </c>
+      <c r="F28" s="120" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="28">
+      <c r="A29" s="107" t="s">
+        <v>378</v>
+      </c>
+      <c r="B29" s="160" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C29" s="36" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D29" s="36" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E29" s="36" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F29" s="122" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="70">
+      <c r="A30" s="102" t="s">
+        <v>378</v>
+      </c>
+      <c r="B30" s="154" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D30" s="33" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E30" s="33" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F30" s="117" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="56">
+      <c r="A31" s="102" t="s">
+        <v>378</v>
+      </c>
+      <c r="B31" s="154" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C31" s="33" t="s">
+        <v>782</v>
+      </c>
+      <c r="D31" s="33" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E31" s="33" t="s">
+        <v>783</v>
+      </c>
+      <c r="F31" s="117" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="28">
+      <c r="A32" s="107" t="s">
+        <v>378</v>
+      </c>
+      <c r="B32" s="160" t="s">
+        <v>785</v>
+      </c>
+      <c r="C32" s="36" t="s">
+        <v>396</v>
+      </c>
+      <c r="D32" s="36" t="s">
+        <v>397</v>
+      </c>
+      <c r="E32" s="36" t="s">
+        <v>398</v>
+      </c>
+      <c r="F32" s="122" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="28">
+      <c r="A33" s="101" t="s">
+        <v>378</v>
+      </c>
+      <c r="B33" s="151" t="s">
+        <v>774</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F33" s="116" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="201" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B34" s="202"/>
+      <c r="C34" s="202"/>
+      <c r="D34" s="202"/>
+      <c r="E34" s="202"/>
+      <c r="F34" s="203"/>
+    </row>
+    <row r="35" spans="1:6" ht="42">
+      <c r="A35" s="101" t="s">
+        <v>401</v>
+      </c>
+      <c r="B35" s="56" t="s">
+        <v>402</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E35" s="10" t="s">
         <v>1012</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="216" t="s">
-        <v>1020</v>
-      </c>
-      <c r="B14" s="217"/>
-      <c r="C14" s="217"/>
-      <c r="D14" s="217"/>
-      <c r="E14" s="217"/>
-      <c r="F14" s="218"/>
-    </row>
-    <row r="15" spans="1:6" ht="28">
-      <c r="A15" s="101" t="s">
-        <v>379</v>
-      </c>
-      <c r="B15" s="56" t="s">
-        <v>380</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>1021</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>1022</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F15" s="116" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="28">
-      <c r="A16" s="104" t="s">
-        <v>379</v>
-      </c>
-      <c r="B16" s="59" t="s">
-        <v>381</v>
-      </c>
-      <c r="C16" s="47" t="s">
-        <v>382</v>
-      </c>
-      <c r="D16" s="47" t="s">
-        <v>383</v>
-      </c>
-      <c r="E16" s="47" t="s">
-        <v>384</v>
-      </c>
-      <c r="F16" s="119" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="28">
-      <c r="A17" s="105" t="s">
-        <v>379</v>
-      </c>
-      <c r="B17" s="60" t="s">
-        <v>386</v>
-      </c>
-      <c r="C17" s="61" t="s">
-        <v>387</v>
-      </c>
-      <c r="D17" s="61" t="s">
-        <v>388</v>
-      </c>
-      <c r="E17" s="61" t="s">
-        <v>384</v>
-      </c>
-      <c r="F17" s="120" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="28">
-      <c r="A18" s="104" t="s">
-        <v>379</v>
-      </c>
-      <c r="B18" s="59" t="s">
-        <v>390</v>
-      </c>
-      <c r="C18" s="47" t="s">
-        <v>391</v>
-      </c>
-      <c r="D18" s="47" t="s">
-        <v>1070</v>
-      </c>
-      <c r="E18" s="47" t="s">
-        <v>384</v>
-      </c>
-      <c r="F18" s="119" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="28">
-      <c r="A19" s="105" t="s">
-        <v>379</v>
-      </c>
-      <c r="B19" s="60" t="s">
-        <v>393</v>
-      </c>
-      <c r="C19" s="61" t="s">
-        <v>394</v>
-      </c>
-      <c r="D19" s="61" t="s">
-        <v>395</v>
-      </c>
-      <c r="E19" s="61" t="s">
-        <v>396</v>
-      </c>
-      <c r="F19" s="120" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="28">
-      <c r="A20" s="105" t="s">
-        <v>379</v>
-      </c>
-      <c r="B20" s="152" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C20" s="61" t="s">
-        <v>399</v>
-      </c>
-      <c r="D20" s="61" t="s">
-        <v>400</v>
-      </c>
-      <c r="E20" s="61" t="s">
+      <c r="F35" s="116" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="84">
+      <c r="A36" s="102" t="s">
         <v>401</v>
       </c>
-      <c r="F20" s="120" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="28">
-      <c r="A21" s="106" t="s">
-        <v>379</v>
-      </c>
-      <c r="B21" s="157" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>403</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>404</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>405</v>
-      </c>
-      <c r="F21" s="121" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="42">
-      <c r="A22" s="106" t="s">
-        <v>379</v>
-      </c>
-      <c r="B22" s="157" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>827</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>828</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>829</v>
-      </c>
-      <c r="F22" s="121" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="56">
-      <c r="A23" s="98" t="s">
-        <v>379</v>
-      </c>
-      <c r="B23" s="159" t="s">
-        <v>1133</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>1148</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>1151</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>1149</v>
-      </c>
-      <c r="F23" s="86" t="s">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="98">
-      <c r="A24" s="105" t="s">
-        <v>379</v>
-      </c>
-      <c r="B24" s="152" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C24" s="61" t="s">
-        <v>1135</v>
-      </c>
-      <c r="D24" s="61" t="s">
-        <v>1152</v>
-      </c>
-      <c r="E24" s="61" t="s">
-        <v>1136</v>
-      </c>
-      <c r="F24" s="120" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="56">
-      <c r="A25" s="105" t="s">
-        <v>379</v>
-      </c>
-      <c r="B25" s="152" t="s">
-        <v>1137</v>
-      </c>
-      <c r="C25" s="61" t="s">
-        <v>1138</v>
-      </c>
-      <c r="D25" s="61" t="s">
-        <v>1153</v>
-      </c>
-      <c r="E25" s="61" t="s">
-        <v>1139</v>
-      </c>
-      <c r="F25" s="120" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="42">
-      <c r="A26" s="105" t="s">
-        <v>379</v>
-      </c>
-      <c r="B26" s="152" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C26" s="61" t="s">
-        <v>1141</v>
-      </c>
-      <c r="D26" s="61" t="s">
-        <v>1154</v>
-      </c>
-      <c r="E26" s="61" t="s">
-        <v>407</v>
-      </c>
-      <c r="F26" s="120" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="42">
-      <c r="A27" s="105" t="s">
-        <v>379</v>
-      </c>
-      <c r="B27" s="152" t="s">
-        <v>592</v>
-      </c>
-      <c r="C27" s="61" t="s">
-        <v>1155</v>
-      </c>
-      <c r="D27" s="61" t="s">
-        <v>1156</v>
-      </c>
-      <c r="E27" s="61" t="s">
-        <v>529</v>
-      </c>
-      <c r="F27" s="120" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="28">
-      <c r="A28" s="107" t="s">
-        <v>379</v>
-      </c>
-      <c r="B28" s="160" t="s">
-        <v>1143</v>
-      </c>
-      <c r="C28" s="36" t="s">
-        <v>830</v>
-      </c>
-      <c r="D28" s="36" t="s">
-        <v>1157</v>
-      </c>
-      <c r="E28" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="F28" s="122" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="42">
-      <c r="A29" s="102" t="s">
-        <v>379</v>
-      </c>
-      <c r="B29" s="154" t="s">
-        <v>1144</v>
-      </c>
-      <c r="C29" s="33" t="s">
-        <v>1145</v>
-      </c>
-      <c r="D29" s="33" t="s">
-        <v>1158</v>
-      </c>
-      <c r="E29" s="33" t="s">
-        <v>1146</v>
-      </c>
-      <c r="F29" s="117" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="98">
-      <c r="A30" s="102" t="s">
-        <v>379</v>
-      </c>
-      <c r="B30" s="154" t="s">
-        <v>1147</v>
-      </c>
-      <c r="C30" s="33" t="s">
-        <v>796</v>
-      </c>
-      <c r="D30" s="33" t="s">
-        <v>1159</v>
-      </c>
-      <c r="E30" s="33" t="s">
-        <v>797</v>
-      </c>
-      <c r="F30" s="117" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="28">
-      <c r="A31" s="107" t="s">
-        <v>379</v>
-      </c>
-      <c r="B31" s="160" t="s">
-        <v>799</v>
-      </c>
-      <c r="C31" s="36" t="s">
-        <v>409</v>
-      </c>
-      <c r="D31" s="36" t="s">
-        <v>410</v>
-      </c>
-      <c r="E31" s="36" t="s">
-        <v>411</v>
-      </c>
-      <c r="F31" s="122" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="28">
-      <c r="A32" s="101" t="s">
-        <v>379</v>
-      </c>
-      <c r="B32" s="151" t="s">
-        <v>788</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>1024</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>1025</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>1019</v>
-      </c>
-      <c r="F32" s="116" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="216" t="s">
-        <v>1026</v>
-      </c>
-      <c r="B33" s="217"/>
-      <c r="C33" s="217"/>
-      <c r="D33" s="217"/>
-      <c r="E33" s="217"/>
-      <c r="F33" s="218"/>
-    </row>
-    <row r="34" spans="1:6" ht="42">
-      <c r="A34" s="101" t="s">
-        <v>414</v>
-      </c>
-      <c r="B34" s="56" t="s">
-        <v>415</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>1027</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>1028</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>1029</v>
-      </c>
-      <c r="F34" s="116" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="84">
-      <c r="A35" s="102" t="s">
-        <v>414</v>
-      </c>
-      <c r="B35" s="154" t="s">
-        <v>592</v>
-      </c>
-      <c r="C35" s="33" t="s">
-        <v>890</v>
-      </c>
-      <c r="D35" s="33" t="s">
-        <v>891</v>
-      </c>
-      <c r="E35" s="35" t="s">
-        <v>892</v>
-      </c>
-      <c r="F35" s="117" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="28">
-      <c r="A36" s="105" t="s">
-        <v>414</v>
-      </c>
-      <c r="B36" s="60" t="s">
-        <v>416</v>
-      </c>
-      <c r="C36" s="61" t="s">
-        <v>417</v>
-      </c>
-      <c r="D36" s="61" t="s">
-        <v>418</v>
-      </c>
-      <c r="E36" s="61" t="s">
-        <v>419</v>
-      </c>
-      <c r="F36" s="120" t="s">
-        <v>420</v>
+      <c r="B36" s="154" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C36" s="33" t="s">
+        <v>874</v>
+      </c>
+      <c r="D36" s="33" t="s">
+        <v>875</v>
+      </c>
+      <c r="E36" s="35" t="s">
+        <v>876</v>
+      </c>
+      <c r="F36" s="117" t="s">
+        <v>877</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="28">
       <c r="A37" s="105" t="s">
+        <v>401</v>
+      </c>
+      <c r="B37" s="60" t="s">
+        <v>403</v>
+      </c>
+      <c r="C37" s="61" t="s">
+        <v>404</v>
+      </c>
+      <c r="D37" s="61" t="s">
+        <v>405</v>
+      </c>
+      <c r="E37" s="61" t="s">
+        <v>406</v>
+      </c>
+      <c r="F37" s="120" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="28">
+      <c r="A38" s="105" t="s">
+        <v>401</v>
+      </c>
+      <c r="B38" s="60" t="s">
+        <v>408</v>
+      </c>
+      <c r="C38" s="61" t="s">
+        <v>409</v>
+      </c>
+      <c r="D38" s="61" t="s">
+        <v>410</v>
+      </c>
+      <c r="E38" s="61" t="s">
+        <v>411</v>
+      </c>
+      <c r="F38" s="120" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="28">
+      <c r="A39" s="104" t="s">
+        <v>401</v>
+      </c>
+      <c r="B39" s="59" t="s">
+        <v>413</v>
+      </c>
+      <c r="C39" s="47" t="s">
         <v>414</v>
       </c>
-      <c r="B37" s="60" t="s">
+      <c r="D39" s="47" t="s">
+        <v>415</v>
+      </c>
+      <c r="E39" s="47" t="s">
+        <v>382</v>
+      </c>
+      <c r="F39" s="119" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="28">
+      <c r="A40" s="99" t="s">
+        <v>401</v>
+      </c>
+      <c r="B40" s="54" t="s">
+        <v>416</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F40" s="85" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="70">
+      <c r="A41" s="99" t="s">
+        <v>401</v>
+      </c>
+      <c r="B41" s="54" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F41" s="85" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="28">
+      <c r="A42" s="105" t="s">
+        <v>401</v>
+      </c>
+      <c r="B42" s="60" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C42" s="61" t="s">
+        <v>420</v>
+      </c>
+      <c r="D42" s="61" t="s">
         <v>421</v>
       </c>
-      <c r="C37" s="61" t="s">
+      <c r="E42" s="61" t="s">
+        <v>411</v>
+      </c>
+      <c r="F42" s="120" t="s">
         <v>422</v>
-      </c>
-      <c r="D37" s="61" t="s">
-        <v>423</v>
-      </c>
-      <c r="E37" s="61" t="s">
-        <v>424</v>
-      </c>
-      <c r="F37" s="120" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="28">
-      <c r="A38" s="104" t="s">
-        <v>414</v>
-      </c>
-      <c r="B38" s="59" t="s">
-        <v>426</v>
-      </c>
-      <c r="C38" s="47" t="s">
-        <v>427</v>
-      </c>
-      <c r="D38" s="47" t="s">
-        <v>428</v>
-      </c>
-      <c r="E38" s="47" t="s">
-        <v>384</v>
-      </c>
-      <c r="F38" s="119" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="28">
-      <c r="A39" s="99" t="s">
-        <v>414</v>
-      </c>
-      <c r="B39" s="54" t="s">
-        <v>429</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>430</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>431</v>
-      </c>
-      <c r="E39" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="F39" s="85" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="70">
-      <c r="A40" s="99" t="s">
-        <v>414</v>
-      </c>
-      <c r="B40" s="54" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C40" s="15" t="s">
-        <v>1031</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>1162</v>
-      </c>
-      <c r="E40" s="15" t="s">
-        <v>1032</v>
-      </c>
-      <c r="F40" s="85" t="s">
-        <v>1033</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="28">
-      <c r="A41" s="105" t="s">
-        <v>414</v>
-      </c>
-      <c r="B41" s="60" t="s">
-        <v>1034</v>
-      </c>
-      <c r="C41" s="61" t="s">
-        <v>433</v>
-      </c>
-      <c r="D41" s="61" t="s">
-        <v>434</v>
-      </c>
-      <c r="E41" s="61" t="s">
-        <v>424</v>
-      </c>
-      <c r="F41" s="120" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="28">
-      <c r="A42" s="102" t="s">
-        <v>414</v>
-      </c>
-      <c r="B42" s="57" t="s">
-        <v>1081</v>
-      </c>
-      <c r="C42" s="33" t="s">
-        <v>436</v>
-      </c>
-      <c r="D42" s="33" t="s">
-        <v>1163</v>
-      </c>
-      <c r="E42" s="35" t="s">
-        <v>437</v>
-      </c>
-      <c r="F42" s="117" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="28">
       <c r="A43" s="102" t="s">
-        <v>414</v>
-      </c>
-      <c r="B43" s="154" t="s">
-        <v>592</v>
+        <v>401</v>
+      </c>
+      <c r="B43" s="57" t="s">
+        <v>1062</v>
       </c>
       <c r="C43" s="33" t="s">
-        <v>815</v>
+        <v>423</v>
       </c>
       <c r="D43" s="33" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E43" s="35" t="s">
+        <v>424</v>
+      </c>
+      <c r="F43" s="117" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="28">
+      <c r="A44" s="102" t="s">
+        <v>401</v>
+      </c>
+      <c r="B44" s="154" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C44" s="33" t="s">
+        <v>801</v>
+      </c>
+      <c r="D44" s="33" t="s">
+        <v>802</v>
+      </c>
+      <c r="E44" s="35" t="s">
+        <v>516</v>
+      </c>
+      <c r="F44" s="117" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="70">
+      <c r="A45" s="102" t="s">
+        <v>401</v>
+      </c>
+      <c r="B45" s="154" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C45" s="33" t="s">
+        <v>854</v>
+      </c>
+      <c r="D45" s="33" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E45" s="35" t="s">
+        <v>855</v>
+      </c>
+      <c r="F45" s="117" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="56">
+      <c r="A46" s="102" t="s">
+        <v>401</v>
+      </c>
+      <c r="B46" s="154" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C46" s="33" t="s">
+        <v>857</v>
+      </c>
+      <c r="D46" s="33" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E46" s="35" t="s">
+        <v>858</v>
+      </c>
+      <c r="F46" s="117" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="45" customHeight="1">
+      <c r="A47" s="102" t="s">
+        <v>401</v>
+      </c>
+      <c r="B47" s="154" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C47" s="33" t="s">
+        <v>867</v>
+      </c>
+      <c r="D47" s="33" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E47" s="35" t="s">
+        <v>868</v>
+      </c>
+      <c r="F47" s="117" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="28">
+      <c r="A48" s="106" t="s">
+        <v>401</v>
+      </c>
+      <c r="B48" s="63" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C48" s="20" t="s">
+        <v>426</v>
+      </c>
+      <c r="D48" s="20" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>427</v>
+      </c>
+      <c r="F48" s="121" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="42">
+      <c r="A49" s="105" t="s">
+        <v>401</v>
+      </c>
+      <c r="B49" s="152" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C49" s="61" t="s">
+        <v>428</v>
+      </c>
+      <c r="D49" s="61" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E49" s="61" t="s">
+        <v>429</v>
+      </c>
+      <c r="F49" s="120" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="28">
+      <c r="A50" s="103" t="s">
+        <v>401</v>
+      </c>
+      <c r="B50" s="155" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C50" s="39" t="s">
+        <v>431</v>
+      </c>
+      <c r="D50" s="39" t="s">
         <v>816</v>
       </c>
-      <c r="E43" s="35" t="s">
-        <v>529</v>
-      </c>
-      <c r="F43" s="117" t="s">
+      <c r="E50" s="39" t="s">
         <v>817</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" ht="70">
-      <c r="A44" s="102" t="s">
-        <v>414</v>
-      </c>
-      <c r="B44" s="154" t="s">
-        <v>592</v>
-      </c>
-      <c r="C44" s="33" t="s">
-        <v>870</v>
-      </c>
-      <c r="D44" s="33" t="s">
-        <v>1170</v>
-      </c>
-      <c r="E44" s="35" t="s">
-        <v>871</v>
-      </c>
-      <c r="F44" s="117" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="56">
-      <c r="A45" s="102" t="s">
-        <v>414</v>
-      </c>
-      <c r="B45" s="154" t="s">
-        <v>592</v>
-      </c>
-      <c r="C45" s="33" t="s">
-        <v>873</v>
-      </c>
-      <c r="D45" s="33" t="s">
-        <v>1171</v>
-      </c>
-      <c r="E45" s="35" t="s">
-        <v>874</v>
-      </c>
-      <c r="F45" s="117" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="45" customHeight="1">
-      <c r="A46" s="102" t="s">
-        <v>414</v>
-      </c>
-      <c r="B46" s="154" t="s">
-        <v>592</v>
-      </c>
-      <c r="C46" s="33" t="s">
-        <v>883</v>
-      </c>
-      <c r="D46" s="33" t="s">
-        <v>1172</v>
-      </c>
-      <c r="E46" s="35" t="s">
-        <v>884</v>
-      </c>
-      <c r="F46" s="117" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="28">
-      <c r="A47" s="106" t="s">
-        <v>414</v>
-      </c>
-      <c r="B47" s="63" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C47" s="20" t="s">
+      <c r="F50" s="118" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="42">
+      <c r="A51" s="98" t="s">
+        <v>401</v>
+      </c>
+      <c r="B51" s="53" t="s">
+        <v>818</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>819</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>820</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>821</v>
+      </c>
+      <c r="F51" s="86" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="56">
+      <c r="A52" s="98" t="s">
+        <v>401</v>
+      </c>
+      <c r="B52" s="159" t="s">
+        <v>823</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>824</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>826</v>
+      </c>
+      <c r="F52" s="86" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="28">
+      <c r="A53" s="101" t="s">
+        <v>401</v>
+      </c>
+      <c r="B53" s="151" t="s">
+        <v>774</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>435</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>827</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="F53" s="116" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="28">
+      <c r="A54" s="109" t="s">
+        <v>401</v>
+      </c>
+      <c r="B54" s="65" t="s">
+        <v>436</v>
+      </c>
+      <c r="C54" s="42" t="s">
+        <v>437</v>
+      </c>
+      <c r="D54" s="42" t="s">
+        <v>438</v>
+      </c>
+      <c r="E54" s="42" t="s">
         <v>439</v>
       </c>
-      <c r="D47" s="20" t="s">
-        <v>1164</v>
-      </c>
-      <c r="E47" s="20" t="s">
+      <c r="F54" s="124" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="28">
+      <c r="A55" s="103" t="s">
+        <v>401</v>
+      </c>
+      <c r="B55" s="58" t="s">
+        <v>436</v>
+      </c>
+      <c r="C55" s="39" t="s">
         <v>440</v>
       </c>
-      <c r="F47" s="121" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="42">
-      <c r="A48" s="105" t="s">
-        <v>414</v>
-      </c>
-      <c r="B48" s="152" t="s">
-        <v>1083</v>
-      </c>
-      <c r="C48" s="61" t="s">
+      <c r="D55" s="39" t="s">
         <v>441</v>
       </c>
-      <c r="D48" s="61" t="s">
-        <v>1165</v>
-      </c>
-      <c r="E48" s="61" t="s">
+      <c r="E55" s="39" t="s">
+        <v>439</v>
+      </c>
+      <c r="F55" s="118" t="s">
         <v>442</v>
       </c>
-      <c r="F48" s="120" t="s">
+    </row>
+    <row r="56" spans="1:6" ht="42">
+      <c r="A56" s="103" t="s">
+        <v>401</v>
+      </c>
+      <c r="B56" s="155" t="s">
+        <v>436</v>
+      </c>
+      <c r="C56" s="39" t="s">
+        <v>798</v>
+      </c>
+      <c r="D56" s="156" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E56" s="39" t="s">
+        <v>799</v>
+      </c>
+      <c r="F56" s="118" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="186" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B57" s="187"/>
+      <c r="C57" s="187"/>
+      <c r="D57" s="187"/>
+      <c r="E57" s="187"/>
+      <c r="F57" s="188"/>
+    </row>
+    <row r="58" spans="1:6" ht="28">
+      <c r="A58" s="101" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" ht="28">
-      <c r="A49" s="103" t="s">
-        <v>414</v>
-      </c>
-      <c r="B49" s="155" t="s">
-        <v>592</v>
-      </c>
-      <c r="C49" s="39" t="s">
+      <c r="B58" s="56" t="s">
+        <v>402</v>
+      </c>
+      <c r="C58" s="10" t="s">
         <v>444</v>
       </c>
-      <c r="D49" s="39" t="s">
-        <v>832</v>
-      </c>
-      <c r="E49" s="39" t="s">
-        <v>833</v>
-      </c>
-      <c r="F49" s="118" t="s">
+      <c r="D58" s="10" t="s">
+        <v>445</v>
+      </c>
+      <c r="E58" s="10" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" ht="42">
-      <c r="A50" s="98" t="s">
-        <v>414</v>
-      </c>
-      <c r="B50" s="53" t="s">
-        <v>834</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>835</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>836</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>837</v>
-      </c>
-      <c r="F50" s="86" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="56">
-      <c r="A51" s="98" t="s">
-        <v>414</v>
-      </c>
-      <c r="B51" s="159" t="s">
-        <v>839</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>840</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>841</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>842</v>
-      </c>
-      <c r="F51" s="86" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="28">
-      <c r="A52" s="101" t="s">
-        <v>414</v>
-      </c>
-      <c r="B52" s="151" t="s">
-        <v>788</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>448</v>
-      </c>
-      <c r="D52" s="10" t="s">
-        <v>843</v>
-      </c>
-      <c r="E52" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="F52" s="116" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="28">
-      <c r="A53" s="109" t="s">
-        <v>414</v>
-      </c>
-      <c r="B53" s="65" t="s">
-        <v>449</v>
-      </c>
-      <c r="C53" s="42" t="s">
-        <v>450</v>
-      </c>
-      <c r="D53" s="42" t="s">
-        <v>451</v>
-      </c>
-      <c r="E53" s="42" t="s">
-        <v>452</v>
-      </c>
-      <c r="F53" s="124" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="28">
-      <c r="A54" s="103" t="s">
-        <v>414</v>
-      </c>
-      <c r="B54" s="58" t="s">
-        <v>449</v>
-      </c>
-      <c r="C54" s="39" t="s">
-        <v>453</v>
-      </c>
-      <c r="D54" s="39" t="s">
-        <v>454</v>
-      </c>
-      <c r="E54" s="39" t="s">
-        <v>452</v>
-      </c>
-      <c r="F54" s="118" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="42">
-      <c r="A55" s="103" t="s">
-        <v>414</v>
-      </c>
-      <c r="B55" s="155" t="s">
-        <v>449</v>
-      </c>
-      <c r="C55" s="39" t="s">
-        <v>812</v>
-      </c>
-      <c r="D55" s="156" t="s">
-        <v>1166</v>
-      </c>
-      <c r="E55" s="39" t="s">
-        <v>813</v>
-      </c>
-      <c r="F55" s="118" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56" s="219" t="s">
-        <v>1066</v>
-      </c>
-      <c r="B56" s="220"/>
-      <c r="C56" s="220"/>
-      <c r="D56" s="220"/>
-      <c r="E56" s="220"/>
-      <c r="F56" s="221"/>
-    </row>
-    <row r="57" spans="1:6" ht="28">
-      <c r="A57" s="101" t="s">
-        <v>456</v>
-      </c>
-      <c r="B57" s="56" t="s">
-        <v>415</v>
-      </c>
-      <c r="C57" s="10" t="s">
-        <v>457</v>
-      </c>
-      <c r="D57" s="10" t="s">
-        <v>458</v>
-      </c>
-      <c r="E57" s="10" t="s">
-        <v>459</v>
-      </c>
-      <c r="F57" s="116" t="s">
+      <c r="F58" s="116" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="28">
-      <c r="A58" s="100" t="s">
-        <v>456</v>
-      </c>
-      <c r="B58" s="55" t="s">
-        <v>460</v>
-      </c>
-      <c r="C58" s="50" t="s">
-        <v>461</v>
-      </c>
-      <c r="D58" s="50" t="s">
-        <v>462</v>
-      </c>
-      <c r="E58" s="50" t="s">
-        <v>463</v>
-      </c>
-      <c r="F58" s="115" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="28">
       <c r="A59" s="100" t="s">
+        <v>443</v>
+      </c>
+      <c r="B59" s="55" t="s">
+        <v>447</v>
+      </c>
+      <c r="C59" s="50" t="s">
+        <v>448</v>
+      </c>
+      <c r="D59" s="50" t="s">
+        <v>449</v>
+      </c>
+      <c r="E59" s="50" t="s">
+        <v>450</v>
+      </c>
+      <c r="F59" s="115" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="28">
+      <c r="A60" s="100" t="s">
+        <v>443</v>
+      </c>
+      <c r="B60" s="55" t="s">
+        <v>452</v>
+      </c>
+      <c r="C60" s="50" t="s">
+        <v>453</v>
+      </c>
+      <c r="D60" s="50" t="s">
+        <v>454</v>
+      </c>
+      <c r="E60" s="50" t="s">
+        <v>455</v>
+      </c>
+      <c r="F60" s="115" t="s">
         <v>456</v>
       </c>
-      <c r="B59" s="55" t="s">
+    </row>
+    <row r="61" spans="1:6" ht="28">
+      <c r="A61" s="101" t="s">
+        <v>443</v>
+      </c>
+      <c r="B61" s="56" t="s">
+        <v>457</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>458</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="F61" s="116" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="28">
+      <c r="A62" s="99" t="s">
+        <v>443</v>
+      </c>
+      <c r="B62" s="54" t="s">
+        <v>461</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>462</v>
+      </c>
+      <c r="D62" s="25" t="s">
+        <v>463</v>
+      </c>
+      <c r="E62" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="F62" s="85" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="28">
+      <c r="A63" s="105" t="s">
+        <v>443</v>
+      </c>
+      <c r="B63" s="60" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C63" s="61" t="s">
+        <v>464</v>
+      </c>
+      <c r="D63" s="61" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E63" s="61" t="s">
+        <v>411</v>
+      </c>
+      <c r="F63" s="120" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="28">
+      <c r="A64" s="106" t="s">
+        <v>443</v>
+      </c>
+      <c r="B64" s="63" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C64" s="20" t="s">
+        <v>466</v>
+      </c>
+      <c r="D64" s="20" t="s">
+        <v>467</v>
+      </c>
+      <c r="E64" s="20" t="s">
+        <v>468</v>
+      </c>
+      <c r="F64" s="121" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="28">
+      <c r="A65" s="105" t="s">
+        <v>443</v>
+      </c>
+      <c r="B65" s="60" t="s">
+        <v>815</v>
+      </c>
+      <c r="C65" s="61" t="s">
+        <v>471</v>
+      </c>
+      <c r="D65" s="61" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E65" s="61" t="s">
         <v>465</v>
       </c>
-      <c r="C59" s="50" t="s">
-        <v>466</v>
-      </c>
-      <c r="D59" s="50" t="s">
-        <v>467</v>
-      </c>
-      <c r="E59" s="50" t="s">
-        <v>468</v>
-      </c>
-      <c r="F59" s="115" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="28">
-      <c r="A60" s="101" t="s">
-        <v>456</v>
-      </c>
-      <c r="B60" s="56" t="s">
-        <v>470</v>
-      </c>
-      <c r="C60" s="10" t="s">
-        <v>471</v>
-      </c>
-      <c r="D60" s="10" t="s">
+      <c r="F65" s="120" t="s">
         <v>472</v>
       </c>
-      <c r="E60" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="F60" s="116" t="s">
+    </row>
+    <row r="66" spans="1:6" ht="45">
+      <c r="A66" s="110" t="s">
+        <v>443</v>
+      </c>
+      <c r="B66" s="91" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C66" s="92" t="s">
+        <v>754</v>
+      </c>
+      <c r="D66" s="92" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E66" s="92" t="s">
+        <v>755</v>
+      </c>
+      <c r="F66" s="125" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="28">
+      <c r="A67" s="105" t="s">
+        <v>443</v>
+      </c>
+      <c r="B67" s="60" t="s">
+        <v>477</v>
+      </c>
+      <c r="C67" s="61" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" ht="28">
-      <c r="A61" s="99" t="s">
-        <v>456</v>
-      </c>
-      <c r="B61" s="54" t="s">
+      <c r="D67" s="61" t="s">
         <v>474</v>
       </c>
-      <c r="C61" s="15" t="s">
+      <c r="E67" s="61" t="s">
         <v>475</v>
       </c>
-      <c r="D61" s="25" t="s">
+      <c r="F67" s="120" t="s">
         <v>476</v>
       </c>
-      <c r="E61" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="F61" s="85" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="28">
-      <c r="A62" s="105" t="s">
-        <v>456</v>
-      </c>
-      <c r="B62" s="60" t="s">
-        <v>1084</v>
-      </c>
-      <c r="C62" s="61" t="s">
-        <v>477</v>
-      </c>
-      <c r="D62" s="61" t="s">
-        <v>1085</v>
-      </c>
-      <c r="E62" s="61" t="s">
-        <v>424</v>
-      </c>
-      <c r="F62" s="120" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="28">
-      <c r="A63" s="106" t="s">
-        <v>456</v>
-      </c>
-      <c r="B63" s="63" t="s">
-        <v>1035</v>
-      </c>
-      <c r="C63" s="20" t="s">
+    </row>
+    <row r="68" spans="1:6" ht="28">
+      <c r="A68" s="107" t="s">
+        <v>443</v>
+      </c>
+      <c r="B68" s="64" t="s">
+        <v>770</v>
+      </c>
+      <c r="C68" s="36" t="s">
+        <v>478</v>
+      </c>
+      <c r="D68" s="36" t="s">
         <v>479</v>
       </c>
-      <c r="D63" s="20" t="s">
+      <c r="E68" s="36" t="s">
         <v>480</v>
       </c>
-      <c r="E63" s="20" t="s">
+      <c r="F68" s="122" t="s">
         <v>481</v>
       </c>
-      <c r="F63" s="121" t="s">
+    </row>
+    <row r="69" spans="1:6" ht="28">
+      <c r="A69" s="109" t="s">
+        <v>443</v>
+      </c>
+      <c r="B69" s="65" t="s">
+        <v>771</v>
+      </c>
+      <c r="C69" s="42" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" ht="28">
-      <c r="A64" s="105" t="s">
-        <v>456</v>
-      </c>
-      <c r="B64" s="60" t="s">
-        <v>831</v>
-      </c>
-      <c r="C64" s="61" t="s">
+      <c r="D69" s="44" t="s">
+        <v>483</v>
+      </c>
+      <c r="E69" s="42" t="s">
         <v>484</v>
       </c>
-      <c r="D64" s="61" t="s">
-        <v>1086</v>
-      </c>
-      <c r="E64" s="61" t="s">
-        <v>478</v>
-      </c>
-      <c r="F64" s="120" t="s">
+      <c r="F69" s="124" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="45">
-      <c r="A65" s="110" t="s">
-        <v>456</v>
-      </c>
-      <c r="B65" s="91" t="s">
-        <v>1087</v>
-      </c>
-      <c r="C65" s="92" t="s">
-        <v>768</v>
-      </c>
-      <c r="D65" s="92" t="s">
-        <v>1088</v>
-      </c>
-      <c r="E65" s="92" t="s">
-        <v>769</v>
-      </c>
-      <c r="F65" s="125" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="28">
-      <c r="A66" s="105" t="s">
-        <v>456</v>
-      </c>
-      <c r="B66" s="60" t="s">
+    <row r="70" spans="1:6" ht="28">
+      <c r="A70" s="101" t="s">
+        <v>443</v>
+      </c>
+      <c r="B70" s="128" t="s">
+        <v>774</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>487</v>
+      </c>
+      <c r="D70" s="10"/>
+      <c r="E70" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="F70" s="116" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" s="186" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B71" s="187"/>
+      <c r="C71" s="187"/>
+      <c r="D71" s="187"/>
+      <c r="E71" s="187"/>
+      <c r="F71" s="188"/>
+    </row>
+    <row r="72" spans="1:6" ht="28">
+      <c r="A72" s="101" t="s">
+        <v>489</v>
+      </c>
+      <c r="B72" s="56" t="s">
+        <v>402</v>
+      </c>
+      <c r="C72" s="10" t="s">
         <v>490</v>
       </c>
-      <c r="C66" s="61" t="s">
-        <v>486</v>
-      </c>
-      <c r="D66" s="61" t="s">
-        <v>487</v>
-      </c>
-      <c r="E66" s="61" t="s">
-        <v>488</v>
-      </c>
-      <c r="F66" s="120" t="s">
+      <c r="D72" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F72" s="116" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="28">
+      <c r="A73" s="105" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" ht="28">
-      <c r="A67" s="107" t="s">
-        <v>456</v>
-      </c>
-      <c r="B67" s="64" t="s">
-        <v>784</v>
-      </c>
-      <c r="C67" s="36" t="s">
-        <v>491</v>
-      </c>
-      <c r="D67" s="36" t="s">
+      <c r="B73" s="60" t="s">
         <v>492</v>
       </c>
-      <c r="E67" s="36" t="s">
+      <c r="C73" s="61" t="s">
         <v>493</v>
       </c>
-      <c r="F67" s="122" t="s">
+      <c r="D73" s="62" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" ht="28">
-      <c r="A68" s="109" t="s">
-        <v>456</v>
-      </c>
-      <c r="B68" s="65" t="s">
-        <v>785</v>
-      </c>
-      <c r="C68" s="42" t="s">
+      <c r="E73" s="61" t="s">
         <v>495</v>
       </c>
-      <c r="D68" s="44" t="s">
+      <c r="F73" s="120" t="s">
         <v>496</v>
       </c>
-      <c r="E68" s="42" t="s">
+    </row>
+    <row r="74" spans="1:6" ht="30">
+      <c r="A74" s="108" t="s">
+        <v>489</v>
+      </c>
+      <c r="B74" s="89" t="s">
+        <v>757</v>
+      </c>
+      <c r="C74" s="90" t="s">
+        <v>758</v>
+      </c>
+      <c r="D74" s="90" t="s">
+        <v>759</v>
+      </c>
+      <c r="E74" s="90" t="s">
+        <v>760</v>
+      </c>
+      <c r="F74" s="123" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="28">
+      <c r="A75" s="103" t="s">
+        <v>489</v>
+      </c>
+      <c r="B75" s="58" t="s">
+        <v>772</v>
+      </c>
+      <c r="C75" s="39" t="s">
         <v>497</v>
       </c>
-      <c r="F68" s="124" t="s">
+      <c r="D75" s="39" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" ht="28">
-      <c r="A69" s="101" t="s">
-        <v>456</v>
-      </c>
-      <c r="B69" s="128" t="s">
-        <v>788</v>
-      </c>
-      <c r="C69" s="10" t="s">
+      <c r="E75" s="39" t="s">
+        <v>499</v>
+      </c>
+      <c r="F75" s="118" t="s">
         <v>500</v>
       </c>
-      <c r="D69" s="10"/>
-      <c r="E69" s="10" t="s">
+    </row>
+    <row r="76" spans="1:6" ht="28">
+      <c r="A76" s="104" t="s">
+        <v>489</v>
+      </c>
+      <c r="B76" s="59" t="s">
+        <v>389</v>
+      </c>
+      <c r="C76" s="47" t="s">
         <v>501</v>
       </c>
-      <c r="F69" s="116" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70" s="219" t="s">
-        <v>1067</v>
-      </c>
-      <c r="B70" s="220"/>
-      <c r="C70" s="220"/>
-      <c r="D70" s="220"/>
-      <c r="E70" s="220"/>
-      <c r="F70" s="221"/>
-    </row>
-    <row r="71" spans="1:6" ht="28">
-      <c r="A71" s="101" t="s">
+      <c r="D76" s="47" t="s">
         <v>502</v>
       </c>
-      <c r="B71" s="56" t="s">
-        <v>415</v>
-      </c>
-      <c r="C71" s="10" t="s">
+      <c r="E76" s="47" t="s">
         <v>503</v>
       </c>
-      <c r="D71" s="10" t="s">
+      <c r="F76" s="119" t="s">
         <v>504</v>
       </c>
-      <c r="E71" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F71" s="116" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="28">
-      <c r="A72" s="105" t="s">
-        <v>502</v>
-      </c>
-      <c r="B72" s="60" t="s">
+    </row>
+    <row r="77" spans="1:6" ht="28">
+      <c r="A77" s="105" t="s">
+        <v>489</v>
+      </c>
+      <c r="B77" s="60" t="s">
         <v>505</v>
       </c>
-      <c r="C72" s="61" t="s">
+      <c r="C77" s="61" t="s">
         <v>506</v>
       </c>
-      <c r="D72" s="62" t="s">
+      <c r="D77" s="61" t="s">
         <v>507</v>
       </c>
-      <c r="E72" s="61" t="s">
+      <c r="E77" s="61" t="s">
         <v>508</v>
       </c>
-      <c r="F72" s="120" t="s">
+      <c r="F77" s="120" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="30">
-      <c r="A73" s="108" t="s">
-        <v>502</v>
-      </c>
-      <c r="B73" s="89" t="s">
-        <v>771</v>
-      </c>
-      <c r="C73" s="90" t="s">
-        <v>772</v>
-      </c>
-      <c r="D73" s="90" t="s">
-        <v>773</v>
-      </c>
-      <c r="E73" s="90" t="s">
-        <v>774</v>
-      </c>
-      <c r="F73" s="123" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="28">
-      <c r="A74" s="103" t="s">
-        <v>502</v>
-      </c>
-      <c r="B74" s="58" t="s">
-        <v>786</v>
-      </c>
-      <c r="C74" s="39" t="s">
+    <row r="78" spans="1:6" ht="28">
+      <c r="A78" s="98" t="s">
+        <v>489</v>
+      </c>
+      <c r="B78" s="53" t="s">
         <v>510</v>
       </c>
-      <c r="D74" s="39" t="s">
+      <c r="C78" s="5" t="s">
         <v>511</v>
       </c>
-      <c r="E74" s="39" t="s">
+      <c r="D78" s="5" t="s">
         <v>512</v>
       </c>
-      <c r="F74" s="118" t="s">
+      <c r="E78" s="5" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" ht="28">
-      <c r="A75" s="104" t="s">
-        <v>502</v>
-      </c>
-      <c r="B75" s="59" t="s">
-        <v>398</v>
-      </c>
-      <c r="C75" s="47" t="s">
+      <c r="F78" s="86" t="s">
         <v>514</v>
       </c>
-      <c r="D75" s="47" t="s">
+    </row>
+    <row r="79" spans="1:6" ht="28">
+      <c r="A79" s="105" t="s">
+        <v>489</v>
+      </c>
+      <c r="B79" s="60" t="s">
         <v>515</v>
       </c>
-      <c r="E75" s="47" t="s">
+      <c r="C79" s="61" t="s">
+        <v>517</v>
+      </c>
+      <c r="D79" s="61" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E79" s="61" t="s">
+        <v>518</v>
+      </c>
+      <c r="F79" s="120" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="28">
+      <c r="A80" s="104" t="s">
+        <v>489</v>
+      </c>
+      <c r="B80" s="59" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C80" s="47" t="s">
+        <v>520</v>
+      </c>
+      <c r="D80" s="47" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E80" s="47" t="s">
         <v>516</v>
       </c>
-      <c r="F75" s="119" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="28">
-      <c r="A76" s="105" t="s">
-        <v>502</v>
-      </c>
-      <c r="B76" s="60" t="s">
-        <v>518</v>
-      </c>
-      <c r="C76" s="61" t="s">
-        <v>519</v>
-      </c>
-      <c r="D76" s="61" t="s">
-        <v>520</v>
-      </c>
-      <c r="E76" s="61" t="s">
+      <c r="F80" s="119" t="s">
         <v>521</v>
       </c>
-      <c r="F76" s="120" t="s">
+    </row>
+    <row r="81" spans="1:6" ht="28">
+      <c r="A81" s="106" t="s">
+        <v>489</v>
+      </c>
+      <c r="B81" s="63" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C81" s="20" t="s">
         <v>522</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" ht="28">
-      <c r="A77" s="98" t="s">
-        <v>502</v>
-      </c>
-      <c r="B77" s="53" t="s">
+      <c r="D81" s="20" t="s">
         <v>523</v>
       </c>
-      <c r="C77" s="5" t="s">
+      <c r="E81" s="20" t="s">
         <v>524</v>
       </c>
-      <c r="D77" s="5" t="s">
+      <c r="F81" s="121" t="s">
         <v>525</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>526</v>
-      </c>
-      <c r="F77" s="86" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="28">
-      <c r="A78" s="105" t="s">
-        <v>502</v>
-      </c>
-      <c r="B78" s="60" t="s">
-        <v>528</v>
-      </c>
-      <c r="C78" s="61" t="s">
-        <v>530</v>
-      </c>
-      <c r="D78" s="61" t="s">
-        <v>1167</v>
-      </c>
-      <c r="E78" s="61" t="s">
-        <v>531</v>
-      </c>
-      <c r="F78" s="120" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="28">
-      <c r="A79" s="104" t="s">
-        <v>502</v>
-      </c>
-      <c r="B79" s="59" t="s">
-        <v>1089</v>
-      </c>
-      <c r="C79" s="47" t="s">
-        <v>533</v>
-      </c>
-      <c r="D79" s="47" t="s">
-        <v>1168</v>
-      </c>
-      <c r="E79" s="47" t="s">
-        <v>529</v>
-      </c>
-      <c r="F79" s="119" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="28">
-      <c r="A80" s="106" t="s">
-        <v>502</v>
-      </c>
-      <c r="B80" s="63" t="s">
-        <v>1090</v>
-      </c>
-      <c r="C80" s="20" t="s">
-        <v>535</v>
-      </c>
-      <c r="D80" s="20" t="s">
-        <v>536</v>
-      </c>
-      <c r="E80" s="20" t="s">
-        <v>537</v>
-      </c>
-      <c r="F80" s="121" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="28">
-      <c r="A81" s="102" t="s">
-        <v>502</v>
-      </c>
-      <c r="B81" s="57" t="s">
-        <v>539</v>
-      </c>
-      <c r="C81" s="33" t="s">
-        <v>540</v>
-      </c>
-      <c r="D81" s="33" t="s">
-        <v>541</v>
-      </c>
-      <c r="E81" s="33" t="s">
-        <v>542</v>
-      </c>
-      <c r="F81" s="117" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="28">
       <c r="A82" s="102" t="s">
-        <v>502</v>
-      </c>
-      <c r="B82" s="154" t="s">
-        <v>592</v>
+        <v>489</v>
+      </c>
+      <c r="B82" s="57" t="s">
+        <v>526</v>
       </c>
       <c r="C82" s="33" t="s">
-        <v>809</v>
+        <v>527</v>
       </c>
       <c r="D82" s="33" t="s">
-        <v>810</v>
+        <v>528</v>
       </c>
       <c r="E82" s="33" t="s">
         <v>529</v>
       </c>
       <c r="F82" s="117" t="s">
-        <v>811</v>
+        <v>29</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="28">
-      <c r="A83" s="107" t="s">
-        <v>502</v>
-      </c>
-      <c r="B83" s="64" t="s">
-        <v>447</v>
-      </c>
-      <c r="C83" s="36" t="s">
-        <v>543</v>
-      </c>
-      <c r="D83" s="36" t="s">
-        <v>544</v>
-      </c>
-      <c r="E83" s="36" t="s">
+      <c r="A83" s="102" t="s">
+        <v>489</v>
+      </c>
+      <c r="B83" s="154" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C83" s="33" t="s">
+        <v>795</v>
+      </c>
+      <c r="D83" s="33" t="s">
+        <v>796</v>
+      </c>
+      <c r="E83" s="33" t="s">
+        <v>516</v>
+      </c>
+      <c r="F83" s="117" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="28">
+      <c r="A84" s="107" t="s">
+        <v>489</v>
+      </c>
+      <c r="B84" s="64" t="s">
+        <v>434</v>
+      </c>
+      <c r="C84" s="36" t="s">
+        <v>530</v>
+      </c>
+      <c r="D84" s="36" t="s">
+        <v>531</v>
+      </c>
+      <c r="E84" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="F83" s="122" t="s">
+      <c r="F84" s="122" t="s">
         <v>208</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="28">
-      <c r="A84" s="101" t="s">
-        <v>502</v>
-      </c>
-      <c r="B84" s="56" t="s">
-        <v>545</v>
-      </c>
-      <c r="C84" s="10" t="s">
-        <v>546</v>
-      </c>
-      <c r="D84" s="10" t="s">
-        <v>547</v>
-      </c>
-      <c r="E84" s="10" t="s">
-        <v>445</v>
-      </c>
-      <c r="F84" s="116" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="28">
       <c r="A85" s="101" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="B85" s="56" t="s">
-        <v>499</v>
+        <v>532</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>548</v>
+        <v>533</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>549</v>
+        <v>534</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>501</v>
+        <v>432</v>
       </c>
       <c r="F85" s="116" t="s">
-        <v>473</v>
+        <v>29</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="28">
-      <c r="A86" s="103" t="s">
-        <v>502</v>
-      </c>
-      <c r="B86" s="58" t="s">
-        <v>449</v>
-      </c>
-      <c r="C86" s="39" t="s">
-        <v>550</v>
-      </c>
-      <c r="D86" s="39" t="s">
-        <v>551</v>
-      </c>
-      <c r="E86" s="39" t="s">
-        <v>452</v>
-      </c>
-      <c r="F86" s="118" t="s">
-        <v>552</v>
+      <c r="A86" s="101" t="s">
+        <v>489</v>
+      </c>
+      <c r="B86" s="56" t="s">
+        <v>486</v>
+      </c>
+      <c r="C86" s="10" t="s">
+        <v>535</v>
+      </c>
+      <c r="D86" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="E86" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="F86" s="116" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="28">
       <c r="A87" s="103" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="B87" s="58" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="C87" s="39" t="s">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="D87" s="39" t="s">
-        <v>554</v>
+        <v>538</v>
       </c>
       <c r="E87" s="39" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="F87" s="118" t="s">
-        <v>555</v>
+        <v>539</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="28">
       <c r="A88" s="103" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="B88" s="58" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="C88" s="39" t="s">
-        <v>556</v>
+        <v>540</v>
       </c>
       <c r="D88" s="39" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="E88" s="39" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="F88" s="118" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="45">
-      <c r="A89" s="108" t="s">
-        <v>502</v>
-      </c>
-      <c r="B89" s="89" t="s">
-        <v>449</v>
-      </c>
-      <c r="C89" s="90" t="s">
-        <v>776</v>
-      </c>
-      <c r="D89" s="95" t="s">
-        <v>777</v>
-      </c>
-      <c r="E89" s="90" t="s">
-        <v>778</v>
-      </c>
-      <c r="F89" s="123" t="s">
-        <v>779</v>
+        <v>542</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="28">
+      <c r="A89" s="103" t="s">
+        <v>489</v>
+      </c>
+      <c r="B89" s="58" t="s">
+        <v>436</v>
+      </c>
+      <c r="C89" s="39" t="s">
+        <v>543</v>
+      </c>
+      <c r="D89" s="39" t="s">
+        <v>544</v>
+      </c>
+      <c r="E89" s="39" t="s">
+        <v>439</v>
+      </c>
+      <c r="F89" s="118" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="45">
       <c r="A90" s="108" t="s">
-        <v>502</v>
-      </c>
-      <c r="B90" s="153" t="s">
-        <v>449</v>
+        <v>489</v>
+      </c>
+      <c r="B90" s="89" t="s">
+        <v>436</v>
       </c>
       <c r="C90" s="90" t="s">
-        <v>806</v>
+        <v>762</v>
       </c>
       <c r="D90" s="95" t="s">
-        <v>807</v>
+        <v>763</v>
       </c>
       <c r="E90" s="90" t="s">
-        <v>778</v>
+        <v>764</v>
       </c>
       <c r="F90" s="123" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91" s="222" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B91" s="223"/>
-      <c r="C91" s="223"/>
-      <c r="D91" s="223"/>
-      <c r="E91" s="223"/>
-      <c r="F91" s="224"/>
-    </row>
-    <row r="92" spans="1:6" ht="28">
-      <c r="A92" s="101" t="s">
-        <v>559</v>
-      </c>
-      <c r="B92" s="56" t="s">
-        <v>415</v>
-      </c>
-      <c r="C92" s="10" t="s">
-        <v>560</v>
-      </c>
-      <c r="D92" s="10"/>
-      <c r="E92" s="10" t="s">
-        <v>459</v>
-      </c>
-      <c r="F92" s="116" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="45">
+      <c r="A91" s="108" t="s">
+        <v>489</v>
+      </c>
+      <c r="B91" s="153" t="s">
+        <v>436</v>
+      </c>
+      <c r="C91" s="90" t="s">
+        <v>792</v>
+      </c>
+      <c r="D91" s="95" t="s">
+        <v>793</v>
+      </c>
+      <c r="E91" s="90" t="s">
+        <v>764</v>
+      </c>
+      <c r="F91" s="123" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" s="189" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B92" s="190"/>
+      <c r="C92" s="190"/>
+      <c r="D92" s="190"/>
+      <c r="E92" s="190"/>
+      <c r="F92" s="191"/>
+    </row>
+    <row r="93" spans="1:6" ht="28">
+      <c r="A93" s="101" t="s">
+        <v>546</v>
+      </c>
+      <c r="B93" s="56" t="s">
+        <v>402</v>
+      </c>
+      <c r="C93" s="10" t="s">
+        <v>547</v>
+      </c>
+      <c r="D93" s="10"/>
+      <c r="E93" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="F93" s="116" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="28">
-      <c r="A93" s="100" t="s">
-        <v>559</v>
-      </c>
-      <c r="B93" s="55" t="s">
-        <v>460</v>
-      </c>
-      <c r="C93" s="50" t="s">
-        <v>561</v>
-      </c>
-      <c r="D93" s="50" t="s">
-        <v>562</v>
-      </c>
-      <c r="E93" s="50" t="s">
-        <v>463</v>
-      </c>
-      <c r="F93" s="115" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="28">
       <c r="A94" s="100" t="s">
+        <v>546</v>
+      </c>
+      <c r="B94" s="55" t="s">
+        <v>447</v>
+      </c>
+      <c r="C94" s="50" t="s">
+        <v>548</v>
+      </c>
+      <c r="D94" s="50" t="s">
+        <v>549</v>
+      </c>
+      <c r="E94" s="50" t="s">
+        <v>450</v>
+      </c>
+      <c r="F94" s="115" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="28">
+      <c r="A95" s="100" t="s">
+        <v>546</v>
+      </c>
+      <c r="B95" s="55" t="s">
+        <v>452</v>
+      </c>
+      <c r="C95" s="50" t="s">
+        <v>551</v>
+      </c>
+      <c r="D95" s="50" t="s">
+        <v>552</v>
+      </c>
+      <c r="E95" s="50" t="s">
+        <v>455</v>
+      </c>
+      <c r="F95" s="115" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="28">
+      <c r="A96" s="101" t="s">
+        <v>546</v>
+      </c>
+      <c r="B96" s="56" t="s">
+        <v>457</v>
+      </c>
+      <c r="C96" s="10" t="s">
+        <v>554</v>
+      </c>
+      <c r="D96" s="10" t="s">
+        <v>555</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>556</v>
+      </c>
+      <c r="F96" s="116" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="28">
+      <c r="A97" s="99" t="s">
+        <v>546</v>
+      </c>
+      <c r="B97" s="54" t="s">
+        <v>461</v>
+      </c>
+      <c r="C97" s="15" t="s">
+        <v>558</v>
+      </c>
+      <c r="D97" s="15" t="s">
         <v>559</v>
       </c>
-      <c r="B94" s="55" t="s">
-        <v>465</v>
-      </c>
-      <c r="C94" s="50" t="s">
+      <c r="E97" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="F97" s="85" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="28">
+      <c r="A98" s="105" t="s">
+        <v>546</v>
+      </c>
+      <c r="B98" s="60" t="s">
+        <v>560</v>
+      </c>
+      <c r="C98" s="61" t="s">
+        <v>561</v>
+      </c>
+      <c r="D98" s="61" t="s">
+        <v>562</v>
+      </c>
+      <c r="E98" s="61" t="s">
+        <v>563</v>
+      </c>
+      <c r="F98" s="120" t="s">
         <v>564</v>
       </c>
-      <c r="D94" s="50" t="s">
+    </row>
+    <row r="99" spans="1:6" ht="56">
+      <c r="A99" s="105" t="s">
+        <v>546</v>
+      </c>
+      <c r="B99" s="60" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C99" s="61" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D99" s="61" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E99" s="61" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F99" s="120" t="s">
         <v>565</v>
       </c>
-      <c r="E94" s="50" t="s">
-        <v>468</v>
-      </c>
-      <c r="F94" s="115" t="s">
+    </row>
+    <row r="100" spans="1:6" ht="28">
+      <c r="A100" s="105" t="s">
+        <v>546</v>
+      </c>
+      <c r="B100" s="60" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C100" s="61" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" ht="28">
-      <c r="A95" s="101" t="s">
-        <v>559</v>
-      </c>
-      <c r="B95" s="56" t="s">
-        <v>470</v>
-      </c>
-      <c r="C95" s="10" t="s">
+      <c r="D100" s="61" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E100" s="61" t="s">
         <v>567</v>
       </c>
-      <c r="D95" s="10" t="s">
+      <c r="F100" s="120" t="s">
         <v>568</v>
       </c>
-      <c r="E95" s="10" t="s">
+    </row>
+    <row r="101" spans="1:6" ht="28">
+      <c r="A101" s="106" t="s">
+        <v>546</v>
+      </c>
+      <c r="B101" s="63" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C101" s="20" t="s">
         <v>569</v>
       </c>
-      <c r="F95" s="116" t="s">
+      <c r="D101" s="20" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E101" s="20" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="96" spans="1:6" ht="28">
-      <c r="A96" s="99" t="s">
-        <v>559</v>
-      </c>
-      <c r="B96" s="54" t="s">
-        <v>474</v>
-      </c>
-      <c r="C96" s="15" t="s">
+      <c r="F101" s="121" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="28">
+      <c r="A102" s="105" t="s">
+        <v>546</v>
+      </c>
+      <c r="B102" s="60" t="s">
         <v>571</v>
       </c>
-      <c r="D96" s="15" t="s">
+      <c r="C102" s="61" t="s">
         <v>572</v>
       </c>
-      <c r="E96" s="15" t="s">
-        <v>192</v>
-      </c>
-      <c r="F96" s="85" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="28">
-      <c r="A97" s="105" t="s">
-        <v>559</v>
-      </c>
-      <c r="B97" s="60" t="s">
+      <c r="D102" s="61" t="s">
         <v>573</v>
       </c>
-      <c r="C97" s="61" t="s">
-        <v>574</v>
-      </c>
-      <c r="D97" s="61" t="s">
-        <v>575</v>
-      </c>
-      <c r="E97" s="61" t="s">
-        <v>576</v>
-      </c>
-      <c r="F97" s="120" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="56">
-      <c r="A98" s="105" t="s">
-        <v>559</v>
-      </c>
-      <c r="B98" s="60" t="s">
-        <v>1076</v>
-      </c>
-      <c r="C98" s="61" t="s">
-        <v>1073</v>
-      </c>
-      <c r="D98" s="61" t="s">
-        <v>1074</v>
-      </c>
-      <c r="E98" s="61" t="s">
-        <v>1075</v>
-      </c>
-      <c r="F98" s="120" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" ht="28">
-      <c r="A99" s="105" t="s">
-        <v>559</v>
-      </c>
-      <c r="B99" s="60" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C99" s="61" t="s">
-        <v>579</v>
-      </c>
-      <c r="D99" s="61" t="s">
-        <v>1078</v>
-      </c>
-      <c r="E99" s="61" t="s">
-        <v>580</v>
-      </c>
-      <c r="F99" s="120" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" ht="28">
-      <c r="A100" s="106" t="s">
-        <v>559</v>
-      </c>
-      <c r="B100" s="63" t="s">
-        <v>1079</v>
-      </c>
-      <c r="C100" s="20" t="s">
-        <v>582</v>
-      </c>
-      <c r="D100" s="20" t="s">
-        <v>1080</v>
-      </c>
-      <c r="E100" s="20" t="s">
-        <v>583</v>
-      </c>
-      <c r="F100" s="121" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" ht="28">
-      <c r="A101" s="105" t="s">
-        <v>559</v>
-      </c>
-      <c r="B101" s="60" t="s">
-        <v>584</v>
-      </c>
-      <c r="C101" s="61" t="s">
-        <v>585</v>
-      </c>
-      <c r="D101" s="61" t="s">
-        <v>586</v>
-      </c>
-      <c r="E101" s="61" t="s">
+      <c r="E102" s="61" t="s">
         <v>98</v>
-      </c>
-      <c r="F101" s="120" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" ht="42">
-      <c r="A102" s="105" t="s">
-        <v>559</v>
-      </c>
-      <c r="B102" s="152" t="s">
-        <v>592</v>
-      </c>
-      <c r="C102" s="61" t="s">
-        <v>804</v>
-      </c>
-      <c r="D102" s="61" t="s">
-        <v>805</v>
-      </c>
-      <c r="E102" s="61" t="s">
-        <v>529</v>
       </c>
       <c r="F102" s="120" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="154">
+    <row r="103" spans="1:6" ht="42">
       <c r="A103" s="105" t="s">
-        <v>559</v>
+        <v>546</v>
       </c>
       <c r="B103" s="152" t="s">
-        <v>592</v>
+        <v>1180</v>
       </c>
       <c r="C103" s="61" t="s">
-        <v>916</v>
+        <v>790</v>
       </c>
       <c r="D103" s="61" t="s">
-        <v>917</v>
+        <v>791</v>
       </c>
       <c r="E103" s="61" t="s">
-        <v>918</v>
+        <v>516</v>
       </c>
       <c r="F103" s="120" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" ht="28">
-      <c r="A104" s="109" t="s">
-        <v>559</v>
-      </c>
-      <c r="B104" s="65" t="s">
-        <v>587</v>
-      </c>
-      <c r="C104" s="42" t="s">
-        <v>588</v>
-      </c>
-      <c r="D104" s="42" t="s">
-        <v>589</v>
-      </c>
-      <c r="E104" s="42" t="s">
-        <v>590</v>
-      </c>
-      <c r="F104" s="124" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="30">
-      <c r="A105" s="111" t="s">
-        <v>559</v>
-      </c>
-      <c r="B105" s="93" t="s">
-        <v>780</v>
-      </c>
-      <c r="C105" s="94" t="s">
-        <v>781</v>
-      </c>
-      <c r="D105" s="94" t="s">
-        <v>782</v>
-      </c>
-      <c r="E105" s="94" t="s">
-        <v>783</v>
-      </c>
-      <c r="F105" s="126" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="154">
+      <c r="A104" s="105" t="s">
+        <v>546</v>
+      </c>
+      <c r="B104" s="152" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C104" s="61" t="s">
+        <v>900</v>
+      </c>
+      <c r="D104" s="61" t="s">
+        <v>901</v>
+      </c>
+      <c r="E104" s="61" t="s">
+        <v>902</v>
+      </c>
+      <c r="F104" s="120" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="28">
+      <c r="A105" s="109" t="s">
+        <v>546</v>
+      </c>
+      <c r="B105" s="65" t="s">
+        <v>574</v>
+      </c>
+      <c r="C105" s="42" t="s">
+        <v>575</v>
+      </c>
+      <c r="D105" s="42" t="s">
+        <v>576</v>
+      </c>
+      <c r="E105" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="F105" s="124" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="30">
+      <c r="A106" s="111" t="s">
+        <v>546</v>
+      </c>
+      <c r="B106" s="93" t="s">
+        <v>766</v>
+      </c>
+      <c r="C106" s="94" t="s">
+        <v>767</v>
+      </c>
+      <c r="D106" s="94" t="s">
+        <v>768</v>
+      </c>
+      <c r="E106" s="94" t="s">
+        <v>769</v>
+      </c>
+      <c r="F106" s="126" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="28">
-      <c r="A106" s="101" t="s">
-        <v>559</v>
-      </c>
-      <c r="B106" s="128" t="s">
-        <v>788</v>
-      </c>
-      <c r="C106" s="10" t="s">
-        <v>787</v>
-      </c>
-      <c r="D106" s="10"/>
-      <c r="E106" s="10" t="s">
-        <v>501</v>
-      </c>
-      <c r="F106" s="116" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" ht="42">
-      <c r="A107" s="102" t="s">
-        <v>559</v>
-      </c>
-      <c r="B107" s="57" t="s">
-        <v>592</v>
-      </c>
-      <c r="C107" s="33" t="s">
-        <v>593</v>
-      </c>
-      <c r="D107" s="33" t="s">
-        <v>594</v>
-      </c>
-      <c r="E107" s="33" t="s">
-        <v>445</v>
-      </c>
-      <c r="F107" s="117" t="s">
+    <row r="107" spans="1:6" ht="28">
+      <c r="A107" s="101" t="s">
+        <v>546</v>
+      </c>
+      <c r="B107" s="128" t="s">
+        <v>774</v>
+      </c>
+      <c r="C107" s="10" t="s">
+        <v>773</v>
+      </c>
+      <c r="D107" s="10"/>
+      <c r="E107" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="F107" s="116" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="42">
+      <c r="A108" s="102" t="s">
+        <v>546</v>
+      </c>
+      <c r="B108" s="154" t="s">
+        <v>774</v>
+      </c>
+      <c r="C108" s="33" t="s">
+        <v>579</v>
+      </c>
+      <c r="D108" s="33" t="s">
+        <v>580</v>
+      </c>
+      <c r="E108" s="33" t="s">
+        <v>432</v>
+      </c>
+      <c r="F108" s="117" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="28">
-      <c r="A108" s="103" t="s">
-        <v>559</v>
-      </c>
-      <c r="B108" s="58" t="s">
-        <v>592</v>
-      </c>
-      <c r="C108" s="39" t="s">
-        <v>820</v>
-      </c>
-      <c r="D108" s="39" t="s">
-        <v>821</v>
-      </c>
-      <c r="E108" s="39" t="s">
-        <v>445</v>
-      </c>
-      <c r="F108" s="118" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109" s="222" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B109" s="223"/>
-      <c r="C109" s="223"/>
-      <c r="D109" s="223"/>
-      <c r="E109" s="223"/>
-      <c r="F109" s="224"/>
-    </row>
-    <row r="110" spans="1:6" ht="28">
-      <c r="A110" s="101" t="s">
-        <v>595</v>
-      </c>
-      <c r="B110" s="56" t="s">
-        <v>415</v>
-      </c>
-      <c r="C110" s="10" t="s">
-        <v>503</v>
-      </c>
-      <c r="D110" s="10" t="s">
-        <v>596</v>
-      </c>
-      <c r="E110" s="10" t="s">
+    <row r="109" spans="1:6" ht="28">
+      <c r="A109" s="103" t="s">
+        <v>546</v>
+      </c>
+      <c r="B109" s="155" t="s">
+        <v>774</v>
+      </c>
+      <c r="C109" s="39" t="s">
+        <v>806</v>
+      </c>
+      <c r="D109" s="39" t="s">
+        <v>807</v>
+      </c>
+      <c r="E109" s="39" t="s">
+        <v>432</v>
+      </c>
+      <c r="F109" s="118" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" s="189" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B110" s="190"/>
+      <c r="C110" s="190"/>
+      <c r="D110" s="190"/>
+      <c r="E110" s="190"/>
+      <c r="F110" s="191"/>
+    </row>
+    <row r="111" spans="1:6" ht="28">
+      <c r="A111" s="101" t="s">
+        <v>581</v>
+      </c>
+      <c r="B111" s="56" t="s">
+        <v>402</v>
+      </c>
+      <c r="C111" s="10" t="s">
+        <v>490</v>
+      </c>
+      <c r="D111" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="E111" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F110" s="116" t="s">
+      <c r="F111" s="116" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" ht="28">
-      <c r="A111" s="105" t="s">
-        <v>595</v>
-      </c>
-      <c r="B111" s="60" t="s">
-        <v>416</v>
-      </c>
-      <c r="C111" s="61" t="s">
-        <v>597</v>
-      </c>
-      <c r="D111" s="61" t="s">
-        <v>598</v>
-      </c>
-      <c r="E111" s="61" t="s">
-        <v>419</v>
-      </c>
-      <c r="F111" s="120" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="28">
       <c r="A112" s="105" t="s">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="B112" s="60" t="s">
-        <v>600</v>
+        <v>403</v>
       </c>
       <c r="C112" s="61" t="s">
-        <v>601</v>
+        <v>583</v>
       </c>
       <c r="D112" s="61" t="s">
-        <v>602</v>
+        <v>584</v>
       </c>
       <c r="E112" s="61" t="s">
-        <v>603</v>
+        <v>406</v>
       </c>
       <c r="F112" s="120" t="s">
-        <v>604</v>
+        <v>585</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="28">
       <c r="A113" s="105" t="s">
+        <v>581</v>
+      </c>
+      <c r="B113" s="60" t="s">
+        <v>586</v>
+      </c>
+      <c r="C113" s="61" t="s">
+        <v>587</v>
+      </c>
+      <c r="D113" s="61" t="s">
+        <v>588</v>
+      </c>
+      <c r="E113" s="61" t="s">
+        <v>589</v>
+      </c>
+      <c r="F113" s="120" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" ht="28">
+      <c r="A114" s="105" t="s">
+        <v>581</v>
+      </c>
+      <c r="B114" s="60" t="s">
+        <v>505</v>
+      </c>
+      <c r="C114" s="61" t="s">
+        <v>591</v>
+      </c>
+      <c r="D114" s="61" t="s">
+        <v>592</v>
+      </c>
+      <c r="E114" s="61" t="s">
+        <v>593</v>
+      </c>
+      <c r="F114" s="120" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="56">
+      <c r="A115" s="105" t="s">
+        <v>581</v>
+      </c>
+      <c r="B115" s="152" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C115" s="61" t="s">
+        <v>786</v>
+      </c>
+      <c r="D115" s="61" t="s">
+        <v>787</v>
+      </c>
+      <c r="E115" s="61" t="s">
+        <v>788</v>
+      </c>
+      <c r="F115" s="120" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="28">
+      <c r="A116" s="98" t="s">
+        <v>581</v>
+      </c>
+      <c r="B116" s="53" t="s">
+        <v>594</v>
+      </c>
+      <c r="C116" s="5" t="s">
         <v>595</v>
       </c>
-      <c r="B113" s="60" t="s">
-        <v>518</v>
-      </c>
-      <c r="C113" s="61" t="s">
+      <c r="D116" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="E116" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="F116" s="86" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="28">
+      <c r="A117" s="102" t="s">
+        <v>581</v>
+      </c>
+      <c r="B117" s="57" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C117" s="33" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D117" s="33" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E117" s="33" t="s">
+        <v>598</v>
+      </c>
+      <c r="F117" s="117" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="28">
+      <c r="A118" s="105" t="s">
+        <v>581</v>
+      </c>
+      <c r="B118" s="60" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C118" s="61" t="s">
+        <v>599</v>
+      </c>
+      <c r="D118" s="61" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E118" s="61" t="s">
+        <v>394</v>
+      </c>
+      <c r="F118" s="120" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="28">
+      <c r="A119" s="106" t="s">
+        <v>581</v>
+      </c>
+      <c r="B119" s="63" t="s">
+        <v>601</v>
+      </c>
+      <c r="C119" s="20" t="s">
+        <v>602</v>
+      </c>
+      <c r="D119" s="20" t="s">
+        <v>603</v>
+      </c>
+      <c r="E119" s="20" t="s">
+        <v>427</v>
+      </c>
+      <c r="F119" s="121" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="28">
+      <c r="A120" s="109" t="s">
+        <v>581</v>
+      </c>
+      <c r="B120" s="65" t="s">
+        <v>470</v>
+      </c>
+      <c r="C120" s="42" t="s">
+        <v>604</v>
+      </c>
+      <c r="D120" s="42" t="s">
         <v>605</v>
       </c>
-      <c r="D113" s="61" t="s">
+      <c r="E120" s="42" t="s">
         <v>606</v>
       </c>
-      <c r="E113" s="61" t="s">
+      <c r="F120" s="124" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="140">
+      <c r="A121" s="99" t="s">
+        <v>581</v>
+      </c>
+      <c r="B121" s="54" t="s">
         <v>607</v>
       </c>
-      <c r="F113" s="120" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" ht="56">
-      <c r="A114" s="105" t="s">
-        <v>595</v>
-      </c>
-      <c r="B114" s="152" t="s">
-        <v>592</v>
-      </c>
-      <c r="C114" s="61" t="s">
-        <v>800</v>
-      </c>
-      <c r="D114" s="61" t="s">
-        <v>801</v>
-      </c>
-      <c r="E114" s="61" t="s">
-        <v>802</v>
-      </c>
-      <c r="F114" s="120" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" ht="28">
-      <c r="A115" s="98" t="s">
-        <v>595</v>
-      </c>
-      <c r="B115" s="53" t="s">
+      <c r="C121" s="15" t="s">
+        <v>881</v>
+      </c>
+      <c r="D121" s="15" t="s">
+        <v>882</v>
+      </c>
+      <c r="E121" s="15" t="s">
+        <v>883</v>
+      </c>
+      <c r="F121" s="85" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="28">
+      <c r="A122" s="103" t="s">
+        <v>581</v>
+      </c>
+      <c r="B122" s="58" t="s">
         <v>608</v>
       </c>
-      <c r="C115" s="5" t="s">
+      <c r="C122" s="39" t="s">
         <v>609</v>
       </c>
-      <c r="D115" s="5" t="s">
+      <c r="D122" s="39" t="s">
         <v>610</v>
       </c>
-      <c r="E115" s="5" t="s">
+      <c r="E122" s="39" t="s">
         <v>611</v>
       </c>
-      <c r="F115" s="86" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" ht="28">
-      <c r="A116" s="102" t="s">
-        <v>595</v>
-      </c>
-      <c r="B116" s="57" t="s">
-        <v>1091</v>
-      </c>
-      <c r="C116" s="33" t="s">
-        <v>1071</v>
-      </c>
-      <c r="D116" s="33" t="s">
-        <v>1072</v>
-      </c>
-      <c r="E116" s="33" t="s">
+      <c r="F122" s="118" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" ht="28">
+      <c r="A123" s="101" t="s">
+        <v>581</v>
+      </c>
+      <c r="B123" s="56" t="s">
         <v>612</v>
       </c>
-      <c r="F116" s="117" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" ht="28">
-      <c r="A117" s="105" t="s">
-        <v>595</v>
-      </c>
-      <c r="B117" s="60" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C117" s="61" t="s">
+      <c r="C123" s="10" t="s">
         <v>613</v>
       </c>
-      <c r="D117" s="61" t="s">
-        <v>1169</v>
-      </c>
-      <c r="E117" s="61" t="s">
-        <v>407</v>
-      </c>
-      <c r="F117" s="120" t="s">
+      <c r="D123" s="10" t="s">
         <v>614</v>
       </c>
-    </row>
-    <row r="118" spans="1:6" ht="28">
-      <c r="A118" s="106" t="s">
-        <v>595</v>
-      </c>
-      <c r="B118" s="63" t="s">
-        <v>615</v>
-      </c>
-      <c r="C118" s="20" t="s">
-        <v>616</v>
-      </c>
-      <c r="D118" s="20" t="s">
-        <v>617</v>
-      </c>
-      <c r="E118" s="20" t="s">
-        <v>440</v>
-      </c>
-      <c r="F118" s="121" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" ht="28">
-      <c r="A119" s="109" t="s">
-        <v>595</v>
-      </c>
-      <c r="B119" s="65" t="s">
-        <v>483</v>
-      </c>
-      <c r="C119" s="42" t="s">
-        <v>618</v>
-      </c>
-      <c r="D119" s="42" t="s">
-        <v>619</v>
-      </c>
-      <c r="E119" s="42" t="s">
-        <v>620</v>
-      </c>
-      <c r="F119" s="124" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" ht="140">
-      <c r="A120" s="99" t="s">
-        <v>595</v>
-      </c>
-      <c r="B120" s="54" t="s">
-        <v>621</v>
-      </c>
-      <c r="C120" s="15" t="s">
-        <v>897</v>
-      </c>
-      <c r="D120" s="15" t="s">
-        <v>898</v>
-      </c>
-      <c r="E120" s="15" t="s">
-        <v>899</v>
-      </c>
-      <c r="F120" s="85" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" ht="28">
-      <c r="A121" s="103" t="s">
-        <v>595</v>
-      </c>
-      <c r="B121" s="58" t="s">
-        <v>622</v>
-      </c>
-      <c r="C121" s="39" t="s">
-        <v>623</v>
-      </c>
-      <c r="D121" s="39" t="s">
-        <v>624</v>
-      </c>
-      <c r="E121" s="39" t="s">
-        <v>625</v>
-      </c>
-      <c r="F121" s="118" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" ht="28">
-      <c r="A122" s="101" t="s">
-        <v>595</v>
-      </c>
-      <c r="B122" s="56" t="s">
-        <v>626</v>
-      </c>
-      <c r="C122" s="10" t="s">
-        <v>627</v>
-      </c>
-      <c r="D122" s="10" t="s">
-        <v>628</v>
-      </c>
-      <c r="E122" s="10" t="s">
-        <v>501</v>
-      </c>
-      <c r="F122" s="116" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" ht="28">
-      <c r="A123" s="103" t="s">
-        <v>595</v>
-      </c>
-      <c r="B123" s="58" t="s">
-        <v>449</v>
-      </c>
-      <c r="C123" s="39" t="s">
-        <v>629</v>
-      </c>
-      <c r="D123" s="39" t="s">
-        <v>630</v>
-      </c>
-      <c r="E123" s="39" t="s">
-        <v>452</v>
-      </c>
-      <c r="F123" s="118" t="s">
-        <v>301</v>
+      <c r="E123" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="F123" s="116" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="28">
       <c r="A124" s="103" t="s">
-        <v>595</v>
+        <v>581</v>
       </c>
       <c r="B124" s="58" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="C124" s="39" t="s">
-        <v>631</v>
+        <v>615</v>
       </c>
       <c r="D124" s="39" t="s">
-        <v>632</v>
+        <v>616</v>
       </c>
       <c r="E124" s="39" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="F124" s="118" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" ht="238">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="28">
       <c r="A125" s="103" t="s">
-        <v>595</v>
-      </c>
-      <c r="B125" s="155" t="s">
-        <v>449</v>
+        <v>581</v>
+      </c>
+      <c r="B125" s="58" t="s">
+        <v>436</v>
       </c>
       <c r="C125" s="39" t="s">
-        <v>906</v>
+        <v>617</v>
       </c>
       <c r="D125" s="39" t="s">
-        <v>907</v>
+        <v>618</v>
       </c>
       <c r="E125" s="39" t="s">
-        <v>908</v>
+        <v>439</v>
       </c>
       <c r="F125" s="118" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" ht="32">
-      <c r="A126" s="104" t="s">
-        <v>595</v>
-      </c>
-      <c r="B126" s="59" t="s">
-        <v>449</v>
-      </c>
-      <c r="C126" s="47" t="s">
-        <v>823</v>
-      </c>
-      <c r="D126" s="47" t="s">
-        <v>824</v>
-      </c>
-      <c r="E126" s="47" t="s">
-        <v>452</v>
-      </c>
-      <c r="F126" s="119" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127" s="225" t="s">
-        <v>635</v>
-      </c>
-      <c r="B127" s="226"/>
-      <c r="C127" s="226"/>
-      <c r="D127" s="226"/>
-      <c r="E127" s="226"/>
-      <c r="F127" s="227"/>
-    </row>
-    <row r="128" spans="1:6" ht="28">
-      <c r="A128" s="101" t="s">
-        <v>636</v>
-      </c>
-      <c r="B128" s="56" t="s">
-        <v>637</v>
-      </c>
-      <c r="C128" s="10" t="s">
-        <v>560</v>
-      </c>
-      <c r="D128" s="10" t="s">
-        <v>638</v>
-      </c>
-      <c r="E128" s="10" t="s">
-        <v>459</v>
-      </c>
-      <c r="F128" s="116" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="238">
+      <c r="A126" s="103" t="s">
+        <v>581</v>
+      </c>
+      <c r="B126" s="155" t="s">
+        <v>436</v>
+      </c>
+      <c r="C126" s="39" t="s">
+        <v>890</v>
+      </c>
+      <c r="D126" s="39" t="s">
+        <v>891</v>
+      </c>
+      <c r="E126" s="39" t="s">
+        <v>892</v>
+      </c>
+      <c r="F126" s="118" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="32">
+      <c r="A127" s="104" t="s">
+        <v>581</v>
+      </c>
+      <c r="B127" s="59" t="s">
+        <v>436</v>
+      </c>
+      <c r="C127" s="47" t="s">
+        <v>809</v>
+      </c>
+      <c r="D127" s="47" t="s">
+        <v>810</v>
+      </c>
+      <c r="E127" s="47" t="s">
+        <v>439</v>
+      </c>
+      <c r="F127" s="119" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="A128" s="192" t="s">
+        <v>621</v>
+      </c>
+      <c r="B128" s="193"/>
+      <c r="C128" s="193"/>
+      <c r="D128" s="193"/>
+      <c r="E128" s="193"/>
+      <c r="F128" s="194"/>
+    </row>
+    <row r="129" spans="1:6" ht="28">
+      <c r="A129" s="101" t="s">
+        <v>622</v>
+      </c>
+      <c r="B129" s="56" t="s">
+        <v>623</v>
+      </c>
+      <c r="C129" s="10" t="s">
+        <v>547</v>
+      </c>
+      <c r="D129" s="10" t="s">
+        <v>624</v>
+      </c>
+      <c r="E129" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="F129" s="116" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" ht="28">
-      <c r="A129" s="100" t="s">
-        <v>636</v>
-      </c>
-      <c r="B129" s="55" t="s">
-        <v>639</v>
-      </c>
-      <c r="C129" s="50" t="s">
-        <v>640</v>
-      </c>
-      <c r="D129" s="50" t="s">
-        <v>641</v>
-      </c>
-      <c r="E129" s="50" t="s">
-        <v>569</v>
-      </c>
-      <c r="F129" s="115" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="28">
       <c r="A130" s="100" t="s">
-        <v>636</v>
+        <v>622</v>
       </c>
       <c r="B130" s="55" t="s">
-        <v>643</v>
+        <v>625</v>
       </c>
       <c r="C130" s="50" t="s">
-        <v>644</v>
+        <v>626</v>
       </c>
       <c r="D130" s="50" t="s">
-        <v>645</v>
+        <v>627</v>
       </c>
       <c r="E130" s="50" t="s">
-        <v>646</v>
+        <v>556</v>
       </c>
       <c r="F130" s="115" t="s">
-        <v>355</v>
+        <v>628</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="28">
       <c r="A131" s="100" t="s">
+        <v>622</v>
+      </c>
+      <c r="B131" s="55" t="s">
+        <v>629</v>
+      </c>
+      <c r="C131" s="50" t="s">
+        <v>630</v>
+      </c>
+      <c r="D131" s="50" t="s">
+        <v>631</v>
+      </c>
+      <c r="E131" s="50" t="s">
+        <v>632</v>
+      </c>
+      <c r="F131" s="115" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="28">
+      <c r="A132" s="100" t="s">
+        <v>622</v>
+      </c>
+      <c r="B132" s="55" t="s">
+        <v>633</v>
+      </c>
+      <c r="C132" s="50" t="s">
+        <v>634</v>
+      </c>
+      <c r="D132" s="50" t="s">
+        <v>635</v>
+      </c>
+      <c r="E132" s="50" t="s">
         <v>636</v>
       </c>
-      <c r="B131" s="55" t="s">
+      <c r="F132" s="115" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="28">
+      <c r="A133" s="99" t="s">
+        <v>622</v>
+      </c>
+      <c r="B133" s="54" t="s">
+        <v>638</v>
+      </c>
+      <c r="C133" s="15" t="s">
+        <v>639</v>
+      </c>
+      <c r="D133" s="15" t="s">
+        <v>640</v>
+      </c>
+      <c r="E133" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="F133" s="85" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" ht="28">
+      <c r="A134" s="98" t="s">
+        <v>622</v>
+      </c>
+      <c r="B134" s="53" t="s">
+        <v>641</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>642</v>
+      </c>
+      <c r="D134" s="5" t="s">
+        <v>643</v>
+      </c>
+      <c r="E134" s="5" t="s">
+        <v>644</v>
+      </c>
+      <c r="F134" s="114" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" ht="28">
+      <c r="A135" s="99" t="s">
+        <v>622</v>
+      </c>
+      <c r="B135" s="54" t="s">
+        <v>645</v>
+      </c>
+      <c r="C135" s="15" t="s">
+        <v>646</v>
+      </c>
+      <c r="D135" s="15" t="s">
         <v>647</v>
       </c>
-      <c r="C131" s="50" t="s">
+      <c r="E135" s="15" t="s">
         <v>648</v>
       </c>
-      <c r="D131" s="50" t="s">
+      <c r="F135" s="113" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" ht="28">
+      <c r="A136" s="98" t="s">
+        <v>622</v>
+      </c>
+      <c r="B136" s="53" t="s">
         <v>649</v>
       </c>
-      <c r="E131" s="50" t="s">
+      <c r="C136" s="5" t="s">
         <v>650</v>
       </c>
-      <c r="F131" s="115" t="s">
+      <c r="D136" s="5" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="132" spans="1:6" ht="28">
-      <c r="A132" s="99" t="s">
-        <v>636</v>
-      </c>
-      <c r="B132" s="54" t="s">
+      <c r="E136" s="5" t="s">
         <v>652</v>
       </c>
-      <c r="C132" s="15" t="s">
+      <c r="F136" s="114" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="29" thickBot="1">
+      <c r="A137" s="112" t="s">
+        <v>622</v>
+      </c>
+      <c r="B137" s="96" t="s">
+        <v>400</v>
+      </c>
+      <c r="C137" s="97" t="s">
         <v>653</v>
       </c>
-      <c r="D132" s="15" t="s">
+      <c r="D137" s="97" t="s">
         <v>654</v>
       </c>
-      <c r="E132" s="15" t="s">
-        <v>354</v>
-      </c>
-      <c r="F132" s="85" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" ht="28">
-      <c r="A133" s="98" t="s">
-        <v>636</v>
-      </c>
-      <c r="B133" s="53" t="s">
+      <c r="E137" s="97" t="s">
         <v>655</v>
       </c>
-      <c r="C133" s="5" t="s">
+      <c r="F137" s="127" t="s">
         <v>656</v>
-      </c>
-      <c r="D133" s="5" t="s">
-        <v>657</v>
-      </c>
-      <c r="E133" s="5" t="s">
-        <v>658</v>
-      </c>
-      <c r="F133" s="114" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" ht="28">
-      <c r="A134" s="99" t="s">
-        <v>636</v>
-      </c>
-      <c r="B134" s="54" t="s">
-        <v>659</v>
-      </c>
-      <c r="C134" s="15" t="s">
-        <v>660</v>
-      </c>
-      <c r="D134" s="15" t="s">
-        <v>661</v>
-      </c>
-      <c r="E134" s="15" t="s">
-        <v>662</v>
-      </c>
-      <c r="F134" s="113" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" ht="28">
-      <c r="A135" s="98" t="s">
-        <v>636</v>
-      </c>
-      <c r="B135" s="53" t="s">
-        <v>663</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>664</v>
-      </c>
-      <c r="D135" s="5" t="s">
-        <v>665</v>
-      </c>
-      <c r="E135" s="5" t="s">
-        <v>666</v>
-      </c>
-      <c r="F135" s="114" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" ht="29" thickBot="1">
-      <c r="A136" s="112" t="s">
-        <v>636</v>
-      </c>
-      <c r="B136" s="96" t="s">
-        <v>413</v>
-      </c>
-      <c r="C136" s="97" t="s">
-        <v>667</v>
-      </c>
-      <c r="D136" s="97" t="s">
-        <v>668</v>
-      </c>
-      <c r="E136" s="97" t="s">
-        <v>669</v>
-      </c>
-      <c r="F136" s="127" t="s">
-        <v>670</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A56:F56"/>
-    <mergeCell ref="A70:F70"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A109:F109"/>
-    <mergeCell ref="A127:F127"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="A110:F110"/>
+    <mergeCell ref="A128:F128"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -17140,22 +17000,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="228" t="s">
-        <v>1002</v>
-      </c>
-      <c r="B1" s="228"/>
-      <c r="C1" s="228"/>
-      <c r="D1" s="228"/>
-      <c r="E1" s="228"/>
+      <c r="A1" s="211" t="s">
+        <v>986</v>
+      </c>
+      <c r="B1" s="211"/>
+      <c r="C1" s="211"/>
+      <c r="D1" s="211"/>
+      <c r="E1" s="211"/>
     </row>
     <row r="3" spans="1:5" ht="24" customHeight="1">
-      <c r="A3" s="229" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B3" s="229"/>
-      <c r="C3" s="229"/>
-      <c r="D3" s="229"/>
-      <c r="E3" s="229"/>
+      <c r="A3" s="212" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B3" s="212"/>
+      <c r="C3" s="212"/>
+      <c r="D3" s="212"/>
+      <c r="E3" s="212"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="12" t="s">
@@ -17179,13 +17039,13 @@
         <v>43</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1045</v>
+        <v>1028</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>1043</v>
+        <v>1026</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>1046</v>
+        <v>1029</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>44</v>
@@ -17230,7 +17090,7 @@
         <v>54</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>882</v>
+        <v>866</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>55</v>
@@ -17247,13 +17107,13 @@
         <v>45</v>
       </c>
       <c r="B9" s="69" t="s">
-        <v>671</v>
+        <v>657</v>
       </c>
       <c r="C9" s="67" t="s">
-        <v>672</v>
+        <v>658</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>673</v>
+        <v>659</v>
       </c>
       <c r="E9" s="68" t="s">
         <v>162</v>
@@ -17264,13 +17124,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="69" t="s">
-        <v>674</v>
+        <v>660</v>
       </c>
       <c r="C10" s="67" t="s">
         <v>182</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>675</v>
+        <v>661</v>
       </c>
       <c r="E10" s="68" t="s">
         <v>53</v>
@@ -17315,30 +17175,30 @@
         <v>58</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>876</v>
+        <v>860</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>872</v>
+        <v>856</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>877</v>
+        <v>861</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>878</v>
+        <v>862</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="42" customHeight="1">
       <c r="A14" s="20" t="s">
-        <v>879</v>
+        <v>863</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>880</v>
+        <v>864</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>875</v>
+        <v>859</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>881</v>
+        <v>865</v>
       </c>
       <c r="E14" s="23" t="s">
         <v>62</v>
@@ -17346,19 +17206,19 @@
     </row>
     <row r="15" spans="1:5" ht="56" customHeight="1">
       <c r="A15" s="20" t="s">
-        <v>886</v>
+        <v>870</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>887</v>
+        <v>871</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>885</v>
+        <v>869</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>888</v>
+        <v>872</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>889</v>
+        <v>873</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="70" customHeight="1">
@@ -17366,30 +17226,30 @@
         <v>80</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>976</v>
+        <v>960</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>894</v>
+        <v>878</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>895</v>
+        <v>879</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>896</v>
+        <v>880</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="62" customHeight="1">
       <c r="A17" s="20" t="s">
-        <v>942</v>
+        <v>926</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>977</v>
+        <v>961</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>949</v>
+        <v>933</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>950</v>
+        <v>934</v>
       </c>
       <c r="E17" s="23" t="s">
         <v>94</v>
@@ -17400,16 +17260,16 @@
         <v>45</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>978</v>
+        <v>962</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>951</v>
+        <v>935</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>952</v>
+        <v>936</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>943</v>
+        <v>927</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="62" customHeight="1">
@@ -17417,27 +17277,27 @@
         <v>45</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>979</v>
+        <v>963</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>953</v>
+        <v>937</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>954</v>
+        <v>938</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>943</v>
+        <v>927</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="30" customHeight="1"/>
     <row r="21" spans="1:5" ht="30" customHeight="1">
-      <c r="A21" s="207" t="s">
+      <c r="A21" s="208" t="s">
         <v>67</v>
       </c>
-      <c r="B21" s="207"/>
-      <c r="C21" s="207"/>
-      <c r="D21" s="207"/>
-      <c r="E21" s="207"/>
+      <c r="B21" s="208"/>
+      <c r="C21" s="208"/>
+      <c r="D21" s="208"/>
+      <c r="E21" s="208"/>
     </row>
     <row r="22" spans="1:5" ht="30" customHeight="1">
       <c r="A22" s="12" t="s">
@@ -17467,7 +17327,7 @@
         <v>29</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>937</v>
+        <v>921</v>
       </c>
       <c r="E23" s="18" t="s">
         <v>69</v>
@@ -17518,7 +17378,7 @@
         <v>82</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>939</v>
+        <v>923</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>83</v>
@@ -17529,13 +17389,13 @@
         <v>84</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>980</v>
+        <v>964</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>85</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>938</v>
+        <v>922</v>
       </c>
       <c r="E27" s="18" t="s">
         <v>86</v>
@@ -17546,13 +17406,13 @@
         <v>80</v>
       </c>
       <c r="B28" s="66" t="s">
-        <v>676</v>
+        <v>662</v>
       </c>
       <c r="C28" s="67" t="s">
-        <v>677</v>
+        <v>663</v>
       </c>
       <c r="D28" s="66" t="s">
-        <v>678</v>
+        <v>664</v>
       </c>
       <c r="E28" s="68" t="s">
         <v>202</v>
@@ -17580,13 +17440,13 @@
         <v>75</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>981</v>
+        <v>965</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>944</v>
+        <v>928</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>945</v>
+        <v>929</v>
       </c>
       <c r="E30" s="18" t="s">
         <v>189</v>
@@ -17597,27 +17457,27 @@
         <v>75</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>982</v>
+        <v>966</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>946</v>
+        <v>930</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>947</v>
+        <v>931</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>948</v>
+        <v>932</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="27.75" customHeight="1"/>
     <row r="33" spans="1:5" ht="30" customHeight="1">
-      <c r="A33" s="209" t="s">
+      <c r="A33" s="210" t="s">
         <v>91</v>
       </c>
-      <c r="B33" s="209"/>
-      <c r="C33" s="209"/>
-      <c r="D33" s="209"/>
-      <c r="E33" s="209"/>
+      <c r="B33" s="210"/>
+      <c r="C33" s="210"/>
+      <c r="D33" s="210"/>
+      <c r="E33" s="210"/>
     </row>
     <row r="34" spans="1:5" ht="30" customHeight="1">
       <c r="A34" s="12" t="s">
@@ -17777,13 +17637,13 @@
         <v>58</v>
       </c>
       <c r="B43" s="73" t="s">
-        <v>679</v>
+        <v>665</v>
       </c>
       <c r="C43" s="71" t="s">
         <v>233</v>
       </c>
       <c r="D43" s="70" t="s">
-        <v>680</v>
+        <v>666</v>
       </c>
       <c r="E43" s="72" t="s">
         <v>90</v>
@@ -17808,33 +17668,33 @@
     </row>
     <row r="45" spans="1:5" ht="140">
       <c r="A45" s="20" t="s">
-        <v>901</v>
+        <v>885</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>902</v>
+        <v>886</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>903</v>
+        <v>887</v>
       </c>
       <c r="D45" s="20" t="s">
-        <v>904</v>
+        <v>888</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>905</v>
+        <v>889</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="154">
       <c r="A46" s="20" t="s">
-        <v>901</v>
+        <v>885</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>920</v>
+        <v>904</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>921</v>
+        <v>905</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>922</v>
+        <v>906</v>
       </c>
       <c r="E46" s="23" t="s">
         <v>167</v>
@@ -17845,13 +17705,13 @@
         <v>58</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>910</v>
+        <v>894</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>911</v>
+        <v>895</v>
       </c>
       <c r="D47" s="20" t="s">
-        <v>912</v>
+        <v>896</v>
       </c>
       <c r="E47" s="23" t="s">
         <v>192</v>
@@ -17862,13 +17722,13 @@
         <v>58</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>913</v>
+        <v>897</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>914</v>
+        <v>898</v>
       </c>
       <c r="D48" s="20" t="s">
-        <v>915</v>
+        <v>899</v>
       </c>
       <c r="E48" s="23" t="s">
         <v>192</v>
@@ -17879,30 +17739,30 @@
         <v>75</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>983</v>
+        <v>967</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>940</v>
+        <v>924</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>941</v>
+        <v>925</v>
       </c>
       <c r="E49" s="23" t="s">
-        <v>936</v>
+        <v>920</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="62" customHeight="1">
       <c r="A50" s="20" t="s">
-        <v>942</v>
+        <v>926</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>984</v>
+        <v>968</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>959</v>
+        <v>943</v>
       </c>
       <c r="D50" s="20" t="s">
-        <v>960</v>
+        <v>944</v>
       </c>
       <c r="E50" s="23" t="s">
         <v>57</v>
@@ -17913,16 +17773,16 @@
         <v>75</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>985</v>
+        <v>969</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>971</v>
+        <v>955</v>
       </c>
       <c r="D51" s="20" t="s">
-        <v>972</v>
+        <v>956</v>
       </c>
       <c r="E51" s="23" t="s">
-        <v>973</v>
+        <v>957</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="62" customHeight="1"/>
@@ -17955,24 +17815,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18">
-      <c r="A1" s="185" t="s">
-        <v>955</v>
-      </c>
-      <c r="B1" s="186"/>
-      <c r="C1" s="186"/>
-      <c r="D1" s="186"/>
-      <c r="E1" s="186"/>
-      <c r="F1" s="187"/>
+      <c r="A1" s="225" t="s">
+        <v>939</v>
+      </c>
+      <c r="B1" s="226"/>
+      <c r="C1" s="226"/>
+      <c r="D1" s="226"/>
+      <c r="E1" s="226"/>
+      <c r="F1" s="227"/>
     </row>
     <row r="2" spans="1:6" ht="41" customHeight="1">
-      <c r="A2" s="188" t="s">
-        <v>956</v>
-      </c>
-      <c r="B2" s="189"/>
-      <c r="C2" s="189"/>
-      <c r="D2" s="189"/>
-      <c r="E2" s="189"/>
-      <c r="F2" s="190"/>
+      <c r="A2" s="228" t="s">
+        <v>940</v>
+      </c>
+      <c r="B2" s="229"/>
+      <c r="C2" s="229"/>
+      <c r="D2" s="229"/>
+      <c r="E2" s="229"/>
+      <c r="F2" s="230"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="77" t="s">
@@ -17995,14 +17855,14 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="191" t="s">
-        <v>1047</v>
-      </c>
-      <c r="B4" s="192"/>
-      <c r="C4" s="192"/>
-      <c r="D4" s="192"/>
-      <c r="E4" s="192"/>
-      <c r="F4" s="193"/>
+      <c r="A4" s="222" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B4" s="223"/>
+      <c r="C4" s="223"/>
+      <c r="D4" s="223"/>
+      <c r="E4" s="223"/>
+      <c r="F4" s="224"/>
     </row>
     <row r="5" spans="1:6" ht="28">
       <c r="A5" s="78" t="s">
@@ -18012,16 +17872,16 @@
         <v>134</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1048</v>
+        <v>1031</v>
       </c>
       <c r="D5" s="27" t="s">
         <v>135</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>1049</v>
+        <v>1032</v>
       </c>
       <c r="F5" s="84" t="s">
-        <v>1050</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="28">
@@ -18032,16 +17892,16 @@
         <v>137</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>1051</v>
+        <v>1034</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>1052</v>
+        <v>1035</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>1053</v>
+        <v>1036</v>
       </c>
       <c r="F6" s="85" t="s">
-        <v>1008</v>
+        <v>992</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28">
@@ -18052,67 +17912,67 @@
         <v>139</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>1054</v>
+        <v>1037</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>53</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>1055</v>
+        <v>1038</v>
       </c>
       <c r="F7" s="86" t="s">
-        <v>1056</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="28">
       <c r="A8" s="81" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="B8" s="75">
         <v>4.5</v>
       </c>
       <c r="C8" s="76" t="s">
-        <v>1057</v>
+        <v>1040</v>
       </c>
       <c r="D8" s="75" t="s">
-        <v>682</v>
+        <v>668</v>
       </c>
       <c r="E8" s="76" t="s">
-        <v>1058</v>
+        <v>1041</v>
       </c>
       <c r="F8" s="87" t="s">
-        <v>1059</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="28">
       <c r="A9" s="82" t="s">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="B9" s="68">
         <v>4.5</v>
       </c>
       <c r="C9" s="66" t="s">
-        <v>1060</v>
+        <v>1043</v>
       </c>
       <c r="D9" s="68" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
       <c r="E9" s="66" t="s">
-        <v>1061</v>
+        <v>1044</v>
       </c>
       <c r="F9" s="88" t="s">
-        <v>1062</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="191" t="s">
+      <c r="A10" s="222" t="s">
         <v>141</v>
       </c>
-      <c r="B10" s="192"/>
-      <c r="C10" s="192"/>
-      <c r="D10" s="192"/>
-      <c r="E10" s="192"/>
-      <c r="F10" s="193"/>
+      <c r="B10" s="223"/>
+      <c r="C10" s="223"/>
+      <c r="D10" s="223"/>
+      <c r="E10" s="223"/>
+      <c r="F10" s="224"/>
     </row>
     <row r="11" spans="1:6" ht="70">
       <c r="A11" s="78" t="s">
@@ -18128,7 +17988,7 @@
         <v>49</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>868</v>
+        <v>852</v>
       </c>
       <c r="F11" s="84" t="s">
         <v>143</v>
@@ -18176,133 +18036,133 @@
     </row>
     <row r="14" spans="1:6" ht="28">
       <c r="A14" s="81" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="B14" s="75">
         <v>4.8</v>
       </c>
       <c r="C14" s="76" t="s">
-        <v>684</v>
+        <v>670</v>
       </c>
       <c r="D14" s="75" t="s">
         <v>57</v>
       </c>
       <c r="E14" s="76" t="s">
-        <v>685</v>
+        <v>671</v>
       </c>
       <c r="F14" s="87" t="s">
-        <v>686</v>
+        <v>672</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28">
       <c r="A15" s="82" t="s">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="B15" s="68">
         <v>4.5999999999999996</v>
       </c>
       <c r="C15" s="66" t="s">
-        <v>715</v>
+        <v>701</v>
       </c>
       <c r="D15" s="68" t="s">
         <v>98</v>
       </c>
       <c r="E15" s="66" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="F15" s="88" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="42">
       <c r="A16" s="82" t="s">
-        <v>757</v>
+        <v>743</v>
       </c>
       <c r="B16" s="165" t="s">
-        <v>862</v>
+        <v>846</v>
       </c>
       <c r="C16" s="66" t="s">
-        <v>863</v>
+        <v>847</v>
       </c>
       <c r="D16" s="68" t="s">
-        <v>682</v>
+        <v>668</v>
       </c>
       <c r="E16" s="66" t="s">
-        <v>864</v>
+        <v>848</v>
       </c>
       <c r="F16" s="88" t="s">
-        <v>406</v>
+        <v>393</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="42">
       <c r="A17" s="82" t="s">
-        <v>760</v>
+        <v>746</v>
       </c>
       <c r="B17" s="165" t="s">
-        <v>865</v>
+        <v>849</v>
       </c>
       <c r="C17" s="66" t="s">
-        <v>866</v>
+        <v>850</v>
       </c>
       <c r="D17" s="68" t="s">
+        <v>835</v>
+      </c>
+      <c r="E17" s="66" t="s">
         <v>851</v>
       </c>
-      <c r="E17" s="66" t="s">
-        <v>867</v>
-      </c>
       <c r="F17" s="88" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="56">
       <c r="A18" s="166" t="s">
-        <v>844</v>
+        <v>828</v>
       </c>
       <c r="B18" s="167" t="s">
         <v>216</v>
       </c>
       <c r="C18" s="168" t="s">
-        <v>986</v>
+        <v>970</v>
       </c>
       <c r="D18" s="169" t="s">
-        <v>943</v>
+        <v>927</v>
       </c>
       <c r="E18" s="168" t="s">
-        <v>964</v>
+        <v>948</v>
       </c>
       <c r="F18" s="170" t="s">
-        <v>951</v>
+        <v>935</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="70">
       <c r="A19" s="166" t="s">
-        <v>848</v>
+        <v>832</v>
       </c>
       <c r="B19" s="167" t="s">
         <v>216</v>
       </c>
       <c r="C19" s="168" t="s">
-        <v>987</v>
+        <v>971</v>
       </c>
       <c r="D19" s="169" t="s">
-        <v>943</v>
+        <v>927</v>
       </c>
       <c r="E19" s="168" t="s">
-        <v>965</v>
+        <v>949</v>
       </c>
       <c r="F19" s="170" t="s">
-        <v>953</v>
+        <v>937</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="191" t="s">
+      <c r="A20" s="222" t="s">
         <v>152</v>
       </c>
-      <c r="B20" s="192"/>
-      <c r="C20" s="192"/>
-      <c r="D20" s="192"/>
-      <c r="E20" s="192"/>
-      <c r="F20" s="193"/>
+      <c r="B20" s="223"/>
+      <c r="C20" s="223"/>
+      <c r="D20" s="223"/>
+      <c r="E20" s="223"/>
+      <c r="F20" s="224"/>
     </row>
     <row r="21" spans="1:6" ht="28">
       <c r="A21" s="78" t="s">
@@ -18312,7 +18172,7 @@
         <v>154</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>957</v>
+        <v>941</v>
       </c>
       <c r="D21" s="27" t="s">
         <v>57</v>
@@ -18372,13 +18232,13 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C24" s="76" t="s">
-        <v>735</v>
+        <v>721</v>
       </c>
       <c r="D24" s="75" t="s">
         <v>218</v>
       </c>
       <c r="E24" s="76" t="s">
-        <v>736</v>
+        <v>722</v>
       </c>
       <c r="F24" s="87" t="s">
         <v>255</v>
@@ -18386,33 +18246,33 @@
     </row>
     <row r="25" spans="1:6" ht="28">
       <c r="A25" s="82" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="B25" s="68">
         <v>4.3</v>
       </c>
       <c r="C25" s="66" t="s">
-        <v>687</v>
+        <v>673</v>
       </c>
       <c r="D25" s="68" t="s">
         <v>218</v>
       </c>
       <c r="E25" s="66" t="s">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="F25" s="88" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="191" t="s">
+      <c r="A26" s="222" t="s">
         <v>165</v>
       </c>
-      <c r="B26" s="192"/>
-      <c r="C26" s="192"/>
-      <c r="D26" s="192"/>
-      <c r="E26" s="192"/>
-      <c r="F26" s="193"/>
+      <c r="B26" s="223"/>
+      <c r="C26" s="223"/>
+      <c r="D26" s="223"/>
+      <c r="E26" s="223"/>
+      <c r="F26" s="224"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="78" t="s">
@@ -18442,13 +18302,13 @@
         <v>137</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>988</v>
+        <v>972</v>
       </c>
       <c r="D28" s="18" t="s">
         <v>170</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>925</v>
+        <v>909</v>
       </c>
       <c r="F28" s="85" t="s">
         <v>171</v>
@@ -18476,53 +18336,53 @@
     </row>
     <row r="30" spans="1:6" ht="42">
       <c r="A30" s="81" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="B30" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C30" s="76" t="s">
-        <v>989</v>
+        <v>973</v>
       </c>
       <c r="D30" s="75" t="s">
         <v>140</v>
       </c>
       <c r="E30" s="76" t="s">
-        <v>926</v>
+        <v>910</v>
       </c>
       <c r="F30" s="87" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="28">
       <c r="A31" s="82" t="s">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="B31" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C31" s="66" t="s">
-        <v>718</v>
+        <v>704</v>
       </c>
       <c r="D31" s="68" t="s">
         <v>192</v>
       </c>
       <c r="E31" s="66" t="s">
-        <v>719</v>
+        <v>705</v>
       </c>
       <c r="F31" s="88" t="s">
-        <v>720</v>
+        <v>706</v>
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="191" t="s">
+      <c r="A32" s="222" t="s">
         <v>176</v>
       </c>
-      <c r="B32" s="192"/>
-      <c r="C32" s="192"/>
-      <c r="D32" s="192"/>
-      <c r="E32" s="192"/>
-      <c r="F32" s="193"/>
+      <c r="B32" s="223"/>
+      <c r="C32" s="223"/>
+      <c r="D32" s="223"/>
+      <c r="E32" s="223"/>
+      <c r="F32" s="224"/>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="78" t="s">
@@ -18572,33 +18432,33 @@
         <v>4.3</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>737</v>
+        <v>723</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>703</v>
+        <v>689</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>738</v>
+        <v>724</v>
       </c>
       <c r="F35" s="86" t="s">
-        <v>723</v>
+        <v>709</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="42">
       <c r="A36" s="81" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="B36" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C36" s="76" t="s">
-        <v>691</v>
+        <v>677</v>
       </c>
       <c r="D36" s="75" t="s">
         <v>145</v>
       </c>
       <c r="E36" s="76" t="s">
-        <v>692</v>
+        <v>678</v>
       </c>
       <c r="F36" s="87" t="s">
         <v>182</v>
@@ -18606,33 +18466,33 @@
     </row>
     <row r="37" spans="1:6" ht="28">
       <c r="A37" s="82" t="s">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="B37" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C37" s="66" t="s">
-        <v>721</v>
+        <v>707</v>
       </c>
       <c r="D37" s="68" t="s">
         <v>53</v>
       </c>
       <c r="E37" s="66" t="s">
-        <v>722</v>
+        <v>708</v>
       </c>
       <c r="F37" s="88" t="s">
-        <v>723</v>
+        <v>709</v>
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="194" t="s">
+      <c r="A38" s="219" t="s">
         <v>184</v>
       </c>
-      <c r="B38" s="195"/>
-      <c r="C38" s="195"/>
-      <c r="D38" s="195"/>
-      <c r="E38" s="195"/>
-      <c r="F38" s="196"/>
+      <c r="B38" s="220"/>
+      <c r="C38" s="220"/>
+      <c r="D38" s="220"/>
+      <c r="E38" s="220"/>
+      <c r="F38" s="221"/>
     </row>
     <row r="39" spans="1:6" ht="28">
       <c r="A39" s="78" t="s">
@@ -18642,16 +18502,16 @@
         <v>4.5</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>745</v>
+        <v>731</v>
       </c>
       <c r="D39" s="27" t="s">
         <v>192</v>
       </c>
       <c r="E39" s="28" t="s">
-        <v>746</v>
+        <v>732</v>
       </c>
       <c r="F39" s="84" t="s">
-        <v>747</v>
+        <v>733</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="42">
@@ -18662,13 +18522,13 @@
         <v>139</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="D40" s="18" t="s">
         <v>162</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>932</v>
+        <v>916</v>
       </c>
       <c r="F40" s="85" t="s">
         <v>186</v>
@@ -18696,19 +18556,19 @@
     </row>
     <row r="42" spans="1:6" ht="28">
       <c r="A42" s="81" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="B42" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C42" s="76" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="D42" s="75" t="s">
         <v>189</v>
       </c>
       <c r="E42" s="76" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="F42" s="87" t="s">
         <v>82</v>
@@ -18716,33 +18576,33 @@
     </row>
     <row r="43" spans="1:6" ht="28">
       <c r="A43" s="82" t="s">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="B43" s="68">
         <v>4.3</v>
       </c>
       <c r="C43" s="66" t="s">
-        <v>724</v>
+        <v>710</v>
       </c>
       <c r="D43" s="68" t="s">
         <v>195</v>
       </c>
       <c r="E43" s="66" t="s">
-        <v>725</v>
+        <v>711</v>
       </c>
       <c r="F43" s="88" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="194" t="s">
+      <c r="A44" s="219" t="s">
         <v>191</v>
       </c>
-      <c r="B44" s="195"/>
-      <c r="C44" s="195"/>
-      <c r="D44" s="195"/>
-      <c r="E44" s="195"/>
-      <c r="F44" s="196"/>
+      <c r="B44" s="220"/>
+      <c r="C44" s="220"/>
+      <c r="D44" s="220"/>
+      <c r="E44" s="220"/>
+      <c r="F44" s="221"/>
     </row>
     <row r="45" spans="1:6" ht="84">
       <c r="A45" s="78" t="s">
@@ -18752,13 +18612,13 @@
         <v>137</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>923</v>
+        <v>907</v>
       </c>
       <c r="D45" s="27" t="s">
         <v>192</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>924</v>
+        <v>908</v>
       </c>
       <c r="F45" s="84" t="s">
         <v>193</v>
@@ -18792,13 +18652,13 @@
         <v>134</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>991</v>
+        <v>975</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>198</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>927</v>
+        <v>911</v>
       </c>
       <c r="F47" s="86" t="s">
         <v>29</v>
@@ -18806,19 +18666,19 @@
     </row>
     <row r="48" spans="1:6" ht="42">
       <c r="A48" s="81" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="B48" s="75">
         <v>4.5</v>
       </c>
       <c r="C48" s="76" t="s">
-        <v>992</v>
+        <v>976</v>
       </c>
       <c r="D48" s="75" t="s">
         <v>79</v>
       </c>
       <c r="E48" s="76" t="s">
-        <v>933</v>
+        <v>917</v>
       </c>
       <c r="F48" s="87" t="s">
         <v>197</v>
@@ -18826,53 +18686,53 @@
     </row>
     <row r="49" spans="1:6" ht="28">
       <c r="A49" s="82" t="s">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="B49" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C49" s="66" t="s">
-        <v>695</v>
+        <v>681</v>
       </c>
       <c r="D49" s="68" t="s">
-        <v>696</v>
+        <v>682</v>
       </c>
       <c r="E49" s="66" t="s">
-        <v>697</v>
+        <v>683</v>
       </c>
       <c r="F49" s="88" t="s">
-        <v>698</v>
+        <v>684</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="84">
       <c r="A50" s="166" t="s">
-        <v>757</v>
+        <v>743</v>
       </c>
       <c r="B50" s="169" t="s">
         <v>216</v>
       </c>
       <c r="C50" s="168" t="s">
-        <v>993</v>
+        <v>977</v>
       </c>
       <c r="D50" s="169" t="s">
-        <v>948</v>
+        <v>932</v>
       </c>
       <c r="E50" s="168" t="s">
-        <v>966</v>
+        <v>950</v>
       </c>
       <c r="F50" s="170" t="s">
-        <v>946</v>
+        <v>930</v>
       </c>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="194" t="s">
+      <c r="A51" s="219" t="s">
         <v>199</v>
       </c>
-      <c r="B51" s="195"/>
-      <c r="C51" s="195"/>
-      <c r="D51" s="195"/>
-      <c r="E51" s="195"/>
-      <c r="F51" s="196"/>
+      <c r="B51" s="220"/>
+      <c r="C51" s="220"/>
+      <c r="D51" s="220"/>
+      <c r="E51" s="220"/>
+      <c r="F51" s="221"/>
     </row>
     <row r="52" spans="1:6" ht="56">
       <c r="A52" s="78" t="s">
@@ -18882,13 +18742,13 @@
         <v>187</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>994</v>
+        <v>978</v>
       </c>
       <c r="D52" s="27" t="s">
         <v>140</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>929</v>
+        <v>913</v>
       </c>
       <c r="F52" s="84" t="s">
         <v>200</v>
@@ -18922,87 +18782,87 @@
         <v>4.5</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>739</v>
+        <v>725</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>192</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>740</v>
+        <v>726</v>
       </c>
       <c r="F54" s="86" t="s">
-        <v>741</v>
+        <v>727</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="28">
       <c r="A55" s="81" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="B55" s="75">
         <v>4.7</v>
       </c>
       <c r="C55" s="76" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D55" s="75" t="s">
         <v>57</v>
       </c>
       <c r="E55" s="76" t="s">
-        <v>700</v>
+        <v>686</v>
       </c>
       <c r="F55" s="87" t="s">
-        <v>701</v>
+        <v>687</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="28">
       <c r="A56" s="81" t="s">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="B56" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C56" s="76" t="s">
-        <v>702</v>
+        <v>688</v>
       </c>
       <c r="D56" s="75" t="s">
-        <v>703</v>
+        <v>689</v>
       </c>
       <c r="E56" s="76" t="s">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="F56" s="87" t="s">
-        <v>705</v>
+        <v>691</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="84">
       <c r="A57" s="171" t="s">
-        <v>757</v>
+        <v>743</v>
       </c>
       <c r="B57" s="172" t="s">
         <v>216</v>
       </c>
       <c r="C57" s="173" t="s">
-        <v>995</v>
+        <v>979</v>
       </c>
       <c r="D57" s="172" t="s">
         <v>189</v>
       </c>
       <c r="E57" s="173" t="s">
-        <v>967</v>
+        <v>951</v>
       </c>
       <c r="F57" s="174" t="s">
-        <v>944</v>
+        <v>928</v>
       </c>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="194" t="s">
+      <c r="A58" s="219" t="s">
         <v>205</v>
       </c>
-      <c r="B58" s="195"/>
-      <c r="C58" s="195"/>
-      <c r="D58" s="195"/>
-      <c r="E58" s="195"/>
-      <c r="F58" s="196"/>
+      <c r="B58" s="220"/>
+      <c r="C58" s="220"/>
+      <c r="D58" s="220"/>
+      <c r="E58" s="220"/>
+      <c r="F58" s="221"/>
     </row>
     <row r="59" spans="1:6" ht="28">
       <c r="A59" s="78" t="s">
@@ -19032,13 +18892,13 @@
         <v>134</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>996</v>
+        <v>980</v>
       </c>
       <c r="D60" s="18" t="s">
         <v>198</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>928</v>
+        <v>912</v>
       </c>
       <c r="F60" s="85" t="s">
         <v>29</v>
@@ -19052,13 +18912,13 @@
         <v>139</v>
       </c>
       <c r="C61" s="29" t="s">
-        <v>997</v>
+        <v>981</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>140</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>930</v>
+        <v>914</v>
       </c>
       <c r="F61" s="86" t="s">
         <v>209</v>
@@ -19066,53 +18926,53 @@
     </row>
     <row r="62" spans="1:6" ht="28">
       <c r="A62" s="81" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="B62" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C62" s="74" t="s">
-        <v>726</v>
+        <v>712</v>
       </c>
       <c r="D62" s="75" t="s">
         <v>192</v>
       </c>
       <c r="E62" s="76" t="s">
-        <v>727</v>
+        <v>713</v>
       </c>
       <c r="F62" s="87" t="s">
-        <v>728</v>
+        <v>714</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="28">
       <c r="A63" s="82" t="s">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="B63" s="68">
         <v>4.5999999999999996</v>
       </c>
       <c r="C63" s="69" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="D63" s="68" t="s">
         <v>44</v>
       </c>
       <c r="E63" s="66" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="F63" s="88" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
     </row>
     <row r="64" spans="1:6">
-      <c r="A64" s="194" t="s">
+      <c r="A64" s="219" t="s">
         <v>210</v>
       </c>
-      <c r="B64" s="195"/>
-      <c r="C64" s="195"/>
-      <c r="D64" s="195"/>
-      <c r="E64" s="195"/>
-      <c r="F64" s="196"/>
+      <c r="B64" s="220"/>
+      <c r="C64" s="220"/>
+      <c r="D64" s="220"/>
+      <c r="E64" s="220"/>
+      <c r="F64" s="221"/>
     </row>
     <row r="65" spans="1:6" ht="28">
       <c r="A65" s="78" t="s">
@@ -19142,13 +19002,13 @@
         <v>137</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>998</v>
+        <v>982</v>
       </c>
       <c r="D66" s="18" t="s">
         <v>86</v>
       </c>
       <c r="E66" s="25" t="s">
-        <v>931</v>
+        <v>915</v>
       </c>
       <c r="F66" s="85" t="s">
         <v>85</v>
@@ -19175,14 +19035,14 @@
       </c>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="197" t="s">
+      <c r="A68" s="213" t="s">
         <v>221</v>
       </c>
-      <c r="B68" s="198"/>
-      <c r="C68" s="198"/>
-      <c r="D68" s="198"/>
-      <c r="E68" s="198"/>
-      <c r="F68" s="199"/>
+      <c r="B68" s="214"/>
+      <c r="C68" s="214"/>
+      <c r="D68" s="214"/>
+      <c r="E68" s="214"/>
+      <c r="F68" s="215"/>
     </row>
     <row r="69" spans="1:6" ht="70">
       <c r="A69" s="78" t="s">
@@ -19198,7 +19058,7 @@
         <v>102</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>869</v>
+        <v>853</v>
       </c>
       <c r="F69" s="84" t="s">
         <v>100</v>
@@ -19212,13 +19072,13 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>729</v>
+        <v>715</v>
       </c>
       <c r="D70" s="18" t="s">
         <v>195</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>744</v>
+        <v>730</v>
       </c>
       <c r="F70" s="85" t="s">
         <v>239</v>
@@ -19246,19 +19106,19 @@
     </row>
     <row r="72" spans="1:6" ht="28">
       <c r="A72" s="81" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="B72" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C72" s="76" t="s">
-        <v>733</v>
+        <v>719</v>
       </c>
       <c r="D72" s="75" t="s">
-        <v>703</v>
+        <v>689</v>
       </c>
       <c r="E72" s="76" t="s">
-        <v>734</v>
+        <v>720</v>
       </c>
       <c r="F72" s="87" t="s">
         <v>239</v>
@@ -19266,39 +19126,39 @@
     </row>
     <row r="73" spans="1:6" ht="70">
       <c r="A73" s="82" t="s">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="B73" s="68">
         <v>4.3</v>
       </c>
       <c r="C73" s="66" t="s">
-        <v>999</v>
+        <v>983</v>
       </c>
       <c r="D73" s="68" t="s">
-        <v>936</v>
+        <v>920</v>
       </c>
       <c r="E73" s="66" t="s">
-        <v>934</v>
+        <v>918</v>
       </c>
       <c r="F73" s="88" t="s">
-        <v>935</v>
+        <v>919</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="28">
       <c r="A74" s="81" t="s">
-        <v>757</v>
+        <v>743</v>
       </c>
       <c r="B74" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C74" s="76" t="s">
-        <v>758</v>
+        <v>744</v>
       </c>
       <c r="D74" s="75" t="s">
         <v>110</v>
       </c>
       <c r="E74" s="76" t="s">
-        <v>759</v>
+        <v>745</v>
       </c>
       <c r="F74" s="87" t="s">
         <v>108</v>
@@ -19306,39 +19166,39 @@
     </row>
     <row r="75" spans="1:6" ht="28">
       <c r="A75" s="82" t="s">
-        <v>760</v>
+        <v>746</v>
       </c>
       <c r="B75" s="68">
         <v>4.5</v>
       </c>
       <c r="C75" s="66" t="s">
-        <v>761</v>
+        <v>747</v>
       </c>
       <c r="D75" s="68" t="s">
         <v>86</v>
       </c>
       <c r="E75" s="66" t="s">
-        <v>762</v>
+        <v>748</v>
       </c>
       <c r="F75" s="88" t="s">
-        <v>763</v>
+        <v>749</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="42">
       <c r="A76" s="82" t="s">
-        <v>844</v>
+        <v>828</v>
       </c>
       <c r="B76" s="165" t="s">
-        <v>854</v>
+        <v>838</v>
       </c>
       <c r="C76" s="66" t="s">
-        <v>855</v>
+        <v>839</v>
       </c>
       <c r="D76" s="68" t="s">
-        <v>856</v>
+        <v>840</v>
       </c>
       <c r="E76" s="66" t="s">
-        <v>857</v>
+        <v>841</v>
       </c>
       <c r="F76" s="88" t="s">
         <v>245</v>
@@ -19346,33 +19206,33 @@
     </row>
     <row r="77" spans="1:6" ht="42">
       <c r="A77" s="82" t="s">
-        <v>848</v>
+        <v>832</v>
       </c>
       <c r="B77" s="165" t="s">
-        <v>858</v>
+        <v>842</v>
       </c>
       <c r="C77" s="66" t="s">
-        <v>859</v>
+        <v>843</v>
       </c>
       <c r="D77" s="68" t="s">
-        <v>851</v>
+        <v>835</v>
       </c>
       <c r="E77" s="66" t="s">
-        <v>860</v>
+        <v>844</v>
       </c>
       <c r="F77" s="88" t="s">
-        <v>861</v>
+        <v>845</v>
       </c>
     </row>
     <row r="78" spans="1:6">
-      <c r="A78" s="197" t="s">
+      <c r="A78" s="213" t="s">
         <v>227</v>
       </c>
-      <c r="B78" s="198"/>
-      <c r="C78" s="198"/>
-      <c r="D78" s="198"/>
-      <c r="E78" s="198"/>
-      <c r="F78" s="199"/>
+      <c r="B78" s="214"/>
+      <c r="C78" s="214"/>
+      <c r="D78" s="214"/>
+      <c r="E78" s="214"/>
+      <c r="F78" s="215"/>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="78" t="s">
@@ -19436,19 +19296,19 @@
     </row>
     <row r="82" spans="1:6" ht="28">
       <c r="A82" s="81" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="B82" s="75">
         <v>4.3</v>
       </c>
       <c r="C82" s="76" t="s">
-        <v>742</v>
+        <v>728</v>
       </c>
       <c r="D82" s="75" t="s">
         <v>192</v>
       </c>
       <c r="E82" s="76" t="s">
-        <v>743</v>
+        <v>729</v>
       </c>
       <c r="F82" s="87" t="s">
         <v>233</v>
@@ -19456,19 +19316,19 @@
     </row>
     <row r="83" spans="1:6" ht="28">
       <c r="A83" s="82" t="s">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="B83" s="68">
         <v>4</v>
       </c>
       <c r="C83" s="66" t="s">
-        <v>710</v>
+        <v>696</v>
       </c>
       <c r="D83" s="68" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="E83" s="66" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="F83" s="88" t="s">
         <v>233</v>
@@ -19476,22 +19336,22 @@
     </row>
     <row r="84" spans="1:6" ht="70">
       <c r="A84" s="161" t="s">
-        <v>757</v>
+        <v>743</v>
       </c>
       <c r="B84" s="162">
         <v>4.5999999999999996</v>
       </c>
       <c r="C84" s="163" t="s">
-        <v>961</v>
+        <v>945</v>
       </c>
       <c r="D84" s="162" t="s">
         <v>167</v>
       </c>
       <c r="E84" s="163" t="s">
-        <v>962</v>
+        <v>946</v>
       </c>
       <c r="F84" s="164" t="s">
-        <v>963</v>
+        <v>947</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="140">
@@ -19502,27 +19362,27 @@
         <v>4.8</v>
       </c>
       <c r="C85" s="181" t="s">
-        <v>1000</v>
+        <v>984</v>
       </c>
       <c r="D85" s="180" t="s">
         <v>57</v>
       </c>
       <c r="E85" s="181" t="s">
-        <v>968</v>
+        <v>952</v>
       </c>
       <c r="F85" s="182" t="s">
-        <v>958</v>
+        <v>942</v>
       </c>
     </row>
     <row r="86" spans="1:6">
-      <c r="A86" s="197" t="s">
+      <c r="A86" s="213" t="s">
         <v>235</v>
       </c>
-      <c r="B86" s="198"/>
-      <c r="C86" s="198"/>
-      <c r="D86" s="198"/>
-      <c r="E86" s="198"/>
-      <c r="F86" s="199"/>
+      <c r="B86" s="214"/>
+      <c r="C86" s="214"/>
+      <c r="D86" s="214"/>
+      <c r="E86" s="214"/>
+      <c r="F86" s="215"/>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="78" t="s">
@@ -19552,13 +19412,13 @@
         <v>4.2</v>
       </c>
       <c r="C88" s="16" t="s">
-        <v>731</v>
+        <v>717</v>
       </c>
       <c r="D88" s="18" t="s">
         <v>106</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>732</v>
+        <v>718</v>
       </c>
       <c r="F88" s="85" t="s">
         <v>239</v>
@@ -19572,13 +19432,13 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>748</v>
+        <v>734</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>192</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>749</v>
+        <v>735</v>
       </c>
       <c r="F89" s="86" t="s">
         <v>239</v>
@@ -19586,19 +19446,19 @@
     </row>
     <row r="90" spans="1:6" ht="28">
       <c r="A90" s="81" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="B90" s="75">
         <v>4.3</v>
       </c>
       <c r="C90" s="76" t="s">
-        <v>709</v>
+        <v>695</v>
       </c>
       <c r="D90" s="75" t="s">
         <v>106</v>
       </c>
       <c r="E90" s="76" t="s">
-        <v>730</v>
+        <v>716</v>
       </c>
       <c r="F90" s="87" t="s">
         <v>239</v>
@@ -19606,19 +19466,19 @@
     </row>
     <row r="91" spans="1:6" ht="28">
       <c r="A91" s="82" t="s">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="B91" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C91" s="66" t="s">
-        <v>750</v>
+        <v>736</v>
       </c>
       <c r="D91" s="68" t="s">
-        <v>751</v>
+        <v>737</v>
       </c>
       <c r="E91" s="66" t="s">
-        <v>752</v>
+        <v>738</v>
       </c>
       <c r="F91" s="88" t="s">
         <v>245</v>
@@ -19626,19 +19486,19 @@
     </row>
     <row r="92" spans="1:6" ht="28">
       <c r="A92" s="81" t="s">
-        <v>757</v>
+        <v>743</v>
       </c>
       <c r="B92" s="75">
         <v>4.5999999999999996</v>
       </c>
       <c r="C92" s="76" t="s">
-        <v>764</v>
+        <v>750</v>
       </c>
       <c r="D92" s="75" t="s">
         <v>115</v>
       </c>
       <c r="E92" s="76" t="s">
-        <v>765</v>
+        <v>751</v>
       </c>
       <c r="F92" s="87" t="s">
         <v>239</v>
@@ -19646,19 +19506,19 @@
     </row>
     <row r="93" spans="1:6" ht="28">
       <c r="A93" s="166" t="s">
-        <v>760</v>
+        <v>746</v>
       </c>
       <c r="B93" s="169" t="s">
         <v>216</v>
       </c>
       <c r="C93" s="168" t="s">
-        <v>766</v>
+        <v>752</v>
       </c>
       <c r="D93" s="169" t="s">
         <v>246</v>
       </c>
       <c r="E93" s="168" t="s">
-        <v>767</v>
+        <v>753</v>
       </c>
       <c r="F93" s="170" t="s">
         <v>100</v>
@@ -19666,19 +19526,19 @@
     </row>
     <row r="94" spans="1:6" ht="42">
       <c r="A94" s="82" t="s">
-        <v>844</v>
+        <v>828</v>
       </c>
       <c r="B94" s="165" t="s">
-        <v>845</v>
+        <v>829</v>
       </c>
       <c r="C94" s="66" t="s">
-        <v>846</v>
+        <v>830</v>
       </c>
       <c r="D94" s="68" t="s">
         <v>167</v>
       </c>
       <c r="E94" s="66" t="s">
-        <v>847</v>
+        <v>831</v>
       </c>
       <c r="F94" s="88" t="s">
         <v>226</v>
@@ -19686,53 +19546,53 @@
     </row>
     <row r="95" spans="1:6" ht="42">
       <c r="A95" s="82" t="s">
-        <v>848</v>
+        <v>832</v>
       </c>
       <c r="B95" s="165" t="s">
-        <v>849</v>
+        <v>833</v>
       </c>
       <c r="C95" s="66" t="s">
-        <v>850</v>
+        <v>834</v>
       </c>
       <c r="D95" s="68" t="s">
-        <v>851</v>
+        <v>835</v>
       </c>
       <c r="E95" s="66" t="s">
-        <v>852</v>
+        <v>836</v>
       </c>
       <c r="F95" s="88" t="s">
-        <v>853</v>
+        <v>837</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="70">
       <c r="A96" s="82" t="s">
-        <v>974</v>
+        <v>958</v>
       </c>
       <c r="B96" s="184">
         <v>4.5</v>
       </c>
       <c r="C96" s="66" t="s">
-        <v>1001</v>
+        <v>985</v>
       </c>
       <c r="D96" s="68" t="s">
         <v>145</v>
       </c>
       <c r="E96" s="66" t="s">
-        <v>975</v>
+        <v>959</v>
       </c>
       <c r="F96" s="88" t="s">
-        <v>971</v>
+        <v>955</v>
       </c>
     </row>
     <row r="97" spans="1:6">
-      <c r="A97" s="197" t="s">
+      <c r="A97" s="213" t="s">
         <v>241</v>
       </c>
-      <c r="B97" s="198"/>
-      <c r="C97" s="198"/>
-      <c r="D97" s="198"/>
-      <c r="E97" s="198"/>
-      <c r="F97" s="199"/>
+      <c r="B97" s="214"/>
+      <c r="C97" s="214"/>
+      <c r="D97" s="214"/>
+      <c r="E97" s="214"/>
+      <c r="F97" s="215"/>
     </row>
     <row r="98" spans="1:6" ht="84">
       <c r="A98" s="78" t="s">
@@ -19742,13 +19602,13 @@
         <v>5</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>969</v>
+        <v>953</v>
       </c>
       <c r="D98" s="27" t="s">
         <v>57</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>970</v>
+        <v>954</v>
       </c>
       <c r="F98" s="84" t="s">
         <v>242</v>
@@ -19782,50 +19642,60 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C100" s="76" t="s">
-        <v>753</v>
+        <v>739</v>
       </c>
       <c r="D100" s="75" t="s">
-        <v>754</v>
+        <v>740</v>
       </c>
       <c r="E100" s="76" t="s">
-        <v>755</v>
+        <v>741</v>
       </c>
       <c r="F100" s="87" t="s">
-        <v>756</v>
+        <v>742</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="28">
       <c r="A101" s="82" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="B101" s="68">
         <v>4.5</v>
       </c>
       <c r="C101" s="66" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="D101" s="68" t="s">
         <v>106</v>
       </c>
       <c r="E101" s="66" t="s">
-        <v>714</v>
+        <v>700</v>
       </c>
       <c r="F101" s="88" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="68" customHeight="1" thickBot="1">
-      <c r="A102" s="200" t="s">
-        <v>1003</v>
-      </c>
-      <c r="B102" s="201"/>
-      <c r="C102" s="201"/>
-      <c r="D102" s="201"/>
-      <c r="E102" s="201"/>
-      <c r="F102" s="202"/>
+      <c r="A102" s="216" t="s">
+        <v>987</v>
+      </c>
+      <c r="B102" s="217"/>
+      <c r="C102" s="217"/>
+      <c r="D102" s="217"/>
+      <c r="E102" s="217"/>
+      <c r="F102" s="218"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A51:F51"/>
     <mergeCell ref="A97:F97"/>
     <mergeCell ref="A102:F102"/>
     <mergeCell ref="A58:F58"/>
@@ -19833,16 +19703,6 @@
     <mergeCell ref="A68:F68"/>
     <mergeCell ref="A78:F78"/>
     <mergeCell ref="A86:F86"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A44:F44"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -19864,12 +19724,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1">
-      <c r="A1" s="210" t="s">
+      <c r="A1" s="195" t="s">
         <v>247</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="212"/>
+      <c r="B1" s="196"/>
+      <c r="C1" s="196"/>
+      <c r="D1" s="197"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="132"/>
@@ -19878,12 +19738,12 @@
       <c r="D2" s="142"/>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
-      <c r="A3" s="230" t="s">
+      <c r="A3" s="231" t="s">
         <v>248</v>
       </c>
-      <c r="B3" s="231"/>
-      <c r="C3" s="231"/>
-      <c r="D3" s="232"/>
+      <c r="B3" s="232"/>
+      <c r="C3" s="232"/>
+      <c r="D3" s="233"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="133" t="s">
@@ -19904,13 +19764,13 @@
         <v>252</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>1063</v>
+        <v>1046</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>1064</v>
+        <v>1047</v>
       </c>
       <c r="D5" s="144" t="s">
-        <v>1065</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="27.75" customHeight="1">
@@ -19946,7 +19806,7 @@
         <v>261</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>882</v>
+        <v>866</v>
       </c>
       <c r="C8" s="41" t="s">
         <v>262</v>
@@ -19971,16 +19831,16 @@
     </row>
     <row r="10" spans="1:4" ht="45" customHeight="1">
       <c r="A10" s="138" t="s">
-        <v>792</v>
+        <v>778</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>1093</v>
+        <v>1073</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>1094</v>
+        <v>1074</v>
       </c>
       <c r="D10" s="148" t="s">
-        <v>1095</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="45" customHeight="1">
@@ -19988,13 +19848,13 @@
         <v>264</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>1096</v>
+        <v>1076</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>1097</v>
+        <v>1077</v>
       </c>
       <c r="D11" s="148" t="s">
-        <v>1098</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="45" customHeight="1">
@@ -20002,13 +19862,13 @@
         <v>253</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>1099</v>
+        <v>1079</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>1100</v>
+        <v>1080</v>
       </c>
       <c r="D12" s="148" t="s">
-        <v>1101</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="45" customHeight="1">
@@ -20016,13 +19876,13 @@
         <v>288</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>1102</v>
+        <v>1082</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>1103</v>
+        <v>1083</v>
       </c>
       <c r="D13" s="148" t="s">
-        <v>1104</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1">
@@ -20032,12 +19892,12 @@
       <c r="D14" s="142"/>
     </row>
     <row r="15" spans="1:4" ht="16">
-      <c r="A15" s="233" t="s">
+      <c r="A15" s="234" t="s">
         <v>268</v>
       </c>
-      <c r="B15" s="234"/>
-      <c r="C15" s="234"/>
-      <c r="D15" s="235"/>
+      <c r="B15" s="235"/>
+      <c r="C15" s="235"/>
+      <c r="D15" s="236"/>
     </row>
     <row r="16" spans="1:4" ht="24" customHeight="1">
       <c r="A16" s="133" t="s">
@@ -20063,8 +19923,8 @@
       <c r="C17" s="35" t="s">
         <v>270</v>
       </c>
-      <c r="D17" s="240" t="s">
-        <v>1129</v>
+      <c r="D17" s="185" t="s">
+        <v>1109</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1">
@@ -20128,27 +19988,27 @@
         <v>277</v>
       </c>
       <c r="B22" s="92" t="s">
-        <v>789</v>
+        <v>775</v>
       </c>
       <c r="C22" s="92" t="s">
-        <v>790</v>
+        <v>776</v>
       </c>
       <c r="D22" s="125" t="s">
-        <v>791</v>
+        <v>777</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="30" customHeight="1">
       <c r="A23" s="140" t="s">
-        <v>792</v>
+        <v>778</v>
       </c>
       <c r="B23" s="90" t="s">
-        <v>793</v>
+        <v>779</v>
       </c>
       <c r="C23" s="90" t="s">
-        <v>794</v>
+        <v>780</v>
       </c>
       <c r="D23" s="149" t="s">
-        <v>795</v>
+        <v>781</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="30" customHeight="1">
@@ -20167,30 +20027,30 @@
     </row>
     <row r="25" spans="1:4" ht="70">
       <c r="A25" s="138" t="s">
-        <v>1105</v>
+        <v>1085</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>1106</v>
+        <v>1086</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>1107</v>
+        <v>1087</v>
       </c>
       <c r="D25" s="148" t="s">
-        <v>1108</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="45" customHeight="1">
       <c r="A26" s="138" t="s">
-        <v>1109</v>
+        <v>1089</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>1110</v>
+        <v>1090</v>
       </c>
       <c r="C26" s="44" t="s">
-        <v>1111</v>
+        <v>1091</v>
       </c>
       <c r="D26" s="148" t="s">
-        <v>1112</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="45" customHeight="1">
@@ -20198,13 +20058,13 @@
         <v>253</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>1113</v>
+        <v>1093</v>
       </c>
       <c r="C27" s="44" t="s">
-        <v>1114</v>
+        <v>1094</v>
       </c>
       <c r="D27" s="148" t="s">
-        <v>1115</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="45" customHeight="1">
@@ -20212,13 +20072,13 @@
         <v>252</v>
       </c>
       <c r="B28" s="43" t="s">
-        <v>1116</v>
+        <v>1096</v>
       </c>
       <c r="C28" s="44" t="s">
-        <v>1117</v>
+        <v>1097</v>
       </c>
       <c r="D28" s="148" t="s">
-        <v>1118</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="30" customHeight="1">
@@ -20256,12 +20116,12 @@
       <c r="D31" s="142"/>
     </row>
     <row r="32" spans="1:4" ht="30" customHeight="1">
-      <c r="A32" s="236" t="s">
+      <c r="A32" s="237" t="s">
         <v>295</v>
       </c>
-      <c r="B32" s="237"/>
-      <c r="C32" s="237"/>
-      <c r="D32" s="238"/>
+      <c r="B32" s="238"/>
+      <c r="C32" s="238"/>
+      <c r="D32" s="239"/>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="133" t="s">
@@ -20349,16 +20209,16 @@
     </row>
     <row r="39" spans="1:4" ht="45" customHeight="1">
       <c r="A39" s="138" t="s">
-        <v>792</v>
+        <v>778</v>
       </c>
       <c r="B39" s="43" t="s">
-        <v>1119</v>
+        <v>1099</v>
       </c>
       <c r="C39" s="44" t="s">
-        <v>1120</v>
+        <v>1100</v>
       </c>
       <c r="D39" s="148" t="s">
-        <v>1121</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="45" customHeight="1">
@@ -20366,27 +20226,27 @@
         <v>257</v>
       </c>
       <c r="B40" s="43" t="s">
-        <v>1122</v>
+        <v>1102</v>
       </c>
       <c r="C40" s="44" t="s">
-        <v>1123</v>
+        <v>1103</v>
       </c>
       <c r="D40" s="148" t="s">
-        <v>1124</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="45" customHeight="1">
       <c r="A41" s="138" t="s">
-        <v>1125</v>
+        <v>1105</v>
       </c>
       <c r="B41" s="43" t="s">
-        <v>1128</v>
+        <v>1108</v>
       </c>
       <c r="C41" s="44" t="s">
-        <v>1126</v>
+        <v>1106</v>
       </c>
       <c r="D41" s="148" t="s">
-        <v>1127</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="27.75" customHeight="1">
@@ -20460,20 +20320,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1">
-      <c r="A1" s="239" t="s">
+      <c r="A1" s="240" t="s">
         <v>318</v>
       </c>
-      <c r="B1" s="239"/>
-      <c r="C1" s="239"/>
-      <c r="D1" s="239"/>
+      <c r="B1" s="240"/>
+      <c r="C1" s="240"/>
+      <c r="D1" s="240"/>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
-      <c r="A3" s="229" t="s">
+      <c r="A3" s="212" t="s">
         <v>248</v>
       </c>
-      <c r="B3" s="229"/>
-      <c r="C3" s="229"/>
-      <c r="D3" s="229"/>
+      <c r="B3" s="212"/>
+      <c r="C3" s="212"/>
+      <c r="D3" s="212"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="12" t="s">
@@ -20532,12 +20392,12 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="24" customHeight="1">
-      <c r="A9" s="207" t="s">
+      <c r="A9" s="208" t="s">
         <v>268</v>
       </c>
-      <c r="B9" s="207"/>
-      <c r="C9" s="207"/>
-      <c r="D9" s="207"/>
+      <c r="B9" s="208"/>
+      <c r="C9" s="208"/>
+      <c r="D9" s="208"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="12" t="s">
@@ -20582,12 +20442,12 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="24" customHeight="1">
-      <c r="A14" s="209" t="s">
+      <c r="A14" s="210" t="s">
         <v>295</v>
       </c>
-      <c r="B14" s="209"/>
-      <c r="C14" s="209"/>
-      <c r="D14" s="209"/>
+      <c r="B14" s="210"/>
+      <c r="C14" s="210"/>
+      <c r="D14" s="210"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="12" t="s">

--- a/tools/itinerary.xlsx
+++ b/tools/itinerary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jitwei/Library/Mobile Documents/com~apple~CloudDocs/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F572039E-4B6A-964F-8403-04F370DCD010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE36E23-A76B-D646-8DAC-73056FB8A442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-6080" yWindow="-21000" windowWidth="38400" windowHeight="21000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="17020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -6192,35 +6192,6 @@
     <t>08:15–09:00</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">🍁 Beishan Street </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">北山街 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ginkgo avenue</t>
-    </r>
-  </si>
-  <si>
     <t>Walk</t>
   </si>
   <si>
@@ -6491,26 +6462,6 @@
     <t>11:00–11:45</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">🍁 Yongfu Temple </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>永福寺</t>
-    </r>
-  </si>
-  <si>
     <t>Same hillside — gilded ginkgo &amp; red maple.</t>
   </si>
   <si>
@@ -6837,26 +6788,6 @@
   </si>
   <si>
     <t>Alt</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">🆕 TRENDY swap: Tianmuli </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>天目里</t>
-    </r>
   </si>
   <si>
     <r>
@@ -7136,35 +7067,6 @@
     <t>12:15–13:00</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">🏨 Nanjing South → Ritz-Carlton </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">丽思 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Deji/Xinjiekou)</t>
-    </r>
-  </si>
-  <si>
     <t>DiDi/Metro L1 (~20 min). Hotel is floors 38–62 of Deji Plaza.</t>
   </si>
   <si>
@@ -7590,44 +7492,6 @@
         <family val="2"/>
       </rPr>
       <t>老门东</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">🆕 TRENDY: Laomendong </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">老门东 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">/ Xiaoxihu </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>小西湖</t>
     </r>
   </si>
   <si>
@@ -8258,53 +8122,6 @@
     <t>17:15–18:15</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">🏨 SHOP: Xinjiekou </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">新街口 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&amp; Deji Plaza </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">德基广场 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(at hotel)</t>
-    </r>
-  </si>
-  <si>
     <t>② Back to CENTRE — your hotel. Flagships; Deji Art Museum; themed washrooms.</t>
   </si>
   <si>
@@ -8379,44 +8196,6 @@
   </si>
   <si>
     <t>19:45–20:45</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">🏨 Nightcap: FLAIR 62F (Ritz) / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">紫峰大厦 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>王府大街</t>
-    </r>
   </si>
   <si>
     <r>
@@ -8843,16 +8622,75 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">🏨 Station → Ritz-Carlton Suzhou </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">丽思 </t>
+      <t xml:space="preserve">DiDi ~15 min. West old-town — &lt;1km Liuyuan </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>留园</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, near Shantang </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>山塘街</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>DiDi</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>姑苏区广济南路</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>369</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号 </t>
     </r>
     <r>
       <rPr>
@@ -8870,54 +8708,57 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t>广济南路</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>), drop bags</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">DiDi ~15 min. West old-town — &lt;1km Liuyuan </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>留园</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, near Shantang </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>山塘街</t>
+      <t>丽思</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Lunch — Suzhou sweet cuisine</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Squirrel mandarin fish </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>松鼠桂鱼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, biluochun </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>碧螺春</t>
     </r>
     <r>
       <rPr>
@@ -8930,26 +8771,397 @@
     </r>
   </si>
   <si>
-    <t>DiDi</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>姑苏区广济南路</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>369</t>
+    <t>14:15–16:00</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">MUST-SEE: Humble Administrator's Garden </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>拙政园</t>
+    </r>
+  </si>
+  <si>
+    <t>NE old town (~15 min DiDi). Suzhou's largest UNESCO garden.</t>
+  </si>
+  <si>
+    <t>Entry ¥70–90</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>姑苏区东北街</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>178</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>姑苏区东北街</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>204</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Optional: Lion Grove Garden </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>狮子林</t>
+    </r>
+  </si>
+  <si>
+    <t>Optional ¥40</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>姑苏区园林路</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>23</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Coffee — Momicafe (Pingjiang Rd </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>平江路</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Momicafe</t>
+  </si>
+  <si>
+    <t>18:00–19:15</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">MUST-SEE: Pingjiang Road </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">平江路 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">canal district (+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>手摇船</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Dinner at Wumen Renjia </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>吴门人家</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">; Pingtan </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>评弹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. Optional hand-rowed boat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">手摇船 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>along the canal (~¥100).</t>
+    </r>
+  </si>
+  <si>
+    <t>19:15–20:15</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Design-award wet market — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>糕团</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>馄饨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">海棠糕 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>stalls &amp; cafés.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Shuangta </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>双塔</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>姑苏区吴殿直街</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
     </r>
     <r>
       <rPr>
@@ -8976,7 +9188,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t>丽思</t>
+      <t>石匠弄</t>
     </r>
     <r>
       <rPr>
@@ -8986,544 +9198,6 @@
         <family val="2"/>
       </rPr>
       <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>Lunch — Suzhou sweet cuisine</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Squirrel mandarin fish </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>松鼠桂鱼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, biluochun </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>碧螺春</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>14:15–16:00</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">MUST-SEE: Humble Administrator's Garden </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>拙政园</t>
-    </r>
-  </si>
-  <si>
-    <t>NE old town (~15 min DiDi). Suzhou's largest UNESCO garden.</t>
-  </si>
-  <si>
-    <t>Entry ¥70–90</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>姑苏区东北街</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>178</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>号</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>姑苏区东北街</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>204</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>号</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Optional: Lion Grove Garden </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>狮子林</t>
-    </r>
-  </si>
-  <si>
-    <t>Optional ¥40</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>姑苏区园林路</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>23</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>号</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Coffee — Momicafe (Pingjiang Rd </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>平江路</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>Momicafe</t>
-  </si>
-  <si>
-    <t>18:00–19:15</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">MUST-SEE: Pingjiang Road </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">平江路 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">canal district (+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>手摇船</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Dinner at Wumen Renjia </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>吴门人家</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">; Pingtan </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>评弹</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. Optional hand-rowed boat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">手摇船 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>along the canal (~¥100).</t>
-    </r>
-  </si>
-  <si>
-    <t>19:15–20:15</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">🆕 TRENDY: Shuangta Market </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>双塔市集</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Design-award wet market — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>糕团</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>馄饨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">海棠糕 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>stalls &amp; cafés.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Shuangta </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>双塔</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>姑苏区吴殿直街</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">号 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>石匠弄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">🛍 Optional: Renheng Cang Street </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">仁恒仓街 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&amp; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>相门城墙</t>
     </r>
   </si>
   <si>
@@ -10089,26 +9763,6 @@
     <t>Single-origin pour-over.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">🆕 SHOP: Shiquan Street </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>十全街</t>
-    </r>
-  </si>
-  <si>
     <t>Vintage boutiques, jade &amp; silk studios.</t>
   </si>
   <si>
@@ -11120,9 +10774,6 @@
     <t>玄武区石象路7号 (钟山)</t>
   </si>
   <si>
-    <t>📚 Optional: Librairie Avant-Garde 先锋书店 (五台山总店)</t>
-  </si>
-  <si>
     <t>One of the world's most beautiful bookstores' — built in an underground car park. Major 打卡 spot; pairs with 颐和路 (both on 广州路/鼓楼). Go before noon at weekends.</t>
   </si>
   <si>
@@ -11204,9 +10855,6 @@
     <t>姑苏区人民路1918号 (北寺塔)</t>
   </si>
   <si>
-    <t>📚 Optional: Momi/猫的天空之城 &amp; Slow Bookstore 慢书房</t>
-  </si>
-  <si>
     <t>On 平江路 itself — 猫空 concept bookstore (originated in Suzhou; 'mail a postcard to the future') + indie 慢书房. Zero detour from the Pingjiang walk.</t>
   </si>
   <si>
@@ -11219,16 +10867,10 @@
     <t>建邺区江山大街 (南京眼/鱼嘴)</t>
   </si>
   <si>
-    <t>🆕 Optional: Xinanli 熙南里 &amp; Pingshi St 评事街</t>
-  </si>
-  <si>
     <t>Restored Qing block just S of 新街口 — 甘熙故居, indie shops, night market &amp; 打卡 lanes. Much closer to the Ritz than 老门东.</t>
   </si>
   <si>
     <t>秦淮区升州路 (熙南里)</t>
-  </si>
-  <si>
-    <t>🆕 TRENDY alt: Yuniaoji 玉鸟集 &amp; Da Wuding 大屋顶 (良渚)</t>
   </si>
   <si>
     <t>Optional alt · 余杭</t>
@@ -11343,7 +10985,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">🍁 SEASONAL swap: Tianping Mountain </t>
+      <t xml:space="preserve">Half-day to Mudu </t>
     </r>
     <r>
       <rPr>
@@ -11352,10 +10994,8 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t>天平山红枫节</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">木渎 </t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -11364,25 +11004,6 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Half-day to Mudu </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">木渎 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
       <t>for PEAK red maples. ¥30.</t>
     </r>
   </si>
@@ -11390,9 +11011,6 @@
     <t>15:15–16:20</t>
   </si>
   <si>
-    <t>🛍 SHOP: Hubin Pedestrian St 湖滨步行街 &amp; 湖滨银泰 in77</t>
-  </si>
-  <si>
     <t>West Lake waterfront strip — musical fountain 音乐喷泉, flagship stores, Hangzhou's most-filmed 打卡 street. Directly continues from the % Arabica stop on the same road.</t>
   </si>
   <si>
@@ -11426,9 +11044,6 @@
     <t>19:00–21:30</t>
   </si>
   <si>
-    <t>★ DINNER SHOW: 宫宴 Song Imperial Banquet</t>
-  </si>
-  <si>
     <t>晚宴 seats 19:00 sharp; runs ~2–3h. Hanfu 妆造 add-on ~¥126 (cannot be booked alone — add to the meal). BOOK BY ~16 OCT 2026 — vendor advises 1 month ahead; sells out 1–2 weeks out. Non-cancellable; confirmed within 1 day.</t>
   </si>
   <si>
@@ -11516,18 +11131,12 @@
     <t>250-yr-old; squirrel mandarin fish. 1,350+ reviews. ⚠️ Ranks LAST (评分 65) among 2026 Dianping 苏帮菜 entries while being the priciest — go for the heritage dish, not value. See ⑧⑨ below.</t>
   </si>
   <si>
-    <t>☕ Optional: 羽和铃 Feather Bell coffee</t>
-  </si>
-  <si>
     <t>Opt · ~¥53pp</t>
   </si>
   <si>
     <t>上城区 清河坊/河坊街 (吴山山脚)</t>
   </si>
   <si>
-    <t>🍦 Optional: 夏序 SASU Gelato</t>
-  </si>
-  <si>
     <t>Opt · ~¥37pp</t>
   </si>
   <si>
@@ -11555,9 +11164,6 @@
     <t>宫宴 Gongyan Palace Banquet (Day 3)</t>
   </si>
   <si>
-    <t>🍵 Optional: 查小文茶客厅 Cha Talk Tea House (四寒茶舍)</t>
-  </si>
-  <si>
     <t>Opt · walk-in 1F</t>
   </si>
   <si>
@@ -11576,9 +11182,6 @@
     <t>¥50–120</t>
   </si>
   <si>
-    <t>🥟 Optional breakfast: 泮芳春煎饺 Pan Fang Chun (中山南路店)</t>
-  </si>
-  <si>
     <t>MICHELIN Bib Gourmand 必比登 3 years running — Hangzhou's most famous pan-fried dumplings 煎饺, ~¥1 each (5 for ¥5). Thin skin, crisp golden base, juicy pork. Verified on Dianping: ~¥17pp, opens 06:00. Queues form early — go before 08:00. Located at the 南宋御街 archway, ~10 min walk from 清河坊/吴山. Also: 鲜肉小馄饨, 葱油拌面, 咸豆花, 现磨豆浆.</t>
   </si>
   <si>
@@ -11624,9 +11227,6 @@
     <t>¥100 (蟹另计)</t>
   </si>
   <si>
-    <t>☕ ALT half-day: Taihu Dongshan 太湖东山 lake-view cafés (sunset)</t>
-  </si>
-  <si>
     <t>From a 苏州文旅 post. DONGSHAN IS THE CLOSER/EASIER SIDE: ~30km &amp; bus 502/621 direct from the city (vs Xishan 45km, needs 太湖大桥 + awkward 地铁5号线→快线11号→岛内公交). ① 望听café·零湖落日 — white walls + wood-fired kiln, floor-to-ceiling Taihu view; 果木窑烤玛格丽塔 pizza, 碧螺春拿铁, 东山大米咖啡; also a 4.8/59 guesthouse (吴中区东山镇莫厘村尚锦2号, 08:00–22:00, 13564174956). ② ATE·阿缇依湖景咖啡 — sunset seats + the red-and-white lighthouse landmark; a Wuzhong day-trip guide names it THE Dongshan sunset stop. ③ 橙色计划 NO.1 露营咖啡 — camping base w/ 巨轮咖啡, BBQ, 篝火DJ. ⚠ NOT a detour you can slot into Day 7 — this REPLACES the afternoon (网师园/十全街/观前街). ⚠ Bonus: mid-Nov is peak 银杏 at 陆巷古村 on the same peninsula. XISHAN ALT (pick one side only, ~1h apart): 湖与Cafe 270° (缥纱路20x, 大众点评4.2, #1 太湖西山热门榜), 树下茶咖 (罗汉坞千年古樟), 野隐·松簧 (风铃溪谷金铎岭半山腰).</t>
   </si>
   <si>
@@ -11654,9 +11254,6 @@
     <t>XISHAN ALTERNATIVE — 270° lake view, 2 floors. 大众点评 4.2, ranked #1 on 太湖西山美食热门榜 (Ctrip shows a lower 3.7 on only 3 reviews). Try 西山拿铁, 黑松露薯条, 栗子巴斯克. Same-side extras: 树下茶咖 (under the 千年古樟 at 罗汉坞 — coffee or a pot of 碧螺春) and 野隐·松簧 (风铃溪谷·金铎岭半山腰, terrace w/ pine-wind + lake view). ⚠ Xishan needs 太湖大桥; public transport is weak (地铁5号线→快线11号→岛内公交) and the bridge jams at weekends. Dongshan and Xishan are ~1h apart — choose ONE.</t>
   </si>
   <si>
-    <t>🦀 Optional: Li Bai Xie 李百蟹·蟹黄面 (Pingjiang 平江路总店)</t>
-  </si>
-  <si>
     <t>NOTE THE SPELLING: 李百蟹 (bǎi 百), not 李白蟹. ZERO DETOUR — it is ON Pingjiang Rd 平江路, which you already walk 18:00–19:15 (row above). Crab-roe noodles 蟹黄面 &amp; 蟹黄拌饭 — golden 蟹粉/蟹膏, FREE noodle &amp; rice refills; also 江南花雕熟醉蟹, 蟹膏, and photogenic Suzhou desserts (草莓奶盖冰, 抹茶豆花, 桂花奶酪). Riverside seats look onto the canal, bridges &amp; boats. ⚠ Queues at meal times — take a queue number on arrival (reported to move fast). Open 10:00–21:30. Trip.com 5.0/5 but only 2 reviews — thin sample, re-check on Dianping. Other branches: 观前街店 (beside Day 7 lunch), 山塘街店 (河景船宴, near hotel).</t>
   </si>
   <si>
@@ -11933,9 +11530,6 @@
     <t>上城区国货路2号</t>
   </si>
   <si>
-    <t>🏨 Check-in Canopy by Hilton West Lake 康铂</t>
-  </si>
-  <si>
     <t>Lifestyle Hilton on 国货路 — 6-min walk to West Lake 西湖, beside Longxiangqiao 龙翔桥 metro. Ask for a high floor.</t>
   </si>
   <si>
@@ -11996,9 +11590,6 @@
     <t>12:45–14:00</t>
   </si>
   <si>
-    <t>🏨 HOTEL MOVE: collect bags at Canopy 康铂 → check in Conrad 康莱德</t>
-  </si>
-  <si>
     <t>DiDi ~35–40 min total</t>
   </si>
   <si>
@@ -12290,15 +11881,9 @@
     <t>13:50–15:50</t>
   </si>
   <si>
-    <t>🍵 MUST-SEE: Longjing Tea Village 龙井茶村 (2h block)</t>
-  </si>
-  <si>
     <t>15:55–16:35</t>
   </si>
   <si>
-    <t>🍁 Jiuxi 九溪烟树 · Manjuelong 满觉陇 (foliage leg)</t>
-  </si>
-  <si>
     <t>Free · short hop</t>
   </si>
   <si>
@@ -12405,9 +11990,6 @@
   </si>
   <si>
     <t>18:20–19:20</t>
-  </si>
-  <si>
-    <t>◆ Dinner — Golden Silk 金丝·听海 (Michelin selected)</t>
   </si>
   <si>
     <t>Zhejiang coastal seafood at the Shangri-La 水知心居 — 招牌江蟹生 (Wenzhou raw marinated crab), 脆皮盐香清远鸡, 头水紫菜海鲜石榴包. Kitchen serves 17:00–20:30. Book ahead; smart-casual dress. ~4 doors from the show gate, so the walk out is 5 min.</t>
@@ -12520,6 +12102,93 @@
   </si>
   <si>
     <t xml:space="preserve">Outdoor water-stage show on West Lake itself (Zhang Yimou 张艺谋 / 王潮歌 / 樊跃; music by Kitaro 喜多郎). ~50–55 min. Starts 19:40. Walk 5 min east along 北山街 from dinner — arrive ~19:25 for ticket collection and 检票. </t>
+  </si>
+  <si>
+    <t>Check-in Canopy by Hilton West Lake 康铂 🏨</t>
+  </si>
+  <si>
+    <t>Beishan Street 北山街 ginkgo avenue 🍁</t>
+  </si>
+  <si>
+    <t>SHOP: Hubin Pedestrian St 湖滨步行街 &amp; 湖滨银泰 in77 🛍</t>
+  </si>
+  <si>
+    <t>MUST-SEE: Longjing Tea Village 龙井茶村 (2h block) 🍵</t>
+  </si>
+  <si>
+    <t>Jiuxi 九溪烟树 · Manjuelong 满觉陇 (foliage leg) 🍁</t>
+  </si>
+  <si>
+    <t>Dinner — Golden Silk 金丝·听海 (Michelin selected) ◆</t>
+  </si>
+  <si>
+    <t>Optional breakfast: 泮芳春煎饺 Pan Fang Chun (中山南路店) 🥟</t>
+  </si>
+  <si>
+    <t>Yongfu Temple 永福寺 🍁</t>
+  </si>
+  <si>
+    <t>HOTEL MOVE: collect bags at Canopy 康铂 → check in Conrad 康莱德 🏨</t>
+  </si>
+  <si>
+    <t>Optional: 羽和铃 Feather Bell coffee ☕</t>
+  </si>
+  <si>
+    <t>Optional: 夏序 SASU Gelato 🍦</t>
+  </si>
+  <si>
+    <t>Optional: 查小文茶客厅 Cha Talk Tea House (四寒茶舍) 🍵</t>
+  </si>
+  <si>
+    <t>DINNER SHOW: 宫宴 Song Imperial Banquet ★</t>
+  </si>
+  <si>
+    <t>TRENDY swap: Tianmuli 天目里 🆕</t>
+  </si>
+  <si>
+    <t>TRENDY alt: Yuniaoji 玉鸟集 &amp; Da Wuding 大屋顶 (良渚) 🆕</t>
+  </si>
+  <si>
+    <t>Nanjing South → Ritz-Carlton 丽思 (Deji/Xinjiekou) 🏨</t>
+  </si>
+  <si>
+    <t>TRENDY: Laomendong 老门东 / Xiaoxihu 小西湖 🆕</t>
+  </si>
+  <si>
+    <t>SHOP: Xinjiekou 新街口 &amp; Deji Plaza 德基广场 (at hotel) 🏨</t>
+  </si>
+  <si>
+    <t>Optional: Xinanli 熙南里 &amp; Pingshi St 评事街 🆕</t>
+  </si>
+  <si>
+    <t>Nightcap: FLAIR 62F (Ritz) / 紫峰大厦 / 王府大街 🏨</t>
+  </si>
+  <si>
+    <t>Optional: Librairie Avant-Garde 先锋书店 (五台山总店) 📚</t>
+  </si>
+  <si>
+    <t>Station → Ritz-Carlton Suzhou 丽思 (广济南路), drop bags 🏨</t>
+  </si>
+  <si>
+    <t>Optional: Momi/猫的天空之城 &amp; Slow Bookstore 慢书房 📚</t>
+  </si>
+  <si>
+    <t>Optional: Li Bai Xie 李百蟹·蟹黄面 (Pingjiang 平江路总店) 🦀</t>
+  </si>
+  <si>
+    <t>TRENDY: Shuangta Market 双塔市集 🆕</t>
+  </si>
+  <si>
+    <t>Optional: Renheng Cang Street 仁恒仓街 &amp; 相门城墙 🛍</t>
+  </si>
+  <si>
+    <t>SHOP: Shiquan Street 十全街 🆕</t>
+  </si>
+  <si>
+    <t>ALT half-day: Taihu Dongshan 太湖东山 lake-view cafés (sunset) ☕</t>
+  </si>
+  <si>
+    <t>SEASONAL swap: Tianping Mountain 天平山红枫节 🍁</t>
   </si>
 </sst>
 </file>
@@ -13088,7 +12757,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="244">
+  <cellXfs count="252">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -13639,6 +13308,42 @@
     <xf numFmtId="0" fontId="7" fillId="15" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -13666,33 +13371,6 @@
     <xf numFmtId="0" fontId="3" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -13720,6 +13398,42 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -13738,42 +13452,6 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -13804,14 +13482,29 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="7" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="24" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -14091,31 +13784,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="31.5" customHeight="1">
-      <c r="A1" s="206" t="s">
+      <c r="A1" s="209" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="206"/>
-      <c r="C1" s="206"/>
-      <c r="D1" s="206"/>
-      <c r="E1" s="206"/>
+      <c r="B1" s="209"/>
+      <c r="C1" s="209"/>
+      <c r="D1" s="209"/>
+      <c r="E1" s="209"/>
     </row>
     <row r="2" spans="1:5" ht="21.75" customHeight="1">
-      <c r="A2" s="207" t="s">
+      <c r="A2" s="210" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="207"/>
-      <c r="C2" s="207"/>
-      <c r="D2" s="207"/>
-      <c r="E2" s="207"/>
+      <c r="B2" s="210"/>
+      <c r="C2" s="210"/>
+      <c r="D2" s="210"/>
+      <c r="E2" s="210"/>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1">
-      <c r="A4" s="208" t="s">
+      <c r="A4" s="211" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="208"/>
-      <c r="C4" s="208"/>
-      <c r="D4" s="208"/>
-      <c r="E4" s="208"/>
+      <c r="B4" s="211"/>
+      <c r="C4" s="211"/>
+      <c r="D4" s="211"/>
+      <c r="E4" s="211"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
@@ -14169,13 +13862,13 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1">
-      <c r="A9" s="209" t="s">
+      <c r="A9" s="212" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="209"/>
-      <c r="C9" s="209"/>
-      <c r="D9" s="209"/>
-      <c r="E9" s="209"/>
+      <c r="B9" s="212"/>
+      <c r="C9" s="212"/>
+      <c r="D9" s="212"/>
+      <c r="E9" s="212"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
@@ -14196,36 +13889,36 @@
     </row>
     <row r="11" spans="1:5" ht="55" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>1019</v>
+        <v>993</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1020</v>
+        <v>994</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1021</v>
+        <v>995</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>1022</v>
+        <v>996</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>992</v>
+        <v>968</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="55" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>1019</v>
+        <v>993</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1023</v>
+        <v>997</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1024</v>
+        <v>998</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1025</v>
+        <v>999</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>1026</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="45.75" customHeight="1">
@@ -14264,41 +13957,41 @@
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1"/>
     <row r="16" spans="1:5" ht="72" customHeight="1">
-      <c r="A16" s="210" t="s">
+      <c r="A16" s="213" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="210"/>
-      <c r="C16" s="210"/>
-      <c r="D16" s="210"/>
-      <c r="E16" s="210"/>
+      <c r="B16" s="213"/>
+      <c r="C16" s="213"/>
+      <c r="D16" s="213"/>
+      <c r="E16" s="213"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="204" t="s">
+      <c r="A17" s="207" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="204"/>
-      <c r="C17" s="204"/>
-      <c r="D17" s="204"/>
-      <c r="E17" s="204"/>
+      <c r="B17" s="207"/>
+      <c r="C17" s="207"/>
+      <c r="D17" s="207"/>
+      <c r="E17" s="207"/>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1"/>
     <row r="19" spans="1:5" ht="31.5" customHeight="1">
-      <c r="A19" s="205" t="s">
+      <c r="A19" s="208" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="205"/>
-      <c r="C19" s="205"/>
-      <c r="D19" s="205"/>
-      <c r="E19" s="205"/>
+      <c r="B19" s="208"/>
+      <c r="C19" s="208"/>
+      <c r="D19" s="208"/>
+      <c r="E19" s="208"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="204" t="s">
+      <c r="A20" s="207" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="204"/>
-      <c r="C20" s="204"/>
-      <c r="D20" s="204"/>
-      <c r="E20" s="204"/>
+      <c r="B20" s="207"/>
+      <c r="C20" s="207"/>
+      <c r="D20" s="207"/>
+      <c r="E20" s="207"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -14333,24 +14026,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18">
-      <c r="A1" s="195" t="s">
-        <v>988</v>
-      </c>
-      <c r="B1" s="196"/>
-      <c r="C1" s="196"/>
-      <c r="D1" s="196"/>
-      <c r="E1" s="196"/>
-      <c r="F1" s="197"/>
+      <c r="A1" s="189" t="s">
+        <v>964</v>
+      </c>
+      <c r="B1" s="190"/>
+      <c r="C1" s="190"/>
+      <c r="D1" s="190"/>
+      <c r="E1" s="190"/>
+      <c r="F1" s="191"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="198" t="s">
+      <c r="A2" s="192" t="s">
         <v>344</v>
       </c>
-      <c r="B2" s="199"/>
-      <c r="C2" s="199"/>
-      <c r="D2" s="199"/>
-      <c r="E2" s="199"/>
-      <c r="F2" s="200"/>
+      <c r="B2" s="193"/>
+      <c r="C2" s="193"/>
+      <c r="D2" s="193"/>
+      <c r="E2" s="193"/>
+      <c r="F2" s="194"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="77" t="s">
@@ -14373,14 +14066,14 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="201" t="s">
-        <v>989</v>
-      </c>
-      <c r="B4" s="202"/>
-      <c r="C4" s="202"/>
-      <c r="D4" s="202"/>
-      <c r="E4" s="202"/>
-      <c r="F4" s="203"/>
+      <c r="A4" s="195" t="s">
+        <v>965</v>
+      </c>
+      <c r="B4" s="196"/>
+      <c r="C4" s="196"/>
+      <c r="D4" s="196"/>
+      <c r="E4" s="196"/>
+      <c r="F4" s="197"/>
     </row>
     <row r="5" spans="1:6" ht="28">
       <c r="A5" s="98" t="s">
@@ -14427,13 +14120,13 @@
         <v>350</v>
       </c>
       <c r="B7" s="158" t="s">
-        <v>811</v>
+        <v>795</v>
       </c>
       <c r="C7" s="50" t="s">
         <v>361</v>
       </c>
       <c r="D7" s="50" t="s">
-        <v>1172</v>
+        <v>1143</v>
       </c>
       <c r="E7" s="50" t="s">
         <v>362</v>
@@ -14470,16 +14163,16 @@
         <v>369</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>990</v>
+        <v>966</v>
       </c>
       <c r="D9" s="50" t="s">
-        <v>991</v>
+        <v>967</v>
       </c>
       <c r="E9" s="50" t="s">
         <v>370</v>
       </c>
       <c r="F9" s="115" t="s">
-        <v>992</v>
+        <v>968</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28">
@@ -14489,17 +14182,17 @@
       <c r="B10" s="56" t="s">
         <v>371</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>993</v>
+      <c r="C10" s="244" t="s">
+        <v>1156</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>994</v>
+        <v>969</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>995</v>
+        <v>970</v>
       </c>
       <c r="F10" s="116" t="s">
-        <v>996</v>
+        <v>971</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="45" customHeight="1">
@@ -14507,19 +14200,19 @@
         <v>350</v>
       </c>
       <c r="B11" s="154" t="s">
-        <v>770</v>
+        <v>758</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>1139</v>
+        <v>1111</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>1140</v>
+        <v>1112</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>1141</v>
+        <v>1113</v>
       </c>
       <c r="F11" s="117" t="s">
-        <v>1142</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="45" customHeight="1">
@@ -14527,19 +14220,19 @@
         <v>350</v>
       </c>
       <c r="B12" s="154" t="s">
-        <v>1143</v>
+        <v>1115</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>1144</v>
+        <v>1116</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>1145</v>
+        <v>1117</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>997</v>
+        <v>972</v>
       </c>
       <c r="F12" s="117" t="s">
-        <v>998</v>
+        <v>973</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28">
@@ -14550,16 +14243,16 @@
         <v>373</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>999</v>
+        <v>974</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>1127</v>
+        <v>1099</v>
       </c>
       <c r="E13" s="41" t="s">
-        <v>1000</v>
+        <v>975</v>
       </c>
       <c r="F13" s="118" t="s">
-        <v>1001</v>
+        <v>976</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="28">
@@ -14576,21 +14269,21 @@
         <v>376</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>1002</v>
+        <v>977</v>
       </c>
       <c r="F14" s="116" t="s">
-        <v>996</v>
+        <v>971</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="201" t="s">
-        <v>1003</v>
-      </c>
-      <c r="B15" s="202"/>
-      <c r="C15" s="202"/>
-      <c r="D15" s="202"/>
-      <c r="E15" s="202"/>
-      <c r="F15" s="203"/>
+      <c r="A15" s="195" t="s">
+        <v>978</v>
+      </c>
+      <c r="B15" s="196"/>
+      <c r="C15" s="196"/>
+      <c r="D15" s="196"/>
+      <c r="E15" s="196"/>
+      <c r="F15" s="197"/>
     </row>
     <row r="16" spans="1:6" ht="28">
       <c r="A16" s="101" t="s">
@@ -14600,16 +14293,16 @@
         <v>379</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>1004</v>
+        <v>979</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>1005</v>
+        <v>980</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>1006</v>
+        <v>981</v>
       </c>
       <c r="F16" s="116" t="s">
-        <v>992</v>
+        <v>968</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="90" customHeight="1">
@@ -14619,17 +14312,17 @@
       <c r="B17" s="59" t="s">
         <v>380</v>
       </c>
-      <c r="C17" s="47" t="s">
-        <v>381</v>
+      <c r="C17" s="186" t="s">
+        <v>1157</v>
       </c>
       <c r="D17" s="47" t="s">
-        <v>1154</v>
-      </c>
-      <c r="E17" s="241" t="s">
-        <v>1155</v>
+        <v>1125</v>
+      </c>
+      <c r="E17" s="186" t="s">
+        <v>1126</v>
       </c>
       <c r="F17" s="119" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="56">
@@ -14637,39 +14330,39 @@
         <v>378</v>
       </c>
       <c r="B18" s="60" t="s">
+        <v>383</v>
+      </c>
+      <c r="C18" s="61" t="s">
         <v>384</v>
       </c>
-      <c r="C18" s="61" t="s">
+      <c r="D18" s="61" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E18" s="187" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F18" s="120" t="s">
         <v>385</v>
-      </c>
-      <c r="D18" s="61" t="s">
-        <v>1171</v>
-      </c>
-      <c r="E18" s="242" t="s">
-        <v>1156</v>
-      </c>
-      <c r="F18" s="120" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="182">
       <c r="A19" s="104" t="s">
         <v>378</v>
       </c>
-      <c r="B19" s="243" t="s">
-        <v>1162</v>
+      <c r="B19" s="188" t="s">
+        <v>1133</v>
       </c>
       <c r="C19" s="47" t="s">
-        <v>1157</v>
+        <v>1128</v>
       </c>
       <c r="D19" s="47" t="s">
-        <v>1168</v>
-      </c>
-      <c r="E19" s="241" t="s">
-        <v>1163</v>
+        <v>1139</v>
+      </c>
+      <c r="E19" s="186" t="s">
+        <v>1134</v>
       </c>
       <c r="F19" s="119" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="70">
@@ -14677,19 +14370,19 @@
         <v>378</v>
       </c>
       <c r="B20" s="152" t="s">
-        <v>1164</v>
+        <v>1135</v>
       </c>
       <c r="C20" s="61" t="s">
-        <v>1158</v>
+        <v>1129</v>
       </c>
       <c r="D20" s="61" t="s">
-        <v>1167</v>
-      </c>
-      <c r="E20" s="242" t="s">
-        <v>1159</v>
+        <v>1138</v>
+      </c>
+      <c r="E20" s="187" t="s">
+        <v>1130</v>
       </c>
       <c r="F20" s="120" t="s">
-        <v>1160</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="28" customHeight="1">
@@ -14697,19 +14390,19 @@
         <v>378</v>
       </c>
       <c r="B21" s="152" t="s">
-        <v>1175</v>
+        <v>1146</v>
       </c>
       <c r="C21" s="61" t="s">
-        <v>1126</v>
+        <v>1098</v>
       </c>
       <c r="D21" s="61" t="s">
-        <v>1170</v>
+        <v>1141</v>
       </c>
       <c r="E21" s="61" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="F21" s="120" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="56" customHeight="1">
@@ -14717,19 +14410,19 @@
         <v>378</v>
       </c>
       <c r="B22" s="152" t="s">
-        <v>1175</v>
+        <v>1146</v>
       </c>
       <c r="C22" s="61" t="s">
-        <v>1161</v>
+        <v>1132</v>
       </c>
       <c r="D22" s="61" t="s">
-        <v>1169</v>
+        <v>1140</v>
       </c>
       <c r="E22" s="61" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="F22" s="120" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="28">
@@ -14737,16 +14430,16 @@
         <v>378</v>
       </c>
       <c r="B23" s="157" t="s">
-        <v>1165</v>
+        <v>1136</v>
       </c>
       <c r="C23" s="20" t="s">
+        <v>389</v>
+      </c>
+      <c r="D23" s="20" t="s">
         <v>390</v>
       </c>
-      <c r="D23" s="20" t="s">
+      <c r="E23" s="20" t="s">
         <v>391</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>392</v>
       </c>
       <c r="F23" s="121" t="s">
         <v>60</v>
@@ -14757,19 +14450,19 @@
         <v>378</v>
       </c>
       <c r="B24" s="157" t="s">
-        <v>1166</v>
-      </c>
-      <c r="C24" s="20" t="s">
-        <v>812</v>
+        <v>1137</v>
+      </c>
+      <c r="C24" s="245" t="s">
+        <v>1158</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>813</v>
+        <v>796</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>814</v>
+        <v>797</v>
       </c>
       <c r="F24" s="121" t="s">
-        <v>805</v>
+        <v>790</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="56">
@@ -14777,19 +14470,19 @@
         <v>378</v>
       </c>
       <c r="B25" s="159" t="s">
-        <v>1110</v>
+        <v>1084</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>1120</v>
+        <v>1092</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>1123</v>
+        <v>1095</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>1121</v>
+        <v>1093</v>
       </c>
       <c r="F25" s="86" t="s">
-        <v>1122</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="110" customHeight="1">
@@ -14797,19 +14490,19 @@
         <v>378</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>1111</v>
-      </c>
-      <c r="C26" s="61" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D26" s="242" t="s">
-        <v>1183</v>
-      </c>
-      <c r="E26" s="242" t="s">
-        <v>1182</v>
+        <v>1085</v>
+      </c>
+      <c r="C26" s="187" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D26" s="187" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E26" s="187" t="s">
+        <v>1153</v>
       </c>
       <c r="F26" s="120" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="56">
@@ -14817,19 +14510,19 @@
         <v>378</v>
       </c>
       <c r="B27" s="152" t="s">
-        <v>1113</v>
-      </c>
-      <c r="C27" s="61" t="s">
-        <v>1114</v>
+        <v>1086</v>
+      </c>
+      <c r="C27" s="187" t="s">
+        <v>1160</v>
       </c>
       <c r="D27" s="61" t="s">
-        <v>1124</v>
+        <v>1096</v>
       </c>
       <c r="E27" s="61" t="s">
-        <v>1115</v>
+        <v>1087</v>
       </c>
       <c r="F27" s="120" t="s">
-        <v>804</v>
+        <v>789</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="42">
@@ -14837,19 +14530,19 @@
         <v>378</v>
       </c>
       <c r="B28" s="152" t="s">
-        <v>1116</v>
+        <v>1088</v>
       </c>
       <c r="C28" s="61" t="s">
-        <v>1117</v>
+        <v>1089</v>
       </c>
       <c r="D28" s="61" t="s">
-        <v>1125</v>
+        <v>1097</v>
       </c>
       <c r="E28" s="61" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F28" s="120" t="s">
-        <v>1118</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="28">
@@ -14857,19 +14550,19 @@
         <v>378</v>
       </c>
       <c r="B29" s="160" t="s">
-        <v>1146</v>
+        <v>1118</v>
       </c>
       <c r="C29" s="36" t="s">
-        <v>1147</v>
+        <v>1119</v>
       </c>
       <c r="D29" s="36" t="s">
-        <v>1148</v>
+        <v>1120</v>
       </c>
       <c r="E29" s="36" t="s">
-        <v>1149</v>
+        <v>1121</v>
       </c>
       <c r="F29" s="122" t="s">
-        <v>937</v>
+        <v>913</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="70">
@@ -14877,19 +14570,19 @@
         <v>378</v>
       </c>
       <c r="B30" s="154" t="s">
-        <v>1150</v>
-      </c>
-      <c r="C30" s="33" t="s">
-        <v>1151</v>
+        <v>1122</v>
+      </c>
+      <c r="C30" s="246" t="s">
+        <v>1161</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>1152</v>
+        <v>1123</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>1153</v>
+        <v>1124</v>
       </c>
       <c r="F30" s="117" t="s">
-        <v>937</v>
+        <v>913</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="56">
@@ -14897,19 +14590,19 @@
         <v>378</v>
       </c>
       <c r="B31" s="154" t="s">
-        <v>1119</v>
+        <v>1091</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>782</v>
+        <v>770</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>1184</v>
+        <v>1155</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>783</v>
+        <v>771</v>
       </c>
       <c r="F31" s="117" t="s">
-        <v>784</v>
+        <v>772</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="28">
@@ -14917,19 +14610,19 @@
         <v>378</v>
       </c>
       <c r="B32" s="160" t="s">
-        <v>785</v>
+        <v>773</v>
       </c>
       <c r="C32" s="36" t="s">
+        <v>395</v>
+      </c>
+      <c r="D32" s="36" t="s">
         <v>396</v>
       </c>
-      <c r="D32" s="36" t="s">
+      <c r="E32" s="36" t="s">
         <v>397</v>
       </c>
-      <c r="E32" s="36" t="s">
+      <c r="F32" s="122" t="s">
         <v>398</v>
-      </c>
-      <c r="F32" s="122" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="28">
@@ -14937,126 +14630,126 @@
         <v>378</v>
       </c>
       <c r="B33" s="151" t="s">
-        <v>774</v>
+        <v>762</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>1007</v>
+        <v>982</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>1008</v>
+        <v>983</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>1002</v>
+        <v>977</v>
       </c>
       <c r="F33" s="116" t="s">
-        <v>996</v>
+        <v>971</v>
       </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="201" t="s">
-        <v>1009</v>
-      </c>
-      <c r="B34" s="202"/>
-      <c r="C34" s="202"/>
-      <c r="D34" s="202"/>
-      <c r="E34" s="202"/>
-      <c r="F34" s="203"/>
+      <c r="A34" s="195" t="s">
+        <v>984</v>
+      </c>
+      <c r="B34" s="196"/>
+      <c r="C34" s="196"/>
+      <c r="D34" s="196"/>
+      <c r="E34" s="196"/>
+      <c r="F34" s="197"/>
     </row>
     <row r="35" spans="1:6" ht="42">
       <c r="A35" s="101" t="s">
+        <v>400</v>
+      </c>
+      <c r="B35" s="56" t="s">
         <v>401</v>
       </c>
-      <c r="B35" s="56" t="s">
-        <v>402</v>
-      </c>
       <c r="C35" s="10" t="s">
-        <v>1010</v>
+        <v>985</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>1011</v>
+        <v>986</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>1012</v>
+        <v>987</v>
       </c>
       <c r="F35" s="116" t="s">
-        <v>992</v>
+        <v>968</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="84">
       <c r="A36" s="102" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B36" s="154" t="s">
-        <v>1176</v>
-      </c>
-      <c r="C36" s="33" t="s">
-        <v>874</v>
+        <v>1147</v>
+      </c>
+      <c r="C36" s="246" t="s">
+        <v>1162</v>
       </c>
       <c r="D36" s="33" t="s">
-        <v>875</v>
+        <v>853</v>
       </c>
       <c r="E36" s="35" t="s">
-        <v>876</v>
+        <v>854</v>
       </c>
       <c r="F36" s="117" t="s">
-        <v>877</v>
+        <v>855</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="28">
       <c r="A37" s="105" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B37" s="60" t="s">
+        <v>402</v>
+      </c>
+      <c r="C37" s="61" t="s">
         <v>403</v>
       </c>
-      <c r="C37" s="61" t="s">
+      <c r="D37" s="61" t="s">
         <v>404</v>
       </c>
-      <c r="D37" s="61" t="s">
+      <c r="E37" s="61" t="s">
         <v>405</v>
       </c>
-      <c r="E37" s="61" t="s">
+      <c r="F37" s="120" t="s">
         <v>406</v>
-      </c>
-      <c r="F37" s="120" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="28">
       <c r="A38" s="105" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B38" s="60" t="s">
+        <v>407</v>
+      </c>
+      <c r="C38" s="61" t="s">
         <v>408</v>
       </c>
-      <c r="C38" s="61" t="s">
+      <c r="D38" s="61" t="s">
         <v>409</v>
       </c>
-      <c r="D38" s="61" t="s">
+      <c r="E38" s="61" t="s">
         <v>410</v>
       </c>
-      <c r="E38" s="61" t="s">
+      <c r="F38" s="120" t="s">
         <v>411</v>
-      </c>
-      <c r="F38" s="120" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="28">
       <c r="A39" s="104" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B39" s="59" t="s">
+        <v>412</v>
+      </c>
+      <c r="C39" s="186" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D39" s="47" t="s">
         <v>413</v>
       </c>
-      <c r="C39" s="47" t="s">
-        <v>414</v>
-      </c>
-      <c r="D39" s="47" t="s">
-        <v>415</v>
-      </c>
       <c r="E39" s="47" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F39" s="119" t="s">
         <v>175</v>
@@ -15064,179 +14757,179 @@
     </row>
     <row r="40" spans="1:6" ht="28">
       <c r="A40" s="99" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B40" s="54" t="s">
+        <v>414</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="D40" s="15" t="s">
         <v>416</v>
-      </c>
-      <c r="C40" s="15" t="s">
-        <v>417</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>418</v>
       </c>
       <c r="E40" s="15" t="s">
         <v>53</v>
       </c>
       <c r="F40" s="85" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="70">
       <c r="A41" s="99" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B41" s="54" t="s">
-        <v>1013</v>
-      </c>
-      <c r="C41" s="15" t="s">
-        <v>1014</v>
+        <v>988</v>
+      </c>
+      <c r="C41" s="247" t="s">
+        <v>1164</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>1128</v>
+        <v>1100</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>1015</v>
+        <v>989</v>
       </c>
       <c r="F41" s="85" t="s">
-        <v>1016</v>
+        <v>990</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="28">
       <c r="A42" s="105" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B42" s="60" t="s">
-        <v>1017</v>
+        <v>991</v>
       </c>
       <c r="C42" s="61" t="s">
+        <v>418</v>
+      </c>
+      <c r="D42" s="61" t="s">
+        <v>419</v>
+      </c>
+      <c r="E42" s="61" t="s">
+        <v>410</v>
+      </c>
+      <c r="F42" s="120" t="s">
         <v>420</v>
-      </c>
-      <c r="D42" s="61" t="s">
-        <v>421</v>
-      </c>
-      <c r="E42" s="61" t="s">
-        <v>411</v>
-      </c>
-      <c r="F42" s="120" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="28">
       <c r="A43" s="102" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B43" s="57" t="s">
-        <v>1062</v>
+        <v>1036</v>
       </c>
       <c r="C43" s="33" t="s">
+        <v>421</v>
+      </c>
+      <c r="D43" s="33" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E43" s="35" t="s">
+        <v>422</v>
+      </c>
+      <c r="F43" s="117" t="s">
         <v>423</v>
-      </c>
-      <c r="D43" s="33" t="s">
-        <v>1129</v>
-      </c>
-      <c r="E43" s="35" t="s">
-        <v>424</v>
-      </c>
-      <c r="F43" s="117" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="28">
       <c r="A44" s="102" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B44" s="154" t="s">
-        <v>1177</v>
+        <v>1148</v>
       </c>
       <c r="C44" s="33" t="s">
-        <v>801</v>
+        <v>786</v>
       </c>
       <c r="D44" s="33" t="s">
-        <v>802</v>
+        <v>787</v>
       </c>
       <c r="E44" s="35" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="F44" s="117" t="s">
-        <v>803</v>
+        <v>788</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="70">
       <c r="A45" s="102" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B45" s="154" t="s">
-        <v>1177</v>
-      </c>
-      <c r="C45" s="33" t="s">
-        <v>854</v>
+        <v>1148</v>
+      </c>
+      <c r="C45" s="246" t="s">
+        <v>1165</v>
       </c>
       <c r="D45" s="33" t="s">
-        <v>1136</v>
+        <v>1108</v>
       </c>
       <c r="E45" s="35" t="s">
-        <v>855</v>
+        <v>836</v>
       </c>
       <c r="F45" s="117" t="s">
-        <v>856</v>
+        <v>837</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="56">
       <c r="A46" s="102" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B46" s="154" t="s">
-        <v>1177</v>
-      </c>
-      <c r="C46" s="33" t="s">
-        <v>857</v>
+        <v>1148</v>
+      </c>
+      <c r="C46" s="246" t="s">
+        <v>1166</v>
       </c>
       <c r="D46" s="33" t="s">
-        <v>1137</v>
+        <v>1109</v>
       </c>
       <c r="E46" s="35" t="s">
-        <v>858</v>
+        <v>838</v>
       </c>
       <c r="F46" s="117" t="s">
-        <v>859</v>
+        <v>839</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="45" customHeight="1">
       <c r="A47" s="102" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B47" s="154" t="s">
-        <v>1177</v>
-      </c>
-      <c r="C47" s="33" t="s">
-        <v>867</v>
+        <v>1148</v>
+      </c>
+      <c r="C47" s="246" t="s">
+        <v>1167</v>
       </c>
       <c r="D47" s="33" t="s">
-        <v>1138</v>
+        <v>1110</v>
       </c>
       <c r="E47" s="35" t="s">
-        <v>868</v>
+        <v>847</v>
       </c>
       <c r="F47" s="117" t="s">
-        <v>869</v>
+        <v>848</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="28">
       <c r="A48" s="106" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B48" s="63" t="s">
-        <v>1063</v>
+        <v>1037</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D48" s="20" t="s">
-        <v>1130</v>
+        <v>1102</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="F48" s="121" t="s">
         <v>64</v>
@@ -15244,96 +14937,96 @@
     </row>
     <row r="49" spans="1:6" ht="42">
       <c r="A49" s="105" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B49" s="152" t="s">
-        <v>1064</v>
+        <v>1038</v>
       </c>
       <c r="C49" s="61" t="s">
+        <v>426</v>
+      </c>
+      <c r="D49" s="61" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E49" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="F49" s="120" t="s">
         <v>428</v>
-      </c>
-      <c r="D49" s="61" t="s">
-        <v>1131</v>
-      </c>
-      <c r="E49" s="61" t="s">
-        <v>429</v>
-      </c>
-      <c r="F49" s="120" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="28">
       <c r="A50" s="103" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B50" s="155" t="s">
-        <v>1178</v>
+        <v>1149</v>
       </c>
       <c r="C50" s="39" t="s">
+        <v>429</v>
+      </c>
+      <c r="D50" s="39" t="s">
+        <v>799</v>
+      </c>
+      <c r="E50" s="39" t="s">
+        <v>800</v>
+      </c>
+      <c r="F50" s="118" t="s">
         <v>431</v>
-      </c>
-      <c r="D50" s="39" t="s">
-        <v>816</v>
-      </c>
-      <c r="E50" s="39" t="s">
-        <v>817</v>
-      </c>
-      <c r="F50" s="118" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="42">
       <c r="A51" s="98" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B51" s="53" t="s">
-        <v>818</v>
+        <v>801</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>819</v>
+        <v>802</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>820</v>
+        <v>803</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>821</v>
+        <v>804</v>
       </c>
       <c r="F51" s="86" t="s">
-        <v>822</v>
+        <v>805</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="56">
       <c r="A52" s="98" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B52" s="159" t="s">
-        <v>823</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>824</v>
+        <v>806</v>
+      </c>
+      <c r="C52" s="248" t="s">
+        <v>1168</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>825</v>
+        <v>807</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>826</v>
+        <v>808</v>
       </c>
       <c r="F52" s="86" t="s">
-        <v>822</v>
+        <v>805</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="28">
       <c r="A53" s="101" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B53" s="151" t="s">
-        <v>774</v>
+        <v>762</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>827</v>
+        <v>809</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>377</v>
@@ -15344,19 +15037,19 @@
     </row>
     <row r="54" spans="1:6" ht="28">
       <c r="A54" s="109" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B54" s="65" t="s">
+        <v>434</v>
+      </c>
+      <c r="C54" s="249" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D54" s="42" t="s">
+        <v>435</v>
+      </c>
+      <c r="E54" s="42" t="s">
         <v>436</v>
-      </c>
-      <c r="C54" s="42" t="s">
-        <v>437</v>
-      </c>
-      <c r="D54" s="42" t="s">
-        <v>438</v>
-      </c>
-      <c r="E54" s="42" t="s">
-        <v>439</v>
       </c>
       <c r="F54" s="124" t="s">
         <v>266</v>
@@ -15364,69 +15057,69 @@
     </row>
     <row r="55" spans="1:6" ht="28">
       <c r="A55" s="103" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B55" s="58" t="s">
+        <v>434</v>
+      </c>
+      <c r="C55" s="39" t="s">
+        <v>437</v>
+      </c>
+      <c r="D55" s="39" t="s">
+        <v>438</v>
+      </c>
+      <c r="E55" s="39" t="s">
         <v>436</v>
       </c>
-      <c r="C55" s="39" t="s">
-        <v>440</v>
-      </c>
-      <c r="D55" s="39" t="s">
-        <v>441</v>
-      </c>
-      <c r="E55" s="39" t="s">
+      <c r="F55" s="118" t="s">
         <v>439</v>
-      </c>
-      <c r="F55" s="118" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="42">
       <c r="A56" s="103" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B56" s="155" t="s">
-        <v>436</v>
-      </c>
-      <c r="C56" s="39" t="s">
-        <v>798</v>
+        <v>434</v>
+      </c>
+      <c r="C56" s="250" t="s">
+        <v>1170</v>
       </c>
       <c r="D56" s="156" t="s">
-        <v>1132</v>
+        <v>1104</v>
       </c>
       <c r="E56" s="39" t="s">
-        <v>799</v>
+        <v>784</v>
       </c>
       <c r="F56" s="118" t="s">
-        <v>800</v>
+        <v>785</v>
       </c>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="186" t="s">
-        <v>1049</v>
-      </c>
-      <c r="B57" s="187"/>
-      <c r="C57" s="187"/>
-      <c r="D57" s="187"/>
-      <c r="E57" s="187"/>
-      <c r="F57" s="188"/>
+      <c r="A57" s="198" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B57" s="199"/>
+      <c r="C57" s="199"/>
+      <c r="D57" s="199"/>
+      <c r="E57" s="199"/>
+      <c r="F57" s="200"/>
     </row>
     <row r="58" spans="1:6" ht="28">
       <c r="A58" s="101" t="s">
+        <v>440</v>
+      </c>
+      <c r="B58" s="56" t="s">
+        <v>401</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="E58" s="10" t="s">
         <v>443</v>
-      </c>
-      <c r="B58" s="56" t="s">
-        <v>402</v>
-      </c>
-      <c r="C58" s="10" t="s">
-        <v>444</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>445</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>446</v>
       </c>
       <c r="F58" s="116" t="s">
         <v>24</v>
@@ -15434,76 +15127,76 @@
     </row>
     <row r="59" spans="1:6" ht="28">
       <c r="A59" s="100" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B59" s="55" t="s">
+        <v>444</v>
+      </c>
+      <c r="C59" s="50" t="s">
+        <v>445</v>
+      </c>
+      <c r="D59" s="50" t="s">
+        <v>446</v>
+      </c>
+      <c r="E59" s="50" t="s">
         <v>447</v>
       </c>
-      <c r="C59" s="50" t="s">
+      <c r="F59" s="115" t="s">
         <v>448</v>
-      </c>
-      <c r="D59" s="50" t="s">
-        <v>449</v>
-      </c>
-      <c r="E59" s="50" t="s">
-        <v>450</v>
-      </c>
-      <c r="F59" s="115" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="28">
       <c r="A60" s="100" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B60" s="55" t="s">
+        <v>449</v>
+      </c>
+      <c r="C60" s="50" t="s">
+        <v>450</v>
+      </c>
+      <c r="D60" s="50" t="s">
+        <v>451</v>
+      </c>
+      <c r="E60" s="50" t="s">
         <v>452</v>
       </c>
-      <c r="C60" s="50" t="s">
+      <c r="F60" s="115" t="s">
         <v>453</v>
-      </c>
-      <c r="D60" s="50" t="s">
-        <v>454</v>
-      </c>
-      <c r="E60" s="50" t="s">
-        <v>455</v>
-      </c>
-      <c r="F60" s="115" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="28">
       <c r="A61" s="101" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B61" s="56" t="s">
-        <v>457</v>
-      </c>
-      <c r="C61" s="10" t="s">
-        <v>458</v>
+        <v>454</v>
+      </c>
+      <c r="C61" s="244" t="s">
+        <v>1171</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>370</v>
       </c>
       <c r="F61" s="116" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="28">
       <c r="A62" s="99" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B62" s="54" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="D62" s="25" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="E62" s="15" t="s">
         <v>145</v>
@@ -15514,19 +15207,19 @@
     </row>
     <row r="63" spans="1:6" ht="28">
       <c r="A63" s="105" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B63" s="60" t="s">
-        <v>1065</v>
+        <v>1039</v>
       </c>
       <c r="C63" s="61" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="D63" s="61" t="s">
-        <v>1173</v>
+        <v>1144</v>
       </c>
       <c r="E63" s="61" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F63" s="120" t="s">
         <v>193</v>
@@ -15534,164 +15227,164 @@
     </row>
     <row r="64" spans="1:6" ht="28">
       <c r="A64" s="106" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B64" s="63" t="s">
-        <v>1018</v>
+        <v>992</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D64" s="20" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E64" s="20" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="F64" s="121" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="28">
       <c r="A65" s="105" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B65" s="60" t="s">
-        <v>815</v>
+        <v>798</v>
       </c>
       <c r="C65" s="61" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="D65" s="61" t="s">
-        <v>1066</v>
+        <v>1040</v>
       </c>
       <c r="E65" s="61" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="F65" s="120" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="45">
       <c r="A66" s="110" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B66" s="91" t="s">
-        <v>1067</v>
+        <v>1041</v>
       </c>
       <c r="C66" s="92" t="s">
-        <v>754</v>
+        <v>743</v>
       </c>
       <c r="D66" s="92" t="s">
-        <v>1068</v>
+        <v>1042</v>
       </c>
       <c r="E66" s="92" t="s">
-        <v>755</v>
+        <v>744</v>
       </c>
       <c r="F66" s="125" t="s">
-        <v>756</v>
+        <v>745</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="28">
       <c r="A67" s="105" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B67" s="60" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C67" s="61" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="D67" s="61" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="E67" s="61" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="F67" s="120" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="28">
       <c r="A68" s="107" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B68" s="64" t="s">
-        <v>770</v>
+        <v>758</v>
       </c>
       <c r="C68" s="36" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="D68" s="36" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="E68" s="36" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="F68" s="122" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="28">
       <c r="A69" s="109" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B69" s="65" t="s">
-        <v>771</v>
-      </c>
-      <c r="C69" s="42" t="s">
-        <v>482</v>
+        <v>759</v>
+      </c>
+      <c r="C69" s="249" t="s">
+        <v>1172</v>
       </c>
       <c r="D69" s="44" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="E69" s="42" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="F69" s="124" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="28">
       <c r="A70" s="101" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B70" s="128" t="s">
-        <v>774</v>
+        <v>762</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="D70" s="10"/>
       <c r="E70" s="10" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="F70" s="116" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="71" spans="1:6">
-      <c r="A71" s="186" t="s">
-        <v>1050</v>
-      </c>
-      <c r="B71" s="187"/>
-      <c r="C71" s="187"/>
-      <c r="D71" s="187"/>
-      <c r="E71" s="187"/>
-      <c r="F71" s="188"/>
+      <c r="A71" s="198" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B71" s="199"/>
+      <c r="C71" s="199"/>
+      <c r="D71" s="199"/>
+      <c r="E71" s="199"/>
+      <c r="F71" s="200"/>
     </row>
     <row r="72" spans="1:6" ht="28">
       <c r="A72" s="101" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B72" s="56" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="E72" s="10" t="s">
         <v>20</v>
@@ -15702,199 +15395,199 @@
     </row>
     <row r="73" spans="1:6" ht="28">
       <c r="A73" s="105" t="s">
+        <v>484</v>
+      </c>
+      <c r="B73" s="60" t="s">
+        <v>487</v>
+      </c>
+      <c r="C73" s="61" t="s">
+        <v>488</v>
+      </c>
+      <c r="D73" s="62" t="s">
         <v>489</v>
       </c>
-      <c r="B73" s="60" t="s">
-        <v>492</v>
-      </c>
-      <c r="C73" s="61" t="s">
-        <v>493</v>
-      </c>
-      <c r="D73" s="62" t="s">
-        <v>494</v>
-      </c>
       <c r="E73" s="61" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="F73" s="120" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="30">
       <c r="A74" s="108" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B74" s="89" t="s">
-        <v>757</v>
+        <v>746</v>
       </c>
       <c r="C74" s="90" t="s">
-        <v>758</v>
+        <v>747</v>
       </c>
       <c r="D74" s="90" t="s">
-        <v>759</v>
+        <v>748</v>
       </c>
       <c r="E74" s="90" t="s">
-        <v>760</v>
+        <v>749</v>
       </c>
       <c r="F74" s="123" t="s">
-        <v>761</v>
+        <v>750</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="28">
       <c r="A75" s="103" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B75" s="58" t="s">
-        <v>772</v>
+        <v>760</v>
       </c>
       <c r="C75" s="39" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="D75" s="39" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="E75" s="39" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="F75" s="118" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="28">
       <c r="A76" s="104" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B76" s="59" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C76" s="47" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="D76" s="47" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="E76" s="47" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="F76" s="119" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="28">
       <c r="A77" s="105" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B77" s="60" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="C77" s="61" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="D77" s="61" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="E77" s="61" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="F77" s="120" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="28">
       <c r="A78" s="98" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B78" s="53" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="F78" s="86" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="28">
       <c r="A79" s="105" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B79" s="60" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="C79" s="61" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="D79" s="61" t="s">
-        <v>1133</v>
+        <v>1105</v>
       </c>
       <c r="E79" s="61" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="F79" s="120" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="28">
       <c r="A80" s="104" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B80" s="59" t="s">
-        <v>1069</v>
+        <v>1043</v>
       </c>
       <c r="C80" s="47" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="D80" s="47" t="s">
-        <v>1134</v>
+        <v>1106</v>
       </c>
       <c r="E80" s="47" t="s">
+        <v>511</v>
+      </c>
+      <c r="F80" s="119" t="s">
         <v>516</v>
-      </c>
-      <c r="F80" s="119" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="28">
       <c r="A81" s="106" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B81" s="63" t="s">
-        <v>1070</v>
+        <v>1044</v>
       </c>
       <c r="C81" s="20" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="D81" s="20" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="E81" s="20" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="F81" s="121" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="28">
       <c r="A82" s="102" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B82" s="57" t="s">
-        <v>526</v>
-      </c>
-      <c r="C82" s="33" t="s">
-        <v>527</v>
+        <v>521</v>
+      </c>
+      <c r="C82" s="246" t="s">
+        <v>1173</v>
       </c>
       <c r="D82" s="33" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="E82" s="33" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="F82" s="117" t="s">
         <v>29</v>
@@ -15902,36 +15595,36 @@
     </row>
     <row r="83" spans="1:6" ht="28">
       <c r="A83" s="102" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B83" s="154" t="s">
-        <v>1179</v>
-      </c>
-      <c r="C83" s="33" t="s">
-        <v>795</v>
+        <v>1150</v>
+      </c>
+      <c r="C83" s="246" t="s">
+        <v>1174</v>
       </c>
       <c r="D83" s="33" t="s">
-        <v>796</v>
+        <v>782</v>
       </c>
       <c r="E83" s="33" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="F83" s="117" t="s">
-        <v>797</v>
+        <v>783</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="28">
       <c r="A84" s="107" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B84" s="64" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C84" s="36" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="D84" s="36" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="E84" s="36" t="s">
         <v>185</v>
@@ -15942,19 +15635,19 @@
     </row>
     <row r="85" spans="1:6" ht="28">
       <c r="A85" s="101" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B85" s="56" t="s">
-        <v>532</v>
-      </c>
-      <c r="C85" s="10" t="s">
-        <v>533</v>
+        <v>526</v>
+      </c>
+      <c r="C85" s="244" t="s">
+        <v>1175</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F85" s="116" t="s">
         <v>29</v>
@@ -15962,147 +15655,147 @@
     </row>
     <row r="86" spans="1:6" ht="28">
       <c r="A86" s="101" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B86" s="56" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="E86" s="10" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="F86" s="116" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="28">
       <c r="A87" s="103" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B87" s="58" t="s">
+        <v>434</v>
+      </c>
+      <c r="C87" s="39" t="s">
+        <v>530</v>
+      </c>
+      <c r="D87" s="39" t="s">
+        <v>531</v>
+      </c>
+      <c r="E87" s="39" t="s">
         <v>436</v>
       </c>
-      <c r="C87" s="39" t="s">
-        <v>537</v>
-      </c>
-      <c r="D87" s="39" t="s">
-        <v>538</v>
-      </c>
-      <c r="E87" s="39" t="s">
-        <v>439</v>
-      </c>
       <c r="F87" s="118" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="28">
       <c r="A88" s="103" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B88" s="58" t="s">
+        <v>434</v>
+      </c>
+      <c r="C88" s="39" t="s">
+        <v>533</v>
+      </c>
+      <c r="D88" s="39" t="s">
+        <v>534</v>
+      </c>
+      <c r="E88" s="39" t="s">
         <v>436</v>
       </c>
-      <c r="C88" s="39" t="s">
-        <v>540</v>
-      </c>
-      <c r="D88" s="39" t="s">
-        <v>541</v>
-      </c>
-      <c r="E88" s="39" t="s">
-        <v>439</v>
-      </c>
       <c r="F88" s="118" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="28">
       <c r="A89" s="103" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B89" s="58" t="s">
+        <v>434</v>
+      </c>
+      <c r="C89" s="39" t="s">
+        <v>536</v>
+      </c>
+      <c r="D89" s="39" t="s">
+        <v>537</v>
+      </c>
+      <c r="E89" s="39" t="s">
         <v>436</v>
       </c>
-      <c r="C89" s="39" t="s">
-        <v>543</v>
-      </c>
-      <c r="D89" s="39" t="s">
-        <v>544</v>
-      </c>
-      <c r="E89" s="39" t="s">
-        <v>439</v>
-      </c>
       <c r="F89" s="118" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="45">
       <c r="A90" s="108" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B90" s="89" t="s">
-        <v>436</v>
-      </c>
-      <c r="C90" s="90" t="s">
-        <v>762</v>
+        <v>434</v>
+      </c>
+      <c r="C90" s="251" t="s">
+        <v>1176</v>
       </c>
       <c r="D90" s="95" t="s">
-        <v>763</v>
+        <v>751</v>
       </c>
       <c r="E90" s="90" t="s">
-        <v>764</v>
+        <v>752</v>
       </c>
       <c r="F90" s="123" t="s">
-        <v>765</v>
+        <v>753</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="45">
       <c r="A91" s="108" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B91" s="153" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C91" s="90" t="s">
-        <v>792</v>
+        <v>779</v>
       </c>
       <c r="D91" s="95" t="s">
-        <v>793</v>
+        <v>780</v>
       </c>
       <c r="E91" s="90" t="s">
-        <v>764</v>
+        <v>752</v>
       </c>
       <c r="F91" s="123" t="s">
-        <v>794</v>
+        <v>781</v>
       </c>
     </row>
     <row r="92" spans="1:6">
-      <c r="A92" s="189" t="s">
-        <v>1051</v>
-      </c>
-      <c r="B92" s="190"/>
-      <c r="C92" s="190"/>
-      <c r="D92" s="190"/>
-      <c r="E92" s="190"/>
-      <c r="F92" s="191"/>
+      <c r="A92" s="201" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B92" s="202"/>
+      <c r="C92" s="202"/>
+      <c r="D92" s="202"/>
+      <c r="E92" s="202"/>
+      <c r="F92" s="203"/>
     </row>
     <row r="93" spans="1:6" ht="28">
       <c r="A93" s="101" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="B93" s="56" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="D93" s="10"/>
       <c r="E93" s="10" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F93" s="116" t="s">
         <v>29</v>
@@ -16110,76 +15803,76 @@
     </row>
     <row r="94" spans="1:6" ht="28">
       <c r="A94" s="100" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="B94" s="55" t="s">
+        <v>444</v>
+      </c>
+      <c r="C94" s="50" t="s">
+        <v>541</v>
+      </c>
+      <c r="D94" s="50" t="s">
+        <v>542</v>
+      </c>
+      <c r="E94" s="50" t="s">
         <v>447</v>
       </c>
-      <c r="C94" s="50" t="s">
-        <v>548</v>
-      </c>
-      <c r="D94" s="50" t="s">
-        <v>549</v>
-      </c>
-      <c r="E94" s="50" t="s">
-        <v>450</v>
-      </c>
       <c r="F94" s="115" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="28">
       <c r="A95" s="100" t="s">
+        <v>539</v>
+      </c>
+      <c r="B95" s="55" t="s">
+        <v>449</v>
+      </c>
+      <c r="C95" s="50" t="s">
+        <v>544</v>
+      </c>
+      <c r="D95" s="50" t="s">
+        <v>545</v>
+      </c>
+      <c r="E95" s="50" t="s">
+        <v>452</v>
+      </c>
+      <c r="F95" s="115" t="s">
         <v>546</v>
-      </c>
-      <c r="B95" s="55" t="s">
-        <v>452</v>
-      </c>
-      <c r="C95" s="50" t="s">
-        <v>551</v>
-      </c>
-      <c r="D95" s="50" t="s">
-        <v>552</v>
-      </c>
-      <c r="E95" s="50" t="s">
-        <v>455</v>
-      </c>
-      <c r="F95" s="115" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="28">
       <c r="A96" s="101" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="B96" s="56" t="s">
-        <v>457</v>
-      </c>
-      <c r="C96" s="10" t="s">
-        <v>554</v>
+        <v>454</v>
+      </c>
+      <c r="C96" s="244" t="s">
+        <v>1177</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="F96" s="116" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="28">
       <c r="A97" s="99" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="B97" s="54" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="D97" s="15" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="E97" s="15" t="s">
         <v>192</v>
@@ -16190,79 +15883,79 @@
     </row>
     <row r="98" spans="1:6" ht="28">
       <c r="A98" s="105" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="B98" s="60" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="C98" s="61" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="D98" s="61" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="E98" s="61" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="F98" s="120" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="56">
       <c r="A99" s="105" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="B99" s="60" t="s">
-        <v>1058</v>
+        <v>1032</v>
       </c>
       <c r="C99" s="61" t="s">
-        <v>1055</v>
+        <v>1029</v>
       </c>
       <c r="D99" s="61" t="s">
-        <v>1056</v>
+        <v>1030</v>
       </c>
       <c r="E99" s="61" t="s">
-        <v>1057</v>
+        <v>1031</v>
       </c>
       <c r="F99" s="120" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="28">
       <c r="A100" s="105" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="B100" s="60" t="s">
-        <v>1059</v>
+        <v>1033</v>
       </c>
       <c r="C100" s="61" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="D100" s="61" t="s">
-        <v>1174</v>
+        <v>1145</v>
       </c>
       <c r="E100" s="61" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="F100" s="120" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="28">
       <c r="A101" s="106" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="B101" s="63" t="s">
-        <v>1060</v>
+        <v>1034</v>
       </c>
       <c r="C101" s="20" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="D101" s="20" t="s">
-        <v>1061</v>
+        <v>1035</v>
       </c>
       <c r="E101" s="20" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="F101" s="121" t="s">
         <v>233</v>
@@ -16270,16 +15963,16 @@
     </row>
     <row r="102" spans="1:6" ht="28">
       <c r="A102" s="105" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="B102" s="60" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="C102" s="61" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="D102" s="61" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="E102" s="61" t="s">
         <v>98</v>
@@ -16290,19 +15983,19 @@
     </row>
     <row r="103" spans="1:6" ht="42">
       <c r="A103" s="105" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="B103" s="152" t="s">
-        <v>1180</v>
-      </c>
-      <c r="C103" s="61" t="s">
-        <v>790</v>
+        <v>1151</v>
+      </c>
+      <c r="C103" s="187" t="s">
+        <v>1178</v>
       </c>
       <c r="D103" s="61" t="s">
-        <v>791</v>
+        <v>778</v>
       </c>
       <c r="E103" s="61" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="F103" s="120" t="s">
         <v>233</v>
@@ -16310,59 +16003,59 @@
     </row>
     <row r="104" spans="1:6" ht="154">
       <c r="A104" s="105" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="B104" s="152" t="s">
-        <v>1180</v>
-      </c>
-      <c r="C104" s="61" t="s">
-        <v>900</v>
+        <v>1151</v>
+      </c>
+      <c r="C104" s="187" t="s">
+        <v>1179</v>
       </c>
       <c r="D104" s="61" t="s">
-        <v>901</v>
+        <v>877</v>
       </c>
       <c r="E104" s="61" t="s">
-        <v>902</v>
+        <v>878</v>
       </c>
       <c r="F104" s="120" t="s">
-        <v>903</v>
+        <v>879</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="28">
       <c r="A105" s="109" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="B105" s="65" t="s">
-        <v>574</v>
-      </c>
-      <c r="C105" s="42" t="s">
-        <v>575</v>
+        <v>566</v>
+      </c>
+      <c r="C105" s="249" t="s">
+        <v>1180</v>
       </c>
       <c r="D105" s="42" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="E105" s="42" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="F105" s="124" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="30">
       <c r="A106" s="111" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="B106" s="93" t="s">
-        <v>766</v>
+        <v>754</v>
       </c>
       <c r="C106" s="94" t="s">
-        <v>767</v>
+        <v>755</v>
       </c>
       <c r="D106" s="94" t="s">
-        <v>768</v>
+        <v>756</v>
       </c>
       <c r="E106" s="94" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="F106" s="126" t="s">
         <v>240</v>
@@ -16370,37 +16063,37 @@
     </row>
     <row r="107" spans="1:6" ht="28">
       <c r="A107" s="101" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="B107" s="128" t="s">
-        <v>774</v>
+        <v>762</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>773</v>
+        <v>761</v>
       </c>
       <c r="D107" s="10"/>
       <c r="E107" s="10" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="F107" s="116" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="42">
       <c r="A108" s="102" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="B108" s="154" t="s">
-        <v>774</v>
-      </c>
-      <c r="C108" s="33" t="s">
-        <v>579</v>
+        <v>762</v>
+      </c>
+      <c r="C108" s="246" t="s">
+        <v>1181</v>
       </c>
       <c r="D108" s="33" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="E108" s="33" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F108" s="117" t="s">
         <v>309</v>
@@ -16408,46 +16101,46 @@
     </row>
     <row r="109" spans="1:6" ht="28">
       <c r="A109" s="103" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="B109" s="155" t="s">
-        <v>774</v>
+        <v>762</v>
       </c>
       <c r="C109" s="39" t="s">
-        <v>806</v>
+        <v>791</v>
       </c>
       <c r="D109" s="39" t="s">
-        <v>807</v>
+        <v>792</v>
       </c>
       <c r="E109" s="39" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F109" s="118" t="s">
-        <v>808</v>
+        <v>793</v>
       </c>
     </row>
     <row r="110" spans="1:6">
-      <c r="A110" s="189" t="s">
-        <v>1052</v>
-      </c>
-      <c r="B110" s="190"/>
-      <c r="C110" s="190"/>
-      <c r="D110" s="190"/>
-      <c r="E110" s="190"/>
-      <c r="F110" s="191"/>
+      <c r="A110" s="201" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B110" s="202"/>
+      <c r="C110" s="202"/>
+      <c r="D110" s="202"/>
+      <c r="E110" s="202"/>
+      <c r="F110" s="203"/>
     </row>
     <row r="111" spans="1:6" ht="28">
       <c r="A111" s="101" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="B111" s="56" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>20</v>
@@ -16458,59 +16151,59 @@
     </row>
     <row r="112" spans="1:6" ht="28">
       <c r="A112" s="105" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="B112" s="60" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C112" s="61" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="D112" s="61" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="E112" s="61" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F112" s="120" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="28">
       <c r="A113" s="105" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="B113" s="60" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="C113" s="61" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="D113" s="61" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="E113" s="61" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="F113" s="120" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="28">
       <c r="A114" s="105" t="s">
+        <v>571</v>
+      </c>
+      <c r="B114" s="60" t="s">
+        <v>500</v>
+      </c>
+      <c r="C114" s="61" t="s">
         <v>581</v>
       </c>
-      <c r="B114" s="60" t="s">
-        <v>505</v>
-      </c>
-      <c r="C114" s="61" t="s">
-        <v>591</v>
-      </c>
       <c r="D114" s="61" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="E114" s="61" t="s">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="F114" s="120" t="s">
         <v>313</v>
@@ -16518,39 +16211,39 @@
     </row>
     <row r="115" spans="1:6" ht="56">
       <c r="A115" s="105" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="B115" s="152" t="s">
-        <v>1181</v>
+        <v>1152</v>
       </c>
       <c r="C115" s="61" t="s">
-        <v>786</v>
+        <v>774</v>
       </c>
       <c r="D115" s="61" t="s">
-        <v>787</v>
+        <v>775</v>
       </c>
       <c r="E115" s="61" t="s">
-        <v>788</v>
+        <v>776</v>
       </c>
       <c r="F115" s="120" t="s">
-        <v>789</v>
+        <v>777</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="28">
       <c r="A116" s="98" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="B116" s="53" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>595</v>
+        <v>585</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>597</v>
+        <v>587</v>
       </c>
       <c r="F116" s="86" t="s">
         <v>100</v>
@@ -16558,19 +16251,19 @@
     </row>
     <row r="117" spans="1:6" ht="28">
       <c r="A117" s="102" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="B117" s="57" t="s">
-        <v>1071</v>
+        <v>1045</v>
       </c>
       <c r="C117" s="33" t="s">
-        <v>1053</v>
+        <v>1027</v>
       </c>
       <c r="D117" s="33" t="s">
-        <v>1054</v>
+        <v>1028</v>
       </c>
       <c r="E117" s="33" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="F117" s="117" t="s">
         <v>239</v>
@@ -16578,39 +16271,39 @@
     </row>
     <row r="118" spans="1:6" ht="28">
       <c r="A118" s="105" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="B118" s="60" t="s">
-        <v>1072</v>
+        <v>1046</v>
       </c>
       <c r="C118" s="61" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="D118" s="61" t="s">
-        <v>1135</v>
+        <v>1107</v>
       </c>
       <c r="E118" s="61" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F118" s="120" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="28">
       <c r="A119" s="106" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="B119" s="63" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="C119" s="20" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="D119" s="20" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="E119" s="20" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="F119" s="121" t="s">
         <v>245</v>
@@ -16618,19 +16311,19 @@
     </row>
     <row r="120" spans="1:6" ht="28">
       <c r="A120" s="109" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="B120" s="65" t="s">
-        <v>470</v>
-      </c>
-      <c r="C120" s="42" t="s">
-        <v>604</v>
+        <v>466</v>
+      </c>
+      <c r="C120" s="249" t="s">
+        <v>1182</v>
       </c>
       <c r="D120" s="42" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="E120" s="42" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="F120" s="124" t="s">
         <v>245</v>
@@ -16638,79 +16331,79 @@
     </row>
     <row r="121" spans="1:6" ht="140">
       <c r="A121" s="99" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="B121" s="54" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>881</v>
+        <v>859</v>
       </c>
       <c r="D121" s="15" t="s">
-        <v>882</v>
+        <v>860</v>
       </c>
       <c r="E121" s="15" t="s">
-        <v>883</v>
+        <v>861</v>
       </c>
       <c r="F121" s="85" t="s">
-        <v>884</v>
+        <v>862</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="28">
       <c r="A122" s="103" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="B122" s="58" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="C122" s="39" t="s">
-        <v>609</v>
+        <v>598</v>
       </c>
       <c r="D122" s="39" t="s">
-        <v>610</v>
+        <v>599</v>
       </c>
       <c r="E122" s="39" t="s">
-        <v>611</v>
+        <v>600</v>
       </c>
       <c r="F122" s="118" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="28">
       <c r="A123" s="101" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="B123" s="56" t="s">
-        <v>612</v>
+        <v>601</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>613</v>
+        <v>602</v>
       </c>
       <c r="D123" s="10" t="s">
-        <v>614</v>
+        <v>603</v>
       </c>
       <c r="E123" s="10" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="F123" s="116" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="28">
       <c r="A124" s="103" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="B124" s="58" t="s">
+        <v>434</v>
+      </c>
+      <c r="C124" s="39" t="s">
+        <v>604</v>
+      </c>
+      <c r="D124" s="39" t="s">
+        <v>605</v>
+      </c>
+      <c r="E124" s="39" t="s">
         <v>436</v>
-      </c>
-      <c r="C124" s="39" t="s">
-        <v>615</v>
-      </c>
-      <c r="D124" s="39" t="s">
-        <v>616</v>
-      </c>
-      <c r="E124" s="39" t="s">
-        <v>439</v>
       </c>
       <c r="F124" s="118" t="s">
         <v>301</v>
@@ -16718,89 +16411,89 @@
     </row>
     <row r="125" spans="1:6" ht="28">
       <c r="A125" s="103" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="B125" s="58" t="s">
+        <v>434</v>
+      </c>
+      <c r="C125" s="39" t="s">
+        <v>606</v>
+      </c>
+      <c r="D125" s="39" t="s">
+        <v>607</v>
+      </c>
+      <c r="E125" s="39" t="s">
         <v>436</v>
       </c>
-      <c r="C125" s="39" t="s">
-        <v>617</v>
-      </c>
-      <c r="D125" s="39" t="s">
-        <v>618</v>
-      </c>
-      <c r="E125" s="39" t="s">
-        <v>439</v>
-      </c>
       <c r="F125" s="118" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="238">
       <c r="A126" s="103" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="B126" s="155" t="s">
+        <v>434</v>
+      </c>
+      <c r="C126" s="250" t="s">
+        <v>1183</v>
+      </c>
+      <c r="D126" s="39" t="s">
+        <v>868</v>
+      </c>
+      <c r="E126" s="39" t="s">
+        <v>869</v>
+      </c>
+      <c r="F126" s="118" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="28">
+      <c r="A127" s="104" t="s">
+        <v>571</v>
+      </c>
+      <c r="B127" s="59" t="s">
+        <v>434</v>
+      </c>
+      <c r="C127" s="186" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D127" s="47" t="s">
+        <v>794</v>
+      </c>
+      <c r="E127" s="47" t="s">
         <v>436</v>
       </c>
-      <c r="C126" s="39" t="s">
-        <v>890</v>
-      </c>
-      <c r="D126" s="39" t="s">
-        <v>891</v>
-      </c>
-      <c r="E126" s="39" t="s">
-        <v>892</v>
-      </c>
-      <c r="F126" s="118" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" ht="32">
-      <c r="A127" s="104" t="s">
-        <v>581</v>
-      </c>
-      <c r="B127" s="59" t="s">
-        <v>436</v>
-      </c>
-      <c r="C127" s="47" t="s">
-        <v>809</v>
-      </c>
-      <c r="D127" s="47" t="s">
-        <v>810</v>
-      </c>
-      <c r="E127" s="47" t="s">
-        <v>439</v>
-      </c>
       <c r="F127" s="119" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
     </row>
     <row r="128" spans="1:6">
-      <c r="A128" s="192" t="s">
-        <v>621</v>
-      </c>
-      <c r="B128" s="193"/>
-      <c r="C128" s="193"/>
-      <c r="D128" s="193"/>
-      <c r="E128" s="193"/>
-      <c r="F128" s="194"/>
+      <c r="A128" s="204" t="s">
+        <v>610</v>
+      </c>
+      <c r="B128" s="205"/>
+      <c r="C128" s="205"/>
+      <c r="D128" s="205"/>
+      <c r="E128" s="205"/>
+      <c r="F128" s="206"/>
     </row>
     <row r="129" spans="1:6" ht="28">
       <c r="A129" s="101" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="B129" s="56" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F129" s="116" t="s">
         <v>33</v>
@@ -16808,39 +16501,39 @@
     </row>
     <row r="130" spans="1:6" ht="28">
       <c r="A130" s="100" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="B130" s="55" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="C130" s="50" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="D130" s="50" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="E130" s="50" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="F130" s="115" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
     </row>
     <row r="131" spans="1:6" ht="28">
       <c r="A131" s="100" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="B131" s="55" t="s">
-        <v>629</v>
+        <v>618</v>
       </c>
       <c r="C131" s="50" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="D131" s="50" t="s">
-        <v>631</v>
+        <v>620</v>
       </c>
       <c r="E131" s="50" t="s">
-        <v>632</v>
+        <v>621</v>
       </c>
       <c r="F131" s="115" t="s">
         <v>355</v>
@@ -16848,99 +16541,99 @@
     </row>
     <row r="132" spans="1:6" ht="28">
       <c r="A132" s="100" t="s">
+        <v>611</v>
+      </c>
+      <c r="B132" s="55" t="s">
         <v>622</v>
       </c>
-      <c r="B132" s="55" t="s">
-        <v>633</v>
-      </c>
       <c r="C132" s="50" t="s">
-        <v>634</v>
+        <v>623</v>
       </c>
       <c r="D132" s="50" t="s">
-        <v>635</v>
+        <v>624</v>
       </c>
       <c r="E132" s="50" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="F132" s="115" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
     </row>
     <row r="133" spans="1:6" ht="28">
       <c r="A133" s="99" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="B133" s="54" t="s">
-        <v>638</v>
+        <v>627</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="D133" s="15" t="s">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="E133" s="15" t="s">
         <v>354</v>
       </c>
       <c r="F133" s="85" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
     </row>
     <row r="134" spans="1:6" ht="28">
       <c r="A134" s="98" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="B134" s="53" t="s">
-        <v>641</v>
+        <v>630</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>642</v>
+        <v>631</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>644</v>
+        <v>633</v>
       </c>
       <c r="F134" s="114" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="28">
       <c r="A135" s="99" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="B135" s="54" t="s">
-        <v>645</v>
+        <v>634</v>
       </c>
       <c r="C135" s="15" t="s">
-        <v>646</v>
+        <v>635</v>
       </c>
       <c r="D135" s="15" t="s">
-        <v>647</v>
+        <v>636</v>
       </c>
       <c r="E135" s="15" t="s">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="F135" s="113" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="28">
       <c r="A136" s="98" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="B136" s="53" t="s">
-        <v>649</v>
+        <v>638</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>650</v>
+        <v>639</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>651</v>
+        <v>640</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>652</v>
+        <v>641</v>
       </c>
       <c r="F136" s="114" t="s">
         <v>216</v>
@@ -16948,36 +16641,36 @@
     </row>
     <row r="137" spans="1:6" ht="29" thickBot="1">
       <c r="A137" s="112" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="B137" s="96" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C137" s="97" t="s">
-        <v>653</v>
+        <v>642</v>
       </c>
       <c r="D137" s="97" t="s">
-        <v>654</v>
+        <v>643</v>
       </c>
       <c r="E137" s="97" t="s">
-        <v>655</v>
+        <v>644</v>
       </c>
       <c r="F137" s="127" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="A110:F110"/>
+    <mergeCell ref="A128:F128"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A71:F71"/>
-    <mergeCell ref="A92:F92"/>
-    <mergeCell ref="A110:F110"/>
-    <mergeCell ref="A128:F128"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -17000,22 +16693,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="211" t="s">
-        <v>986</v>
-      </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
+      <c r="A1" s="214" t="s">
+        <v>962</v>
+      </c>
+      <c r="B1" s="214"/>
+      <c r="C1" s="214"/>
+      <c r="D1" s="214"/>
+      <c r="E1" s="214"/>
     </row>
     <row r="3" spans="1:5" ht="24" customHeight="1">
-      <c r="A3" s="212" t="s">
-        <v>1027</v>
-      </c>
-      <c r="B3" s="212"/>
-      <c r="C3" s="212"/>
-      <c r="D3" s="212"/>
-      <c r="E3" s="212"/>
+      <c r="A3" s="215" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B3" s="215"/>
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
+      <c r="E3" s="215"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="12" t="s">
@@ -17039,13 +16732,13 @@
         <v>43</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1028</v>
+        <v>1002</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>1026</v>
+        <v>1000</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>1029</v>
+        <v>1003</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>44</v>
@@ -17090,7 +16783,7 @@
         <v>54</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>866</v>
+        <v>846</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>55</v>
@@ -17107,13 +16800,13 @@
         <v>45</v>
       </c>
       <c r="B9" s="69" t="s">
-        <v>657</v>
+        <v>646</v>
       </c>
       <c r="C9" s="67" t="s">
-        <v>658</v>
+        <v>647</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
       <c r="E9" s="68" t="s">
         <v>162</v>
@@ -17124,13 +16817,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="69" t="s">
-        <v>660</v>
+        <v>649</v>
       </c>
       <c r="C10" s="67" t="s">
         <v>182</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>661</v>
+        <v>650</v>
       </c>
       <c r="E10" s="68" t="s">
         <v>53</v>
@@ -17175,30 +16868,30 @@
         <v>58</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>860</v>
+        <v>840</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>856</v>
+        <v>837</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>861</v>
+        <v>841</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>862</v>
+        <v>842</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="42" customHeight="1">
       <c r="A14" s="20" t="s">
-        <v>863</v>
+        <v>843</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>864</v>
+        <v>844</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>859</v>
+        <v>839</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>865</v>
+        <v>845</v>
       </c>
       <c r="E14" s="23" t="s">
         <v>62</v>
@@ -17206,19 +16899,19 @@
     </row>
     <row r="15" spans="1:5" ht="56" customHeight="1">
       <c r="A15" s="20" t="s">
-        <v>870</v>
+        <v>849</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>871</v>
+        <v>850</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>869</v>
+        <v>848</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>872</v>
+        <v>851</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>873</v>
+        <v>852</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="70" customHeight="1">
@@ -17226,30 +16919,30 @@
         <v>80</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>960</v>
+        <v>936</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>878</v>
+        <v>856</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>879</v>
+        <v>857</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>880</v>
+        <v>858</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="62" customHeight="1">
       <c r="A17" s="20" t="s">
-        <v>926</v>
+        <v>902</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>961</v>
+        <v>937</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>933</v>
+        <v>909</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>934</v>
+        <v>910</v>
       </c>
       <c r="E17" s="23" t="s">
         <v>94</v>
@@ -17260,16 +16953,16 @@
         <v>45</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>962</v>
+        <v>938</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>935</v>
+        <v>911</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>936</v>
+        <v>912</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>927</v>
+        <v>903</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="62" customHeight="1">
@@ -17277,27 +16970,27 @@
         <v>45</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>963</v>
+        <v>939</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>937</v>
+        <v>913</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>938</v>
+        <v>914</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>927</v>
+        <v>903</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="30" customHeight="1"/>
     <row r="21" spans="1:5" ht="30" customHeight="1">
-      <c r="A21" s="208" t="s">
+      <c r="A21" s="211" t="s">
         <v>67</v>
       </c>
-      <c r="B21" s="208"/>
-      <c r="C21" s="208"/>
-      <c r="D21" s="208"/>
-      <c r="E21" s="208"/>
+      <c r="B21" s="211"/>
+      <c r="C21" s="211"/>
+      <c r="D21" s="211"/>
+      <c r="E21" s="211"/>
     </row>
     <row r="22" spans="1:5" ht="30" customHeight="1">
       <c r="A22" s="12" t="s">
@@ -17327,7 +17020,7 @@
         <v>29</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>921</v>
+        <v>897</v>
       </c>
       <c r="E23" s="18" t="s">
         <v>69</v>
@@ -17378,7 +17071,7 @@
         <v>82</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>923</v>
+        <v>899</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>83</v>
@@ -17389,13 +17082,13 @@
         <v>84</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>964</v>
+        <v>940</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>85</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>922</v>
+        <v>898</v>
       </c>
       <c r="E27" s="18" t="s">
         <v>86</v>
@@ -17406,13 +17099,13 @@
         <v>80</v>
       </c>
       <c r="B28" s="66" t="s">
-        <v>662</v>
+        <v>651</v>
       </c>
       <c r="C28" s="67" t="s">
-        <v>663</v>
+        <v>652</v>
       </c>
       <c r="D28" s="66" t="s">
-        <v>664</v>
+        <v>653</v>
       </c>
       <c r="E28" s="68" t="s">
         <v>202</v>
@@ -17440,13 +17133,13 @@
         <v>75</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>928</v>
+        <v>904</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>929</v>
+        <v>905</v>
       </c>
       <c r="E30" s="18" t="s">
         <v>189</v>
@@ -17457,27 +17150,27 @@
         <v>75</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>930</v>
+        <v>906</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>931</v>
+        <v>907</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>932</v>
+        <v>908</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="27.75" customHeight="1"/>
     <row r="33" spans="1:5" ht="30" customHeight="1">
-      <c r="A33" s="210" t="s">
+      <c r="A33" s="213" t="s">
         <v>91</v>
       </c>
-      <c r="B33" s="210"/>
-      <c r="C33" s="210"/>
-      <c r="D33" s="210"/>
-      <c r="E33" s="210"/>
+      <c r="B33" s="213"/>
+      <c r="C33" s="213"/>
+      <c r="D33" s="213"/>
+      <c r="E33" s="213"/>
     </row>
     <row r="34" spans="1:5" ht="30" customHeight="1">
       <c r="A34" s="12" t="s">
@@ -17637,13 +17330,13 @@
         <v>58</v>
       </c>
       <c r="B43" s="73" t="s">
-        <v>665</v>
+        <v>654</v>
       </c>
       <c r="C43" s="71" t="s">
         <v>233</v>
       </c>
       <c r="D43" s="70" t="s">
-        <v>666</v>
+        <v>655</v>
       </c>
       <c r="E43" s="72" t="s">
         <v>90</v>
@@ -17668,33 +17361,33 @@
     </row>
     <row r="45" spans="1:5" ht="140">
       <c r="A45" s="20" t="s">
-        <v>885</v>
+        <v>863</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>886</v>
+        <v>864</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>887</v>
+        <v>865</v>
       </c>
       <c r="D45" s="20" t="s">
-        <v>888</v>
+        <v>866</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>889</v>
+        <v>867</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="154">
       <c r="A46" s="20" t="s">
-        <v>885</v>
+        <v>863</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>904</v>
+        <v>880</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>905</v>
+        <v>881</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>906</v>
+        <v>882</v>
       </c>
       <c r="E46" s="23" t="s">
         <v>167</v>
@@ -17705,13 +17398,13 @@
         <v>58</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>894</v>
+        <v>871</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>895</v>
+        <v>872</v>
       </c>
       <c r="D47" s="20" t="s">
-        <v>896</v>
+        <v>873</v>
       </c>
       <c r="E47" s="23" t="s">
         <v>192</v>
@@ -17722,13 +17415,13 @@
         <v>58</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>897</v>
+        <v>874</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>898</v>
+        <v>875</v>
       </c>
       <c r="D48" s="20" t="s">
-        <v>899</v>
+        <v>876</v>
       </c>
       <c r="E48" s="23" t="s">
         <v>192</v>
@@ -17739,30 +17432,30 @@
         <v>75</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>967</v>
+        <v>943</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>924</v>
+        <v>900</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>925</v>
+        <v>901</v>
       </c>
       <c r="E49" s="23" t="s">
-        <v>920</v>
+        <v>896</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="62" customHeight="1">
       <c r="A50" s="20" t="s">
-        <v>926</v>
+        <v>902</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>943</v>
+        <v>919</v>
       </c>
       <c r="D50" s="20" t="s">
-        <v>944</v>
+        <v>920</v>
       </c>
       <c r="E50" s="23" t="s">
         <v>57</v>
@@ -17773,16 +17466,16 @@
         <v>75</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>969</v>
+        <v>945</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>955</v>
+        <v>931</v>
       </c>
       <c r="D51" s="20" t="s">
-        <v>956</v>
+        <v>932</v>
       </c>
       <c r="E51" s="23" t="s">
-        <v>957</v>
+        <v>933</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="62" customHeight="1"/>
@@ -17815,24 +17508,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18">
-      <c r="A1" s="225" t="s">
-        <v>939</v>
-      </c>
-      <c r="B1" s="226"/>
-      <c r="C1" s="226"/>
-      <c r="D1" s="226"/>
-      <c r="E1" s="226"/>
-      <c r="F1" s="227"/>
+      <c r="A1" s="216" t="s">
+        <v>915</v>
+      </c>
+      <c r="B1" s="217"/>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
+      <c r="F1" s="218"/>
     </row>
     <row r="2" spans="1:6" ht="41" customHeight="1">
-      <c r="A2" s="228" t="s">
-        <v>940</v>
-      </c>
-      <c r="B2" s="229"/>
-      <c r="C2" s="229"/>
-      <c r="D2" s="229"/>
-      <c r="E2" s="229"/>
-      <c r="F2" s="230"/>
+      <c r="A2" s="219" t="s">
+        <v>916</v>
+      </c>
+      <c r="B2" s="220"/>
+      <c r="C2" s="220"/>
+      <c r="D2" s="220"/>
+      <c r="E2" s="220"/>
+      <c r="F2" s="221"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="77" t="s">
@@ -17856,7 +17549,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="222" t="s">
-        <v>1030</v>
+        <v>1004</v>
       </c>
       <c r="B4" s="223"/>
       <c r="C4" s="223"/>
@@ -17872,16 +17565,16 @@
         <v>134</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1031</v>
+        <v>1005</v>
       </c>
       <c r="D5" s="27" t="s">
         <v>135</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>1032</v>
+        <v>1006</v>
       </c>
       <c r="F5" s="84" t="s">
-        <v>1033</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="28">
@@ -17892,16 +17585,16 @@
         <v>137</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>1034</v>
+        <v>1008</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>1035</v>
+        <v>1009</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>1036</v>
+        <v>1010</v>
       </c>
       <c r="F6" s="85" t="s">
-        <v>992</v>
+        <v>968</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28">
@@ -17912,56 +17605,56 @@
         <v>139</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>1037</v>
+        <v>1011</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>53</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>1038</v>
+        <v>1012</v>
       </c>
       <c r="F7" s="86" t="s">
-        <v>1039</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="28">
       <c r="A8" s="81" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="B8" s="75">
         <v>4.5</v>
       </c>
       <c r="C8" s="76" t="s">
-        <v>1040</v>
+        <v>1014</v>
       </c>
       <c r="D8" s="75" t="s">
-        <v>668</v>
+        <v>657</v>
       </c>
       <c r="E8" s="76" t="s">
-        <v>1041</v>
+        <v>1015</v>
       </c>
       <c r="F8" s="87" t="s">
-        <v>1042</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="28">
       <c r="A9" s="82" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="B9" s="68">
         <v>4.5</v>
       </c>
       <c r="C9" s="66" t="s">
-        <v>1043</v>
+        <v>1017</v>
       </c>
       <c r="D9" s="68" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="E9" s="66" t="s">
-        <v>1044</v>
+        <v>1018</v>
       </c>
       <c r="F9" s="88" t="s">
-        <v>1045</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -17988,7 +17681,7 @@
         <v>49</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>852</v>
+        <v>834</v>
       </c>
       <c r="F11" s="84" t="s">
         <v>143</v>
@@ -18036,122 +17729,122 @@
     </row>
     <row r="14" spans="1:6" ht="28">
       <c r="A14" s="81" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="B14" s="75">
         <v>4.8</v>
       </c>
       <c r="C14" s="76" t="s">
-        <v>670</v>
+        <v>659</v>
       </c>
       <c r="D14" s="75" t="s">
         <v>57</v>
       </c>
       <c r="E14" s="76" t="s">
-        <v>671</v>
+        <v>660</v>
       </c>
       <c r="F14" s="87" t="s">
-        <v>672</v>
+        <v>661</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28">
       <c r="A15" s="82" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="B15" s="68">
         <v>4.5999999999999996</v>
       </c>
       <c r="C15" s="66" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D15" s="68" t="s">
         <v>98</v>
       </c>
       <c r="E15" s="66" t="s">
-        <v>702</v>
+        <v>691</v>
       </c>
       <c r="F15" s="88" t="s">
-        <v>703</v>
+        <v>692</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="42">
       <c r="A16" s="82" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="B16" s="165" t="s">
-        <v>846</v>
+        <v>828</v>
       </c>
       <c r="C16" s="66" t="s">
-        <v>847</v>
+        <v>829</v>
       </c>
       <c r="D16" s="68" t="s">
-        <v>668</v>
+        <v>657</v>
       </c>
       <c r="E16" s="66" t="s">
-        <v>848</v>
+        <v>830</v>
       </c>
       <c r="F16" s="88" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="42">
       <c r="A17" s="82" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
       <c r="B17" s="165" t="s">
-        <v>849</v>
+        <v>831</v>
       </c>
       <c r="C17" s="66" t="s">
-        <v>850</v>
+        <v>832</v>
       </c>
       <c r="D17" s="68" t="s">
-        <v>835</v>
+        <v>817</v>
       </c>
       <c r="E17" s="66" t="s">
-        <v>851</v>
+        <v>833</v>
       </c>
       <c r="F17" s="88" t="s">
-        <v>703</v>
+        <v>692</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="56">
       <c r="A18" s="166" t="s">
-        <v>828</v>
+        <v>810</v>
       </c>
       <c r="B18" s="167" t="s">
         <v>216</v>
       </c>
       <c r="C18" s="168" t="s">
-        <v>970</v>
+        <v>946</v>
       </c>
       <c r="D18" s="169" t="s">
-        <v>927</v>
+        <v>903</v>
       </c>
       <c r="E18" s="168" t="s">
-        <v>948</v>
+        <v>924</v>
       </c>
       <c r="F18" s="170" t="s">
-        <v>935</v>
+        <v>911</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="70">
       <c r="A19" s="166" t="s">
-        <v>832</v>
+        <v>814</v>
       </c>
       <c r="B19" s="167" t="s">
         <v>216</v>
       </c>
       <c r="C19" s="168" t="s">
-        <v>971</v>
+        <v>947</v>
       </c>
       <c r="D19" s="169" t="s">
-        <v>927</v>
+        <v>903</v>
       </c>
       <c r="E19" s="168" t="s">
-        <v>949</v>
+        <v>925</v>
       </c>
       <c r="F19" s="170" t="s">
-        <v>937</v>
+        <v>913</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -18172,7 +17865,7 @@
         <v>154</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>941</v>
+        <v>917</v>
       </c>
       <c r="D21" s="27" t="s">
         <v>57</v>
@@ -18232,13 +17925,13 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C24" s="76" t="s">
-        <v>721</v>
+        <v>710</v>
       </c>
       <c r="D24" s="75" t="s">
         <v>218</v>
       </c>
       <c r="E24" s="76" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="F24" s="87" t="s">
         <v>255</v>
@@ -18246,22 +17939,22 @@
     </row>
     <row r="25" spans="1:6" ht="28">
       <c r="A25" s="82" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="B25" s="68">
         <v>4.3</v>
       </c>
       <c r="C25" s="66" t="s">
-        <v>673</v>
+        <v>662</v>
       </c>
       <c r="D25" s="68" t="s">
         <v>218</v>
       </c>
       <c r="E25" s="66" t="s">
-        <v>674</v>
+        <v>663</v>
       </c>
       <c r="F25" s="88" t="s">
-        <v>675</v>
+        <v>664</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -18302,13 +17995,13 @@
         <v>137</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>972</v>
+        <v>948</v>
       </c>
       <c r="D28" s="18" t="s">
         <v>170</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>909</v>
+        <v>885</v>
       </c>
       <c r="F28" s="85" t="s">
         <v>171</v>
@@ -18336,42 +18029,42 @@
     </row>
     <row r="30" spans="1:6" ht="42">
       <c r="A30" s="81" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="B30" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C30" s="76" t="s">
-        <v>973</v>
+        <v>949</v>
       </c>
       <c r="D30" s="75" t="s">
         <v>140</v>
       </c>
       <c r="E30" s="76" t="s">
-        <v>910</v>
+        <v>886</v>
       </c>
       <c r="F30" s="87" t="s">
-        <v>676</v>
+        <v>665</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="28">
       <c r="A31" s="82" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="B31" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C31" s="66" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
       <c r="D31" s="68" t="s">
         <v>192</v>
       </c>
       <c r="E31" s="66" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="F31" s="88" t="s">
-        <v>706</v>
+        <v>695</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -18432,33 +18125,33 @@
         <v>4.3</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>689</v>
+        <v>678</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="F35" s="86" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="42">
       <c r="A36" s="81" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="B36" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C36" s="76" t="s">
-        <v>677</v>
+        <v>666</v>
       </c>
       <c r="D36" s="75" t="s">
         <v>145</v>
       </c>
       <c r="E36" s="76" t="s">
-        <v>678</v>
+        <v>667</v>
       </c>
       <c r="F36" s="87" t="s">
         <v>182</v>
@@ -18466,33 +18159,33 @@
     </row>
     <row r="37" spans="1:6" ht="28">
       <c r="A37" s="82" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="B37" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C37" s="66" t="s">
-        <v>707</v>
+        <v>696</v>
       </c>
       <c r="D37" s="68" t="s">
         <v>53</v>
       </c>
       <c r="E37" s="66" t="s">
-        <v>708</v>
+        <v>697</v>
       </c>
       <c r="F37" s="88" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="219" t="s">
+      <c r="A38" s="225" t="s">
         <v>184</v>
       </c>
-      <c r="B38" s="220"/>
-      <c r="C38" s="220"/>
-      <c r="D38" s="220"/>
-      <c r="E38" s="220"/>
-      <c r="F38" s="221"/>
+      <c r="B38" s="226"/>
+      <c r="C38" s="226"/>
+      <c r="D38" s="226"/>
+      <c r="E38" s="226"/>
+      <c r="F38" s="227"/>
     </row>
     <row r="39" spans="1:6" ht="28">
       <c r="A39" s="78" t="s">
@@ -18502,16 +18195,16 @@
         <v>4.5</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="D39" s="27" t="s">
         <v>192</v>
       </c>
       <c r="E39" s="28" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="F39" s="84" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="42">
@@ -18522,13 +18215,13 @@
         <v>139</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>974</v>
+        <v>950</v>
       </c>
       <c r="D40" s="18" t="s">
         <v>162</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>916</v>
+        <v>892</v>
       </c>
       <c r="F40" s="85" t="s">
         <v>186</v>
@@ -18556,19 +18249,19 @@
     </row>
     <row r="42" spans="1:6" ht="28">
       <c r="A42" s="81" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="B42" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C42" s="76" t="s">
-        <v>679</v>
+        <v>668</v>
       </c>
       <c r="D42" s="75" t="s">
         <v>189</v>
       </c>
       <c r="E42" s="76" t="s">
-        <v>680</v>
+        <v>669</v>
       </c>
       <c r="F42" s="87" t="s">
         <v>82</v>
@@ -18576,33 +18269,33 @@
     </row>
     <row r="43" spans="1:6" ht="28">
       <c r="A43" s="82" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="B43" s="68">
         <v>4.3</v>
       </c>
       <c r="C43" s="66" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="D43" s="68" t="s">
         <v>195</v>
       </c>
       <c r="E43" s="66" t="s">
-        <v>711</v>
+        <v>700</v>
       </c>
       <c r="F43" s="88" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="219" t="s">
+      <c r="A44" s="225" t="s">
         <v>191</v>
       </c>
-      <c r="B44" s="220"/>
-      <c r="C44" s="220"/>
-      <c r="D44" s="220"/>
-      <c r="E44" s="220"/>
-      <c r="F44" s="221"/>
+      <c r="B44" s="226"/>
+      <c r="C44" s="226"/>
+      <c r="D44" s="226"/>
+      <c r="E44" s="226"/>
+      <c r="F44" s="227"/>
     </row>
     <row r="45" spans="1:6" ht="84">
       <c r="A45" s="78" t="s">
@@ -18612,13 +18305,13 @@
         <v>137</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>907</v>
+        <v>883</v>
       </c>
       <c r="D45" s="27" t="s">
         <v>192</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>908</v>
+        <v>884</v>
       </c>
       <c r="F45" s="84" t="s">
         <v>193</v>
@@ -18652,13 +18345,13 @@
         <v>134</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>975</v>
+        <v>951</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>198</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>911</v>
+        <v>887</v>
       </c>
       <c r="F47" s="86" t="s">
         <v>29</v>
@@ -18666,19 +18359,19 @@
     </row>
     <row r="48" spans="1:6" ht="42">
       <c r="A48" s="81" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="B48" s="75">
         <v>4.5</v>
       </c>
       <c r="C48" s="76" t="s">
-        <v>976</v>
+        <v>952</v>
       </c>
       <c r="D48" s="75" t="s">
         <v>79</v>
       </c>
       <c r="E48" s="76" t="s">
-        <v>917</v>
+        <v>893</v>
       </c>
       <c r="F48" s="87" t="s">
         <v>197</v>
@@ -18686,53 +18379,53 @@
     </row>
     <row r="49" spans="1:6" ht="28">
       <c r="A49" s="82" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="B49" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C49" s="66" t="s">
-        <v>681</v>
+        <v>670</v>
       </c>
       <c r="D49" s="68" t="s">
-        <v>682</v>
+        <v>671</v>
       </c>
       <c r="E49" s="66" t="s">
-        <v>683</v>
+        <v>672</v>
       </c>
       <c r="F49" s="88" t="s">
-        <v>684</v>
+        <v>673</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="84">
       <c r="A50" s="166" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="B50" s="169" t="s">
         <v>216</v>
       </c>
       <c r="C50" s="168" t="s">
-        <v>977</v>
+        <v>953</v>
       </c>
       <c r="D50" s="169" t="s">
-        <v>932</v>
+        <v>908</v>
       </c>
       <c r="E50" s="168" t="s">
-        <v>950</v>
+        <v>926</v>
       </c>
       <c r="F50" s="170" t="s">
-        <v>930</v>
+        <v>906</v>
       </c>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="219" t="s">
+      <c r="A51" s="225" t="s">
         <v>199</v>
       </c>
-      <c r="B51" s="220"/>
-      <c r="C51" s="220"/>
-      <c r="D51" s="220"/>
-      <c r="E51" s="220"/>
-      <c r="F51" s="221"/>
+      <c r="B51" s="226"/>
+      <c r="C51" s="226"/>
+      <c r="D51" s="226"/>
+      <c r="E51" s="226"/>
+      <c r="F51" s="227"/>
     </row>
     <row r="52" spans="1:6" ht="56">
       <c r="A52" s="78" t="s">
@@ -18742,13 +18435,13 @@
         <v>187</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>978</v>
+        <v>954</v>
       </c>
       <c r="D52" s="27" t="s">
         <v>140</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>913</v>
+        <v>889</v>
       </c>
       <c r="F52" s="84" t="s">
         <v>200</v>
@@ -18782,87 +18475,87 @@
         <v>4.5</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>725</v>
+        <v>714</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>192</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="F54" s="86" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="28">
       <c r="A55" s="81" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="B55" s="75">
         <v>4.7</v>
       </c>
       <c r="C55" s="76" t="s">
-        <v>685</v>
+        <v>674</v>
       </c>
       <c r="D55" s="75" t="s">
         <v>57</v>
       </c>
       <c r="E55" s="76" t="s">
-        <v>686</v>
+        <v>675</v>
       </c>
       <c r="F55" s="87" t="s">
-        <v>687</v>
+        <v>676</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="28">
       <c r="A56" s="81" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="B56" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C56" s="76" t="s">
-        <v>688</v>
+        <v>677</v>
       </c>
       <c r="D56" s="75" t="s">
-        <v>689</v>
+        <v>678</v>
       </c>
       <c r="E56" s="76" t="s">
-        <v>690</v>
+        <v>679</v>
       </c>
       <c r="F56" s="87" t="s">
-        <v>691</v>
+        <v>680</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="84">
       <c r="A57" s="171" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="B57" s="172" t="s">
         <v>216</v>
       </c>
       <c r="C57" s="173" t="s">
-        <v>979</v>
+        <v>955</v>
       </c>
       <c r="D57" s="172" t="s">
         <v>189</v>
       </c>
       <c r="E57" s="173" t="s">
-        <v>951</v>
+        <v>927</v>
       </c>
       <c r="F57" s="174" t="s">
-        <v>928</v>
+        <v>904</v>
       </c>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="219" t="s">
+      <c r="A58" s="225" t="s">
         <v>205</v>
       </c>
-      <c r="B58" s="220"/>
-      <c r="C58" s="220"/>
-      <c r="D58" s="220"/>
-      <c r="E58" s="220"/>
-      <c r="F58" s="221"/>
+      <c r="B58" s="226"/>
+      <c r="C58" s="226"/>
+      <c r="D58" s="226"/>
+      <c r="E58" s="226"/>
+      <c r="F58" s="227"/>
     </row>
     <row r="59" spans="1:6" ht="28">
       <c r="A59" s="78" t="s">
@@ -18892,13 +18585,13 @@
         <v>134</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>980</v>
+        <v>956</v>
       </c>
       <c r="D60" s="18" t="s">
         <v>198</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>912</v>
+        <v>888</v>
       </c>
       <c r="F60" s="85" t="s">
         <v>29</v>
@@ -18912,13 +18605,13 @@
         <v>139</v>
       </c>
       <c r="C61" s="29" t="s">
-        <v>981</v>
+        <v>957</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>140</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>914</v>
+        <v>890</v>
       </c>
       <c r="F61" s="86" t="s">
         <v>209</v>
@@ -18926,53 +18619,53 @@
     </row>
     <row r="62" spans="1:6" ht="28">
       <c r="A62" s="81" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="B62" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C62" s="74" t="s">
-        <v>712</v>
+        <v>701</v>
       </c>
       <c r="D62" s="75" t="s">
         <v>192</v>
       </c>
       <c r="E62" s="76" t="s">
-        <v>713</v>
+        <v>702</v>
       </c>
       <c r="F62" s="87" t="s">
-        <v>714</v>
+        <v>703</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="28">
       <c r="A63" s="82" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="B63" s="68">
         <v>4.5999999999999996</v>
       </c>
       <c r="C63" s="69" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
       <c r="D63" s="68" t="s">
         <v>44</v>
       </c>
       <c r="E63" s="66" t="s">
-        <v>693</v>
+        <v>682</v>
       </c>
       <c r="F63" s="88" t="s">
-        <v>694</v>
+        <v>683</v>
       </c>
     </row>
     <row r="64" spans="1:6">
-      <c r="A64" s="219" t="s">
+      <c r="A64" s="225" t="s">
         <v>210</v>
       </c>
-      <c r="B64" s="220"/>
-      <c r="C64" s="220"/>
-      <c r="D64" s="220"/>
-      <c r="E64" s="220"/>
-      <c r="F64" s="221"/>
+      <c r="B64" s="226"/>
+      <c r="C64" s="226"/>
+      <c r="D64" s="226"/>
+      <c r="E64" s="226"/>
+      <c r="F64" s="227"/>
     </row>
     <row r="65" spans="1:6" ht="28">
       <c r="A65" s="78" t="s">
@@ -19002,13 +18695,13 @@
         <v>137</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>982</v>
+        <v>958</v>
       </c>
       <c r="D66" s="18" t="s">
         <v>86</v>
       </c>
       <c r="E66" s="25" t="s">
-        <v>915</v>
+        <v>891</v>
       </c>
       <c r="F66" s="85" t="s">
         <v>85</v>
@@ -19035,14 +18728,14 @@
       </c>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="213" t="s">
+      <c r="A68" s="228" t="s">
         <v>221</v>
       </c>
-      <c r="B68" s="214"/>
-      <c r="C68" s="214"/>
-      <c r="D68" s="214"/>
-      <c r="E68" s="214"/>
-      <c r="F68" s="215"/>
+      <c r="B68" s="229"/>
+      <c r="C68" s="229"/>
+      <c r="D68" s="229"/>
+      <c r="E68" s="229"/>
+      <c r="F68" s="230"/>
     </row>
     <row r="69" spans="1:6" ht="70">
       <c r="A69" s="78" t="s">
@@ -19058,7 +18751,7 @@
         <v>102</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>853</v>
+        <v>835</v>
       </c>
       <c r="F69" s="84" t="s">
         <v>100</v>
@@ -19072,13 +18765,13 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>715</v>
+        <v>704</v>
       </c>
       <c r="D70" s="18" t="s">
         <v>195</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="F70" s="85" t="s">
         <v>239</v>
@@ -19106,19 +18799,19 @@
     </row>
     <row r="72" spans="1:6" ht="28">
       <c r="A72" s="81" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="B72" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C72" s="76" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="D72" s="75" t="s">
-        <v>689</v>
+        <v>678</v>
       </c>
       <c r="E72" s="76" t="s">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="F72" s="87" t="s">
         <v>239</v>
@@ -19126,39 +18819,39 @@
     </row>
     <row r="73" spans="1:6" ht="70">
       <c r="A73" s="82" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="B73" s="68">
         <v>4.3</v>
       </c>
       <c r="C73" s="66" t="s">
-        <v>983</v>
+        <v>959</v>
       </c>
       <c r="D73" s="68" t="s">
-        <v>920</v>
+        <v>896</v>
       </c>
       <c r="E73" s="66" t="s">
-        <v>918</v>
+        <v>894</v>
       </c>
       <c r="F73" s="88" t="s">
-        <v>919</v>
+        <v>895</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="28">
       <c r="A74" s="81" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="B74" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C74" s="76" t="s">
-        <v>744</v>
+        <v>733</v>
       </c>
       <c r="D74" s="75" t="s">
         <v>110</v>
       </c>
       <c r="E74" s="76" t="s">
-        <v>745</v>
+        <v>734</v>
       </c>
       <c r="F74" s="87" t="s">
         <v>108</v>
@@ -19166,39 +18859,39 @@
     </row>
     <row r="75" spans="1:6" ht="28">
       <c r="A75" s="82" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
       <c r="B75" s="68">
         <v>4.5</v>
       </c>
       <c r="C75" s="66" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
       <c r="D75" s="68" t="s">
         <v>86</v>
       </c>
       <c r="E75" s="66" t="s">
-        <v>748</v>
+        <v>737</v>
       </c>
       <c r="F75" s="88" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="42">
       <c r="A76" s="82" t="s">
-        <v>828</v>
+        <v>810</v>
       </c>
       <c r="B76" s="165" t="s">
-        <v>838</v>
+        <v>820</v>
       </c>
       <c r="C76" s="66" t="s">
-        <v>839</v>
+        <v>821</v>
       </c>
       <c r="D76" s="68" t="s">
-        <v>840</v>
+        <v>822</v>
       </c>
       <c r="E76" s="66" t="s">
-        <v>841</v>
+        <v>823</v>
       </c>
       <c r="F76" s="88" t="s">
         <v>245</v>
@@ -19206,33 +18899,33 @@
     </row>
     <row r="77" spans="1:6" ht="42">
       <c r="A77" s="82" t="s">
-        <v>832</v>
+        <v>814</v>
       </c>
       <c r="B77" s="165" t="s">
-        <v>842</v>
+        <v>824</v>
       </c>
       <c r="C77" s="66" t="s">
-        <v>843</v>
+        <v>825</v>
       </c>
       <c r="D77" s="68" t="s">
-        <v>835</v>
+        <v>817</v>
       </c>
       <c r="E77" s="66" t="s">
-        <v>844</v>
+        <v>826</v>
       </c>
       <c r="F77" s="88" t="s">
-        <v>845</v>
+        <v>827</v>
       </c>
     </row>
     <row r="78" spans="1:6">
-      <c r="A78" s="213" t="s">
+      <c r="A78" s="228" t="s">
         <v>227</v>
       </c>
-      <c r="B78" s="214"/>
-      <c r="C78" s="214"/>
-      <c r="D78" s="214"/>
-      <c r="E78" s="214"/>
-      <c r="F78" s="215"/>
+      <c r="B78" s="229"/>
+      <c r="C78" s="229"/>
+      <c r="D78" s="229"/>
+      <c r="E78" s="229"/>
+      <c r="F78" s="230"/>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="78" t="s">
@@ -19296,19 +18989,19 @@
     </row>
     <row r="82" spans="1:6" ht="28">
       <c r="A82" s="81" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="B82" s="75">
         <v>4.3</v>
       </c>
       <c r="C82" s="76" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="D82" s="75" t="s">
         <v>192</v>
       </c>
       <c r="E82" s="76" t="s">
-        <v>729</v>
+        <v>718</v>
       </c>
       <c r="F82" s="87" t="s">
         <v>233</v>
@@ -19316,19 +19009,19 @@
     </row>
     <row r="83" spans="1:6" ht="28">
       <c r="A83" s="82" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="B83" s="68">
         <v>4</v>
       </c>
       <c r="C83" s="66" t="s">
-        <v>696</v>
+        <v>685</v>
       </c>
       <c r="D83" s="68" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="E83" s="66" t="s">
-        <v>698</v>
+        <v>687</v>
       </c>
       <c r="F83" s="88" t="s">
         <v>233</v>
@@ -19336,22 +19029,22 @@
     </row>
     <row r="84" spans="1:6" ht="70">
       <c r="A84" s="161" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="B84" s="162">
         <v>4.5999999999999996</v>
       </c>
       <c r="C84" s="163" t="s">
-        <v>945</v>
+        <v>921</v>
       </c>
       <c r="D84" s="162" t="s">
         <v>167</v>
       </c>
       <c r="E84" s="163" t="s">
-        <v>946</v>
+        <v>922</v>
       </c>
       <c r="F84" s="164" t="s">
-        <v>947</v>
+        <v>923</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="140">
@@ -19362,27 +19055,27 @@
         <v>4.8</v>
       </c>
       <c r="C85" s="181" t="s">
-        <v>984</v>
+        <v>960</v>
       </c>
       <c r="D85" s="180" t="s">
         <v>57</v>
       </c>
       <c r="E85" s="181" t="s">
-        <v>952</v>
+        <v>928</v>
       </c>
       <c r="F85" s="182" t="s">
-        <v>942</v>
+        <v>918</v>
       </c>
     </row>
     <row r="86" spans="1:6">
-      <c r="A86" s="213" t="s">
+      <c r="A86" s="228" t="s">
         <v>235</v>
       </c>
-      <c r="B86" s="214"/>
-      <c r="C86" s="214"/>
-      <c r="D86" s="214"/>
-      <c r="E86" s="214"/>
-      <c r="F86" s="215"/>
+      <c r="B86" s="229"/>
+      <c r="C86" s="229"/>
+      <c r="D86" s="229"/>
+      <c r="E86" s="229"/>
+      <c r="F86" s="230"/>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="78" t="s">
@@ -19412,13 +19105,13 @@
         <v>4.2</v>
       </c>
       <c r="C88" s="16" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="D88" s="18" t="s">
         <v>106</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="F88" s="85" t="s">
         <v>239</v>
@@ -19432,13 +19125,13 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>192</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>735</v>
+        <v>724</v>
       </c>
       <c r="F89" s="86" t="s">
         <v>239</v>
@@ -19446,19 +19139,19 @@
     </row>
     <row r="90" spans="1:6" ht="28">
       <c r="A90" s="81" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="B90" s="75">
         <v>4.3</v>
       </c>
       <c r="C90" s="76" t="s">
-        <v>695</v>
+        <v>684</v>
       </c>
       <c r="D90" s="75" t="s">
         <v>106</v>
       </c>
       <c r="E90" s="76" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="F90" s="87" t="s">
         <v>239</v>
@@ -19466,19 +19159,19 @@
     </row>
     <row r="91" spans="1:6" ht="28">
       <c r="A91" s="82" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="B91" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C91" s="66" t="s">
-        <v>736</v>
+        <v>725</v>
       </c>
       <c r="D91" s="68" t="s">
-        <v>737</v>
+        <v>726</v>
       </c>
       <c r="E91" s="66" t="s">
-        <v>738</v>
+        <v>727</v>
       </c>
       <c r="F91" s="88" t="s">
         <v>245</v>
@@ -19486,19 +19179,19 @@
     </row>
     <row r="92" spans="1:6" ht="28">
       <c r="A92" s="81" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="B92" s="75">
         <v>4.5999999999999996</v>
       </c>
       <c r="C92" s="76" t="s">
-        <v>750</v>
+        <v>739</v>
       </c>
       <c r="D92" s="75" t="s">
         <v>115</v>
       </c>
       <c r="E92" s="76" t="s">
-        <v>751</v>
+        <v>740</v>
       </c>
       <c r="F92" s="87" t="s">
         <v>239</v>
@@ -19506,19 +19199,19 @@
     </row>
     <row r="93" spans="1:6" ht="28">
       <c r="A93" s="166" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
       <c r="B93" s="169" t="s">
         <v>216</v>
       </c>
       <c r="C93" s="168" t="s">
-        <v>752</v>
+        <v>741</v>
       </c>
       <c r="D93" s="169" t="s">
         <v>246</v>
       </c>
       <c r="E93" s="168" t="s">
-        <v>753</v>
+        <v>742</v>
       </c>
       <c r="F93" s="170" t="s">
         <v>100</v>
@@ -19526,19 +19219,19 @@
     </row>
     <row r="94" spans="1:6" ht="42">
       <c r="A94" s="82" t="s">
-        <v>828</v>
+        <v>810</v>
       </c>
       <c r="B94" s="165" t="s">
-        <v>829</v>
+        <v>811</v>
       </c>
       <c r="C94" s="66" t="s">
-        <v>830</v>
+        <v>812</v>
       </c>
       <c r="D94" s="68" t="s">
         <v>167</v>
       </c>
       <c r="E94" s="66" t="s">
-        <v>831</v>
+        <v>813</v>
       </c>
       <c r="F94" s="88" t="s">
         <v>226</v>
@@ -19546,53 +19239,53 @@
     </row>
     <row r="95" spans="1:6" ht="42">
       <c r="A95" s="82" t="s">
-        <v>832</v>
+        <v>814</v>
       </c>
       <c r="B95" s="165" t="s">
-        <v>833</v>
+        <v>815</v>
       </c>
       <c r="C95" s="66" t="s">
-        <v>834</v>
+        <v>816</v>
       </c>
       <c r="D95" s="68" t="s">
-        <v>835</v>
+        <v>817</v>
       </c>
       <c r="E95" s="66" t="s">
-        <v>836</v>
+        <v>818</v>
       </c>
       <c r="F95" s="88" t="s">
-        <v>837</v>
+        <v>819</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="70">
       <c r="A96" s="82" t="s">
-        <v>958</v>
+        <v>934</v>
       </c>
       <c r="B96" s="184">
         <v>4.5</v>
       </c>
       <c r="C96" s="66" t="s">
-        <v>985</v>
+        <v>961</v>
       </c>
       <c r="D96" s="68" t="s">
         <v>145</v>
       </c>
       <c r="E96" s="66" t="s">
-        <v>959</v>
+        <v>935</v>
       </c>
       <c r="F96" s="88" t="s">
-        <v>955</v>
+        <v>931</v>
       </c>
     </row>
     <row r="97" spans="1:6">
-      <c r="A97" s="213" t="s">
+      <c r="A97" s="228" t="s">
         <v>241</v>
       </c>
-      <c r="B97" s="214"/>
-      <c r="C97" s="214"/>
-      <c r="D97" s="214"/>
-      <c r="E97" s="214"/>
-      <c r="F97" s="215"/>
+      <c r="B97" s="229"/>
+      <c r="C97" s="229"/>
+      <c r="D97" s="229"/>
+      <c r="E97" s="229"/>
+      <c r="F97" s="230"/>
     </row>
     <row r="98" spans="1:6" ht="84">
       <c r="A98" s="78" t="s">
@@ -19602,13 +19295,13 @@
         <v>5</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>953</v>
+        <v>929</v>
       </c>
       <c r="D98" s="27" t="s">
         <v>57</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>954</v>
+        <v>930</v>
       </c>
       <c r="F98" s="84" t="s">
         <v>242</v>
@@ -19642,60 +19335,50 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C100" s="76" t="s">
-        <v>739</v>
+        <v>728</v>
       </c>
       <c r="D100" s="75" t="s">
-        <v>740</v>
+        <v>729</v>
       </c>
       <c r="E100" s="76" t="s">
-        <v>741</v>
+        <v>730</v>
       </c>
       <c r="F100" s="87" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="28">
       <c r="A101" s="82" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="B101" s="68">
         <v>4.5</v>
       </c>
       <c r="C101" s="66" t="s">
-        <v>699</v>
+        <v>688</v>
       </c>
       <c r="D101" s="68" t="s">
         <v>106</v>
       </c>
       <c r="E101" s="66" t="s">
-        <v>700</v>
+        <v>689</v>
       </c>
       <c r="F101" s="88" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="68" customHeight="1" thickBot="1">
-      <c r="A102" s="216" t="s">
-        <v>987</v>
-      </c>
-      <c r="B102" s="217"/>
-      <c r="C102" s="217"/>
-      <c r="D102" s="217"/>
-      <c r="E102" s="217"/>
-      <c r="F102" s="218"/>
+      <c r="A102" s="231" t="s">
+        <v>963</v>
+      </c>
+      <c r="B102" s="232"/>
+      <c r="C102" s="232"/>
+      <c r="D102" s="232"/>
+      <c r="E102" s="232"/>
+      <c r="F102" s="233"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A44:F44"/>
-    <mergeCell ref="A51:F51"/>
     <mergeCell ref="A97:F97"/>
     <mergeCell ref="A102:F102"/>
     <mergeCell ref="A58:F58"/>
@@ -19703,6 +19386,16 @@
     <mergeCell ref="A68:F68"/>
     <mergeCell ref="A78:F78"/>
     <mergeCell ref="A86:F86"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -19724,12 +19417,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1">
-      <c r="A1" s="195" t="s">
+      <c r="A1" s="189" t="s">
         <v>247</v>
       </c>
-      <c r="B1" s="196"/>
-      <c r="C1" s="196"/>
-      <c r="D1" s="197"/>
+      <c r="B1" s="190"/>
+      <c r="C1" s="190"/>
+      <c r="D1" s="191"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="132"/>
@@ -19738,12 +19431,12 @@
       <c r="D2" s="142"/>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
-      <c r="A3" s="231" t="s">
+      <c r="A3" s="234" t="s">
         <v>248</v>
       </c>
-      <c r="B3" s="232"/>
-      <c r="C3" s="232"/>
-      <c r="D3" s="233"/>
+      <c r="B3" s="235"/>
+      <c r="C3" s="235"/>
+      <c r="D3" s="236"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="133" t="s">
@@ -19764,13 +19457,13 @@
         <v>252</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>1046</v>
+        <v>1020</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>1047</v>
+        <v>1021</v>
       </c>
       <c r="D5" s="144" t="s">
-        <v>1048</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="27.75" customHeight="1">
@@ -19806,7 +19499,7 @@
         <v>261</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>866</v>
+        <v>846</v>
       </c>
       <c r="C8" s="41" t="s">
         <v>262</v>
@@ -19831,16 +19524,16 @@
     </row>
     <row r="10" spans="1:4" ht="45" customHeight="1">
       <c r="A10" s="138" t="s">
-        <v>778</v>
+        <v>766</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>1073</v>
+        <v>1047</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>1074</v>
+        <v>1048</v>
       </c>
       <c r="D10" s="148" t="s">
-        <v>1075</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="45" customHeight="1">
@@ -19848,13 +19541,13 @@
         <v>264</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>1076</v>
+        <v>1050</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>1077</v>
+        <v>1051</v>
       </c>
       <c r="D11" s="148" t="s">
-        <v>1078</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="45" customHeight="1">
@@ -19862,13 +19555,13 @@
         <v>253</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>1079</v>
+        <v>1053</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>1080</v>
+        <v>1054</v>
       </c>
       <c r="D12" s="148" t="s">
-        <v>1081</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="45" customHeight="1">
@@ -19876,13 +19569,13 @@
         <v>288</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>1082</v>
+        <v>1056</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>1083</v>
+        <v>1057</v>
       </c>
       <c r="D13" s="148" t="s">
-        <v>1084</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1">
@@ -19892,12 +19585,12 @@
       <c r="D14" s="142"/>
     </row>
     <row r="15" spans="1:4" ht="16">
-      <c r="A15" s="234" t="s">
+      <c r="A15" s="237" t="s">
         <v>268</v>
       </c>
-      <c r="B15" s="235"/>
-      <c r="C15" s="235"/>
-      <c r="D15" s="236"/>
+      <c r="B15" s="238"/>
+      <c r="C15" s="238"/>
+      <c r="D15" s="239"/>
     </row>
     <row r="16" spans="1:4" ht="24" customHeight="1">
       <c r="A16" s="133" t="s">
@@ -19924,7 +19617,7 @@
         <v>270</v>
       </c>
       <c r="D17" s="185" t="s">
-        <v>1109</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1">
@@ -19988,27 +19681,27 @@
         <v>277</v>
       </c>
       <c r="B22" s="92" t="s">
-        <v>775</v>
+        <v>763</v>
       </c>
       <c r="C22" s="92" t="s">
-        <v>776</v>
+        <v>764</v>
       </c>
       <c r="D22" s="125" t="s">
-        <v>777</v>
+        <v>765</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="30" customHeight="1">
       <c r="A23" s="140" t="s">
-        <v>778</v>
+        <v>766</v>
       </c>
       <c r="B23" s="90" t="s">
-        <v>779</v>
+        <v>767</v>
       </c>
       <c r="C23" s="90" t="s">
-        <v>780</v>
+        <v>768</v>
       </c>
       <c r="D23" s="149" t="s">
-        <v>781</v>
+        <v>769</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="30" customHeight="1">
@@ -20027,30 +19720,30 @@
     </row>
     <row r="25" spans="1:4" ht="70">
       <c r="A25" s="138" t="s">
-        <v>1085</v>
+        <v>1059</v>
       </c>
       <c r="B25" s="43" t="s">
-        <v>1086</v>
+        <v>1060</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>1087</v>
+        <v>1061</v>
       </c>
       <c r="D25" s="148" t="s">
-        <v>1088</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="45" customHeight="1">
       <c r="A26" s="138" t="s">
-        <v>1089</v>
+        <v>1063</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>1090</v>
+        <v>1064</v>
       </c>
       <c r="C26" s="44" t="s">
-        <v>1091</v>
+        <v>1065</v>
       </c>
       <c r="D26" s="148" t="s">
-        <v>1092</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="45" customHeight="1">
@@ -20058,13 +19751,13 @@
         <v>253</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>1093</v>
+        <v>1067</v>
       </c>
       <c r="C27" s="44" t="s">
-        <v>1094</v>
+        <v>1068</v>
       </c>
       <c r="D27" s="148" t="s">
-        <v>1095</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="45" customHeight="1">
@@ -20072,13 +19765,13 @@
         <v>252</v>
       </c>
       <c r="B28" s="43" t="s">
-        <v>1096</v>
+        <v>1070</v>
       </c>
       <c r="C28" s="44" t="s">
-        <v>1097</v>
+        <v>1071</v>
       </c>
       <c r="D28" s="148" t="s">
-        <v>1098</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="30" customHeight="1">
@@ -20116,12 +19809,12 @@
       <c r="D31" s="142"/>
     </row>
     <row r="32" spans="1:4" ht="30" customHeight="1">
-      <c r="A32" s="237" t="s">
+      <c r="A32" s="240" t="s">
         <v>295</v>
       </c>
-      <c r="B32" s="238"/>
-      <c r="C32" s="238"/>
-      <c r="D32" s="239"/>
+      <c r="B32" s="241"/>
+      <c r="C32" s="241"/>
+      <c r="D32" s="242"/>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="133" t="s">
@@ -20209,16 +19902,16 @@
     </row>
     <row r="39" spans="1:4" ht="45" customHeight="1">
       <c r="A39" s="138" t="s">
-        <v>778</v>
+        <v>766</v>
       </c>
       <c r="B39" s="43" t="s">
-        <v>1099</v>
+        <v>1073</v>
       </c>
       <c r="C39" s="44" t="s">
-        <v>1100</v>
+        <v>1074</v>
       </c>
       <c r="D39" s="148" t="s">
-        <v>1101</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="45" customHeight="1">
@@ -20226,27 +19919,27 @@
         <v>257</v>
       </c>
       <c r="B40" s="43" t="s">
-        <v>1102</v>
+        <v>1076</v>
       </c>
       <c r="C40" s="44" t="s">
-        <v>1103</v>
+        <v>1077</v>
       </c>
       <c r="D40" s="148" t="s">
-        <v>1104</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="45" customHeight="1">
       <c r="A41" s="138" t="s">
-        <v>1105</v>
+        <v>1079</v>
       </c>
       <c r="B41" s="43" t="s">
-        <v>1108</v>
+        <v>1082</v>
       </c>
       <c r="C41" s="44" t="s">
-        <v>1106</v>
+        <v>1080</v>
       </c>
       <c r="D41" s="148" t="s">
-        <v>1107</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="27.75" customHeight="1">
@@ -20320,20 +20013,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1">
-      <c r="A1" s="240" t="s">
+      <c r="A1" s="243" t="s">
         <v>318</v>
       </c>
-      <c r="B1" s="240"/>
-      <c r="C1" s="240"/>
-      <c r="D1" s="240"/>
+      <c r="B1" s="243"/>
+      <c r="C1" s="243"/>
+      <c r="D1" s="243"/>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
-      <c r="A3" s="212" t="s">
+      <c r="A3" s="215" t="s">
         <v>248</v>
       </c>
-      <c r="B3" s="212"/>
-      <c r="C3" s="212"/>
-      <c r="D3" s="212"/>
+      <c r="B3" s="215"/>
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="12" t="s">
@@ -20392,12 +20085,12 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="24" customHeight="1">
-      <c r="A9" s="208" t="s">
+      <c r="A9" s="211" t="s">
         <v>268</v>
       </c>
-      <c r="B9" s="208"/>
-      <c r="C9" s="208"/>
-      <c r="D9" s="208"/>
+      <c r="B9" s="211"/>
+      <c r="C9" s="211"/>
+      <c r="D9" s="211"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="12" t="s">
@@ -20442,12 +20135,12 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="24" customHeight="1">
-      <c r="A14" s="210" t="s">
+      <c r="A14" s="213" t="s">
         <v>295</v>
       </c>
-      <c r="B14" s="210"/>
-      <c r="C14" s="210"/>
-      <c r="D14" s="210"/>
+      <c r="B14" s="213"/>
+      <c r="C14" s="213"/>
+      <c r="D14" s="213"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="12" t="s">

--- a/tools/itinerary.xlsx
+++ b/tools/itinerary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jitwei/Library/Mobile Documents/com~apple~CloudDocs/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE36E23-A76B-D646-8DAC-73056FB8A442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D7B613-D649-E941-BCE2-95BB534206AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="17020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1725" uniqueCount="1185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1752" uniqueCount="1210">
   <si>
     <r>
       <rPr>
@@ -6248,9 +6248,6 @@
     <t>西湖区苏堤</t>
   </si>
   <si>
-    <t>11:15–12:15</t>
-  </si>
-  <si>
     <t>Coffee — % Arabica lakeside</t>
   </si>
   <si>
@@ -6746,9 +6743,6 @@
     <t>拱墅区运河码头</t>
   </si>
   <si>
-    <t>18:30–19:45</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -7147,47 +7141,6 @@
     <t>13:00–14:00</t>
   </si>
   <si>
-    <t>Lunch — first Nanjing duck</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">盐水鸭 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&amp; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鸭血粉丝汤 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Nanjing Da Pai Dang downstairs in Deji).</t>
-    </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -7220,35 +7173,6 @@
     <t>Entry ¥50</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Coffee — Ink Coffee </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>新街口</t>
-    </r>
-  </si>
-  <si>
-    <t>Nanjing's best-rated specialty spot.</t>
-  </si>
-  <si>
-    <t>Ink Coffee</t>
-  </si>
-  <si>
-    <t>秦淮区新街口</t>
-  </si>
-  <si>
     <t>16:45–17:45</t>
   </si>
   <si>
@@ -7581,9 +7505,6 @@
       </rPr>
       <t>号</t>
     </r>
-  </si>
-  <si>
-    <t>20:45</t>
   </si>
   <si>
     <r>
@@ -7688,69 +7609,178 @@
     </r>
   </si>
   <si>
-    <t>09:00–10:00</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">MUST-SEE: Sun Yat-sen Mausoleum </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>中山陵</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">① 钟山风景区 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>east cluster. The 392-step stairway.</t>
-    </r>
-  </si>
-  <si>
-    <t>Free · book</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>玄武区石象路</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>7</t>
+    <t>玄武区紫金山明孝陵</t>
+  </si>
+  <si>
+    <t>11:45–12:15</t>
+  </si>
+  <si>
+    <t>玄武区明孝陵</t>
+  </si>
+  <si>
+    <t>¥50–90</t>
+  </si>
+  <si>
+    <t>玄武区</t>
+  </si>
+  <si>
+    <t>Opt · Free</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Optional day-trip: Niushou Mtn </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>牛首山 佛顶宫</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Viral opulent modern Buddhist palace, far south (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>江宁</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">). Needs ~half day — swap the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>玄武</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鸡鸣寺 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>block.</t>
+    </r>
+  </si>
+  <si>
+    <t>江宁区宁丹大道</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Optional: Hongshan Forest Zoo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>红山森林动物园</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">No-cage native-habitat zoo (north) — capybara </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">水豚 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>&amp; red panda. Half-day, family-friendly.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>玄武区和燕路</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>168</t>
     </r>
     <r>
       <rPr>
@@ -7761,700 +7791,6 @@
       </rPr>
       <t>号</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Optional: Music Platform </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>音乐台</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Beside </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中山陵 — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">semicircular stage where white pigeons </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">白鸽 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>gather &amp; swirl. Iconic photo.</t>
-    </r>
-  </si>
-  <si>
-    <t>Opt · ¥10</t>
-  </si>
-  <si>
-    <t>玄武区中山陵音乐台</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">MUST-SEE + 🍁: Ming Xiaoling Sacred Way </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>石象路</t>
-    </r>
-  </si>
-  <si>
-    <t>Same hill — '600m most beautiful autumn avenue'. Peak foliage!</t>
-  </si>
-  <si>
-    <t>Entry ¥70</t>
-  </si>
-  <si>
-    <t>玄武区紫金山明孝陵</t>
-  </si>
-  <si>
-    <t>11:45–12:15</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">MUST-SEE: Ming Xiaoling tomb </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>明孝陵</t>
-    </r>
-  </si>
-  <si>
-    <t>UNESCO Ming founding-emperor tomb.</t>
-  </si>
-  <si>
-    <t>(incl.)</t>
-  </si>
-  <si>
-    <t>玄武区明孝陵</t>
-  </si>
-  <si>
-    <t>12:15–13:15</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Lunch — Purple Mtn foot / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">玄武 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>area</t>
-    </r>
-  </si>
-  <si>
-    <t>Casual lunch heading west off the mountain.</t>
-  </si>
-  <si>
-    <t>¥50–90</t>
-  </si>
-  <si>
-    <t>玄武区</t>
-  </si>
-  <si>
-    <t>13:30–14:30</t>
-  </si>
-  <si>
-    <t>Opt · Free</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Optional: Jiming Temple </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鸡鸣寺 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">&amp; Taicheng wall </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>台城</t>
-    </r>
-  </si>
-  <si>
-    <t>Opt · ¥10+¥30</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>玄武区鸡鸣寺路</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>号</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Optional: Xuanwu Lake </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>玄武湖 十里长堤</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>玄武区玄武巷</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>号</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Coffee — Sculpting in Time </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">雕刻时光 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(Gulou </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>鼓楼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>Wind-down latte on the way back.</t>
-  </si>
-  <si>
-    <t>Café</t>
-  </si>
-  <si>
-    <t>鼓楼区</t>
-  </si>
-  <si>
-    <t>17:15–18:15</t>
-  </si>
-  <si>
-    <t>② Back to CENTRE — your hotel. Flagships; Deji Art Museum; themed washrooms.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Xinjiekou </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>新街口</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Dinner — Nanjing Impressions </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南京大牌档 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(Shiziqiao </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>狮子桥</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>Duck feast + folk music, north of Xinjiekou.</t>
-  </si>
-  <si>
-    <t>19:45–20:45</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Skyline drinks at your hotel's 62F, OR </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">紫峰 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">deck, OR café-hop </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>王府大街</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Pack for Suzhou </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>苏州</t>
-    </r>
-  </si>
-  <si>
-    <t>Move to Suzhou tomorrow.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Optional day-trip: Niushou Mtn </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>牛首山 佛顶宫</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Viral opulent modern Buddhist palace, far south (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>江宁</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">). Needs ~half day — swap the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>玄武</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鸡鸣寺 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>block.</t>
-    </r>
-  </si>
-  <si>
-    <t>江宁区宁丹大道</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Optional: Hongshan Forest Zoo </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>红山森林动物园</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">No-cage native-habitat zoo (north) — capybara </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">水豚 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>&amp; red panda. Half-day, family-friendly.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>玄武区和燕路</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>168</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>号</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Optional stroll: Yihe Road </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>颐和路</t>
-    </r>
-  </si>
-  <si>
-    <t>1930s plane-tree villa streets near Gulou — atmospheric photo walk if time allows.</t>
   </si>
   <si>
     <t>鼓楼区颐和路</t>
@@ -10759,21 +10095,6 @@
     <t>秦淮区中华门外雨花路1号</t>
   </si>
   <si>
-    <t>10:00–10:30</t>
-  </si>
-  <si>
-    <t>Optional: Meiling Palace 美龄宫</t>
-  </si>
-  <si>
-    <t>On the 钟山 combo ticket you already hold — the '梧桐项链' plane-tree necklace view; Republic-era villa. Between 中山陵 and 石象路.</t>
-  </si>
-  <si>
-    <t>Opt · (incl. 联票)</t>
-  </si>
-  <si>
-    <t>玄武区石象路7号 (钟山)</t>
-  </si>
-  <si>
     <t>One of the world's most beautiful bookstores' — built in an underground car park. Major 打卡 spot; pairs with 颐和路 (both on 广州路/鼓楼). Go before noon at weekends.</t>
   </si>
   <si>
@@ -10801,9 +10122,6 @@
     <t>20:50–21:30</t>
   </si>
   <si>
-    <t>10:35–11:10</t>
-  </si>
-  <si>
     <t>Return to Ritz-Carlton 丽思 (~10 min from 山塘街)</t>
   </si>
   <si>
@@ -10865,9 +10183,6 @@
   </si>
   <si>
     <t>建邺区江山大街 (南京眼/鱼嘴)</t>
-  </si>
-  <si>
-    <t>Restored Qing block just S of 新街口 — 甘熙故居, indie shops, night market &amp; 打卡 lanes. Much closer to the Ritz than 老门东.</t>
   </si>
   <si>
     <t>秦淮区升州路 (熙南里)</t>
@@ -11125,12 +10440,6 @@
     <t>DIANPING #11 杭帮菜 (评分 77) — top-12 ranking at under half 楼外楼's price; old-school 杭帮菜</t>
   </si>
   <si>
-    <t>1848 lakeside icon; vinegar fish, Dongpo pork. ⚠️ NOT in the 2026 Dianping 杭帮菜 top-16 — famous &amp; scenic, but locals rank it below its reputation. See ⑥⑦ below.</t>
-  </si>
-  <si>
-    <t>250-yr-old; squirrel mandarin fish. 1,350+ reviews. ⚠️ Ranks LAST (评分 65) among 2026 Dianping 苏帮菜 entries while being the priciest — go for the heritage dish, not value. See ⑧⑨ below.</t>
-  </si>
-  <si>
     <t>Opt · ~¥53pp</t>
   </si>
   <si>
@@ -11146,9 +10455,6 @@
     <t>羽和铃 Feather Bell (Day 2 · Opt)</t>
   </si>
   <si>
-    <t>Courtyard café at the foot of Wushan 吴山, steps up from Hefang St. Hand-brew Ethiopia, plum soda 梅子露, scones &amp; chiffon cake. Verified on Dianping.</t>
-  </si>
-  <si>
     <t>¥45–60</t>
   </si>
   <si>
@@ -11158,9 +10464,6 @@
     <t>夏序 SASU Gelato (Day 2 · Opt)</t>
   </si>
   <si>
-    <t>Reviewers call it Hangzhou's best Italian gelato — pistachio, matcha, chocolate. ~5 min from Hefang St; little queuing off-peak. Verified on Dianping.</t>
-  </si>
-  <si>
     <t>宫宴 Gongyan Palace Banquet (Day 3)</t>
   </si>
   <si>
@@ -11182,9 +10485,6 @@
     <t>¥50–120</t>
   </si>
   <si>
-    <t>MICHELIN Bib Gourmand 必比登 3 years running — Hangzhou's most famous pan-fried dumplings 煎饺, ~¥1 each (5 for ¥5). Thin skin, crisp golden base, juicy pork. Verified on Dianping: ~¥17pp, opens 06:00. Queues form early — go before 08:00. Located at the 南宋御街 archway, ~10 min walk from 清河坊/吴山. Also: 鲜肉小馄饨, 葱油拌面, 咸豆花, 现磨豆浆.</t>
-  </si>
-  <si>
     <t>Opt · ~¥17pp · 06:00开</t>
   </si>
   <si>
@@ -11194,9 +10494,6 @@
     <t>上城区中山南路479号 (吴山广场/河坊街)</t>
   </si>
   <si>
-    <t>MICHELIN Bib Gourmand 必比登 3 yrs running. Founder 泮芳春 has run it 18+ yrs. Signature 煎饺 ~¥1 each — thin skin, crisp base, juicy pork. Also 鲜肉小馄饨, 葱油拌面, 咸豆花, 现磨浓豆浆, 龙井茶叶蛋. Opens 06:00; queue before 08:00. Verified on Dianping (~¥17pp). NOTE: family split — 朝晖路 store is now "芳春/芳楠春" (different owners); 中山南路 &amp; 鼓楼 are the founder's own.</t>
-  </si>
-  <si>
     <t>¥15–25</t>
   </si>
   <si>
@@ -11221,9 +10518,6 @@
     <t>姑苏区山塘街 (walkable from the Ritz)</t>
   </si>
   <si>
-    <t>HAIRY CRAB 大闸蟹 season pick. 招牌熟醉蟹, 阳澄湖大闸蟹 (时令价), 蟹粉豆腐. 4.8/5 but only 21 reviews; 拒绝料包. Queues &gt;1h at meal times. Prestige alt: 新聚丰菜馆 太监弄店 (1904, 黑珍珠+米其林指南, 清炒蟹粉, ¥215–389, closes 20:30). Lake-view alt: 璞园春舍 on 阳澄湖莲花岛 — boat required, board by 16:30, book 3+ days ahead. Season: 9月下旬–12月; 农历十月 = 公蟹蟹膏. Source: Ctrip reviews via news summary — re-check on Dianping before going.</t>
-  </si>
-  <si>
     <t>¥100 (蟹另计)</t>
   </si>
   <si>
@@ -11254,9 +10548,6 @@
     <t>XISHAN ALTERNATIVE — 270° lake view, 2 floors. 大众点评 4.2, ranked #1 on 太湖西山美食热门榜 (Ctrip shows a lower 3.7 on only 3 reviews). Try 西山拿铁, 黑松露薯条, 栗子巴斯克. Same-side extras: 树下茶咖 (under the 千年古樟 at 罗汉坞 — coffee or a pot of 碧螺春) and 野隐·松簧 (风铃溪谷·金铎岭半山腰, terrace w/ pine-wind + lake view). ⚠ Xishan needs 太湖大桥; public transport is weak (地铁5号线→快线11号→岛内公交) and the bridge jams at weekends. Dongshan and Xishan are ~1h apart — choose ONE.</t>
   </si>
   <si>
-    <t>NOTE THE SPELLING: 李百蟹 (bǎi 百), not 李白蟹. ZERO DETOUR — it is ON Pingjiang Rd 平江路, which you already walk 18:00–19:15 (row above). Crab-roe noodles 蟹黄面 &amp; 蟹黄拌饭 — golden 蟹粉/蟹膏, FREE noodle &amp; rice refills; also 江南花雕熟醉蟹, 蟹膏, and photogenic Suzhou desserts (草莓奶盖冰, 抹茶豆花, 桂花奶酪). Riverside seats look onto the canal, bridges &amp; boats. ⚠ Queues at meal times — take a queue number on arrival (reported to move fast). Open 10:00–21:30. Trip.com 5.0/5 but only 2 reviews — thin sample, re-check on Dianping. Other branches: 观前街店 (beside Day 7 lunch), 山塘街店 (河景船宴, near hotel).</t>
-  </si>
-  <si>
     <t>Opt · 10:00–21:30</t>
   </si>
   <si>
@@ -11269,9 +10560,6 @@
     <t>姑苏区狮林寺巷99号 琵琶语评弹茶馆·北馆1层 (on 平江路)</t>
   </si>
   <si>
-    <t>CRAB-ROE NOODLES, zero detour — sits on the Pingjiang Rd 平江路 stretch already in Day 6. 蟹黄面 / 蟹黄拌饭 with free noodle &amp; rice refills; 江南花雕熟醉蟹, 蟹膏; Suzhou desserts (草莓奶盖冰, 抹茶豆花, 桂花奶酪). Canal-side windows over bridges &amp; boats. Open 10:00–21:30; take a queue number on arrival. Spelling is 李百蟹 (百), not 李白蟹. Branches also at 观前街 and 山塘街 (河景船宴). Trip.com 5.0/5 on only 2 reviews — thin sample; re-check on Dianping.</t>
-  </si>
-  <si>
     <t>李百蟹·蟹黄面 Li Bai Xie Crab-Roe Noodles (夫子庙店)</t>
   </si>
   <si>
@@ -11383,9 +10671,6 @@
     <t>姑苏区平江街道大儒巷54号 (丁宅, off 平江路)</t>
   </si>
   <si>
-    <t>MICHELIN ⭐ 1-STAR 2026. Address CONFIRMED — 大儒巷54号, a lane off 平江路, so it IS walkable from your Day 6 Pingjiang Rd evening. Ming-dynasty 丁宅 relocated here in 2011; garden setting with 评弹. 新苏州菜, 不时不食. Trip.com 4.8, #1 Suzhou fine dining. ⚠ Book ~1 week ahead — very few tables; set menu from 2 pax. 11:30–14:00 / 17:30–21:00.</t>
-  </si>
-  <si>
     <t>李百蟹·蟹黄面 Li Bai Xie (平江路总店)</t>
   </si>
   <si>
@@ -11407,9 +10692,6 @@
     <t>MICHELIN 必比登 BIB GOURMAND 2026 (新晋/NEW). Locals rate its 牛肉锅贴 above the 夫子庙 tourist names — crisp shell, juicy filling; 牛肉小馄饨 too. 鼓楼区江西路, the same western side as 马祥兴 — a cheap alternative on this block.</t>
   </si>
   <si>
-    <t>MICHELIN ⭐ 1-STAR 2026 — 大儒巷54号 is a lane just OFF 平江路, so it is walkable from tonight's canal stroll. 丁宅, a Ming mansion relocated here in 2011; garden setting with 评弹. 新苏州菜, 不时不食 — 松鼠黄鱼, 碧螺虾仁, 响油蟹䰾. Trip.com 4.8, #1 Suzhou fine dining. ⚠ BOOK ~1 WEEK AHEAD — very few tables; set menu from 2 pax. 11:30–14:00 / 17:30–21:00. Tel +86 512 6610 9177.</t>
-  </si>
-  <si>
     <t>SU Yan 苏宴 (W Suzhou, Jinji Lake 金鸡湖)</t>
   </si>
   <si>
@@ -11419,9 +10701,6 @@
     <t>姑苏区虎丘街道山塘街方基上38号楼 (白居易码头对面)</t>
   </si>
   <si>
-    <t>2026 Bib Gourmand. Noodle sub-brand of Michelin 1★ 鼎膳. Red or white broth simmered 6–8 hrs; 21 hot + 12 cold 浇头. Try 烟熏青鱼面 (signature carried over from 鼎膳), 焖肉面, 塘园五虾面. Verified via 姑苏发布 (区委宣传部) &amp; 苏州市文广旅局.</t>
-  </si>
-  <si>
     <t>~¥40–80</t>
   </si>
   <si>
@@ -11509,9 +10788,6 @@
     <t>🔴 Tangyuan 塘园·苏式面菜馆 (Shantang 山塘街)</t>
   </si>
   <si>
-    <t>DINING &amp; CAFÉS — Hangzhou 杭州 · Nanjing 南京 · Suzhou 苏州 · 15–22 Nov 2026. MICHELIN 2026 (沪苏浙) key: ⭐ = Star 星级 · 🔴 = Bib Gourmand 必比登 · ◆ = Selected 指南入选 — icon appears in front of the venue name. Nanjing's full 必比登 list is published; Hangzhou &amp; Suzhou published only new entrants — route-relevant ones are included here. Addresses verified against official/municipal sources; unverified items are labelled.</t>
-  </si>
-  <si>
     <t>Options ranked by rating, popularity &amp; distance from the day's route. ★ 宫宴 = banquet. 🏨 = at/near hotel. MICHELIN 2026 (沪苏浙, released 9 Apr 2026) key: ⭐ = Star 星级 · 🔴 = Bib Gourmand 必比登 · ◆ = Selected 指南入选 — icon appears in front of the restaurant name. Totals: Hangzhou 88 listings (34 必比登) · Nanjing 41 (21 必比登, 4 ⭐) · Suzhou 38 (18 必比登, 3 ⭐). Nanjing's 21 必比登 are fully published; Hangzhou &amp; Suzhou released only the new entrants by name — remaining 必比登 names are unpublished.</t>
   </si>
   <si>
@@ -11752,12 +11028,6 @@
     <t>打卡 highlight — illuminated glazed pagoda 琉璃塔 &amp; ruins light show 光影秀. ~1.2km from 中华门. Comfortable buffer now before the 19:00 cruise.</t>
   </si>
   <si>
-    <t>14:40–16:30</t>
-  </si>
-  <si>
-    <t>16:40–17:15</t>
-  </si>
-  <si>
     <t>13:30–14:15</t>
   </si>
   <si>
@@ -11938,19 +11208,7 @@
     <t>Hangzhou's "art ceiling" — Tadao Ando 安藤忠雄 大屋顶 + 柳亦春 大谷仓 with 单向空间 bookstore; 128 boutiques, 85% independent. Metro L2 to 良渚; needs a half-day.</t>
   </si>
   <si>
-    <t>Iconic yellow temple (求姻缘); climb 台城 明城墙 overlooking Xuanwu Lake.</t>
-  </si>
-  <si>
-    <t>Jiangnan's largest royal lake park; the 十里长堤 causeway is a stunning sunset spot — allow the full stretch to walk it properly.</t>
-  </si>
-  <si>
     <t>④ SOUTH old town. The most exquisite of the small gardens and the one most worth lingering in.</t>
-  </si>
-  <si>
-    <t>Verified on Dianping (~¥53pp). Bamboo-wind-chime courtyard cafe at the foot of Wushan 吴山, a few steps up from Hefang St — directly below the 14:15 吴山/城隍阁 stop and beside the 15:00 清河坊 browse. Specialty hand-brew, plum-soda, scones &amp; chiffon cake.</t>
-  </si>
-  <si>
-    <t>Verified on Dianping (~¥37pp). Called by reviewers Hangzhou's best Italian gelato — pistachio, matcha &amp; chocolate are the standouts. On Guangfu Rd 光复路, ~5 min from 清河坊 and right off 南宋御街. Little queuing off-peak.</t>
   </si>
   <si>
     <t>Award-winning tea house on Dajing Lane 大井巷 — the Southern Song lane you walk at 15:00, so it is a zero-detour stop. Owner 查文 is a Hangzhou tea-culture inheritor. 1F: walk-in tasting + tea/teaware retail — local 西湖龙井 plus Taiwan high-mtn oolong, Fuding white, Wuyi rock tea. Creative tea mocktails (茶逗逗 w/ tea jelly) brewed espresso-style. 2F tatami tea room needs advance booking 预约.</t>
@@ -12078,9 +11336,6 @@
   </si>
   <si>
     <t>17:30</t>
-  </si>
-  <si>
-    <t>18:15</t>
   </si>
   <si>
     <t>19:15</t>
@@ -12158,12 +11413,6 @@
     <t>SHOP: Xinjiekou 新街口 &amp; Deji Plaza 德基广场 (at hotel) 🏨</t>
   </si>
   <si>
-    <t>Optional: Xinanli 熙南里 &amp; Pingshi St 评事街 🆕</t>
-  </si>
-  <si>
-    <t>Nightcap: FLAIR 62F (Ritz) / 紫峰大厦 / 王府大街 🏨</t>
-  </si>
-  <si>
     <t>Optional: Librairie Avant-Garde 先锋书店 (五台山总店) 📚</t>
   </si>
   <si>
@@ -12189,6 +11438,312 @@
   </si>
   <si>
     <t>SEASONAL swap: Tianping Mountain 天平山红枫节 🍁</t>
+  </si>
+  <si>
+    <t>Xinanli 熙南里 &amp; Pingshi St 评事街 🆕</t>
+  </si>
+  <si>
+    <t>📸 Trendy/New</t>
+  </si>
+  <si>
+    <t>西桥 Xiqiao Lane — 紫峰大厦 framed shot (Day 5 alt)</t>
+  </si>
+  <si>
+    <t>鼓楼区西桥 (江苏路↔云南路) · 近宁海中学北门 · 地铁云南路站 · free</t>
+  </si>
+  <si>
+    <t>A 550m residential lane, not a bridge. Looking east it frames the 318m 紫峰大厦 between apartment blocks — the "时空隧道" market-life-vs-skyscraper shot. Best at dawn or dusk blue hour. Shoot from the zebra crossing by 宁海中学北门; live traffic, stay on the pavement. Chains with 颐和路 + 先锋书店 + 金银街 into a 2–3h Gulou citywalk.</t>
+  </si>
+  <si>
+    <t>MUST-SEE: Sun Yat-sen Mausoleum 中山陵</t>
+  </si>
+  <si>
+    <t>玄武区石象路7号</t>
+  </si>
+  <si>
+    <t>MUST-SEE + 🍁: Ming Xiaoling Sacred Way 石象路</t>
+  </si>
+  <si>
+    <t>MUST-SEE: Ming Xiaoling tomb 明孝陵</t>
+  </si>
+  <si>
+    <t>Lunch — Purple Mtn foot / 玄武 area</t>
+  </si>
+  <si>
+    <t>Jiming Temple 鸡鸣寺 &amp; Taicheng wall 台城</t>
+  </si>
+  <si>
+    <t>¥10 + ¥30</t>
+  </si>
+  <si>
+    <t>玄武区鸡鸣寺路1号</t>
+  </si>
+  <si>
+    <t>Free</t>
+  </si>
+  <si>
+    <t>鼓楼区西桥 (近宁海中学北门)</t>
+  </si>
+  <si>
+    <t>Optional: Xuanwu Lake 玄武湖 十里长堤</t>
+  </si>
+  <si>
+    <t>MOVED OUT of the timeline to make room for the Gulou citywalk. Jiangnan's largest royal lake park; the 十里长堤 causeway is a stunning sunset spot but needs ~2h to walk properly. You still get the lake from above at 台城 (14:15 row). Swap back in for the citywalk if you prefer water over streets.</t>
+  </si>
+  <si>
+    <t>Free · book 12 Nov</t>
+  </si>
+  <si>
+    <t>Straight on from 石象路 through 棂星门 — same ticket. UNESCO Ming founding-emperor tomb.</t>
+  </si>
+  <si>
+    <t>Same ¥70 ticket</t>
+  </si>
+  <si>
+    <t>① 钟山 east cluster. 392-step stairway. FREE but booking is compulsory (免费不免票) — reserve the 08:30–10:30 slot on the 钟山风景名胜区 WeChat mini-program; tickets drop 16:00 on 12 Nov (7 days ahead). Metro L2 苜蓿园 — no driving, parking is balloted.</t>
+  </si>
+  <si>
+    <t>10:30–11:15</t>
+  </si>
+  <si>
+    <t>观光车 ~10 min west (¥10/ride). '600m most beautiful autumn avenue' — stone elephants at peak foliage. THE autumn shot of the trip. Buy 明孝陵 ¥70 on its own — the ¥100 联票 no longer pays off now that 美龄宫/音乐台 are cut.</t>
+  </si>
+  <si>
+    <t>¥70 (covers both)</t>
+  </si>
+  <si>
+    <t>12:00–13:00</t>
+  </si>
+  <si>
+    <t>Off the hill by 12:00. DiDi to 鸡鸣寺 after (~15 min).</t>
+  </si>
+  <si>
+    <t>13:15–14:30</t>
+  </si>
+  <si>
+    <t>Iconic yellow temple (求姻缘); climb 台城 明城墙 for the Xuanwu Lake view from above — no need for the 2h causeway walk.</t>
+  </si>
+  <si>
+    <t>🌆 Blue hour: 紫峰大厦 from 西桥 (loop back)</t>
+  </si>
+  <si>
+    <t>Pack for Suzhou 苏州</t>
+  </si>
+  <si>
+    <t>Overnight: Ritz 丽思</t>
+  </si>
+  <si>
+    <t>14:45–15:10</t>
+  </si>
+  <si>
+    <t>🚶 CITYWALK ① Xiqiao Lane 西桥 — 紫峰机位</t>
+  </si>
+  <si>
+    <t>Metro L3 鸡鸣寺 → 大行宫 → L4 云南路 (~15 min), exit 4. The 550m lane that frames the 318m 紫峰大厦 between apartment blocks — locals call this spot the 紫峰机位. Shoot from the 宁海中学北门 three-way crossing, 1x lens, tower dead centre. ⚠ Live traffic road — stay on the crossing.</t>
+  </si>
+  <si>
+    <t>Free · 25 min</t>
+  </si>
+  <si>
+    <t>15:15–16:00</t>
+  </si>
+  <si>
+    <t>🚶 CITYWALK ② Yihe Road 颐和路 公馆区</t>
+  </si>
+  <si>
+    <t>"一条颐和路，半部民国史" — 225 protected 1930s villas under plane trees, at their best in Nov. MUST: the 歪脖子树 crooked-tree photo spot (queues — go straight there). Starbucks 非遗概念店 inside a villa. 先锋书店 颐和路店 at 江苏路39号 if open (was under renovation in 2025).</t>
+  </si>
+  <si>
+    <t>Free · 45 min</t>
+  </si>
+  <si>
+    <t>16:05–16:45</t>
+  </si>
+  <si>
+    <t>🚶 CITYWALK ③ Jinyin St 金银街 — murals &amp; crafts</t>
+  </si>
+  <si>
+    <t>Next to Nanjing Univ. MUST: the "我们如此热爱南京" graffiti wall + the 3D cat mural. Shops: 景德镇的瓷 (handmade ceramics, ¥5 small flowers → ¥400 original cups) · 梦虞·非遗文创 Gulou's first 绒花 silk-velvet-flower studio (30 hrs of thread per blossom) · 晚风来信·特调咖啡 (story card with every blend) · 秀饼啊 bakery (cheap Japanese-style).</t>
+  </si>
+  <si>
+    <t>Free · 40 min</t>
+  </si>
+  <si>
+    <t>鼓楼区金银街</t>
+  </si>
+  <si>
+    <t>16:45–17:30</t>
+  </si>
+  <si>
+    <t>🚶 CITYWALK ④ Taogu Xincun 陶谷新村 — vintage &amp; books</t>
+  </si>
+  <si>
+    <t>The real shopping stretch (上海路106号). 好脾气古着店 &amp; Coy — the two vintage stores people travel from Beijing/Shanghai for · 老宇宙商店 design oddities · 学人书店 / 唯楚书店 second-hand &amp; out-of-print books · 挚馥调香室 brainwave-scanned DIY perfume (1 of only 2 in China). ⚠ Locals say it "不适合匆忙打卡" — in 45 min you'll do 2–3 shops properly, not all. Pick vintage OR crafts.</t>
+  </si>
+  <si>
+    <t>鼓楼区上海路106号 (陶谷新村)</t>
+  </si>
+  <si>
+    <t>17:30–18:05</t>
+  </si>
+  <si>
+    <t>Double back as the tower lights up (~17:40 sunset mid-Nov) — this is 西桥 at its best. Shoot from the 宁海中学北门 crossing again; the lit tower against the dark lane is the money shot.</t>
+  </si>
+  <si>
+    <t>Free · 35 min</t>
+  </si>
+  <si>
+    <t>18:05–18:30</t>
+  </si>
+  <si>
+    <t>Transfer: 西桥 → Xinanli 熙南里</t>
+  </si>
+  <si>
+    <t>Metro 云南路 → 三山街 (L4→L1, ~20 min) or DiDi ~15 min. Heading south-east across the old town.</t>
+  </si>
+  <si>
+    <t>Metro/DiDi ~25 min</t>
+  </si>
+  <si>
+    <t>Dinner — Nanjing Impressions 南京大牌档 (德基广场7层) 🏨</t>
+  </si>
+  <si>
+    <t>¥80–120 · 025-84722777</t>
+  </si>
+  <si>
+    <t>玄武区中山路18号 德基广场7层</t>
+  </si>
+  <si>
+    <t>Straight down from dinner — same building. Flagships + the ¥16M themed washrooms (free, no booking). Deji trades till ~22:00. Deji Art Museum 8F needs advance 实名预约, so treat as browse-only tonight.</t>
+  </si>
+  <si>
+    <t>Xinjiekou 新街口 · till ~22:00</t>
+  </si>
+  <si>
+    <t>Nightcap: FLAIR 62F (Ritz) 🏨</t>
+  </si>
+  <si>
+    <t>Skyline drinks 62 floors up, in your own hotel. Zero travel to bed.</t>
+  </si>
+  <si>
+    <t>09:15–10:15</t>
+  </si>
+  <si>
+    <t>Early-ish start tomorrow for the G-train to Suzhou. Bags down, 龙井/绒花 souvenirs wrapped.</t>
+  </si>
+  <si>
+    <t>玄武区中山路18号 (丽思·德基)</t>
+  </si>
+  <si>
+    <t>13:15–14:15</t>
+  </si>
+  <si>
+    <t>Lunch — first Nanjing duck: 韩复兴 老门东店 🦆</t>
+  </si>
+  <si>
+    <t>秦淮区箍桶巷 (老门东)</t>
+  </si>
+  <si>
+    <t>Coffee — 一木家 Yimujia (老城南) ☕</t>
+  </si>
+  <si>
+    <t>~¥35 · 信府河</t>
+  </si>
+  <si>
+    <t>秦淮区信府河105号</t>
+  </si>
+  <si>
+    <t>Optional: Guochuang Yuan 国创园 (江南造币厂旧址) 🏭</t>
+  </si>
+  <si>
+    <t>Qing-to-Mao industrial site, not a retail park. Founded 1896 as the 江南铸造银元制钱总局 — the mint that struck 光绪元宝 silver dollars — then 中华民国江南造币厂, then 南京第二机床厂 (1959). Converted 2012 with 40+ 1950s–60s factory halls kept intact: gears, old lathes, chimneys, chimney-stack brickwork. Designated a 南京市历史风貌区 in 2017; three halls listed as 工业遗产类历史建筑. The old foundry is now the 江南造币博物馆. ⚠ Go in DAYLIGHT — the draw is the architecture. It sits WEST of 中华门 near 朝天宫站 (L5), off the south-bound afternoon chain, so slot it in only if 夫子庙 underwhelms or the 画舫 cruise is rained off.</t>
+  </si>
+  <si>
+    <t>Optional alt · Free · 全天</t>
+  </si>
+  <si>
+    <t>秦淮区来凤街菱角市66号</t>
+  </si>
+  <si>
+    <t>18:30–20:00</t>
+  </si>
+  <si>
+    <t>21:15–21:50</t>
+  </si>
+  <si>
+    <t>21:50–22:50</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>FishTank 鱼缸咖啡 (Day 5)</t>
+  </si>
+  <si>
+    <t>~¥54 pp</t>
+  </si>
+  <si>
+    <t>Nanjing's classic 盐水鸭 house — 秦淮区箍桶巷, right inside 老门东 and directly on this afternoon's southward route. 盐水鸭 + 鸭血粉丝汤 + 鸭油烧饼. Alt: 章云板鸭 评事街店 (4.7★, ~¥30pp, takeaway 卤味 — 20yr institution, expect a queue).</t>
+  </si>
+  <si>
+    <t>秦淮区信府河105号, backing onto the 秦淮河 with 画舫 drifting past — a preview of tonight's cruise. Modern-meets-classical interior; the 舒芙蕾 soufflé is the order. Alt next door: 边界 Border Coffee, 信府河58-60号.</t>
+  </si>
+  <si>
+    <t>Restored Qing block on 升州路 — lantern-lit lanes, indie shops &amp; night market. ⚠ 甘熙故居 (南京市民俗博物馆) is 9:00–17:30, 17:00 停止入馆, closed Mon — at this hour you see the exterior and the lanes only, not the interior. 全国重点文物保护单位, known as "九十九间半" (actually 162 rooms across 十九进院落, 9,500+㎡, built 嘉庆 era). Its 非遗 hall is where 绒花 master 赵树宪 works — the same craft as 梦虞·非遗文创 on 金银街 this afternoon. Ticket ¥20; some sources say free with real-name online booking — check before going. Metro L1 三山街站 exit 2/3, ~350m. Coffee stop: FishTank 鱼缸咖啡 (black storefront, street-front row).</t>
+  </si>
+  <si>
+    <t>Duck feast 盐水鸭 + 鸭血粉丝汤 + folk music. 德基广场7层, inside your hotel building — zero transfer, and you end the night at home. Tel 025-84722777. Alt branch: 夫子庙平江府店 (大石坝街48号).</t>
+  </si>
+  <si>
+    <t>秦淮区 熙南里街区 (临街一隅, near 升州路)</t>
+  </si>
+  <si>
+    <t>One of Nanjing's earliest specialty-coffee pioneers, opened 2012. Black storefront, conspicuous among the block's traditional teahouses. Ranked #2 in 城市惠's Nanjing specialty-coffee list (口味 4.5 / 环境 4.5 / 服务 4.5).</t>
+  </si>
+  <si>
+    <t>DINING &amp; CAFÉS — Hangzhou 杭州 · Nanjing 南京 · Suzhou 苏州 · 15–22 Nov 2026. MICHELIN 2026 (沪苏浙) key: ⭐ = Star 星级 · 🔴 = Bib Gourmand 必比登 · ◆ = Selected 指南入选 — icon appears in front of the venue name.</t>
+  </si>
+  <si>
+    <t>Courtyard café at the foot of Wushan 吴山, steps up from Hefang St. Hand-brew Ethiopia, plum soda 梅子露, scones &amp; chiffon cake. ~¥53pp.</t>
+  </si>
+  <si>
+    <t>Reviewers call it Hangzhou's best Italian gelato — pistachio, matcha, chocolate. ~5 min from Hefang St; little queuing off-peak. ~¥37pp.</t>
+  </si>
+  <si>
+    <t>MICHELIN Bib Gourmand 必比登 3 yrs running. Founder 泮芳春 has run it 18+ yrs. Signature 煎饺 ~¥1 each — thin skin, crisp base, juicy pork. Also 鲜肉小馄饨, 葱油拌面, 咸豆花, 现磨浓豆浆, 龙井茶叶蛋. ~¥17pp; opens 06:00, queue before 08:00. NOTE: family split — 朝晖路 store is now "芳春/芳楠春" (different owners); 中山南路 &amp; 鼓楼 are the founder's own.</t>
+  </si>
+  <si>
+    <t>MICHELIN ⭐ 1-STAR 2026. 大儒巷54号, a lane off 平江路 — walkable from your Day 6 Pingjiang Rd evening. Ming-dynasty 丁宅 relocated here in 2011; garden setting with 评弹. 新苏州菜, 不时不食. Trip.com 4.8, #1 Suzhou fine dining. ⚠ Book ~1 week ahead — very few tables; set menu from 2 pax. 11:30–14:00 / 17:30–21:00.</t>
+  </si>
+  <si>
+    <t>2026 Bib Gourmand. Noodle sub-brand of Michelin 1★ 鼎膳. Red or white broth simmered 6–8 hrs; 21 hot + 12 cold 浇头. Try 烟熏青鱼面 (signature carried over from 鼎膳), 焖肉面, 塘园五虾面.</t>
+  </si>
+  <si>
+    <t>1848 lakeside icon; vinegar fish, Dongpo pork. ⚠️ NOT in the 2026 Dianping 杭帮菜 top-16 — famous &amp; scenic, but locals rank it below its reputation.</t>
+  </si>
+  <si>
+    <t>250-yr-old; squirrel mandarin fish. 1,350+ reviews. ⚠️ Ranks LAST (评分 65) among 2026 Dianping 苏帮菜 entries while being the priciest — go for the heritage dish, not value.</t>
+  </si>
+  <si>
+    <t>MICHELIN ⭐ 1-STAR 2026 — 大儒巷54号, a lane just OFF 平江路, walkable from tonight's canal stroll. 丁宅, a Ming mansion relocated here in 2011; garden setting with 评弹. 新苏州菜, 不时不食 — 松鼠黄鱼, 碧螺虾仁, 响油蟹䰾. Trip.com 4.8, #1 Suzhou fine dining. ⚠ BOOK ~1 WEEK AHEAD — very few tables; set menu from 2 pax. 11:30–14:00 / 17:30–21:00. Tel +86 512 6610 9177.</t>
+  </si>
+  <si>
+    <t>MICHELIN Bib Gourmand 必比登 3 years running — Hangzhou's most famous pan-fried dumplings 煎饺, ~¥1 each (5 for ¥5). Thin skin, crisp golden base, juicy pork. ~¥17pp, opens 06:00. Queues form early — go before 08:00. Located at the 南宋御街 archway, ~10 min walk from 清河坊/吴山. Also: 鲜肉小馄饨, 葱油拌面, 咸豆花, 现磨豆浆.</t>
+  </si>
+  <si>
+    <t>Bamboo-wind-chime courtyard cafe at the foot of Wushan 吴山, a few steps up from Hefang St — directly below the 14:15 吴山/城隍阁 stop and beside the 15:00 清河坊 browse. Specialty hand-brew, plum-soda, scones &amp; chiffon cake. ~¥53pp.</t>
+  </si>
+  <si>
+    <t>Called by reviewers Hangzhou's best Italian gelato — pistachio, matcha &amp; chocolate are the standouts. On Guangfu Rd 光复路, ~5 min from 清河坊 and right off 南宋御街. Little queuing off-peak. ~¥37pp.</t>
+  </si>
+  <si>
+    <t>NOTE THE SPELLING: 李百蟹 (bǎi 百), not 李白蟹. ZERO DETOUR — it is ON Pingjiang Rd 平江路, which you already walk 18:00–19:15 (row above). Crab-roe noodles 蟹黄面 &amp; 蟹黄拌饭 — golden 蟹粉/蟹膏, FREE noodle &amp; rice refills; also 江南花雕熟醉蟹, 蟹膏, and photogenic Suzhou desserts (草莓奶盖冰, 抹茶豆花, 桂花奶酪). Riverside seats look onto the canal, bridges &amp; boats. ⚠ Queues at meal times — take a queue number on arrival (reported to move fast). Open 10:00–21:30. Other branches: 观前街店 (beside Day 7 lunch), 山塘街店 (河景船宴, near hotel).</t>
+  </si>
+  <si>
+    <t>HAIRY CRAB 大闸蟹 season pick. 招牌熟醉蟹, 阳澄湖大闸蟹 (时令价), 蟹粉豆腐. 拒绝料包. ⚠ Queues &gt;1h at meal times. Prestige alt: 新聚丰菜馆 太监弄店 (1904, 黑珍珠+米其林指南, 清炒蟹粉, ¥215–389, closes 20:30).</t>
+  </si>
+  <si>
+    <t>CRAB-ROE NOODLES, zero detour — sits on the Pingjiang Rd 平江路 stretch already in Day 6. 蟹黄面 / 蟹黄拌饭 with free noodle &amp; rice refills; 江南花雕熟醉蟹, 蟹膏; Suzhou desserts (草莓奶盖冰, 抹茶豆花, 桂花奶酪). Canal-side windows onto bridges &amp; boats. ⚠ Queues at meal times — take a number on arrival. Open 10:00–21:30.</t>
   </si>
 </sst>
 </file>
@@ -12757,7 +12312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="252">
+  <cellXfs count="253">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -13317,6 +12872,57 @@
     <xf numFmtId="49" fontId="10" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="24" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -13344,33 +12950,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -13398,6 +12977,42 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -13416,42 +13031,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -13482,29 +13061,8 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="24" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="10" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -13784,31 +13342,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="31.5" customHeight="1">
-      <c r="A1" s="209" t="s">
+      <c r="A1" s="217" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="209"/>
-      <c r="C1" s="209"/>
-      <c r="D1" s="209"/>
-      <c r="E1" s="209"/>
+      <c r="B1" s="217"/>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
     </row>
     <row r="2" spans="1:5" ht="21.75" customHeight="1">
-      <c r="A2" s="210" t="s">
+      <c r="A2" s="218" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="210"/>
-      <c r="C2" s="210"/>
-      <c r="D2" s="210"/>
-      <c r="E2" s="210"/>
+      <c r="B2" s="218"/>
+      <c r="C2" s="218"/>
+      <c r="D2" s="218"/>
+      <c r="E2" s="218"/>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1">
-      <c r="A4" s="211" t="s">
+      <c r="A4" s="219" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="211"/>
-      <c r="C4" s="211"/>
-      <c r="D4" s="211"/>
-      <c r="E4" s="211"/>
+      <c r="B4" s="219"/>
+      <c r="C4" s="219"/>
+      <c r="D4" s="219"/>
+      <c r="E4" s="219"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
@@ -13862,13 +13420,13 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1">
-      <c r="A9" s="212" t="s">
+      <c r="A9" s="220" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="212"/>
-      <c r="C9" s="212"/>
-      <c r="D9" s="212"/>
-      <c r="E9" s="212"/>
+      <c r="B9" s="220"/>
+      <c r="C9" s="220"/>
+      <c r="D9" s="220"/>
+      <c r="E9" s="220"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
@@ -13889,36 +13447,36 @@
     </row>
     <row r="11" spans="1:5" ht="55" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>993</v>
+        <v>925</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>994</v>
+        <v>926</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>995</v>
+        <v>927</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>996</v>
+        <v>928</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>968</v>
+        <v>900</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="55" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>993</v>
+        <v>925</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>997</v>
+        <v>929</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>998</v>
+        <v>930</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>999</v>
+        <v>931</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>1000</v>
+        <v>932</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="45.75" customHeight="1">
@@ -13957,41 +13515,41 @@
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1"/>
     <row r="16" spans="1:5" ht="72" customHeight="1">
-      <c r="A16" s="213" t="s">
+      <c r="A16" s="221" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="213"/>
-      <c r="C16" s="213"/>
-      <c r="D16" s="213"/>
-      <c r="E16" s="213"/>
+      <c r="B16" s="221"/>
+      <c r="C16" s="221"/>
+      <c r="D16" s="221"/>
+      <c r="E16" s="221"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="207" t="s">
+      <c r="A17" s="215" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="207"/>
-      <c r="C17" s="207"/>
-      <c r="D17" s="207"/>
-      <c r="E17" s="207"/>
+      <c r="B17" s="215"/>
+      <c r="C17" s="215"/>
+      <c r="D17" s="215"/>
+      <c r="E17" s="215"/>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1"/>
     <row r="19" spans="1:5" ht="31.5" customHeight="1">
-      <c r="A19" s="208" t="s">
+      <c r="A19" s="216" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="208"/>
-      <c r="C19" s="208"/>
-      <c r="D19" s="208"/>
-      <c r="E19" s="208"/>
+      <c r="B19" s="216"/>
+      <c r="C19" s="216"/>
+      <c r="D19" s="216"/>
+      <c r="E19" s="216"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="207" t="s">
+      <c r="A20" s="215" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="207"/>
-      <c r="C20" s="207"/>
-      <c r="D20" s="207"/>
-      <c r="E20" s="207"/>
+      <c r="B20" s="215"/>
+      <c r="C20" s="215"/>
+      <c r="D20" s="215"/>
+      <c r="E20" s="215"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -14014,7 +13572,7 @@
   <sheetPr>
     <tabColor rgb="FFC55A11"/>
   </sheetPr>
-  <dimension ref="A1:F137"/>
+  <dimension ref="A1:F140"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -14026,24 +13584,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18">
-      <c r="A1" s="189" t="s">
-        <v>964</v>
-      </c>
-      <c r="B1" s="190"/>
-      <c r="C1" s="190"/>
-      <c r="D1" s="190"/>
-      <c r="E1" s="190"/>
-      <c r="F1" s="191"/>
+      <c r="A1" s="206" t="s">
+        <v>896</v>
+      </c>
+      <c r="B1" s="207"/>
+      <c r="C1" s="207"/>
+      <c r="D1" s="207"/>
+      <c r="E1" s="207"/>
+      <c r="F1" s="208"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="192" t="s">
+      <c r="A2" s="209" t="s">
         <v>344</v>
       </c>
-      <c r="B2" s="193"/>
-      <c r="C2" s="193"/>
-      <c r="D2" s="193"/>
-      <c r="E2" s="193"/>
-      <c r="F2" s="194"/>
+      <c r="B2" s="210"/>
+      <c r="C2" s="210"/>
+      <c r="D2" s="210"/>
+      <c r="E2" s="210"/>
+      <c r="F2" s="211"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="77" t="s">
@@ -14066,14 +13624,14 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="195" t="s">
-        <v>965</v>
-      </c>
-      <c r="B4" s="196"/>
-      <c r="C4" s="196"/>
-      <c r="D4" s="196"/>
-      <c r="E4" s="196"/>
-      <c r="F4" s="197"/>
+      <c r="A4" s="212" t="s">
+        <v>897</v>
+      </c>
+      <c r="B4" s="213"/>
+      <c r="C4" s="213"/>
+      <c r="D4" s="213"/>
+      <c r="E4" s="213"/>
+      <c r="F4" s="214"/>
     </row>
     <row r="5" spans="1:6" ht="28">
       <c r="A5" s="98" t="s">
@@ -14120,13 +13678,13 @@
         <v>350</v>
       </c>
       <c r="B7" s="158" t="s">
-        <v>795</v>
+        <v>740</v>
       </c>
       <c r="C7" s="50" t="s">
         <v>361</v>
       </c>
       <c r="D7" s="50" t="s">
-        <v>1143</v>
+        <v>1069</v>
       </c>
       <c r="E7" s="50" t="s">
         <v>362</v>
@@ -14163,16 +13721,16 @@
         <v>369</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>966</v>
+        <v>898</v>
       </c>
       <c r="D9" s="50" t="s">
-        <v>967</v>
+        <v>899</v>
       </c>
       <c r="E9" s="50" t="s">
         <v>370</v>
       </c>
       <c r="F9" s="115" t="s">
-        <v>968</v>
+        <v>900</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28">
@@ -14182,17 +13740,17 @@
       <c r="B10" s="56" t="s">
         <v>371</v>
       </c>
-      <c r="C10" s="244" t="s">
-        <v>1156</v>
+      <c r="C10" s="189" t="s">
+        <v>1081</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>969</v>
+        <v>901</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>970</v>
+        <v>902</v>
       </c>
       <c r="F10" s="116" t="s">
-        <v>971</v>
+        <v>903</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="45" customHeight="1">
@@ -14200,19 +13758,19 @@
         <v>350</v>
       </c>
       <c r="B11" s="154" t="s">
-        <v>758</v>
+        <v>705</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>1111</v>
+        <v>1037</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>1112</v>
+        <v>1038</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>1113</v>
+        <v>1039</v>
       </c>
       <c r="F11" s="117" t="s">
-        <v>1114</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="45" customHeight="1">
@@ -14220,19 +13778,19 @@
         <v>350</v>
       </c>
       <c r="B12" s="154" t="s">
-        <v>1115</v>
+        <v>1041</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>1116</v>
+        <v>1042</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>1117</v>
+        <v>1043</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>972</v>
+        <v>904</v>
       </c>
       <c r="F12" s="117" t="s">
-        <v>973</v>
+        <v>905</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28">
@@ -14243,16 +13801,16 @@
         <v>373</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>974</v>
+        <v>906</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>1099</v>
+        <v>1029</v>
       </c>
       <c r="E13" s="41" t="s">
-        <v>975</v>
+        <v>907</v>
       </c>
       <c r="F13" s="118" t="s">
-        <v>976</v>
+        <v>908</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="28">
@@ -14269,21 +13827,21 @@
         <v>376</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>977</v>
+        <v>909</v>
       </c>
       <c r="F14" s="116" t="s">
-        <v>971</v>
+        <v>903</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="195" t="s">
-        <v>978</v>
-      </c>
-      <c r="B15" s="196"/>
-      <c r="C15" s="196"/>
-      <c r="D15" s="196"/>
-      <c r="E15" s="196"/>
-      <c r="F15" s="197"/>
+      <c r="A15" s="212" t="s">
+        <v>910</v>
+      </c>
+      <c r="B15" s="213"/>
+      <c r="C15" s="213"/>
+      <c r="D15" s="213"/>
+      <c r="E15" s="213"/>
+      <c r="F15" s="214"/>
     </row>
     <row r="16" spans="1:6" ht="28">
       <c r="A16" s="101" t="s">
@@ -14293,16 +13851,16 @@
         <v>379</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>979</v>
+        <v>911</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>980</v>
+        <v>912</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>981</v>
+        <v>913</v>
       </c>
       <c r="F16" s="116" t="s">
-        <v>968</v>
+        <v>900</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="90" customHeight="1">
@@ -14313,13 +13871,13 @@
         <v>380</v>
       </c>
       <c r="C17" s="186" t="s">
-        <v>1157</v>
+        <v>1082</v>
       </c>
       <c r="D17" s="47" t="s">
-        <v>1125</v>
+        <v>1051</v>
       </c>
       <c r="E17" s="186" t="s">
-        <v>1126</v>
+        <v>1052</v>
       </c>
       <c r="F17" s="119" t="s">
         <v>382</v>
@@ -14336,10 +13894,10 @@
         <v>384</v>
       </c>
       <c r="D18" s="61" t="s">
-        <v>1142</v>
+        <v>1068</v>
       </c>
       <c r="E18" s="187" t="s">
-        <v>1127</v>
+        <v>1053</v>
       </c>
       <c r="F18" s="120" t="s">
         <v>385</v>
@@ -14350,16 +13908,16 @@
         <v>378</v>
       </c>
       <c r="B19" s="188" t="s">
-        <v>1133</v>
+        <v>1059</v>
       </c>
       <c r="C19" s="47" t="s">
-        <v>1128</v>
+        <v>1054</v>
       </c>
       <c r="D19" s="47" t="s">
-        <v>1139</v>
+        <v>1065</v>
       </c>
       <c r="E19" s="186" t="s">
-        <v>1134</v>
+        <v>1060</v>
       </c>
       <c r="F19" s="119" t="s">
         <v>386</v>
@@ -14370,19 +13928,19 @@
         <v>378</v>
       </c>
       <c r="B20" s="152" t="s">
-        <v>1135</v>
+        <v>1061</v>
       </c>
       <c r="C20" s="61" t="s">
-        <v>1129</v>
+        <v>1055</v>
       </c>
       <c r="D20" s="61" t="s">
-        <v>1138</v>
+        <v>1064</v>
       </c>
       <c r="E20" s="187" t="s">
-        <v>1130</v>
+        <v>1056</v>
       </c>
       <c r="F20" s="120" t="s">
-        <v>1131</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="28" customHeight="1">
@@ -14390,19 +13948,19 @@
         <v>378</v>
       </c>
       <c r="B21" s="152" t="s">
-        <v>1146</v>
+        <v>1072</v>
       </c>
       <c r="C21" s="61" t="s">
-        <v>1098</v>
+        <v>1028</v>
       </c>
       <c r="D21" s="61" t="s">
-        <v>1141</v>
+        <v>1067</v>
       </c>
       <c r="E21" s="61" t="s">
-        <v>511</v>
+        <v>483</v>
       </c>
       <c r="F21" s="120" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="56" customHeight="1">
@@ -14410,16 +13968,16 @@
         <v>378</v>
       </c>
       <c r="B22" s="152" t="s">
-        <v>1146</v>
+        <v>1072</v>
       </c>
       <c r="C22" s="61" t="s">
-        <v>1132</v>
+        <v>1058</v>
       </c>
       <c r="D22" s="61" t="s">
-        <v>1140</v>
+        <v>1066</v>
       </c>
       <c r="E22" s="61" t="s">
-        <v>511</v>
+        <v>483</v>
       </c>
       <c r="F22" s="120" t="s">
         <v>387</v>
@@ -14430,16 +13988,16 @@
         <v>378</v>
       </c>
       <c r="B23" s="157" t="s">
-        <v>1136</v>
+        <v>1062</v>
       </c>
       <c r="C23" s="20" t="s">
+        <v>388</v>
+      </c>
+      <c r="D23" s="20" t="s">
         <v>389</v>
       </c>
-      <c r="D23" s="20" t="s">
+      <c r="E23" s="20" t="s">
         <v>390</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>391</v>
       </c>
       <c r="F23" s="121" t="s">
         <v>60</v>
@@ -14450,19 +14008,19 @@
         <v>378</v>
       </c>
       <c r="B24" s="157" t="s">
-        <v>1137</v>
-      </c>
-      <c r="C24" s="245" t="s">
-        <v>1158</v>
+        <v>1063</v>
+      </c>
+      <c r="C24" s="190" t="s">
+        <v>1083</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>796</v>
+        <v>741</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>797</v>
+        <v>742</v>
       </c>
       <c r="F24" s="121" t="s">
-        <v>790</v>
+        <v>735</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="56">
@@ -14470,19 +14028,19 @@
         <v>378</v>
       </c>
       <c r="B25" s="159" t="s">
-        <v>1084</v>
+        <v>1014</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>1092</v>
+        <v>1022</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>1095</v>
+        <v>1025</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>1093</v>
+        <v>1023</v>
       </c>
       <c r="F25" s="86" t="s">
-        <v>1094</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="110" customHeight="1">
@@ -14490,19 +14048,19 @@
         <v>378</v>
       </c>
       <c r="B26" s="152" t="s">
-        <v>1085</v>
+        <v>1015</v>
       </c>
       <c r="C26" s="187" t="s">
-        <v>1159</v>
+        <v>1084</v>
       </c>
       <c r="D26" s="187" t="s">
-        <v>1154</v>
+        <v>1079</v>
       </c>
       <c r="E26" s="187" t="s">
-        <v>1153</v>
+        <v>1078</v>
       </c>
       <c r="F26" s="120" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="56">
@@ -14510,19 +14068,19 @@
         <v>378</v>
       </c>
       <c r="B27" s="152" t="s">
-        <v>1086</v>
+        <v>1016</v>
       </c>
       <c r="C27" s="187" t="s">
-        <v>1160</v>
+        <v>1085</v>
       </c>
       <c r="D27" s="61" t="s">
-        <v>1096</v>
+        <v>1026</v>
       </c>
       <c r="E27" s="61" t="s">
-        <v>1087</v>
+        <v>1017</v>
       </c>
       <c r="F27" s="120" t="s">
-        <v>789</v>
+        <v>734</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="42">
@@ -14530,19 +14088,19 @@
         <v>378</v>
       </c>
       <c r="B28" s="152" t="s">
-        <v>1088</v>
+        <v>1018</v>
       </c>
       <c r="C28" s="61" t="s">
-        <v>1089</v>
+        <v>1019</v>
       </c>
       <c r="D28" s="61" t="s">
-        <v>1097</v>
+        <v>1027</v>
       </c>
       <c r="E28" s="61" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F28" s="120" t="s">
-        <v>1090</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="28">
@@ -14550,19 +14108,19 @@
         <v>378</v>
       </c>
       <c r="B29" s="160" t="s">
-        <v>1118</v>
+        <v>1044</v>
       </c>
       <c r="C29" s="36" t="s">
-        <v>1119</v>
+        <v>1045</v>
       </c>
       <c r="D29" s="36" t="s">
-        <v>1120</v>
+        <v>1046</v>
       </c>
       <c r="E29" s="36" t="s">
-        <v>1121</v>
+        <v>1047</v>
       </c>
       <c r="F29" s="122" t="s">
-        <v>913</v>
+        <v>849</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="70">
@@ -14570,19 +14128,19 @@
         <v>378</v>
       </c>
       <c r="B30" s="154" t="s">
-        <v>1122</v>
-      </c>
-      <c r="C30" s="246" t="s">
-        <v>1161</v>
+        <v>1048</v>
+      </c>
+      <c r="C30" s="191" t="s">
+        <v>1086</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>1123</v>
+        <v>1049</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>1124</v>
+        <v>1050</v>
       </c>
       <c r="F30" s="117" t="s">
-        <v>913</v>
+        <v>849</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="56">
@@ -14590,19 +14148,19 @@
         <v>378</v>
       </c>
       <c r="B31" s="154" t="s">
-        <v>1091</v>
+        <v>1021</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>770</v>
+        <v>716</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>1155</v>
+        <v>1080</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>771</v>
+        <v>717</v>
       </c>
       <c r="F31" s="117" t="s">
-        <v>772</v>
+        <v>718</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="28">
@@ -14610,19 +14168,19 @@
         <v>378</v>
       </c>
       <c r="B32" s="160" t="s">
-        <v>773</v>
+        <v>719</v>
       </c>
       <c r="C32" s="36" t="s">
+        <v>394</v>
+      </c>
+      <c r="D32" s="36" t="s">
         <v>395</v>
       </c>
-      <c r="D32" s="36" t="s">
+      <c r="E32" s="36" t="s">
         <v>396</v>
       </c>
-      <c r="E32" s="36" t="s">
+      <c r="F32" s="122" t="s">
         <v>397</v>
-      </c>
-      <c r="F32" s="122" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="28">
@@ -14630,123 +14188,123 @@
         <v>378</v>
       </c>
       <c r="B33" s="151" t="s">
-        <v>762</v>
+        <v>708</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>982</v>
+        <v>914</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>983</v>
+        <v>915</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>977</v>
+        <v>909</v>
       </c>
       <c r="F33" s="116" t="s">
-        <v>971</v>
+        <v>903</v>
       </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="195" t="s">
-        <v>984</v>
-      </c>
-      <c r="B34" s="196"/>
-      <c r="C34" s="196"/>
-      <c r="D34" s="196"/>
-      <c r="E34" s="196"/>
-      <c r="F34" s="197"/>
+      <c r="A34" s="212" t="s">
+        <v>916</v>
+      </c>
+      <c r="B34" s="213"/>
+      <c r="C34" s="213"/>
+      <c r="D34" s="213"/>
+      <c r="E34" s="213"/>
+      <c r="F34" s="214"/>
     </row>
     <row r="35" spans="1:6" ht="42">
       <c r="A35" s="101" t="s">
+        <v>399</v>
+      </c>
+      <c r="B35" s="56" t="s">
         <v>400</v>
       </c>
-      <c r="B35" s="56" t="s">
-        <v>401</v>
-      </c>
       <c r="C35" s="10" t="s">
-        <v>985</v>
+        <v>917</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>986</v>
+        <v>918</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>987</v>
+        <v>919</v>
       </c>
       <c r="F35" s="116" t="s">
-        <v>968</v>
+        <v>900</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="84">
       <c r="A36" s="102" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B36" s="154" t="s">
-        <v>1147</v>
-      </c>
-      <c r="C36" s="246" t="s">
-        <v>1162</v>
+        <v>1073</v>
+      </c>
+      <c r="C36" s="191" t="s">
+        <v>1087</v>
       </c>
       <c r="D36" s="33" t="s">
-        <v>853</v>
+        <v>1204</v>
       </c>
       <c r="E36" s="35" t="s">
-        <v>854</v>
+        <v>794</v>
       </c>
       <c r="F36" s="117" t="s">
-        <v>855</v>
+        <v>795</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="28">
       <c r="A37" s="105" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B37" s="60" t="s">
+        <v>401</v>
+      </c>
+      <c r="C37" s="61" t="s">
         <v>402</v>
       </c>
-      <c r="C37" s="61" t="s">
+      <c r="D37" s="61" t="s">
         <v>403</v>
       </c>
-      <c r="D37" s="61" t="s">
+      <c r="E37" s="61" t="s">
         <v>404</v>
       </c>
-      <c r="E37" s="61" t="s">
+      <c r="F37" s="120" t="s">
         <v>405</v>
-      </c>
-      <c r="F37" s="120" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="28">
       <c r="A38" s="105" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B38" s="60" t="s">
+        <v>406</v>
+      </c>
+      <c r="C38" s="61" t="s">
         <v>407</v>
       </c>
-      <c r="C38" s="61" t="s">
+      <c r="D38" s="61" t="s">
         <v>408</v>
       </c>
-      <c r="D38" s="61" t="s">
+      <c r="E38" s="61" t="s">
         <v>409</v>
       </c>
-      <c r="E38" s="61" t="s">
+      <c r="F38" s="120" t="s">
         <v>410</v>
-      </c>
-      <c r="F38" s="120" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="28">
       <c r="A39" s="104" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B39" s="59" t="s">
+        <v>411</v>
+      </c>
+      <c r="C39" s="186" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D39" s="47" t="s">
         <v>412</v>
-      </c>
-      <c r="C39" s="186" t="s">
-        <v>1163</v>
-      </c>
-      <c r="D39" s="47" t="s">
-        <v>413</v>
       </c>
       <c r="E39" s="47" t="s">
         <v>381</v>
@@ -14757,179 +14315,179 @@
     </row>
     <row r="40" spans="1:6" ht="28">
       <c r="A40" s="99" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B40" s="54" t="s">
+        <v>413</v>
+      </c>
+      <c r="C40" s="15" t="s">
         <v>414</v>
       </c>
-      <c r="C40" s="15" t="s">
+      <c r="D40" s="15" t="s">
         <v>415</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>416</v>
       </c>
       <c r="E40" s="15" t="s">
         <v>53</v>
       </c>
       <c r="F40" s="85" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="70">
       <c r="A41" s="99" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B41" s="54" t="s">
-        <v>988</v>
-      </c>
-      <c r="C41" s="247" t="s">
-        <v>1164</v>
+        <v>920</v>
+      </c>
+      <c r="C41" s="192" t="s">
+        <v>1089</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>1100</v>
+        <v>1030</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>989</v>
+        <v>921</v>
       </c>
       <c r="F41" s="85" t="s">
-        <v>990</v>
+        <v>922</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="28">
       <c r="A42" s="105" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B42" s="60" t="s">
-        <v>991</v>
+        <v>923</v>
       </c>
       <c r="C42" s="61" t="s">
+        <v>417</v>
+      </c>
+      <c r="D42" s="61" t="s">
         <v>418</v>
       </c>
-      <c r="D42" s="61" t="s">
+      <c r="E42" s="61" t="s">
+        <v>409</v>
+      </c>
+      <c r="F42" s="120" t="s">
         <v>419</v>
-      </c>
-      <c r="E42" s="61" t="s">
-        <v>410</v>
-      </c>
-      <c r="F42" s="120" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="28">
       <c r="A43" s="102" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B43" s="57" t="s">
-        <v>1036</v>
+        <v>968</v>
       </c>
       <c r="C43" s="33" t="s">
+        <v>420</v>
+      </c>
+      <c r="D43" s="33" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E43" s="35" t="s">
         <v>421</v>
       </c>
-      <c r="D43" s="33" t="s">
-        <v>1101</v>
-      </c>
-      <c r="E43" s="35" t="s">
+      <c r="F43" s="117" t="s">
         <v>422</v>
-      </c>
-      <c r="F43" s="117" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="28">
       <c r="A44" s="102" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B44" s="154" t="s">
-        <v>1148</v>
+        <v>1074</v>
       </c>
       <c r="C44" s="33" t="s">
-        <v>786</v>
+        <v>731</v>
       </c>
       <c r="D44" s="33" t="s">
-        <v>787</v>
+        <v>732</v>
       </c>
       <c r="E44" s="35" t="s">
-        <v>511</v>
+        <v>483</v>
       </c>
       <c r="F44" s="117" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="70">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="56">
       <c r="A45" s="102" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B45" s="154" t="s">
-        <v>1148</v>
-      </c>
-      <c r="C45" s="246" t="s">
-        <v>1165</v>
+        <v>1074</v>
+      </c>
+      <c r="C45" s="191" t="s">
+        <v>1090</v>
       </c>
       <c r="D45" s="33" t="s">
-        <v>1108</v>
+        <v>1205</v>
       </c>
       <c r="E45" s="35" t="s">
-        <v>836</v>
+        <v>779</v>
       </c>
       <c r="F45" s="117" t="s">
-        <v>837</v>
+        <v>780</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="56">
       <c r="A46" s="102" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B46" s="154" t="s">
-        <v>1148</v>
-      </c>
-      <c r="C46" s="246" t="s">
-        <v>1166</v>
+        <v>1074</v>
+      </c>
+      <c r="C46" s="191" t="s">
+        <v>1091</v>
       </c>
       <c r="D46" s="33" t="s">
-        <v>1109</v>
+        <v>1206</v>
       </c>
       <c r="E46" s="35" t="s">
-        <v>838</v>
+        <v>781</v>
       </c>
       <c r="F46" s="117" t="s">
-        <v>839</v>
+        <v>782</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="45" customHeight="1">
       <c r="A47" s="102" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B47" s="154" t="s">
-        <v>1148</v>
-      </c>
-      <c r="C47" s="246" t="s">
-        <v>1167</v>
+        <v>1074</v>
+      </c>
+      <c r="C47" s="191" t="s">
+        <v>1092</v>
       </c>
       <c r="D47" s="33" t="s">
-        <v>1110</v>
+        <v>1036</v>
       </c>
       <c r="E47" s="35" t="s">
-        <v>847</v>
+        <v>788</v>
       </c>
       <c r="F47" s="117" t="s">
-        <v>848</v>
+        <v>789</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="28">
       <c r="A48" s="106" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B48" s="63" t="s">
-        <v>1037</v>
+        <v>969</v>
       </c>
       <c r="C48" s="20" t="s">
+        <v>423</v>
+      </c>
+      <c r="D48" s="20" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E48" s="20" t="s">
         <v>424</v>
-      </c>
-      <c r="D48" s="20" t="s">
-        <v>1102</v>
-      </c>
-      <c r="E48" s="20" t="s">
-        <v>425</v>
       </c>
       <c r="F48" s="121" t="s">
         <v>64</v>
@@ -14937,96 +14495,96 @@
     </row>
     <row r="49" spans="1:6" ht="42">
       <c r="A49" s="105" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B49" s="152" t="s">
-        <v>1038</v>
+        <v>970</v>
       </c>
       <c r="C49" s="61" t="s">
+        <v>425</v>
+      </c>
+      <c r="D49" s="61" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E49" s="61" t="s">
         <v>426</v>
       </c>
-      <c r="D49" s="61" t="s">
-        <v>1103</v>
-      </c>
-      <c r="E49" s="61" t="s">
+      <c r="F49" s="120" t="s">
         <v>427</v>
-      </c>
-      <c r="F49" s="120" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="28">
       <c r="A50" s="103" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B50" s="155" t="s">
-        <v>1149</v>
+        <v>1075</v>
       </c>
       <c r="C50" s="39" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D50" s="39" t="s">
-        <v>799</v>
+        <v>744</v>
       </c>
       <c r="E50" s="39" t="s">
-        <v>800</v>
+        <v>745</v>
       </c>
       <c r="F50" s="118" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="42">
       <c r="A51" s="98" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B51" s="53" t="s">
-        <v>801</v>
+        <v>746</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>802</v>
+        <v>747</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>803</v>
+        <v>748</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>804</v>
+        <v>749</v>
       </c>
       <c r="F51" s="86" t="s">
-        <v>805</v>
+        <v>750</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="56">
       <c r="A52" s="98" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B52" s="159" t="s">
-        <v>806</v>
-      </c>
-      <c r="C52" s="248" t="s">
-        <v>1168</v>
+        <v>751</v>
+      </c>
+      <c r="C52" s="193" t="s">
+        <v>1093</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>807</v>
+        <v>752</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>808</v>
+        <v>753</v>
       </c>
       <c r="F52" s="86" t="s">
-        <v>805</v>
+        <v>750</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="28">
       <c r="A53" s="101" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B53" s="151" t="s">
-        <v>762</v>
+        <v>708</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>809</v>
+        <v>754</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>377</v>
@@ -15037,19 +14595,19 @@
     </row>
     <row r="54" spans="1:6" ht="28">
       <c r="A54" s="109" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B54" s="65" t="s">
+        <v>432</v>
+      </c>
+      <c r="C54" s="194" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D54" s="42" t="s">
+        <v>433</v>
+      </c>
+      <c r="E54" s="42" t="s">
         <v>434</v>
-      </c>
-      <c r="C54" s="249" t="s">
-        <v>1169</v>
-      </c>
-      <c r="D54" s="42" t="s">
-        <v>435</v>
-      </c>
-      <c r="E54" s="42" t="s">
-        <v>436</v>
       </c>
       <c r="F54" s="124" t="s">
         <v>266</v>
@@ -15057,69 +14615,69 @@
     </row>
     <row r="55" spans="1:6" ht="28">
       <c r="A55" s="103" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B55" s="58" t="s">
+        <v>432</v>
+      </c>
+      <c r="C55" s="39" t="s">
+        <v>435</v>
+      </c>
+      <c r="D55" s="39" t="s">
+        <v>436</v>
+      </c>
+      <c r="E55" s="39" t="s">
         <v>434</v>
       </c>
-      <c r="C55" s="39" t="s">
+      <c r="F55" s="118" t="s">
         <v>437</v>
-      </c>
-      <c r="D55" s="39" t="s">
-        <v>438</v>
-      </c>
-      <c r="E55" s="39" t="s">
-        <v>436</v>
-      </c>
-      <c r="F55" s="118" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="42">
       <c r="A56" s="103" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B56" s="155" t="s">
-        <v>434</v>
-      </c>
-      <c r="C56" s="250" t="s">
-        <v>1170</v>
+        <v>432</v>
+      </c>
+      <c r="C56" s="195" t="s">
+        <v>1095</v>
       </c>
       <c r="D56" s="156" t="s">
-        <v>1104</v>
+        <v>1034</v>
       </c>
       <c r="E56" s="39" t="s">
-        <v>784</v>
+        <v>729</v>
       </c>
       <c r="F56" s="118" t="s">
-        <v>785</v>
+        <v>730</v>
       </c>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="198" t="s">
-        <v>1023</v>
-      </c>
-      <c r="B57" s="199"/>
-      <c r="C57" s="199"/>
-      <c r="D57" s="199"/>
-      <c r="E57" s="199"/>
-      <c r="F57" s="200"/>
+      <c r="A57" s="197" t="s">
+        <v>955</v>
+      </c>
+      <c r="B57" s="198"/>
+      <c r="C57" s="198"/>
+      <c r="D57" s="198"/>
+      <c r="E57" s="198"/>
+      <c r="F57" s="199"/>
     </row>
     <row r="58" spans="1:6" ht="28">
       <c r="A58" s="101" t="s">
+        <v>438</v>
+      </c>
+      <c r="B58" s="56" t="s">
+        <v>400</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="D58" s="10" t="s">
         <v>440</v>
       </c>
-      <c r="B58" s="56" t="s">
-        <v>401</v>
-      </c>
-      <c r="C58" s="10" t="s">
+      <c r="E58" s="10" t="s">
         <v>441</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>442</v>
-      </c>
-      <c r="E58" s="10" t="s">
-        <v>443</v>
       </c>
       <c r="F58" s="116" t="s">
         <v>24</v>
@@ -15127,1550 +14685,1610 @@
     </row>
     <row r="59" spans="1:6" ht="28">
       <c r="A59" s="100" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B59" s="55" t="s">
+        <v>442</v>
+      </c>
+      <c r="C59" s="50" t="s">
+        <v>443</v>
+      </c>
+      <c r="D59" s="50" t="s">
         <v>444</v>
       </c>
-      <c r="C59" s="50" t="s">
+      <c r="E59" s="50" t="s">
         <v>445</v>
       </c>
-      <c r="D59" s="50" t="s">
+      <c r="F59" s="115" t="s">
         <v>446</v>
-      </c>
-      <c r="E59" s="50" t="s">
-        <v>447</v>
-      </c>
-      <c r="F59" s="115" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="28">
       <c r="A60" s="100" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B60" s="55" t="s">
+        <v>447</v>
+      </c>
+      <c r="C60" s="50" t="s">
+        <v>448</v>
+      </c>
+      <c r="D60" s="50" t="s">
         <v>449</v>
       </c>
-      <c r="C60" s="50" t="s">
+      <c r="E60" s="50" t="s">
         <v>450</v>
       </c>
-      <c r="D60" s="50" t="s">
+      <c r="F60" s="115" t="s">
         <v>451</v>
-      </c>
-      <c r="E60" s="50" t="s">
-        <v>452</v>
-      </c>
-      <c r="F60" s="115" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="28">
       <c r="A61" s="101" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B61" s="56" t="s">
-        <v>454</v>
-      </c>
-      <c r="C61" s="244" t="s">
-        <v>1171</v>
+        <v>452</v>
+      </c>
+      <c r="C61" s="189" t="s">
+        <v>1096</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>370</v>
       </c>
       <c r="F61" s="116" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="28">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="56">
       <c r="A62" s="99" t="s">
-        <v>440</v>
-      </c>
-      <c r="B62" s="54" t="s">
-        <v>457</v>
+        <v>438</v>
+      </c>
+      <c r="B62" s="252" t="s">
+        <v>1173</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>458</v>
+        <v>1174</v>
       </c>
       <c r="D62" s="25" t="s">
-        <v>459</v>
+        <v>1189</v>
       </c>
       <c r="E62" s="15" t="s">
         <v>145</v>
       </c>
       <c r="F62" s="85" t="s">
-        <v>270</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="28">
       <c r="A63" s="105" t="s">
-        <v>440</v>
-      </c>
-      <c r="B63" s="60" t="s">
-        <v>1039</v>
+        <v>438</v>
+      </c>
+      <c r="B63" s="152" t="s">
+        <v>971</v>
       </c>
       <c r="C63" s="61" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="D63" s="61" t="s">
-        <v>1144</v>
+        <v>1070</v>
       </c>
       <c r="E63" s="61" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F63" s="120" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="28">
+    <row r="64" spans="1:6" ht="86" customHeight="1">
       <c r="A64" s="106" t="s">
-        <v>440</v>
-      </c>
-      <c r="B64" s="63" t="s">
-        <v>992</v>
+        <v>438</v>
+      </c>
+      <c r="B64" s="157" t="s">
+        <v>924</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>462</v>
+        <v>1176</v>
       </c>
       <c r="D64" s="20" t="s">
-        <v>463</v>
+        <v>1190</v>
       </c>
       <c r="E64" s="20" t="s">
-        <v>464</v>
+        <v>1177</v>
       </c>
       <c r="F64" s="121" t="s">
-        <v>465</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="28">
       <c r="A65" s="105" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B65" s="60" t="s">
-        <v>798</v>
+        <v>743</v>
       </c>
       <c r="C65" s="61" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="D65" s="61" t="s">
-        <v>1040</v>
+        <v>972</v>
       </c>
       <c r="E65" s="61" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="F65" s="120" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="45">
       <c r="A66" s="110" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B66" s="91" t="s">
-        <v>1041</v>
+        <v>973</v>
       </c>
       <c r="C66" s="92" t="s">
-        <v>743</v>
+        <v>695</v>
       </c>
       <c r="D66" s="92" t="s">
-        <v>1042</v>
+        <v>974</v>
       </c>
       <c r="E66" s="92" t="s">
-        <v>744</v>
+        <v>696</v>
       </c>
       <c r="F66" s="125" t="s">
-        <v>745</v>
+        <v>697</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="28">
       <c r="A67" s="105" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B67" s="60" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="C67" s="61" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="D67" s="61" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="E67" s="61" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="F67" s="120" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="28">
       <c r="A68" s="107" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B68" s="64" t="s">
-        <v>758</v>
+        <v>705</v>
       </c>
       <c r="C68" s="36" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="D68" s="36" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="E68" s="36" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="F68" s="122" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="28">
       <c r="A69" s="109" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B69" s="65" t="s">
-        <v>759</v>
-      </c>
-      <c r="C69" s="249" t="s">
-        <v>1172</v>
+        <v>706</v>
+      </c>
+      <c r="C69" s="194" t="s">
+        <v>1097</v>
       </c>
       <c r="D69" s="44" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="E69" s="42" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="F69" s="124" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="28">
       <c r="A70" s="101" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B70" s="128" t="s">
-        <v>762</v>
+        <v>708</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="D70" s="10"/>
       <c r="E70" s="10" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="F70" s="116" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71" s="198" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B71" s="199"/>
-      <c r="C71" s="199"/>
-      <c r="D71" s="199"/>
-      <c r="E71" s="199"/>
-      <c r="F71" s="200"/>
-    </row>
-    <row r="72" spans="1:6" ht="28">
-      <c r="A72" s="101" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="100" customHeight="1">
+      <c r="A71" s="101" t="s">
+        <v>438</v>
+      </c>
+      <c r="B71" s="128" t="s">
+        <v>432</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>1179</v>
+      </c>
+      <c r="D71" s="10" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F71" s="116" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" s="197" t="s">
+        <v>956</v>
+      </c>
+      <c r="B72" s="198"/>
+      <c r="C72" s="198"/>
+      <c r="D72" s="198"/>
+      <c r="E72" s="198"/>
+      <c r="F72" s="199"/>
+    </row>
+    <row r="73" spans="1:6" ht="56" customHeight="1">
+      <c r="A73" s="101" t="s">
+        <v>475</v>
+      </c>
+      <c r="B73" s="56" t="s">
+        <v>400</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>476</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F73" s="116" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="56" customHeight="1">
+      <c r="A74" s="105" t="s">
+        <v>475</v>
+      </c>
+      <c r="B74" s="152" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C74" s="61" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D74" s="62" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E74" s="61" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F74" s="120" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="56" customHeight="1">
+      <c r="A75" s="104" t="s">
+        <v>475</v>
+      </c>
+      <c r="B75" s="188" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C75" s="47" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D75" s="47" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E75" s="47" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F75" s="119" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="56" customHeight="1">
+      <c r="A76" s="105" t="s">
+        <v>475</v>
+      </c>
+      <c r="B76" s="152" t="s">
+        <v>574</v>
+      </c>
+      <c r="C76" s="61" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D76" s="61" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E76" s="61" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F76" s="120" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="56" customHeight="1">
+      <c r="A77" s="98" t="s">
+        <v>475</v>
+      </c>
+      <c r="B77" s="159" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="F77" s="86" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="72" customHeight="1">
+      <c r="A78" s="105" t="s">
+        <v>475</v>
+      </c>
+      <c r="B78" s="152" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C78" s="61" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D78" s="61" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E78" s="61" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F78" s="120" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="72" customHeight="1">
+      <c r="A79" s="104" t="s">
+        <v>475</v>
+      </c>
+      <c r="B79" s="188" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C79" s="47" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D79" s="47" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E79" s="47" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F79" s="119" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="86" customHeight="1">
+      <c r="A80" s="104" t="s">
+        <v>475</v>
+      </c>
+      <c r="B80" s="188" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C80" s="47" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D80" s="47" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E80" s="47" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F80" s="119" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="86" customHeight="1">
+      <c r="A81" s="104" t="s">
+        <v>475</v>
+      </c>
+      <c r="B81" s="188" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C81" s="47" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D81" s="47" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E81" s="47" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F81" s="119" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="72" customHeight="1">
+      <c r="A82" s="104" t="s">
+        <v>475</v>
+      </c>
+      <c r="B82" s="188" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C82" s="47" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D82" s="47" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E82" s="47" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F82" s="119" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="56" customHeight="1">
+      <c r="A83" s="106" t="s">
+        <v>475</v>
+      </c>
+      <c r="B83" s="157" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C83" s="20" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D83" s="20" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E83" s="20" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F83" s="121" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="72" customHeight="1">
+      <c r="A84" s="102" t="s">
+        <v>475</v>
+      </c>
+      <c r="B84" s="154" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C84" s="191" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D84" s="33" t="s">
+        <v>1161</v>
+      </c>
+      <c r="E84" s="33" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F84" s="117" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="150" customHeight="1">
+      <c r="A85" s="102" t="s">
+        <v>475</v>
+      </c>
+      <c r="B85" s="154" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C85" s="191" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D85" s="33" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E85" s="33" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F85" s="117" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="72" customHeight="1">
+      <c r="A86" s="107" t="s">
+        <v>475</v>
+      </c>
+      <c r="B86" s="160" t="s">
+        <v>549</v>
+      </c>
+      <c r="C86" s="36" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D86" s="36" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E86" s="36" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F86" s="122" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="56" customHeight="1">
+      <c r="A87" s="101" t="s">
+        <v>475</v>
+      </c>
+      <c r="B87" s="151" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C87" s="189" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D87" s="10" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>1167</v>
+      </c>
+      <c r="F87" s="116" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="56" customHeight="1">
+      <c r="A88" s="101" t="s">
+        <v>475</v>
+      </c>
+      <c r="B88" s="151" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C88" s="10" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D88" s="10" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="F88" s="116" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="28">
+      <c r="A89" s="101" t="s">
+        <v>475</v>
+      </c>
+      <c r="B89" s="151" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C89" s="10" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D89" s="10" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F89" s="116" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="28">
+      <c r="A90" s="103" t="s">
+        <v>475</v>
+      </c>
+      <c r="B90" s="155" t="s">
+        <v>432</v>
+      </c>
+      <c r="C90" s="39" t="s">
         <v>484</v>
       </c>
-      <c r="B72" s="56" t="s">
-        <v>401</v>
-      </c>
-      <c r="C72" s="10" t="s">
+      <c r="D90" s="39" t="s">
         <v>485</v>
       </c>
-      <c r="D72" s="10" t="s">
+      <c r="E90" s="39" t="s">
+        <v>434</v>
+      </c>
+      <c r="F90" s="118" t="s">
         <v>486</v>
       </c>
-      <c r="E72" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F72" s="116" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="28">
-      <c r="A73" s="105" t="s">
-        <v>484</v>
-      </c>
-      <c r="B73" s="60" t="s">
+    </row>
+    <row r="91" spans="1:6" ht="86" customHeight="1">
+      <c r="A91" s="103" t="s">
+        <v>475</v>
+      </c>
+      <c r="B91" s="155" t="s">
+        <v>432</v>
+      </c>
+      <c r="C91" s="39" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D91" s="39" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E91" s="39" t="s">
+        <v>699</v>
+      </c>
+      <c r="F91" s="118" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="28">
+      <c r="A92" s="103" t="s">
+        <v>475</v>
+      </c>
+      <c r="B92" s="58" t="s">
+        <v>432</v>
+      </c>
+      <c r="C92" s="39" t="s">
         <v>487</v>
       </c>
-      <c r="C73" s="61" t="s">
+      <c r="D92" s="39" t="s">
         <v>488</v>
       </c>
-      <c r="D73" s="62" t="s">
+      <c r="E92" s="39" t="s">
+        <v>434</v>
+      </c>
+      <c r="F92" s="118" t="s">
         <v>489</v>
       </c>
-      <c r="E73" s="61" t="s">
-        <v>490</v>
-      </c>
-      <c r="F73" s="120" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="30">
-      <c r="A74" s="108" t="s">
-        <v>484</v>
-      </c>
-      <c r="B74" s="89" t="s">
-        <v>746</v>
-      </c>
-      <c r="C74" s="90" t="s">
-        <v>747</v>
-      </c>
-      <c r="D74" s="90" t="s">
-        <v>748</v>
-      </c>
-      <c r="E74" s="90" t="s">
-        <v>749</v>
-      </c>
-      <c r="F74" s="123" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="28">
-      <c r="A75" s="103" t="s">
-        <v>484</v>
-      </c>
-      <c r="B75" s="58" t="s">
-        <v>760</v>
-      </c>
-      <c r="C75" s="39" t="s">
-        <v>492</v>
-      </c>
-      <c r="D75" s="39" t="s">
-        <v>493</v>
-      </c>
-      <c r="E75" s="39" t="s">
-        <v>494</v>
-      </c>
-      <c r="F75" s="118" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="28">
-      <c r="A76" s="104" t="s">
-        <v>484</v>
-      </c>
-      <c r="B76" s="59" t="s">
-        <v>388</v>
-      </c>
-      <c r="C76" s="47" t="s">
-        <v>496</v>
-      </c>
-      <c r="D76" s="47" t="s">
-        <v>497</v>
-      </c>
-      <c r="E76" s="47" t="s">
-        <v>498</v>
-      </c>
-      <c r="F76" s="119" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="28">
-      <c r="A77" s="105" t="s">
-        <v>484</v>
-      </c>
-      <c r="B77" s="60" t="s">
-        <v>500</v>
-      </c>
-      <c r="C77" s="61" t="s">
-        <v>501</v>
-      </c>
-      <c r="D77" s="61" t="s">
-        <v>502</v>
-      </c>
-      <c r="E77" s="61" t="s">
-        <v>503</v>
-      </c>
-      <c r="F77" s="120" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="28">
-      <c r="A78" s="98" t="s">
-        <v>484</v>
-      </c>
-      <c r="B78" s="53" t="s">
-        <v>505</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>506</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>507</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>508</v>
-      </c>
-      <c r="F78" s="86" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="28">
-      <c r="A79" s="105" t="s">
-        <v>484</v>
-      </c>
-      <c r="B79" s="60" t="s">
-        <v>510</v>
-      </c>
-      <c r="C79" s="61" t="s">
-        <v>512</v>
-      </c>
-      <c r="D79" s="61" t="s">
-        <v>1105</v>
-      </c>
-      <c r="E79" s="61" t="s">
-        <v>513</v>
-      </c>
-      <c r="F79" s="120" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="28">
-      <c r="A80" s="104" t="s">
-        <v>484</v>
-      </c>
-      <c r="B80" s="59" t="s">
-        <v>1043</v>
-      </c>
-      <c r="C80" s="47" t="s">
-        <v>515</v>
-      </c>
-      <c r="D80" s="47" t="s">
-        <v>1106</v>
-      </c>
-      <c r="E80" s="47" t="s">
-        <v>511</v>
-      </c>
-      <c r="F80" s="119" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="28">
-      <c r="A81" s="106" t="s">
-        <v>484</v>
-      </c>
-      <c r="B81" s="63" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C81" s="20" t="s">
-        <v>517</v>
-      </c>
-      <c r="D81" s="20" t="s">
-        <v>518</v>
-      </c>
-      <c r="E81" s="20" t="s">
-        <v>519</v>
-      </c>
-      <c r="F81" s="121" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="28">
-      <c r="A82" s="102" t="s">
-        <v>484</v>
-      </c>
-      <c r="B82" s="57" t="s">
-        <v>521</v>
-      </c>
-      <c r="C82" s="246" t="s">
-        <v>1173</v>
-      </c>
-      <c r="D82" s="33" t="s">
-        <v>522</v>
-      </c>
-      <c r="E82" s="33" t="s">
-        <v>523</v>
-      </c>
-      <c r="F82" s="117" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="28">
-      <c r="A83" s="102" t="s">
-        <v>484</v>
-      </c>
-      <c r="B83" s="154" t="s">
-        <v>1150</v>
-      </c>
-      <c r="C83" s="246" t="s">
-        <v>1174</v>
-      </c>
-      <c r="D83" s="33" t="s">
-        <v>782</v>
-      </c>
-      <c r="E83" s="33" t="s">
-        <v>511</v>
-      </c>
-      <c r="F83" s="117" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="28">
-      <c r="A84" s="107" t="s">
-        <v>484</v>
-      </c>
-      <c r="B84" s="64" t="s">
+    </row>
+    <row r="93" spans="1:6" ht="45">
+      <c r="A93" s="108" t="s">
+        <v>475</v>
+      </c>
+      <c r="B93" s="89" t="s">
         <v>432</v>
       </c>
-      <c r="C84" s="36" t="s">
-        <v>524</v>
-      </c>
-      <c r="D84" s="36" t="s">
-        <v>525</v>
-      </c>
-      <c r="E84" s="36" t="s">
-        <v>185</v>
-      </c>
-      <c r="F84" s="122" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="28">
-      <c r="A85" s="101" t="s">
-        <v>484</v>
-      </c>
-      <c r="B85" s="56" t="s">
-        <v>526</v>
-      </c>
-      <c r="C85" s="244" t="s">
-        <v>1175</v>
-      </c>
-      <c r="D85" s="10" t="s">
-        <v>527</v>
-      </c>
-      <c r="E85" s="10" t="s">
-        <v>430</v>
-      </c>
-      <c r="F85" s="116" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="28">
-      <c r="A86" s="101" t="s">
-        <v>484</v>
-      </c>
-      <c r="B86" s="56" t="s">
-        <v>481</v>
-      </c>
-      <c r="C86" s="10" t="s">
-        <v>528</v>
-      </c>
-      <c r="D86" s="10" t="s">
-        <v>529</v>
-      </c>
-      <c r="E86" s="10" t="s">
-        <v>483</v>
-      </c>
-      <c r="F86" s="116" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="28">
-      <c r="A87" s="103" t="s">
-        <v>484</v>
-      </c>
-      <c r="B87" s="58" t="s">
-        <v>434</v>
-      </c>
-      <c r="C87" s="39" t="s">
-        <v>530</v>
-      </c>
-      <c r="D87" s="39" t="s">
-        <v>531</v>
-      </c>
-      <c r="E87" s="39" t="s">
-        <v>436</v>
-      </c>
-      <c r="F87" s="118" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="28">
-      <c r="A88" s="103" t="s">
-        <v>484</v>
-      </c>
-      <c r="B88" s="58" t="s">
-        <v>434</v>
-      </c>
-      <c r="C88" s="39" t="s">
-        <v>533</v>
-      </c>
-      <c r="D88" s="39" t="s">
-        <v>534</v>
-      </c>
-      <c r="E88" s="39" t="s">
-        <v>436</v>
-      </c>
-      <c r="F88" s="118" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="28">
-      <c r="A89" s="103" t="s">
-        <v>484</v>
-      </c>
-      <c r="B89" s="58" t="s">
-        <v>434</v>
-      </c>
-      <c r="C89" s="39" t="s">
-        <v>536</v>
-      </c>
-      <c r="D89" s="39" t="s">
-        <v>537</v>
-      </c>
-      <c r="E89" s="39" t="s">
-        <v>436</v>
-      </c>
-      <c r="F89" s="118" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="45">
-      <c r="A90" s="108" t="s">
-        <v>484</v>
-      </c>
-      <c r="B90" s="89" t="s">
-        <v>434</v>
-      </c>
-      <c r="C90" s="251" t="s">
-        <v>1176</v>
-      </c>
-      <c r="D90" s="95" t="s">
-        <v>751</v>
-      </c>
-      <c r="E90" s="90" t="s">
-        <v>752</v>
-      </c>
-      <c r="F90" s="123" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="45">
-      <c r="A91" s="108" t="s">
-        <v>484</v>
-      </c>
-      <c r="B91" s="153" t="s">
-        <v>434</v>
-      </c>
-      <c r="C91" s="90" t="s">
-        <v>779</v>
-      </c>
-      <c r="D91" s="95" t="s">
-        <v>780</v>
-      </c>
-      <c r="E91" s="90" t="s">
-        <v>752</v>
-      </c>
-      <c r="F91" s="123" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92" s="201" t="s">
-        <v>1025</v>
-      </c>
-      <c r="B92" s="202"/>
-      <c r="C92" s="202"/>
-      <c r="D92" s="202"/>
-      <c r="E92" s="202"/>
-      <c r="F92" s="203"/>
-    </row>
-    <row r="93" spans="1:6" ht="28">
-      <c r="A93" s="101" t="s">
-        <v>539</v>
-      </c>
-      <c r="B93" s="56" t="s">
-        <v>401</v>
-      </c>
-      <c r="C93" s="10" t="s">
-        <v>540</v>
-      </c>
-      <c r="D93" s="10"/>
-      <c r="E93" s="10" t="s">
-        <v>443</v>
-      </c>
-      <c r="F93" s="116" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="28">
-      <c r="A94" s="100" t="s">
-        <v>539</v>
-      </c>
-      <c r="B94" s="55" t="s">
-        <v>444</v>
-      </c>
-      <c r="C94" s="50" t="s">
-        <v>541</v>
-      </c>
-      <c r="D94" s="50" t="s">
-        <v>542</v>
-      </c>
-      <c r="E94" s="50" t="s">
-        <v>447</v>
-      </c>
-      <c r="F94" s="115" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="28">
-      <c r="A95" s="100" t="s">
-        <v>539</v>
-      </c>
-      <c r="B95" s="55" t="s">
-        <v>449</v>
-      </c>
-      <c r="C95" s="50" t="s">
-        <v>544</v>
-      </c>
-      <c r="D95" s="50" t="s">
-        <v>545</v>
-      </c>
-      <c r="E95" s="50" t="s">
-        <v>452</v>
-      </c>
-      <c r="F95" s="115" t="s">
-        <v>546</v>
-      </c>
+      <c r="C93" s="196" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D93" s="95" t="s">
+        <v>698</v>
+      </c>
+      <c r="E93" s="90" t="s">
+        <v>699</v>
+      </c>
+      <c r="F93" s="123" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="45">
+      <c r="A94" s="108" t="s">
+        <v>475</v>
+      </c>
+      <c r="B94" s="153" t="s">
+        <v>432</v>
+      </c>
+      <c r="C94" s="90" t="s">
+        <v>725</v>
+      </c>
+      <c r="D94" s="95" t="s">
+        <v>726</v>
+      </c>
+      <c r="E94" s="90" t="s">
+        <v>699</v>
+      </c>
+      <c r="F94" s="123" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" s="200" t="s">
+        <v>957</v>
+      </c>
+      <c r="B95" s="201"/>
+      <c r="C95" s="201"/>
+      <c r="D95" s="201"/>
+      <c r="E95" s="201"/>
+      <c r="F95" s="202"/>
     </row>
     <row r="96" spans="1:6" ht="28">
       <c r="A96" s="101" t="s">
-        <v>539</v>
+        <v>491</v>
       </c>
       <c r="B96" s="56" t="s">
-        <v>454</v>
-      </c>
-      <c r="C96" s="244" t="s">
-        <v>1177</v>
-      </c>
-      <c r="D96" s="10" t="s">
-        <v>547</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="C96" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="D96" s="10"/>
       <c r="E96" s="10" t="s">
-        <v>548</v>
+        <v>441</v>
       </c>
       <c r="F96" s="116" t="s">
-        <v>549</v>
+        <v>29</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="28">
-      <c r="A97" s="99" t="s">
-        <v>539</v>
-      </c>
-      <c r="B97" s="54" t="s">
-        <v>457</v>
-      </c>
-      <c r="C97" s="15" t="s">
-        <v>550</v>
-      </c>
-      <c r="D97" s="15" t="s">
-        <v>551</v>
-      </c>
-      <c r="E97" s="15" t="s">
+      <c r="A97" s="100" t="s">
+        <v>491</v>
+      </c>
+      <c r="B97" s="55" t="s">
+        <v>442</v>
+      </c>
+      <c r="C97" s="50" t="s">
+        <v>493</v>
+      </c>
+      <c r="D97" s="50" t="s">
+        <v>494</v>
+      </c>
+      <c r="E97" s="50" t="s">
+        <v>445</v>
+      </c>
+      <c r="F97" s="115" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="28">
+      <c r="A98" s="100" t="s">
+        <v>491</v>
+      </c>
+      <c r="B98" s="55" t="s">
+        <v>447</v>
+      </c>
+      <c r="C98" s="50" t="s">
+        <v>496</v>
+      </c>
+      <c r="D98" s="50" t="s">
+        <v>497</v>
+      </c>
+      <c r="E98" s="50" t="s">
+        <v>450</v>
+      </c>
+      <c r="F98" s="115" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="28">
+      <c r="A99" s="101" t="s">
+        <v>491</v>
+      </c>
+      <c r="B99" s="56" t="s">
+        <v>452</v>
+      </c>
+      <c r="C99" s="189" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D99" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="E99" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="F99" s="116" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="28">
+      <c r="A100" s="99" t="s">
+        <v>491</v>
+      </c>
+      <c r="B100" s="54" t="s">
+        <v>455</v>
+      </c>
+      <c r="C100" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="D100" s="15" t="s">
+        <v>503</v>
+      </c>
+      <c r="E100" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="F97" s="85" t="s">
+      <c r="F100" s="85" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="28">
-      <c r="A98" s="105" t="s">
-        <v>539</v>
-      </c>
-      <c r="B98" s="60" t="s">
-        <v>552</v>
-      </c>
-      <c r="C98" s="61" t="s">
-        <v>553</v>
-      </c>
-      <c r="D98" s="61" t="s">
-        <v>554</v>
-      </c>
-      <c r="E98" s="61" t="s">
-        <v>555</v>
-      </c>
-      <c r="F98" s="120" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" ht="56">
-      <c r="A99" s="105" t="s">
-        <v>539</v>
-      </c>
-      <c r="B99" s="60" t="s">
-        <v>1032</v>
-      </c>
-      <c r="C99" s="61" t="s">
-        <v>1029</v>
-      </c>
-      <c r="D99" s="61" t="s">
-        <v>1030</v>
-      </c>
-      <c r="E99" s="61" t="s">
-        <v>1031</v>
-      </c>
-      <c r="F99" s="120" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" ht="28">
-      <c r="A100" s="105" t="s">
-        <v>539</v>
-      </c>
-      <c r="B100" s="60" t="s">
-        <v>1033</v>
-      </c>
-      <c r="C100" s="61" t="s">
-        <v>558</v>
-      </c>
-      <c r="D100" s="61" t="s">
-        <v>1145</v>
-      </c>
-      <c r="E100" s="61" t="s">
-        <v>559</v>
-      </c>
-      <c r="F100" s="120" t="s">
-        <v>560</v>
-      </c>
-    </row>
     <row r="101" spans="1:6" ht="28">
-      <c r="A101" s="106" t="s">
-        <v>539</v>
-      </c>
-      <c r="B101" s="63" t="s">
-        <v>1034</v>
-      </c>
-      <c r="C101" s="20" t="s">
-        <v>561</v>
-      </c>
-      <c r="D101" s="20" t="s">
-        <v>1035</v>
-      </c>
-      <c r="E101" s="20" t="s">
-        <v>562</v>
-      </c>
-      <c r="F101" s="121" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" ht="28">
+      <c r="A101" s="105" t="s">
+        <v>491</v>
+      </c>
+      <c r="B101" s="60" t="s">
+        <v>504</v>
+      </c>
+      <c r="C101" s="61" t="s">
+        <v>505</v>
+      </c>
+      <c r="D101" s="61" t="s">
+        <v>506</v>
+      </c>
+      <c r="E101" s="61" t="s">
+        <v>507</v>
+      </c>
+      <c r="F101" s="120" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="56">
       <c r="A102" s="105" t="s">
-        <v>539</v>
+        <v>491</v>
       </c>
       <c r="B102" s="60" t="s">
-        <v>563</v>
+        <v>964</v>
       </c>
       <c r="C102" s="61" t="s">
-        <v>564</v>
+        <v>961</v>
       </c>
       <c r="D102" s="61" t="s">
-        <v>565</v>
+        <v>962</v>
       </c>
       <c r="E102" s="61" t="s">
-        <v>98</v>
+        <v>963</v>
       </c>
       <c r="F102" s="120" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" ht="42">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="28">
       <c r="A103" s="105" t="s">
-        <v>539</v>
-      </c>
-      <c r="B103" s="152" t="s">
-        <v>1151</v>
-      </c>
-      <c r="C103" s="187" t="s">
-        <v>1178</v>
+        <v>491</v>
+      </c>
+      <c r="B103" s="60" t="s">
+        <v>965</v>
+      </c>
+      <c r="C103" s="61" t="s">
+        <v>510</v>
       </c>
       <c r="D103" s="61" t="s">
-        <v>778</v>
+        <v>1071</v>
       </c>
       <c r="E103" s="61" t="s">
         <v>511</v>
       </c>
       <c r="F103" s="120" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="28">
+      <c r="A104" s="106" t="s">
+        <v>491</v>
+      </c>
+      <c r="B104" s="63" t="s">
+        <v>966</v>
+      </c>
+      <c r="C104" s="20" t="s">
+        <v>513</v>
+      </c>
+      <c r="D104" s="20" t="s">
+        <v>967</v>
+      </c>
+      <c r="E104" s="20" t="s">
+        <v>514</v>
+      </c>
+      <c r="F104" s="121" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="154">
-      <c r="A104" s="105" t="s">
+    <row r="105" spans="1:6" ht="28">
+      <c r="A105" s="105" t="s">
+        <v>491</v>
+      </c>
+      <c r="B105" s="60" t="s">
+        <v>515</v>
+      </c>
+      <c r="C105" s="61" t="s">
+        <v>516</v>
+      </c>
+      <c r="D105" s="61" t="s">
+        <v>517</v>
+      </c>
+      <c r="E105" s="61" t="s">
+        <v>98</v>
+      </c>
+      <c r="F105" s="120" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="42">
+      <c r="A106" s="105" t="s">
+        <v>491</v>
+      </c>
+      <c r="B106" s="152" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C106" s="187" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D106" s="61" t="s">
+        <v>724</v>
+      </c>
+      <c r="E106" s="61" t="s">
+        <v>483</v>
+      </c>
+      <c r="F106" s="120" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="140">
+      <c r="A107" s="105" t="s">
+        <v>491</v>
+      </c>
+      <c r="B107" s="152" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C107" s="187" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D107" s="61" t="s">
+        <v>1207</v>
+      </c>
+      <c r="E107" s="61" t="s">
+        <v>815</v>
+      </c>
+      <c r="F107" s="120" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="28">
+      <c r="A108" s="109" t="s">
+        <v>491</v>
+      </c>
+      <c r="B108" s="65" t="s">
+        <v>518</v>
+      </c>
+      <c r="C108" s="194" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D108" s="42" t="s">
+        <v>519</v>
+      </c>
+      <c r="E108" s="42" t="s">
+        <v>520</v>
+      </c>
+      <c r="F108" s="124" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="30">
+      <c r="A109" s="111" t="s">
+        <v>491</v>
+      </c>
+      <c r="B109" s="93" t="s">
+        <v>701</v>
+      </c>
+      <c r="C109" s="94" t="s">
+        <v>702</v>
+      </c>
+      <c r="D109" s="94" t="s">
+        <v>703</v>
+      </c>
+      <c r="E109" s="94" t="s">
+        <v>704</v>
+      </c>
+      <c r="F109" s="126" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="28">
+      <c r="A110" s="101" t="s">
+        <v>491</v>
+      </c>
+      <c r="B110" s="128" t="s">
+        <v>708</v>
+      </c>
+      <c r="C110" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="D110" s="10"/>
+      <c r="E110" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="F110" s="116" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="42">
+      <c r="A111" s="102" t="s">
+        <v>491</v>
+      </c>
+      <c r="B111" s="154" t="s">
+        <v>708</v>
+      </c>
+      <c r="C111" s="191" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D111" s="33" t="s">
+        <v>522</v>
+      </c>
+      <c r="E111" s="33" t="s">
+        <v>429</v>
+      </c>
+      <c r="F111" s="117" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="28">
+      <c r="A112" s="103" t="s">
+        <v>491</v>
+      </c>
+      <c r="B112" s="155" t="s">
+        <v>708</v>
+      </c>
+      <c r="C112" s="39" t="s">
+        <v>736</v>
+      </c>
+      <c r="D112" s="39" t="s">
+        <v>737</v>
+      </c>
+      <c r="E112" s="39" t="s">
+        <v>429</v>
+      </c>
+      <c r="F112" s="118" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" s="200" t="s">
+        <v>958</v>
+      </c>
+      <c r="B113" s="201"/>
+      <c r="C113" s="201"/>
+      <c r="D113" s="201"/>
+      <c r="E113" s="201"/>
+      <c r="F113" s="202"/>
+    </row>
+    <row r="114" spans="1:6" ht="28">
+      <c r="A114" s="101" t="s">
+        <v>523</v>
+      </c>
+      <c r="B114" s="56" t="s">
+        <v>400</v>
+      </c>
+      <c r="C114" s="10" t="s">
+        <v>476</v>
+      </c>
+      <c r="D114" s="10" t="s">
+        <v>524</v>
+      </c>
+      <c r="E114" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F114" s="116" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="28">
+      <c r="A115" s="105" t="s">
+        <v>523</v>
+      </c>
+      <c r="B115" s="60" t="s">
+        <v>401</v>
+      </c>
+      <c r="C115" s="61" t="s">
+        <v>525</v>
+      </c>
+      <c r="D115" s="61" t="s">
+        <v>526</v>
+      </c>
+      <c r="E115" s="61" t="s">
+        <v>404</v>
+      </c>
+      <c r="F115" s="120" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="28">
+      <c r="A116" s="105" t="s">
+        <v>523</v>
+      </c>
+      <c r="B116" s="60" t="s">
+        <v>528</v>
+      </c>
+      <c r="C116" s="61" t="s">
+        <v>529</v>
+      </c>
+      <c r="D116" s="61" t="s">
+        <v>530</v>
+      </c>
+      <c r="E116" s="61" t="s">
+        <v>531</v>
+      </c>
+      <c r="F116" s="120" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" ht="28">
+      <c r="A117" s="105" t="s">
+        <v>523</v>
+      </c>
+      <c r="B117" s="60" t="s">
+        <v>479</v>
+      </c>
+      <c r="C117" s="61" t="s">
+        <v>533</v>
+      </c>
+      <c r="D117" s="61" t="s">
+        <v>534</v>
+      </c>
+      <c r="E117" s="61" t="s">
+        <v>535</v>
+      </c>
+      <c r="F117" s="120" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="56">
+      <c r="A118" s="105" t="s">
+        <v>523</v>
+      </c>
+      <c r="B118" s="152" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C118" s="61" t="s">
+        <v>720</v>
+      </c>
+      <c r="D118" s="61" t="s">
+        <v>721</v>
+      </c>
+      <c r="E118" s="61" t="s">
+        <v>722</v>
+      </c>
+      <c r="F118" s="120" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="28">
+      <c r="A119" s="98" t="s">
+        <v>523</v>
+      </c>
+      <c r="B119" s="53" t="s">
+        <v>536</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>537</v>
+      </c>
+      <c r="D119" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="E119" s="5" t="s">
         <v>539</v>
       </c>
-      <c r="B104" s="152" t="s">
-        <v>1151</v>
-      </c>
-      <c r="C104" s="187" t="s">
-        <v>1179</v>
-      </c>
-      <c r="D104" s="61" t="s">
-        <v>877</v>
-      </c>
-      <c r="E104" s="61" t="s">
-        <v>878</v>
-      </c>
-      <c r="F104" s="120" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="28">
-      <c r="A105" s="109" t="s">
-        <v>539</v>
-      </c>
-      <c r="B105" s="65" t="s">
-        <v>566</v>
-      </c>
-      <c r="C105" s="249" t="s">
-        <v>1180</v>
-      </c>
-      <c r="D105" s="42" t="s">
-        <v>567</v>
-      </c>
-      <c r="E105" s="42" t="s">
-        <v>568</v>
-      </c>
-      <c r="F105" s="124" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" ht="30">
-      <c r="A106" s="111" t="s">
-        <v>539</v>
-      </c>
-      <c r="B106" s="93" t="s">
-        <v>754</v>
-      </c>
-      <c r="C106" s="94" t="s">
-        <v>755</v>
-      </c>
-      <c r="D106" s="94" t="s">
-        <v>756</v>
-      </c>
-      <c r="E106" s="94" t="s">
-        <v>757</v>
-      </c>
-      <c r="F106" s="126" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" ht="28">
-      <c r="A107" s="101" t="s">
-        <v>539</v>
-      </c>
-      <c r="B107" s="128" t="s">
-        <v>762</v>
-      </c>
-      <c r="C107" s="10" t="s">
-        <v>761</v>
-      </c>
-      <c r="D107" s="10"/>
-      <c r="E107" s="10" t="s">
-        <v>483</v>
-      </c>
-      <c r="F107" s="116" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" ht="42">
-      <c r="A108" s="102" t="s">
-        <v>539</v>
-      </c>
-      <c r="B108" s="154" t="s">
-        <v>762</v>
-      </c>
-      <c r="C108" s="246" t="s">
-        <v>1181</v>
-      </c>
-      <c r="D108" s="33" t="s">
-        <v>570</v>
-      </c>
-      <c r="E108" s="33" t="s">
-        <v>430</v>
-      </c>
-      <c r="F108" s="117" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" ht="28">
-      <c r="A109" s="103" t="s">
-        <v>539</v>
-      </c>
-      <c r="B109" s="155" t="s">
-        <v>762</v>
-      </c>
-      <c r="C109" s="39" t="s">
-        <v>791</v>
-      </c>
-      <c r="D109" s="39" t="s">
-        <v>792</v>
-      </c>
-      <c r="E109" s="39" t="s">
-        <v>430</v>
-      </c>
-      <c r="F109" s="118" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110" s="201" t="s">
-        <v>1026</v>
-      </c>
-      <c r="B110" s="202"/>
-      <c r="C110" s="202"/>
-      <c r="D110" s="202"/>
-      <c r="E110" s="202"/>
-      <c r="F110" s="203"/>
-    </row>
-    <row r="111" spans="1:6" ht="28">
-      <c r="A111" s="101" t="s">
-        <v>571</v>
-      </c>
-      <c r="B111" s="56" t="s">
-        <v>401</v>
-      </c>
-      <c r="C111" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="D111" s="10" t="s">
-        <v>572</v>
-      </c>
-      <c r="E111" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F111" s="116" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="28">
-      <c r="A112" s="105" t="s">
-        <v>571</v>
-      </c>
-      <c r="B112" s="60" t="s">
-        <v>402</v>
-      </c>
-      <c r="C112" s="61" t="s">
-        <v>573</v>
-      </c>
-      <c r="D112" s="61" t="s">
-        <v>574</v>
-      </c>
-      <c r="E112" s="61" t="s">
-        <v>405</v>
-      </c>
-      <c r="F112" s="120" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" ht="28">
-      <c r="A113" s="105" t="s">
-        <v>571</v>
-      </c>
-      <c r="B113" s="60" t="s">
-        <v>576</v>
-      </c>
-      <c r="C113" s="61" t="s">
-        <v>577</v>
-      </c>
-      <c r="D113" s="61" t="s">
-        <v>578</v>
-      </c>
-      <c r="E113" s="61" t="s">
-        <v>579</v>
-      </c>
-      <c r="F113" s="120" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" ht="28">
-      <c r="A114" s="105" t="s">
-        <v>571</v>
-      </c>
-      <c r="B114" s="60" t="s">
-        <v>500</v>
-      </c>
-      <c r="C114" s="61" t="s">
-        <v>581</v>
-      </c>
-      <c r="D114" s="61" t="s">
-        <v>582</v>
-      </c>
-      <c r="E114" s="61" t="s">
-        <v>583</v>
-      </c>
-      <c r="F114" s="120" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" ht="56">
-      <c r="A115" s="105" t="s">
-        <v>571</v>
-      </c>
-      <c r="B115" s="152" t="s">
-        <v>1152</v>
-      </c>
-      <c r="C115" s="61" t="s">
-        <v>774</v>
-      </c>
-      <c r="D115" s="61" t="s">
-        <v>775</v>
-      </c>
-      <c r="E115" s="61" t="s">
-        <v>776</v>
-      </c>
-      <c r="F115" s="120" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" ht="28">
-      <c r="A116" s="98" t="s">
-        <v>571</v>
-      </c>
-      <c r="B116" s="53" t="s">
-        <v>584</v>
-      </c>
-      <c r="C116" s="5" t="s">
-        <v>585</v>
-      </c>
-      <c r="D116" s="5" t="s">
-        <v>586</v>
-      </c>
-      <c r="E116" s="5" t="s">
-        <v>587</v>
-      </c>
-      <c r="F116" s="86" t="s">
+      <c r="F119" s="86" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="28">
-      <c r="A117" s="102" t="s">
-        <v>571</v>
-      </c>
-      <c r="B117" s="57" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C117" s="33" t="s">
-        <v>1027</v>
-      </c>
-      <c r="D117" s="33" t="s">
-        <v>1028</v>
-      </c>
-      <c r="E117" s="33" t="s">
-        <v>588</v>
-      </c>
-      <c r="F117" s="117" t="s">
+    <row r="120" spans="1:6" ht="28">
+      <c r="A120" s="102" t="s">
+        <v>523</v>
+      </c>
+      <c r="B120" s="57" t="s">
+        <v>975</v>
+      </c>
+      <c r="C120" s="33" t="s">
+        <v>959</v>
+      </c>
+      <c r="D120" s="33" t="s">
+        <v>960</v>
+      </c>
+      <c r="E120" s="33" t="s">
+        <v>540</v>
+      </c>
+      <c r="F120" s="117" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="28">
-      <c r="A118" s="105" t="s">
-        <v>571</v>
-      </c>
-      <c r="B118" s="60" t="s">
-        <v>1046</v>
-      </c>
-      <c r="C118" s="61" t="s">
-        <v>589</v>
-      </c>
-      <c r="D118" s="61" t="s">
-        <v>1107</v>
-      </c>
-      <c r="E118" s="61" t="s">
-        <v>393</v>
-      </c>
-      <c r="F118" s="120" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" ht="28">
-      <c r="A119" s="106" t="s">
-        <v>571</v>
-      </c>
-      <c r="B119" s="63" t="s">
-        <v>591</v>
-      </c>
-      <c r="C119" s="20" t="s">
-        <v>592</v>
-      </c>
-      <c r="D119" s="20" t="s">
-        <v>593</v>
-      </c>
-      <c r="E119" s="20" t="s">
-        <v>425</v>
-      </c>
-      <c r="F119" s="121" t="s">
+    <row r="121" spans="1:6" ht="28">
+      <c r="A121" s="105" t="s">
+        <v>523</v>
+      </c>
+      <c r="B121" s="60" t="s">
+        <v>976</v>
+      </c>
+      <c r="C121" s="61" t="s">
+        <v>541</v>
+      </c>
+      <c r="D121" s="61" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E121" s="61" t="s">
+        <v>392</v>
+      </c>
+      <c r="F121" s="120" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" ht="28">
+      <c r="A122" s="106" t="s">
+        <v>523</v>
+      </c>
+      <c r="B122" s="63" t="s">
+        <v>543</v>
+      </c>
+      <c r="C122" s="20" t="s">
+        <v>544</v>
+      </c>
+      <c r="D122" s="20" t="s">
+        <v>545</v>
+      </c>
+      <c r="E122" s="20" t="s">
+        <v>424</v>
+      </c>
+      <c r="F122" s="121" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="28">
-      <c r="A120" s="109" t="s">
-        <v>571</v>
-      </c>
-      <c r="B120" s="65" t="s">
-        <v>466</v>
-      </c>
-      <c r="C120" s="249" t="s">
-        <v>1182</v>
-      </c>
-      <c r="D120" s="42" t="s">
-        <v>594</v>
-      </c>
-      <c r="E120" s="42" t="s">
-        <v>595</v>
-      </c>
-      <c r="F120" s="124" t="s">
+    <row r="123" spans="1:6" ht="28">
+      <c r="A123" s="109" t="s">
+        <v>523</v>
+      </c>
+      <c r="B123" s="65" t="s">
+        <v>458</v>
+      </c>
+      <c r="C123" s="194" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D123" s="42" t="s">
+        <v>546</v>
+      </c>
+      <c r="E123" s="42" t="s">
+        <v>547</v>
+      </c>
+      <c r="F123" s="124" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="140">
-      <c r="A121" s="99" t="s">
-        <v>571</v>
-      </c>
-      <c r="B121" s="54" t="s">
-        <v>596</v>
-      </c>
-      <c r="C121" s="15" t="s">
-        <v>859</v>
-      </c>
-      <c r="D121" s="15" t="s">
-        <v>860</v>
-      </c>
-      <c r="E121" s="15" t="s">
-        <v>861</v>
-      </c>
-      <c r="F121" s="85" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" ht="28">
-      <c r="A122" s="103" t="s">
-        <v>571</v>
-      </c>
-      <c r="B122" s="58" t="s">
-        <v>597</v>
-      </c>
-      <c r="C122" s="39" t="s">
-        <v>598</v>
-      </c>
-      <c r="D122" s="39" t="s">
-        <v>599</v>
-      </c>
-      <c r="E122" s="39" t="s">
-        <v>600</v>
-      </c>
-      <c r="F122" s="118" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" ht="28">
-      <c r="A123" s="101" t="s">
-        <v>571</v>
-      </c>
-      <c r="B123" s="56" t="s">
-        <v>601</v>
-      </c>
-      <c r="C123" s="10" t="s">
-        <v>602</v>
-      </c>
-      <c r="D123" s="10" t="s">
-        <v>603</v>
-      </c>
-      <c r="E123" s="10" t="s">
-        <v>483</v>
-      </c>
-      <c r="F123" s="116" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" ht="28">
-      <c r="A124" s="103" t="s">
-        <v>571</v>
-      </c>
-      <c r="B124" s="58" t="s">
-        <v>434</v>
-      </c>
-      <c r="C124" s="39" t="s">
-        <v>604</v>
-      </c>
-      <c r="D124" s="39" t="s">
-        <v>605</v>
-      </c>
-      <c r="E124" s="39" t="s">
-        <v>436</v>
-      </c>
-      <c r="F124" s="118" t="s">
-        <v>301</v>
+    <row r="124" spans="1:6" ht="140">
+      <c r="A124" s="99" t="s">
+        <v>523</v>
+      </c>
+      <c r="B124" s="54" t="s">
+        <v>548</v>
+      </c>
+      <c r="C124" s="15" t="s">
+        <v>798</v>
+      </c>
+      <c r="D124" s="15" t="s">
+        <v>799</v>
+      </c>
+      <c r="E124" s="15" t="s">
+        <v>800</v>
+      </c>
+      <c r="F124" s="85" t="s">
+        <v>801</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="28">
       <c r="A125" s="103" t="s">
+        <v>523</v>
+      </c>
+      <c r="B125" s="58" t="s">
+        <v>549</v>
+      </c>
+      <c r="C125" s="39" t="s">
+        <v>550</v>
+      </c>
+      <c r="D125" s="39" t="s">
+        <v>551</v>
+      </c>
+      <c r="E125" s="39" t="s">
+        <v>552</v>
+      </c>
+      <c r="F125" s="118" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" ht="28">
+      <c r="A126" s="101" t="s">
+        <v>523</v>
+      </c>
+      <c r="B126" s="56" t="s">
+        <v>553</v>
+      </c>
+      <c r="C126" s="10" t="s">
+        <v>554</v>
+      </c>
+      <c r="D126" s="10" t="s">
+        <v>555</v>
+      </c>
+      <c r="E126" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="F126" s="116" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" ht="28">
+      <c r="A127" s="103" t="s">
+        <v>523</v>
+      </c>
+      <c r="B127" s="58" t="s">
+        <v>432</v>
+      </c>
+      <c r="C127" s="39" t="s">
+        <v>556</v>
+      </c>
+      <c r="D127" s="39" t="s">
+        <v>557</v>
+      </c>
+      <c r="E127" s="39" t="s">
+        <v>434</v>
+      </c>
+      <c r="F127" s="118" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="28">
+      <c r="A128" s="103" t="s">
+        <v>523</v>
+      </c>
+      <c r="B128" s="58" t="s">
+        <v>432</v>
+      </c>
+      <c r="C128" s="39" t="s">
+        <v>558</v>
+      </c>
+      <c r="D128" s="39" t="s">
+        <v>559</v>
+      </c>
+      <c r="E128" s="39" t="s">
+        <v>434</v>
+      </c>
+      <c r="F128" s="118" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="238">
+      <c r="A129" s="103" t="s">
+        <v>523</v>
+      </c>
+      <c r="B129" s="155" t="s">
+        <v>432</v>
+      </c>
+      <c r="C129" s="195" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D129" s="39" t="s">
+        <v>806</v>
+      </c>
+      <c r="E129" s="39" t="s">
+        <v>807</v>
+      </c>
+      <c r="F129" s="118" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="28">
+      <c r="A130" s="104" t="s">
+        <v>523</v>
+      </c>
+      <c r="B130" s="59" t="s">
+        <v>432</v>
+      </c>
+      <c r="C130" s="186" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D130" s="47" t="s">
+        <v>739</v>
+      </c>
+      <c r="E130" s="47" t="s">
+        <v>434</v>
+      </c>
+      <c r="F130" s="119" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
+      <c r="A131" s="203" t="s">
+        <v>562</v>
+      </c>
+      <c r="B131" s="204"/>
+      <c r="C131" s="204"/>
+      <c r="D131" s="204"/>
+      <c r="E131" s="204"/>
+      <c r="F131" s="205"/>
+    </row>
+    <row r="132" spans="1:6" ht="28">
+      <c r="A132" s="101" t="s">
+        <v>563</v>
+      </c>
+      <c r="B132" s="56" t="s">
+        <v>564</v>
+      </c>
+      <c r="C132" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="D132" s="10" t="s">
+        <v>565</v>
+      </c>
+      <c r="E132" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="F132" s="116" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="28">
+      <c r="A133" s="100" t="s">
+        <v>563</v>
+      </c>
+      <c r="B133" s="55" t="s">
+        <v>566</v>
+      </c>
+      <c r="C133" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="D133" s="50" t="s">
+        <v>568</v>
+      </c>
+      <c r="E133" s="50" t="s">
+        <v>500</v>
+      </c>
+      <c r="F133" s="115" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" ht="28">
+      <c r="A134" s="100" t="s">
+        <v>563</v>
+      </c>
+      <c r="B134" s="55" t="s">
+        <v>570</v>
+      </c>
+      <c r="C134" s="50" t="s">
         <v>571</v>
       </c>
-      <c r="B125" s="58" t="s">
-        <v>434</v>
-      </c>
-      <c r="C125" s="39" t="s">
-        <v>606</v>
-      </c>
-      <c r="D125" s="39" t="s">
-        <v>607</v>
-      </c>
-      <c r="E125" s="39" t="s">
-        <v>436</v>
-      </c>
-      <c r="F125" s="118" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" ht="238">
-      <c r="A126" s="103" t="s">
-        <v>571</v>
-      </c>
-      <c r="B126" s="155" t="s">
-        <v>434</v>
-      </c>
-      <c r="C126" s="250" t="s">
-        <v>1183</v>
-      </c>
-      <c r="D126" s="39" t="s">
-        <v>868</v>
-      </c>
-      <c r="E126" s="39" t="s">
-        <v>869</v>
-      </c>
-      <c r="F126" s="118" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" ht="28">
-      <c r="A127" s="104" t="s">
-        <v>571</v>
-      </c>
-      <c r="B127" s="59" t="s">
-        <v>434</v>
-      </c>
-      <c r="C127" s="186" t="s">
-        <v>1184</v>
-      </c>
-      <c r="D127" s="47" t="s">
-        <v>794</v>
-      </c>
-      <c r="E127" s="47" t="s">
-        <v>436</v>
-      </c>
-      <c r="F127" s="119" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128" s="204" t="s">
-        <v>610</v>
-      </c>
-      <c r="B128" s="205"/>
-      <c r="C128" s="205"/>
-      <c r="D128" s="205"/>
-      <c r="E128" s="205"/>
-      <c r="F128" s="206"/>
-    </row>
-    <row r="129" spans="1:6" ht="28">
-      <c r="A129" s="101" t="s">
-        <v>611</v>
-      </c>
-      <c r="B129" s="56" t="s">
-        <v>612</v>
-      </c>
-      <c r="C129" s="10" t="s">
-        <v>540</v>
-      </c>
-      <c r="D129" s="10" t="s">
-        <v>613</v>
-      </c>
-      <c r="E129" s="10" t="s">
-        <v>443</v>
-      </c>
-      <c r="F129" s="116" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" ht="28">
-      <c r="A130" s="100" t="s">
-        <v>611</v>
-      </c>
-      <c r="B130" s="55" t="s">
-        <v>614</v>
-      </c>
-      <c r="C130" s="50" t="s">
-        <v>615</v>
-      </c>
-      <c r="D130" s="50" t="s">
-        <v>616</v>
-      </c>
-      <c r="E130" s="50" t="s">
-        <v>548</v>
-      </c>
-      <c r="F130" s="115" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" ht="28">
-      <c r="A131" s="100" t="s">
-        <v>611</v>
-      </c>
-      <c r="B131" s="55" t="s">
-        <v>618</v>
-      </c>
-      <c r="C131" s="50" t="s">
-        <v>619</v>
-      </c>
-      <c r="D131" s="50" t="s">
-        <v>620</v>
-      </c>
-      <c r="E131" s="50" t="s">
-        <v>621</v>
-      </c>
-      <c r="F131" s="115" t="s">
+      <c r="D134" s="50" t="s">
+        <v>572</v>
+      </c>
+      <c r="E134" s="50" t="s">
+        <v>573</v>
+      </c>
+      <c r="F134" s="115" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="132" spans="1:6" ht="28">
-      <c r="A132" s="100" t="s">
-        <v>611</v>
-      </c>
-      <c r="B132" s="55" t="s">
-        <v>622</v>
-      </c>
-      <c r="C132" s="50" t="s">
-        <v>623</v>
-      </c>
-      <c r="D132" s="50" t="s">
-        <v>624</v>
-      </c>
-      <c r="E132" s="50" t="s">
-        <v>625</v>
-      </c>
-      <c r="F132" s="115" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" ht="28">
-      <c r="A133" s="99" t="s">
-        <v>611</v>
-      </c>
-      <c r="B133" s="54" t="s">
-        <v>627</v>
-      </c>
-      <c r="C133" s="15" t="s">
-        <v>628</v>
-      </c>
-      <c r="D133" s="15" t="s">
-        <v>629</v>
-      </c>
-      <c r="E133" s="15" t="s">
+    <row r="135" spans="1:6" ht="28">
+      <c r="A135" s="100" t="s">
+        <v>563</v>
+      </c>
+      <c r="B135" s="55" t="s">
+        <v>574</v>
+      </c>
+      <c r="C135" s="50" t="s">
+        <v>575</v>
+      </c>
+      <c r="D135" s="50" t="s">
+        <v>576</v>
+      </c>
+      <c r="E135" s="50" t="s">
+        <v>577</v>
+      </c>
+      <c r="F135" s="115" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" ht="28">
+      <c r="A136" s="99" t="s">
+        <v>563</v>
+      </c>
+      <c r="B136" s="54" t="s">
+        <v>579</v>
+      </c>
+      <c r="C136" s="15" t="s">
+        <v>580</v>
+      </c>
+      <c r="D136" s="15" t="s">
+        <v>581</v>
+      </c>
+      <c r="E136" s="15" t="s">
         <v>354</v>
       </c>
-      <c r="F133" s="85" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" ht="28">
-      <c r="A134" s="98" t="s">
-        <v>611</v>
-      </c>
-      <c r="B134" s="53" t="s">
-        <v>630</v>
-      </c>
-      <c r="C134" s="5" t="s">
-        <v>631</v>
-      </c>
-      <c r="D134" s="5" t="s">
-        <v>632</v>
-      </c>
-      <c r="E134" s="5" t="s">
-        <v>633</v>
-      </c>
-      <c r="F134" s="114" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" ht="28">
-      <c r="A135" s="99" t="s">
-        <v>611</v>
-      </c>
-      <c r="B135" s="54" t="s">
-        <v>634</v>
-      </c>
-      <c r="C135" s="15" t="s">
-        <v>635</v>
-      </c>
-      <c r="D135" s="15" t="s">
-        <v>636</v>
-      </c>
-      <c r="E135" s="15" t="s">
-        <v>637</v>
-      </c>
-      <c r="F135" s="113" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" ht="28">
-      <c r="A136" s="98" t="s">
-        <v>611</v>
-      </c>
-      <c r="B136" s="53" t="s">
-        <v>638</v>
-      </c>
-      <c r="C136" s="5" t="s">
-        <v>639</v>
-      </c>
-      <c r="D136" s="5" t="s">
-        <v>640</v>
-      </c>
-      <c r="E136" s="5" t="s">
-        <v>641</v>
-      </c>
-      <c r="F136" s="114" t="s">
+      <c r="F136" s="85" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="28">
+      <c r="A137" s="98" t="s">
+        <v>563</v>
+      </c>
+      <c r="B137" s="53" t="s">
+        <v>582</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="D137" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="E137" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="F137" s="114" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="28">
+      <c r="A138" s="99" t="s">
+        <v>563</v>
+      </c>
+      <c r="B138" s="54" t="s">
+        <v>586</v>
+      </c>
+      <c r="C138" s="15" t="s">
+        <v>587</v>
+      </c>
+      <c r="D138" s="15" t="s">
+        <v>588</v>
+      </c>
+      <c r="E138" s="15" t="s">
+        <v>589</v>
+      </c>
+      <c r="F138" s="113" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" ht="28">
+      <c r="A139" s="98" t="s">
+        <v>563</v>
+      </c>
+      <c r="B139" s="53" t="s">
+        <v>590</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>592</v>
+      </c>
+      <c r="E139" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="F139" s="114" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="137" spans="1:6" ht="29" thickBot="1">
-      <c r="A137" s="112" t="s">
-        <v>611</v>
-      </c>
-      <c r="B137" s="96" t="s">
-        <v>399</v>
-      </c>
-      <c r="C137" s="97" t="s">
-        <v>642</v>
-      </c>
-      <c r="D137" s="97" t="s">
-        <v>643</v>
-      </c>
-      <c r="E137" s="97" t="s">
-        <v>644</v>
-      </c>
-      <c r="F137" s="127" t="s">
-        <v>645</v>
+    <row r="140" spans="1:6" ht="29" thickBot="1">
+      <c r="A140" s="112" t="s">
+        <v>563</v>
+      </c>
+      <c r="B140" s="96" t="s">
+        <v>398</v>
+      </c>
+      <c r="C140" s="97" t="s">
+        <v>594</v>
+      </c>
+      <c r="D140" s="97" t="s">
+        <v>595</v>
+      </c>
+      <c r="E140" s="97" t="s">
+        <v>596</v>
+      </c>
+      <c r="F140" s="127" t="s">
+        <v>597</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A71:F71"/>
-    <mergeCell ref="A92:F92"/>
-    <mergeCell ref="A110:F110"/>
-    <mergeCell ref="A128:F128"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="A95:F95"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A131:F131"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -16693,22 +16311,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="214" t="s">
-        <v>962</v>
-      </c>
-      <c r="B1" s="214"/>
-      <c r="C1" s="214"/>
-      <c r="D1" s="214"/>
-      <c r="E1" s="214"/>
+      <c r="A1" s="222" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B1" s="222"/>
+      <c r="C1" s="222"/>
+      <c r="D1" s="222"/>
+      <c r="E1" s="222"/>
     </row>
     <row r="3" spans="1:5" ht="24" customHeight="1">
-      <c r="A3" s="215" t="s">
-        <v>1001</v>
-      </c>
-      <c r="B3" s="215"/>
-      <c r="C3" s="215"/>
-      <c r="D3" s="215"/>
-      <c r="E3" s="215"/>
+      <c r="A3" s="223" t="s">
+        <v>933</v>
+      </c>
+      <c r="B3" s="223"/>
+      <c r="C3" s="223"/>
+      <c r="D3" s="223"/>
+      <c r="E3" s="223"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="12" t="s">
@@ -16732,13 +16350,13 @@
         <v>43</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1002</v>
+        <v>934</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>1000</v>
+        <v>932</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>1003</v>
+        <v>935</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>44</v>
@@ -16783,7 +16401,7 @@
         <v>54</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>846</v>
+        <v>787</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>55</v>
@@ -16800,13 +16418,13 @@
         <v>45</v>
       </c>
       <c r="B9" s="69" t="s">
-        <v>646</v>
+        <v>598</v>
       </c>
       <c r="C9" s="67" t="s">
-        <v>647</v>
+        <v>599</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>648</v>
+        <v>600</v>
       </c>
       <c r="E9" s="68" t="s">
         <v>162</v>
@@ -16817,13 +16435,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="69" t="s">
-        <v>649</v>
+        <v>601</v>
       </c>
       <c r="C10" s="67" t="s">
         <v>182</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>650</v>
+        <v>602</v>
       </c>
       <c r="E10" s="68" t="s">
         <v>53</v>
@@ -16868,30 +16486,30 @@
         <v>58</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>840</v>
+        <v>783</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>837</v>
+        <v>780</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>841</v>
+        <v>1196</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>842</v>
+        <v>784</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="42" customHeight="1">
       <c r="A14" s="20" t="s">
-        <v>843</v>
+        <v>785</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>844</v>
+        <v>786</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>839</v>
+        <v>782</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>845</v>
+        <v>1197</v>
       </c>
       <c r="E14" s="23" t="s">
         <v>62</v>
@@ -16899,19 +16517,19 @@
     </row>
     <row r="15" spans="1:5" ht="56" customHeight="1">
       <c r="A15" s="20" t="s">
-        <v>849</v>
+        <v>790</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>850</v>
+        <v>791</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>848</v>
+        <v>789</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>851</v>
+        <v>792</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>852</v>
+        <v>793</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="70" customHeight="1">
@@ -16919,30 +16537,30 @@
         <v>80</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>936</v>
+        <v>869</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>856</v>
+        <v>796</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>857</v>
+        <v>1198</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>858</v>
+        <v>797</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="62" customHeight="1">
       <c r="A17" s="20" t="s">
-        <v>902</v>
+        <v>838</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>937</v>
+        <v>870</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>909</v>
+        <v>845</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>910</v>
+        <v>846</v>
       </c>
       <c r="E17" s="23" t="s">
         <v>94</v>
@@ -16953,16 +16571,16 @@
         <v>45</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>938</v>
+        <v>871</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>911</v>
+        <v>847</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>912</v>
+        <v>848</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>903</v>
+        <v>839</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="62" customHeight="1">
@@ -16970,27 +16588,27 @@
         <v>45</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>939</v>
+        <v>872</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>913</v>
+        <v>849</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>914</v>
+        <v>850</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>903</v>
+        <v>839</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="30" customHeight="1"/>
     <row r="21" spans="1:5" ht="30" customHeight="1">
-      <c r="A21" s="211" t="s">
+      <c r="A21" s="219" t="s">
         <v>67</v>
       </c>
-      <c r="B21" s="211"/>
-      <c r="C21" s="211"/>
-      <c r="D21" s="211"/>
-      <c r="E21" s="211"/>
+      <c r="B21" s="219"/>
+      <c r="C21" s="219"/>
+      <c r="D21" s="219"/>
+      <c r="E21" s="219"/>
     </row>
     <row r="22" spans="1:5" ht="30" customHeight="1">
       <c r="A22" s="12" t="s">
@@ -17020,7 +16638,7 @@
         <v>29</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>897</v>
+        <v>833</v>
       </c>
       <c r="E23" s="18" t="s">
         <v>69</v>
@@ -17071,7 +16689,7 @@
         <v>82</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>899</v>
+        <v>835</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>83</v>
@@ -17082,13 +16700,13 @@
         <v>84</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>940</v>
+        <v>873</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>85</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>898</v>
+        <v>834</v>
       </c>
       <c r="E27" s="18" t="s">
         <v>86</v>
@@ -17099,13 +16717,13 @@
         <v>80</v>
       </c>
       <c r="B28" s="66" t="s">
-        <v>651</v>
+        <v>603</v>
       </c>
       <c r="C28" s="67" t="s">
-        <v>652</v>
+        <v>604</v>
       </c>
       <c r="D28" s="66" t="s">
-        <v>653</v>
+        <v>605</v>
       </c>
       <c r="E28" s="68" t="s">
         <v>202</v>
@@ -17133,13 +16751,13 @@
         <v>75</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>941</v>
+        <v>874</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>904</v>
+        <v>840</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>905</v>
+        <v>841</v>
       </c>
       <c r="E30" s="18" t="s">
         <v>189</v>
@@ -17150,278 +16768,278 @@
         <v>75</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>942</v>
+        <v>875</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>906</v>
+        <v>842</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>907</v>
+        <v>843</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="27.75" customHeight="1"/>
-    <row r="33" spans="1:5" ht="30" customHeight="1">
-      <c r="A33" s="213" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="62" customHeight="1">
+      <c r="A32" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>1193</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="30" customHeight="1"/>
+    <row r="34" spans="1:5" ht="30" customHeight="1">
+      <c r="A34" s="221" t="s">
         <v>91</v>
       </c>
-      <c r="B33" s="213"/>
-      <c r="C33" s="213"/>
-      <c r="D33" s="213"/>
-      <c r="E33" s="213"/>
-    </row>
-    <row r="34" spans="1:5" ht="30" customHeight="1">
-      <c r="A34" s="12" t="s">
+      <c r="B34" s="221"/>
+      <c r="C34" s="221"/>
+      <c r="D34" s="221"/>
+      <c r="E34" s="221"/>
+    </row>
+    <row r="35" spans="1:5" ht="27.75" customHeight="1">
+      <c r="A35" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B35" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C35" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D35" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E34" s="12" t="s">
+      <c r="E35" s="12" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A35" s="5" t="s">
+    <row r="36" spans="1:5" ht="28">
+      <c r="A36" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B36" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C36" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D36" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E36" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="15" t="s">
+    <row r="37" spans="1:5">
+      <c r="A37" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B37" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C37" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D36" s="15" t="s">
+      <c r="D37" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="E36" s="18" t="s">
+      <c r="E37" s="18" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B38" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C38" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D38" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E38" s="4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="28">
-      <c r="A38" s="15" t="s">
+    <row r="39" spans="1:5" ht="28">
+      <c r="A39" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B39" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="C39" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="D38" s="25" t="s">
+      <c r="D39" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="E38" s="18" t="s">
+      <c r="E39" s="18" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="28">
-      <c r="A39" s="5" t="s">
+    <row r="40" spans="1:5" ht="110" customHeight="1">
+      <c r="A40" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B40" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C40" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D40" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E40" s="4" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="110" customHeight="1">
-      <c r="A40" s="15" t="s">
+    <row r="41" spans="1:5" ht="130" customHeight="1">
+      <c r="A41" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="B41" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C41" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="D41" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="E40" s="18" t="s">
+      <c r="E41" s="18" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="130" customHeight="1">
-      <c r="A41" s="5" t="s">
+    <row r="42" spans="1:5" ht="150" customHeight="1">
+      <c r="A42" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="B42" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="C42" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="D41" s="24" t="s">
+      <c r="D42" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E42" s="4" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="150" customHeight="1">
-      <c r="A42" s="15" t="s">
+    <row r="43" spans="1:5" ht="28">
+      <c r="A43" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="B42" s="19" t="s">
+      <c r="B43" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C43" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="D43" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="E42" s="18" t="s">
+      <c r="E43" s="18" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="28">
-      <c r="A43" s="70" t="s">
+    <row r="44" spans="1:5" ht="28">
+      <c r="A44" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="B43" s="73" t="s">
-        <v>654</v>
-      </c>
-      <c r="C43" s="71" t="s">
+      <c r="B44" s="73" t="s">
+        <v>606</v>
+      </c>
+      <c r="C44" s="71" t="s">
         <v>233</v>
       </c>
-      <c r="D43" s="70" t="s">
-        <v>655</v>
-      </c>
-      <c r="E43" s="72" t="s">
+      <c r="D44" s="70" t="s">
+        <v>607</v>
+      </c>
+      <c r="E44" s="72" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="28">
-      <c r="A44" s="20" t="s">
+    <row r="45" spans="1:5" ht="28">
+      <c r="A45" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="B44" s="21" t="s">
+      <c r="B45" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="C44" s="22" t="s">
+      <c r="C45" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="D44" s="20" t="s">
+      <c r="D45" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="E44" s="23" t="s">
+      <c r="E45" s="23" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="140">
-      <c r="A45" s="20" t="s">
-        <v>863</v>
-      </c>
-      <c r="B45" s="21" t="s">
-        <v>864</v>
-      </c>
-      <c r="C45" s="22" t="s">
-        <v>865</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>866</v>
-      </c>
-      <c r="E45" s="23" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="154">
+    <row r="46" spans="1:5" ht="70">
       <c r="A46" s="20" t="s">
-        <v>863</v>
+        <v>802</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>880</v>
+        <v>803</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>881</v>
+        <v>804</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>882</v>
+        <v>1208</v>
       </c>
       <c r="E46" s="23" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="112">
+      <c r="A47" s="20" t="s">
+        <v>802</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>817</v>
+      </c>
+      <c r="C47" s="22" t="s">
+        <v>818</v>
+      </c>
+      <c r="D47" s="20" t="s">
+        <v>1209</v>
+      </c>
+      <c r="E47" s="23" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="154">
-      <c r="A47" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="B47" s="21" t="s">
-        <v>871</v>
-      </c>
-      <c r="C47" s="22" t="s">
-        <v>872</v>
-      </c>
-      <c r="D47" s="20" t="s">
-        <v>873</v>
-      </c>
-      <c r="E47" s="23" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="168">
+    <row r="48" spans="1:5" ht="154">
       <c r="A48" s="20" t="s">
         <v>58</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>874</v>
+        <v>809</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>875</v>
+        <v>810</v>
       </c>
       <c r="D48" s="20" t="s">
-        <v>876</v>
+        <v>811</v>
       </c>
       <c r="E48" s="23" t="s">
         <v>192</v>
@@ -17429,62 +17047,78 @@
     </row>
     <row r="49" spans="1:5" ht="62" customHeight="1">
       <c r="A49" s="20" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>943</v>
+        <v>812</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>900</v>
+        <v>813</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>901</v>
+        <v>814</v>
       </c>
       <c r="E49" s="23" t="s">
-        <v>896</v>
+        <v>192</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="62" customHeight="1">
       <c r="A50" s="20" t="s">
-        <v>902</v>
+        <v>75</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>944</v>
+        <v>876</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>919</v>
+        <v>836</v>
       </c>
       <c r="D50" s="20" t="s">
-        <v>920</v>
+        <v>837</v>
       </c>
       <c r="E50" s="23" t="s">
-        <v>57</v>
+        <v>832</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="62" customHeight="1">
       <c r="A51" s="20" t="s">
+        <v>838</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>877</v>
+      </c>
+      <c r="C51" s="22" t="s">
+        <v>855</v>
+      </c>
+      <c r="D51" s="20" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E51" s="23" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="62" customHeight="1">
+      <c r="A52" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="B51" s="21" t="s">
-        <v>945</v>
-      </c>
-      <c r="C51" s="22" t="s">
-        <v>931</v>
-      </c>
-      <c r="D51" s="20" t="s">
-        <v>932</v>
-      </c>
-      <c r="E51" s="23" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="62" customHeight="1"/>
+      <c r="B52" s="21" t="s">
+        <v>878</v>
+      </c>
+      <c r="C52" s="22" t="s">
+        <v>865</v>
+      </c>
+      <c r="D52" s="20" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E52" s="23" t="s">
+        <v>866</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A34:E34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -17508,24 +17142,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18">
-      <c r="A1" s="216" t="s">
-        <v>915</v>
-      </c>
-      <c r="B1" s="217"/>
-      <c r="C1" s="217"/>
-      <c r="D1" s="217"/>
-      <c r="E1" s="217"/>
-      <c r="F1" s="218"/>
+      <c r="A1" s="236" t="s">
+        <v>851</v>
+      </c>
+      <c r="B1" s="237"/>
+      <c r="C1" s="237"/>
+      <c r="D1" s="237"/>
+      <c r="E1" s="237"/>
+      <c r="F1" s="238"/>
     </row>
     <row r="2" spans="1:6" ht="41" customHeight="1">
-      <c r="A2" s="219" t="s">
-        <v>916</v>
-      </c>
-      <c r="B2" s="220"/>
-      <c r="C2" s="220"/>
-      <c r="D2" s="220"/>
-      <c r="E2" s="220"/>
-      <c r="F2" s="221"/>
+      <c r="A2" s="239" t="s">
+        <v>852</v>
+      </c>
+      <c r="B2" s="240"/>
+      <c r="C2" s="240"/>
+      <c r="D2" s="240"/>
+      <c r="E2" s="240"/>
+      <c r="F2" s="241"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="77" t="s">
@@ -17548,14 +17182,14 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="222" t="s">
-        <v>1004</v>
-      </c>
-      <c r="B4" s="223"/>
-      <c r="C4" s="223"/>
-      <c r="D4" s="223"/>
-      <c r="E4" s="223"/>
-      <c r="F4" s="224"/>
+      <c r="A4" s="233" t="s">
+        <v>936</v>
+      </c>
+      <c r="B4" s="234"/>
+      <c r="C4" s="234"/>
+      <c r="D4" s="234"/>
+      <c r="E4" s="234"/>
+      <c r="F4" s="235"/>
     </row>
     <row r="5" spans="1:6" ht="28">
       <c r="A5" s="78" t="s">
@@ -17565,16 +17199,16 @@
         <v>134</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1005</v>
+        <v>937</v>
       </c>
       <c r="D5" s="27" t="s">
         <v>135</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>1006</v>
+        <v>938</v>
       </c>
       <c r="F5" s="84" t="s">
-        <v>1007</v>
+        <v>939</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="28">
@@ -17585,16 +17219,16 @@
         <v>137</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>1008</v>
+        <v>940</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>1009</v>
+        <v>941</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>1010</v>
+        <v>942</v>
       </c>
       <c r="F6" s="85" t="s">
-        <v>968</v>
+        <v>900</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28">
@@ -17605,69 +17239,69 @@
         <v>139</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>1011</v>
+        <v>943</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>53</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>1012</v>
+        <v>944</v>
       </c>
       <c r="F7" s="86" t="s">
-        <v>1013</v>
+        <v>945</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="28">
       <c r="A8" s="81" t="s">
-        <v>656</v>
+        <v>608</v>
       </c>
       <c r="B8" s="75">
         <v>4.5</v>
       </c>
       <c r="C8" s="76" t="s">
-        <v>1014</v>
+        <v>946</v>
       </c>
       <c r="D8" s="75" t="s">
-        <v>657</v>
+        <v>609</v>
       </c>
       <c r="E8" s="76" t="s">
-        <v>1015</v>
+        <v>947</v>
       </c>
       <c r="F8" s="87" t="s">
-        <v>1016</v>
+        <v>948</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="28">
       <c r="A9" s="82" t="s">
-        <v>658</v>
+        <v>610</v>
       </c>
       <c r="B9" s="68">
         <v>4.5</v>
       </c>
       <c r="C9" s="66" t="s">
-        <v>1017</v>
+        <v>949</v>
       </c>
       <c r="D9" s="68" t="s">
-        <v>508</v>
+        <v>481</v>
       </c>
       <c r="E9" s="66" t="s">
-        <v>1018</v>
+        <v>950</v>
       </c>
       <c r="F9" s="88" t="s">
-        <v>1019</v>
+        <v>951</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="222" t="s">
+      <c r="A10" s="233" t="s">
         <v>141</v>
       </c>
-      <c r="B10" s="223"/>
-      <c r="C10" s="223"/>
-      <c r="D10" s="223"/>
-      <c r="E10" s="223"/>
-      <c r="F10" s="224"/>
-    </row>
-    <row r="11" spans="1:6" ht="70">
+      <c r="B10" s="234"/>
+      <c r="C10" s="234"/>
+      <c r="D10" s="234"/>
+      <c r="E10" s="234"/>
+      <c r="F10" s="235"/>
+    </row>
+    <row r="11" spans="1:6" ht="56">
       <c r="A11" s="78" t="s">
         <v>133</v>
       </c>
@@ -17681,7 +17315,7 @@
         <v>49</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>834</v>
+        <v>1201</v>
       </c>
       <c r="F11" s="84" t="s">
         <v>143</v>
@@ -17729,133 +17363,133 @@
     </row>
     <row r="14" spans="1:6" ht="28">
       <c r="A14" s="81" t="s">
-        <v>656</v>
+        <v>608</v>
       </c>
       <c r="B14" s="75">
         <v>4.8</v>
       </c>
       <c r="C14" s="76" t="s">
-        <v>659</v>
+        <v>611</v>
       </c>
       <c r="D14" s="75" t="s">
         <v>57</v>
       </c>
       <c r="E14" s="76" t="s">
-        <v>660</v>
+        <v>612</v>
       </c>
       <c r="F14" s="87" t="s">
-        <v>661</v>
+        <v>613</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28">
       <c r="A15" s="82" t="s">
-        <v>658</v>
+        <v>610</v>
       </c>
       <c r="B15" s="68">
         <v>4.5999999999999996</v>
       </c>
       <c r="C15" s="66" t="s">
-        <v>690</v>
+        <v>642</v>
       </c>
       <c r="D15" s="68" t="s">
         <v>98</v>
       </c>
       <c r="E15" s="66" t="s">
-        <v>691</v>
+        <v>643</v>
       </c>
       <c r="F15" s="88" t="s">
-        <v>692</v>
+        <v>644</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="42">
       <c r="A16" s="82" t="s">
-        <v>732</v>
+        <v>684</v>
       </c>
       <c r="B16" s="165" t="s">
-        <v>828</v>
+        <v>773</v>
       </c>
       <c r="C16" s="66" t="s">
-        <v>829</v>
+        <v>774</v>
       </c>
       <c r="D16" s="68" t="s">
-        <v>657</v>
+        <v>609</v>
       </c>
       <c r="E16" s="66" t="s">
-        <v>830</v>
+        <v>775</v>
       </c>
       <c r="F16" s="88" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="42">
       <c r="A17" s="82" t="s">
-        <v>735</v>
+        <v>687</v>
       </c>
       <c r="B17" s="165" t="s">
-        <v>831</v>
+        <v>776</v>
       </c>
       <c r="C17" s="66" t="s">
-        <v>832</v>
+        <v>777</v>
       </c>
       <c r="D17" s="68" t="s">
-        <v>817</v>
+        <v>762</v>
       </c>
       <c r="E17" s="66" t="s">
-        <v>833</v>
+        <v>778</v>
       </c>
       <c r="F17" s="88" t="s">
-        <v>692</v>
+        <v>644</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="56">
       <c r="A18" s="166" t="s">
-        <v>810</v>
+        <v>755</v>
       </c>
       <c r="B18" s="167" t="s">
         <v>216</v>
       </c>
       <c r="C18" s="168" t="s">
-        <v>946</v>
+        <v>879</v>
       </c>
       <c r="D18" s="169" t="s">
-        <v>903</v>
+        <v>839</v>
       </c>
       <c r="E18" s="168" t="s">
-        <v>924</v>
+        <v>859</v>
       </c>
       <c r="F18" s="170" t="s">
-        <v>911</v>
+        <v>847</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="70">
       <c r="A19" s="166" t="s">
-        <v>814</v>
+        <v>759</v>
       </c>
       <c r="B19" s="167" t="s">
         <v>216</v>
       </c>
       <c r="C19" s="168" t="s">
-        <v>947</v>
+        <v>880</v>
       </c>
       <c r="D19" s="169" t="s">
-        <v>903</v>
+        <v>839</v>
       </c>
       <c r="E19" s="168" t="s">
-        <v>925</v>
+        <v>860</v>
       </c>
       <c r="F19" s="170" t="s">
-        <v>913</v>
+        <v>849</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="222" t="s">
+      <c r="A20" s="233" t="s">
         <v>152</v>
       </c>
-      <c r="B20" s="223"/>
-      <c r="C20" s="223"/>
-      <c r="D20" s="223"/>
-      <c r="E20" s="223"/>
-      <c r="F20" s="224"/>
+      <c r="B20" s="234"/>
+      <c r="C20" s="234"/>
+      <c r="D20" s="234"/>
+      <c r="E20" s="234"/>
+      <c r="F20" s="235"/>
     </row>
     <row r="21" spans="1:6" ht="28">
       <c r="A21" s="78" t="s">
@@ -17865,7 +17499,7 @@
         <v>154</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>917</v>
+        <v>853</v>
       </c>
       <c r="D21" s="27" t="s">
         <v>57</v>
@@ -17925,13 +17559,13 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C24" s="76" t="s">
-        <v>710</v>
+        <v>662</v>
       </c>
       <c r="D24" s="75" t="s">
         <v>218</v>
       </c>
       <c r="E24" s="76" t="s">
-        <v>711</v>
+        <v>663</v>
       </c>
       <c r="F24" s="87" t="s">
         <v>255</v>
@@ -17939,33 +17573,33 @@
     </row>
     <row r="25" spans="1:6" ht="28">
       <c r="A25" s="82" t="s">
-        <v>656</v>
+        <v>608</v>
       </c>
       <c r="B25" s="68">
         <v>4.3</v>
       </c>
       <c r="C25" s="66" t="s">
-        <v>662</v>
+        <v>614</v>
       </c>
       <c r="D25" s="68" t="s">
         <v>218</v>
       </c>
       <c r="E25" s="66" t="s">
-        <v>663</v>
+        <v>615</v>
       </c>
       <c r="F25" s="88" t="s">
-        <v>664</v>
+        <v>616</v>
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="222" t="s">
+      <c r="A26" s="233" t="s">
         <v>165</v>
       </c>
-      <c r="B26" s="223"/>
-      <c r="C26" s="223"/>
-      <c r="D26" s="223"/>
-      <c r="E26" s="223"/>
-      <c r="F26" s="224"/>
+      <c r="B26" s="234"/>
+      <c r="C26" s="234"/>
+      <c r="D26" s="234"/>
+      <c r="E26" s="234"/>
+      <c r="F26" s="235"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="78" t="s">
@@ -17995,13 +17629,13 @@
         <v>137</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>948</v>
+        <v>881</v>
       </c>
       <c r="D28" s="18" t="s">
         <v>170</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>885</v>
+        <v>821</v>
       </c>
       <c r="F28" s="85" t="s">
         <v>171</v>
@@ -18029,53 +17663,53 @@
     </row>
     <row r="30" spans="1:6" ht="42">
       <c r="A30" s="81" t="s">
-        <v>656</v>
+        <v>608</v>
       </c>
       <c r="B30" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C30" s="76" t="s">
-        <v>949</v>
+        <v>882</v>
       </c>
       <c r="D30" s="75" t="s">
         <v>140</v>
       </c>
       <c r="E30" s="76" t="s">
-        <v>886</v>
+        <v>822</v>
       </c>
       <c r="F30" s="87" t="s">
-        <v>665</v>
+        <v>617</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="28">
       <c r="A31" s="82" t="s">
-        <v>658</v>
+        <v>610</v>
       </c>
       <c r="B31" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C31" s="66" t="s">
-        <v>693</v>
+        <v>645</v>
       </c>
       <c r="D31" s="68" t="s">
         <v>192</v>
       </c>
       <c r="E31" s="66" t="s">
-        <v>694</v>
+        <v>646</v>
       </c>
       <c r="F31" s="88" t="s">
-        <v>695</v>
+        <v>647</v>
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="222" t="s">
+      <c r="A32" s="233" t="s">
         <v>176</v>
       </c>
-      <c r="B32" s="223"/>
-      <c r="C32" s="223"/>
-      <c r="D32" s="223"/>
-      <c r="E32" s="223"/>
-      <c r="F32" s="224"/>
+      <c r="B32" s="234"/>
+      <c r="C32" s="234"/>
+      <c r="D32" s="234"/>
+      <c r="E32" s="234"/>
+      <c r="F32" s="235"/>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="78" t="s">
@@ -18125,33 +17759,33 @@
         <v>4.3</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>712</v>
+        <v>664</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>678</v>
+        <v>630</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>713</v>
+        <v>665</v>
       </c>
       <c r="F35" s="86" t="s">
-        <v>698</v>
+        <v>650</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="42">
       <c r="A36" s="81" t="s">
-        <v>656</v>
+        <v>608</v>
       </c>
       <c r="B36" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C36" s="76" t="s">
-        <v>666</v>
+        <v>618</v>
       </c>
       <c r="D36" s="75" t="s">
         <v>145</v>
       </c>
       <c r="E36" s="76" t="s">
-        <v>667</v>
+        <v>619</v>
       </c>
       <c r="F36" s="87" t="s">
         <v>182</v>
@@ -18159,33 +17793,33 @@
     </row>
     <row r="37" spans="1:6" ht="28">
       <c r="A37" s="82" t="s">
-        <v>658</v>
+        <v>610</v>
       </c>
       <c r="B37" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C37" s="66" t="s">
-        <v>696</v>
+        <v>648</v>
       </c>
       <c r="D37" s="68" t="s">
         <v>53</v>
       </c>
       <c r="E37" s="66" t="s">
-        <v>697</v>
+        <v>649</v>
       </c>
       <c r="F37" s="88" t="s">
-        <v>698</v>
+        <v>650</v>
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="225" t="s">
+      <c r="A38" s="230" t="s">
         <v>184</v>
       </c>
-      <c r="B38" s="226"/>
-      <c r="C38" s="226"/>
-      <c r="D38" s="226"/>
-      <c r="E38" s="226"/>
-      <c r="F38" s="227"/>
+      <c r="B38" s="231"/>
+      <c r="C38" s="231"/>
+      <c r="D38" s="231"/>
+      <c r="E38" s="231"/>
+      <c r="F38" s="232"/>
     </row>
     <row r="39" spans="1:6" ht="28">
       <c r="A39" s="78" t="s">
@@ -18195,16 +17829,16 @@
         <v>4.5</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>720</v>
+        <v>672</v>
       </c>
       <c r="D39" s="27" t="s">
         <v>192</v>
       </c>
       <c r="E39" s="28" t="s">
-        <v>721</v>
+        <v>673</v>
       </c>
       <c r="F39" s="84" t="s">
-        <v>722</v>
+        <v>674</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="42">
@@ -18215,13 +17849,13 @@
         <v>139</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>950</v>
+        <v>883</v>
       </c>
       <c r="D40" s="18" t="s">
         <v>162</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>892</v>
+        <v>828</v>
       </c>
       <c r="F40" s="85" t="s">
         <v>186</v>
@@ -18249,19 +17883,19 @@
     </row>
     <row r="42" spans="1:6" ht="28">
       <c r="A42" s="81" t="s">
-        <v>656</v>
+        <v>608</v>
       </c>
       <c r="B42" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C42" s="76" t="s">
-        <v>668</v>
+        <v>620</v>
       </c>
       <c r="D42" s="75" t="s">
         <v>189</v>
       </c>
       <c r="E42" s="76" t="s">
-        <v>669</v>
+        <v>621</v>
       </c>
       <c r="F42" s="87" t="s">
         <v>82</v>
@@ -18269,33 +17903,33 @@
     </row>
     <row r="43" spans="1:6" ht="28">
       <c r="A43" s="82" t="s">
-        <v>658</v>
+        <v>610</v>
       </c>
       <c r="B43" s="68">
         <v>4.3</v>
       </c>
       <c r="C43" s="66" t="s">
-        <v>699</v>
+        <v>651</v>
       </c>
       <c r="D43" s="68" t="s">
         <v>195</v>
       </c>
       <c r="E43" s="66" t="s">
-        <v>700</v>
+        <v>652</v>
       </c>
       <c r="F43" s="88" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="225" t="s">
+      <c r="A44" s="230" t="s">
         <v>191</v>
       </c>
-      <c r="B44" s="226"/>
-      <c r="C44" s="226"/>
-      <c r="D44" s="226"/>
-      <c r="E44" s="226"/>
-      <c r="F44" s="227"/>
+      <c r="B44" s="231"/>
+      <c r="C44" s="231"/>
+      <c r="D44" s="231"/>
+      <c r="E44" s="231"/>
+      <c r="F44" s="232"/>
     </row>
     <row r="45" spans="1:6" ht="84">
       <c r="A45" s="78" t="s">
@@ -18305,13 +17939,13 @@
         <v>137</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>883</v>
+        <v>819</v>
       </c>
       <c r="D45" s="27" t="s">
         <v>192</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>884</v>
+        <v>820</v>
       </c>
       <c r="F45" s="84" t="s">
         <v>193</v>
@@ -18345,13 +17979,13 @@
         <v>134</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>951</v>
+        <v>884</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>198</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>887</v>
+        <v>823</v>
       </c>
       <c r="F47" s="86" t="s">
         <v>29</v>
@@ -18359,19 +17993,19 @@
     </row>
     <row r="48" spans="1:6" ht="42">
       <c r="A48" s="81" t="s">
-        <v>656</v>
+        <v>608</v>
       </c>
       <c r="B48" s="75">
         <v>4.5</v>
       </c>
       <c r="C48" s="76" t="s">
-        <v>952</v>
+        <v>885</v>
       </c>
       <c r="D48" s="75" t="s">
         <v>79</v>
       </c>
       <c r="E48" s="76" t="s">
-        <v>893</v>
+        <v>829</v>
       </c>
       <c r="F48" s="87" t="s">
         <v>197</v>
@@ -18379,53 +18013,53 @@
     </row>
     <row r="49" spans="1:6" ht="28">
       <c r="A49" s="82" t="s">
-        <v>658</v>
+        <v>610</v>
       </c>
       <c r="B49" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C49" s="66" t="s">
-        <v>670</v>
+        <v>622</v>
       </c>
       <c r="D49" s="68" t="s">
-        <v>671</v>
+        <v>623</v>
       </c>
       <c r="E49" s="66" t="s">
-        <v>672</v>
+        <v>624</v>
       </c>
       <c r="F49" s="88" t="s">
-        <v>673</v>
+        <v>625</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="84">
       <c r="A50" s="166" t="s">
-        <v>732</v>
+        <v>684</v>
       </c>
       <c r="B50" s="169" t="s">
         <v>216</v>
       </c>
       <c r="C50" s="168" t="s">
-        <v>953</v>
+        <v>886</v>
       </c>
       <c r="D50" s="169" t="s">
-        <v>908</v>
+        <v>844</v>
       </c>
       <c r="E50" s="168" t="s">
-        <v>926</v>
+        <v>861</v>
       </c>
       <c r="F50" s="170" t="s">
-        <v>906</v>
+        <v>842</v>
       </c>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="225" t="s">
+      <c r="A51" s="230" t="s">
         <v>199</v>
       </c>
-      <c r="B51" s="226"/>
-      <c r="C51" s="226"/>
-      <c r="D51" s="226"/>
-      <c r="E51" s="226"/>
-      <c r="F51" s="227"/>
+      <c r="B51" s="231"/>
+      <c r="C51" s="231"/>
+      <c r="D51" s="231"/>
+      <c r="E51" s="231"/>
+      <c r="F51" s="232"/>
     </row>
     <row r="52" spans="1:6" ht="56">
       <c r="A52" s="78" t="s">
@@ -18435,13 +18069,13 @@
         <v>187</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>954</v>
+        <v>887</v>
       </c>
       <c r="D52" s="27" t="s">
         <v>140</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>889</v>
+        <v>825</v>
       </c>
       <c r="F52" s="84" t="s">
         <v>200</v>
@@ -18475,87 +18109,87 @@
         <v>4.5</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>714</v>
+        <v>666</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>192</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>715</v>
+        <v>667</v>
       </c>
       <c r="F54" s="86" t="s">
-        <v>716</v>
+        <v>668</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="28">
       <c r="A55" s="81" t="s">
-        <v>656</v>
+        <v>608</v>
       </c>
       <c r="B55" s="75">
         <v>4.7</v>
       </c>
       <c r="C55" s="76" t="s">
-        <v>674</v>
+        <v>626</v>
       </c>
       <c r="D55" s="75" t="s">
         <v>57</v>
       </c>
       <c r="E55" s="76" t="s">
-        <v>675</v>
+        <v>627</v>
       </c>
       <c r="F55" s="87" t="s">
-        <v>676</v>
+        <v>628</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="28">
       <c r="A56" s="81" t="s">
-        <v>658</v>
+        <v>610</v>
       </c>
       <c r="B56" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C56" s="76" t="s">
-        <v>677</v>
+        <v>629</v>
       </c>
       <c r="D56" s="75" t="s">
-        <v>678</v>
+        <v>630</v>
       </c>
       <c r="E56" s="76" t="s">
-        <v>679</v>
+        <v>631</v>
       </c>
       <c r="F56" s="87" t="s">
-        <v>680</v>
+        <v>632</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="84">
       <c r="A57" s="171" t="s">
-        <v>732</v>
+        <v>684</v>
       </c>
       <c r="B57" s="172" t="s">
         <v>216</v>
       </c>
       <c r="C57" s="173" t="s">
-        <v>955</v>
+        <v>888</v>
       </c>
       <c r="D57" s="172" t="s">
         <v>189</v>
       </c>
       <c r="E57" s="173" t="s">
-        <v>927</v>
+        <v>862</v>
       </c>
       <c r="F57" s="174" t="s">
-        <v>904</v>
+        <v>840</v>
       </c>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="225" t="s">
+      <c r="A58" s="230" t="s">
         <v>205</v>
       </c>
-      <c r="B58" s="226"/>
-      <c r="C58" s="226"/>
-      <c r="D58" s="226"/>
-      <c r="E58" s="226"/>
-      <c r="F58" s="227"/>
+      <c r="B58" s="231"/>
+      <c r="C58" s="231"/>
+      <c r="D58" s="231"/>
+      <c r="E58" s="231"/>
+      <c r="F58" s="232"/>
     </row>
     <row r="59" spans="1:6" ht="28">
       <c r="A59" s="78" t="s">
@@ -18585,13 +18219,13 @@
         <v>134</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>956</v>
+        <v>889</v>
       </c>
       <c r="D60" s="18" t="s">
         <v>198</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>888</v>
+        <v>824</v>
       </c>
       <c r="F60" s="85" t="s">
         <v>29</v>
@@ -18605,13 +18239,13 @@
         <v>139</v>
       </c>
       <c r="C61" s="29" t="s">
-        <v>957</v>
+        <v>890</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>140</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>890</v>
+        <v>826</v>
       </c>
       <c r="F61" s="86" t="s">
         <v>209</v>
@@ -18619,53 +18253,53 @@
     </row>
     <row r="62" spans="1:6" ht="28">
       <c r="A62" s="81" t="s">
-        <v>656</v>
+        <v>608</v>
       </c>
       <c r="B62" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C62" s="74" t="s">
-        <v>701</v>
+        <v>653</v>
       </c>
       <c r="D62" s="75" t="s">
         <v>192</v>
       </c>
       <c r="E62" s="76" t="s">
-        <v>702</v>
+        <v>654</v>
       </c>
       <c r="F62" s="87" t="s">
-        <v>703</v>
+        <v>655</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="28">
       <c r="A63" s="82" t="s">
-        <v>658</v>
+        <v>610</v>
       </c>
       <c r="B63" s="68">
         <v>4.5999999999999996</v>
       </c>
       <c r="C63" s="69" t="s">
-        <v>681</v>
+        <v>633</v>
       </c>
       <c r="D63" s="68" t="s">
         <v>44</v>
       </c>
       <c r="E63" s="66" t="s">
-        <v>682</v>
+        <v>634</v>
       </c>
       <c r="F63" s="88" t="s">
-        <v>683</v>
+        <v>635</v>
       </c>
     </row>
     <row r="64" spans="1:6">
-      <c r="A64" s="225" t="s">
+      <c r="A64" s="230" t="s">
         <v>210</v>
       </c>
-      <c r="B64" s="226"/>
-      <c r="C64" s="226"/>
-      <c r="D64" s="226"/>
-      <c r="E64" s="226"/>
-      <c r="F64" s="227"/>
+      <c r="B64" s="231"/>
+      <c r="C64" s="231"/>
+      <c r="D64" s="231"/>
+      <c r="E64" s="231"/>
+      <c r="F64" s="232"/>
     </row>
     <row r="65" spans="1:6" ht="28">
       <c r="A65" s="78" t="s">
@@ -18695,13 +18329,13 @@
         <v>137</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>958</v>
+        <v>891</v>
       </c>
       <c r="D66" s="18" t="s">
         <v>86</v>
       </c>
       <c r="E66" s="25" t="s">
-        <v>891</v>
+        <v>827</v>
       </c>
       <c r="F66" s="85" t="s">
         <v>85</v>
@@ -18728,14 +18362,14 @@
       </c>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="228" t="s">
+      <c r="A68" s="224" t="s">
         <v>221</v>
       </c>
-      <c r="B68" s="229"/>
-      <c r="C68" s="229"/>
-      <c r="D68" s="229"/>
-      <c r="E68" s="229"/>
-      <c r="F68" s="230"/>
+      <c r="B68" s="225"/>
+      <c r="C68" s="225"/>
+      <c r="D68" s="225"/>
+      <c r="E68" s="225"/>
+      <c r="F68" s="226"/>
     </row>
     <row r="69" spans="1:6" ht="70">
       <c r="A69" s="78" t="s">
@@ -18751,7 +18385,7 @@
         <v>102</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>835</v>
+        <v>1202</v>
       </c>
       <c r="F69" s="84" t="s">
         <v>100</v>
@@ -18765,13 +18399,13 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>704</v>
+        <v>656</v>
       </c>
       <c r="D70" s="18" t="s">
         <v>195</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>719</v>
+        <v>671</v>
       </c>
       <c r="F70" s="85" t="s">
         <v>239</v>
@@ -18799,19 +18433,19 @@
     </row>
     <row r="72" spans="1:6" ht="28">
       <c r="A72" s="81" t="s">
-        <v>656</v>
+        <v>608</v>
       </c>
       <c r="B72" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C72" s="76" t="s">
-        <v>708</v>
+        <v>660</v>
       </c>
       <c r="D72" s="75" t="s">
-        <v>678</v>
+        <v>630</v>
       </c>
       <c r="E72" s="76" t="s">
-        <v>709</v>
+        <v>661</v>
       </c>
       <c r="F72" s="87" t="s">
         <v>239</v>
@@ -18819,39 +18453,39 @@
     </row>
     <row r="73" spans="1:6" ht="70">
       <c r="A73" s="82" t="s">
-        <v>658</v>
+        <v>610</v>
       </c>
       <c r="B73" s="68">
         <v>4.3</v>
       </c>
       <c r="C73" s="66" t="s">
-        <v>959</v>
+        <v>892</v>
       </c>
       <c r="D73" s="68" t="s">
-        <v>896</v>
+        <v>832</v>
       </c>
       <c r="E73" s="66" t="s">
-        <v>894</v>
+        <v>830</v>
       </c>
       <c r="F73" s="88" t="s">
-        <v>895</v>
+        <v>831</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="28">
       <c r="A74" s="81" t="s">
-        <v>732</v>
+        <v>684</v>
       </c>
       <c r="B74" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C74" s="76" t="s">
-        <v>733</v>
+        <v>685</v>
       </c>
       <c r="D74" s="75" t="s">
         <v>110</v>
       </c>
       <c r="E74" s="76" t="s">
-        <v>734</v>
+        <v>686</v>
       </c>
       <c r="F74" s="87" t="s">
         <v>108</v>
@@ -18859,39 +18493,39 @@
     </row>
     <row r="75" spans="1:6" ht="28">
       <c r="A75" s="82" t="s">
-        <v>735</v>
+        <v>687</v>
       </c>
       <c r="B75" s="68">
         <v>4.5</v>
       </c>
       <c r="C75" s="66" t="s">
-        <v>736</v>
+        <v>688</v>
       </c>
       <c r="D75" s="68" t="s">
         <v>86</v>
       </c>
       <c r="E75" s="66" t="s">
-        <v>737</v>
+        <v>689</v>
       </c>
       <c r="F75" s="88" t="s">
-        <v>738</v>
+        <v>690</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="42">
       <c r="A76" s="82" t="s">
-        <v>810</v>
+        <v>755</v>
       </c>
       <c r="B76" s="165" t="s">
-        <v>820</v>
+        <v>765</v>
       </c>
       <c r="C76" s="66" t="s">
-        <v>821</v>
+        <v>766</v>
       </c>
       <c r="D76" s="68" t="s">
-        <v>822</v>
+        <v>767</v>
       </c>
       <c r="E76" s="66" t="s">
-        <v>823</v>
+        <v>768</v>
       </c>
       <c r="F76" s="88" t="s">
         <v>245</v>
@@ -18899,33 +18533,33 @@
     </row>
     <row r="77" spans="1:6" ht="42">
       <c r="A77" s="82" t="s">
-        <v>814</v>
+        <v>759</v>
       </c>
       <c r="B77" s="165" t="s">
-        <v>824</v>
+        <v>769</v>
       </c>
       <c r="C77" s="66" t="s">
-        <v>825</v>
+        <v>770</v>
       </c>
       <c r="D77" s="68" t="s">
-        <v>817</v>
+        <v>762</v>
       </c>
       <c r="E77" s="66" t="s">
-        <v>826</v>
+        <v>771</v>
       </c>
       <c r="F77" s="88" t="s">
-        <v>827</v>
+        <v>772</v>
       </c>
     </row>
     <row r="78" spans="1:6">
-      <c r="A78" s="228" t="s">
+      <c r="A78" s="224" t="s">
         <v>227</v>
       </c>
-      <c r="B78" s="229"/>
-      <c r="C78" s="229"/>
-      <c r="D78" s="229"/>
-      <c r="E78" s="229"/>
-      <c r="F78" s="230"/>
+      <c r="B78" s="225"/>
+      <c r="C78" s="225"/>
+      <c r="D78" s="225"/>
+      <c r="E78" s="225"/>
+      <c r="F78" s="226"/>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="78" t="s">
@@ -18989,19 +18623,19 @@
     </row>
     <row r="82" spans="1:6" ht="28">
       <c r="A82" s="81" t="s">
-        <v>656</v>
+        <v>608</v>
       </c>
       <c r="B82" s="75">
         <v>4.3</v>
       </c>
       <c r="C82" s="76" t="s">
-        <v>717</v>
+        <v>669</v>
       </c>
       <c r="D82" s="75" t="s">
         <v>192</v>
       </c>
       <c r="E82" s="76" t="s">
-        <v>718</v>
+        <v>670</v>
       </c>
       <c r="F82" s="87" t="s">
         <v>233</v>
@@ -19009,19 +18643,19 @@
     </row>
     <row r="83" spans="1:6" ht="28">
       <c r="A83" s="82" t="s">
-        <v>658</v>
+        <v>610</v>
       </c>
       <c r="B83" s="68">
         <v>4</v>
       </c>
       <c r="C83" s="66" t="s">
-        <v>685</v>
+        <v>637</v>
       </c>
       <c r="D83" s="68" t="s">
-        <v>686</v>
+        <v>638</v>
       </c>
       <c r="E83" s="66" t="s">
-        <v>687</v>
+        <v>639</v>
       </c>
       <c r="F83" s="88" t="s">
         <v>233</v>
@@ -19029,22 +18663,22 @@
     </row>
     <row r="84" spans="1:6" ht="70">
       <c r="A84" s="161" t="s">
-        <v>732</v>
+        <v>684</v>
       </c>
       <c r="B84" s="162">
         <v>4.5999999999999996</v>
       </c>
       <c r="C84" s="163" t="s">
-        <v>921</v>
+        <v>856</v>
       </c>
       <c r="D84" s="162" t="s">
         <v>167</v>
       </c>
       <c r="E84" s="163" t="s">
-        <v>922</v>
+        <v>857</v>
       </c>
       <c r="F84" s="164" t="s">
-        <v>923</v>
+        <v>858</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="140">
@@ -19055,27 +18689,27 @@
         <v>4.8</v>
       </c>
       <c r="C85" s="181" t="s">
-        <v>960</v>
+        <v>893</v>
       </c>
       <c r="D85" s="180" t="s">
         <v>57</v>
       </c>
       <c r="E85" s="181" t="s">
-        <v>928</v>
+        <v>1203</v>
       </c>
       <c r="F85" s="182" t="s">
-        <v>918</v>
+        <v>854</v>
       </c>
     </row>
     <row r="86" spans="1:6">
-      <c r="A86" s="228" t="s">
+      <c r="A86" s="224" t="s">
         <v>235</v>
       </c>
-      <c r="B86" s="229"/>
-      <c r="C86" s="229"/>
-      <c r="D86" s="229"/>
-      <c r="E86" s="229"/>
-      <c r="F86" s="230"/>
+      <c r="B86" s="225"/>
+      <c r="C86" s="225"/>
+      <c r="D86" s="225"/>
+      <c r="E86" s="225"/>
+      <c r="F86" s="226"/>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="78" t="s">
@@ -19105,13 +18739,13 @@
         <v>4.2</v>
       </c>
       <c r="C88" s="16" t="s">
-        <v>706</v>
+        <v>658</v>
       </c>
       <c r="D88" s="18" t="s">
         <v>106</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>707</v>
+        <v>659</v>
       </c>
       <c r="F88" s="85" t="s">
         <v>239</v>
@@ -19125,13 +18759,13 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>723</v>
+        <v>675</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>192</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>724</v>
+        <v>676</v>
       </c>
       <c r="F89" s="86" t="s">
         <v>239</v>
@@ -19139,19 +18773,19 @@
     </row>
     <row r="90" spans="1:6" ht="28">
       <c r="A90" s="81" t="s">
-        <v>656</v>
+        <v>608</v>
       </c>
       <c r="B90" s="75">
         <v>4.3</v>
       </c>
       <c r="C90" s="76" t="s">
-        <v>684</v>
+        <v>636</v>
       </c>
       <c r="D90" s="75" t="s">
         <v>106</v>
       </c>
       <c r="E90" s="76" t="s">
-        <v>705</v>
+        <v>657</v>
       </c>
       <c r="F90" s="87" t="s">
         <v>239</v>
@@ -19159,19 +18793,19 @@
     </row>
     <row r="91" spans="1:6" ht="28">
       <c r="A91" s="82" t="s">
-        <v>658</v>
+        <v>610</v>
       </c>
       <c r="B91" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C91" s="66" t="s">
-        <v>725</v>
+        <v>677</v>
       </c>
       <c r="D91" s="68" t="s">
-        <v>726</v>
+        <v>678</v>
       </c>
       <c r="E91" s="66" t="s">
-        <v>727</v>
+        <v>679</v>
       </c>
       <c r="F91" s="88" t="s">
         <v>245</v>
@@ -19179,19 +18813,19 @@
     </row>
     <row r="92" spans="1:6" ht="28">
       <c r="A92" s="81" t="s">
-        <v>732</v>
+        <v>684</v>
       </c>
       <c r="B92" s="75">
         <v>4.5999999999999996</v>
       </c>
       <c r="C92" s="76" t="s">
-        <v>739</v>
+        <v>691</v>
       </c>
       <c r="D92" s="75" t="s">
         <v>115</v>
       </c>
       <c r="E92" s="76" t="s">
-        <v>740</v>
+        <v>692</v>
       </c>
       <c r="F92" s="87" t="s">
         <v>239</v>
@@ -19199,19 +18833,19 @@
     </row>
     <row r="93" spans="1:6" ht="28">
       <c r="A93" s="166" t="s">
-        <v>735</v>
+        <v>687</v>
       </c>
       <c r="B93" s="169" t="s">
         <v>216</v>
       </c>
       <c r="C93" s="168" t="s">
-        <v>741</v>
+        <v>693</v>
       </c>
       <c r="D93" s="169" t="s">
         <v>246</v>
       </c>
       <c r="E93" s="168" t="s">
-        <v>742</v>
+        <v>694</v>
       </c>
       <c r="F93" s="170" t="s">
         <v>100</v>
@@ -19219,19 +18853,19 @@
     </row>
     <row r="94" spans="1:6" ht="42">
       <c r="A94" s="82" t="s">
-        <v>810</v>
+        <v>755</v>
       </c>
       <c r="B94" s="165" t="s">
-        <v>811</v>
+        <v>756</v>
       </c>
       <c r="C94" s="66" t="s">
-        <v>812</v>
+        <v>757</v>
       </c>
       <c r="D94" s="68" t="s">
         <v>167</v>
       </c>
       <c r="E94" s="66" t="s">
-        <v>813</v>
+        <v>758</v>
       </c>
       <c r="F94" s="88" t="s">
         <v>226</v>
@@ -19239,53 +18873,53 @@
     </row>
     <row r="95" spans="1:6" ht="42">
       <c r="A95" s="82" t="s">
-        <v>814</v>
+        <v>759</v>
       </c>
       <c r="B95" s="165" t="s">
-        <v>815</v>
+        <v>760</v>
       </c>
       <c r="C95" s="66" t="s">
-        <v>816</v>
+        <v>761</v>
       </c>
       <c r="D95" s="68" t="s">
-        <v>817</v>
+        <v>762</v>
       </c>
       <c r="E95" s="66" t="s">
-        <v>818</v>
+        <v>763</v>
       </c>
       <c r="F95" s="88" t="s">
-        <v>819</v>
+        <v>764</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="70">
       <c r="A96" s="82" t="s">
-        <v>934</v>
+        <v>867</v>
       </c>
       <c r="B96" s="184">
         <v>4.5</v>
       </c>
       <c r="C96" s="66" t="s">
-        <v>961</v>
+        <v>894</v>
       </c>
       <c r="D96" s="68" t="s">
         <v>145</v>
       </c>
       <c r="E96" s="66" t="s">
-        <v>935</v>
+        <v>868</v>
       </c>
       <c r="F96" s="88" t="s">
-        <v>931</v>
+        <v>865</v>
       </c>
     </row>
     <row r="97" spans="1:6">
-      <c r="A97" s="228" t="s">
+      <c r="A97" s="224" t="s">
         <v>241</v>
       </c>
-      <c r="B97" s="229"/>
-      <c r="C97" s="229"/>
-      <c r="D97" s="229"/>
-      <c r="E97" s="229"/>
-      <c r="F97" s="230"/>
+      <c r="B97" s="225"/>
+      <c r="C97" s="225"/>
+      <c r="D97" s="225"/>
+      <c r="E97" s="225"/>
+      <c r="F97" s="226"/>
     </row>
     <row r="98" spans="1:6" ht="84">
       <c r="A98" s="78" t="s">
@@ -19295,13 +18929,13 @@
         <v>5</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>929</v>
+        <v>863</v>
       </c>
       <c r="D98" s="27" t="s">
         <v>57</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>930</v>
+        <v>864</v>
       </c>
       <c r="F98" s="84" t="s">
         <v>242</v>
@@ -19335,50 +18969,60 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C100" s="76" t="s">
-        <v>728</v>
+        <v>680</v>
       </c>
       <c r="D100" s="75" t="s">
-        <v>729</v>
+        <v>681</v>
       </c>
       <c r="E100" s="76" t="s">
-        <v>730</v>
+        <v>682</v>
       </c>
       <c r="F100" s="87" t="s">
-        <v>731</v>
+        <v>683</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="28">
       <c r="A101" s="82" t="s">
-        <v>656</v>
+        <v>608</v>
       </c>
       <c r="B101" s="68">
         <v>4.5</v>
       </c>
       <c r="C101" s="66" t="s">
-        <v>688</v>
+        <v>640</v>
       </c>
       <c r="D101" s="68" t="s">
         <v>106</v>
       </c>
       <c r="E101" s="66" t="s">
-        <v>689</v>
+        <v>641</v>
       </c>
       <c r="F101" s="88" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="68" customHeight="1" thickBot="1">
-      <c r="A102" s="231" t="s">
-        <v>963</v>
-      </c>
-      <c r="B102" s="232"/>
-      <c r="C102" s="232"/>
-      <c r="D102" s="232"/>
-      <c r="E102" s="232"/>
-      <c r="F102" s="233"/>
+      <c r="A102" s="227" t="s">
+        <v>895</v>
+      </c>
+      <c r="B102" s="228"/>
+      <c r="C102" s="228"/>
+      <c r="D102" s="228"/>
+      <c r="E102" s="228"/>
+      <c r="F102" s="229"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A51:F51"/>
     <mergeCell ref="A97:F97"/>
     <mergeCell ref="A102:F102"/>
     <mergeCell ref="A58:F58"/>
@@ -19386,16 +19030,6 @@
     <mergeCell ref="A68:F68"/>
     <mergeCell ref="A78:F78"/>
     <mergeCell ref="A86:F86"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A44:F44"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -19417,12 +19051,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1">
-      <c r="A1" s="189" t="s">
+      <c r="A1" s="206" t="s">
         <v>247</v>
       </c>
-      <c r="B1" s="190"/>
-      <c r="C1" s="190"/>
-      <c r="D1" s="191"/>
+      <c r="B1" s="207"/>
+      <c r="C1" s="207"/>
+      <c r="D1" s="208"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="132"/>
@@ -19431,12 +19065,12 @@
       <c r="D2" s="142"/>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
-      <c r="A3" s="234" t="s">
+      <c r="A3" s="242" t="s">
         <v>248</v>
       </c>
-      <c r="B3" s="235"/>
-      <c r="C3" s="235"/>
-      <c r="D3" s="236"/>
+      <c r="B3" s="243"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="244"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="133" t="s">
@@ -19457,13 +19091,13 @@
         <v>252</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>1020</v>
+        <v>952</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>1021</v>
+        <v>953</v>
       </c>
       <c r="D5" s="144" t="s">
-        <v>1022</v>
+        <v>954</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="27.75" customHeight="1">
@@ -19499,7 +19133,7 @@
         <v>261</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>846</v>
+        <v>787</v>
       </c>
       <c r="C8" s="41" t="s">
         <v>262</v>
@@ -19524,16 +19158,16 @@
     </row>
     <row r="10" spans="1:4" ht="45" customHeight="1">
       <c r="A10" s="138" t="s">
-        <v>766</v>
+        <v>712</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>1047</v>
+        <v>977</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>1048</v>
+        <v>978</v>
       </c>
       <c r="D10" s="148" t="s">
-        <v>1049</v>
+        <v>979</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="45" customHeight="1">
@@ -19541,13 +19175,13 @@
         <v>264</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>1050</v>
+        <v>980</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>1051</v>
+        <v>981</v>
       </c>
       <c r="D11" s="148" t="s">
-        <v>1052</v>
+        <v>982</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="45" customHeight="1">
@@ -19555,13 +19189,13 @@
         <v>253</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>1053</v>
+        <v>983</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>1054</v>
+        <v>984</v>
       </c>
       <c r="D12" s="148" t="s">
-        <v>1055</v>
+        <v>985</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="45" customHeight="1">
@@ -19569,13 +19203,13 @@
         <v>288</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>1056</v>
+        <v>986</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>1057</v>
+        <v>987</v>
       </c>
       <c r="D13" s="148" t="s">
-        <v>1058</v>
+        <v>988</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1">
@@ -19585,12 +19219,12 @@
       <c r="D14" s="142"/>
     </row>
     <row r="15" spans="1:4" ht="16">
-      <c r="A15" s="237" t="s">
+      <c r="A15" s="245" t="s">
         <v>268</v>
       </c>
-      <c r="B15" s="238"/>
-      <c r="C15" s="238"/>
-      <c r="D15" s="239"/>
+      <c r="B15" s="246"/>
+      <c r="C15" s="246"/>
+      <c r="D15" s="247"/>
     </row>
     <row r="16" spans="1:4" ht="24" customHeight="1">
       <c r="A16" s="133" t="s">
@@ -19617,7 +19251,7 @@
         <v>270</v>
       </c>
       <c r="D17" s="185" t="s">
-        <v>1083</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1">
@@ -19681,111 +19315,111 @@
         <v>277</v>
       </c>
       <c r="B22" s="92" t="s">
-        <v>763</v>
+        <v>709</v>
       </c>
       <c r="C22" s="92" t="s">
-        <v>764</v>
+        <v>710</v>
       </c>
       <c r="D22" s="125" t="s">
-        <v>765</v>
+        <v>711</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="30" customHeight="1">
       <c r="A23" s="140" t="s">
-        <v>766</v>
+        <v>712</v>
       </c>
       <c r="B23" s="90" t="s">
-        <v>767</v>
+        <v>713</v>
       </c>
       <c r="C23" s="90" t="s">
-        <v>768</v>
+        <v>714</v>
       </c>
       <c r="D23" s="149" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="30" customHeight="1">
-      <c r="A24" s="138" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="72" customHeight="1">
+      <c r="A24" s="140" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B24" s="90" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C24" s="90" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D24" s="149" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="28">
+      <c r="A25" s="138" t="s">
         <v>264</v>
       </c>
-      <c r="B24" s="43" t="s">
+      <c r="B25" s="43" t="s">
         <v>285</v>
       </c>
-      <c r="C24" s="44" t="s">
+      <c r="C25" s="44" t="s">
         <v>286</v>
       </c>
-      <c r="D24" s="148" t="s">
+      <c r="D25" s="148" t="s">
         <v>287</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="70">
-      <c r="A25" s="138" t="s">
-        <v>1059</v>
-      </c>
-      <c r="B25" s="43" t="s">
-        <v>1060</v>
-      </c>
-      <c r="C25" s="44" t="s">
-        <v>1061</v>
-      </c>
-      <c r="D25" s="148" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="45" customHeight="1">
       <c r="A26" s="138" t="s">
-        <v>1063</v>
+        <v>989</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>1064</v>
+        <v>990</v>
       </c>
       <c r="C26" s="44" t="s">
-        <v>1065</v>
+        <v>991</v>
       </c>
       <c r="D26" s="148" t="s">
-        <v>1066</v>
+        <v>992</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="45" customHeight="1">
       <c r="A27" s="138" t="s">
-        <v>253</v>
+        <v>993</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>1067</v>
+        <v>994</v>
       </c>
       <c r="C27" s="44" t="s">
-        <v>1068</v>
+        <v>995</v>
       </c>
       <c r="D27" s="148" t="s">
-        <v>1069</v>
+        <v>996</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="45" customHeight="1">
       <c r="A28" s="138" t="s">
+        <v>253</v>
+      </c>
+      <c r="B28" s="43" t="s">
+        <v>997</v>
+      </c>
+      <c r="C28" s="44" t="s">
+        <v>998</v>
+      </c>
+      <c r="D28" s="148" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="30" customHeight="1">
+      <c r="A29" s="138" t="s">
         <v>252</v>
       </c>
-      <c r="B28" s="43" t="s">
-        <v>1070</v>
-      </c>
-      <c r="C28" s="44" t="s">
-        <v>1071</v>
-      </c>
-      <c r="D28" s="148" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="30" customHeight="1">
-      <c r="A29" s="137" t="s">
-        <v>288</v>
-      </c>
-      <c r="B29" s="40" t="s">
-        <v>289</v>
-      </c>
-      <c r="C29" s="41" t="s">
-        <v>290</v>
-      </c>
-      <c r="D29" s="147" t="s">
-        <v>291</v>
+      <c r="B29" s="43" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C29" s="44" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D29" s="148" t="s">
+        <v>1002</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="27.75" customHeight="1">
@@ -19793,97 +19427,97 @@
         <v>288</v>
       </c>
       <c r="B30" s="40" t="s">
+        <v>289</v>
+      </c>
+      <c r="C30" s="41" t="s">
+        <v>290</v>
+      </c>
+      <c r="D30" s="147" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="30" customHeight="1">
+      <c r="A31" s="137" t="s">
+        <v>288</v>
+      </c>
+      <c r="B31" s="40" t="s">
         <v>292</v>
       </c>
-      <c r="C30" s="41" t="s">
+      <c r="C31" s="41" t="s">
         <v>293</v>
       </c>
-      <c r="D30" s="147" t="s">
+      <c r="D31" s="147" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="30" customHeight="1">
-      <c r="A31" s="132"/>
-      <c r="B31" s="129"/>
-      <c r="C31" s="129"/>
-      <c r="D31" s="142"/>
-    </row>
     <row r="32" spans="1:4" ht="30" customHeight="1">
-      <c r="A32" s="240" t="s">
+      <c r="A32" s="132"/>
+      <c r="B32" s="129"/>
+      <c r="C32" s="129"/>
+      <c r="D32" s="142"/>
+    </row>
+    <row r="33" spans="1:4" ht="16">
+      <c r="A33" s="248" t="s">
         <v>295</v>
       </c>
-      <c r="B32" s="241"/>
-      <c r="C32" s="241"/>
-      <c r="D32" s="242"/>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="133" t="s">
+      <c r="B33" s="249"/>
+      <c r="C33" s="249"/>
+      <c r="D33" s="250"/>
+    </row>
+    <row r="34" spans="1:4" ht="24" customHeight="1">
+      <c r="A34" s="133" t="s">
         <v>249</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B34" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C34" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="D33" s="143" t="s">
+      <c r="D34" s="143" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="24" customHeight="1">
-      <c r="A34" s="135" t="s">
+    <row r="35" spans="1:4">
+      <c r="A35" s="135" t="s">
         <v>253</v>
       </c>
-      <c r="B34" s="34" t="s">
+      <c r="B35" s="34" t="s">
         <v>296</v>
       </c>
-      <c r="C34" s="35" t="s">
+      <c r="C35" s="35" t="s">
         <v>239</v>
       </c>
-      <c r="D34" s="145" t="s">
+      <c r="D35" s="145" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="28">
-      <c r="A35" s="136" t="s">
+    <row r="36" spans="1:4" ht="27.75" customHeight="1">
+      <c r="A36" s="136" t="s">
         <v>257</v>
       </c>
-      <c r="B35" s="37" t="s">
+      <c r="B36" s="37" t="s">
         <v>298</v>
       </c>
-      <c r="C35" s="38" t="s">
+      <c r="C36" s="38" t="s">
         <v>240</v>
       </c>
-      <c r="D35" s="146" t="s">
+      <c r="D36" s="146" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A36" s="134" t="s">
+    <row r="37" spans="1:4" ht="30" customHeight="1">
+      <c r="A37" s="134" t="s">
         <v>252</v>
       </c>
-      <c r="B36" s="31" t="s">
+      <c r="B37" s="31" t="s">
         <v>300</v>
       </c>
-      <c r="C36" s="32" t="s">
+      <c r="C37" s="32" t="s">
         <v>301</v>
       </c>
-      <c r="D36" s="144" t="s">
+      <c r="D37" s="144" t="s">
         <v>302</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="30" customHeight="1">
-      <c r="A37" s="138" t="s">
-        <v>264</v>
-      </c>
-      <c r="B37" s="43" t="s">
-        <v>303</v>
-      </c>
-      <c r="C37" s="44" t="s">
-        <v>304</v>
-      </c>
-      <c r="D37" s="148" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="27.75" customHeight="1">
@@ -19891,107 +19525,120 @@
         <v>264</v>
       </c>
       <c r="B38" s="43" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C38" s="44" t="s">
-        <v>245</v>
+        <v>304</v>
       </c>
       <c r="D38" s="148" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="45" customHeight="1">
       <c r="A39" s="138" t="s">
-        <v>766</v>
+        <v>264</v>
       </c>
       <c r="B39" s="43" t="s">
-        <v>1073</v>
+        <v>306</v>
       </c>
       <c r="C39" s="44" t="s">
-        <v>1074</v>
+        <v>245</v>
       </c>
       <c r="D39" s="148" t="s">
-        <v>1075</v>
+        <v>307</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="45" customHeight="1">
       <c r="A40" s="138" t="s">
-        <v>257</v>
+        <v>712</v>
       </c>
       <c r="B40" s="43" t="s">
-        <v>1076</v>
+        <v>1003</v>
       </c>
       <c r="C40" s="44" t="s">
-        <v>1077</v>
+        <v>1004</v>
       </c>
       <c r="D40" s="148" t="s">
-        <v>1078</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="45" customHeight="1">
       <c r="A41" s="138" t="s">
-        <v>1079</v>
+        <v>257</v>
       </c>
       <c r="B41" s="43" t="s">
-        <v>1082</v>
+        <v>1006</v>
       </c>
       <c r="C41" s="44" t="s">
-        <v>1080</v>
+        <v>1007</v>
       </c>
       <c r="D41" s="148" t="s">
-        <v>1081</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A42" s="135" t="s">
+      <c r="A42" s="138" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B42" s="43" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C42" s="44" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D42" s="148" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="27.75" customHeight="1">
+      <c r="A43" s="135" t="s">
         <v>253</v>
       </c>
-      <c r="B42" s="46" t="s">
+      <c r="B43" s="46" t="s">
         <v>308</v>
       </c>
-      <c r="C42" s="35" t="s">
+      <c r="C43" s="35" t="s">
         <v>309</v>
       </c>
-      <c r="D42" s="145" t="s">
+      <c r="D43" s="145" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A43" s="137" t="s">
+    <row r="44" spans="1:4" ht="30" customHeight="1">
+      <c r="A44" s="137" t="s">
         <v>311</v>
       </c>
-      <c r="B43" s="40" t="s">
+      <c r="B44" s="40" t="s">
         <v>312</v>
       </c>
-      <c r="C43" s="41" t="s">
+      <c r="C44" s="41" t="s">
         <v>313</v>
       </c>
-      <c r="D43" s="147" t="s">
+      <c r="D44" s="147" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="30" customHeight="1" thickBot="1">
-      <c r="A44" s="141" t="s">
+    <row r="45" spans="1:4" ht="30" customHeight="1" thickBot="1">
+      <c r="A45" s="141" t="s">
         <v>288</v>
       </c>
-      <c r="B44" s="130" t="s">
+      <c r="B45" s="130" t="s">
         <v>315</v>
       </c>
-      <c r="C44" s="131" t="s">
+      <c r="C45" s="131" t="s">
         <v>316</v>
       </c>
-      <c r="D44" s="150" t="s">
+      <c r="D45" s="150" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="30" customHeight="1"/>
     <row r="46" spans="1:4" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -20013,20 +19660,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1">
-      <c r="A1" s="243" t="s">
+      <c r="A1" s="251" t="s">
         <v>318</v>
       </c>
-      <c r="B1" s="243"/>
-      <c r="C1" s="243"/>
-      <c r="D1" s="243"/>
+      <c r="B1" s="251"/>
+      <c r="C1" s="251"/>
+      <c r="D1" s="251"/>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
-      <c r="A3" s="215" t="s">
+      <c r="A3" s="223" t="s">
         <v>248</v>
       </c>
-      <c r="B3" s="215"/>
-      <c r="C3" s="215"/>
-      <c r="D3" s="215"/>
+      <c r="B3" s="223"/>
+      <c r="C3" s="223"/>
+      <c r="D3" s="223"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="12" t="s">
@@ -20085,12 +19732,12 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="24" customHeight="1">
-      <c r="A9" s="211" t="s">
+      <c r="A9" s="219" t="s">
         <v>268</v>
       </c>
-      <c r="B9" s="211"/>
-      <c r="C9" s="211"/>
-      <c r="D9" s="211"/>
+      <c r="B9" s="219"/>
+      <c r="C9" s="219"/>
+      <c r="D9" s="219"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="12" t="s">
@@ -20135,12 +19782,12 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="24" customHeight="1">
-      <c r="A14" s="213" t="s">
+      <c r="A14" s="221" t="s">
         <v>295</v>
       </c>
-      <c r="B14" s="213"/>
-      <c r="C14" s="213"/>
-      <c r="D14" s="213"/>
+      <c r="B14" s="221"/>
+      <c r="C14" s="221"/>
+      <c r="D14" s="221"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="12" t="s">

--- a/tools/itinerary.xlsx
+++ b/tools/itinerary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jitwei/Library/Mobile Documents/com~apple~CloudDocs/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D7B613-D649-E941-BCE2-95BB534206AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A106C67-AECF-0E47-90F2-B8C1AA2C8FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="17020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1752" uniqueCount="1210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="1218">
   <si>
     <r>
       <rPr>
@@ -8278,9 +8278,6 @@
     <t>Momicafe</t>
   </si>
   <si>
-    <t>18:00–19:15</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -8316,215 +8313,6 @@
         <family val="2"/>
       </rPr>
       <t>手摇船</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Dinner at Wumen Renjia </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>吴门人家</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">; Pingtan </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>评弹</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. Optional hand-rowed boat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">手摇船 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>along the canal (~¥100).</t>
-    </r>
-  </si>
-  <si>
-    <t>19:15–20:15</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Design-award wet market — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>糕团</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>馄饨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">海棠糕 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>stalls &amp; cafés.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Shuangta </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>双塔</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>姑苏区吴殿直街</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">号 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>石匠弄</t>
     </r>
     <r>
       <rPr>
@@ -9135,52 +8923,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">NEW-EXP: Master-of-Nets night Kunqu </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>网师园夜昆曲</t>
-    </r>
-  </si>
-  <si>
-    <t>Same garden (2-min walk) — Kunqu &amp; Pingtan (book).</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Wangshi </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>网师园</t>
-    </r>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">Return to Ritz </t>
     </r>
     <r>
@@ -10104,15 +9846,9 @@
     <t>鼓楼区广州路173号</t>
   </si>
   <si>
-    <t>20:30–21:30</t>
-  </si>
-  <si>
     <t>STREET FOOD: Shantang Street 山塘街 night market</t>
   </si>
   <si>
-    <t>Promoted from Alt — TOP-7 Suzhou sight, free, and walkable from the Ritz. Canal food under red lanterns; 姑苏20:30 keeps it open late.</t>
-  </si>
-  <si>
     <t>山塘街 · walkable</t>
   </si>
   <si>
@@ -10171,9 +9907,6 @@
   </si>
   <si>
     <t>姑苏区人民路1918号 (北寺塔)</t>
-  </si>
-  <si>
-    <t>On 平江路 itself — 猫空 concept bookstore (originated in Suzhou; 'mail a postcard to the future') + indie 慢书房. Zero detour from the Pingjiang walk.</t>
   </si>
   <si>
     <t>Optional alt: Nanjing Eye 南京眼 &amp; Yuzui Wetland 鱼嘴湿地</t>
@@ -10999,9 +10732,6 @@
   </si>
   <si>
     <t>16:35–17:15</t>
-  </si>
-  <si>
-    <t>17:15–18:00</t>
   </si>
   <si>
     <t>Canal-front drip coffee — golden hour, with time to actually sit.</t>
@@ -11336,9 +11066,6 @@
   </si>
   <si>
     <t>17:30</t>
-  </si>
-  <si>
-    <t>19:15</t>
   </si>
   <si>
     <t>12:15</t>
@@ -11419,15 +11146,6 @@
     <t>Station → Ritz-Carlton Suzhou 丽思 (广济南路), drop bags 🏨</t>
   </si>
   <si>
-    <t>Optional: Momi/猫的天空之城 &amp; Slow Bookstore 慢书房 📚</t>
-  </si>
-  <si>
-    <t>Optional: Li Bai Xie 李百蟹·蟹黄面 (Pingjiang 平江路总店) 🦀</t>
-  </si>
-  <si>
-    <t>TRENDY: Shuangta Market 双塔市集 🆕</t>
-  </si>
-  <si>
     <t>Optional: Renheng Cang Street 仁恒仓街 &amp; 相门城墙 🛍</t>
   </si>
   <si>
@@ -11605,6 +11323,9 @@
     <t>Metro/DiDi ~25 min</t>
   </si>
   <si>
+    <t>19:45–21:00</t>
+  </si>
+  <si>
     <t>Dinner — Nanjing Impressions 南京大牌档 (德基广场7层) 🏨</t>
   </si>
   <si>
@@ -11737,13 +11458,88 @@
     <t>Called by reviewers Hangzhou's best Italian gelato — pistachio, matcha &amp; chocolate are the standouts. On Guangfu Rd 光复路, ~5 min from 清河坊 and right off 南宋御街. Little queuing off-peak. ~¥37pp.</t>
   </si>
   <si>
-    <t>NOTE THE SPELLING: 李百蟹 (bǎi 百), not 李白蟹. ZERO DETOUR — it is ON Pingjiang Rd 平江路, which you already walk 18:00–19:15 (row above). Crab-roe noodles 蟹黄面 &amp; 蟹黄拌饭 — golden 蟹粉/蟹膏, FREE noodle &amp; rice refills; also 江南花雕熟醉蟹, 蟹膏, and photogenic Suzhou desserts (草莓奶盖冰, 抹茶豆花, 桂花奶酪). Riverside seats look onto the canal, bridges &amp; boats. ⚠ Queues at meal times — take a queue number on arrival (reported to move fast). Open 10:00–21:30. Other branches: 观前街店 (beside Day 7 lunch), 山塘街店 (河景船宴, near hotel).</t>
-  </si>
-  <si>
     <t>HAIRY CRAB 大闸蟹 season pick. 招牌熟醉蟹, 阳澄湖大闸蟹 (时令价), 蟹粉豆腐. 拒绝料包. ⚠ Queues &gt;1h at meal times. Prestige alt: 新聚丰菜馆 太监弄店 (1904, 黑珍珠+米其林指南, 清炒蟹粉, ¥215–389, closes 20:30).</t>
   </si>
   <si>
     <t>CRAB-ROE NOODLES, zero detour — sits on the Pingjiang Rd 平江路 stretch already in Day 6. 蟹黄面 / 蟹黄拌饭 with free noodle &amp; rice refills; 江南花雕熟醉蟹, 蟹膏; Suzhou desserts (草莓奶盖冰, 抹茶豆花, 桂花奶酪). Canal-side windows onto bridges &amp; boats. ⚠ Queues at meal times — take a number on arrival. Open 10:00–21:30.</t>
+  </si>
+  <si>
+    <t>17:00–17:45</t>
+  </si>
+  <si>
+    <t>17:45–18:30</t>
+  </si>
+  <si>
+    <t>Canal lanes, bridges &amp; waterside houses at dusk. Optional hand-rowed boat 手摇船 (~¥100) — board here. Dinner is now its own row below.</t>
+  </si>
+  <si>
+    <t>Dinner — Wumen Renjia 吴门人家 (潘儒巷32号) 🍽</t>
+  </si>
+  <si>
+    <t>Heritage 苏帮菜 in a Qing courtyard mansion opposite 狮子林 — I.M. Pei ate here while building 苏博. 松鼠桂鱼, 响油鳝糊, 手剥虾仁, 樱桃肉, 赤豆糖粥. ⚠ LAST ORDERS ~20:30 and the kitchen winds down early — arrive by 18:30, do not push this later. ⚠ Book ahead; private rooms need reservation. Tel +86 512 6728 8041. Note: Tripadvisor lists the door as 潘儒巷31号.</t>
+  </si>
+  <si>
+    <t>¥150–250 · book</t>
+  </si>
+  <si>
+    <t>姑苏区潘儒巷32号 (近狮子林)</t>
+  </si>
+  <si>
+    <t>Opt</t>
+  </si>
+  <si>
+    <t>Optional: 猫的天空之城 &amp; Slow Bookstore 慢书房 📚</t>
+  </si>
+  <si>
+    <t>On 平江路 itself — 猫空 concept bookstore (originated in Suzhou; "mail a postcard to the future") + indie 慢书房. Zero detour, slot into the 17:45–18:30 canal walk.</t>
+  </si>
+  <si>
+    <t>Optional: Li Bai Xie 李百蟹·蟹黄面 (平江路总店) 🦀</t>
+  </si>
+  <si>
+    <t>ALTERNATIVE to 吴门人家 if you want something lighter and unbooked. Spelling: 李百蟹 (bǎi 百), not 李白蟹. ON 平江路 — zero detour. Crab-roe noodles 蟹黄面 &amp; 蟹黄拌饭, free noodle &amp; rice refills; 江南花雕熟醉蟹, 蟹膏; desserts 草莓奶盖冰, 抹茶豆花, 桂花奶酪. Canal-side seats. Open 10:00–21:30 — much later than 吴门人家. ⚠ Queues at meal times; take a number. Other branches: 观前街店, 山塘街店.</t>
+  </si>
+  <si>
+    <t>20:15–21:30</t>
+  </si>
+  <si>
+    <t>TOP-7 Suzhou sight, free, and walkable from the Ritz. Canal food under red lanterns; 姑苏20:30 keeps it open late. ~25 min by DiDi from 平江路 — go direct, no cross-town detour.</t>
+  </si>
+  <si>
+    <t>Optional: Shuangta Market 双塔市集 🆕</t>
+  </si>
+  <si>
+    <t>MOVED OFF DAY 6 EVENING — this is a converted wet market 菜场, so the produce stalls and 糕团/馄饨/海棠糕 counters are DAYTIME trade and largely shut by evening. Design-award interior; best as a morning or mid-day snack stop. SE old town (吴殿直街2号), near 网师园 — easiest to pair with the 14:30 网师园 visit rather than the morning gardens.</t>
+  </si>
+  <si>
+    <t>Opt · daytime</t>
+  </si>
+  <si>
+    <t>姑苏区吴殿直街2号 (石匠弄)</t>
+  </si>
+  <si>
+    <t>Shantang Street 山塘街 night walk &amp; lanterns 🏮</t>
+  </si>
+  <si>
+    <t>Stay where you already are — the farewell dinner is ON 山塘街, so the evening costs zero transit. Red lanterns reflect off the canal after dark; the stretch between 通贵桥 and 星桥 is the photogenic core. Optional 手摇船 night boat from 山塘街 landing (~¥60–100, negotiate before boarding). Quieter and more local than 平江路 at night. Walk back west to 阊门 for a taxi, or Metro L2 山塘街站.</t>
+  </si>
+  <si>
+    <t>Walk · free</t>
+  </si>
+  <si>
+    <t>姑苏区山塘街 (通贵桥–星桥段)</t>
+  </si>
+  <si>
+    <t>Optional: Master-of-Nets night Kunqu 网师园夜昆曲</t>
+  </si>
+  <si>
+    <t>🔴 SEASONAL — LIKELY CLOSED ON 21 NOV. The night garden 夜花园 runs 3月–11月 only; the 2025 season ended 16 Nov, with the operator confirming no sessions after mid-Nov. Your date falls just outside that window. 2026 dates are not yet published — re-check on the 苏州园林旅游 or 君到苏州 WeChat 公众号; night tickets release 7 days ahead. Night ticket ¥100 is SEPARATE from the ¥40 day ticket (not interchangeable). Performances cancelled in heavy rain; Saturday sessions sell out fastest. IF it is running, swap the evening: dinner on 十全街/凤凰街 ~17:30, garden ~19:30, 山塘街 after — do NOT try to reach it from 山塘街 at 20:00, that is a 5–6km cross-city hop.</t>
+  </si>
+  <si>
+    <t>Opt · ¥100 · book 7d ahead</t>
+  </si>
+  <si>
+    <t>姑苏区阔家头巷11号 (网师园)</t>
   </si>
 </sst>
 </file>
@@ -12312,7 +12108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="253">
+  <cellXfs count="254">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -12591,9 +12387,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="24" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -13062,6 +12855,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="26" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -13342,31 +13141,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="31.5" customHeight="1">
-      <c r="A1" s="217" t="s">
+      <c r="A1" s="216" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="217"/>
-      <c r="C1" s="217"/>
-      <c r="D1" s="217"/>
-      <c r="E1" s="217"/>
+      <c r="B1" s="216"/>
+      <c r="C1" s="216"/>
+      <c r="D1" s="216"/>
+      <c r="E1" s="216"/>
     </row>
     <row r="2" spans="1:5" ht="21.75" customHeight="1">
-      <c r="A2" s="218" t="s">
+      <c r="A2" s="217" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="218"/>
-      <c r="C2" s="218"/>
-      <c r="D2" s="218"/>
-      <c r="E2" s="218"/>
+      <c r="B2" s="217"/>
+      <c r="C2" s="217"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="217"/>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1">
-      <c r="A4" s="219" t="s">
+      <c r="A4" s="218" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="219"/>
-      <c r="C4" s="219"/>
-      <c r="D4" s="219"/>
-      <c r="E4" s="219"/>
+      <c r="B4" s="218"/>
+      <c r="C4" s="218"/>
+      <c r="D4" s="218"/>
+      <c r="E4" s="218"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
@@ -13420,13 +13219,13 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1">
-      <c r="A9" s="220" t="s">
+      <c r="A9" s="219" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="220"/>
-      <c r="C9" s="220"/>
-      <c r="D9" s="220"/>
-      <c r="E9" s="220"/>
+      <c r="B9" s="219"/>
+      <c r="C9" s="219"/>
+      <c r="D9" s="219"/>
+      <c r="E9" s="219"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
@@ -13447,36 +13246,36 @@
     </row>
     <row r="11" spans="1:5" ht="55" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>925</v>
+        <v>912</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>926</v>
+        <v>913</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>927</v>
+        <v>914</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>928</v>
+        <v>915</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>900</v>
+        <v>887</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="55" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>925</v>
+        <v>912</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>929</v>
+        <v>916</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>930</v>
+        <v>917</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>931</v>
+        <v>918</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>932</v>
+        <v>919</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="45.75" customHeight="1">
@@ -13515,41 +13314,41 @@
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1"/>
     <row r="16" spans="1:5" ht="72" customHeight="1">
-      <c r="A16" s="221" t="s">
+      <c r="A16" s="220" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="221"/>
-      <c r="C16" s="221"/>
-      <c r="D16" s="221"/>
-      <c r="E16" s="221"/>
+      <c r="B16" s="220"/>
+      <c r="C16" s="220"/>
+      <c r="D16" s="220"/>
+      <c r="E16" s="220"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="215" t="s">
+      <c r="A17" s="214" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="215"/>
-      <c r="C17" s="215"/>
-      <c r="D17" s="215"/>
-      <c r="E17" s="215"/>
+      <c r="B17" s="214"/>
+      <c r="C17" s="214"/>
+      <c r="D17" s="214"/>
+      <c r="E17" s="214"/>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1"/>
     <row r="19" spans="1:5" ht="31.5" customHeight="1">
-      <c r="A19" s="216" t="s">
+      <c r="A19" s="215" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="216"/>
-      <c r="C19" s="216"/>
-      <c r="D19" s="216"/>
-      <c r="E19" s="216"/>
+      <c r="B19" s="215"/>
+      <c r="C19" s="215"/>
+      <c r="D19" s="215"/>
+      <c r="E19" s="215"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="215" t="s">
+      <c r="A20" s="214" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="215"/>
-      <c r="C20" s="215"/>
-      <c r="D20" s="215"/>
-      <c r="E20" s="215"/>
+      <c r="B20" s="214"/>
+      <c r="C20" s="214"/>
+      <c r="D20" s="214"/>
+      <c r="E20" s="214"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -13572,7 +13371,7 @@
   <sheetPr>
     <tabColor rgb="FFC55A11"/>
   </sheetPr>
-  <dimension ref="A1:F140"/>
+  <dimension ref="A1:F142"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -13584,24 +13383,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18">
-      <c r="A1" s="206" t="s">
-        <v>896</v>
-      </c>
-      <c r="B1" s="207"/>
-      <c r="C1" s="207"/>
-      <c r="D1" s="207"/>
-      <c r="E1" s="207"/>
-      <c r="F1" s="208"/>
+      <c r="A1" s="205" t="s">
+        <v>883</v>
+      </c>
+      <c r="B1" s="206"/>
+      <c r="C1" s="206"/>
+      <c r="D1" s="206"/>
+      <c r="E1" s="206"/>
+      <c r="F1" s="207"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="209" t="s">
+      <c r="A2" s="208" t="s">
         <v>344</v>
       </c>
-      <c r="B2" s="210"/>
-      <c r="C2" s="210"/>
-      <c r="D2" s="210"/>
-      <c r="E2" s="210"/>
-      <c r="F2" s="211"/>
+      <c r="B2" s="209"/>
+      <c r="C2" s="209"/>
+      <c r="D2" s="209"/>
+      <c r="E2" s="209"/>
+      <c r="F2" s="210"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="77" t="s">
@@ -13624,17 +13423,17 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="212" t="s">
-        <v>897</v>
-      </c>
-      <c r="B4" s="213"/>
-      <c r="C4" s="213"/>
-      <c r="D4" s="213"/>
-      <c r="E4" s="213"/>
-      <c r="F4" s="214"/>
+      <c r="A4" s="211" t="s">
+        <v>884</v>
+      </c>
+      <c r="B4" s="212"/>
+      <c r="C4" s="212"/>
+      <c r="D4" s="212"/>
+      <c r="E4" s="212"/>
+      <c r="F4" s="213"/>
     </row>
     <row r="5" spans="1:6" ht="28">
-      <c r="A5" s="98" t="s">
+      <c r="A5" s="97" t="s">
         <v>350</v>
       </c>
       <c r="B5" s="53" t="s">
@@ -13654,7 +13453,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="28">
-      <c r="A6" s="99" t="s">
+      <c r="A6" s="98" t="s">
         <v>350</v>
       </c>
       <c r="B6" s="54" t="s">
@@ -13669,32 +13468,32 @@
       <c r="E6" s="15" t="s">
         <v>359</v>
       </c>
-      <c r="F6" s="113" t="s">
+      <c r="F6" s="112" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28">
-      <c r="A7" s="100" t="s">
+      <c r="A7" s="99" t="s">
         <v>350</v>
       </c>
-      <c r="B7" s="158" t="s">
-        <v>740</v>
+      <c r="B7" s="157" t="s">
+        <v>727</v>
       </c>
       <c r="C7" s="50" t="s">
         <v>361</v>
       </c>
       <c r="D7" s="50" t="s">
-        <v>1069</v>
+        <v>1055</v>
       </c>
       <c r="E7" s="50" t="s">
         <v>362</v>
       </c>
-      <c r="F7" s="115" t="s">
+      <c r="F7" s="114" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="28">
-      <c r="A8" s="100" t="s">
+      <c r="A8" s="99" t="s">
         <v>350</v>
       </c>
       <c r="B8" s="55" t="s">
@@ -13709,112 +13508,112 @@
       <c r="E8" s="50" t="s">
         <v>367</v>
       </c>
-      <c r="F8" s="115" t="s">
+      <c r="F8" s="114" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="28">
-      <c r="A9" s="100" t="s">
+      <c r="A9" s="99" t="s">
         <v>350</v>
       </c>
       <c r="B9" s="55" t="s">
         <v>369</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>898</v>
+        <v>885</v>
       </c>
       <c r="D9" s="50" t="s">
-        <v>899</v>
+        <v>886</v>
       </c>
       <c r="E9" s="50" t="s">
         <v>370</v>
       </c>
-      <c r="F9" s="115" t="s">
-        <v>900</v>
+      <c r="F9" s="114" t="s">
+        <v>887</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28">
-      <c r="A10" s="101" t="s">
+      <c r="A10" s="100" t="s">
         <v>350</v>
       </c>
       <c r="B10" s="56" t="s">
         <v>371</v>
       </c>
-      <c r="C10" s="189" t="s">
-        <v>1081</v>
+      <c r="C10" s="188" t="s">
+        <v>1066</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>901</v>
+        <v>888</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>902</v>
-      </c>
-      <c r="F10" s="116" t="s">
-        <v>903</v>
+        <v>889</v>
+      </c>
+      <c r="F10" s="115" t="s">
+        <v>890</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="45" customHeight="1">
-      <c r="A11" s="102" t="s">
+      <c r="A11" s="101" t="s">
         <v>350</v>
       </c>
-      <c r="B11" s="154" t="s">
-        <v>705</v>
+      <c r="B11" s="153" t="s">
+        <v>693</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>1037</v>
+        <v>1023</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>1038</v>
+        <v>1024</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>1039</v>
-      </c>
-      <c r="F11" s="117" t="s">
-        <v>1040</v>
+        <v>1025</v>
+      </c>
+      <c r="F11" s="116" t="s">
+        <v>1026</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="45" customHeight="1">
-      <c r="A12" s="102" t="s">
+      <c r="A12" s="101" t="s">
         <v>350</v>
       </c>
-      <c r="B12" s="154" t="s">
-        <v>1041</v>
+      <c r="B12" s="153" t="s">
+        <v>1027</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>1042</v>
+        <v>1028</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>1043</v>
+        <v>1029</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>904</v>
-      </c>
-      <c r="F12" s="117" t="s">
-        <v>905</v>
+        <v>891</v>
+      </c>
+      <c r="F12" s="116" t="s">
+        <v>892</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28">
-      <c r="A13" s="103" t="s">
+      <c r="A13" s="102" t="s">
         <v>350</v>
       </c>
       <c r="B13" s="58" t="s">
         <v>373</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>906</v>
+        <v>893</v>
       </c>
       <c r="D13" s="39" t="s">
-        <v>1029</v>
+        <v>1015</v>
       </c>
       <c r="E13" s="41" t="s">
-        <v>907</v>
-      </c>
-      <c r="F13" s="118" t="s">
-        <v>908</v>
+        <v>894</v>
+      </c>
+      <c r="F13" s="117" t="s">
+        <v>895</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="28">
-      <c r="A14" s="101" t="s">
+      <c r="A14" s="100" t="s">
         <v>350</v>
       </c>
       <c r="B14" s="56" t="s">
@@ -13827,64 +13626,64 @@
         <v>376</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>909</v>
-      </c>
-      <c r="F14" s="116" t="s">
-        <v>903</v>
+        <v>896</v>
+      </c>
+      <c r="F14" s="115" t="s">
+        <v>890</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="212" t="s">
-        <v>910</v>
-      </c>
-      <c r="B15" s="213"/>
-      <c r="C15" s="213"/>
-      <c r="D15" s="213"/>
-      <c r="E15" s="213"/>
-      <c r="F15" s="214"/>
+      <c r="A15" s="211" t="s">
+        <v>897</v>
+      </c>
+      <c r="B15" s="212"/>
+      <c r="C15" s="212"/>
+      <c r="D15" s="212"/>
+      <c r="E15" s="212"/>
+      <c r="F15" s="213"/>
     </row>
     <row r="16" spans="1:6" ht="28">
-      <c r="A16" s="101" t="s">
+      <c r="A16" s="100" t="s">
         <v>378</v>
       </c>
       <c r="B16" s="56" t="s">
         <v>379</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>911</v>
+        <v>898</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>912</v>
+        <v>899</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>913</v>
-      </c>
-      <c r="F16" s="116" t="s">
         <v>900</v>
       </c>
+      <c r="F16" s="115" t="s">
+        <v>887</v>
+      </c>
     </row>
     <row r="17" spans="1:6" ht="90" customHeight="1">
-      <c r="A17" s="104" t="s">
+      <c r="A17" s="103" t="s">
         <v>378</v>
       </c>
       <c r="B17" s="59" t="s">
         <v>380</v>
       </c>
-      <c r="C17" s="186" t="s">
-        <v>1082</v>
+      <c r="C17" s="185" t="s">
+        <v>1067</v>
       </c>
       <c r="D17" s="47" t="s">
-        <v>1051</v>
-      </c>
-      <c r="E17" s="186" t="s">
-        <v>1052</v>
-      </c>
-      <c r="F17" s="119" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E17" s="185" t="s">
+        <v>1038</v>
+      </c>
+      <c r="F17" s="118" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="56">
-      <c r="A18" s="105" t="s">
+      <c r="A18" s="104" t="s">
         <v>378</v>
       </c>
       <c r="B18" s="60" t="s">
@@ -13894,101 +13693,101 @@
         <v>384</v>
       </c>
       <c r="D18" s="61" t="s">
-        <v>1068</v>
-      </c>
-      <c r="E18" s="187" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E18" s="186" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F18" s="119" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="182">
+      <c r="A19" s="103" t="s">
+        <v>378</v>
+      </c>
+      <c r="B19" s="187" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C19" s="47" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D19" s="47" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E19" s="185" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F19" s="118" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="70">
+      <c r="A20" s="104" t="s">
+        <v>378</v>
+      </c>
+      <c r="B20" s="151" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C20" s="61" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D20" s="61" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E20" s="186" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F20" s="119" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="28" customHeight="1">
+      <c r="A21" s="104" t="s">
+        <v>378</v>
+      </c>
+      <c r="B21" s="151" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C21" s="61" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D21" s="61" t="s">
         <v>1053</v>
-      </c>
-      <c r="F18" s="120" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="182">
-      <c r="A19" s="104" t="s">
-        <v>378</v>
-      </c>
-      <c r="B19" s="188" t="s">
-        <v>1059</v>
-      </c>
-      <c r="C19" s="47" t="s">
-        <v>1054</v>
-      </c>
-      <c r="D19" s="47" t="s">
-        <v>1065</v>
-      </c>
-      <c r="E19" s="186" t="s">
-        <v>1060</v>
-      </c>
-      <c r="F19" s="119" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="70">
-      <c r="A20" s="105" t="s">
-        <v>378</v>
-      </c>
-      <c r="B20" s="152" t="s">
-        <v>1061</v>
-      </c>
-      <c r="C20" s="61" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D20" s="61" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E20" s="187" t="s">
-        <v>1056</v>
-      </c>
-      <c r="F20" s="120" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="28" customHeight="1">
-      <c r="A21" s="105" t="s">
-        <v>378</v>
-      </c>
-      <c r="B21" s="152" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C21" s="61" t="s">
-        <v>1028</v>
-      </c>
-      <c r="D21" s="61" t="s">
-        <v>1067</v>
       </c>
       <c r="E21" s="61" t="s">
         <v>483</v>
       </c>
-      <c r="F21" s="120" t="s">
+      <c r="F21" s="119" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="56" customHeight="1">
-      <c r="A22" s="105" t="s">
+      <c r="A22" s="104" t="s">
         <v>378</v>
       </c>
-      <c r="B22" s="152" t="s">
-        <v>1072</v>
+      <c r="B22" s="151" t="s">
+        <v>1058</v>
       </c>
       <c r="C22" s="61" t="s">
-        <v>1058</v>
+        <v>1044</v>
       </c>
       <c r="D22" s="61" t="s">
-        <v>1066</v>
+        <v>1052</v>
       </c>
       <c r="E22" s="61" t="s">
         <v>483</v>
       </c>
-      <c r="F22" s="120" t="s">
+      <c r="F22" s="119" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="28">
-      <c r="A23" s="106" t="s">
+      <c r="A23" s="105" t="s">
         <v>378</v>
       </c>
-      <c r="B23" s="157" t="s">
-        <v>1062</v>
+      <c r="B23" s="156" t="s">
+        <v>1048</v>
       </c>
       <c r="C23" s="20" t="s">
         <v>388</v>
@@ -13999,176 +13798,176 @@
       <c r="E23" s="20" t="s">
         <v>390</v>
       </c>
-      <c r="F23" s="121" t="s">
+      <c r="F23" s="120" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="42">
-      <c r="A24" s="106" t="s">
+      <c r="A24" s="105" t="s">
         <v>378</v>
       </c>
-      <c r="B24" s="157" t="s">
+      <c r="B24" s="156" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C24" s="189" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>728</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>729</v>
+      </c>
+      <c r="F24" s="120" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="56">
+      <c r="A25" s="97" t="s">
+        <v>378</v>
+      </c>
+      <c r="B25" s="158" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F25" s="86" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="110" customHeight="1">
+      <c r="A26" s="104" t="s">
+        <v>378</v>
+      </c>
+      <c r="B26" s="151" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C26" s="186" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D26" s="186" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E26" s="186" t="s">
         <v>1063</v>
       </c>
-      <c r="C24" s="190" t="s">
-        <v>1083</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>741</v>
-      </c>
-      <c r="E24" s="20" t="s">
-        <v>742</v>
-      </c>
-      <c r="F24" s="121" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="56">
-      <c r="A25" s="98" t="s">
+      <c r="F26" s="119" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="56">
+      <c r="A27" s="104" t="s">
         <v>378</v>
       </c>
-      <c r="B25" s="159" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>1022</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>1025</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F25" s="86" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="110" customHeight="1">
-      <c r="A26" s="105" t="s">
+      <c r="B27" s="151" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C27" s="186" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D27" s="61" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E27" s="61" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F27" s="119" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="42">
+      <c r="A28" s="104" t="s">
         <v>378</v>
       </c>
-      <c r="B26" s="152" t="s">
-        <v>1015</v>
-      </c>
-      <c r="C26" s="187" t="s">
-        <v>1084</v>
-      </c>
-      <c r="D26" s="187" t="s">
-        <v>1079</v>
-      </c>
-      <c r="E26" s="187" t="s">
-        <v>1078</v>
-      </c>
-      <c r="F26" s="120" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="56">
-      <c r="A27" s="105" t="s">
-        <v>378</v>
-      </c>
-      <c r="B27" s="152" t="s">
-        <v>1016</v>
-      </c>
-      <c r="C27" s="187" t="s">
-        <v>1085</v>
-      </c>
-      <c r="D27" s="61" t="s">
-        <v>1026</v>
-      </c>
-      <c r="E27" s="61" t="s">
-        <v>1017</v>
-      </c>
-      <c r="F27" s="120" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="42">
-      <c r="A28" s="105" t="s">
-        <v>378</v>
-      </c>
-      <c r="B28" s="152" t="s">
-        <v>1018</v>
+      <c r="B28" s="151" t="s">
+        <v>1004</v>
       </c>
       <c r="C28" s="61" t="s">
-        <v>1019</v>
+        <v>1005</v>
       </c>
       <c r="D28" s="61" t="s">
-        <v>1027</v>
+        <v>1013</v>
       </c>
       <c r="E28" s="61" t="s">
         <v>392</v>
       </c>
-      <c r="F28" s="120" t="s">
-        <v>1020</v>
+      <c r="F28" s="119" t="s">
+        <v>1006</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="28">
-      <c r="A29" s="107" t="s">
+      <c r="A29" s="106" t="s">
         <v>378</v>
       </c>
-      <c r="B29" s="160" t="s">
-        <v>1044</v>
+      <c r="B29" s="159" t="s">
+        <v>1030</v>
       </c>
       <c r="C29" s="36" t="s">
-        <v>1045</v>
+        <v>1031</v>
       </c>
       <c r="D29" s="36" t="s">
-        <v>1046</v>
+        <v>1032</v>
       </c>
       <c r="E29" s="36" t="s">
-        <v>1047</v>
-      </c>
-      <c r="F29" s="122" t="s">
-        <v>849</v>
+        <v>1033</v>
+      </c>
+      <c r="F29" s="121" t="s">
+        <v>836</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="70">
-      <c r="A30" s="102" t="s">
+      <c r="A30" s="101" t="s">
         <v>378</v>
       </c>
-      <c r="B30" s="154" t="s">
-        <v>1048</v>
-      </c>
-      <c r="C30" s="191" t="s">
-        <v>1086</v>
+      <c r="B30" s="153" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C30" s="190" t="s">
+        <v>1071</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>1049</v>
+        <v>1035</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>1050</v>
-      </c>
-      <c r="F30" s="117" t="s">
-        <v>849</v>
+        <v>1036</v>
+      </c>
+      <c r="F30" s="116" t="s">
+        <v>836</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="56">
-      <c r="A31" s="102" t="s">
+      <c r="A31" s="101" t="s">
         <v>378</v>
       </c>
-      <c r="B31" s="154" t="s">
-        <v>1021</v>
+      <c r="B31" s="153" t="s">
+        <v>1007</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>716</v>
+        <v>704</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>1080</v>
+        <v>1065</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>717</v>
-      </c>
-      <c r="F31" s="117" t="s">
-        <v>718</v>
+        <v>705</v>
+      </c>
+      <c r="F31" s="116" t="s">
+        <v>706</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="28">
-      <c r="A32" s="107" t="s">
+      <c r="A32" s="106" t="s">
         <v>378</v>
       </c>
-      <c r="B32" s="160" t="s">
-        <v>719</v>
+      <c r="B32" s="159" t="s">
+        <v>707</v>
       </c>
       <c r="C32" s="36" t="s">
         <v>394</v>
@@ -14179,82 +13978,82 @@
       <c r="E32" s="36" t="s">
         <v>396</v>
       </c>
-      <c r="F32" s="122" t="s">
+      <c r="F32" s="121" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="28">
-      <c r="A33" s="101" t="s">
+      <c r="A33" s="100" t="s">
         <v>378</v>
       </c>
-      <c r="B33" s="151" t="s">
-        <v>708</v>
+      <c r="B33" s="150" t="s">
+        <v>696</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>914</v>
+        <v>901</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>915</v>
+        <v>902</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>909</v>
-      </c>
-      <c r="F33" s="116" t="s">
+        <v>896</v>
+      </c>
+      <c r="F33" s="115" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="211" t="s">
         <v>903</v>
       </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="212" t="s">
-        <v>916</v>
-      </c>
-      <c r="B34" s="213"/>
-      <c r="C34" s="213"/>
-      <c r="D34" s="213"/>
-      <c r="E34" s="213"/>
-      <c r="F34" s="214"/>
+      <c r="B34" s="212"/>
+      <c r="C34" s="212"/>
+      <c r="D34" s="212"/>
+      <c r="E34" s="212"/>
+      <c r="F34" s="213"/>
     </row>
     <row r="35" spans="1:6" ht="42">
-      <c r="A35" s="101" t="s">
+      <c r="A35" s="100" t="s">
         <v>399</v>
       </c>
       <c r="B35" s="56" t="s">
         <v>400</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>917</v>
+        <v>904</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>918</v>
+        <v>905</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>919</v>
-      </c>
-      <c r="F35" s="116" t="s">
-        <v>900</v>
+        <v>906</v>
+      </c>
+      <c r="F35" s="115" t="s">
+        <v>887</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="84">
-      <c r="A36" s="102" t="s">
+      <c r="A36" s="101" t="s">
         <v>399</v>
       </c>
-      <c r="B36" s="154" t="s">
-        <v>1073</v>
-      </c>
-      <c r="C36" s="191" t="s">
-        <v>1087</v>
+      <c r="B36" s="153" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C36" s="190" t="s">
+        <v>1072</v>
       </c>
       <c r="D36" s="33" t="s">
-        <v>1204</v>
+        <v>1187</v>
       </c>
       <c r="E36" s="35" t="s">
-        <v>794</v>
-      </c>
-      <c r="F36" s="117" t="s">
-        <v>795</v>
+        <v>781</v>
+      </c>
+      <c r="F36" s="116" t="s">
+        <v>782</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="28">
-      <c r="A37" s="105" t="s">
+      <c r="A37" s="104" t="s">
         <v>399</v>
       </c>
       <c r="B37" s="60" t="s">
@@ -14269,12 +14068,12 @@
       <c r="E37" s="61" t="s">
         <v>404</v>
       </c>
-      <c r="F37" s="120" t="s">
+      <c r="F37" s="119" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="28">
-      <c r="A38" s="105" t="s">
+      <c r="A38" s="104" t="s">
         <v>399</v>
       </c>
       <c r="B38" s="60" t="s">
@@ -14289,19 +14088,19 @@
       <c r="E38" s="61" t="s">
         <v>409</v>
       </c>
-      <c r="F38" s="120" t="s">
+      <c r="F38" s="119" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="28">
-      <c r="A39" s="104" t="s">
+      <c r="A39" s="103" t="s">
         <v>399</v>
       </c>
       <c r="B39" s="59" t="s">
         <v>411</v>
       </c>
-      <c r="C39" s="186" t="s">
-        <v>1088</v>
+      <c r="C39" s="185" t="s">
+        <v>1073</v>
       </c>
       <c r="D39" s="47" t="s">
         <v>412</v>
@@ -14309,12 +14108,12 @@
       <c r="E39" s="47" t="s">
         <v>381</v>
       </c>
-      <c r="F39" s="119" t="s">
+      <c r="F39" s="118" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="28">
-      <c r="A40" s="99" t="s">
+      <c r="A40" s="98" t="s">
         <v>399</v>
       </c>
       <c r="B40" s="54" t="s">
@@ -14334,31 +14133,31 @@
       </c>
     </row>
     <row r="41" spans="1:6" ht="70">
-      <c r="A41" s="99" t="s">
+      <c r="A41" s="98" t="s">
         <v>399</v>
       </c>
       <c r="B41" s="54" t="s">
-        <v>920</v>
-      </c>
-      <c r="C41" s="192" t="s">
-        <v>1089</v>
+        <v>907</v>
+      </c>
+      <c r="C41" s="191" t="s">
+        <v>1074</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>1030</v>
+        <v>1016</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>921</v>
+        <v>908</v>
       </c>
       <c r="F41" s="85" t="s">
-        <v>922</v>
+        <v>909</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="28">
-      <c r="A42" s="105" t="s">
+      <c r="A42" s="104" t="s">
         <v>399</v>
       </c>
       <c r="B42" s="60" t="s">
-        <v>923</v>
+        <v>910</v>
       </c>
       <c r="C42" s="61" t="s">
         <v>417</v>
@@ -14369,239 +14168,239 @@
       <c r="E42" s="61" t="s">
         <v>409</v>
       </c>
-      <c r="F42" s="120" t="s">
+      <c r="F42" s="119" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="28">
-      <c r="A43" s="102" t="s">
+      <c r="A43" s="101" t="s">
         <v>399</v>
       </c>
       <c r="B43" s="57" t="s">
-        <v>968</v>
+        <v>954</v>
       </c>
       <c r="C43" s="33" t="s">
         <v>420</v>
       </c>
       <c r="D43" s="33" t="s">
-        <v>1031</v>
+        <v>1017</v>
       </c>
       <c r="E43" s="35" t="s">
         <v>421</v>
       </c>
-      <c r="F43" s="117" t="s">
+      <c r="F43" s="116" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="28">
-      <c r="A44" s="102" t="s">
+      <c r="A44" s="101" t="s">
         <v>399</v>
       </c>
-      <c r="B44" s="154" t="s">
-        <v>1074</v>
+      <c r="B44" s="153" t="s">
+        <v>1060</v>
       </c>
       <c r="C44" s="33" t="s">
-        <v>731</v>
+        <v>718</v>
       </c>
       <c r="D44" s="33" t="s">
-        <v>732</v>
+        <v>719</v>
       </c>
       <c r="E44" s="35" t="s">
         <v>483</v>
       </c>
-      <c r="F44" s="117" t="s">
-        <v>733</v>
+      <c r="F44" s="116" t="s">
+        <v>720</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="56">
-      <c r="A45" s="102" t="s">
+      <c r="A45" s="101" t="s">
         <v>399</v>
       </c>
-      <c r="B45" s="154" t="s">
-        <v>1074</v>
-      </c>
-      <c r="C45" s="191" t="s">
-        <v>1090</v>
+      <c r="B45" s="153" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C45" s="190" t="s">
+        <v>1075</v>
       </c>
       <c r="D45" s="33" t="s">
-        <v>1205</v>
+        <v>1188</v>
       </c>
       <c r="E45" s="35" t="s">
-        <v>779</v>
-      </c>
-      <c r="F45" s="117" t="s">
-        <v>780</v>
+        <v>766</v>
+      </c>
+      <c r="F45" s="116" t="s">
+        <v>767</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="56">
-      <c r="A46" s="102" t="s">
+      <c r="A46" s="101" t="s">
         <v>399</v>
       </c>
-      <c r="B46" s="154" t="s">
-        <v>1074</v>
-      </c>
-      <c r="C46" s="191" t="s">
-        <v>1091</v>
+      <c r="B46" s="153" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C46" s="190" t="s">
+        <v>1076</v>
       </c>
       <c r="D46" s="33" t="s">
-        <v>1206</v>
+        <v>1189</v>
       </c>
       <c r="E46" s="35" t="s">
-        <v>781</v>
-      </c>
-      <c r="F46" s="117" t="s">
-        <v>782</v>
+        <v>768</v>
+      </c>
+      <c r="F46" s="116" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="45" customHeight="1">
-      <c r="A47" s="102" t="s">
+      <c r="A47" s="101" t="s">
         <v>399</v>
       </c>
-      <c r="B47" s="154" t="s">
-        <v>1074</v>
-      </c>
-      <c r="C47" s="191" t="s">
-        <v>1092</v>
+      <c r="B47" s="153" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C47" s="190" t="s">
+        <v>1077</v>
       </c>
       <c r="D47" s="33" t="s">
-        <v>1036</v>
+        <v>1022</v>
       </c>
       <c r="E47" s="35" t="s">
-        <v>788</v>
-      </c>
-      <c r="F47" s="117" t="s">
-        <v>789</v>
+        <v>775</v>
+      </c>
+      <c r="F47" s="116" t="s">
+        <v>776</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="28">
-      <c r="A48" s="106" t="s">
+      <c r="A48" s="105" t="s">
         <v>399</v>
       </c>
       <c r="B48" s="63" t="s">
-        <v>969</v>
+        <v>955</v>
       </c>
       <c r="C48" s="20" t="s">
         <v>423</v>
       </c>
       <c r="D48" s="20" t="s">
-        <v>1032</v>
+        <v>1018</v>
       </c>
       <c r="E48" s="20" t="s">
         <v>424</v>
       </c>
-      <c r="F48" s="121" t="s">
+      <c r="F48" s="120" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="42">
-      <c r="A49" s="105" t="s">
+      <c r="A49" s="104" t="s">
         <v>399</v>
       </c>
-      <c r="B49" s="152" t="s">
-        <v>970</v>
+      <c r="B49" s="151" t="s">
+        <v>956</v>
       </c>
       <c r="C49" s="61" t="s">
         <v>425</v>
       </c>
       <c r="D49" s="61" t="s">
-        <v>1033</v>
+        <v>1019</v>
       </c>
       <c r="E49" s="61" t="s">
         <v>426</v>
       </c>
-      <c r="F49" s="120" t="s">
+      <c r="F49" s="119" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="28">
-      <c r="A50" s="103" t="s">
+      <c r="A50" s="102" t="s">
         <v>399</v>
       </c>
-      <c r="B50" s="155" t="s">
-        <v>1075</v>
+      <c r="B50" s="154" t="s">
+        <v>1061</v>
       </c>
       <c r="C50" s="39" t="s">
         <v>428</v>
       </c>
       <c r="D50" s="39" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="E50" s="39" t="s">
-        <v>745</v>
-      </c>
-      <c r="F50" s="118" t="s">
+        <v>732</v>
+      </c>
+      <c r="F50" s="117" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="42">
-      <c r="A51" s="98" t="s">
+      <c r="A51" s="97" t="s">
         <v>399</v>
       </c>
       <c r="B51" s="53" t="s">
-        <v>746</v>
+        <v>733</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>747</v>
+        <v>734</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
       <c r="F51" s="86" t="s">
-        <v>750</v>
+        <v>737</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="56">
-      <c r="A52" s="98" t="s">
+      <c r="A52" s="97" t="s">
         <v>399</v>
       </c>
-      <c r="B52" s="159" t="s">
-        <v>751</v>
-      </c>
-      <c r="C52" s="193" t="s">
-        <v>1093</v>
+      <c r="B52" s="158" t="s">
+        <v>738</v>
+      </c>
+      <c r="C52" s="192" t="s">
+        <v>1078</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>752</v>
+        <v>739</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>753</v>
+        <v>740</v>
       </c>
       <c r="F52" s="86" t="s">
-        <v>750</v>
+        <v>737</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="28">
-      <c r="A53" s="101" t="s">
+      <c r="A53" s="100" t="s">
         <v>399</v>
       </c>
-      <c r="B53" s="151" t="s">
-        <v>708</v>
+      <c r="B53" s="150" t="s">
+        <v>696</v>
       </c>
       <c r="C53" s="10" t="s">
         <v>431</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>754</v>
+        <v>741</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>377</v>
       </c>
-      <c r="F53" s="116" t="s">
+      <c r="F53" s="115" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="28">
-      <c r="A54" s="109" t="s">
+      <c r="A54" s="108" t="s">
         <v>399</v>
       </c>
       <c r="B54" s="65" t="s">
         <v>432</v>
       </c>
-      <c r="C54" s="194" t="s">
-        <v>1094</v>
+      <c r="C54" s="193" t="s">
+        <v>1079</v>
       </c>
       <c r="D54" s="42" t="s">
         <v>433</v>
@@ -14609,12 +14408,12 @@
       <c r="E54" s="42" t="s">
         <v>434</v>
       </c>
-      <c r="F54" s="124" t="s">
+      <c r="F54" s="123" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="28">
-      <c r="A55" s="103" t="s">
+      <c r="A55" s="102" t="s">
         <v>399</v>
       </c>
       <c r="B55" s="58" t="s">
@@ -14629,42 +14428,42 @@
       <c r="E55" s="39" t="s">
         <v>434</v>
       </c>
-      <c r="F55" s="118" t="s">
+      <c r="F55" s="117" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="42">
-      <c r="A56" s="103" t="s">
+      <c r="A56" s="102" t="s">
         <v>399</v>
       </c>
-      <c r="B56" s="155" t="s">
+      <c r="B56" s="154" t="s">
         <v>432</v>
       </c>
-      <c r="C56" s="195" t="s">
-        <v>1095</v>
-      </c>
-      <c r="D56" s="156" t="s">
-        <v>1034</v>
+      <c r="C56" s="194" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D56" s="155" t="s">
+        <v>1020</v>
       </c>
       <c r="E56" s="39" t="s">
-        <v>729</v>
-      </c>
-      <c r="F56" s="118" t="s">
-        <v>730</v>
+        <v>716</v>
+      </c>
+      <c r="F56" s="117" t="s">
+        <v>717</v>
       </c>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="197" t="s">
-        <v>955</v>
-      </c>
-      <c r="B57" s="198"/>
-      <c r="C57" s="198"/>
-      <c r="D57" s="198"/>
-      <c r="E57" s="198"/>
-      <c r="F57" s="199"/>
+      <c r="A57" s="196" t="s">
+        <v>942</v>
+      </c>
+      <c r="B57" s="197"/>
+      <c r="C57" s="197"/>
+      <c r="D57" s="197"/>
+      <c r="E57" s="197"/>
+      <c r="F57" s="198"/>
     </row>
     <row r="58" spans="1:6" ht="28">
-      <c r="A58" s="101" t="s">
+      <c r="A58" s="100" t="s">
         <v>438</v>
       </c>
       <c r="B58" s="56" t="s">
@@ -14679,12 +14478,12 @@
       <c r="E58" s="10" t="s">
         <v>441</v>
       </c>
-      <c r="F58" s="116" t="s">
+      <c r="F58" s="115" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="28">
-      <c r="A59" s="100" t="s">
+      <c r="A59" s="99" t="s">
         <v>438</v>
       </c>
       <c r="B59" s="55" t="s">
@@ -14699,12 +14498,12 @@
       <c r="E59" s="50" t="s">
         <v>445</v>
       </c>
-      <c r="F59" s="115" t="s">
+      <c r="F59" s="114" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="28">
-      <c r="A60" s="100" t="s">
+      <c r="A60" s="99" t="s">
         <v>438</v>
       </c>
       <c r="B60" s="55" t="s">
@@ -14719,19 +14518,19 @@
       <c r="E60" s="50" t="s">
         <v>450</v>
       </c>
-      <c r="F60" s="115" t="s">
+      <c r="F60" s="114" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="28">
-      <c r="A61" s="101" t="s">
+      <c r="A61" s="100" t="s">
         <v>438</v>
       </c>
       <c r="B61" s="56" t="s">
         <v>452</v>
       </c>
-      <c r="C61" s="189" t="s">
-        <v>1096</v>
+      <c r="C61" s="188" t="s">
+        <v>1081</v>
       </c>
       <c r="D61" s="10" t="s">
         <v>453</v>
@@ -14739,112 +14538,112 @@
       <c r="E61" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="F61" s="116" t="s">
+      <c r="F61" s="115" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="56">
-      <c r="A62" s="99" t="s">
+      <c r="A62" s="98" t="s">
         <v>438</v>
       </c>
-      <c r="B62" s="252" t="s">
-        <v>1173</v>
+      <c r="B62" s="251" t="s">
+        <v>1156</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>1174</v>
+        <v>1157</v>
       </c>
       <c r="D62" s="25" t="s">
-        <v>1189</v>
+        <v>1172</v>
       </c>
       <c r="E62" s="15" t="s">
         <v>145</v>
       </c>
       <c r="F62" s="85" t="s">
-        <v>1175</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="28">
-      <c r="A63" s="105" t="s">
+      <c r="A63" s="104" t="s">
         <v>438</v>
       </c>
-      <c r="B63" s="152" t="s">
-        <v>971</v>
+      <c r="B63" s="151" t="s">
+        <v>957</v>
       </c>
       <c r="C63" s="61" t="s">
         <v>456</v>
       </c>
       <c r="D63" s="61" t="s">
-        <v>1070</v>
+        <v>1056</v>
       </c>
       <c r="E63" s="61" t="s">
         <v>409</v>
       </c>
-      <c r="F63" s="120" t="s">
+      <c r="F63" s="119" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="86" customHeight="1">
-      <c r="A64" s="106" t="s">
+      <c r="A64" s="105" t="s">
         <v>438</v>
       </c>
-      <c r="B64" s="157" t="s">
-        <v>924</v>
+      <c r="B64" s="156" t="s">
+        <v>911</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>1176</v>
+        <v>1159</v>
       </c>
       <c r="D64" s="20" t="s">
-        <v>1190</v>
+        <v>1173</v>
       </c>
       <c r="E64" s="20" t="s">
-        <v>1177</v>
-      </c>
-      <c r="F64" s="121" t="s">
-        <v>1178</v>
+        <v>1160</v>
+      </c>
+      <c r="F64" s="120" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="28">
-      <c r="A65" s="105" t="s">
+      <c r="A65" s="104" t="s">
         <v>438</v>
       </c>
       <c r="B65" s="60" t="s">
-        <v>743</v>
+        <v>730</v>
       </c>
       <c r="C65" s="61" t="s">
         <v>459</v>
       </c>
       <c r="D65" s="61" t="s">
-        <v>972</v>
+        <v>958</v>
       </c>
       <c r="E65" s="61" t="s">
         <v>457</v>
       </c>
-      <c r="F65" s="120" t="s">
+      <c r="F65" s="119" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="45">
-      <c r="A66" s="110" t="s">
+      <c r="A66" s="109" t="s">
         <v>438</v>
       </c>
       <c r="B66" s="91" t="s">
-        <v>973</v>
+        <v>959</v>
       </c>
       <c r="C66" s="92" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D66" s="92" t="s">
-        <v>974</v>
+        <v>960</v>
       </c>
       <c r="E66" s="92" t="s">
-        <v>696</v>
-      </c>
-      <c r="F66" s="125" t="s">
-        <v>697</v>
+        <v>686</v>
+      </c>
+      <c r="F66" s="124" t="s">
+        <v>687</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="28">
-      <c r="A67" s="105" t="s">
+      <c r="A67" s="104" t="s">
         <v>438</v>
       </c>
       <c r="B67" s="60" t="s">
@@ -14859,16 +14658,16 @@
       <c r="E67" s="61" t="s">
         <v>463</v>
       </c>
-      <c r="F67" s="120" t="s">
+      <c r="F67" s="119" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="28">
-      <c r="A68" s="107" t="s">
+      <c r="A68" s="106" t="s">
         <v>438</v>
       </c>
       <c r="B68" s="64" t="s">
-        <v>705</v>
+        <v>693</v>
       </c>
       <c r="C68" s="36" t="s">
         <v>466</v>
@@ -14879,19 +14678,19 @@
       <c r="E68" s="36" t="s">
         <v>468</v>
       </c>
-      <c r="F68" s="122" t="s">
+      <c r="F68" s="121" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="28">
-      <c r="A69" s="109" t="s">
+      <c r="A69" s="108" t="s">
         <v>438</v>
       </c>
       <c r="B69" s="65" t="s">
-        <v>706</v>
-      </c>
-      <c r="C69" s="194" t="s">
-        <v>1097</v>
+        <v>694</v>
+      </c>
+      <c r="C69" s="193" t="s">
+        <v>1082</v>
       </c>
       <c r="D69" s="44" t="s">
         <v>470</v>
@@ -14899,16 +14698,16 @@
       <c r="E69" s="42" t="s">
         <v>471</v>
       </c>
-      <c r="F69" s="124" t="s">
+      <c r="F69" s="123" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="28">
-      <c r="A70" s="101" t="s">
+      <c r="A70" s="100" t="s">
         <v>438</v>
       </c>
-      <c r="B70" s="128" t="s">
-        <v>708</v>
+      <c r="B70" s="127" t="s">
+        <v>696</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>473</v>
@@ -14917,42 +14716,42 @@
       <c r="E70" s="10" t="s">
         <v>474</v>
       </c>
-      <c r="F70" s="116" t="s">
+      <c r="F70" s="115" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="100" customHeight="1">
-      <c r="A71" s="101" t="s">
+      <c r="A71" s="100" t="s">
         <v>438</v>
       </c>
-      <c r="B71" s="128" t="s">
+      <c r="B71" s="127" t="s">
         <v>432</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>1179</v>
+        <v>1162</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>1180</v>
+        <v>1163</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>1181</v>
-      </c>
-      <c r="F71" s="116" t="s">
-        <v>1182</v>
+        <v>1164</v>
+      </c>
+      <c r="F71" s="115" t="s">
+        <v>1165</v>
       </c>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="197" t="s">
-        <v>956</v>
-      </c>
-      <c r="B72" s="198"/>
-      <c r="C72" s="198"/>
-      <c r="D72" s="198"/>
-      <c r="E72" s="198"/>
-      <c r="F72" s="199"/>
+      <c r="A72" s="196" t="s">
+        <v>943</v>
+      </c>
+      <c r="B72" s="197"/>
+      <c r="C72" s="197"/>
+      <c r="D72" s="197"/>
+      <c r="E72" s="197"/>
+      <c r="F72" s="198"/>
     </row>
     <row r="73" spans="1:6" ht="56" customHeight="1">
-      <c r="A73" s="101" t="s">
+      <c r="A73" s="100" t="s">
         <v>475</v>
       </c>
       <c r="B73" s="56" t="s">
@@ -14967,82 +14766,82 @@
       <c r="E73" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F73" s="116" t="s">
+      <c r="F73" s="115" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="56" customHeight="1">
-      <c r="A74" s="105" t="s">
+      <c r="A74" s="104" t="s">
         <v>475</v>
       </c>
-      <c r="B74" s="152" t="s">
-        <v>1170</v>
+      <c r="B74" s="151" t="s">
+        <v>1153</v>
       </c>
       <c r="C74" s="61" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D74" s="62" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E74" s="61" t="s">
+        <v>1107</v>
+      </c>
+      <c r="F74" s="119" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="56" customHeight="1">
+      <c r="A75" s="103" t="s">
+        <v>475</v>
+      </c>
+      <c r="B75" s="187" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C75" s="47" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D75" s="47" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E75" s="47" t="s">
         <v>1113</v>
       </c>
-      <c r="D74" s="62" t="s">
-        <v>1128</v>
-      </c>
-      <c r="E74" s="61" t="s">
-        <v>1125</v>
-      </c>
-      <c r="F74" s="120" t="s">
+      <c r="F75" s="118" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="56" customHeight="1">
+      <c r="A76" s="104" t="s">
+        <v>475</v>
+      </c>
+      <c r="B76" s="151" t="s">
+        <v>564</v>
+      </c>
+      <c r="C76" s="61" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D76" s="61" t="s">
+        <v>1108</v>
+      </c>
+      <c r="E76" s="61" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F76" s="119" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="56" customHeight="1">
+      <c r="A77" s="97" t="s">
+        <v>475</v>
+      </c>
+      <c r="B77" s="158" t="s">
         <v>1114</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" ht="56" customHeight="1">
-      <c r="A75" s="104" t="s">
-        <v>475</v>
-      </c>
-      <c r="B75" s="188" t="s">
-        <v>1129</v>
-      </c>
-      <c r="C75" s="47" t="s">
+      <c r="C77" s="5" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D77" s="5" t="s">
         <v>1115</v>
-      </c>
-      <c r="D75" s="47" t="s">
-        <v>1130</v>
-      </c>
-      <c r="E75" s="47" t="s">
-        <v>1131</v>
-      </c>
-      <c r="F75" s="119" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="56" customHeight="1">
-      <c r="A76" s="105" t="s">
-        <v>475</v>
-      </c>
-      <c r="B76" s="152" t="s">
-        <v>574</v>
-      </c>
-      <c r="C76" s="61" t="s">
-        <v>1116</v>
-      </c>
-      <c r="D76" s="61" t="s">
-        <v>1126</v>
-      </c>
-      <c r="E76" s="61" t="s">
-        <v>1127</v>
-      </c>
-      <c r="F76" s="120" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="56" customHeight="1">
-      <c r="A77" s="98" t="s">
-        <v>475</v>
-      </c>
-      <c r="B77" s="159" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>1117</v>
-      </c>
-      <c r="D77" s="5" t="s">
-        <v>1133</v>
       </c>
       <c r="E77" s="5" t="s">
         <v>481</v>
@@ -15052,250 +14851,250 @@
       </c>
     </row>
     <row r="78" spans="1:6" ht="72" customHeight="1">
-      <c r="A78" s="105" t="s">
+      <c r="A78" s="104" t="s">
         <v>475</v>
       </c>
-      <c r="B78" s="152" t="s">
+      <c r="B78" s="151" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C78" s="61" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D78" s="61" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E78" s="61" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F78" s="119" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="72" customHeight="1">
+      <c r="A79" s="103" t="s">
+        <v>475</v>
+      </c>
+      <c r="B79" s="187" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C79" s="47" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D79" s="47" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E79" s="47" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F79" s="118" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="86" customHeight="1">
+      <c r="A80" s="103" t="s">
+        <v>475</v>
+      </c>
+      <c r="B80" s="187" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C80" s="47" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D80" s="47" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E80" s="47" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F80" s="118" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="86" customHeight="1">
+      <c r="A81" s="103" t="s">
+        <v>475</v>
+      </c>
+      <c r="B81" s="187" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C81" s="47" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D81" s="47" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E81" s="47" t="s">
+        <v>1132</v>
+      </c>
+      <c r="F81" s="118" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="72" customHeight="1">
+      <c r="A82" s="103" t="s">
+        <v>475</v>
+      </c>
+      <c r="B82" s="187" t="s">
         <v>1134</v>
       </c>
-      <c r="C78" s="61" t="s">
+      <c r="C82" s="47" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D82" s="47" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E82" s="47" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F82" s="118" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="56" customHeight="1">
+      <c r="A83" s="105" t="s">
+        <v>475</v>
+      </c>
+      <c r="B83" s="156" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C83" s="20" t="s">
         <v>1118</v>
       </c>
-      <c r="D78" s="61" t="s">
-        <v>1135</v>
-      </c>
-      <c r="E78" s="61" t="s">
-        <v>1119</v>
-      </c>
-      <c r="F78" s="120" t="s">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="72" customHeight="1">
-      <c r="A79" s="104" t="s">
+      <c r="D83" s="20" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E83" s="20" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F83" s="120" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="72" customHeight="1">
+      <c r="A84" s="101" t="s">
         <v>475</v>
       </c>
-      <c r="B79" s="188" t="s">
-        <v>1139</v>
-      </c>
-      <c r="C79" s="47" t="s">
-        <v>1140</v>
-      </c>
-      <c r="D79" s="47" t="s">
+      <c r="B84" s="153" t="s">
         <v>1141</v>
       </c>
-      <c r="E79" s="47" t="s">
+      <c r="C84" s="190" t="s">
         <v>1142</v>
       </c>
-      <c r="F79" s="119" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="86" customHeight="1">
-      <c r="A80" s="104" t="s">
+      <c r="D84" s="33" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E84" s="33" t="s">
+        <v>1144</v>
+      </c>
+      <c r="F84" s="116" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="150" customHeight="1">
+      <c r="A85" s="101" t="s">
         <v>475</v>
       </c>
-      <c r="B80" s="188" t="s">
-        <v>1143</v>
-      </c>
-      <c r="C80" s="47" t="s">
-        <v>1144</v>
-      </c>
-      <c r="D80" s="47" t="s">
-        <v>1145</v>
-      </c>
-      <c r="E80" s="47" t="s">
+      <c r="B85" s="153" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C85" s="190" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D85" s="33" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E85" s="33" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F85" s="116" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="72" customHeight="1">
+      <c r="A86" s="106" t="s">
+        <v>475</v>
+      </c>
+      <c r="B86" s="159" t="s">
+        <v>543</v>
+      </c>
+      <c r="C86" s="36" t="s">
         <v>1146</v>
       </c>
-      <c r="F80" s="119" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="86" customHeight="1">
-      <c r="A81" s="104" t="s">
+      <c r="D86" s="36" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E86" s="36" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F86" s="121" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="56" customHeight="1">
+      <c r="A87" s="100" t="s">
         <v>475</v>
       </c>
-      <c r="B81" s="188" t="s">
-        <v>1147</v>
-      </c>
-      <c r="C81" s="47" t="s">
-        <v>1148</v>
-      </c>
-      <c r="D81" s="47" t="s">
+      <c r="B87" s="150" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C87" s="188" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D87" s="10" t="s">
         <v>1149</v>
       </c>
-      <c r="E81" s="47" t="s">
+      <c r="E87" s="10" t="s">
         <v>1150</v>
       </c>
-      <c r="F81" s="119" t="s">
+      <c r="F87" s="115" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="56" customHeight="1">
+      <c r="A88" s="100" t="s">
+        <v>475</v>
+      </c>
+      <c r="B88" s="150" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C88" s="10" t="s">
         <v>1151</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" ht="72" customHeight="1">
-      <c r="A82" s="104" t="s">
-        <v>475</v>
-      </c>
-      <c r="B82" s="188" t="s">
+      <c r="D88" s="10" t="s">
         <v>1152</v>
-      </c>
-      <c r="C82" s="47" t="s">
-        <v>1153</v>
-      </c>
-      <c r="D82" s="47" t="s">
-        <v>1154</v>
-      </c>
-      <c r="E82" s="47" t="s">
-        <v>1146</v>
-      </c>
-      <c r="F82" s="119" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="56" customHeight="1">
-      <c r="A83" s="106" t="s">
-        <v>475</v>
-      </c>
-      <c r="B83" s="157" t="s">
-        <v>1156</v>
-      </c>
-      <c r="C83" s="20" t="s">
-        <v>1136</v>
-      </c>
-      <c r="D83" s="20" t="s">
-        <v>1157</v>
-      </c>
-      <c r="E83" s="20" t="s">
-        <v>1158</v>
-      </c>
-      <c r="F83" s="121" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="72" customHeight="1">
-      <c r="A84" s="102" t="s">
-        <v>475</v>
-      </c>
-      <c r="B84" s="154" t="s">
-        <v>1159</v>
-      </c>
-      <c r="C84" s="191" t="s">
-        <v>1160</v>
-      </c>
-      <c r="D84" s="33" t="s">
-        <v>1161</v>
-      </c>
-      <c r="E84" s="33" t="s">
-        <v>1162</v>
-      </c>
-      <c r="F84" s="117" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="150" customHeight="1">
-      <c r="A85" s="102" t="s">
-        <v>475</v>
-      </c>
-      <c r="B85" s="154" t="s">
-        <v>1183</v>
-      </c>
-      <c r="C85" s="191" t="s">
-        <v>1108</v>
-      </c>
-      <c r="D85" s="33" t="s">
-        <v>1191</v>
-      </c>
-      <c r="E85" s="33" t="s">
-        <v>1121</v>
-      </c>
-      <c r="F85" s="117" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="72" customHeight="1">
-      <c r="A86" s="107" t="s">
-        <v>475</v>
-      </c>
-      <c r="B86" s="160" t="s">
-        <v>549</v>
-      </c>
-      <c r="C86" s="36" t="s">
-        <v>1163</v>
-      </c>
-      <c r="D86" s="36" t="s">
-        <v>1192</v>
-      </c>
-      <c r="E86" s="36" t="s">
-        <v>1164</v>
-      </c>
-      <c r="F86" s="122" t="s">
-        <v>1165</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="56" customHeight="1">
-      <c r="A87" s="101" t="s">
-        <v>475</v>
-      </c>
-      <c r="B87" s="151" t="s">
-        <v>1184</v>
-      </c>
-      <c r="C87" s="189" t="s">
-        <v>1098</v>
-      </c>
-      <c r="D87" s="10" t="s">
-        <v>1166</v>
-      </c>
-      <c r="E87" s="10" t="s">
-        <v>1167</v>
-      </c>
-      <c r="F87" s="116" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="56" customHeight="1">
-      <c r="A88" s="101" t="s">
-        <v>475</v>
-      </c>
-      <c r="B88" s="151" t="s">
-        <v>1185</v>
-      </c>
-      <c r="C88" s="10" t="s">
-        <v>1168</v>
-      </c>
-      <c r="D88" s="10" t="s">
-        <v>1169</v>
       </c>
       <c r="E88" s="10" t="s">
         <v>429</v>
       </c>
-      <c r="F88" s="116" t="s">
-        <v>635</v>
+      <c r="F88" s="115" t="s">
+        <v>625</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="28">
-      <c r="A89" s="101" t="s">
+      <c r="A89" s="100" t="s">
         <v>475</v>
       </c>
-      <c r="B89" s="151" t="s">
-        <v>1186</v>
+      <c r="B89" s="150" t="s">
+        <v>1169</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>1137</v>
+        <v>1119</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>1171</v>
+        <v>1154</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>1138</v>
-      </c>
-      <c r="F89" s="116" t="s">
-        <v>1172</v>
+        <v>1120</v>
+      </c>
+      <c r="F89" s="115" t="s">
+        <v>1155</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="28">
-      <c r="A90" s="103" t="s">
+      <c r="A90" s="102" t="s">
         <v>475</v>
       </c>
-      <c r="B90" s="155" t="s">
+      <c r="B90" s="154" t="s">
         <v>432</v>
       </c>
       <c r="C90" s="39" t="s">
@@ -15307,32 +15106,32 @@
       <c r="E90" s="39" t="s">
         <v>434</v>
       </c>
-      <c r="F90" s="118" t="s">
+      <c r="F90" s="117" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="86" customHeight="1">
-      <c r="A91" s="103" t="s">
+      <c r="A91" s="102" t="s">
         <v>475</v>
       </c>
-      <c r="B91" s="155" t="s">
+      <c r="B91" s="154" t="s">
         <v>432</v>
       </c>
       <c r="C91" s="39" t="s">
-        <v>1123</v>
+        <v>1105</v>
       </c>
       <c r="D91" s="39" t="s">
-        <v>1124</v>
+        <v>1106</v>
       </c>
       <c r="E91" s="39" t="s">
-        <v>699</v>
-      </c>
-      <c r="F91" s="118" t="s">
-        <v>632</v>
+        <v>689</v>
+      </c>
+      <c r="F91" s="117" t="s">
+        <v>622</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="28">
-      <c r="A92" s="103" t="s">
+      <c r="A92" s="102" t="s">
         <v>475</v>
       </c>
       <c r="B92" s="58" t="s">
@@ -15347,62 +15146,62 @@
       <c r="E92" s="39" t="s">
         <v>434</v>
       </c>
-      <c r="F92" s="118" t="s">
+      <c r="F92" s="117" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="45">
-      <c r="A93" s="108" t="s">
+      <c r="A93" s="107" t="s">
         <v>475</v>
       </c>
       <c r="B93" s="89" t="s">
         <v>432</v>
       </c>
-      <c r="C93" s="196" t="s">
-        <v>1099</v>
-      </c>
-      <c r="D93" s="95" t="s">
-        <v>698</v>
+      <c r="C93" s="195" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D93" s="94" t="s">
+        <v>688</v>
       </c>
       <c r="E93" s="90" t="s">
-        <v>699</v>
-      </c>
-      <c r="F93" s="123" t="s">
-        <v>700</v>
+        <v>689</v>
+      </c>
+      <c r="F93" s="122" t="s">
+        <v>690</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="45">
-      <c r="A94" s="108" t="s">
+      <c r="A94" s="107" t="s">
         <v>475</v>
       </c>
-      <c r="B94" s="153" t="s">
+      <c r="B94" s="152" t="s">
         <v>432</v>
       </c>
       <c r="C94" s="90" t="s">
-        <v>725</v>
-      </c>
-      <c r="D94" s="95" t="s">
-        <v>726</v>
+        <v>712</v>
+      </c>
+      <c r="D94" s="94" t="s">
+        <v>713</v>
       </c>
       <c r="E94" s="90" t="s">
-        <v>699</v>
-      </c>
-      <c r="F94" s="123" t="s">
-        <v>727</v>
+        <v>689</v>
+      </c>
+      <c r="F94" s="122" t="s">
+        <v>714</v>
       </c>
     </row>
     <row r="95" spans="1:6">
-      <c r="A95" s="200" t="s">
-        <v>957</v>
-      </c>
-      <c r="B95" s="201"/>
-      <c r="C95" s="201"/>
-      <c r="D95" s="201"/>
-      <c r="E95" s="201"/>
-      <c r="F95" s="202"/>
+      <c r="A95" s="199" t="s">
+        <v>944</v>
+      </c>
+      <c r="B95" s="200"/>
+      <c r="C95" s="200"/>
+      <c r="D95" s="200"/>
+      <c r="E95" s="200"/>
+      <c r="F95" s="201"/>
     </row>
     <row r="96" spans="1:6" ht="28">
-      <c r="A96" s="101" t="s">
+      <c r="A96" s="100" t="s">
         <v>491</v>
       </c>
       <c r="B96" s="56" t="s">
@@ -15415,12 +15214,12 @@
       <c r="E96" s="10" t="s">
         <v>441</v>
       </c>
-      <c r="F96" s="116" t="s">
+      <c r="F96" s="115" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="28">
-      <c r="A97" s="100" t="s">
+      <c r="A97" s="99" t="s">
         <v>491</v>
       </c>
       <c r="B97" s="55" t="s">
@@ -15435,12 +15234,12 @@
       <c r="E97" s="50" t="s">
         <v>445</v>
       </c>
-      <c r="F97" s="115" t="s">
+      <c r="F97" s="114" t="s">
         <v>495</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="28">
-      <c r="A98" s="100" t="s">
+      <c r="A98" s="99" t="s">
         <v>491</v>
       </c>
       <c r="B98" s="55" t="s">
@@ -15455,19 +15254,19 @@
       <c r="E98" s="50" t="s">
         <v>450</v>
       </c>
-      <c r="F98" s="115" t="s">
+      <c r="F98" s="114" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="28">
-      <c r="A99" s="101" t="s">
+      <c r="A99" s="100" t="s">
         <v>491</v>
       </c>
       <c r="B99" s="56" t="s">
         <v>452</v>
       </c>
-      <c r="C99" s="189" t="s">
-        <v>1100</v>
+      <c r="C99" s="188" t="s">
+        <v>1085</v>
       </c>
       <c r="D99" s="10" t="s">
         <v>499</v>
@@ -15475,12 +15274,12 @@
       <c r="E99" s="10" t="s">
         <v>500</v>
       </c>
-      <c r="F99" s="116" t="s">
+      <c r="F99" s="115" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="28">
-      <c r="A100" s="99" t="s">
+      <c r="A100" s="98" t="s">
         <v>491</v>
       </c>
       <c r="B100" s="54" t="s">
@@ -15500,7 +15299,7 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="28">
-      <c r="A101" s="105" t="s">
+      <c r="A101" s="104" t="s">
         <v>491</v>
       </c>
       <c r="B101" s="60" t="s">
@@ -15515,241 +15314,241 @@
       <c r="E101" s="61" t="s">
         <v>507</v>
       </c>
-      <c r="F101" s="120" t="s">
+      <c r="F101" s="119" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="56">
-      <c r="A102" s="105" t="s">
+      <c r="A102" s="104" t="s">
         <v>491</v>
       </c>
       <c r="B102" s="60" t="s">
-        <v>964</v>
+        <v>951</v>
       </c>
       <c r="C102" s="61" t="s">
-        <v>961</v>
+        <v>948</v>
       </c>
       <c r="D102" s="61" t="s">
-        <v>962</v>
+        <v>949</v>
       </c>
       <c r="E102" s="61" t="s">
-        <v>963</v>
-      </c>
-      <c r="F102" s="120" t="s">
+        <v>950</v>
+      </c>
+      <c r="F102" s="119" t="s">
         <v>509</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="28">
-      <c r="A103" s="105" t="s">
+      <c r="A103" s="104" t="s">
         <v>491</v>
       </c>
       <c r="B103" s="60" t="s">
-        <v>965</v>
+        <v>952</v>
       </c>
       <c r="C103" s="61" t="s">
         <v>510</v>
       </c>
       <c r="D103" s="61" t="s">
-        <v>1071</v>
+        <v>1057</v>
       </c>
       <c r="E103" s="61" t="s">
         <v>511</v>
       </c>
-      <c r="F103" s="120" t="s">
+      <c r="F103" s="119" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="28">
-      <c r="A104" s="106" t="s">
+      <c r="A104" s="105" t="s">
         <v>491</v>
       </c>
-      <c r="B104" s="63" t="s">
-        <v>966</v>
+      <c r="B104" s="156" t="s">
+        <v>1192</v>
       </c>
       <c r="C104" s="20" t="s">
         <v>513</v>
       </c>
       <c r="D104" s="20" t="s">
-        <v>967</v>
+        <v>953</v>
       </c>
       <c r="E104" s="20" t="s">
         <v>514</v>
       </c>
-      <c r="F104" s="121" t="s">
+      <c r="F104" s="120" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="28">
-      <c r="A105" s="105" t="s">
+    <row r="105" spans="1:6" ht="58" customHeight="1">
+      <c r="A105" s="104" t="s">
         <v>491</v>
       </c>
-      <c r="B105" s="60" t="s">
+      <c r="B105" s="151" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C105" s="61" t="s">
         <v>515</v>
       </c>
-      <c r="C105" s="61" t="s">
-        <v>516</v>
-      </c>
       <c r="D105" s="61" t="s">
-        <v>517</v>
+        <v>1194</v>
       </c>
       <c r="E105" s="61" t="s">
         <v>98</v>
       </c>
-      <c r="F105" s="120" t="s">
+      <c r="F105" s="119" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="42">
-      <c r="A106" s="105" t="s">
+    <row r="106" spans="1:6" ht="100" customHeight="1">
+      <c r="A106" s="104" t="s">
         <v>491</v>
       </c>
-      <c r="B106" s="152" t="s">
-        <v>1076</v>
-      </c>
-      <c r="C106" s="187" t="s">
-        <v>1101</v>
+      <c r="B106" s="151" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C106" s="186" t="s">
+        <v>1195</v>
       </c>
       <c r="D106" s="61" t="s">
-        <v>724</v>
+        <v>1196</v>
       </c>
       <c r="E106" s="61" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F106" s="119" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="58" customHeight="1">
+      <c r="A107" s="104" t="s">
+        <v>491</v>
+      </c>
+      <c r="B107" s="151" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C107" s="186" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D107" s="61" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E107" s="61" t="s">
         <v>483</v>
       </c>
-      <c r="F106" s="120" t="s">
+      <c r="F107" s="119" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="140">
-      <c r="A107" s="105" t="s">
+    <row r="108" spans="1:6" ht="100" customHeight="1">
+      <c r="A108" s="108" t="s">
         <v>491</v>
       </c>
-      <c r="B107" s="152" t="s">
-        <v>1076</v>
-      </c>
-      <c r="C107" s="187" t="s">
-        <v>1102</v>
-      </c>
-      <c r="D107" s="61" t="s">
-        <v>1207</v>
-      </c>
-      <c r="E107" s="61" t="s">
-        <v>815</v>
-      </c>
-      <c r="F107" s="120" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" ht="28">
-      <c r="A108" s="109" t="s">
+      <c r="B108" s="252" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C108" s="193" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D108" s="42" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E108" s="42" t="s">
+        <v>802</v>
+      </c>
+      <c r="F108" s="123" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="58" customHeight="1">
+      <c r="A109" s="110" t="s">
         <v>491</v>
       </c>
-      <c r="B108" s="65" t="s">
-        <v>518</v>
-      </c>
-      <c r="C108" s="194" t="s">
-        <v>1103</v>
-      </c>
-      <c r="D108" s="42" t="s">
-        <v>519</v>
-      </c>
-      <c r="E108" s="42" t="s">
-        <v>520</v>
-      </c>
-      <c r="F108" s="124" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" ht="30">
-      <c r="A109" s="111" t="s">
+      <c r="B109" s="253" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C109" s="93" t="s">
+        <v>691</v>
+      </c>
+      <c r="D109" s="93" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E109" s="93" t="s">
+        <v>692</v>
+      </c>
+      <c r="F109" s="125" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="28">
+      <c r="A110" s="100" t="s">
         <v>491</v>
       </c>
-      <c r="B109" s="93" t="s">
-        <v>701</v>
-      </c>
-      <c r="C109" s="94" t="s">
-        <v>702</v>
-      </c>
-      <c r="D109" s="94" t="s">
-        <v>703</v>
-      </c>
-      <c r="E109" s="94" t="s">
-        <v>704</v>
-      </c>
-      <c r="F109" s="126" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" ht="28">
-      <c r="A110" s="101" t="s">
-        <v>491</v>
-      </c>
-      <c r="B110" s="128" t="s">
-        <v>708</v>
+      <c r="B110" s="127" t="s">
+        <v>696</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>707</v>
+        <v>695</v>
       </c>
       <c r="D110" s="10"/>
       <c r="E110" s="10" t="s">
         <v>474</v>
       </c>
-      <c r="F110" s="116" t="s">
+      <c r="F110" s="115" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="42">
-      <c r="A111" s="102" t="s">
+      <c r="A111" s="101" t="s">
         <v>491</v>
       </c>
-      <c r="B111" s="154" t="s">
-        <v>708</v>
-      </c>
-      <c r="C111" s="191" t="s">
-        <v>1104</v>
+      <c r="B111" s="153" t="s">
+        <v>696</v>
+      </c>
+      <c r="C111" s="190" t="s">
+        <v>1086</v>
       </c>
       <c r="D111" s="33" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="E111" s="33" t="s">
         <v>429</v>
       </c>
-      <c r="F111" s="117" t="s">
+      <c r="F111" s="116" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="28">
-      <c r="A112" s="103" t="s">
+      <c r="A112" s="102" t="s">
         <v>491</v>
       </c>
-      <c r="B112" s="155" t="s">
-        <v>708</v>
+      <c r="B112" s="154" t="s">
+        <v>696</v>
       </c>
       <c r="C112" s="39" t="s">
-        <v>736</v>
+        <v>723</v>
       </c>
       <c r="D112" s="39" t="s">
-        <v>737</v>
+        <v>724</v>
       </c>
       <c r="E112" s="39" t="s">
         <v>429</v>
       </c>
-      <c r="F112" s="118" t="s">
-        <v>738</v>
+      <c r="F112" s="117" t="s">
+        <v>725</v>
       </c>
     </row>
     <row r="113" spans="1:6">
-      <c r="A113" s="200" t="s">
-        <v>958</v>
-      </c>
-      <c r="B113" s="201"/>
-      <c r="C113" s="201"/>
-      <c r="D113" s="201"/>
-      <c r="E113" s="201"/>
-      <c r="F113" s="202"/>
+      <c r="A113" s="199" t="s">
+        <v>945</v>
+      </c>
+      <c r="B113" s="200"/>
+      <c r="C113" s="200"/>
+      <c r="D113" s="200"/>
+      <c r="E113" s="200"/>
+      <c r="F113" s="201"/>
     </row>
     <row r="114" spans="1:6" ht="28">
-      <c r="A114" s="101" t="s">
-        <v>523</v>
+      <c r="A114" s="100" t="s">
+        <v>517</v>
       </c>
       <c r="B114" s="56" t="s">
         <v>400</v>
@@ -15758,523 +15557,563 @@
         <v>476</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="E114" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F114" s="116" t="s">
+      <c r="F114" s="115" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="28">
-      <c r="A115" s="105" t="s">
-        <v>523</v>
+      <c r="A115" s="104" t="s">
+        <v>517</v>
       </c>
       <c r="B115" s="60" t="s">
         <v>401</v>
       </c>
       <c r="C115" s="61" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D115" s="61" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="E115" s="61" t="s">
         <v>404</v>
       </c>
-      <c r="F115" s="120" t="s">
-        <v>527</v>
+      <c r="F115" s="119" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="28">
-      <c r="A116" s="105" t="s">
+      <c r="A116" s="104" t="s">
+        <v>517</v>
+      </c>
+      <c r="B116" s="60" t="s">
+        <v>522</v>
+      </c>
+      <c r="C116" s="61" t="s">
         <v>523</v>
       </c>
-      <c r="B116" s="60" t="s">
-        <v>528</v>
-      </c>
-      <c r="C116" s="61" t="s">
-        <v>529</v>
-      </c>
       <c r="D116" s="61" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="E116" s="61" t="s">
-        <v>531</v>
-      </c>
-      <c r="F116" s="120" t="s">
-        <v>532</v>
+        <v>525</v>
+      </c>
+      <c r="F116" s="119" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="28">
-      <c r="A117" s="105" t="s">
-        <v>523</v>
+      <c r="A117" s="104" t="s">
+        <v>517</v>
       </c>
       <c r="B117" s="60" t="s">
         <v>479</v>
       </c>
       <c r="C117" s="61" t="s">
+        <v>527</v>
+      </c>
+      <c r="D117" s="61" t="s">
+        <v>528</v>
+      </c>
+      <c r="E117" s="61" t="s">
+        <v>529</v>
+      </c>
+      <c r="F117" s="119" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" ht="56">
+      <c r="A118" s="104" t="s">
+        <v>517</v>
+      </c>
+      <c r="B118" s="151" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C118" s="61" t="s">
+        <v>708</v>
+      </c>
+      <c r="D118" s="61" t="s">
+        <v>709</v>
+      </c>
+      <c r="E118" s="61" t="s">
+        <v>710</v>
+      </c>
+      <c r="F118" s="119" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="28">
+      <c r="A119" s="97" t="s">
+        <v>517</v>
+      </c>
+      <c r="B119" s="53" t="s">
+        <v>530</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="D119" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="E119" s="5" t="s">
         <v>533</v>
-      </c>
-      <c r="D117" s="61" t="s">
-        <v>534</v>
-      </c>
-      <c r="E117" s="61" t="s">
-        <v>535</v>
-      </c>
-      <c r="F117" s="120" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" ht="56">
-      <c r="A118" s="105" t="s">
-        <v>523</v>
-      </c>
-      <c r="B118" s="152" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C118" s="61" t="s">
-        <v>720</v>
-      </c>
-      <c r="D118" s="61" t="s">
-        <v>721</v>
-      </c>
-      <c r="E118" s="61" t="s">
-        <v>722</v>
-      </c>
-      <c r="F118" s="120" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" ht="28">
-      <c r="A119" s="98" t="s">
-        <v>523</v>
-      </c>
-      <c r="B119" s="53" t="s">
-        <v>536</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>537</v>
-      </c>
-      <c r="D119" s="5" t="s">
-        <v>538</v>
-      </c>
-      <c r="E119" s="5" t="s">
-        <v>539</v>
       </c>
       <c r="F119" s="86" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="28">
-      <c r="A120" s="102" t="s">
-        <v>523</v>
+      <c r="A120" s="101" t="s">
+        <v>517</v>
       </c>
       <c r="B120" s="57" t="s">
-        <v>975</v>
+        <v>961</v>
       </c>
       <c r="C120" s="33" t="s">
-        <v>959</v>
+        <v>946</v>
       </c>
       <c r="D120" s="33" t="s">
-        <v>960</v>
+        <v>947</v>
       </c>
       <c r="E120" s="33" t="s">
-        <v>540</v>
-      </c>
-      <c r="F120" s="117" t="s">
+        <v>534</v>
+      </c>
+      <c r="F120" s="116" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="28">
-      <c r="A121" s="105" t="s">
-        <v>523</v>
+      <c r="A121" s="104" t="s">
+        <v>517</v>
       </c>
       <c r="B121" s="60" t="s">
-        <v>976</v>
+        <v>962</v>
       </c>
       <c r="C121" s="61" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="D121" s="61" t="s">
-        <v>1035</v>
+        <v>1021</v>
       </c>
       <c r="E121" s="61" t="s">
         <v>392</v>
       </c>
-      <c r="F121" s="120" t="s">
-        <v>542</v>
+      <c r="F121" s="119" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="28">
-      <c r="A122" s="106" t="s">
-        <v>523</v>
+      <c r="A122" s="105" t="s">
+        <v>517</v>
       </c>
       <c r="B122" s="63" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="C122" s="20" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="D122" s="20" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="E122" s="20" t="s">
         <v>424</v>
       </c>
-      <c r="F122" s="121" t="s">
+      <c r="F122" s="120" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="28">
-      <c r="A123" s="109" t="s">
-        <v>523</v>
+      <c r="A123" s="108" t="s">
+        <v>517</v>
       </c>
       <c r="B123" s="65" t="s">
         <v>458</v>
       </c>
-      <c r="C123" s="194" t="s">
-        <v>1105</v>
+      <c r="C123" s="193" t="s">
+        <v>1087</v>
       </c>
       <c r="D123" s="42" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="E123" s="42" t="s">
-        <v>547</v>
-      </c>
-      <c r="F123" s="124" t="s">
+        <v>541</v>
+      </c>
+      <c r="F123" s="123" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="140">
-      <c r="A124" s="99" t="s">
-        <v>523</v>
+      <c r="A124" s="98" t="s">
+        <v>517</v>
       </c>
       <c r="B124" s="54" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>798</v>
+        <v>785</v>
       </c>
       <c r="D124" s="15" t="s">
-        <v>799</v>
+        <v>786</v>
       </c>
       <c r="E124" s="15" t="s">
-        <v>800</v>
+        <v>787</v>
       </c>
       <c r="F124" s="85" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" ht="28">
-      <c r="A125" s="103" t="s">
-        <v>523</v>
-      </c>
-      <c r="B125" s="58" t="s">
-        <v>549</v>
+        <v>788</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" ht="110" customHeight="1">
+      <c r="A125" s="102" t="s">
+        <v>517</v>
+      </c>
+      <c r="B125" s="154" t="s">
+        <v>1145</v>
       </c>
       <c r="C125" s="39" t="s">
-        <v>550</v>
+        <v>1210</v>
       </c>
       <c r="D125" s="39" t="s">
-        <v>551</v>
+        <v>1211</v>
       </c>
       <c r="E125" s="39" t="s">
-        <v>552</v>
-      </c>
-      <c r="F125" s="118" t="s">
-        <v>542</v>
+        <v>1212</v>
+      </c>
+      <c r="F125" s="117" t="s">
+        <v>1213</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="28">
-      <c r="A126" s="101" t="s">
-        <v>523</v>
-      </c>
-      <c r="B126" s="56" t="s">
-        <v>553</v>
+      <c r="A126" s="100" t="s">
+        <v>517</v>
+      </c>
+      <c r="B126" s="150" t="s">
+        <v>398</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="D126" s="10" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="E126" s="10" t="s">
         <v>474</v>
       </c>
-      <c r="F126" s="116" t="s">
+      <c r="F126" s="115" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="127" spans="1:6" ht="28">
-      <c r="A127" s="103" t="s">
-        <v>523</v>
-      </c>
-      <c r="B127" s="58" t="s">
+    <row r="127" spans="1:6" ht="165" customHeight="1">
+      <c r="A127" s="102" t="s">
+        <v>517</v>
+      </c>
+      <c r="B127" s="154" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C127" s="39" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D127" s="39" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E127" s="39" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F127" s="117" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" ht="100" customHeight="1">
+      <c r="A128" s="102" t="s">
+        <v>517</v>
+      </c>
+      <c r="B128" s="154" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C128" s="39" t="s">
+        <v>1206</v>
+      </c>
+      <c r="D128" s="39" t="s">
+        <v>1207</v>
+      </c>
+      <c r="E128" s="39" t="s">
+        <v>1208</v>
+      </c>
+      <c r="F128" s="117" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="28">
+      <c r="A129" s="102" t="s">
+        <v>517</v>
+      </c>
+      <c r="B129" s="58" t="s">
         <v>432</v>
       </c>
-      <c r="C127" s="39" t="s">
-        <v>556</v>
-      </c>
-      <c r="D127" s="39" t="s">
-        <v>557</v>
-      </c>
-      <c r="E127" s="39" t="s">
+      <c r="C129" s="39" t="s">
+        <v>546</v>
+      </c>
+      <c r="D129" s="39" t="s">
+        <v>547</v>
+      </c>
+      <c r="E129" s="39" t="s">
         <v>434</v>
       </c>
-      <c r="F127" s="118" t="s">
+      <c r="F129" s="117" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="128" spans="1:6" ht="28">
-      <c r="A128" s="103" t="s">
-        <v>523</v>
-      </c>
-      <c r="B128" s="58" t="s">
+    <row r="130" spans="1:6" ht="28">
+      <c r="A130" s="102" t="s">
+        <v>517</v>
+      </c>
+      <c r="B130" s="58" t="s">
         <v>432</v>
       </c>
-      <c r="C128" s="39" t="s">
-        <v>558</v>
-      </c>
-      <c r="D128" s="39" t="s">
-        <v>559</v>
-      </c>
-      <c r="E128" s="39" t="s">
+      <c r="C130" s="39" t="s">
+        <v>548</v>
+      </c>
+      <c r="D130" s="39" t="s">
+        <v>549</v>
+      </c>
+      <c r="E130" s="39" t="s">
         <v>434</v>
       </c>
-      <c r="F128" s="118" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" ht="238">
-      <c r="A129" s="103" t="s">
-        <v>523</v>
-      </c>
-      <c r="B129" s="155" t="s">
+      <c r="F130" s="117" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" ht="238">
+      <c r="A131" s="102" t="s">
+        <v>517</v>
+      </c>
+      <c r="B131" s="154" t="s">
         <v>432</v>
       </c>
-      <c r="C129" s="195" t="s">
-        <v>1106</v>
-      </c>
-      <c r="D129" s="39" t="s">
-        <v>806</v>
-      </c>
-      <c r="E129" s="39" t="s">
-        <v>807</v>
-      </c>
-      <c r="F129" s="118" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" ht="28">
-      <c r="A130" s="104" t="s">
-        <v>523</v>
-      </c>
-      <c r="B130" s="59" t="s">
+      <c r="C131" s="194" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D131" s="39" t="s">
+        <v>793</v>
+      </c>
+      <c r="E131" s="39" t="s">
+        <v>794</v>
+      </c>
+      <c r="F131" s="117" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="28">
+      <c r="A132" s="103" t="s">
+        <v>517</v>
+      </c>
+      <c r="B132" s="59" t="s">
         <v>432</v>
       </c>
-      <c r="C130" s="186" t="s">
-        <v>1107</v>
-      </c>
-      <c r="D130" s="47" t="s">
-        <v>739</v>
-      </c>
-      <c r="E130" s="47" t="s">
+      <c r="C132" s="185" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D132" s="47" t="s">
+        <v>726</v>
+      </c>
+      <c r="E132" s="47" t="s">
         <v>434</v>
       </c>
-      <c r="F130" s="119" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
-      <c r="A131" s="203" t="s">
-        <v>562</v>
-      </c>
-      <c r="B131" s="204"/>
-      <c r="C131" s="204"/>
-      <c r="D131" s="204"/>
-      <c r="E131" s="204"/>
-      <c r="F131" s="205"/>
-    </row>
-    <row r="132" spans="1:6" ht="28">
-      <c r="A132" s="101" t="s">
-        <v>563</v>
-      </c>
-      <c r="B132" s="56" t="s">
-        <v>564</v>
-      </c>
-      <c r="C132" s="10" t="s">
-        <v>492</v>
-      </c>
-      <c r="D132" s="10" t="s">
-        <v>565</v>
-      </c>
-      <c r="E132" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="F132" s="116" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" ht="28">
-      <c r="A133" s="100" t="s">
-        <v>563</v>
-      </c>
-      <c r="B133" s="55" t="s">
-        <v>566</v>
-      </c>
-      <c r="C133" s="50" t="s">
-        <v>567</v>
-      </c>
-      <c r="D133" s="50" t="s">
-        <v>568</v>
-      </c>
-      <c r="E133" s="50" t="s">
-        <v>500</v>
-      </c>
-      <c r="F133" s="115" t="s">
-        <v>569</v>
-      </c>
+      <c r="F132" s="118" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="A133" s="202" t="s">
+        <v>552</v>
+      </c>
+      <c r="B133" s="203"/>
+      <c r="C133" s="203"/>
+      <c r="D133" s="203"/>
+      <c r="E133" s="203"/>
+      <c r="F133" s="204"/>
     </row>
     <row r="134" spans="1:6" ht="28">
       <c r="A134" s="100" t="s">
-        <v>563</v>
-      </c>
-      <c r="B134" s="55" t="s">
-        <v>570</v>
-      </c>
-      <c r="C134" s="50" t="s">
-        <v>571</v>
-      </c>
-      <c r="D134" s="50" t="s">
-        <v>572</v>
-      </c>
-      <c r="E134" s="50" t="s">
-        <v>573</v>
+        <v>553</v>
+      </c>
+      <c r="B134" s="56" t="s">
+        <v>554</v>
+      </c>
+      <c r="C134" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="D134" s="10" t="s">
+        <v>555</v>
+      </c>
+      <c r="E134" s="10" t="s">
+        <v>441</v>
       </c>
       <c r="F134" s="115" t="s">
-        <v>355</v>
+        <v>33</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="28">
-      <c r="A135" s="100" t="s">
-        <v>563</v>
+      <c r="A135" s="99" t="s">
+        <v>553</v>
       </c>
       <c r="B135" s="55" t="s">
-        <v>574</v>
+        <v>556</v>
       </c>
       <c r="C135" s="50" t="s">
-        <v>575</v>
+        <v>557</v>
       </c>
       <c r="D135" s="50" t="s">
-        <v>576</v>
+        <v>558</v>
       </c>
       <c r="E135" s="50" t="s">
-        <v>577</v>
-      </c>
-      <c r="F135" s="115" t="s">
-        <v>578</v>
+        <v>500</v>
+      </c>
+      <c r="F135" s="114" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="28">
       <c r="A136" s="99" t="s">
+        <v>553</v>
+      </c>
+      <c r="B136" s="55" t="s">
+        <v>560</v>
+      </c>
+      <c r="C136" s="50" t="s">
+        <v>561</v>
+      </c>
+      <c r="D136" s="50" t="s">
+        <v>562</v>
+      </c>
+      <c r="E136" s="50" t="s">
         <v>563</v>
       </c>
-      <c r="B136" s="54" t="s">
+      <c r="F136" s="114" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="28">
+      <c r="A137" s="99" t="s">
+        <v>553</v>
+      </c>
+      <c r="B137" s="55" t="s">
+        <v>564</v>
+      </c>
+      <c r="C137" s="50" t="s">
+        <v>565</v>
+      </c>
+      <c r="D137" s="50" t="s">
+        <v>566</v>
+      </c>
+      <c r="E137" s="50" t="s">
+        <v>567</v>
+      </c>
+      <c r="F137" s="114" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="28">
+      <c r="A138" s="98" t="s">
+        <v>553</v>
+      </c>
+      <c r="B138" s="54" t="s">
+        <v>569</v>
+      </c>
+      <c r="C138" s="15" t="s">
+        <v>570</v>
+      </c>
+      <c r="D138" s="15" t="s">
+        <v>571</v>
+      </c>
+      <c r="E138" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="F138" s="85" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" ht="28">
+      <c r="A139" s="97" t="s">
+        <v>553</v>
+      </c>
+      <c r="B139" s="53" t="s">
+        <v>572</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>573</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="E139" s="5" t="s">
+        <v>575</v>
+      </c>
+      <c r="F139" s="113" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" ht="28">
+      <c r="A140" s="98" t="s">
+        <v>553</v>
+      </c>
+      <c r="B140" s="54" t="s">
+        <v>576</v>
+      </c>
+      <c r="C140" s="15" t="s">
+        <v>577</v>
+      </c>
+      <c r="D140" s="15" t="s">
+        <v>578</v>
+      </c>
+      <c r="E140" s="15" t="s">
         <v>579</v>
       </c>
-      <c r="C136" s="15" t="s">
+      <c r="F140" s="112" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" ht="28">
+      <c r="A141" s="97" t="s">
+        <v>553</v>
+      </c>
+      <c r="B141" s="53" t="s">
         <v>580</v>
       </c>
-      <c r="D136" s="15" t="s">
+      <c r="C141" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="E136" s="15" t="s">
-        <v>354</v>
-      </c>
-      <c r="F136" s="85" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" ht="28">
-      <c r="A137" s="98" t="s">
-        <v>563</v>
-      </c>
-      <c r="B137" s="53" t="s">
+      <c r="D141" s="5" t="s">
         <v>582</v>
       </c>
-      <c r="C137" s="5" t="s">
+      <c r="E141" s="5" t="s">
         <v>583</v>
       </c>
-      <c r="D137" s="5" t="s">
+      <c r="F141" s="113" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="29" thickBot="1">
+      <c r="A142" s="111" t="s">
+        <v>553</v>
+      </c>
+      <c r="B142" s="95" t="s">
+        <v>398</v>
+      </c>
+      <c r="C142" s="96" t="s">
         <v>584</v>
       </c>
-      <c r="E137" s="5" t="s">
+      <c r="D142" s="96" t="s">
         <v>585</v>
       </c>
-      <c r="F137" s="114" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" ht="28">
-      <c r="A138" s="99" t="s">
-        <v>563</v>
-      </c>
-      <c r="B138" s="54" t="s">
+      <c r="E142" s="96" t="s">
         <v>586</v>
       </c>
-      <c r="C138" s="15" t="s">
+      <c r="F142" s="126" t="s">
         <v>587</v>
-      </c>
-      <c r="D138" s="15" t="s">
-        <v>588</v>
-      </c>
-      <c r="E138" s="15" t="s">
-        <v>589</v>
-      </c>
-      <c r="F138" s="113" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" ht="28">
-      <c r="A139" s="98" t="s">
-        <v>563</v>
-      </c>
-      <c r="B139" s="53" t="s">
-        <v>590</v>
-      </c>
-      <c r="C139" s="5" t="s">
-        <v>591</v>
-      </c>
-      <c r="D139" s="5" t="s">
-        <v>592</v>
-      </c>
-      <c r="E139" s="5" t="s">
-        <v>593</v>
-      </c>
-      <c r="F139" s="114" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" ht="29" thickBot="1">
-      <c r="A140" s="112" t="s">
-        <v>563</v>
-      </c>
-      <c r="B140" s="96" t="s">
-        <v>398</v>
-      </c>
-      <c r="C140" s="97" t="s">
-        <v>594</v>
-      </c>
-      <c r="D140" s="97" t="s">
-        <v>595</v>
-      </c>
-      <c r="E140" s="97" t="s">
-        <v>596</v>
-      </c>
-      <c r="F140" s="127" t="s">
-        <v>597</v>
       </c>
     </row>
   </sheetData>
@@ -16288,7 +16127,7 @@
     <mergeCell ref="A72:F72"/>
     <mergeCell ref="A95:F95"/>
     <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A131:F131"/>
+    <mergeCell ref="A133:F133"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -16311,22 +16150,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75" customHeight="1">
-      <c r="A1" s="222" t="s">
-        <v>1195</v>
-      </c>
-      <c r="B1" s="222"/>
-      <c r="C1" s="222"/>
-      <c r="D1" s="222"/>
-      <c r="E1" s="222"/>
+      <c r="A1" s="221" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B1" s="221"/>
+      <c r="C1" s="221"/>
+      <c r="D1" s="221"/>
+      <c r="E1" s="221"/>
     </row>
     <row r="3" spans="1:5" ht="24" customHeight="1">
-      <c r="A3" s="223" t="s">
-        <v>933</v>
-      </c>
-      <c r="B3" s="223"/>
-      <c r="C3" s="223"/>
-      <c r="D3" s="223"/>
-      <c r="E3" s="223"/>
+      <c r="A3" s="222" t="s">
+        <v>920</v>
+      </c>
+      <c r="B3" s="222"/>
+      <c r="C3" s="222"/>
+      <c r="D3" s="222"/>
+      <c r="E3" s="222"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="12" t="s">
@@ -16350,13 +16189,13 @@
         <v>43</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>934</v>
+        <v>921</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>932</v>
+        <v>919</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>935</v>
+        <v>922</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>44</v>
@@ -16401,7 +16240,7 @@
         <v>54</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>787</v>
+        <v>774</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>55</v>
@@ -16418,13 +16257,13 @@
         <v>45</v>
       </c>
       <c r="B9" s="69" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="C9" s="67" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="E9" s="68" t="s">
         <v>162</v>
@@ -16435,13 +16274,13 @@
         <v>45</v>
       </c>
       <c r="B10" s="69" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="C10" s="67" t="s">
         <v>182</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="E10" s="68" t="s">
         <v>53</v>
@@ -16486,30 +16325,30 @@
         <v>58</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>783</v>
+        <v>770</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>780</v>
+        <v>767</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>1196</v>
+        <v>1179</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>784</v>
+        <v>771</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="42" customHeight="1">
       <c r="A14" s="20" t="s">
-        <v>785</v>
+        <v>772</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>786</v>
+        <v>773</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>782</v>
+        <v>769</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>1197</v>
+        <v>1180</v>
       </c>
       <c r="E14" s="23" t="s">
         <v>62</v>
@@ -16517,19 +16356,19 @@
     </row>
     <row r="15" spans="1:5" ht="56" customHeight="1">
       <c r="A15" s="20" t="s">
-        <v>790</v>
+        <v>777</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>791</v>
+        <v>778</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>789</v>
+        <v>776</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>792</v>
+        <v>779</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>793</v>
+        <v>780</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="70" customHeight="1">
@@ -16537,30 +16376,30 @@
         <v>80</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>869</v>
+        <v>856</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>796</v>
+        <v>783</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>1198</v>
+        <v>1181</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>797</v>
+        <v>784</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="62" customHeight="1">
       <c r="A17" s="20" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>870</v>
+        <v>857</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>845</v>
+        <v>832</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>846</v>
+        <v>833</v>
       </c>
       <c r="E17" s="23" t="s">
         <v>94</v>
@@ -16571,16 +16410,16 @@
         <v>45</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>871</v>
+        <v>858</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>847</v>
+        <v>834</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>848</v>
+        <v>835</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="62" customHeight="1">
@@ -16588,27 +16427,27 @@
         <v>45</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>872</v>
+        <v>859</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>849</v>
+        <v>836</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>850</v>
+        <v>837</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="30" customHeight="1"/>
     <row r="21" spans="1:5" ht="30" customHeight="1">
-      <c r="A21" s="219" t="s">
+      <c r="A21" s="218" t="s">
         <v>67</v>
       </c>
-      <c r="B21" s="219"/>
-      <c r="C21" s="219"/>
-      <c r="D21" s="219"/>
-      <c r="E21" s="219"/>
+      <c r="B21" s="218"/>
+      <c r="C21" s="218"/>
+      <c r="D21" s="218"/>
+      <c r="E21" s="218"/>
     </row>
     <row r="22" spans="1:5" ht="30" customHeight="1">
       <c r="A22" s="12" t="s">
@@ -16638,7 +16477,7 @@
         <v>29</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>833</v>
+        <v>820</v>
       </c>
       <c r="E23" s="18" t="s">
         <v>69</v>
@@ -16689,7 +16528,7 @@
         <v>82</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>835</v>
+        <v>822</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>83</v>
@@ -16700,13 +16539,13 @@
         <v>84</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>873</v>
+        <v>860</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>85</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>834</v>
+        <v>821</v>
       </c>
       <c r="E27" s="18" t="s">
         <v>86</v>
@@ -16717,13 +16556,13 @@
         <v>80</v>
       </c>
       <c r="B28" s="66" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="C28" s="67" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="D28" s="66" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="E28" s="68" t="s">
         <v>202</v>
@@ -16751,13 +16590,13 @@
         <v>75</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>874</v>
+        <v>861</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>840</v>
+        <v>827</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>841</v>
+        <v>828</v>
       </c>
       <c r="E30" s="18" t="s">
         <v>189</v>
@@ -16768,16 +16607,16 @@
         <v>75</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>875</v>
+        <v>862</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>842</v>
+        <v>829</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>843</v>
+        <v>830</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>844</v>
+        <v>831</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="62" customHeight="1">
@@ -16785,27 +16624,27 @@
         <v>58</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>1187</v>
+        <v>1170</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>1193</v>
+        <v>1176</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>1194</v>
+        <v>1177</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>1188</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="30" customHeight="1"/>
     <row r="34" spans="1:5" ht="30" customHeight="1">
-      <c r="A34" s="221" t="s">
+      <c r="A34" s="220" t="s">
         <v>91</v>
       </c>
-      <c r="B34" s="221"/>
-      <c r="C34" s="221"/>
-      <c r="D34" s="221"/>
-      <c r="E34" s="221"/>
+      <c r="B34" s="220"/>
+      <c r="C34" s="220"/>
+      <c r="D34" s="220"/>
+      <c r="E34" s="220"/>
     </row>
     <row r="35" spans="1:5" ht="27.75" customHeight="1">
       <c r="A35" s="12" t="s">
@@ -16965,13 +16804,13 @@
         <v>58</v>
       </c>
       <c r="B44" s="73" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
       <c r="C44" s="71" t="s">
         <v>233</v>
       </c>
       <c r="D44" s="70" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="E44" s="72" t="s">
         <v>90</v>
@@ -16996,33 +16835,33 @@
     </row>
     <row r="46" spans="1:5" ht="70">
       <c r="A46" s="20" t="s">
-        <v>802</v>
+        <v>789</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>803</v>
+        <v>790</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>804</v>
+        <v>791</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>1208</v>
+        <v>1190</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>805</v>
+        <v>792</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="112">
       <c r="A47" s="20" t="s">
-        <v>802</v>
+        <v>789</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>817</v>
+        <v>804</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>818</v>
+        <v>805</v>
       </c>
       <c r="D47" s="20" t="s">
-        <v>1209</v>
+        <v>1191</v>
       </c>
       <c r="E47" s="23" t="s">
         <v>167</v>
@@ -17033,13 +16872,13 @@
         <v>58</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>809</v>
+        <v>796</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>810</v>
+        <v>797</v>
       </c>
       <c r="D48" s="20" t="s">
-        <v>811</v>
+        <v>798</v>
       </c>
       <c r="E48" s="23" t="s">
         <v>192</v>
@@ -17050,13 +16889,13 @@
         <v>58</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>812</v>
+        <v>799</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>813</v>
+        <v>800</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>814</v>
+        <v>801</v>
       </c>
       <c r="E49" s="23" t="s">
         <v>192</v>
@@ -17067,30 +16906,30 @@
         <v>75</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>876</v>
+        <v>863</v>
       </c>
       <c r="C50" s="22" t="s">
-        <v>836</v>
+        <v>823</v>
       </c>
       <c r="D50" s="20" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
       <c r="E50" s="23" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="62" customHeight="1">
       <c r="A51" s="20" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>877</v>
+        <v>864</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>855</v>
+        <v>842</v>
       </c>
       <c r="D51" s="20" t="s">
-        <v>1199</v>
+        <v>1182</v>
       </c>
       <c r="E51" s="23" t="s">
         <v>57</v>
@@ -17101,16 +16940,16 @@
         <v>75</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>878</v>
+        <v>865</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>865</v>
+        <v>852</v>
       </c>
       <c r="D52" s="20" t="s">
-        <v>1200</v>
+        <v>1183</v>
       </c>
       <c r="E52" s="23" t="s">
-        <v>866</v>
+        <v>853</v>
       </c>
     </row>
   </sheetData>
@@ -17142,24 +16981,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18">
-      <c r="A1" s="236" t="s">
-        <v>851</v>
-      </c>
-      <c r="B1" s="237"/>
-      <c r="C1" s="237"/>
-      <c r="D1" s="237"/>
-      <c r="E1" s="237"/>
-      <c r="F1" s="238"/>
+      <c r="A1" s="235" t="s">
+        <v>838</v>
+      </c>
+      <c r="B1" s="236"/>
+      <c r="C1" s="236"/>
+      <c r="D1" s="236"/>
+      <c r="E1" s="236"/>
+      <c r="F1" s="237"/>
     </row>
     <row r="2" spans="1:6" ht="41" customHeight="1">
-      <c r="A2" s="239" t="s">
-        <v>852</v>
-      </c>
-      <c r="B2" s="240"/>
-      <c r="C2" s="240"/>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="241"/>
+      <c r="A2" s="238" t="s">
+        <v>839</v>
+      </c>
+      <c r="B2" s="239"/>
+      <c r="C2" s="239"/>
+      <c r="D2" s="239"/>
+      <c r="E2" s="239"/>
+      <c r="F2" s="240"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="77" t="s">
@@ -17182,14 +17021,14 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="233" t="s">
-        <v>936</v>
-      </c>
-      <c r="B4" s="234"/>
-      <c r="C4" s="234"/>
-      <c r="D4" s="234"/>
-      <c r="E4" s="234"/>
-      <c r="F4" s="235"/>
+      <c r="A4" s="232" t="s">
+        <v>923</v>
+      </c>
+      <c r="B4" s="233"/>
+      <c r="C4" s="233"/>
+      <c r="D4" s="233"/>
+      <c r="E4" s="233"/>
+      <c r="F4" s="234"/>
     </row>
     <row r="5" spans="1:6" ht="28">
       <c r="A5" s="78" t="s">
@@ -17199,16 +17038,16 @@
         <v>134</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>937</v>
+        <v>924</v>
       </c>
       <c r="D5" s="27" t="s">
         <v>135</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>938</v>
+        <v>925</v>
       </c>
       <c r="F5" s="84" t="s">
-        <v>939</v>
+        <v>926</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="28">
@@ -17219,16 +17058,16 @@
         <v>137</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>940</v>
+        <v>927</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>941</v>
+        <v>928</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>942</v>
+        <v>929</v>
       </c>
       <c r="F6" s="85" t="s">
-        <v>900</v>
+        <v>887</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28">
@@ -17239,67 +17078,67 @@
         <v>139</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>943</v>
+        <v>930</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>53</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>944</v>
+        <v>931</v>
       </c>
       <c r="F7" s="86" t="s">
-        <v>945</v>
+        <v>932</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="28">
       <c r="A8" s="81" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="B8" s="75">
         <v>4.5</v>
       </c>
       <c r="C8" s="76" t="s">
-        <v>946</v>
+        <v>933</v>
       </c>
       <c r="D8" s="75" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="E8" s="76" t="s">
-        <v>947</v>
+        <v>934</v>
       </c>
       <c r="F8" s="87" t="s">
-        <v>948</v>
+        <v>935</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="28">
       <c r="A9" s="82" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="B9" s="68">
         <v>4.5</v>
       </c>
       <c r="C9" s="66" t="s">
-        <v>949</v>
+        <v>936</v>
       </c>
       <c r="D9" s="68" t="s">
         <v>481</v>
       </c>
       <c r="E9" s="66" t="s">
-        <v>950</v>
+        <v>937</v>
       </c>
       <c r="F9" s="88" t="s">
-        <v>951</v>
+        <v>938</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="233" t="s">
+      <c r="A10" s="232" t="s">
         <v>141</v>
       </c>
-      <c r="B10" s="234"/>
-      <c r="C10" s="234"/>
-      <c r="D10" s="234"/>
-      <c r="E10" s="234"/>
-      <c r="F10" s="235"/>
+      <c r="B10" s="233"/>
+      <c r="C10" s="233"/>
+      <c r="D10" s="233"/>
+      <c r="E10" s="233"/>
+      <c r="F10" s="234"/>
     </row>
     <row r="11" spans="1:6" ht="56">
       <c r="A11" s="78" t="s">
@@ -17315,7 +17154,7 @@
         <v>49</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>1201</v>
+        <v>1184</v>
       </c>
       <c r="F11" s="84" t="s">
         <v>143</v>
@@ -17363,59 +17202,59 @@
     </row>
     <row r="14" spans="1:6" ht="28">
       <c r="A14" s="81" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="B14" s="75">
         <v>4.8</v>
       </c>
       <c r="C14" s="76" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="D14" s="75" t="s">
         <v>57</v>
       </c>
       <c r="E14" s="76" t="s">
-        <v>612</v>
+        <v>602</v>
       </c>
       <c r="F14" s="87" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28">
       <c r="A15" s="82" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="B15" s="68">
         <v>4.5999999999999996</v>
       </c>
       <c r="C15" s="66" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
       <c r="D15" s="68" t="s">
         <v>98</v>
       </c>
       <c r="E15" s="66" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="F15" s="88" t="s">
-        <v>644</v>
+        <v>634</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="42">
       <c r="A16" s="82" t="s">
-        <v>684</v>
-      </c>
-      <c r="B16" s="165" t="s">
-        <v>773</v>
+        <v>674</v>
+      </c>
+      <c r="B16" s="164" t="s">
+        <v>760</v>
       </c>
       <c r="C16" s="66" t="s">
-        <v>774</v>
+        <v>761</v>
       </c>
       <c r="D16" s="68" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="E16" s="66" t="s">
-        <v>775</v>
+        <v>762</v>
       </c>
       <c r="F16" s="88" t="s">
         <v>391</v>
@@ -17423,73 +17262,73 @@
     </row>
     <row r="17" spans="1:6" ht="42">
       <c r="A17" s="82" t="s">
-        <v>687</v>
-      </c>
-      <c r="B17" s="165" t="s">
-        <v>776</v>
+        <v>677</v>
+      </c>
+      <c r="B17" s="164" t="s">
+        <v>763</v>
       </c>
       <c r="C17" s="66" t="s">
-        <v>777</v>
+        <v>764</v>
       </c>
       <c r="D17" s="68" t="s">
-        <v>762</v>
+        <v>749</v>
       </c>
       <c r="E17" s="66" t="s">
-        <v>778</v>
+        <v>765</v>
       </c>
       <c r="F17" s="88" t="s">
-        <v>644</v>
+        <v>634</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="56">
-      <c r="A18" s="166" t="s">
-        <v>755</v>
-      </c>
-      <c r="B18" s="167" t="s">
+      <c r="A18" s="165" t="s">
+        <v>742</v>
+      </c>
+      <c r="B18" s="166" t="s">
         <v>216</v>
       </c>
-      <c r="C18" s="168" t="s">
-        <v>879</v>
-      </c>
-      <c r="D18" s="169" t="s">
-        <v>839</v>
-      </c>
-      <c r="E18" s="168" t="s">
-        <v>859</v>
-      </c>
-      <c r="F18" s="170" t="s">
+      <c r="C18" s="167" t="s">
+        <v>866</v>
+      </c>
+      <c r="D18" s="168" t="s">
+        <v>826</v>
+      </c>
+      <c r="E18" s="167" t="s">
+        <v>846</v>
+      </c>
+      <c r="F18" s="169" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="70">
+      <c r="A19" s="165" t="s">
+        <v>746</v>
+      </c>
+      <c r="B19" s="166" t="s">
+        <v>216</v>
+      </c>
+      <c r="C19" s="167" t="s">
+        <v>867</v>
+      </c>
+      <c r="D19" s="168" t="s">
+        <v>826</v>
+      </c>
+      <c r="E19" s="167" t="s">
         <v>847</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="70">
-      <c r="A19" s="166" t="s">
-        <v>759</v>
-      </c>
-      <c r="B19" s="167" t="s">
-        <v>216</v>
-      </c>
-      <c r="C19" s="168" t="s">
-        <v>880</v>
-      </c>
-      <c r="D19" s="169" t="s">
-        <v>839</v>
-      </c>
-      <c r="E19" s="168" t="s">
-        <v>860</v>
-      </c>
-      <c r="F19" s="170" t="s">
-        <v>849</v>
+      <c r="F19" s="169" t="s">
+        <v>836</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="233" t="s">
+      <c r="A20" s="232" t="s">
         <v>152</v>
       </c>
-      <c r="B20" s="234"/>
-      <c r="C20" s="234"/>
-      <c r="D20" s="234"/>
-      <c r="E20" s="234"/>
-      <c r="F20" s="235"/>
+      <c r="B20" s="233"/>
+      <c r="C20" s="233"/>
+      <c r="D20" s="233"/>
+      <c r="E20" s="233"/>
+      <c r="F20" s="234"/>
     </row>
     <row r="21" spans="1:6" ht="28">
       <c r="A21" s="78" t="s">
@@ -17499,7 +17338,7 @@
         <v>154</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>853</v>
+        <v>840</v>
       </c>
       <c r="D21" s="27" t="s">
         <v>57</v>
@@ -17559,13 +17398,13 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C24" s="76" t="s">
-        <v>662</v>
+        <v>652</v>
       </c>
       <c r="D24" s="75" t="s">
         <v>218</v>
       </c>
       <c r="E24" s="76" t="s">
-        <v>663</v>
+        <v>653</v>
       </c>
       <c r="F24" s="87" t="s">
         <v>255</v>
@@ -17573,33 +17412,33 @@
     </row>
     <row r="25" spans="1:6" ht="28">
       <c r="A25" s="82" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="B25" s="68">
         <v>4.3</v>
       </c>
       <c r="C25" s="66" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="D25" s="68" t="s">
         <v>218</v>
       </c>
       <c r="E25" s="66" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="F25" s="88" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="233" t="s">
+      <c r="A26" s="232" t="s">
         <v>165</v>
       </c>
-      <c r="B26" s="234"/>
-      <c r="C26" s="234"/>
-      <c r="D26" s="234"/>
-      <c r="E26" s="234"/>
-      <c r="F26" s="235"/>
+      <c r="B26" s="233"/>
+      <c r="C26" s="233"/>
+      <c r="D26" s="233"/>
+      <c r="E26" s="233"/>
+      <c r="F26" s="234"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="78" t="s">
@@ -17629,13 +17468,13 @@
         <v>137</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>881</v>
+        <v>868</v>
       </c>
       <c r="D28" s="18" t="s">
         <v>170</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>821</v>
+        <v>808</v>
       </c>
       <c r="F28" s="85" t="s">
         <v>171</v>
@@ -17663,53 +17502,53 @@
     </row>
     <row r="30" spans="1:6" ht="42">
       <c r="A30" s="81" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="B30" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C30" s="76" t="s">
-        <v>882</v>
+        <v>869</v>
       </c>
       <c r="D30" s="75" t="s">
         <v>140</v>
       </c>
       <c r="E30" s="76" t="s">
-        <v>822</v>
+        <v>809</v>
       </c>
       <c r="F30" s="87" t="s">
-        <v>617</v>
+        <v>607</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="28">
       <c r="A31" s="82" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="B31" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C31" s="66" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="D31" s="68" t="s">
         <v>192</v>
       </c>
       <c r="E31" s="66" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
       <c r="F31" s="88" t="s">
-        <v>647</v>
+        <v>637</v>
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="233" t="s">
+      <c r="A32" s="232" t="s">
         <v>176</v>
       </c>
-      <c r="B32" s="234"/>
-      <c r="C32" s="234"/>
-      <c r="D32" s="234"/>
-      <c r="E32" s="234"/>
-      <c r="F32" s="235"/>
+      <c r="B32" s="233"/>
+      <c r="C32" s="233"/>
+      <c r="D32" s="233"/>
+      <c r="E32" s="233"/>
+      <c r="F32" s="234"/>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="78" t="s">
@@ -17759,33 +17598,33 @@
         <v>4.3</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="F35" s="86" t="s">
-        <v>650</v>
+        <v>640</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="42">
       <c r="A36" s="81" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="B36" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C36" s="76" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="D36" s="75" t="s">
         <v>145</v>
       </c>
       <c r="E36" s="76" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="F36" s="87" t="s">
         <v>182</v>
@@ -17793,33 +17632,33 @@
     </row>
     <row r="37" spans="1:6" ht="28">
       <c r="A37" s="82" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="B37" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C37" s="66" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="D37" s="68" t="s">
         <v>53</v>
       </c>
       <c r="E37" s="66" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
       <c r="F37" s="88" t="s">
-        <v>650</v>
+        <v>640</v>
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="230" t="s">
+      <c r="A38" s="229" t="s">
         <v>184</v>
       </c>
-      <c r="B38" s="231"/>
-      <c r="C38" s="231"/>
-      <c r="D38" s="231"/>
-      <c r="E38" s="231"/>
-      <c r="F38" s="232"/>
+      <c r="B38" s="230"/>
+      <c r="C38" s="230"/>
+      <c r="D38" s="230"/>
+      <c r="E38" s="230"/>
+      <c r="F38" s="231"/>
     </row>
     <row r="39" spans="1:6" ht="28">
       <c r="A39" s="78" t="s">
@@ -17829,16 +17668,16 @@
         <v>4.5</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>672</v>
+        <v>662</v>
       </c>
       <c r="D39" s="27" t="s">
         <v>192</v>
       </c>
       <c r="E39" s="28" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="F39" s="84" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="42">
@@ -17849,13 +17688,13 @@
         <v>139</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>883</v>
+        <v>870</v>
       </c>
       <c r="D40" s="18" t="s">
         <v>162</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>828</v>
+        <v>815</v>
       </c>
       <c r="F40" s="85" t="s">
         <v>186</v>
@@ -17883,19 +17722,19 @@
     </row>
     <row r="42" spans="1:6" ht="28">
       <c r="A42" s="81" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="B42" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C42" s="76" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="D42" s="75" t="s">
         <v>189</v>
       </c>
       <c r="E42" s="76" t="s">
-        <v>621</v>
+        <v>611</v>
       </c>
       <c r="F42" s="87" t="s">
         <v>82</v>
@@ -17903,33 +17742,33 @@
     </row>
     <row r="43" spans="1:6" ht="28">
       <c r="A43" s="82" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="B43" s="68">
         <v>4.3</v>
       </c>
       <c r="C43" s="66" t="s">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="D43" s="68" t="s">
         <v>195</v>
       </c>
       <c r="E43" s="66" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
       <c r="F43" s="88" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="230" t="s">
+      <c r="A44" s="229" t="s">
         <v>191</v>
       </c>
-      <c r="B44" s="231"/>
-      <c r="C44" s="231"/>
-      <c r="D44" s="231"/>
-      <c r="E44" s="231"/>
-      <c r="F44" s="232"/>
+      <c r="B44" s="230"/>
+      <c r="C44" s="230"/>
+      <c r="D44" s="230"/>
+      <c r="E44" s="230"/>
+      <c r="F44" s="231"/>
     </row>
     <row r="45" spans="1:6" ht="84">
       <c r="A45" s="78" t="s">
@@ -17939,13 +17778,13 @@
         <v>137</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>819</v>
+        <v>806</v>
       </c>
       <c r="D45" s="27" t="s">
         <v>192</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>820</v>
+        <v>807</v>
       </c>
       <c r="F45" s="84" t="s">
         <v>193</v>
@@ -17979,13 +17818,13 @@
         <v>134</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>884</v>
+        <v>871</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>198</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>823</v>
+        <v>810</v>
       </c>
       <c r="F47" s="86" t="s">
         <v>29</v>
@@ -17993,19 +17832,19 @@
     </row>
     <row r="48" spans="1:6" ht="42">
       <c r="A48" s="81" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="B48" s="75">
         <v>4.5</v>
       </c>
       <c r="C48" s="76" t="s">
-        <v>885</v>
+        <v>872</v>
       </c>
       <c r="D48" s="75" t="s">
         <v>79</v>
       </c>
       <c r="E48" s="76" t="s">
-        <v>829</v>
+        <v>816</v>
       </c>
       <c r="F48" s="87" t="s">
         <v>197</v>
@@ -18013,53 +17852,53 @@
     </row>
     <row r="49" spans="1:6" ht="28">
       <c r="A49" s="82" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="B49" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C49" s="66" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
       <c r="D49" s="68" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="E49" s="66" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="F49" s="88" t="s">
-        <v>625</v>
+        <v>615</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="84">
-      <c r="A50" s="166" t="s">
-        <v>684</v>
-      </c>
-      <c r="B50" s="169" t="s">
+      <c r="A50" s="165" t="s">
+        <v>674</v>
+      </c>
+      <c r="B50" s="168" t="s">
         <v>216</v>
       </c>
-      <c r="C50" s="168" t="s">
-        <v>886</v>
-      </c>
-      <c r="D50" s="169" t="s">
-        <v>844</v>
-      </c>
-      <c r="E50" s="168" t="s">
-        <v>861</v>
-      </c>
-      <c r="F50" s="170" t="s">
-        <v>842</v>
+      <c r="C50" s="167" t="s">
+        <v>873</v>
+      </c>
+      <c r="D50" s="168" t="s">
+        <v>831</v>
+      </c>
+      <c r="E50" s="167" t="s">
+        <v>848</v>
+      </c>
+      <c r="F50" s="169" t="s">
+        <v>829</v>
       </c>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="230" t="s">
+      <c r="A51" s="229" t="s">
         <v>199</v>
       </c>
-      <c r="B51" s="231"/>
-      <c r="C51" s="231"/>
-      <c r="D51" s="231"/>
-      <c r="E51" s="231"/>
-      <c r="F51" s="232"/>
+      <c r="B51" s="230"/>
+      <c r="C51" s="230"/>
+      <c r="D51" s="230"/>
+      <c r="E51" s="230"/>
+      <c r="F51" s="231"/>
     </row>
     <row r="52" spans="1:6" ht="56">
       <c r="A52" s="78" t="s">
@@ -18069,13 +17908,13 @@
         <v>187</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>887</v>
+        <v>874</v>
       </c>
       <c r="D52" s="27" t="s">
         <v>140</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>825</v>
+        <v>812</v>
       </c>
       <c r="F52" s="84" t="s">
         <v>200</v>
@@ -18109,87 +17948,87 @@
         <v>4.5</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>666</v>
+        <v>656</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>192</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="F54" s="86" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="28">
       <c r="A55" s="81" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="B55" s="75">
         <v>4.7</v>
       </c>
       <c r="C55" s="76" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="D55" s="75" t="s">
         <v>57</v>
       </c>
       <c r="E55" s="76" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="F55" s="87" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="28">
       <c r="A56" s="81" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="B56" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C56" s="76" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="D56" s="75" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="E56" s="76" t="s">
-        <v>631</v>
+        <v>621</v>
       </c>
       <c r="F56" s="87" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="84">
-      <c r="A57" s="171" t="s">
-        <v>684</v>
-      </c>
-      <c r="B57" s="172" t="s">
+      <c r="A57" s="170" t="s">
+        <v>674</v>
+      </c>
+      <c r="B57" s="171" t="s">
         <v>216</v>
       </c>
-      <c r="C57" s="173" t="s">
-        <v>888</v>
-      </c>
-      <c r="D57" s="172" t="s">
+      <c r="C57" s="172" t="s">
+        <v>875</v>
+      </c>
+      <c r="D57" s="171" t="s">
         <v>189</v>
       </c>
-      <c r="E57" s="173" t="s">
-        <v>862</v>
-      </c>
-      <c r="F57" s="174" t="s">
-        <v>840</v>
+      <c r="E57" s="172" t="s">
+        <v>849</v>
+      </c>
+      <c r="F57" s="173" t="s">
+        <v>827</v>
       </c>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="230" t="s">
+      <c r="A58" s="229" t="s">
         <v>205</v>
       </c>
-      <c r="B58" s="231"/>
-      <c r="C58" s="231"/>
-      <c r="D58" s="231"/>
-      <c r="E58" s="231"/>
-      <c r="F58" s="232"/>
+      <c r="B58" s="230"/>
+      <c r="C58" s="230"/>
+      <c r="D58" s="230"/>
+      <c r="E58" s="230"/>
+      <c r="F58" s="231"/>
     </row>
     <row r="59" spans="1:6" ht="28">
       <c r="A59" s="78" t="s">
@@ -18219,13 +18058,13 @@
         <v>134</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>889</v>
+        <v>876</v>
       </c>
       <c r="D60" s="18" t="s">
         <v>198</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>824</v>
+        <v>811</v>
       </c>
       <c r="F60" s="85" t="s">
         <v>29</v>
@@ -18239,13 +18078,13 @@
         <v>139</v>
       </c>
       <c r="C61" s="29" t="s">
-        <v>890</v>
+        <v>877</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>140</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>826</v>
+        <v>813</v>
       </c>
       <c r="F61" s="86" t="s">
         <v>209</v>
@@ -18253,53 +18092,53 @@
     </row>
     <row r="62" spans="1:6" ht="28">
       <c r="A62" s="81" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="B62" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C62" s="74" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="D62" s="75" t="s">
         <v>192</v>
       </c>
       <c r="E62" s="76" t="s">
-        <v>654</v>
+        <v>644</v>
       </c>
       <c r="F62" s="87" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="28">
       <c r="A63" s="82" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="B63" s="68">
         <v>4.5999999999999996</v>
       </c>
       <c r="C63" s="69" t="s">
-        <v>633</v>
+        <v>623</v>
       </c>
       <c r="D63" s="68" t="s">
         <v>44</v>
       </c>
       <c r="E63" s="66" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
       <c r="F63" s="88" t="s">
-        <v>635</v>
+        <v>625</v>
       </c>
     </row>
     <row r="64" spans="1:6">
-      <c r="A64" s="230" t="s">
+      <c r="A64" s="229" t="s">
         <v>210</v>
       </c>
-      <c r="B64" s="231"/>
-      <c r="C64" s="231"/>
-      <c r="D64" s="231"/>
-      <c r="E64" s="231"/>
-      <c r="F64" s="232"/>
+      <c r="B64" s="230"/>
+      <c r="C64" s="230"/>
+      <c r="D64" s="230"/>
+      <c r="E64" s="230"/>
+      <c r="F64" s="231"/>
     </row>
     <row r="65" spans="1:6" ht="28">
       <c r="A65" s="78" t="s">
@@ -18329,13 +18168,13 @@
         <v>137</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>891</v>
+        <v>878</v>
       </c>
       <c r="D66" s="18" t="s">
         <v>86</v>
       </c>
       <c r="E66" s="25" t="s">
-        <v>827</v>
+        <v>814</v>
       </c>
       <c r="F66" s="85" t="s">
         <v>85</v>
@@ -18362,14 +18201,14 @@
       </c>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="224" t="s">
+      <c r="A68" s="223" t="s">
         <v>221</v>
       </c>
-      <c r="B68" s="225"/>
-      <c r="C68" s="225"/>
-      <c r="D68" s="225"/>
-      <c r="E68" s="225"/>
-      <c r="F68" s="226"/>
+      <c r="B68" s="224"/>
+      <c r="C68" s="224"/>
+      <c r="D68" s="224"/>
+      <c r="E68" s="224"/>
+      <c r="F68" s="225"/>
     </row>
     <row r="69" spans="1:6" ht="70">
       <c r="A69" s="78" t="s">
@@ -18385,7 +18224,7 @@
         <v>102</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>1202</v>
+        <v>1185</v>
       </c>
       <c r="F69" s="84" t="s">
         <v>100</v>
@@ -18399,13 +18238,13 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="D70" s="18" t="s">
         <v>195</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="F70" s="85" t="s">
         <v>239</v>
@@ -18433,19 +18272,19 @@
     </row>
     <row r="72" spans="1:6" ht="28">
       <c r="A72" s="81" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="B72" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C72" s="76" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="D72" s="75" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="E72" s="76" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="F72" s="87" t="s">
         <v>239</v>
@@ -18453,39 +18292,39 @@
     </row>
     <row r="73" spans="1:6" ht="70">
       <c r="A73" s="82" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="B73" s="68">
         <v>4.3</v>
       </c>
       <c r="C73" s="66" t="s">
-        <v>892</v>
+        <v>879</v>
       </c>
       <c r="D73" s="68" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
       <c r="E73" s="66" t="s">
-        <v>830</v>
+        <v>817</v>
       </c>
       <c r="F73" s="88" t="s">
-        <v>831</v>
+        <v>818</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="28">
       <c r="A74" s="81" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="B74" s="75">
         <v>4.4000000000000004</v>
       </c>
       <c r="C74" s="76" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="D74" s="75" t="s">
         <v>110</v>
       </c>
       <c r="E74" s="76" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="F74" s="87" t="s">
         <v>108</v>
@@ -18493,39 +18332,39 @@
     </row>
     <row r="75" spans="1:6" ht="28">
       <c r="A75" s="82" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="B75" s="68">
         <v>4.5</v>
       </c>
       <c r="C75" s="66" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="D75" s="68" t="s">
         <v>86</v>
       </c>
       <c r="E75" s="66" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="F75" s="88" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="42">
       <c r="A76" s="82" t="s">
+        <v>742</v>
+      </c>
+      <c r="B76" s="164" t="s">
+        <v>752</v>
+      </c>
+      <c r="C76" s="66" t="s">
+        <v>753</v>
+      </c>
+      <c r="D76" s="68" t="s">
+        <v>754</v>
+      </c>
+      <c r="E76" s="66" t="s">
         <v>755</v>
-      </c>
-      <c r="B76" s="165" t="s">
-        <v>765</v>
-      </c>
-      <c r="C76" s="66" t="s">
-        <v>766</v>
-      </c>
-      <c r="D76" s="68" t="s">
-        <v>767</v>
-      </c>
-      <c r="E76" s="66" t="s">
-        <v>768</v>
       </c>
       <c r="F76" s="88" t="s">
         <v>245</v>
@@ -18533,33 +18372,33 @@
     </row>
     <row r="77" spans="1:6" ht="42">
       <c r="A77" s="82" t="s">
+        <v>746</v>
+      </c>
+      <c r="B77" s="164" t="s">
+        <v>756</v>
+      </c>
+      <c r="C77" s="66" t="s">
+        <v>757</v>
+      </c>
+      <c r="D77" s="68" t="s">
+        <v>749</v>
+      </c>
+      <c r="E77" s="66" t="s">
+        <v>758</v>
+      </c>
+      <c r="F77" s="88" t="s">
         <v>759</v>
       </c>
-      <c r="B77" s="165" t="s">
-        <v>769</v>
-      </c>
-      <c r="C77" s="66" t="s">
-        <v>770</v>
-      </c>
-      <c r="D77" s="68" t="s">
-        <v>762</v>
-      </c>
-      <c r="E77" s="66" t="s">
-        <v>771</v>
-      </c>
-      <c r="F77" s="88" t="s">
-        <v>772</v>
-      </c>
     </row>
     <row r="78" spans="1:6">
-      <c r="A78" s="224" t="s">
+      <c r="A78" s="223" t="s">
         <v>227</v>
       </c>
-      <c r="B78" s="225"/>
-      <c r="C78" s="225"/>
-      <c r="D78" s="225"/>
-      <c r="E78" s="225"/>
-      <c r="F78" s="226"/>
+      <c r="B78" s="224"/>
+      <c r="C78" s="224"/>
+      <c r="D78" s="224"/>
+      <c r="E78" s="224"/>
+      <c r="F78" s="225"/>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="78" t="s">
@@ -18602,40 +18441,40 @@
       </c>
     </row>
     <row r="81" spans="1:6">
-      <c r="A81" s="175" t="s">
+      <c r="A81" s="174" t="s">
         <v>138</v>
       </c>
-      <c r="B81" s="176" t="s">
+      <c r="B81" s="175" t="s">
         <v>134</v>
       </c>
-      <c r="C81" s="177" t="s">
+      <c r="C81" s="176" t="s">
         <v>92</v>
       </c>
-      <c r="D81" s="176" t="s">
+      <c r="D81" s="175" t="s">
         <v>94</v>
       </c>
-      <c r="E81" s="177" t="s">
+      <c r="E81" s="176" t="s">
         <v>234</v>
       </c>
-      <c r="F81" s="178" t="s">
+      <c r="F81" s="177" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="28">
       <c r="A82" s="81" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="B82" s="75">
         <v>4.3</v>
       </c>
       <c r="C82" s="76" t="s">
-        <v>669</v>
+        <v>659</v>
       </c>
       <c r="D82" s="75" t="s">
         <v>192</v>
       </c>
       <c r="E82" s="76" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="F82" s="87" t="s">
         <v>233</v>
@@ -18643,73 +18482,73 @@
     </row>
     <row r="83" spans="1:6" ht="28">
       <c r="A83" s="82" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="B83" s="68">
         <v>4</v>
       </c>
       <c r="C83" s="66" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="D83" s="68" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="E83" s="66" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="F83" s="88" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="70">
-      <c r="A84" s="161" t="s">
-        <v>684</v>
-      </c>
-      <c r="B84" s="162">
+      <c r="A84" s="160" t="s">
+        <v>674</v>
+      </c>
+      <c r="B84" s="161">
         <v>4.5999999999999996</v>
       </c>
-      <c r="C84" s="163" t="s">
-        <v>856</v>
-      </c>
-      <c r="D84" s="162" t="s">
+      <c r="C84" s="162" t="s">
+        <v>843</v>
+      </c>
+      <c r="D84" s="161" t="s">
         <v>167</v>
       </c>
-      <c r="E84" s="163" t="s">
-        <v>857</v>
-      </c>
-      <c r="F84" s="164" t="s">
-        <v>858</v>
+      <c r="E84" s="162" t="s">
+        <v>844</v>
+      </c>
+      <c r="F84" s="163" t="s">
+        <v>845</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="140">
-      <c r="A85" s="179" t="s">
+      <c r="A85" s="178" t="s">
         <v>153</v>
       </c>
-      <c r="B85" s="180">
+      <c r="B85" s="179">
         <v>4.8</v>
       </c>
-      <c r="C85" s="181" t="s">
-        <v>893</v>
-      </c>
-      <c r="D85" s="180" t="s">
+      <c r="C85" s="180" t="s">
+        <v>880</v>
+      </c>
+      <c r="D85" s="179" t="s">
         <v>57</v>
       </c>
-      <c r="E85" s="181" t="s">
-        <v>1203</v>
-      </c>
-      <c r="F85" s="182" t="s">
-        <v>854</v>
+      <c r="E85" s="180" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F85" s="181" t="s">
+        <v>841</v>
       </c>
     </row>
     <row r="86" spans="1:6">
-      <c r="A86" s="224" t="s">
+      <c r="A86" s="223" t="s">
         <v>235</v>
       </c>
-      <c r="B86" s="225"/>
-      <c r="C86" s="225"/>
-      <c r="D86" s="225"/>
-      <c r="E86" s="225"/>
-      <c r="F86" s="226"/>
+      <c r="B86" s="224"/>
+      <c r="C86" s="224"/>
+      <c r="D86" s="224"/>
+      <c r="E86" s="224"/>
+      <c r="F86" s="225"/>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="78" t="s">
@@ -18739,13 +18578,13 @@
         <v>4.2</v>
       </c>
       <c r="C88" s="16" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="D88" s="18" t="s">
         <v>106</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>659</v>
+        <v>649</v>
       </c>
       <c r="F88" s="85" t="s">
         <v>239</v>
@@ -18759,13 +18598,13 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>192</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="F89" s="86" t="s">
         <v>239</v>
@@ -18773,19 +18612,19 @@
     </row>
     <row r="90" spans="1:6" ht="28">
       <c r="A90" s="81" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="B90" s="75">
         <v>4.3</v>
       </c>
       <c r="C90" s="76" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="D90" s="75" t="s">
         <v>106</v>
       </c>
       <c r="E90" s="76" t="s">
-        <v>657</v>
+        <v>647</v>
       </c>
       <c r="F90" s="87" t="s">
         <v>239</v>
@@ -18793,19 +18632,19 @@
     </row>
     <row r="91" spans="1:6" ht="28">
       <c r="A91" s="82" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="B91" s="68">
         <v>4.4000000000000004</v>
       </c>
       <c r="C91" s="66" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="D91" s="68" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="E91" s="66" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="F91" s="88" t="s">
         <v>245</v>
@@ -18813,59 +18652,59 @@
     </row>
     <row r="92" spans="1:6" ht="28">
       <c r="A92" s="81" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="B92" s="75">
         <v>4.5999999999999996</v>
       </c>
       <c r="C92" s="76" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
       <c r="D92" s="75" t="s">
         <v>115</v>
       </c>
       <c r="E92" s="76" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="F92" s="87" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="28">
-      <c r="A93" s="166" t="s">
-        <v>687</v>
-      </c>
-      <c r="B93" s="169" t="s">
+      <c r="A93" s="165" t="s">
+        <v>677</v>
+      </c>
+      <c r="B93" s="168" t="s">
         <v>216</v>
       </c>
-      <c r="C93" s="168" t="s">
-        <v>693</v>
-      </c>
-      <c r="D93" s="169" t="s">
+      <c r="C93" s="167" t="s">
+        <v>683</v>
+      </c>
+      <c r="D93" s="168" t="s">
         <v>246</v>
       </c>
-      <c r="E93" s="168" t="s">
-        <v>694</v>
-      </c>
-      <c r="F93" s="170" t="s">
+      <c r="E93" s="167" t="s">
+        <v>684</v>
+      </c>
+      <c r="F93" s="169" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="42">
       <c r="A94" s="82" t="s">
-        <v>755</v>
-      </c>
-      <c r="B94" s="165" t="s">
-        <v>756</v>
+        <v>742</v>
+      </c>
+      <c r="B94" s="164" t="s">
+        <v>743</v>
       </c>
       <c r="C94" s="66" t="s">
-        <v>757</v>
+        <v>744</v>
       </c>
       <c r="D94" s="68" t="s">
         <v>167</v>
       </c>
       <c r="E94" s="66" t="s">
-        <v>758</v>
+        <v>745</v>
       </c>
       <c r="F94" s="88" t="s">
         <v>226</v>
@@ -18873,69 +18712,69 @@
     </row>
     <row r="95" spans="1:6" ht="42">
       <c r="A95" s="82" t="s">
-        <v>759</v>
-      </c>
-      <c r="B95" s="165" t="s">
-        <v>760</v>
+        <v>746</v>
+      </c>
+      <c r="B95" s="164" t="s">
+        <v>747</v>
       </c>
       <c r="C95" s="66" t="s">
-        <v>761</v>
+        <v>748</v>
       </c>
       <c r="D95" s="68" t="s">
-        <v>762</v>
+        <v>749</v>
       </c>
       <c r="E95" s="66" t="s">
-        <v>763</v>
+        <v>750</v>
       </c>
       <c r="F95" s="88" t="s">
-        <v>764</v>
+        <v>751</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="70">
       <c r="A96" s="82" t="s">
-        <v>867</v>
-      </c>
-      <c r="B96" s="184">
+        <v>854</v>
+      </c>
+      <c r="B96" s="183">
         <v>4.5</v>
       </c>
       <c r="C96" s="66" t="s">
-        <v>894</v>
+        <v>881</v>
       </c>
       <c r="D96" s="68" t="s">
         <v>145</v>
       </c>
       <c r="E96" s="66" t="s">
-        <v>868</v>
+        <v>855</v>
       </c>
       <c r="F96" s="88" t="s">
-        <v>865</v>
+        <v>852</v>
       </c>
     </row>
     <row r="97" spans="1:6">
-      <c r="A97" s="224" t="s">
+      <c r="A97" s="223" t="s">
         <v>241</v>
       </c>
-      <c r="B97" s="225"/>
-      <c r="C97" s="225"/>
-      <c r="D97" s="225"/>
-      <c r="E97" s="225"/>
-      <c r="F97" s="226"/>
+      <c r="B97" s="224"/>
+      <c r="C97" s="224"/>
+      <c r="D97" s="224"/>
+      <c r="E97" s="224"/>
+      <c r="F97" s="225"/>
     </row>
     <row r="98" spans="1:6" ht="84">
       <c r="A98" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="B98" s="183">
+      <c r="B98" s="182">
         <v>5</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>863</v>
+        <v>850</v>
       </c>
       <c r="D98" s="27" t="s">
         <v>57</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>864</v>
+        <v>851</v>
       </c>
       <c r="F98" s="84" t="s">
         <v>242</v>
@@ -18969,47 +18808,47 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="C100" s="76" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="D100" s="75" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="E100" s="76" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="F100" s="87" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="28">
       <c r="A101" s="82" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="B101" s="68">
         <v>4.5</v>
       </c>
       <c r="C101" s="66" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="D101" s="68" t="s">
         <v>106</v>
       </c>
       <c r="E101" s="66" t="s">
-        <v>641</v>
+        <v>631</v>
       </c>
       <c r="F101" s="88" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="68" customHeight="1" thickBot="1">
-      <c r="A102" s="227" t="s">
-        <v>895</v>
-      </c>
-      <c r="B102" s="228"/>
-      <c r="C102" s="228"/>
-      <c r="D102" s="228"/>
-      <c r="E102" s="228"/>
-      <c r="F102" s="229"/>
+      <c r="A102" s="226" t="s">
+        <v>882</v>
+      </c>
+      <c r="B102" s="227"/>
+      <c r="C102" s="227"/>
+      <c r="D102" s="227"/>
+      <c r="E102" s="227"/>
+      <c r="F102" s="228"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -19051,29 +18890,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1">
-      <c r="A1" s="206" t="s">
+      <c r="A1" s="205" t="s">
         <v>247</v>
       </c>
-      <c r="B1" s="207"/>
-      <c r="C1" s="207"/>
-      <c r="D1" s="208"/>
+      <c r="B1" s="206"/>
+      <c r="C1" s="206"/>
+      <c r="D1" s="207"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="132"/>
-      <c r="B2" s="129"/>
-      <c r="C2" s="129"/>
-      <c r="D2" s="142"/>
+      <c r="A2" s="131"/>
+      <c r="B2" s="128"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="141"/>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
-      <c r="A3" s="242" t="s">
+      <c r="A3" s="241" t="s">
         <v>248</v>
       </c>
-      <c r="B3" s="243"/>
-      <c r="C3" s="243"/>
-      <c r="D3" s="244"/>
+      <c r="B3" s="242"/>
+      <c r="C3" s="242"/>
+      <c r="D3" s="243"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="133" t="s">
+      <c r="A4" s="132" t="s">
         <v>249</v>
       </c>
       <c r="B4" s="12" t="s">
@@ -19082,26 +18921,26 @@
       <c r="C4" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="D4" s="143" t="s">
+      <c r="D4" s="142" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" customHeight="1">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="133" t="s">
         <v>252</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>952</v>
+        <v>939</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>953</v>
-      </c>
-      <c r="D5" s="144" t="s">
-        <v>954</v>
+        <v>940</v>
+      </c>
+      <c r="D5" s="143" t="s">
+        <v>941</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A6" s="135" t="s">
+      <c r="A6" s="134" t="s">
         <v>253</v>
       </c>
       <c r="B6" s="34" t="s">
@@ -19110,12 +18949,12 @@
       <c r="C6" s="35" t="s">
         <v>255</v>
       </c>
-      <c r="D6" s="145" t="s">
+      <c r="D6" s="144" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A7" s="136" t="s">
+      <c r="A7" s="135" t="s">
         <v>257</v>
       </c>
       <c r="B7" s="37" t="s">
@@ -19124,26 +18963,26 @@
       <c r="C7" s="38" t="s">
         <v>259</v>
       </c>
-      <c r="D7" s="146" t="s">
+      <c r="D7" s="145" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1">
-      <c r="A8" s="137" t="s">
+      <c r="A8" s="136" t="s">
         <v>261</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>787</v>
+        <v>774</v>
       </c>
       <c r="C8" s="41" t="s">
         <v>262</v>
       </c>
-      <c r="D8" s="147" t="s">
+      <c r="D8" s="146" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A9" s="138" t="s">
+      <c r="A9" s="137" t="s">
         <v>264</v>
       </c>
       <c r="B9" s="43" t="s">
@@ -19152,82 +18991,82 @@
       <c r="C9" s="44" t="s">
         <v>266</v>
       </c>
-      <c r="D9" s="148" t="s">
+      <c r="D9" s="147" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="45" customHeight="1">
-      <c r="A10" s="138" t="s">
-        <v>712</v>
+      <c r="A10" s="137" t="s">
+        <v>700</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>977</v>
+        <v>963</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>978</v>
-      </c>
-      <c r="D10" s="148" t="s">
-        <v>979</v>
+        <v>964</v>
+      </c>
+      <c r="D10" s="147" t="s">
+        <v>965</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="45" customHeight="1">
-      <c r="A11" s="138" t="s">
+      <c r="A11" s="137" t="s">
         <v>264</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>980</v>
+        <v>966</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>981</v>
-      </c>
-      <c r="D11" s="148" t="s">
-        <v>982</v>
+        <v>967</v>
+      </c>
+      <c r="D11" s="147" t="s">
+        <v>968</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="45" customHeight="1">
-      <c r="A12" s="138" t="s">
+      <c r="A12" s="137" t="s">
         <v>253</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>983</v>
+        <v>969</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>984</v>
-      </c>
-      <c r="D12" s="148" t="s">
-        <v>985</v>
+        <v>970</v>
+      </c>
+      <c r="D12" s="147" t="s">
+        <v>971</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="45" customHeight="1">
-      <c r="A13" s="138" t="s">
+      <c r="A13" s="137" t="s">
         <v>288</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>986</v>
+        <v>972</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>987</v>
-      </c>
-      <c r="D13" s="148" t="s">
-        <v>988</v>
+        <v>973</v>
+      </c>
+      <c r="D13" s="147" t="s">
+        <v>974</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1">
-      <c r="A14" s="132"/>
-      <c r="B14" s="129"/>
-      <c r="C14" s="129"/>
-      <c r="D14" s="142"/>
+      <c r="A14" s="131"/>
+      <c r="B14" s="128"/>
+      <c r="C14" s="128"/>
+      <c r="D14" s="141"/>
     </row>
     <row r="15" spans="1:4" ht="16">
-      <c r="A15" s="245" t="s">
+      <c r="A15" s="244" t="s">
         <v>268</v>
       </c>
-      <c r="B15" s="246"/>
-      <c r="C15" s="246"/>
-      <c r="D15" s="247"/>
+      <c r="B15" s="245"/>
+      <c r="C15" s="245"/>
+      <c r="D15" s="246"/>
     </row>
     <row r="16" spans="1:4" ht="24" customHeight="1">
-      <c r="A16" s="133" t="s">
+      <c r="A16" s="132" t="s">
         <v>249</v>
       </c>
       <c r="B16" s="12" t="s">
@@ -19236,12 +19075,12 @@
       <c r="C16" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="D16" s="143" t="s">
+      <c r="D16" s="142" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="70">
-      <c r="A17" s="135" t="s">
+      <c r="A17" s="134" t="s">
         <v>253</v>
       </c>
       <c r="B17" s="34" t="s">
@@ -19250,12 +19089,12 @@
       <c r="C17" s="35" t="s">
         <v>270</v>
       </c>
-      <c r="D17" s="185" t="s">
-        <v>1013</v>
+      <c r="D17" s="184" t="s">
+        <v>999</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1">
-      <c r="A18" s="136" t="s">
+      <c r="A18" s="135" t="s">
         <v>257</v>
       </c>
       <c r="B18" s="37" t="s">
@@ -19264,12 +19103,12 @@
       <c r="C18" s="38" t="s">
         <v>208</v>
       </c>
-      <c r="D18" s="146" t="s">
+      <c r="D18" s="145" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A19" s="136" t="s">
+      <c r="A19" s="135" t="s">
         <v>273</v>
       </c>
       <c r="B19" s="45" t="s">
@@ -19278,12 +19117,12 @@
       <c r="C19" s="38" t="s">
         <v>275</v>
       </c>
-      <c r="D19" s="146" t="s">
+      <c r="D19" s="145" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="30" customHeight="1">
-      <c r="A20" s="137" t="s">
+      <c r="A20" s="136" t="s">
         <v>278</v>
       </c>
       <c r="B20" s="40" t="s">
@@ -19292,12 +19131,12 @@
       <c r="C20" s="41" t="s">
         <v>280</v>
       </c>
-      <c r="D20" s="147" t="s">
+      <c r="D20" s="146" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="30" customHeight="1">
-      <c r="A21" s="134" t="s">
+      <c r="A21" s="133" t="s">
         <v>252</v>
       </c>
       <c r="B21" s="31" t="s">
@@ -19306,54 +19145,54 @@
       <c r="C21" s="32" t="s">
         <v>283</v>
       </c>
-      <c r="D21" s="144" t="s">
+      <c r="D21" s="143" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="30" customHeight="1">
-      <c r="A22" s="139" t="s">
+      <c r="A22" s="138" t="s">
         <v>277</v>
       </c>
       <c r="B22" s="92" t="s">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="C22" s="92" t="s">
-        <v>710</v>
-      </c>
-      <c r="D22" s="125" t="s">
-        <v>711</v>
+        <v>698</v>
+      </c>
+      <c r="D22" s="124" t="s">
+        <v>699</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="30" customHeight="1">
-      <c r="A23" s="140" t="s">
-        <v>712</v>
+      <c r="A23" s="139" t="s">
+        <v>700</v>
       </c>
       <c r="B23" s="90" t="s">
-        <v>713</v>
+        <v>701</v>
       </c>
       <c r="C23" s="90" t="s">
-        <v>714</v>
-      </c>
-      <c r="D23" s="149" t="s">
-        <v>715</v>
+        <v>702</v>
+      </c>
+      <c r="D23" s="148" t="s">
+        <v>703</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="72" customHeight="1">
-      <c r="A24" s="140" t="s">
-        <v>1109</v>
+      <c r="A24" s="139" t="s">
+        <v>1091</v>
       </c>
       <c r="B24" s="90" t="s">
-        <v>1110</v>
+        <v>1092</v>
       </c>
       <c r="C24" s="90" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D24" s="149" t="s">
-        <v>1112</v>
+        <v>1093</v>
+      </c>
+      <c r="D24" s="148" t="s">
+        <v>1094</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="28">
-      <c r="A25" s="138" t="s">
+      <c r="A25" s="137" t="s">
         <v>264</v>
       </c>
       <c r="B25" s="43" t="s">
@@ -19362,68 +19201,68 @@
       <c r="C25" s="44" t="s">
         <v>286</v>
       </c>
-      <c r="D25" s="148" t="s">
+      <c r="D25" s="147" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="45" customHeight="1">
-      <c r="A26" s="138" t="s">
-        <v>989</v>
+      <c r="A26" s="137" t="s">
+        <v>975</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>990</v>
+        <v>976</v>
       </c>
       <c r="C26" s="44" t="s">
-        <v>991</v>
-      </c>
-      <c r="D26" s="148" t="s">
-        <v>992</v>
+        <v>977</v>
+      </c>
+      <c r="D26" s="147" t="s">
+        <v>978</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="45" customHeight="1">
-      <c r="A27" s="138" t="s">
-        <v>993</v>
+      <c r="A27" s="137" t="s">
+        <v>979</v>
       </c>
       <c r="B27" s="43" t="s">
-        <v>994</v>
+        <v>980</v>
       </c>
       <c r="C27" s="44" t="s">
-        <v>995</v>
-      </c>
-      <c r="D27" s="148" t="s">
-        <v>996</v>
+        <v>981</v>
+      </c>
+      <c r="D27" s="147" t="s">
+        <v>982</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="45" customHeight="1">
-      <c r="A28" s="138" t="s">
+      <c r="A28" s="137" t="s">
         <v>253</v>
       </c>
       <c r="B28" s="43" t="s">
-        <v>997</v>
+        <v>983</v>
       </c>
       <c r="C28" s="44" t="s">
-        <v>998</v>
-      </c>
-      <c r="D28" s="148" t="s">
-        <v>999</v>
+        <v>984</v>
+      </c>
+      <c r="D28" s="147" t="s">
+        <v>985</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="30" customHeight="1">
-      <c r="A29" s="138" t="s">
+      <c r="A29" s="137" t="s">
         <v>252</v>
       </c>
       <c r="B29" s="43" t="s">
-        <v>1000</v>
+        <v>986</v>
       </c>
       <c r="C29" s="44" t="s">
-        <v>1001</v>
-      </c>
-      <c r="D29" s="148" t="s">
-        <v>1002</v>
+        <v>987</v>
+      </c>
+      <c r="D29" s="147" t="s">
+        <v>988</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A30" s="137" t="s">
+      <c r="A30" s="136" t="s">
         <v>288</v>
       </c>
       <c r="B30" s="40" t="s">
@@ -19432,12 +19271,12 @@
       <c r="C30" s="41" t="s">
         <v>290</v>
       </c>
-      <c r="D30" s="147" t="s">
+      <c r="D30" s="146" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="30" customHeight="1">
-      <c r="A31" s="137" t="s">
+      <c r="A31" s="136" t="s">
         <v>288</v>
       </c>
       <c r="B31" s="40" t="s">
@@ -19446,26 +19285,26 @@
       <c r="C31" s="41" t="s">
         <v>293</v>
       </c>
-      <c r="D31" s="147" t="s">
+      <c r="D31" s="146" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="30" customHeight="1">
-      <c r="A32" s="132"/>
-      <c r="B32" s="129"/>
-      <c r="C32" s="129"/>
-      <c r="D32" s="142"/>
+      <c r="A32" s="131"/>
+      <c r="B32" s="128"/>
+      <c r="C32" s="128"/>
+      <c r="D32" s="141"/>
     </row>
     <row r="33" spans="1:4" ht="16">
-      <c r="A33" s="248" t="s">
+      <c r="A33" s="247" t="s">
         <v>295</v>
       </c>
-      <c r="B33" s="249"/>
-      <c r="C33" s="249"/>
-      <c r="D33" s="250"/>
+      <c r="B33" s="248"/>
+      <c r="C33" s="248"/>
+      <c r="D33" s="249"/>
     </row>
     <row r="34" spans="1:4" ht="24" customHeight="1">
-      <c r="A34" s="133" t="s">
+      <c r="A34" s="132" t="s">
         <v>249</v>
       </c>
       <c r="B34" s="12" t="s">
@@ -19474,12 +19313,12 @@
       <c r="C34" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="D34" s="143" t="s">
+      <c r="D34" s="142" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="135" t="s">
+      <c r="A35" s="134" t="s">
         <v>253</v>
       </c>
       <c r="B35" s="34" t="s">
@@ -19488,12 +19327,12 @@
       <c r="C35" s="35" t="s">
         <v>239</v>
       </c>
-      <c r="D35" s="145" t="s">
+      <c r="D35" s="144" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A36" s="136" t="s">
+      <c r="A36" s="135" t="s">
         <v>257</v>
       </c>
       <c r="B36" s="37" t="s">
@@ -19502,12 +19341,12 @@
       <c r="C36" s="38" t="s">
         <v>240</v>
       </c>
-      <c r="D36" s="146" t="s">
+      <c r="D36" s="145" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="30" customHeight="1">
-      <c r="A37" s="134" t="s">
+      <c r="A37" s="133" t="s">
         <v>252</v>
       </c>
       <c r="B37" s="31" t="s">
@@ -19516,12 +19355,12 @@
       <c r="C37" s="32" t="s">
         <v>301</v>
       </c>
-      <c r="D37" s="144" t="s">
+      <c r="D37" s="143" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A38" s="138" t="s">
+      <c r="A38" s="137" t="s">
         <v>264</v>
       </c>
       <c r="B38" s="43" t="s">
@@ -19530,12 +19369,12 @@
       <c r="C38" s="44" t="s">
         <v>304</v>
       </c>
-      <c r="D38" s="148" t="s">
+      <c r="D38" s="147" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="45" customHeight="1">
-      <c r="A39" s="138" t="s">
+      <c r="A39" s="137" t="s">
         <v>264</v>
       </c>
       <c r="B39" s="43" t="s">
@@ -19544,54 +19383,54 @@
       <c r="C39" s="44" t="s">
         <v>245</v>
       </c>
-      <c r="D39" s="148" t="s">
+      <c r="D39" s="147" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="45" customHeight="1">
-      <c r="A40" s="138" t="s">
-        <v>712</v>
+      <c r="A40" s="137" t="s">
+        <v>700</v>
       </c>
       <c r="B40" s="43" t="s">
-        <v>1003</v>
+        <v>989</v>
       </c>